--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="285">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -619,6 +619,9 @@
     <t>['8', '37', '66']</t>
   </si>
   <si>
+    <t>['43']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -805,9 +808,6 @@
     <t>['20', '63']</t>
   </si>
   <si>
-    <t>['43']</t>
-  </si>
-  <si>
     <t>['30', '51']</t>
   </si>
   <si>
@@ -866,6 +866,9 @@
   </si>
   <si>
     <t>['63']</t>
+  </si>
+  <si>
+    <t>['35', '82', '90+2']</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP185"/>
+  <dimension ref="A1:BP187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1483,7 +1486,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1767,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ3">
         <v>1.33</v>
@@ -2307,7 +2310,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q6">
         <v>2.25</v>
@@ -2513,7 +2516,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2594,7 +2597,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ7">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2719,7 +2722,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3337,7 +3340,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3415,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ11">
         <v>1.83</v>
@@ -3543,7 +3546,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3749,7 +3752,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3955,7 +3958,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4161,7 +4164,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4367,7 +4370,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4779,7 +4782,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -4857,7 +4860,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ18">
         <v>1.08</v>
@@ -4985,7 +4988,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5191,7 +5194,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5478,7 +5481,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ21">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -5603,7 +5606,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5809,7 +5812,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -7251,7 +7254,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7457,7 +7460,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7535,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -7663,7 +7666,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7869,7 +7872,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8075,7 +8078,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8153,7 +8156,7 @@
         <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ34">
         <v>0.5</v>
@@ -8281,7 +8284,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8487,7 +8490,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q36">
         <v>4</v>
@@ -8693,7 +8696,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9311,7 +9314,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9392,7 +9395,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ40">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9517,7 +9520,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9595,7 +9598,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
         <v>1.27</v>
@@ -9723,7 +9726,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10422,7 +10425,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ45">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR45">
         <v>1.51</v>
@@ -10753,7 +10756,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11165,7 +11168,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -12067,7 +12070,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ53">
         <v>1.83</v>
@@ -12195,7 +12198,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12401,7 +12404,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12813,7 +12816,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -12891,7 +12894,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ57">
         <v>0.45</v>
@@ -13225,7 +13228,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13431,7 +13434,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13843,7 +13846,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13921,7 +13924,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ62">
         <v>0.45</v>
@@ -14130,7 +14133,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ63">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -14873,7 +14876,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15285,7 +15288,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15491,7 +15494,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15697,7 +15700,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15903,7 +15906,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16190,7 +16193,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ73">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR73">
         <v>1.51</v>
@@ -16393,7 +16396,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ74">
         <v>1.64</v>
@@ -16521,7 +16524,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16727,7 +16730,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16933,7 +16936,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17345,7 +17348,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17423,7 +17426,7 @@
         <v>1.2</v>
       </c>
       <c r="AP79">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ79">
         <v>1.09</v>
@@ -17757,7 +17760,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18169,7 +18172,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18787,7 +18790,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19486,7 +19489,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ89">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR89">
         <v>1.6</v>
@@ -19611,7 +19614,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19689,7 +19692,7 @@
         <v>1.71</v>
       </c>
       <c r="AP90">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ90">
         <v>1.5</v>
@@ -19817,7 +19820,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20023,7 +20026,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20229,7 +20232,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20307,7 +20310,7 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ93">
         <v>1.09</v>
@@ -20641,7 +20644,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -21877,7 +21880,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22495,7 +22498,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -23113,7 +23116,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23191,10 +23194,10 @@
         <v>0.71</v>
       </c>
       <c r="AP107">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ107">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR107">
         <v>1.21</v>
@@ -23319,7 +23322,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23731,7 +23734,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23937,7 +23940,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24143,7 +24146,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24349,7 +24352,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24761,7 +24764,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -25173,7 +25176,7 @@
         <v>127</v>
       </c>
       <c r="P117" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q117">
         <v>2.88</v>
@@ -25457,7 +25460,7 @@
         <v>0.71</v>
       </c>
       <c r="AP118">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ118">
         <v>0.5</v>
@@ -25997,7 +26000,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26203,7 +26206,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26821,7 +26824,7 @@
         <v>86</v>
       </c>
       <c r="P125" t="s">
-        <v>263</v>
+        <v>201</v>
       </c>
       <c r="Q125">
         <v>3.3</v>
@@ -26899,7 +26902,7 @@
         <v>0.57</v>
       </c>
       <c r="AP125">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ125">
         <v>0.83</v>
@@ -28057,7 +28060,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28263,7 +28266,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28341,7 +28344,7 @@
         <v>1.78</v>
       </c>
       <c r="AP132">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ132">
         <v>1.5</v>
@@ -28962,7 +28965,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ135">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR135">
         <v>1.36</v>
@@ -29989,7 +29992,7 @@
         <v>0.13</v>
       </c>
       <c r="AP140">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ140">
         <v>0.92</v>
@@ -30529,7 +30532,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30735,7 +30738,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -31434,7 +31437,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ147">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR147">
         <v>1.41</v>
@@ -31559,7 +31562,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -32461,7 +32464,7 @@
         <v>1.44</v>
       </c>
       <c r="AP152">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ152">
         <v>1.08</v>
@@ -33903,7 +33906,7 @@
         <v>1.78</v>
       </c>
       <c r="AP159">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ159">
         <v>1.64</v>
@@ -34727,7 +34730,7 @@
         <v>0.9</v>
       </c>
       <c r="AP163">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ163">
         <v>0.83</v>
@@ -36169,7 +36172,7 @@
         <v>1.2</v>
       </c>
       <c r="AP170">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ170">
         <v>1.09</v>
@@ -36297,7 +36300,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36915,7 +36918,7 @@
         <v>195</v>
       </c>
       <c r="P174" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q174">
         <v>4.7</v>
@@ -37202,7 +37205,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ175">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR175">
         <v>1.78</v>
@@ -39338,6 +39341,418 @@
       </c>
       <c r="BP185">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7486680</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45688.5</v>
+      </c>
+      <c r="F186">
+        <v>24</v>
+      </c>
+      <c r="G186" t="s">
+        <v>71</v>
+      </c>
+      <c r="H186" t="s">
+        <v>73</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186">
+        <v>0</v>
+      </c>
+      <c r="N186">
+        <v>0</v>
+      </c>
+      <c r="O186" t="s">
+        <v>86</v>
+      </c>
+      <c r="P186" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q186">
+        <v>2.9</v>
+      </c>
+      <c r="R186">
+        <v>1.96</v>
+      </c>
+      <c r="S186">
+        <v>4</v>
+      </c>
+      <c r="T186">
+        <v>1.56</v>
+      </c>
+      <c r="U186">
+        <v>2.3</v>
+      </c>
+      <c r="V186">
+        <v>3.3</v>
+      </c>
+      <c r="W186">
+        <v>1.28</v>
+      </c>
+      <c r="X186">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y186">
+        <v>1.04</v>
+      </c>
+      <c r="Z186">
+        <v>2.26</v>
+      </c>
+      <c r="AA186">
+        <v>3</v>
+      </c>
+      <c r="AB186">
+        <v>3.37</v>
+      </c>
+      <c r="AC186">
+        <v>1.08</v>
+      </c>
+      <c r="AD186">
+        <v>7</v>
+      </c>
+      <c r="AE186">
+        <v>1.44</v>
+      </c>
+      <c r="AF186">
+        <v>2.7</v>
+      </c>
+      <c r="AG186">
+        <v>2.24</v>
+      </c>
+      <c r="AH186">
+        <v>1.55</v>
+      </c>
+      <c r="AI186">
+        <v>1.95</v>
+      </c>
+      <c r="AJ186">
+        <v>1.74</v>
+      </c>
+      <c r="AK186">
+        <v>1.3</v>
+      </c>
+      <c r="AL186">
+        <v>1.32</v>
+      </c>
+      <c r="AM186">
+        <v>1.53</v>
+      </c>
+      <c r="AN186">
+        <v>1.73</v>
+      </c>
+      <c r="AO186">
+        <v>1</v>
+      </c>
+      <c r="AP186">
+        <v>1.67</v>
+      </c>
+      <c r="AQ186">
+        <v>1</v>
+      </c>
+      <c r="AR186">
+        <v>1.23</v>
+      </c>
+      <c r="AS186">
+        <v>1.2</v>
+      </c>
+      <c r="AT186">
+        <v>2.43</v>
+      </c>
+      <c r="AU186">
+        <v>2</v>
+      </c>
+      <c r="AV186">
+        <v>4</v>
+      </c>
+      <c r="AW186">
+        <v>10</v>
+      </c>
+      <c r="AX186">
+        <v>15</v>
+      </c>
+      <c r="AY186">
+        <v>12</v>
+      </c>
+      <c r="AZ186">
+        <v>23</v>
+      </c>
+      <c r="BA186">
+        <v>2</v>
+      </c>
+      <c r="BB186">
+        <v>1</v>
+      </c>
+      <c r="BC186">
+        <v>3</v>
+      </c>
+      <c r="BD186">
+        <v>1.76</v>
+      </c>
+      <c r="BE186">
+        <v>6.4</v>
+      </c>
+      <c r="BF186">
+        <v>2.3</v>
+      </c>
+      <c r="BG186">
+        <v>1.52</v>
+      </c>
+      <c r="BH186">
+        <v>2.3</v>
+      </c>
+      <c r="BI186">
+        <v>1.87</v>
+      </c>
+      <c r="BJ186">
+        <v>1.79</v>
+      </c>
+      <c r="BK186">
+        <v>2.4</v>
+      </c>
+      <c r="BL186">
+        <v>1.48</v>
+      </c>
+      <c r="BM186">
+        <v>3.15</v>
+      </c>
+      <c r="BN186">
+        <v>1.29</v>
+      </c>
+      <c r="BO186">
+        <v>4.35</v>
+      </c>
+      <c r="BP186">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7486988</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45688.625</v>
+      </c>
+      <c r="F187">
+        <v>24</v>
+      </c>
+      <c r="G187" t="s">
+        <v>79</v>
+      </c>
+      <c r="H187" t="s">
+        <v>83</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+      <c r="J187">
+        <v>1</v>
+      </c>
+      <c r="K187">
+        <v>2</v>
+      </c>
+      <c r="L187">
+        <v>1</v>
+      </c>
+      <c r="M187">
+        <v>3</v>
+      </c>
+      <c r="N187">
+        <v>4</v>
+      </c>
+      <c r="O187" t="s">
+        <v>201</v>
+      </c>
+      <c r="P187" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q187">
+        <v>3.85</v>
+      </c>
+      <c r="R187">
+        <v>1.99</v>
+      </c>
+      <c r="S187">
+        <v>2.9</v>
+      </c>
+      <c r="T187">
+        <v>1.54</v>
+      </c>
+      <c r="U187">
+        <v>2.36</v>
+      </c>
+      <c r="V187">
+        <v>3.2</v>
+      </c>
+      <c r="W187">
+        <v>1.3</v>
+      </c>
+      <c r="X187">
+        <v>10.5</v>
+      </c>
+      <c r="Y187">
+        <v>1.03</v>
+      </c>
+      <c r="Z187">
+        <v>3.22</v>
+      </c>
+      <c r="AA187">
+        <v>3</v>
+      </c>
+      <c r="AB187">
+        <v>2.32</v>
+      </c>
+      <c r="AC187">
+        <v>1.07</v>
+      </c>
+      <c r="AD187">
+        <v>7.5</v>
+      </c>
+      <c r="AE187">
+        <v>1.41</v>
+      </c>
+      <c r="AF187">
+        <v>2.8</v>
+      </c>
+      <c r="AG187">
+        <v>2.22</v>
+      </c>
+      <c r="AH187">
+        <v>1.56</v>
+      </c>
+      <c r="AI187">
+        <v>1.89</v>
+      </c>
+      <c r="AJ187">
+        <v>1.79</v>
+      </c>
+      <c r="AK187">
+        <v>1.52</v>
+      </c>
+      <c r="AL187">
+        <v>1.32</v>
+      </c>
+      <c r="AM187">
+        <v>1.31</v>
+      </c>
+      <c r="AN187">
+        <v>1.09</v>
+      </c>
+      <c r="AO187">
+        <v>1.36</v>
+      </c>
+      <c r="AP187">
+        <v>1</v>
+      </c>
+      <c r="AQ187">
+        <v>1.5</v>
+      </c>
+      <c r="AR187">
+        <v>1.38</v>
+      </c>
+      <c r="AS187">
+        <v>1.13</v>
+      </c>
+      <c r="AT187">
+        <v>2.51</v>
+      </c>
+      <c r="AU187">
+        <v>4</v>
+      </c>
+      <c r="AV187">
+        <v>7</v>
+      </c>
+      <c r="AW187">
+        <v>5</v>
+      </c>
+      <c r="AX187">
+        <v>8</v>
+      </c>
+      <c r="AY187">
+        <v>9</v>
+      </c>
+      <c r="AZ187">
+        <v>18</v>
+      </c>
+      <c r="BA187">
+        <v>1</v>
+      </c>
+      <c r="BB187">
+        <v>9</v>
+      </c>
+      <c r="BC187">
+        <v>10</v>
+      </c>
+      <c r="BD187">
+        <v>2.12</v>
+      </c>
+      <c r="BE187">
+        <v>6.25</v>
+      </c>
+      <c r="BF187">
+        <v>1.9</v>
+      </c>
+      <c r="BG187">
+        <v>1.47</v>
+      </c>
+      <c r="BH187">
+        <v>2.43</v>
+      </c>
+      <c r="BI187">
+        <v>1.81</v>
+      </c>
+      <c r="BJ187">
+        <v>1.85</v>
+      </c>
+      <c r="BK187">
+        <v>2.3</v>
+      </c>
+      <c r="BL187">
+        <v>1.52</v>
+      </c>
+      <c r="BM187">
+        <v>3.05</v>
+      </c>
+      <c r="BN187">
+        <v>1.3</v>
+      </c>
+      <c r="BO187">
+        <v>4.1</v>
+      </c>
+      <c r="BP187">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="287">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -620,6 +620,12 @@
   </si>
   <si>
     <t>['43']</t>
+  </si>
+  <si>
+    <t>['7', '71']</t>
+  </si>
+  <si>
+    <t>['20', '79']</t>
   </si>
   <si>
     <t>['19']</t>
@@ -1230,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP187"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1486,7 +1492,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -2185,7 +2191,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ5">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2310,7 +2316,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q6">
         <v>2.25</v>
@@ -2516,7 +2522,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2722,7 +2728,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2800,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ8">
         <v>1.08</v>
@@ -3009,7 +3015,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ9">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3340,7 +3346,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3546,7 +3552,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3752,7 +3758,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3958,7 +3964,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4036,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ14">
         <v>0.92</v>
@@ -4164,7 +4170,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4370,7 +4376,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4451,7 +4457,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ16">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4654,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ17">
         <v>0.83</v>
@@ -4782,7 +4788,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -4988,7 +4994,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5194,7 +5200,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5275,7 +5281,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ20">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR20">
         <v>1.45</v>
@@ -5606,7 +5612,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5812,7 +5818,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6305,7 +6311,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ25">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>0.95</v>
@@ -6508,7 +6514,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ26">
         <v>0.92</v>
@@ -6717,7 +6723,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ27">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR27">
         <v>1</v>
@@ -7254,7 +7260,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7460,7 +7466,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7666,7 +7672,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7747,7 +7753,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ32">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR32">
         <v>1.69</v>
@@ -7872,7 +7878,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8078,7 +8084,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8284,7 +8290,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8490,7 +8496,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q36">
         <v>4</v>
@@ -8571,7 +8577,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ36">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>1.67</v>
@@ -8696,7 +8702,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9314,7 +9320,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9520,7 +9526,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9726,7 +9732,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -9807,7 +9813,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ42">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR42">
         <v>1.69</v>
@@ -10010,7 +10016,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -10628,10 +10634,10 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ46">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR46">
         <v>1.57</v>
@@ -10756,7 +10762,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11168,7 +11174,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11249,7 +11255,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ49">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR49">
         <v>1.48</v>
@@ -12198,7 +12204,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12404,7 +12410,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12688,10 +12694,10 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ56">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR56">
         <v>1.46</v>
@@ -12816,7 +12822,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13103,7 +13109,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ58">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR58">
         <v>2.03</v>
@@ -13228,7 +13234,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13306,7 +13312,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ59">
         <v>1.27</v>
@@ -13434,7 +13440,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13846,7 +13852,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13927,7 +13933,7 @@
         <v>1</v>
       </c>
       <c r="AQ62">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR62">
         <v>1.4</v>
@@ -14130,7 +14136,7 @@
         <v>0.75</v>
       </c>
       <c r="AP63">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ63">
         <v>1.5</v>
@@ -14876,7 +14882,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15288,7 +15294,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15494,7 +15500,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15700,7 +15706,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15906,7 +15912,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -15984,10 +15990,10 @@
         <v>0.8</v>
       </c>
       <c r="AP72">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ72">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR72">
         <v>1.78</v>
@@ -16190,7 +16196,7 @@
         <v>0.6</v>
       </c>
       <c r="AP73">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ73">
         <v>1.5</v>
@@ -16524,7 +16530,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16730,7 +16736,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16811,7 +16817,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ76">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR76">
         <v>1.67</v>
@@ -16936,7 +16942,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17014,7 +17020,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ77">
         <v>1.33</v>
@@ -17348,7 +17354,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17429,7 +17435,7 @@
         <v>1</v>
       </c>
       <c r="AQ79">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR79">
         <v>1.52</v>
@@ -17760,7 +17766,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18172,7 +18178,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18790,7 +18796,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19614,7 +19620,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19820,7 +19826,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20026,7 +20032,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20104,7 +20110,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ92">
         <v>1.33</v>
@@ -20232,7 +20238,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20313,7 +20319,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ93">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR93">
         <v>1.25</v>
@@ -20516,10 +20522,10 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ94">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.89</v>
@@ -20644,7 +20650,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20725,7 +20731,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ95">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR95">
         <v>1.89</v>
@@ -21134,7 +21140,7 @@
         <v>1.67</v>
       </c>
       <c r="AP97">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ97">
         <v>1.08</v>
@@ -21880,7 +21886,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22498,7 +22504,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22579,7 +22585,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ104">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR104">
         <v>1.78</v>
@@ -22785,7 +22791,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ105">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR105">
         <v>1.58</v>
@@ -23116,7 +23122,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23322,7 +23328,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23400,7 +23406,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ108">
         <v>1.08</v>
@@ -23609,7 +23615,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ109">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR109">
         <v>2.02</v>
@@ -23734,7 +23740,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23812,7 +23818,7 @@
         <v>1.63</v>
       </c>
       <c r="AP110">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ110">
         <v>1.5</v>
@@ -23940,7 +23946,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24146,7 +24152,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24352,7 +24358,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24764,7 +24770,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -25048,7 +25054,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ116">
         <v>0.83</v>
@@ -25176,7 +25182,7 @@
         <v>127</v>
       </c>
       <c r="P117" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q117">
         <v>2.88</v>
@@ -25872,7 +25878,7 @@
         <v>0.63</v>
       </c>
       <c r="AP120">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ120">
         <v>0.5</v>
@@ -26000,7 +26006,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26206,7 +26212,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26287,7 +26293,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ122">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR122">
         <v>1.54</v>
@@ -27030,7 +27036,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27108,7 +27114,7 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ126">
         <v>1.83</v>
@@ -27520,7 +27526,7 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ128">
         <v>1.64</v>
@@ -27726,7 +27732,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ129">
         <v>1.83</v>
@@ -27935,7 +27941,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ130">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR130">
         <v>1.47</v>
@@ -28060,7 +28066,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28266,7 +28272,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28472,7 +28478,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28553,7 +28559,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ133">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR133">
         <v>1.85</v>
@@ -29168,7 +29174,7 @@
         <v>0.57</v>
       </c>
       <c r="AP136">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ136">
         <v>0.45</v>
@@ -29296,7 +29302,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29580,7 +29586,7 @@
         <v>0.88</v>
       </c>
       <c r="AP138">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ138">
         <v>0.83</v>
@@ -29914,7 +29920,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30326,7 +30332,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30407,7 +30413,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ142">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR142">
         <v>1.14</v>
@@ -30532,7 +30538,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30738,7 +30744,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30816,7 +30822,7 @@
         <v>0.75</v>
       </c>
       <c r="AP144">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ144">
         <v>1</v>
@@ -30944,7 +30950,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31022,7 +31028,7 @@
         <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ145">
         <v>1.83</v>
@@ -31231,7 +31237,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ146">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR146">
         <v>1.46</v>
@@ -31356,7 +31362,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31562,7 +31568,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31768,7 +31774,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -31974,7 +31980,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32592,7 +32598,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32670,7 +32676,7 @@
         <v>2</v>
       </c>
       <c r="AP153">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ153">
         <v>1.64</v>
@@ -32798,7 +32804,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -32876,7 +32882,7 @@
         <v>0.44</v>
       </c>
       <c r="AP154">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ154">
         <v>0.92</v>
@@ -33288,7 +33294,7 @@
         <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ156">
         <v>1</v>
@@ -33416,7 +33422,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33497,7 +33503,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ157">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR157">
         <v>1.79</v>
@@ -33622,7 +33628,7 @@
         <v>187</v>
       </c>
       <c r="P158" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q158">
         <v>2.63</v>
@@ -33700,7 +33706,7 @@
         <v>1.44</v>
       </c>
       <c r="AP158">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ158">
         <v>1.27</v>
@@ -34321,7 +34327,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ161">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR161">
         <v>1.54</v>
@@ -34858,7 +34864,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35270,7 +35276,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35557,7 +35563,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ167">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR167">
         <v>1.24</v>
@@ -35888,7 +35894,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36094,7 +36100,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36175,7 +36181,7 @@
         <v>1</v>
       </c>
       <c r="AQ170">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR170">
         <v>1.38</v>
@@ -36300,7 +36306,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36506,7 +36512,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36584,10 +36590,10 @@
         <v>0.5</v>
       </c>
       <c r="AP172">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ172">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR172">
         <v>1.54</v>
@@ -36790,7 +36796,7 @@
         <v>1.3</v>
       </c>
       <c r="AP173">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ173">
         <v>1.27</v>
@@ -36918,7 +36924,7 @@
         <v>195</v>
       </c>
       <c r="P174" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q174">
         <v>4.7</v>
@@ -36996,7 +37002,7 @@
         <v>1.7</v>
       </c>
       <c r="AP174">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ174">
         <v>1.64</v>
@@ -37536,7 +37542,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -38154,7 +38160,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38772,7 +38778,7 @@
         <v>86</v>
       </c>
       <c r="P183" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q183">
         <v>5.2</v>
@@ -39596,7 +39602,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -39753,6 +39759,624 @@
       </c>
       <c r="BP187">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7486675</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45689.39583333334</v>
+      </c>
+      <c r="F188">
+        <v>24</v>
+      </c>
+      <c r="G188" t="s">
+        <v>76</v>
+      </c>
+      <c r="H188" t="s">
+        <v>72</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
+      </c>
+      <c r="M188">
+        <v>0</v>
+      </c>
+      <c r="N188">
+        <v>0</v>
+      </c>
+      <c r="O188" t="s">
+        <v>86</v>
+      </c>
+      <c r="P188" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q188">
+        <v>3.65</v>
+      </c>
+      <c r="R188">
+        <v>2.01</v>
+      </c>
+      <c r="S188">
+        <v>2.95</v>
+      </c>
+      <c r="T188">
+        <v>1.51</v>
+      </c>
+      <c r="U188">
+        <v>2.4</v>
+      </c>
+      <c r="V188">
+        <v>3.2</v>
+      </c>
+      <c r="W188">
+        <v>1.32</v>
+      </c>
+      <c r="X188">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y188">
+        <v>1.05</v>
+      </c>
+      <c r="Z188">
+        <v>2.94</v>
+      </c>
+      <c r="AA188">
+        <v>3.15</v>
+      </c>
+      <c r="AB188">
+        <v>2.42</v>
+      </c>
+      <c r="AC188">
+        <v>1.02</v>
+      </c>
+      <c r="AD188">
+        <v>7.8</v>
+      </c>
+      <c r="AE188">
+        <v>1.38</v>
+      </c>
+      <c r="AF188">
+        <v>2.9</v>
+      </c>
+      <c r="AG188">
+        <v>2.1</v>
+      </c>
+      <c r="AH188">
+        <v>1.6</v>
+      </c>
+      <c r="AI188">
+        <v>1.82</v>
+      </c>
+      <c r="AJ188">
+        <v>1.85</v>
+      </c>
+      <c r="AK188">
+        <v>1.47</v>
+      </c>
+      <c r="AL188">
+        <v>1.33</v>
+      </c>
+      <c r="AM188">
+        <v>1.34</v>
+      </c>
+      <c r="AN188">
+        <v>1.18</v>
+      </c>
+      <c r="AO188">
+        <v>1.09</v>
+      </c>
+      <c r="AP188">
+        <v>1.17</v>
+      </c>
+      <c r="AQ188">
+        <v>1.08</v>
+      </c>
+      <c r="AR188">
+        <v>1.69</v>
+      </c>
+      <c r="AS188">
+        <v>1.56</v>
+      </c>
+      <c r="AT188">
+        <v>3.25</v>
+      </c>
+      <c r="AU188">
+        <v>10</v>
+      </c>
+      <c r="AV188">
+        <v>5</v>
+      </c>
+      <c r="AW188">
+        <v>12</v>
+      </c>
+      <c r="AX188">
+        <v>3</v>
+      </c>
+      <c r="AY188">
+        <v>26</v>
+      </c>
+      <c r="AZ188">
+        <v>10</v>
+      </c>
+      <c r="BA188">
+        <v>9</v>
+      </c>
+      <c r="BB188">
+        <v>3</v>
+      </c>
+      <c r="BC188">
+        <v>12</v>
+      </c>
+      <c r="BD188">
+        <v>2.17</v>
+      </c>
+      <c r="BE188">
+        <v>6.4</v>
+      </c>
+      <c r="BF188">
+        <v>1.84</v>
+      </c>
+      <c r="BG188">
+        <v>1.45</v>
+      </c>
+      <c r="BH188">
+        <v>2.48</v>
+      </c>
+      <c r="BI188">
+        <v>1.77</v>
+      </c>
+      <c r="BJ188">
+        <v>1.9</v>
+      </c>
+      <c r="BK188">
+        <v>2.23</v>
+      </c>
+      <c r="BL188">
+        <v>1.56</v>
+      </c>
+      <c r="BM188">
+        <v>2.9</v>
+      </c>
+      <c r="BN188">
+        <v>1.34</v>
+      </c>
+      <c r="BO188">
+        <v>3.9</v>
+      </c>
+      <c r="BP188">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7486676</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F189">
+        <v>24</v>
+      </c>
+      <c r="G189" t="s">
+        <v>85</v>
+      </c>
+      <c r="H189" t="s">
+        <v>84</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="J189">
+        <v>1</v>
+      </c>
+      <c r="K189">
+        <v>2</v>
+      </c>
+      <c r="L189">
+        <v>2</v>
+      </c>
+      <c r="M189">
+        <v>1</v>
+      </c>
+      <c r="N189">
+        <v>3</v>
+      </c>
+      <c r="O189" t="s">
+        <v>202</v>
+      </c>
+      <c r="P189" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q189">
+        <v>2.7</v>
+      </c>
+      <c r="R189">
+        <v>2.03</v>
+      </c>
+      <c r="S189">
+        <v>4.1</v>
+      </c>
+      <c r="T189">
+        <v>1.51</v>
+      </c>
+      <c r="U189">
+        <v>2.4</v>
+      </c>
+      <c r="V189">
+        <v>3.2</v>
+      </c>
+      <c r="W189">
+        <v>1.32</v>
+      </c>
+      <c r="X189">
+        <v>8.9</v>
+      </c>
+      <c r="Y189">
+        <v>1.04</v>
+      </c>
+      <c r="Z189">
+        <v>2.14</v>
+      </c>
+      <c r="AA189">
+        <v>3.26</v>
+      </c>
+      <c r="AB189">
+        <v>3.39</v>
+      </c>
+      <c r="AC189">
+        <v>1.02</v>
+      </c>
+      <c r="AD189">
+        <v>7.8</v>
+      </c>
+      <c r="AE189">
+        <v>1.53</v>
+      </c>
+      <c r="AF189">
+        <v>2.38</v>
+      </c>
+      <c r="AG189">
+        <v>2.4</v>
+      </c>
+      <c r="AH189">
+        <v>1.48</v>
+      </c>
+      <c r="AI189">
+        <v>1.85</v>
+      </c>
+      <c r="AJ189">
+        <v>1.82</v>
+      </c>
+      <c r="AK189">
+        <v>1.27</v>
+      </c>
+      <c r="AL189">
+        <v>1.31</v>
+      </c>
+      <c r="AM189">
+        <v>1.58</v>
+      </c>
+      <c r="AN189">
+        <v>1.09</v>
+      </c>
+      <c r="AO189">
+        <v>0.45</v>
+      </c>
+      <c r="AP189">
+        <v>1.25</v>
+      </c>
+      <c r="AQ189">
+        <v>0.42</v>
+      </c>
+      <c r="AR189">
+        <v>1.34</v>
+      </c>
+      <c r="AS189">
+        <v>1.12</v>
+      </c>
+      <c r="AT189">
+        <v>2.46</v>
+      </c>
+      <c r="AU189">
+        <v>8</v>
+      </c>
+      <c r="AV189">
+        <v>4</v>
+      </c>
+      <c r="AW189">
+        <v>1</v>
+      </c>
+      <c r="AX189">
+        <v>5</v>
+      </c>
+      <c r="AY189">
+        <v>9</v>
+      </c>
+      <c r="AZ189">
+        <v>10</v>
+      </c>
+      <c r="BA189">
+        <v>5</v>
+      </c>
+      <c r="BB189">
+        <v>3</v>
+      </c>
+      <c r="BC189">
+        <v>8</v>
+      </c>
+      <c r="BD189">
+        <v>1.73</v>
+      </c>
+      <c r="BE189">
+        <v>6.4</v>
+      </c>
+      <c r="BF189">
+        <v>2.33</v>
+      </c>
+      <c r="BG189">
+        <v>1.48</v>
+      </c>
+      <c r="BH189">
+        <v>2.4</v>
+      </c>
+      <c r="BI189">
+        <v>1.82</v>
+      </c>
+      <c r="BJ189">
+        <v>1.85</v>
+      </c>
+      <c r="BK189">
+        <v>2.33</v>
+      </c>
+      <c r="BL189">
+        <v>1.5</v>
+      </c>
+      <c r="BM189">
+        <v>3.05</v>
+      </c>
+      <c r="BN189">
+        <v>1.3</v>
+      </c>
+      <c r="BO189">
+        <v>4.1</v>
+      </c>
+      <c r="BP189">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7486679</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45689.625</v>
+      </c>
+      <c r="F190">
+        <v>24</v>
+      </c>
+      <c r="G190" t="s">
+        <v>82</v>
+      </c>
+      <c r="H190" t="s">
+        <v>81</v>
+      </c>
+      <c r="I190">
+        <v>1</v>
+      </c>
+      <c r="J190">
+        <v>1</v>
+      </c>
+      <c r="K190">
+        <v>2</v>
+      </c>
+      <c r="L190">
+        <v>2</v>
+      </c>
+      <c r="M190">
+        <v>1</v>
+      </c>
+      <c r="N190">
+        <v>3</v>
+      </c>
+      <c r="O190" t="s">
+        <v>203</v>
+      </c>
+      <c r="P190" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q190">
+        <v>3</v>
+      </c>
+      <c r="R190">
+        <v>2.05</v>
+      </c>
+      <c r="S190">
+        <v>3.45</v>
+      </c>
+      <c r="T190">
+        <v>1.48</v>
+      </c>
+      <c r="U190">
+        <v>2.45</v>
+      </c>
+      <c r="V190">
+        <v>3.14</v>
+      </c>
+      <c r="W190">
+        <v>1.33</v>
+      </c>
+      <c r="X190">
+        <v>9.1</v>
+      </c>
+      <c r="Y190">
+        <v>1.04</v>
+      </c>
+      <c r="Z190">
+        <v>2.49</v>
+      </c>
+      <c r="AA190">
+        <v>3.25</v>
+      </c>
+      <c r="AB190">
+        <v>2.77</v>
+      </c>
+      <c r="AC190">
+        <v>1.02</v>
+      </c>
+      <c r="AD190">
+        <v>7.8</v>
+      </c>
+      <c r="AE190">
+        <v>1.35</v>
+      </c>
+      <c r="AF190">
+        <v>3.05</v>
+      </c>
+      <c r="AG190">
+        <v>2</v>
+      </c>
+      <c r="AH190">
+        <v>1.75</v>
+      </c>
+      <c r="AI190">
+        <v>1.76</v>
+      </c>
+      <c r="AJ190">
+        <v>1.91</v>
+      </c>
+      <c r="AK190">
+        <v>1.37</v>
+      </c>
+      <c r="AL190">
+        <v>1.32</v>
+      </c>
+      <c r="AM190">
+        <v>1.45</v>
+      </c>
+      <c r="AN190">
+        <v>2.09</v>
+      </c>
+      <c r="AO190">
+        <v>1.09</v>
+      </c>
+      <c r="AP190">
+        <v>2.17</v>
+      </c>
+      <c r="AQ190">
+        <v>1</v>
+      </c>
+      <c r="AR190">
+        <v>1.64</v>
+      </c>
+      <c r="AS190">
+        <v>1.42</v>
+      </c>
+      <c r="AT190">
+        <v>3.06</v>
+      </c>
+      <c r="AU190">
+        <v>6</v>
+      </c>
+      <c r="AV190">
+        <v>4</v>
+      </c>
+      <c r="AW190">
+        <v>5</v>
+      </c>
+      <c r="AX190">
+        <v>9</v>
+      </c>
+      <c r="AY190">
+        <v>12</v>
+      </c>
+      <c r="AZ190">
+        <v>16</v>
+      </c>
+      <c r="BA190">
+        <v>5</v>
+      </c>
+      <c r="BB190">
+        <v>7</v>
+      </c>
+      <c r="BC190">
+        <v>12</v>
+      </c>
+      <c r="BD190">
+        <v>1.77</v>
+      </c>
+      <c r="BE190">
+        <v>6.1</v>
+      </c>
+      <c r="BF190">
+        <v>2.3</v>
+      </c>
+      <c r="BG190">
+        <v>1.5</v>
+      </c>
+      <c r="BH190">
+        <v>2.35</v>
+      </c>
+      <c r="BI190">
+        <v>1.86</v>
+      </c>
+      <c r="BJ190">
+        <v>1.8</v>
+      </c>
+      <c r="BK190">
+        <v>2.38</v>
+      </c>
+      <c r="BL190">
+        <v>1.49</v>
+      </c>
+      <c r="BM190">
+        <v>3.15</v>
+      </c>
+      <c r="BN190">
+        <v>1.29</v>
+      </c>
+      <c r="BO190">
+        <v>4.3</v>
+      </c>
+      <c r="BP190">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="291">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -628,10 +628,16 @@
     <t>['20', '79']</t>
   </si>
   <si>
-    <t>['19']</t>
+    <t>['2', '42', '49', '79']</t>
   </si>
   <si>
     <t>['57']</t>
+  </si>
+  <si>
+    <t>['35', '88']</t>
+  </si>
+  <si>
+    <t>['19']</t>
   </si>
   <si>
     <t>['14', '34']</t>
@@ -875,6 +881,12 @@
   </si>
   <si>
     <t>['35', '82', '90+2']</t>
+  </si>
+  <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
+    <t>['45']</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1492,7 +1504,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1570,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
         <v>1.08</v>
@@ -1985,7 +1997,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ4">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2394,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ6">
         <v>1.5</v>
@@ -2522,7 +2534,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2728,7 +2740,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3346,7 +3358,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3552,7 +3564,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3630,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -3758,7 +3770,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3839,7 +3851,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ13">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3964,7 +3976,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4170,7 +4182,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4251,7 +4263,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ15">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4376,7 +4388,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4788,7 +4800,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -4994,7 +5006,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5072,7 +5084,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ19">
         <v>1.08</v>
@@ -5200,7 +5212,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5612,7 +5624,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5690,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
         <v>0.5</v>
@@ -5818,7 +5830,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6926,10 +6938,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ28">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -7132,10 +7144,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ29">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR29">
         <v>2.09</v>
@@ -7260,7 +7272,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7466,7 +7478,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7672,7 +7684,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7878,7 +7890,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -7956,7 +7968,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ33">
         <v>0.83</v>
@@ -8084,7 +8096,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8290,7 +8302,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8496,7 +8508,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q36">
         <v>4</v>
@@ -8702,7 +8714,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9320,7 +9332,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9526,7 +9538,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9607,7 +9619,7 @@
         <v>1</v>
       </c>
       <c r="AQ41">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR41">
         <v>1.24</v>
@@ -9732,7 +9744,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -9810,7 +9822,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ42">
         <v>0.42</v>
@@ -10222,10 +10234,10 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ44">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR44">
         <v>2.23</v>
@@ -10762,7 +10774,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -10840,7 +10852,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
         <v>0.92</v>
@@ -11174,7 +11186,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -12204,7 +12216,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12410,7 +12422,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12822,7 +12834,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -12903,7 +12915,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ57">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR57">
         <v>1.23</v>
@@ -13106,7 +13118,7 @@
         <v>1.25</v>
       </c>
       <c r="AP58">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -13234,7 +13246,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13315,7 +13327,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ59">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR59">
         <v>1.8</v>
@@ -13440,7 +13452,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13518,10 +13530,10 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ60">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR60">
         <v>1.71</v>
@@ -13724,7 +13736,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ61">
         <v>1</v>
@@ -13852,7 +13864,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14882,7 +14894,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15294,7 +15306,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15500,7 +15512,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15706,7 +15718,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15912,7 +15924,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16405,7 +16417,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ74">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR74">
         <v>1.37</v>
@@ -16530,7 +16542,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16608,10 +16620,10 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ75">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR75">
         <v>2.05</v>
@@ -16736,7 +16748,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16814,7 +16826,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ76">
         <v>1.08</v>
@@ -16942,7 +16954,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17229,7 +17241,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ78">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR78">
         <v>1.54</v>
@@ -17354,7 +17366,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17766,7 +17778,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18178,7 +18190,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18796,7 +18808,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19080,7 +19092,7 @@
         <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ87">
         <v>1.08</v>
@@ -19289,7 +19301,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ88">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR88">
         <v>1.66</v>
@@ -19492,7 +19504,7 @@
         <v>0.67</v>
       </c>
       <c r="AP89">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ89">
         <v>1.5</v>
@@ -19620,7 +19632,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19826,7 +19838,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -19907,7 +19919,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ91">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR91">
         <v>1.87</v>
@@ -20032,7 +20044,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20238,7 +20250,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20650,7 +20662,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20728,7 +20740,7 @@
         <v>0.83</v>
       </c>
       <c r="AP95">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ95">
         <v>0.42</v>
@@ -21555,7 +21567,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ99">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR99">
         <v>1.24</v>
@@ -21758,7 +21770,7 @@
         <v>0.67</v>
       </c>
       <c r="AP100">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ100">
         <v>0.5</v>
@@ -21886,7 +21898,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22504,7 +22516,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22997,7 +23009,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ106">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR106">
         <v>1.16</v>
@@ -23122,7 +23134,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23328,7 +23340,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23612,7 +23624,7 @@
         <v>1.29</v>
       </c>
       <c r="AP109">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -23740,7 +23752,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23946,7 +23958,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24024,7 +24036,7 @@
         <v>1.29</v>
       </c>
       <c r="AP111">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111">
         <v>1.33</v>
@@ -24152,7 +24164,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24233,7 +24245,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ112">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR112">
         <v>1.44</v>
@@ -24358,7 +24370,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24439,7 +24451,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ113">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR113">
         <v>1.54</v>
@@ -24770,7 +24782,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -25182,7 +25194,7 @@
         <v>127</v>
       </c>
       <c r="P117" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q117">
         <v>2.88</v>
@@ -25260,7 +25272,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ117">
         <v>1.83</v>
@@ -26006,7 +26018,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26087,7 +26099,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ121">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR121">
         <v>1.14</v>
@@ -26212,7 +26224,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26496,7 +26508,7 @@
         <v>0.14</v>
       </c>
       <c r="AP123">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ123">
         <v>0.92</v>
@@ -27036,7 +27048,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27323,7 +27335,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ127">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR127">
         <v>1.4</v>
@@ -27529,7 +27541,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ128">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR128">
         <v>1.38</v>
@@ -28066,7 +28078,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28144,7 +28156,7 @@
         <v>1.25</v>
       </c>
       <c r="AP131">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ131">
         <v>1.08</v>
@@ -28272,7 +28284,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28478,7 +28490,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28762,7 +28774,7 @@
         <v>1.25</v>
       </c>
       <c r="AP134">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ134">
         <v>1.08</v>
@@ -29177,7 +29189,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ136">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR136">
         <v>1.72</v>
@@ -29302,7 +29314,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29795,7 +29807,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ139">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR139">
         <v>1.55</v>
@@ -29920,7 +29932,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30207,7 +30219,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ141">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR141">
         <v>1.41</v>
@@ -30332,7 +30344,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30538,7 +30550,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30616,10 +30628,10 @@
         <v>1.86</v>
       </c>
       <c r="AP143">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ143">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR143">
         <v>1.8</v>
@@ -30744,7 +30756,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30950,7 +30962,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31362,7 +31374,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31568,7 +31580,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31774,7 +31786,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -31980,7 +31992,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32264,7 +32276,7 @@
         <v>0.67</v>
       </c>
       <c r="AP151">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ151">
         <v>0.5</v>
@@ -32598,7 +32610,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32679,7 +32691,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ153">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -32804,7 +32816,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33091,7 +33103,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ155">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR155">
         <v>1.16</v>
@@ -33422,7 +33434,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33500,7 +33512,7 @@
         <v>1.33</v>
       </c>
       <c r="AP157">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ157">
         <v>1.08</v>
@@ -33628,7 +33640,7 @@
         <v>187</v>
       </c>
       <c r="P158" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q158">
         <v>2.63</v>
@@ -33709,7 +33721,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ158">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR158">
         <v>1.5</v>
@@ -33915,7 +33927,7 @@
         <v>1</v>
       </c>
       <c r="AQ159">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR159">
         <v>1.46</v>
@@ -34118,7 +34130,7 @@
         <v>1.67</v>
       </c>
       <c r="AP160">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ160">
         <v>1.83</v>
@@ -34864,7 +34876,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35276,7 +35288,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35894,7 +35906,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36100,7 +36112,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36306,7 +36318,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36384,7 +36396,7 @@
         <v>0.7</v>
       </c>
       <c r="AP171">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ171">
         <v>0.92</v>
@@ -36512,7 +36524,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36799,7 +36811,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ173">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR173">
         <v>1.4</v>
@@ -36924,7 +36936,7 @@
         <v>195</v>
       </c>
       <c r="P174" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q174">
         <v>4.7</v>
@@ -37005,7 +37017,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ174">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR174">
         <v>1.61</v>
@@ -37208,7 +37220,7 @@
         <v>1.4</v>
       </c>
       <c r="AP175">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ175">
         <v>1.5</v>
@@ -37414,7 +37426,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ176">
         <v>1</v>
@@ -37542,7 +37554,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -37623,7 +37635,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ177">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR177">
         <v>1.54</v>
@@ -38160,7 +38172,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38778,7 +38790,7 @@
         <v>86</v>
       </c>
       <c r="P183" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q183">
         <v>5.2</v>
@@ -39602,7 +39614,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -40014,7 +40026,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40220,7 +40232,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40376,6 +40388,624 @@
         <v>4.3</v>
       </c>
       <c r="BP190">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7486681</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45690.51041666666</v>
+      </c>
+      <c r="F191">
+        <v>24</v>
+      </c>
+      <c r="G191" t="s">
+        <v>80</v>
+      </c>
+      <c r="H191" t="s">
+        <v>78</v>
+      </c>
+      <c r="I191">
+        <v>2</v>
+      </c>
+      <c r="J191">
+        <v>1</v>
+      </c>
+      <c r="K191">
+        <v>3</v>
+      </c>
+      <c r="L191">
+        <v>4</v>
+      </c>
+      <c r="M191">
+        <v>1</v>
+      </c>
+      <c r="N191">
+        <v>5</v>
+      </c>
+      <c r="O191" t="s">
+        <v>204</v>
+      </c>
+      <c r="P191" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q191">
+        <v>1.91</v>
+      </c>
+      <c r="R191">
+        <v>2.38</v>
+      </c>
+      <c r="S191">
+        <v>8</v>
+      </c>
+      <c r="T191">
+        <v>1.36</v>
+      </c>
+      <c r="U191">
+        <v>3</v>
+      </c>
+      <c r="V191">
+        <v>2.75</v>
+      </c>
+      <c r="W191">
+        <v>1.4</v>
+      </c>
+      <c r="X191">
+        <v>7</v>
+      </c>
+      <c r="Y191">
+        <v>1.1</v>
+      </c>
+      <c r="Z191">
+        <v>1.43</v>
+      </c>
+      <c r="AA191">
+        <v>4.4</v>
+      </c>
+      <c r="AB191">
+        <v>6.9</v>
+      </c>
+      <c r="AC191">
+        <v>1.01</v>
+      </c>
+      <c r="AD191">
+        <v>11</v>
+      </c>
+      <c r="AE191">
+        <v>1.26</v>
+      </c>
+      <c r="AF191">
+        <v>3.65</v>
+      </c>
+      <c r="AG191">
+        <v>1.8</v>
+      </c>
+      <c r="AH191">
+        <v>1.94</v>
+      </c>
+      <c r="AI191">
+        <v>2.25</v>
+      </c>
+      <c r="AJ191">
+        <v>1.57</v>
+      </c>
+      <c r="AK191">
+        <v>1.07</v>
+      </c>
+      <c r="AL191">
+        <v>1.15</v>
+      </c>
+      <c r="AM191">
+        <v>2.55</v>
+      </c>
+      <c r="AN191">
+        <v>1.82</v>
+      </c>
+      <c r="AO191">
+        <v>0.45</v>
+      </c>
+      <c r="AP191">
+        <v>1.92</v>
+      </c>
+      <c r="AQ191">
+        <v>0.42</v>
+      </c>
+      <c r="AR191">
+        <v>1.78</v>
+      </c>
+      <c r="AS191">
+        <v>1.36</v>
+      </c>
+      <c r="AT191">
+        <v>3.14</v>
+      </c>
+      <c r="AU191">
+        <v>8</v>
+      </c>
+      <c r="AV191">
+        <v>5</v>
+      </c>
+      <c r="AW191">
+        <v>15</v>
+      </c>
+      <c r="AX191">
+        <v>4</v>
+      </c>
+      <c r="AY191">
+        <v>25</v>
+      </c>
+      <c r="AZ191">
+        <v>9</v>
+      </c>
+      <c r="BA191">
+        <v>9</v>
+      </c>
+      <c r="BB191">
+        <v>2</v>
+      </c>
+      <c r="BC191">
+        <v>11</v>
+      </c>
+      <c r="BD191">
+        <v>1.3</v>
+      </c>
+      <c r="BE191">
+        <v>7</v>
+      </c>
+      <c r="BF191">
+        <v>3.9</v>
+      </c>
+      <c r="BG191">
+        <v>1.4</v>
+      </c>
+      <c r="BH191">
+        <v>2.65</v>
+      </c>
+      <c r="BI191">
+        <v>1.66</v>
+      </c>
+      <c r="BJ191">
+        <v>2.04</v>
+      </c>
+      <c r="BK191">
+        <v>2.08</v>
+      </c>
+      <c r="BL191">
+        <v>1.64</v>
+      </c>
+      <c r="BM191">
+        <v>2.65</v>
+      </c>
+      <c r="BN191">
+        <v>1.4</v>
+      </c>
+      <c r="BO191">
+        <v>3.55</v>
+      </c>
+      <c r="BP191">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7486678</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45690.625</v>
+      </c>
+      <c r="F192">
+        <v>24</v>
+      </c>
+      <c r="G192" t="s">
+        <v>74</v>
+      </c>
+      <c r="H192" t="s">
+        <v>75</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>1</v>
+      </c>
+      <c r="M192">
+        <v>1</v>
+      </c>
+      <c r="N192">
+        <v>2</v>
+      </c>
+      <c r="O192" t="s">
+        <v>205</v>
+      </c>
+      <c r="P192" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q192">
+        <v>2.63</v>
+      </c>
+      <c r="R192">
+        <v>2.05</v>
+      </c>
+      <c r="S192">
+        <v>4.5</v>
+      </c>
+      <c r="T192">
+        <v>1.44</v>
+      </c>
+      <c r="U192">
+        <v>2.63</v>
+      </c>
+      <c r="V192">
+        <v>3.25</v>
+      </c>
+      <c r="W192">
+        <v>1.33</v>
+      </c>
+      <c r="X192">
+        <v>10</v>
+      </c>
+      <c r="Y192">
+        <v>1.06</v>
+      </c>
+      <c r="Z192">
+        <v>2.09</v>
+      </c>
+      <c r="AA192">
+        <v>3.41</v>
+      </c>
+      <c r="AB192">
+        <v>3.35</v>
+      </c>
+      <c r="AC192">
+        <v>1.06</v>
+      </c>
+      <c r="AD192">
+        <v>8</v>
+      </c>
+      <c r="AE192">
+        <v>1.35</v>
+      </c>
+      <c r="AF192">
+        <v>3.05</v>
+      </c>
+      <c r="AG192">
+        <v>1.98</v>
+      </c>
+      <c r="AH192">
+        <v>1.77</v>
+      </c>
+      <c r="AI192">
+        <v>1.91</v>
+      </c>
+      <c r="AJ192">
+        <v>1.8</v>
+      </c>
+      <c r="AK192">
+        <v>1.25</v>
+      </c>
+      <c r="AL192">
+        <v>1.29</v>
+      </c>
+      <c r="AM192">
+        <v>1.67</v>
+      </c>
+      <c r="AN192">
+        <v>1.73</v>
+      </c>
+      <c r="AO192">
+        <v>1.64</v>
+      </c>
+      <c r="AP192">
+        <v>1.67</v>
+      </c>
+      <c r="AQ192">
+        <v>1.58</v>
+      </c>
+      <c r="AR192">
+        <v>2.13</v>
+      </c>
+      <c r="AS192">
+        <v>1.28</v>
+      </c>
+      <c r="AT192">
+        <v>3.41</v>
+      </c>
+      <c r="AU192">
+        <v>4</v>
+      </c>
+      <c r="AV192">
+        <v>5</v>
+      </c>
+      <c r="AW192">
+        <v>4</v>
+      </c>
+      <c r="AX192">
+        <v>7</v>
+      </c>
+      <c r="AY192">
+        <v>8</v>
+      </c>
+      <c r="AZ192">
+        <v>12</v>
+      </c>
+      <c r="BA192">
+        <v>2</v>
+      </c>
+      <c r="BB192">
+        <v>4</v>
+      </c>
+      <c r="BC192">
+        <v>6</v>
+      </c>
+      <c r="BD192">
+        <v>1.68</v>
+      </c>
+      <c r="BE192">
+        <v>6.4</v>
+      </c>
+      <c r="BF192">
+        <v>2.43</v>
+      </c>
+      <c r="BG192">
+        <v>1.47</v>
+      </c>
+      <c r="BH192">
+        <v>2.43</v>
+      </c>
+      <c r="BI192">
+        <v>1.8</v>
+      </c>
+      <c r="BJ192">
+        <v>1.86</v>
+      </c>
+      <c r="BK192">
+        <v>2.28</v>
+      </c>
+      <c r="BL192">
+        <v>1.52</v>
+      </c>
+      <c r="BM192">
+        <v>2.95</v>
+      </c>
+      <c r="BN192">
+        <v>1.33</v>
+      </c>
+      <c r="BO192">
+        <v>3.95</v>
+      </c>
+      <c r="BP192">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7486677</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45691.625</v>
+      </c>
+      <c r="F193">
+        <v>24</v>
+      </c>
+      <c r="G193" t="s">
+        <v>70</v>
+      </c>
+      <c r="H193" t="s">
+        <v>77</v>
+      </c>
+      <c r="I193">
+        <v>1</v>
+      </c>
+      <c r="J193">
+        <v>1</v>
+      </c>
+      <c r="K193">
+        <v>2</v>
+      </c>
+      <c r="L193">
+        <v>2</v>
+      </c>
+      <c r="M193">
+        <v>1</v>
+      </c>
+      <c r="N193">
+        <v>3</v>
+      </c>
+      <c r="O193" t="s">
+        <v>206</v>
+      </c>
+      <c r="P193" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q193">
+        <v>3.25</v>
+      </c>
+      <c r="R193">
+        <v>1.95</v>
+      </c>
+      <c r="S193">
+        <v>3.75</v>
+      </c>
+      <c r="T193">
+        <v>1.53</v>
+      </c>
+      <c r="U193">
+        <v>2.38</v>
+      </c>
+      <c r="V193">
+        <v>3.75</v>
+      </c>
+      <c r="W193">
+        <v>1.25</v>
+      </c>
+      <c r="X193">
+        <v>11</v>
+      </c>
+      <c r="Y193">
+        <v>1.05</v>
+      </c>
+      <c r="Z193">
+        <v>2.17</v>
+      </c>
+      <c r="AA193">
+        <v>3.12</v>
+      </c>
+      <c r="AB193">
+        <v>3.47</v>
+      </c>
+      <c r="AC193">
+        <v>1.03</v>
+      </c>
+      <c r="AD193">
+        <v>7.4</v>
+      </c>
+      <c r="AE193">
+        <v>1.44</v>
+      </c>
+      <c r="AF193">
+        <v>2.65</v>
+      </c>
+      <c r="AG193">
+        <v>2.25</v>
+      </c>
+      <c r="AH193">
+        <v>1.53</v>
+      </c>
+      <c r="AI193">
+        <v>2</v>
+      </c>
+      <c r="AJ193">
+        <v>1.73</v>
+      </c>
+      <c r="AK193">
+        <v>1.32</v>
+      </c>
+      <c r="AL193">
+        <v>1.34</v>
+      </c>
+      <c r="AM193">
+        <v>1.49</v>
+      </c>
+      <c r="AN193">
+        <v>1.36</v>
+      </c>
+      <c r="AO193">
+        <v>1.27</v>
+      </c>
+      <c r="AP193">
+        <v>1.5</v>
+      </c>
+      <c r="AQ193">
+        <v>1.17</v>
+      </c>
+      <c r="AR193">
+        <v>1.72</v>
+      </c>
+      <c r="AS193">
+        <v>1.33</v>
+      </c>
+      <c r="AT193">
+        <v>3.05</v>
+      </c>
+      <c r="AU193">
+        <v>3</v>
+      </c>
+      <c r="AV193">
+        <v>5</v>
+      </c>
+      <c r="AW193">
+        <v>6</v>
+      </c>
+      <c r="AX193">
+        <v>6</v>
+      </c>
+      <c r="AY193">
+        <v>11</v>
+      </c>
+      <c r="AZ193">
+        <v>13</v>
+      </c>
+      <c r="BA193">
+        <v>4</v>
+      </c>
+      <c r="BB193">
+        <v>8</v>
+      </c>
+      <c r="BC193">
+        <v>12</v>
+      </c>
+      <c r="BD193">
+        <v>1.84</v>
+      </c>
+      <c r="BE193">
+        <v>6.25</v>
+      </c>
+      <c r="BF193">
+        <v>2.18</v>
+      </c>
+      <c r="BG193">
+        <v>1.5</v>
+      </c>
+      <c r="BH193">
+        <v>2.35</v>
+      </c>
+      <c r="BI193">
+        <v>1.83</v>
+      </c>
+      <c r="BJ193">
+        <v>1.83</v>
+      </c>
+      <c r="BK193">
+        <v>2.35</v>
+      </c>
+      <c r="BL193">
+        <v>1.5</v>
+      </c>
+      <c r="BM193">
+        <v>3.15</v>
+      </c>
+      <c r="BN193">
+        <v>1.3</v>
+      </c>
+      <c r="BO193">
+        <v>4.3</v>
+      </c>
+      <c r="BP193">
         <v>1.16</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="293">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -637,6 +637,12 @@
     <t>['35', '88']</t>
   </si>
   <si>
+    <t>['23', '90+7']</t>
+  </si>
+  <si>
+    <t>['10']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -695,9 +701,6 @@
   </si>
   <si>
     <t>['13']</t>
-  </si>
-  <si>
-    <t>['10']</t>
   </si>
   <si>
     <t>['32', '82']</t>
@@ -887,6 +890,9 @@
   </si>
   <si>
     <t>['45']</t>
+  </si>
+  <si>
+    <t>['14', '72']</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP193"/>
+  <dimension ref="A1:BP198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1504,7 +1510,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1585,7 +1591,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2409,7 +2415,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2534,7 +2540,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2612,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ7">
         <v>1.5</v>
@@ -2740,7 +2746,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2821,7 +2827,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ8">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3233,7 +3239,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ10">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3358,7 +3364,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3564,7 +3570,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3642,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -3770,7 +3776,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3848,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
         <v>1.58</v>
@@ -3976,7 +3982,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4057,7 +4063,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ14">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4182,7 +4188,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4260,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
         <v>1.17</v>
@@ -4388,7 +4394,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4466,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ16">
         <v>1.08</v>
@@ -4800,7 +4806,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -4881,7 +4887,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ18">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR18">
         <v>0.84</v>
@@ -5006,7 +5012,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5087,7 +5093,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ19">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>1.85</v>
@@ -5212,7 +5218,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5624,7 +5630,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5705,7 +5711,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR22">
         <v>1.89</v>
@@ -5830,7 +5836,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -5908,7 +5914,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ23">
         <v>1.33</v>
@@ -6117,7 +6123,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ24">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR24">
         <v>1.56</v>
@@ -6529,7 +6535,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ26">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR26">
         <v>1.29</v>
@@ -6732,7 +6738,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ27">
         <v>0.42</v>
@@ -7144,7 +7150,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
         <v>1.17</v>
@@ -7272,7 +7278,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7350,10 +7356,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR30">
         <v>1.69</v>
@@ -7478,7 +7484,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7684,7 +7690,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7762,7 +7768,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ32">
         <v>1.08</v>
@@ -7890,7 +7896,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8096,7 +8102,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8177,7 +8183,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ34">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR34">
         <v>1.21</v>
@@ -8302,7 +8308,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8383,7 +8389,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ35">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>1.45</v>
@@ -8508,7 +8514,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="Q36">
         <v>4</v>
@@ -8586,7 +8592,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8714,7 +8720,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -8998,10 +9004,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ38">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>1.73</v>
@@ -9207,7 +9213,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ39">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR39">
         <v>0.8100000000000001</v>
@@ -9332,7 +9338,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9538,7 +9544,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9744,7 +9750,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -9822,7 +9828,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ42">
         <v>0.42</v>
@@ -10440,7 +10446,7 @@
         <v>0.67</v>
       </c>
       <c r="AP45">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>1.5</v>
@@ -10774,7 +10780,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -10855,7 +10861,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR47">
         <v>1.66</v>
@@ -11061,7 +11067,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ48">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>0.93</v>
@@ -11186,7 +11192,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11473,7 +11479,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ50">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR50">
         <v>1.71</v>
@@ -11676,7 +11682,7 @@
         <v>2.33</v>
       </c>
       <c r="AP51">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ51">
         <v>1.33</v>
@@ -11882,10 +11888,10 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ52">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR52">
         <v>1.69</v>
@@ -12216,7 +12222,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12294,10 +12300,10 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ54">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR54">
         <v>1.5</v>
@@ -12422,7 +12428,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12834,7 +12840,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13118,7 +13124,7 @@
         <v>1.25</v>
       </c>
       <c r="AP58">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -13246,7 +13252,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13452,7 +13458,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13864,7 +13870,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14357,7 +14363,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ64">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -14560,10 +14566,10 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ65">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR65">
         <v>1.18</v>
@@ -14766,10 +14772,10 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ66">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.39</v>
@@ -14894,7 +14900,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15306,7 +15312,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15384,7 +15390,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ69">
         <v>1.83</v>
@@ -15512,7 +15518,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15593,7 +15599,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ70">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -15718,7 +15724,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15796,10 +15802,10 @@
         <v>1.8</v>
       </c>
       <c r="AP71">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR71">
         <v>1.35</v>
@@ -15924,7 +15930,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16542,7 +16548,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16748,7 +16754,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16954,7 +16960,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17366,7 +17372,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17653,7 +17659,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ80">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR80">
         <v>1.06</v>
@@ -17778,7 +17784,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -17856,10 +17862,10 @@
         <v>0.6</v>
       </c>
       <c r="AP81">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ81">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR81">
         <v>1.21</v>
@@ -18065,7 +18071,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ82">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR82">
         <v>1.61</v>
@@ -18190,7 +18196,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18268,7 +18274,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ83">
         <v>1</v>
@@ -18474,10 +18480,10 @@
         <v>1.8</v>
       </c>
       <c r="AP84">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR84">
         <v>1.43</v>
@@ -18680,7 +18686,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ85">
         <v>0.83</v>
@@ -18808,7 +18814,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19092,10 +19098,10 @@
         <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ87">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR87">
         <v>1.94</v>
@@ -19632,7 +19638,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19713,7 +19719,7 @@
         <v>1</v>
       </c>
       <c r="AQ90">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR90">
         <v>1.38</v>
@@ -19838,7 +19844,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -19916,7 +19922,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ91">
         <v>0.42</v>
@@ -20044,7 +20050,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20250,7 +20256,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20662,7 +20668,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20946,10 +20952,10 @@
         <v>0.2</v>
       </c>
       <c r="AP96">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ96">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR96">
         <v>1.35</v>
@@ -21155,7 +21161,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ97">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR97">
         <v>1.37</v>
@@ -21770,10 +21776,10 @@
         <v>0.67</v>
       </c>
       <c r="AP100">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR100">
         <v>1.91</v>
@@ -21898,7 +21904,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21976,7 +21982,7 @@
         <v>1.25</v>
       </c>
       <c r="AP101">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ101">
         <v>1.83</v>
@@ -22185,7 +22191,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ102">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR102">
         <v>1.5</v>
@@ -22388,7 +22394,7 @@
         <v>0.6</v>
       </c>
       <c r="AP103">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ103">
         <v>0.83</v>
@@ -22516,7 +22522,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22594,7 +22600,7 @@
         <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ104">
         <v>1.08</v>
@@ -23134,7 +23140,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23340,7 +23346,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23421,7 +23427,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ108">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR108">
         <v>1.42</v>
@@ -23752,7 +23758,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23833,7 +23839,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ110">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR110">
         <v>1.9</v>
@@ -23958,7 +23964,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24164,7 +24170,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24242,7 +24248,7 @@
         <v>1.5</v>
       </c>
       <c r="AP112">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ112">
         <v>1.58</v>
@@ -24370,7 +24376,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24654,7 +24660,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
         <v>1</v>
@@ -24782,7 +24788,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24863,7 +24869,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ115">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR115">
         <v>1.47</v>
@@ -25194,7 +25200,7 @@
         <v>127</v>
       </c>
       <c r="P117" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q117">
         <v>2.88</v>
@@ -25272,7 +25278,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ117">
         <v>1.83</v>
@@ -25481,7 +25487,7 @@
         <v>1</v>
       </c>
       <c r="AQ118">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR118">
         <v>1.37</v>
@@ -25684,10 +25690,10 @@
         <v>0.17</v>
       </c>
       <c r="AP119">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ119">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR119">
         <v>1.46</v>
@@ -25893,7 +25899,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ120">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR120">
         <v>1.36</v>
@@ -26018,7 +26024,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26096,7 +26102,7 @@
         <v>1.8</v>
       </c>
       <c r="AP121">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ121">
         <v>1.58</v>
@@ -26224,7 +26230,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26508,10 +26514,10 @@
         <v>0.14</v>
       </c>
       <c r="AP123">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ123">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR123">
         <v>1.82</v>
@@ -26714,7 +26720,7 @@
         <v>0.86</v>
       </c>
       <c r="AP124">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -27048,7 +27054,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27332,7 +27338,7 @@
         <v>1.29</v>
       </c>
       <c r="AP127">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ127">
         <v>1.17</v>
@@ -28078,7 +28084,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28159,7 +28165,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ131">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR131">
         <v>1.58</v>
@@ -28284,7 +28290,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28365,7 +28371,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ132">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR132">
         <v>1.25</v>
@@ -28490,7 +28496,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28568,7 +28574,7 @@
         <v>1.25</v>
       </c>
       <c r="AP133">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ133">
         <v>1</v>
@@ -28777,7 +28783,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ134">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR134">
         <v>2.06</v>
@@ -29314,7 +29320,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29804,7 +29810,7 @@
         <v>1.5</v>
       </c>
       <c r="AP139">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ139">
         <v>1.17</v>
@@ -29932,7 +29938,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30013,7 +30019,7 @@
         <v>1</v>
       </c>
       <c r="AQ140">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR140">
         <v>1.45</v>
@@ -30216,7 +30222,7 @@
         <v>0.63</v>
       </c>
       <c r="AP141">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ141">
         <v>0.42</v>
@@ -30344,7 +30350,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30422,7 +30428,7 @@
         <v>1.38</v>
       </c>
       <c r="AP142">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ142">
         <v>1.08</v>
@@ -30550,7 +30556,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30628,7 +30634,7 @@
         <v>1.86</v>
       </c>
       <c r="AP143">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ143">
         <v>1.58</v>
@@ -30756,7 +30762,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30962,7 +30968,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31374,7 +31380,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31452,7 +31458,7 @@
         <v>1.22</v>
       </c>
       <c r="AP147">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ147">
         <v>1.5</v>
@@ -31580,7 +31586,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31786,7 +31792,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -31867,7 +31873,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ149">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR149">
         <v>1.6</v>
@@ -31992,7 +31998,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32279,7 +32285,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ151">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR151">
         <v>2.01</v>
@@ -32485,7 +32491,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ152">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR152">
         <v>1.23</v>
@@ -32610,7 +32616,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32816,7 +32822,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -32897,7 +32903,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ154">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR154">
         <v>1.64</v>
@@ -33100,7 +33106,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP155">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ155">
         <v>0.42</v>
@@ -33434,7 +33440,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33512,7 +33518,7 @@
         <v>1.33</v>
       </c>
       <c r="AP157">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ157">
         <v>1.08</v>
@@ -33640,7 +33646,7 @@
         <v>187</v>
       </c>
       <c r="P158" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q158">
         <v>2.63</v>
@@ -34336,7 +34342,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP161">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ161">
         <v>0.42</v>
@@ -34545,7 +34551,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ162">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR162">
         <v>1.45</v>
@@ -34876,7 +34882,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -34954,7 +34960,7 @@
         <v>1.3</v>
       </c>
       <c r="AP164">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ164">
         <v>1.33</v>
@@ -35163,7 +35169,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ165">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR165">
         <v>1.27</v>
@@ -35288,7 +35294,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35366,10 +35372,10 @@
         <v>1.3</v>
       </c>
       <c r="AP166">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ166">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR166">
         <v>1.81</v>
@@ -35572,7 +35578,7 @@
         <v>1.1</v>
       </c>
       <c r="AP167">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ167">
         <v>1</v>
@@ -35781,7 +35787,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ168">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR168">
         <v>1.63</v>
@@ -35906,7 +35912,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36112,7 +36118,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36318,7 +36324,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36399,7 +36405,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ171">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR171">
         <v>2.04</v>
@@ -36524,7 +36530,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36936,7 +36942,7 @@
         <v>195</v>
       </c>
       <c r="P174" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="Q174">
         <v>4.7</v>
@@ -37220,7 +37226,7 @@
         <v>1.4</v>
       </c>
       <c r="AP175">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ175">
         <v>1.5</v>
@@ -37554,7 +37560,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -37632,7 +37638,7 @@
         <v>0.5</v>
       </c>
       <c r="AP177">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ177">
         <v>0.42</v>
@@ -37838,10 +37844,10 @@
         <v>1.18</v>
       </c>
       <c r="AP178">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ178">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR178">
         <v>1.45</v>
@@ -38044,10 +38050,10 @@
         <v>1.55</v>
       </c>
       <c r="AP179">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ179">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR179">
         <v>1.24</v>
@@ -38172,7 +38178,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38253,7 +38259,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ180">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR180">
         <v>1.37</v>
@@ -38456,7 +38462,7 @@
         <v>1.45</v>
       </c>
       <c r="AP181">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ181">
         <v>1.33</v>
@@ -38665,7 +38671,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ182">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR182">
         <v>1.35</v>
@@ -38790,7 +38796,7 @@
         <v>86</v>
       </c>
       <c r="P183" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q183">
         <v>5.2</v>
@@ -39077,7 +39083,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ184">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR184">
         <v>1.32</v>
@@ -39280,7 +39286,7 @@
         <v>0.91</v>
       </c>
       <c r="AP185">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ185">
         <v>0.83</v>
@@ -39614,7 +39620,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -40026,7 +40032,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40232,7 +40238,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40438,7 +40444,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40516,7 +40522,7 @@
         <v>0.45</v>
       </c>
       <c r="AP191">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ191">
         <v>0.42</v>
@@ -40850,7 +40856,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -41007,6 +41013,1036 @@
       </c>
       <c r="BP193">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7486683</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45692.45833333334</v>
+      </c>
+      <c r="F194">
+        <v>25</v>
+      </c>
+      <c r="G194" t="s">
+        <v>84</v>
+      </c>
+      <c r="H194" t="s">
+        <v>76</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>1</v>
+      </c>
+      <c r="K194">
+        <v>1</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>2</v>
+      </c>
+      <c r="N194">
+        <v>2</v>
+      </c>
+      <c r="O194" t="s">
+        <v>86</v>
+      </c>
+      <c r="P194" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q194">
+        <v>3.15</v>
+      </c>
+      <c r="R194">
+        <v>1.91</v>
+      </c>
+      <c r="S194">
+        <v>3.75</v>
+      </c>
+      <c r="T194">
+        <v>1.61</v>
+      </c>
+      <c r="U194">
+        <v>2.21</v>
+      </c>
+      <c r="V194">
+        <v>3.65</v>
+      </c>
+      <c r="W194">
+        <v>1.25</v>
+      </c>
+      <c r="X194">
+        <v>9.5</v>
+      </c>
+      <c r="Y194">
+        <v>1.03</v>
+      </c>
+      <c r="Z194">
+        <v>2.42</v>
+      </c>
+      <c r="AA194">
+        <v>3.12</v>
+      </c>
+      <c r="AB194">
+        <v>2.98</v>
+      </c>
+      <c r="AC194">
+        <v>1.08</v>
+      </c>
+      <c r="AD194">
+        <v>6.5</v>
+      </c>
+      <c r="AE194">
+        <v>1.48</v>
+      </c>
+      <c r="AF194">
+        <v>2.5</v>
+      </c>
+      <c r="AG194">
+        <v>2.37</v>
+      </c>
+      <c r="AH194">
+        <v>1.48</v>
+      </c>
+      <c r="AI194">
+        <v>2.03</v>
+      </c>
+      <c r="AJ194">
+        <v>1.68</v>
+      </c>
+      <c r="AK194">
+        <v>1.35</v>
+      </c>
+      <c r="AL194">
+        <v>1.32</v>
+      </c>
+      <c r="AM194">
+        <v>1.47</v>
+      </c>
+      <c r="AN194">
+        <v>1.17</v>
+      </c>
+      <c r="AO194">
+        <v>0.5</v>
+      </c>
+      <c r="AP194">
+        <v>1.08</v>
+      </c>
+      <c r="AQ194">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR194">
+        <v>1.47</v>
+      </c>
+      <c r="AS194">
+        <v>1.23</v>
+      </c>
+      <c r="AT194">
+        <v>2.7</v>
+      </c>
+      <c r="AU194">
+        <v>2</v>
+      </c>
+      <c r="AV194">
+        <v>8</v>
+      </c>
+      <c r="AW194">
+        <v>4</v>
+      </c>
+      <c r="AX194">
+        <v>10</v>
+      </c>
+      <c r="AY194">
+        <v>6</v>
+      </c>
+      <c r="AZ194">
+        <v>21</v>
+      </c>
+      <c r="BA194">
+        <v>3</v>
+      </c>
+      <c r="BB194">
+        <v>6</v>
+      </c>
+      <c r="BC194">
+        <v>9</v>
+      </c>
+      <c r="BD194">
+        <v>1.82</v>
+      </c>
+      <c r="BE194">
+        <v>6.25</v>
+      </c>
+      <c r="BF194">
+        <v>2.2</v>
+      </c>
+      <c r="BG194">
+        <v>1.53</v>
+      </c>
+      <c r="BH194">
+        <v>2.25</v>
+      </c>
+      <c r="BI194">
+        <v>1.9</v>
+      </c>
+      <c r="BJ194">
+        <v>1.76</v>
+      </c>
+      <c r="BK194">
+        <v>2.45</v>
+      </c>
+      <c r="BL194">
+        <v>1.46</v>
+      </c>
+      <c r="BM194">
+        <v>3.3</v>
+      </c>
+      <c r="BN194">
+        <v>1.27</v>
+      </c>
+      <c r="BO194">
+        <v>4.4</v>
+      </c>
+      <c r="BP194">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7486989</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45692.54166666666</v>
+      </c>
+      <c r="F195">
+        <v>25</v>
+      </c>
+      <c r="G195" t="s">
+        <v>81</v>
+      </c>
+      <c r="H195" t="s">
+        <v>79</v>
+      </c>
+      <c r="I195">
+        <v>1</v>
+      </c>
+      <c r="J195">
+        <v>1</v>
+      </c>
+      <c r="K195">
+        <v>2</v>
+      </c>
+      <c r="L195">
+        <v>2</v>
+      </c>
+      <c r="M195">
+        <v>1</v>
+      </c>
+      <c r="N195">
+        <v>3</v>
+      </c>
+      <c r="O195" t="s">
+        <v>207</v>
+      </c>
+      <c r="P195" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q195">
+        <v>1.89</v>
+      </c>
+      <c r="R195">
+        <v>2.31</v>
+      </c>
+      <c r="S195">
+        <v>7.2</v>
+      </c>
+      <c r="T195">
+        <v>1.38</v>
+      </c>
+      <c r="U195">
+        <v>2.75</v>
+      </c>
+      <c r="V195">
+        <v>2.7</v>
+      </c>
+      <c r="W195">
+        <v>1.41</v>
+      </c>
+      <c r="X195">
+        <v>6.75</v>
+      </c>
+      <c r="Y195">
+        <v>1.06</v>
+      </c>
+      <c r="Z195">
+        <v>1.41</v>
+      </c>
+      <c r="AA195">
+        <v>4.4</v>
+      </c>
+      <c r="AB195">
+        <v>7.4</v>
+      </c>
+      <c r="AC195">
+        <v>1.02</v>
+      </c>
+      <c r="AD195">
+        <v>10</v>
+      </c>
+      <c r="AE195">
+        <v>1.31</v>
+      </c>
+      <c r="AF195">
+        <v>3.25</v>
+      </c>
+      <c r="AG195">
+        <v>1.92</v>
+      </c>
+      <c r="AH195">
+        <v>1.82</v>
+      </c>
+      <c r="AI195">
+        <v>2.15</v>
+      </c>
+      <c r="AJ195">
+        <v>1.6</v>
+      </c>
+      <c r="AK195">
+        <v>1.08</v>
+      </c>
+      <c r="AL195">
+        <v>1.17</v>
+      </c>
+      <c r="AM195">
+        <v>2.43</v>
+      </c>
+      <c r="AN195">
+        <v>1.92</v>
+      </c>
+      <c r="AO195">
+        <v>1.08</v>
+      </c>
+      <c r="AP195">
+        <v>2</v>
+      </c>
+      <c r="AQ195">
+        <v>1</v>
+      </c>
+      <c r="AR195">
+        <v>1.63</v>
+      </c>
+      <c r="AS195">
+        <v>1.31</v>
+      </c>
+      <c r="AT195">
+        <v>2.94</v>
+      </c>
+      <c r="AU195">
+        <v>12</v>
+      </c>
+      <c r="AV195">
+        <v>5</v>
+      </c>
+      <c r="AW195">
+        <v>23</v>
+      </c>
+      <c r="AX195">
+        <v>8</v>
+      </c>
+      <c r="AY195">
+        <v>42</v>
+      </c>
+      <c r="AZ195">
+        <v>14</v>
+      </c>
+      <c r="BA195">
+        <v>8</v>
+      </c>
+      <c r="BB195">
+        <v>4</v>
+      </c>
+      <c r="BC195">
+        <v>12</v>
+      </c>
+      <c r="BD195">
+        <v>1.33</v>
+      </c>
+      <c r="BE195">
+        <v>7</v>
+      </c>
+      <c r="BF195">
+        <v>3.65</v>
+      </c>
+      <c r="BG195">
+        <v>1.45</v>
+      </c>
+      <c r="BH195">
+        <v>2.48</v>
+      </c>
+      <c r="BI195">
+        <v>1.76</v>
+      </c>
+      <c r="BJ195">
+        <v>1.9</v>
+      </c>
+      <c r="BK195">
+        <v>2.2</v>
+      </c>
+      <c r="BL195">
+        <v>1.56</v>
+      </c>
+      <c r="BM195">
+        <v>2.9</v>
+      </c>
+      <c r="BN195">
+        <v>1.34</v>
+      </c>
+      <c r="BO195">
+        <v>3.9</v>
+      </c>
+      <c r="BP195">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7486684</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45692.64583333334</v>
+      </c>
+      <c r="F196">
+        <v>25</v>
+      </c>
+      <c r="G196" t="s">
+        <v>83</v>
+      </c>
+      <c r="H196" t="s">
+        <v>85</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <v>1</v>
+      </c>
+      <c r="M196">
+        <v>0</v>
+      </c>
+      <c r="N196">
+        <v>1</v>
+      </c>
+      <c r="O196" t="s">
+        <v>169</v>
+      </c>
+      <c r="P196" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q196">
+        <v>2.25</v>
+      </c>
+      <c r="R196">
+        <v>2.06</v>
+      </c>
+      <c r="S196">
+        <v>5.8</v>
+      </c>
+      <c r="T196">
+        <v>1.52</v>
+      </c>
+      <c r="U196">
+        <v>2.39</v>
+      </c>
+      <c r="V196">
+        <v>3.2</v>
+      </c>
+      <c r="W196">
+        <v>1.32</v>
+      </c>
+      <c r="X196">
+        <v>8</v>
+      </c>
+      <c r="Y196">
+        <v>1.04</v>
+      </c>
+      <c r="Z196">
+        <v>1.67</v>
+      </c>
+      <c r="AA196">
+        <v>3.57</v>
+      </c>
+      <c r="AB196">
+        <v>5.2</v>
+      </c>
+      <c r="AC196">
+        <v>1.06</v>
+      </c>
+      <c r="AD196">
+        <v>7.5</v>
+      </c>
+      <c r="AE196">
+        <v>1.43</v>
+      </c>
+      <c r="AF196">
+        <v>2.7</v>
+      </c>
+      <c r="AG196">
+        <v>2.2</v>
+      </c>
+      <c r="AH196">
+        <v>1.55</v>
+      </c>
+      <c r="AI196">
+        <v>2.16</v>
+      </c>
+      <c r="AJ196">
+        <v>1.6</v>
+      </c>
+      <c r="AK196">
+        <v>1.14</v>
+      </c>
+      <c r="AL196">
+        <v>1.25</v>
+      </c>
+      <c r="AM196">
+        <v>1.96</v>
+      </c>
+      <c r="AN196">
+        <v>1.92</v>
+      </c>
+      <c r="AO196">
+        <v>1.08</v>
+      </c>
+      <c r="AP196">
+        <v>2</v>
+      </c>
+      <c r="AQ196">
+        <v>1</v>
+      </c>
+      <c r="AR196">
+        <v>1.24</v>
+      </c>
+      <c r="AS196">
+        <v>1.36</v>
+      </c>
+      <c r="AT196">
+        <v>2.6</v>
+      </c>
+      <c r="AU196">
+        <v>5</v>
+      </c>
+      <c r="AV196">
+        <v>3</v>
+      </c>
+      <c r="AW196">
+        <v>6</v>
+      </c>
+      <c r="AX196">
+        <v>2</v>
+      </c>
+      <c r="AY196">
+        <v>15</v>
+      </c>
+      <c r="AZ196">
+        <v>5</v>
+      </c>
+      <c r="BA196">
+        <v>4</v>
+      </c>
+      <c r="BB196">
+        <v>2</v>
+      </c>
+      <c r="BC196">
+        <v>6</v>
+      </c>
+      <c r="BD196">
+        <v>1.52</v>
+      </c>
+      <c r="BE196">
+        <v>6.5</v>
+      </c>
+      <c r="BF196">
+        <v>2.8</v>
+      </c>
+      <c r="BG196">
+        <v>1.5</v>
+      </c>
+      <c r="BH196">
+        <v>2.35</v>
+      </c>
+      <c r="BI196">
+        <v>1.84</v>
+      </c>
+      <c r="BJ196">
+        <v>1.82</v>
+      </c>
+      <c r="BK196">
+        <v>2.35</v>
+      </c>
+      <c r="BL196">
+        <v>1.5</v>
+      </c>
+      <c r="BM196">
+        <v>3.1</v>
+      </c>
+      <c r="BN196">
+        <v>1.3</v>
+      </c>
+      <c r="BO196">
+        <v>4.1</v>
+      </c>
+      <c r="BP196">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7487073</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45693.54166666666</v>
+      </c>
+      <c r="F197">
+        <v>25</v>
+      </c>
+      <c r="G197" t="s">
+        <v>75</v>
+      </c>
+      <c r="H197" t="s">
+        <v>71</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>1</v>
+      </c>
+      <c r="L197">
+        <v>1</v>
+      </c>
+      <c r="M197">
+        <v>0</v>
+      </c>
+      <c r="N197">
+        <v>1</v>
+      </c>
+      <c r="O197" t="s">
+        <v>201</v>
+      </c>
+      <c r="P197" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q197">
+        <v>2.2</v>
+      </c>
+      <c r="R197">
+        <v>2.12</v>
+      </c>
+      <c r="S197">
+        <v>5.8</v>
+      </c>
+      <c r="T197">
+        <v>1.46</v>
+      </c>
+      <c r="U197">
+        <v>2.55</v>
+      </c>
+      <c r="V197">
+        <v>3</v>
+      </c>
+      <c r="W197">
+        <v>1.33</v>
+      </c>
+      <c r="X197">
+        <v>7.5</v>
+      </c>
+      <c r="Y197">
+        <v>1.05</v>
+      </c>
+      <c r="Z197">
+        <v>1.67</v>
+      </c>
+      <c r="AA197">
+        <v>3.59</v>
+      </c>
+      <c r="AB197">
+        <v>5.2</v>
+      </c>
+      <c r="AC197">
+        <v>1.07</v>
+      </c>
+      <c r="AD197">
+        <v>7.5</v>
+      </c>
+      <c r="AE197">
+        <v>1.38</v>
+      </c>
+      <c r="AF197">
+        <v>2.9</v>
+      </c>
+      <c r="AG197">
+        <v>1.92</v>
+      </c>
+      <c r="AH197">
+        <v>1.82</v>
+      </c>
+      <c r="AI197">
+        <v>2.08</v>
+      </c>
+      <c r="AJ197">
+        <v>1.67</v>
+      </c>
+      <c r="AK197">
+        <v>1.15</v>
+      </c>
+      <c r="AL197">
+        <v>1.25</v>
+      </c>
+      <c r="AM197">
+        <v>2.09</v>
+      </c>
+      <c r="AN197">
+        <v>1.75</v>
+      </c>
+      <c r="AO197">
+        <v>0.92</v>
+      </c>
+      <c r="AP197">
+        <v>1.85</v>
+      </c>
+      <c r="AQ197">
+        <v>0.85</v>
+      </c>
+      <c r="AR197">
+        <v>1.86</v>
+      </c>
+      <c r="AS197">
+        <v>1.31</v>
+      </c>
+      <c r="AT197">
+        <v>3.17</v>
+      </c>
+      <c r="AU197">
+        <v>2</v>
+      </c>
+      <c r="AV197">
+        <v>3</v>
+      </c>
+      <c r="AW197">
+        <v>11</v>
+      </c>
+      <c r="AX197">
+        <v>4</v>
+      </c>
+      <c r="AY197">
+        <v>15</v>
+      </c>
+      <c r="AZ197">
+        <v>8</v>
+      </c>
+      <c r="BA197">
+        <v>3</v>
+      </c>
+      <c r="BB197">
+        <v>4</v>
+      </c>
+      <c r="BC197">
+        <v>7</v>
+      </c>
+      <c r="BD197">
+        <v>1.5</v>
+      </c>
+      <c r="BE197">
+        <v>6.5</v>
+      </c>
+      <c r="BF197">
+        <v>2.9</v>
+      </c>
+      <c r="BG197">
+        <v>1.48</v>
+      </c>
+      <c r="BH197">
+        <v>2.4</v>
+      </c>
+      <c r="BI197">
+        <v>1.81</v>
+      </c>
+      <c r="BJ197">
+        <v>1.85</v>
+      </c>
+      <c r="BK197">
+        <v>2.28</v>
+      </c>
+      <c r="BL197">
+        <v>1.53</v>
+      </c>
+      <c r="BM197">
+        <v>2.95</v>
+      </c>
+      <c r="BN197">
+        <v>1.33</v>
+      </c>
+      <c r="BO197">
+        <v>4</v>
+      </c>
+      <c r="BP197">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7486686</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45693.64583333334</v>
+      </c>
+      <c r="F198">
+        <v>25</v>
+      </c>
+      <c r="G198" t="s">
+        <v>80</v>
+      </c>
+      <c r="H198" t="s">
+        <v>82</v>
+      </c>
+      <c r="I198">
+        <v>1</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>1</v>
+      </c>
+      <c r="L198">
+        <v>1</v>
+      </c>
+      <c r="M198">
+        <v>0</v>
+      </c>
+      <c r="N198">
+        <v>1</v>
+      </c>
+      <c r="O198" t="s">
+        <v>208</v>
+      </c>
+      <c r="P198" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q198">
+        <v>2.75</v>
+      </c>
+      <c r="R198">
+        <v>2.06</v>
+      </c>
+      <c r="S198">
+        <v>3.9</v>
+      </c>
+      <c r="T198">
+        <v>1.48</v>
+      </c>
+      <c r="U198">
+        <v>2.5</v>
+      </c>
+      <c r="V198">
+        <v>2.95</v>
+      </c>
+      <c r="W198">
+        <v>1.35</v>
+      </c>
+      <c r="X198">
+        <v>7</v>
+      </c>
+      <c r="Y198">
+        <v>1.06</v>
+      </c>
+      <c r="Z198">
+        <v>2.05</v>
+      </c>
+      <c r="AA198">
+        <v>2.8</v>
+      </c>
+      <c r="AB198">
+        <v>4</v>
+      </c>
+      <c r="AC198">
+        <v>1.07</v>
+      </c>
+      <c r="AD198">
+        <v>7.5</v>
+      </c>
+      <c r="AE198">
+        <v>1.5</v>
+      </c>
+      <c r="AF198">
+        <v>2.4</v>
+      </c>
+      <c r="AG198">
+        <v>1.95</v>
+      </c>
+      <c r="AH198">
+        <v>1.7</v>
+      </c>
+      <c r="AI198">
+        <v>1.78</v>
+      </c>
+      <c r="AJ198">
+        <v>1.89</v>
+      </c>
+      <c r="AK198">
+        <v>1.29</v>
+      </c>
+      <c r="AL198">
+        <v>1.31</v>
+      </c>
+      <c r="AM198">
+        <v>1.56</v>
+      </c>
+      <c r="AN198">
+        <v>1.92</v>
+      </c>
+      <c r="AO198">
+        <v>1.5</v>
+      </c>
+      <c r="AP198">
+        <v>2</v>
+      </c>
+      <c r="AQ198">
+        <v>1.38</v>
+      </c>
+      <c r="AR198">
+        <v>1.82</v>
+      </c>
+      <c r="AS198">
+        <v>1.38</v>
+      </c>
+      <c r="AT198">
+        <v>3.2</v>
+      </c>
+      <c r="AU198">
+        <v>6</v>
+      </c>
+      <c r="AV198">
+        <v>7</v>
+      </c>
+      <c r="AW198">
+        <v>10</v>
+      </c>
+      <c r="AX198">
+        <v>15</v>
+      </c>
+      <c r="AY198">
+        <v>17</v>
+      </c>
+      <c r="AZ198">
+        <v>24</v>
+      </c>
+      <c r="BA198">
+        <v>2</v>
+      </c>
+      <c r="BB198">
+        <v>8</v>
+      </c>
+      <c r="BC198">
+        <v>10</v>
+      </c>
+      <c r="BD198">
+        <v>1.74</v>
+      </c>
+      <c r="BE198">
+        <v>6.1</v>
+      </c>
+      <c r="BF198">
+        <v>2.33</v>
+      </c>
+      <c r="BG198">
+        <v>1.44</v>
+      </c>
+      <c r="BH198">
+        <v>2.5</v>
+      </c>
+      <c r="BI198">
+        <v>1.74</v>
+      </c>
+      <c r="BJ198">
+        <v>1.93</v>
+      </c>
+      <c r="BK198">
+        <v>2.2</v>
+      </c>
+      <c r="BL198">
+        <v>1.57</v>
+      </c>
+      <c r="BM198">
+        <v>2.9</v>
+      </c>
+      <c r="BN198">
+        <v>1.34</v>
+      </c>
+      <c r="BO198">
+        <v>3.9</v>
+      </c>
+      <c r="BP198">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="293">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -643,6 +643,9 @@
     <t>['10']</t>
   </si>
   <si>
+    <t>['17']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -812,9 +815,6 @@
   </si>
   <si>
     <t>['2']</t>
-  </si>
-  <si>
-    <t>['17']</t>
   </si>
   <si>
     <t>['45+2']</t>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP198"/>
+  <dimension ref="A1:BP201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1510,7 +1510,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ4">
         <v>0.42</v>
@@ -2540,7 +2540,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2746,7 +2746,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ9">
         <v>0.42</v>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ10">
         <v>0.6899999999999999</v>
@@ -3364,7 +3364,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3445,7 +3445,7 @@
         <v>1</v>
       </c>
       <c r="AQ11">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3651,7 +3651,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3982,7 +3982,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4188,7 +4188,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4394,7 +4394,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4681,7 +4681,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ17">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -5012,7 +5012,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5218,7 +5218,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5296,7 +5296,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ20">
         <v>0.42</v>
@@ -5502,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ21">
         <v>1.5</v>
@@ -5630,7 +5630,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5836,7 +5836,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6326,7 +6326,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -7278,7 +7278,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7484,7 +7484,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7565,7 +7565,7 @@
         <v>1</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR31">
         <v>1</v>
@@ -7690,7 +7690,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7896,7 +7896,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -7977,7 +7977,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ33">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR33">
         <v>2.11</v>
@@ -8102,7 +8102,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8308,7 +8308,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8720,7 +8720,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -8798,7 +8798,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ37">
         <v>1.33</v>
@@ -9210,7 +9210,7 @@
         <v>1.67</v>
       </c>
       <c r="AP39">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ39">
         <v>1.38</v>
@@ -9338,7 +9338,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9416,7 +9416,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ40">
         <v>1.5</v>
@@ -9544,7 +9544,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9750,7 +9750,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10037,7 +10037,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR43">
         <v>1.6</v>
@@ -10780,7 +10780,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11064,7 +11064,7 @@
         <v>2.33</v>
       </c>
       <c r="AP48">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -11192,7 +11192,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11270,7 +11270,7 @@
         <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ49">
         <v>1</v>
@@ -11476,7 +11476,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -12097,7 +12097,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ53">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR53">
         <v>1.19</v>
@@ -12222,7 +12222,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12428,7 +12428,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12509,7 +12509,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ55">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR55">
         <v>1.71</v>
@@ -12840,7 +12840,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13252,7 +13252,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13458,7 +13458,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13745,7 +13745,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ61">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR61">
         <v>2.06</v>
@@ -13870,7 +13870,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14360,7 +14360,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ64">
         <v>0.6899999999999999</v>
@@ -14900,7 +14900,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -14978,10 +14978,10 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ67">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR67">
         <v>0.97</v>
@@ -15184,7 +15184,7 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ68">
         <v>1.33</v>
@@ -15312,7 +15312,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15393,7 +15393,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ69">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR69">
         <v>1.9</v>
@@ -15518,7 +15518,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15724,7 +15724,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15930,7 +15930,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16548,7 +16548,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16754,7 +16754,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16960,7 +16960,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17372,7 +17372,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17656,7 +17656,7 @@
         <v>0.25</v>
       </c>
       <c r="AP80">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ80">
         <v>0.85</v>
@@ -17784,7 +17784,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18068,7 +18068,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ82">
         <v>1.38</v>
@@ -18196,7 +18196,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18277,7 +18277,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR83">
         <v>1.79</v>
@@ -18689,7 +18689,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ85">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18814,7 +18814,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -18892,10 +18892,10 @@
         <v>0.67</v>
       </c>
       <c r="AP86">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ86">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR86">
         <v>1.56</v>
@@ -19638,7 +19638,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19844,7 +19844,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20050,7 +20050,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20256,7 +20256,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20668,7 +20668,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -21364,10 +21364,10 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ98">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR98">
         <v>1.57</v>
@@ -21570,7 +21570,7 @@
         <v>1.67</v>
       </c>
       <c r="AP99">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ99">
         <v>1.58</v>
@@ -21904,7 +21904,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21985,7 +21985,7 @@
         <v>2</v>
       </c>
       <c r="AQ101">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR101">
         <v>1.23</v>
@@ -22188,7 +22188,7 @@
         <v>1.17</v>
       </c>
       <c r="AP102">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22397,7 +22397,7 @@
         <v>2</v>
       </c>
       <c r="AQ103">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR103">
         <v>1.37</v>
@@ -22522,7 +22522,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -23012,7 +23012,7 @@
         <v>0.67</v>
       </c>
       <c r="AP106">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ106">
         <v>0.42</v>
@@ -23140,7 +23140,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23346,7 +23346,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23758,7 +23758,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23964,7 +23964,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24170,7 +24170,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24376,7 +24376,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24454,7 +24454,7 @@
         <v>1.33</v>
       </c>
       <c r="AP113">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ113">
         <v>1.17</v>
@@ -24663,7 +24663,7 @@
         <v>2</v>
       </c>
       <c r="AQ114">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR114">
         <v>1.16</v>
@@ -24788,7 +24788,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24866,7 +24866,7 @@
         <v>1.43</v>
       </c>
       <c r="AP115">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ115">
         <v>1</v>
@@ -25075,7 +25075,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ116">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR116">
         <v>1.34</v>
@@ -25200,7 +25200,7 @@
         <v>127</v>
       </c>
       <c r="P117" t="s">
-        <v>266</v>
+        <v>209</v>
       </c>
       <c r="Q117">
         <v>2.88</v>
@@ -25281,7 +25281,7 @@
         <v>2</v>
       </c>
       <c r="AQ117">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR117">
         <v>1.93</v>
@@ -26308,7 +26308,7 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ122">
         <v>1.08</v>
@@ -26723,7 +26723,7 @@
         <v>2</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR124">
         <v>1.43</v>
@@ -26929,7 +26929,7 @@
         <v>1</v>
       </c>
       <c r="AQ125">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR125">
         <v>1.4</v>
@@ -27135,7 +27135,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ126">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR126">
         <v>1.38</v>
@@ -27753,7 +27753,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ129">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR129">
         <v>1.77</v>
@@ -27956,7 +27956,7 @@
         <v>0.63</v>
       </c>
       <c r="AP130">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ130">
         <v>0.42</v>
@@ -28084,7 +28084,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28290,7 +28290,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28986,7 +28986,7 @@
         <v>1</v>
       </c>
       <c r="AP135">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ135">
         <v>1.5</v>
@@ -29607,7 +29607,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ138">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR138">
         <v>1.66</v>
@@ -30556,7 +30556,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30762,7 +30762,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30843,7 +30843,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ144">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR144">
         <v>1.39</v>
@@ -31049,7 +31049,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ145">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR145">
         <v>1.39</v>
@@ -31252,7 +31252,7 @@
         <v>1.22</v>
       </c>
       <c r="AP146">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ146">
         <v>1</v>
@@ -31586,7 +31586,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31664,7 +31664,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ148">
         <v>1.33</v>
@@ -32076,10 +32076,10 @@
         <v>0.89</v>
       </c>
       <c r="AP150">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ150">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR150">
         <v>1.49</v>
@@ -33315,7 +33315,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ156">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR156">
         <v>1.39</v>
@@ -34139,7 +34139,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ160">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR160">
         <v>1.52</v>
@@ -34548,7 +34548,7 @@
         <v>1.6</v>
       </c>
       <c r="AP162">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ162">
         <v>1.38</v>
@@ -34757,7 +34757,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ163">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR163">
         <v>1.24</v>
@@ -35166,7 +35166,7 @@
         <v>1.3</v>
       </c>
       <c r="AP165">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ165">
         <v>1</v>
@@ -35990,10 +35990,10 @@
         <v>1.6</v>
       </c>
       <c r="AP169">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ169">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR169">
         <v>1.46</v>
@@ -36324,7 +36324,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -37435,7 +37435,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ176">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR176">
         <v>1.54</v>
@@ -38256,7 +38256,7 @@
         <v>0.73</v>
       </c>
       <c r="AP180">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ180">
         <v>0.85</v>
@@ -38668,7 +38668,7 @@
         <v>1.18</v>
       </c>
       <c r="AP182">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ182">
         <v>1</v>
@@ -38877,7 +38877,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ183">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR183">
         <v>1.63</v>
@@ -39080,7 +39080,7 @@
         <v>0.55</v>
       </c>
       <c r="AP184">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ184">
         <v>0.6899999999999999</v>
@@ -39289,7 +39289,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ185">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR185">
         <v>1.75</v>
@@ -39495,7 +39495,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ186">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR186">
         <v>1.23</v>
@@ -42043,6 +42043,624 @@
       </c>
       <c r="BP198">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7486687</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45694.45833333334</v>
+      </c>
+      <c r="F199">
+        <v>25</v>
+      </c>
+      <c r="G199" t="s">
+        <v>78</v>
+      </c>
+      <c r="H199" t="s">
+        <v>73</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>1</v>
+      </c>
+      <c r="N199">
+        <v>1</v>
+      </c>
+      <c r="O199" t="s">
+        <v>86</v>
+      </c>
+      <c r="P199" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q199">
+        <v>3.1</v>
+      </c>
+      <c r="R199">
+        <v>1.98</v>
+      </c>
+      <c r="S199">
+        <v>3.65</v>
+      </c>
+      <c r="T199">
+        <v>1.51</v>
+      </c>
+      <c r="U199">
+        <v>2.4</v>
+      </c>
+      <c r="V199">
+        <v>3.2</v>
+      </c>
+      <c r="W199">
+        <v>1.29</v>
+      </c>
+      <c r="X199">
+        <v>8</v>
+      </c>
+      <c r="Y199">
+        <v>1.04</v>
+      </c>
+      <c r="Z199">
+        <v>2.47</v>
+      </c>
+      <c r="AA199">
+        <v>3.07</v>
+      </c>
+      <c r="AB199">
+        <v>2.95</v>
+      </c>
+      <c r="AC199">
+        <v>1.06</v>
+      </c>
+      <c r="AD199">
+        <v>8.5</v>
+      </c>
+      <c r="AE199">
+        <v>1.41</v>
+      </c>
+      <c r="AF199">
+        <v>2.75</v>
+      </c>
+      <c r="AG199">
+        <v>2.25</v>
+      </c>
+      <c r="AH199">
+        <v>1.53</v>
+      </c>
+      <c r="AI199">
+        <v>1.91</v>
+      </c>
+      <c r="AJ199">
+        <v>1.8</v>
+      </c>
+      <c r="AK199">
+        <v>1.36</v>
+      </c>
+      <c r="AL199">
+        <v>1.34</v>
+      </c>
+      <c r="AM199">
+        <v>1.49</v>
+      </c>
+      <c r="AN199">
+        <v>1.42</v>
+      </c>
+      <c r="AO199">
+        <v>1</v>
+      </c>
+      <c r="AP199">
+        <v>1.31</v>
+      </c>
+      <c r="AQ199">
+        <v>1.15</v>
+      </c>
+      <c r="AR199">
+        <v>1.46</v>
+      </c>
+      <c r="AS199">
+        <v>1.26</v>
+      </c>
+      <c r="AT199">
+        <v>2.72</v>
+      </c>
+      <c r="AU199">
+        <v>2</v>
+      </c>
+      <c r="AV199">
+        <v>2</v>
+      </c>
+      <c r="AW199">
+        <v>9</v>
+      </c>
+      <c r="AX199">
+        <v>11</v>
+      </c>
+      <c r="AY199">
+        <v>12</v>
+      </c>
+      <c r="AZ199">
+        <v>15</v>
+      </c>
+      <c r="BA199">
+        <v>3</v>
+      </c>
+      <c r="BB199">
+        <v>5</v>
+      </c>
+      <c r="BC199">
+        <v>8</v>
+      </c>
+      <c r="BD199">
+        <v>1.88</v>
+      </c>
+      <c r="BE199">
+        <v>6.25</v>
+      </c>
+      <c r="BF199">
+        <v>2.15</v>
+      </c>
+      <c r="BG199">
+        <v>1.48</v>
+      </c>
+      <c r="BH199">
+        <v>2.4</v>
+      </c>
+      <c r="BI199">
+        <v>1.82</v>
+      </c>
+      <c r="BJ199">
+        <v>1.84</v>
+      </c>
+      <c r="BK199">
+        <v>2.33</v>
+      </c>
+      <c r="BL199">
+        <v>1.5</v>
+      </c>
+      <c r="BM199">
+        <v>3.05</v>
+      </c>
+      <c r="BN199">
+        <v>1.3</v>
+      </c>
+      <c r="BO199">
+        <v>4.1</v>
+      </c>
+      <c r="BP199">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7486682</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45694.54166666666</v>
+      </c>
+      <c r="F200">
+        <v>25</v>
+      </c>
+      <c r="G200" t="s">
+        <v>72</v>
+      </c>
+      <c r="H200" t="s">
+        <v>70</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>1</v>
+      </c>
+      <c r="L200">
+        <v>1</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>1</v>
+      </c>
+      <c r="O200" t="s">
+        <v>209</v>
+      </c>
+      <c r="P200" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q200">
+        <v>2.6</v>
+      </c>
+      <c r="R200">
+        <v>2.07</v>
+      </c>
+      <c r="S200">
+        <v>4.3</v>
+      </c>
+      <c r="T200">
+        <v>1.48</v>
+      </c>
+      <c r="U200">
+        <v>2.45</v>
+      </c>
+      <c r="V200">
+        <v>3.05</v>
+      </c>
+      <c r="W200">
+        <v>1.33</v>
+      </c>
+      <c r="X200">
+        <v>7</v>
+      </c>
+      <c r="Y200">
+        <v>1.06</v>
+      </c>
+      <c r="Z200">
+        <v>2.03</v>
+      </c>
+      <c r="AA200">
+        <v>3.33</v>
+      </c>
+      <c r="AB200">
+        <v>3.62</v>
+      </c>
+      <c r="AC200">
+        <v>1.05</v>
+      </c>
+      <c r="AD200">
+        <v>8</v>
+      </c>
+      <c r="AE200">
+        <v>1.36</v>
+      </c>
+      <c r="AF200">
+        <v>3</v>
+      </c>
+      <c r="AG200">
+        <v>2.05</v>
+      </c>
+      <c r="AH200">
+        <v>1.7</v>
+      </c>
+      <c r="AI200">
+        <v>1.84</v>
+      </c>
+      <c r="AJ200">
+        <v>1.83</v>
+      </c>
+      <c r="AK200">
+        <v>1.25</v>
+      </c>
+      <c r="AL200">
+        <v>1.29</v>
+      </c>
+      <c r="AM200">
+        <v>1.66</v>
+      </c>
+      <c r="AN200">
+        <v>1.75</v>
+      </c>
+      <c r="AO200">
+        <v>0.83</v>
+      </c>
+      <c r="AP200">
+        <v>1.85</v>
+      </c>
+      <c r="AQ200">
+        <v>0.77</v>
+      </c>
+      <c r="AR200">
+        <v>1.39</v>
+      </c>
+      <c r="AS200">
+        <v>1.27</v>
+      </c>
+      <c r="AT200">
+        <v>2.66</v>
+      </c>
+      <c r="AU200">
+        <v>5</v>
+      </c>
+      <c r="AV200">
+        <v>2</v>
+      </c>
+      <c r="AW200">
+        <v>13</v>
+      </c>
+      <c r="AX200">
+        <v>11</v>
+      </c>
+      <c r="AY200">
+        <v>24</v>
+      </c>
+      <c r="AZ200">
+        <v>17</v>
+      </c>
+      <c r="BA200">
+        <v>8</v>
+      </c>
+      <c r="BB200">
+        <v>7</v>
+      </c>
+      <c r="BC200">
+        <v>15</v>
+      </c>
+      <c r="BD200">
+        <v>0</v>
+      </c>
+      <c r="BE200">
+        <v>0</v>
+      </c>
+      <c r="BF200">
+        <v>0</v>
+      </c>
+      <c r="BG200">
+        <v>0</v>
+      </c>
+      <c r="BH200">
+        <v>0</v>
+      </c>
+      <c r="BI200">
+        <v>0</v>
+      </c>
+      <c r="BJ200">
+        <v>0</v>
+      </c>
+      <c r="BK200">
+        <v>0</v>
+      </c>
+      <c r="BL200">
+        <v>0</v>
+      </c>
+      <c r="BM200">
+        <v>0</v>
+      </c>
+      <c r="BN200">
+        <v>0</v>
+      </c>
+      <c r="BO200">
+        <v>0</v>
+      </c>
+      <c r="BP200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7486685</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45694.64583333334</v>
+      </c>
+      <c r="F201">
+        <v>25</v>
+      </c>
+      <c r="G201" t="s">
+        <v>77</v>
+      </c>
+      <c r="H201" t="s">
+        <v>74</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
+      </c>
+      <c r="N201">
+        <v>0</v>
+      </c>
+      <c r="O201" t="s">
+        <v>86</v>
+      </c>
+      <c r="P201" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q201">
+        <v>4.8</v>
+      </c>
+      <c r="R201">
+        <v>2.08</v>
+      </c>
+      <c r="S201">
+        <v>2.43</v>
+      </c>
+      <c r="T201">
+        <v>1.46</v>
+      </c>
+      <c r="U201">
+        <v>2.55</v>
+      </c>
+      <c r="V201">
+        <v>2.85</v>
+      </c>
+      <c r="W201">
+        <v>1.37</v>
+      </c>
+      <c r="X201">
+        <v>7</v>
+      </c>
+      <c r="Y201">
+        <v>1.07</v>
+      </c>
+      <c r="Z201">
+        <v>4.2</v>
+      </c>
+      <c r="AA201">
+        <v>3.45</v>
+      </c>
+      <c r="AB201">
+        <v>1.85</v>
+      </c>
+      <c r="AC201">
+        <v>1.05</v>
+      </c>
+      <c r="AD201">
+        <v>8</v>
+      </c>
+      <c r="AE201">
+        <v>1.36</v>
+      </c>
+      <c r="AF201">
+        <v>2.95</v>
+      </c>
+      <c r="AG201">
+        <v>2.05</v>
+      </c>
+      <c r="AH201">
+        <v>1.7</v>
+      </c>
+      <c r="AI201">
+        <v>1.94</v>
+      </c>
+      <c r="AJ201">
+        <v>1.77</v>
+      </c>
+      <c r="AK201">
+        <v>1.85</v>
+      </c>
+      <c r="AL201">
+        <v>1.27</v>
+      </c>
+      <c r="AM201">
+        <v>1.21</v>
+      </c>
+      <c r="AN201">
+        <v>1.75</v>
+      </c>
+      <c r="AO201">
+        <v>1.83</v>
+      </c>
+      <c r="AP201">
+        <v>1.69</v>
+      </c>
+      <c r="AQ201">
+        <v>1.77</v>
+      </c>
+      <c r="AR201">
+        <v>1.3</v>
+      </c>
+      <c r="AS201">
+        <v>1.57</v>
+      </c>
+      <c r="AT201">
+        <v>2.87</v>
+      </c>
+      <c r="AU201">
+        <v>0</v>
+      </c>
+      <c r="AV201">
+        <v>7</v>
+      </c>
+      <c r="AW201">
+        <v>12</v>
+      </c>
+      <c r="AX201">
+        <v>6</v>
+      </c>
+      <c r="AY201">
+        <v>13</v>
+      </c>
+      <c r="AZ201">
+        <v>15</v>
+      </c>
+      <c r="BA201">
+        <v>1</v>
+      </c>
+      <c r="BB201">
+        <v>6</v>
+      </c>
+      <c r="BC201">
+        <v>7</v>
+      </c>
+      <c r="BD201">
+        <v>0</v>
+      </c>
+      <c r="BE201">
+        <v>0</v>
+      </c>
+      <c r="BF201">
+        <v>0</v>
+      </c>
+      <c r="BG201">
+        <v>0</v>
+      </c>
+      <c r="BH201">
+        <v>0</v>
+      </c>
+      <c r="BI201">
+        <v>0</v>
+      </c>
+      <c r="BJ201">
+        <v>0</v>
+      </c>
+      <c r="BK201">
+        <v>0</v>
+      </c>
+      <c r="BL201">
+        <v>0</v>
+      </c>
+      <c r="BM201">
+        <v>0</v>
+      </c>
+      <c r="BN201">
+        <v>0</v>
+      </c>
+      <c r="BO201">
+        <v>0</v>
+      </c>
+      <c r="BP201">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="294">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -646,6 +646,9 @@
     <t>['17']</t>
   </si>
   <si>
+    <t>['11']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -1254,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP201"/>
+  <dimension ref="A1:BP202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1510,7 +1513,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -2540,7 +2543,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2621,7 +2624,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2746,7 +2749,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2824,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -3364,7 +3367,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3570,7 +3573,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3776,7 +3779,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3982,7 +3985,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4188,7 +4191,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4394,7 +4397,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4806,7 +4809,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -5012,7 +5015,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5218,7 +5221,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5505,7 +5508,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ21">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -5630,7 +5633,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5836,7 +5839,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -7278,7 +7281,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7484,7 +7487,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7690,7 +7693,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7896,7 +7899,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8102,7 +8105,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8308,7 +8311,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8720,7 +8723,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9338,7 +9341,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9419,7 +9422,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ40">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9544,7 +9547,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9750,7 +9753,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10034,7 +10037,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ43">
         <v>1.15</v>
@@ -10449,7 +10452,7 @@
         <v>2</v>
       </c>
       <c r="AQ45">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR45">
         <v>1.51</v>
@@ -10780,7 +10783,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11192,7 +11195,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -12222,7 +12225,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12428,7 +12431,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12840,7 +12843,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13252,7 +13255,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13330,7 +13333,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ59">
         <v>1.17</v>
@@ -13458,7 +13461,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13870,7 +13873,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14157,7 +14160,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -14900,7 +14903,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15312,7 +15315,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15518,7 +15521,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15724,7 +15727,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15930,7 +15933,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16008,7 +16011,7 @@
         <v>0.8</v>
       </c>
       <c r="AP72">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ72">
         <v>0.42</v>
@@ -16217,7 +16220,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ73">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR73">
         <v>1.51</v>
@@ -16548,7 +16551,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16754,7 +16757,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16960,7 +16963,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17372,7 +17375,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17784,7 +17787,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18196,7 +18199,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18814,7 +18817,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19513,7 +19516,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ89">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR89">
         <v>1.6</v>
@@ -19638,7 +19641,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19844,7 +19847,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20050,7 +20053,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20256,7 +20259,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20540,7 +20543,7 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20668,7 +20671,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -21904,7 +21907,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22522,7 +22525,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -23140,7 +23143,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23221,7 +23224,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ107">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR107">
         <v>1.21</v>
@@ -23346,7 +23349,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23758,7 +23761,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23836,7 +23839,7 @@
         <v>1.63</v>
       </c>
       <c r="AP110">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ110">
         <v>1.38</v>
@@ -23964,7 +23967,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24170,7 +24173,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24376,7 +24379,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24788,7 +24791,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -26024,7 +26027,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26230,7 +26233,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -27054,7 +27057,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27750,7 +27753,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ129">
         <v>1.77</v>
@@ -28084,7 +28087,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28290,7 +28293,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28496,7 +28499,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28989,7 +28992,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ135">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR135">
         <v>1.36</v>
@@ -29192,7 +29195,7 @@
         <v>0.57</v>
       </c>
       <c r="AP136">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ136">
         <v>0.42</v>
@@ -29320,7 +29323,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29604,7 +29607,7 @@
         <v>0.88</v>
       </c>
       <c r="AP138">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ138">
         <v>0.77</v>
@@ -29938,7 +29941,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30350,7 +30353,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30556,7 +30559,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30762,7 +30765,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30968,7 +30971,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31380,7 +31383,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31461,7 +31464,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ147">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR147">
         <v>1.41</v>
@@ -31586,7 +31589,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31792,7 +31795,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -31998,7 +32001,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32616,7 +32619,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32822,7 +32825,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -32900,7 +32903,7 @@
         <v>0.44</v>
       </c>
       <c r="AP154">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ154">
         <v>0.85</v>
@@ -33440,7 +33443,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33646,7 +33649,7 @@
         <v>187</v>
       </c>
       <c r="P158" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q158">
         <v>2.63</v>
@@ -34882,7 +34885,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35294,7 +35297,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35912,7 +35915,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36118,7 +36121,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36324,7 +36327,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36530,7 +36533,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -37020,7 +37023,7 @@
         <v>1.7</v>
       </c>
       <c r="AP174">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ174">
         <v>1.58</v>
@@ -37229,7 +37232,7 @@
         <v>2</v>
       </c>
       <c r="AQ175">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR175">
         <v>1.78</v>
@@ -37560,7 +37563,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -38178,7 +38181,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38796,7 +38799,7 @@
         <v>86</v>
       </c>
       <c r="P183" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q183">
         <v>5.2</v>
@@ -39620,7 +39623,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -39701,7 +39704,7 @@
         <v>1</v>
       </c>
       <c r="AQ187">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR187">
         <v>1.38</v>
@@ -39904,7 +39907,7 @@
         <v>1.09</v>
       </c>
       <c r="AP188">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ188">
         <v>1.08</v>
@@ -40032,7 +40035,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40238,7 +40241,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40444,7 +40447,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40856,7 +40859,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -41062,7 +41065,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -42660,6 +42663,212 @@
         <v>0</v>
       </c>
       <c r="BP201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7486690</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45695.625</v>
+      </c>
+      <c r="F202">
+        <v>26</v>
+      </c>
+      <c r="G202" t="s">
+        <v>76</v>
+      </c>
+      <c r="H202" t="s">
+        <v>83</v>
+      </c>
+      <c r="I202">
+        <v>1</v>
+      </c>
+      <c r="J202">
+        <v>1</v>
+      </c>
+      <c r="K202">
+        <v>2</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="M202">
+        <v>1</v>
+      </c>
+      <c r="N202">
+        <v>2</v>
+      </c>
+      <c r="O202" t="s">
+        <v>210</v>
+      </c>
+      <c r="P202" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q202">
+        <v>3.75</v>
+      </c>
+      <c r="R202">
+        <v>1.95</v>
+      </c>
+      <c r="S202">
+        <v>3.4</v>
+      </c>
+      <c r="T202">
+        <v>1.53</v>
+      </c>
+      <c r="U202">
+        <v>2.38</v>
+      </c>
+      <c r="V202">
+        <v>3.75</v>
+      </c>
+      <c r="W202">
+        <v>1.25</v>
+      </c>
+      <c r="X202">
+        <v>11</v>
+      </c>
+      <c r="Y202">
+        <v>1.05</v>
+      </c>
+      <c r="Z202">
+        <v>3.33</v>
+      </c>
+      <c r="AA202">
+        <v>3.09</v>
+      </c>
+      <c r="AB202">
+        <v>2.24</v>
+      </c>
+      <c r="AC202">
+        <v>0</v>
+      </c>
+      <c r="AD202">
+        <v>0</v>
+      </c>
+      <c r="AE202">
+        <v>0</v>
+      </c>
+      <c r="AF202">
+        <v>0</v>
+      </c>
+      <c r="AG202">
+        <v>2.3</v>
+      </c>
+      <c r="AH202">
+        <v>1.5</v>
+      </c>
+      <c r="AI202">
+        <v>2</v>
+      </c>
+      <c r="AJ202">
+        <v>1.73</v>
+      </c>
+      <c r="AK202">
+        <v>1.54</v>
+      </c>
+      <c r="AL202">
+        <v>1.32</v>
+      </c>
+      <c r="AM202">
+        <v>1.29</v>
+      </c>
+      <c r="AN202">
+        <v>1.17</v>
+      </c>
+      <c r="AO202">
+        <v>1.5</v>
+      </c>
+      <c r="AP202">
+        <v>1.15</v>
+      </c>
+      <c r="AQ202">
+        <v>1.46</v>
+      </c>
+      <c r="AR202">
+        <v>1.75</v>
+      </c>
+      <c r="AS202">
+        <v>1.21</v>
+      </c>
+      <c r="AT202">
+        <v>2.96</v>
+      </c>
+      <c r="AU202">
+        <v>4</v>
+      </c>
+      <c r="AV202">
+        <v>2</v>
+      </c>
+      <c r="AW202">
+        <v>8</v>
+      </c>
+      <c r="AX202">
+        <v>3</v>
+      </c>
+      <c r="AY202">
+        <v>18</v>
+      </c>
+      <c r="AZ202">
+        <v>5</v>
+      </c>
+      <c r="BA202">
+        <v>3</v>
+      </c>
+      <c r="BB202">
+        <v>1</v>
+      </c>
+      <c r="BC202">
+        <v>4</v>
+      </c>
+      <c r="BD202">
+        <v>0</v>
+      </c>
+      <c r="BE202">
+        <v>0</v>
+      </c>
+      <c r="BF202">
+        <v>0</v>
+      </c>
+      <c r="BG202">
+        <v>0</v>
+      </c>
+      <c r="BH202">
+        <v>0</v>
+      </c>
+      <c r="BI202">
+        <v>0</v>
+      </c>
+      <c r="BJ202">
+        <v>0</v>
+      </c>
+      <c r="BK202">
+        <v>0</v>
+      </c>
+      <c r="BL202">
+        <v>0</v>
+      </c>
+      <c r="BM202">
+        <v>0</v>
+      </c>
+      <c r="BN202">
+        <v>0</v>
+      </c>
+      <c r="BO202">
+        <v>0</v>
+      </c>
+      <c r="BP202">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="295">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -897,6 +897,9 @@
   <si>
     <t>['14', '72']</t>
   </si>
+  <si>
+    <t>['76']</t>
+  </si>
 </sst>
 </file>
 
@@ -1257,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP202"/>
+  <dimension ref="A1:BP204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1800,7 +1803,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ3">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -3445,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ11">
         <v>1.77</v>
@@ -4681,7 +4684,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ17">
         <v>0.77</v>
@@ -5920,7 +5923,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ23">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR23">
         <v>2</v>
@@ -6535,7 +6538,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ26">
         <v>0.85</v>
@@ -7565,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ31">
         <v>1.15</v>
@@ -8804,7 +8807,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR37">
         <v>1.39</v>
@@ -9625,7 +9628,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ41">
         <v>1.17</v>
@@ -11688,7 +11691,7 @@
         <v>2</v>
       </c>
       <c r="AQ51">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR51">
         <v>1.33</v>
@@ -12715,7 +12718,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ56">
         <v>1.08</v>
@@ -13951,7 +13954,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ62">
         <v>0.42</v>
@@ -15190,7 +15193,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ68">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR68">
         <v>1.66</v>
@@ -16217,7 +16220,7 @@
         <v>0.6</v>
       </c>
       <c r="AP73">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ73">
         <v>1.46</v>
@@ -17044,7 +17047,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ77">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR77">
         <v>1.36</v>
@@ -17453,7 +17456,7 @@
         <v>1.2</v>
       </c>
       <c r="AP79">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -19719,7 +19722,7 @@
         <v>1.71</v>
       </c>
       <c r="AP90">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ90">
         <v>1.38</v>
@@ -20131,10 +20134,10 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ92">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR92">
         <v>1.5</v>
@@ -23427,7 +23430,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -24048,7 +24051,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ111">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR111">
         <v>1.65</v>
@@ -25487,7 +25490,7 @@
         <v>0.71</v>
       </c>
       <c r="AP118">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ118">
         <v>0.6899999999999999</v>
@@ -25899,7 +25902,7 @@
         <v>0.63</v>
       </c>
       <c r="AP120">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ120">
         <v>0.6899999999999999</v>
@@ -26929,7 +26932,7 @@
         <v>0.57</v>
       </c>
       <c r="AP125">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ125">
         <v>0.77</v>
@@ -27547,7 +27550,7 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ128">
         <v>1.58</v>
@@ -29404,7 +29407,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ137">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR137">
         <v>1.59</v>
@@ -30019,7 +30022,7 @@
         <v>0.13</v>
       </c>
       <c r="AP140">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ140">
         <v>0.85</v>
@@ -31049,7 +31052,7 @@
         <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ145">
         <v>1.77</v>
@@ -31670,7 +31673,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ148">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR148">
         <v>1.32</v>
@@ -33315,7 +33318,7 @@
         <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ156">
         <v>1.15</v>
@@ -33933,7 +33936,7 @@
         <v>1.78</v>
       </c>
       <c r="AP159">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ159">
         <v>1.58</v>
@@ -34966,7 +34969,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ164">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR164">
         <v>1.45</v>
@@ -36199,7 +36202,7 @@
         <v>1.2</v>
       </c>
       <c r="AP170">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ170">
         <v>1.08</v>
@@ -36817,7 +36820,7 @@
         <v>1.3</v>
       </c>
       <c r="AP173">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ173">
         <v>1.17</v>
@@ -38468,7 +38471,7 @@
         <v>2</v>
       </c>
       <c r="AQ181">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR181">
         <v>1.62</v>
@@ -39701,7 +39704,7 @@
         <v>1.36</v>
       </c>
       <c r="AP187">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ187">
         <v>1.46</v>
@@ -40113,7 +40116,7 @@
         <v>0.45</v>
       </c>
       <c r="AP189">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ189">
         <v>0.42</v>
@@ -42869,6 +42872,418 @@
         <v>0</v>
       </c>
       <c r="BP202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7486692</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45696.45833333334</v>
+      </c>
+      <c r="F203">
+        <v>26</v>
+      </c>
+      <c r="G203" t="s">
+        <v>79</v>
+      </c>
+      <c r="H203" t="s">
+        <v>80</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="M203">
+        <v>1</v>
+      </c>
+      <c r="N203">
+        <v>1</v>
+      </c>
+      <c r="O203" t="s">
+        <v>86</v>
+      </c>
+      <c r="P203" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q203">
+        <v>6</v>
+      </c>
+      <c r="R203">
+        <v>2.2</v>
+      </c>
+      <c r="S203">
+        <v>2.2</v>
+      </c>
+      <c r="T203">
+        <v>1.4</v>
+      </c>
+      <c r="U203">
+        <v>2.75</v>
+      </c>
+      <c r="V203">
+        <v>2.75</v>
+      </c>
+      <c r="W203">
+        <v>1.4</v>
+      </c>
+      <c r="X203">
+        <v>8</v>
+      </c>
+      <c r="Y203">
+        <v>1.08</v>
+      </c>
+      <c r="Z203">
+        <v>4.1</v>
+      </c>
+      <c r="AA203">
+        <v>3.29</v>
+      </c>
+      <c r="AB203">
+        <v>1.91</v>
+      </c>
+      <c r="AC203">
+        <v>0</v>
+      </c>
+      <c r="AD203">
+        <v>0</v>
+      </c>
+      <c r="AE203">
+        <v>2.88</v>
+      </c>
+      <c r="AF203">
+        <v>1.41</v>
+      </c>
+      <c r="AG203">
+        <v>2.13</v>
+      </c>
+      <c r="AH203">
+        <v>1.65</v>
+      </c>
+      <c r="AI203">
+        <v>1.91</v>
+      </c>
+      <c r="AJ203">
+        <v>1.8</v>
+      </c>
+      <c r="AK203">
+        <v>0</v>
+      </c>
+      <c r="AL203">
+        <v>0</v>
+      </c>
+      <c r="AM203">
+        <v>0</v>
+      </c>
+      <c r="AN203">
+        <v>1</v>
+      </c>
+      <c r="AO203">
+        <v>1.33</v>
+      </c>
+      <c r="AP203">
+        <v>0.92</v>
+      </c>
+      <c r="AQ203">
+        <v>1.46</v>
+      </c>
+      <c r="AR203">
+        <v>1.35</v>
+      </c>
+      <c r="AS203">
+        <v>1.54</v>
+      </c>
+      <c r="AT203">
+        <v>2.89</v>
+      </c>
+      <c r="AU203">
+        <v>2</v>
+      </c>
+      <c r="AV203">
+        <v>8</v>
+      </c>
+      <c r="AW203">
+        <v>10</v>
+      </c>
+      <c r="AX203">
+        <v>9</v>
+      </c>
+      <c r="AY203">
+        <v>13</v>
+      </c>
+      <c r="AZ203">
+        <v>20</v>
+      </c>
+      <c r="BA203">
+        <v>2</v>
+      </c>
+      <c r="BB203">
+        <v>4</v>
+      </c>
+      <c r="BC203">
+        <v>6</v>
+      </c>
+      <c r="BD203">
+        <v>0</v>
+      </c>
+      <c r="BE203">
+        <v>0</v>
+      </c>
+      <c r="BF203">
+        <v>0</v>
+      </c>
+      <c r="BG203">
+        <v>0</v>
+      </c>
+      <c r="BH203">
+        <v>0</v>
+      </c>
+      <c r="BI203">
+        <v>0</v>
+      </c>
+      <c r="BJ203">
+        <v>0</v>
+      </c>
+      <c r="BK203">
+        <v>0</v>
+      </c>
+      <c r="BL203">
+        <v>0</v>
+      </c>
+      <c r="BM203">
+        <v>0</v>
+      </c>
+      <c r="BN203">
+        <v>0</v>
+      </c>
+      <c r="BO203">
+        <v>0</v>
+      </c>
+      <c r="BP203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7486691</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45696.58333333334</v>
+      </c>
+      <c r="F204">
+        <v>26</v>
+      </c>
+      <c r="G204" t="s">
+        <v>85</v>
+      </c>
+      <c r="H204" t="s">
+        <v>81</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>2</v>
+      </c>
+      <c r="O204" t="s">
+        <v>195</v>
+      </c>
+      <c r="P204" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q204">
+        <v>4</v>
+      </c>
+      <c r="R204">
+        <v>1.91</v>
+      </c>
+      <c r="S204">
+        <v>3.25</v>
+      </c>
+      <c r="T204">
+        <v>1.57</v>
+      </c>
+      <c r="U204">
+        <v>2.25</v>
+      </c>
+      <c r="V204">
+        <v>3.75</v>
+      </c>
+      <c r="W204">
+        <v>1.25</v>
+      </c>
+      <c r="X204">
+        <v>13</v>
+      </c>
+      <c r="Y204">
+        <v>1.04</v>
+      </c>
+      <c r="Z204">
+        <v>3.57</v>
+      </c>
+      <c r="AA204">
+        <v>3.09</v>
+      </c>
+      <c r="AB204">
+        <v>2.14</v>
+      </c>
+      <c r="AC204">
+        <v>0</v>
+      </c>
+      <c r="AD204">
+        <v>0</v>
+      </c>
+      <c r="AE204">
+        <v>1.5</v>
+      </c>
+      <c r="AF204">
+        <v>2.45</v>
+      </c>
+      <c r="AG204">
+        <v>2.55</v>
+      </c>
+      <c r="AH204">
+        <v>1.49</v>
+      </c>
+      <c r="AI204">
+        <v>2.2</v>
+      </c>
+      <c r="AJ204">
+        <v>1.62</v>
+      </c>
+      <c r="AK204">
+        <v>0</v>
+      </c>
+      <c r="AL204">
+        <v>0</v>
+      </c>
+      <c r="AM204">
+        <v>0</v>
+      </c>
+      <c r="AN204">
+        <v>1.25</v>
+      </c>
+      <c r="AO204">
+        <v>1</v>
+      </c>
+      <c r="AP204">
+        <v>1.23</v>
+      </c>
+      <c r="AQ204">
+        <v>1</v>
+      </c>
+      <c r="AR204">
+        <v>1.36</v>
+      </c>
+      <c r="AS204">
+        <v>1.42</v>
+      </c>
+      <c r="AT204">
+        <v>2.78</v>
+      </c>
+      <c r="AU204">
+        <v>4</v>
+      </c>
+      <c r="AV204">
+        <v>3</v>
+      </c>
+      <c r="AW204">
+        <v>8</v>
+      </c>
+      <c r="AX204">
+        <v>13</v>
+      </c>
+      <c r="AY204">
+        <v>13</v>
+      </c>
+      <c r="AZ204">
+        <v>22</v>
+      </c>
+      <c r="BA204">
+        <v>3</v>
+      </c>
+      <c r="BB204">
+        <v>4</v>
+      </c>
+      <c r="BC204">
+        <v>7</v>
+      </c>
+      <c r="BD204">
+        <v>0</v>
+      </c>
+      <c r="BE204">
+        <v>0</v>
+      </c>
+      <c r="BF204">
+        <v>0</v>
+      </c>
+      <c r="BG204">
+        <v>0</v>
+      </c>
+      <c r="BH204">
+        <v>0</v>
+      </c>
+      <c r="BI204">
+        <v>0</v>
+      </c>
+      <c r="BJ204">
+        <v>0</v>
+      </c>
+      <c r="BK204">
+        <v>0</v>
+      </c>
+      <c r="BL204">
+        <v>0</v>
+      </c>
+      <c r="BM204">
+        <v>0</v>
+      </c>
+      <c r="BN204">
+        <v>0</v>
+      </c>
+      <c r="BO204">
+        <v>0</v>
+      </c>
+      <c r="BP204">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="298">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -649,6 +649,12 @@
     <t>['11']</t>
   </si>
   <si>
+    <t>['61', '77']</t>
+  </si>
+  <si>
+    <t>['8', '15', '27']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -899,6 +905,9 @@
   </si>
   <si>
     <t>['76']</t>
+  </si>
+  <si>
+    <t>['90', '90+6']</t>
   </si>
 </sst>
 </file>
@@ -1260,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP204"/>
+  <dimension ref="A1:BP207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1516,7 +1525,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1800,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ3">
         <v>1.46</v>
@@ -2009,7 +2018,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ4">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2418,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ6">
         <v>1.38</v>
@@ -2546,7 +2555,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2752,7 +2761,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3370,7 +3379,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3576,7 +3585,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3782,7 +3791,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3988,7 +3997,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4066,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ14">
         <v>0.85</v>
@@ -4194,7 +4203,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4275,7 +4284,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4400,7 +4409,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4481,7 +4490,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ16">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4812,7 +4821,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -4890,7 +4899,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -5018,7 +5027,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5096,7 +5105,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5224,7 +5233,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5636,7 +5645,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5842,7 +5851,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6953,7 +6962,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ28">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -7159,7 +7168,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR29">
         <v>2.09</v>
@@ -7284,7 +7293,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7490,7 +7499,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7696,7 +7705,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7777,7 +7786,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.69</v>
@@ -7902,7 +7911,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -7980,7 +7989,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ33">
         <v>0.77</v>
@@ -8108,7 +8117,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8186,7 +8195,7 @@
         <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ34">
         <v>0.6899999999999999</v>
@@ -8314,7 +8323,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8726,7 +8735,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9344,7 +9353,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9550,7 +9559,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9631,7 +9640,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ41">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR41">
         <v>1.24</v>
@@ -9756,7 +9765,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10246,10 +10255,10 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ44">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR44">
         <v>2.23</v>
@@ -10658,10 +10667,10 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ46">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR46">
         <v>1.57</v>
@@ -10786,7 +10795,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11198,7 +11207,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -12100,7 +12109,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ53">
         <v>1.77</v>
@@ -12228,7 +12237,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12434,7 +12443,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12721,7 +12730,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ56">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>1.46</v>
@@ -12846,7 +12855,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -12924,10 +12933,10 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ57">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR57">
         <v>1.23</v>
@@ -13258,7 +13267,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13339,7 +13348,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ59">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR59">
         <v>1.8</v>
@@ -13464,7 +13473,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13748,7 +13757,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ61">
         <v>1.15</v>
@@ -13876,7 +13885,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14160,7 +14169,7 @@
         <v>0.75</v>
       </c>
       <c r="AP63">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ63">
         <v>1.46</v>
@@ -14906,7 +14915,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15318,7 +15327,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15524,7 +15533,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15730,7 +15739,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15936,7 +15945,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16426,7 +16435,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ74">
         <v>1.58</v>
@@ -16554,7 +16563,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16632,10 +16641,10 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ75">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR75">
         <v>2.05</v>
@@ -16760,7 +16769,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16841,7 +16850,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ76">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR76">
         <v>1.67</v>
@@ -16966,7 +16975,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17044,7 +17053,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ77">
         <v>1.46</v>
@@ -17253,7 +17262,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ78">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR78">
         <v>1.54</v>
@@ -17378,7 +17387,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17790,7 +17799,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18202,7 +18211,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18820,7 +18829,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19313,7 +19322,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ88">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR88">
         <v>1.66</v>
@@ -19644,7 +19653,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19850,7 +19859,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -19931,7 +19940,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ91">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR91">
         <v>1.87</v>
@@ -20056,7 +20065,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20262,7 +20271,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20340,10 +20349,10 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ93">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>1.25</v>
@@ -20674,7 +20683,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20752,7 +20761,7 @@
         <v>0.83</v>
       </c>
       <c r="AP95">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ95">
         <v>0.42</v>
@@ -21164,7 +21173,7 @@
         <v>1.67</v>
       </c>
       <c r="AP97">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ97">
         <v>1</v>
@@ -21910,7 +21919,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22528,7 +22537,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22609,7 +22618,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ104">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR104">
         <v>1.78</v>
@@ -23021,7 +23030,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ106">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR106">
         <v>1.16</v>
@@ -23146,7 +23155,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23224,7 +23233,7 @@
         <v>0.71</v>
       </c>
       <c r="AP107">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ107">
         <v>1.46</v>
@@ -23352,7 +23361,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23636,7 +23645,7 @@
         <v>1.29</v>
       </c>
       <c r="AP109">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -23764,7 +23773,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23970,7 +23979,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24176,7 +24185,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24382,7 +24391,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24463,7 +24472,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ113">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR113">
         <v>1.54</v>
@@ -24794,7 +24803,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -25078,7 +25087,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ116">
         <v>0.77</v>
@@ -26030,7 +26039,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26236,7 +26245,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26317,7 +26326,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ122">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR122">
         <v>1.54</v>
@@ -27060,7 +27069,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27138,7 +27147,7 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ126">
         <v>1.77</v>
@@ -27347,7 +27356,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ127">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR127">
         <v>1.4</v>
@@ -28090,7 +28099,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28296,7 +28305,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28374,7 +28383,7 @@
         <v>1.78</v>
       </c>
       <c r="AP132">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ132">
         <v>1.38</v>
@@ -28502,7 +28511,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28786,7 +28795,7 @@
         <v>1.25</v>
       </c>
       <c r="AP134">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ134">
         <v>1</v>
@@ -29201,7 +29210,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ136">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR136">
         <v>1.72</v>
@@ -29326,7 +29335,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29819,7 +29828,7 @@
         <v>2</v>
       </c>
       <c r="AQ139">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR139">
         <v>1.55</v>
@@ -29944,7 +29953,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30231,7 +30240,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ141">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR141">
         <v>1.41</v>
@@ -30356,7 +30365,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30437,7 +30446,7 @@
         <v>2</v>
       </c>
       <c r="AQ142">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR142">
         <v>1.14</v>
@@ -30562,7 +30571,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30768,7 +30777,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30846,7 +30855,7 @@
         <v>0.75</v>
       </c>
       <c r="AP144">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ144">
         <v>1.15</v>
@@ -30974,7 +30983,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31386,7 +31395,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31592,7 +31601,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31798,7 +31807,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32004,7 +32013,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32288,7 +32297,7 @@
         <v>0.67</v>
       </c>
       <c r="AP151">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ151">
         <v>0.6899999999999999</v>
@@ -32494,7 +32503,7 @@
         <v>1.44</v>
       </c>
       <c r="AP152">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ152">
         <v>1</v>
@@ -32622,7 +32631,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32700,7 +32709,7 @@
         <v>2</v>
       </c>
       <c r="AP153">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ153">
         <v>1.58</v>
@@ -32828,7 +32837,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33115,7 +33124,7 @@
         <v>2</v>
       </c>
       <c r="AQ155">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR155">
         <v>1.16</v>
@@ -33446,7 +33455,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33527,7 +33536,7 @@
         <v>2</v>
       </c>
       <c r="AQ157">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR157">
         <v>1.79</v>
@@ -33652,7 +33661,7 @@
         <v>187</v>
       </c>
       <c r="P158" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q158">
         <v>2.63</v>
@@ -33730,10 +33739,10 @@
         <v>1.44</v>
       </c>
       <c r="AP158">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ158">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR158">
         <v>1.5</v>
@@ -34760,7 +34769,7 @@
         <v>0.9</v>
       </c>
       <c r="AP163">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ163">
         <v>0.77</v>
@@ -34888,7 +34897,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35300,7 +35309,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35918,7 +35927,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36124,7 +36133,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36205,7 +36214,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ170">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR170">
         <v>1.38</v>
@@ -36330,7 +36339,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36408,7 +36417,7 @@
         <v>0.7</v>
       </c>
       <c r="AP171">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ171">
         <v>0.85</v>
@@ -36536,7 +36545,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36614,7 +36623,7 @@
         <v>0.5</v>
       </c>
       <c r="AP172">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ172">
         <v>0.42</v>
@@ -36823,7 +36832,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ173">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR173">
         <v>1.4</v>
@@ -37566,7 +37575,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -37647,7 +37656,7 @@
         <v>2</v>
       </c>
       <c r="AQ177">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR177">
         <v>1.54</v>
@@ -38184,7 +38193,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38802,7 +38811,7 @@
         <v>86</v>
       </c>
       <c r="P183" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q183">
         <v>5.2</v>
@@ -39498,7 +39507,7 @@
         <v>1</v>
       </c>
       <c r="AP186">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ186">
         <v>1.15</v>
@@ -39626,7 +39635,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -39913,7 +39922,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ188">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR188">
         <v>1.69</v>
@@ -40038,7 +40047,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40244,7 +40253,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40322,7 +40331,7 @@
         <v>1.09</v>
       </c>
       <c r="AP190">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ190">
         <v>1</v>
@@ -40450,7 +40459,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40531,7 +40540,7 @@
         <v>2</v>
       </c>
       <c r="AQ191">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR191">
         <v>1.78</v>
@@ -40734,7 +40743,7 @@
         <v>1.64</v>
       </c>
       <c r="AP192">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ192">
         <v>1.58</v>
@@ -40862,7 +40871,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -40943,7 +40952,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ193">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR193">
         <v>1.72</v>
@@ -41068,7 +41077,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -42716,7 +42725,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -42922,7 +42931,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43285,6 +43294,624 @@
       </c>
       <c r="BP204">
         <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7486990</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45697.39583333334</v>
+      </c>
+      <c r="F205">
+        <v>26</v>
+      </c>
+      <c r="G205" t="s">
+        <v>71</v>
+      </c>
+      <c r="H205" t="s">
+        <v>77</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>1</v>
+      </c>
+      <c r="M205">
+        <v>1</v>
+      </c>
+      <c r="N205">
+        <v>2</v>
+      </c>
+      <c r="O205" t="s">
+        <v>130</v>
+      </c>
+      <c r="P205" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q205">
+        <v>3.1</v>
+      </c>
+      <c r="R205">
+        <v>1.91</v>
+      </c>
+      <c r="S205">
+        <v>4.33</v>
+      </c>
+      <c r="T205">
+        <v>1.57</v>
+      </c>
+      <c r="U205">
+        <v>2.25</v>
+      </c>
+      <c r="V205">
+        <v>3.75</v>
+      </c>
+      <c r="W205">
+        <v>1.25</v>
+      </c>
+      <c r="X205">
+        <v>13</v>
+      </c>
+      <c r="Y205">
+        <v>1.04</v>
+      </c>
+      <c r="Z205">
+        <v>2.48</v>
+      </c>
+      <c r="AA205">
+        <v>3.1</v>
+      </c>
+      <c r="AB205">
+        <v>2.91</v>
+      </c>
+      <c r="AC205">
+        <v>1.11</v>
+      </c>
+      <c r="AD205">
+        <v>6.2</v>
+      </c>
+      <c r="AE205">
+        <v>1.48</v>
+      </c>
+      <c r="AF205">
+        <v>2.37</v>
+      </c>
+      <c r="AG205">
+        <v>2.69</v>
+      </c>
+      <c r="AH205">
+        <v>1.41</v>
+      </c>
+      <c r="AI205">
+        <v>2.2</v>
+      </c>
+      <c r="AJ205">
+        <v>1.62</v>
+      </c>
+      <c r="AK205">
+        <v>1.3</v>
+      </c>
+      <c r="AL205">
+        <v>1.38</v>
+      </c>
+      <c r="AM205">
+        <v>1.58</v>
+      </c>
+      <c r="AN205">
+        <v>1.67</v>
+      </c>
+      <c r="AO205">
+        <v>1.17</v>
+      </c>
+      <c r="AP205">
+        <v>1.62</v>
+      </c>
+      <c r="AQ205">
+        <v>1.15</v>
+      </c>
+      <c r="AR205">
+        <v>1.24</v>
+      </c>
+      <c r="AS205">
+        <v>1.33</v>
+      </c>
+      <c r="AT205">
+        <v>2.57</v>
+      </c>
+      <c r="AU205">
+        <v>3</v>
+      </c>
+      <c r="AV205">
+        <v>6</v>
+      </c>
+      <c r="AW205">
+        <v>8</v>
+      </c>
+      <c r="AX205">
+        <v>6</v>
+      </c>
+      <c r="AY205">
+        <v>16</v>
+      </c>
+      <c r="AZ205">
+        <v>14</v>
+      </c>
+      <c r="BA205">
+        <v>5</v>
+      </c>
+      <c r="BB205">
+        <v>2</v>
+      </c>
+      <c r="BC205">
+        <v>7</v>
+      </c>
+      <c r="BD205">
+        <v>1.82</v>
+      </c>
+      <c r="BE205">
+        <v>5.65</v>
+      </c>
+      <c r="BF205">
+        <v>2.45</v>
+      </c>
+      <c r="BG205">
+        <v>1.44</v>
+      </c>
+      <c r="BH205">
+        <v>2.55</v>
+      </c>
+      <c r="BI205">
+        <v>1.82</v>
+      </c>
+      <c r="BJ205">
+        <v>1.85</v>
+      </c>
+      <c r="BK205">
+        <v>2.45</v>
+      </c>
+      <c r="BL205">
+        <v>1.48</v>
+      </c>
+      <c r="BM205">
+        <v>3.55</v>
+      </c>
+      <c r="BN205">
+        <v>1.24</v>
+      </c>
+      <c r="BO205">
+        <v>4.2</v>
+      </c>
+      <c r="BP205">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7486694</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45697.5</v>
+      </c>
+      <c r="F206">
+        <v>26</v>
+      </c>
+      <c r="G206" t="s">
+        <v>82</v>
+      </c>
+      <c r="H206" t="s">
+        <v>78</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>2</v>
+      </c>
+      <c r="M206">
+        <v>2</v>
+      </c>
+      <c r="N206">
+        <v>4</v>
+      </c>
+      <c r="O206" t="s">
+        <v>211</v>
+      </c>
+      <c r="P206" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q206">
+        <v>1.91</v>
+      </c>
+      <c r="R206">
+        <v>2.3</v>
+      </c>
+      <c r="S206">
+        <v>8</v>
+      </c>
+      <c r="T206">
+        <v>1.4</v>
+      </c>
+      <c r="U206">
+        <v>2.75</v>
+      </c>
+      <c r="V206">
+        <v>2.75</v>
+      </c>
+      <c r="W206">
+        <v>1.4</v>
+      </c>
+      <c r="X206">
+        <v>8</v>
+      </c>
+      <c r="Y206">
+        <v>1.08</v>
+      </c>
+      <c r="Z206">
+        <v>1.42</v>
+      </c>
+      <c r="AA206">
+        <v>4.5</v>
+      </c>
+      <c r="AB206">
+        <v>7</v>
+      </c>
+      <c r="AC206">
+        <v>1.04</v>
+      </c>
+      <c r="AD206">
+        <v>9</v>
+      </c>
+      <c r="AE206">
+        <v>1.3</v>
+      </c>
+      <c r="AF206">
+        <v>3.3</v>
+      </c>
+      <c r="AG206">
+        <v>1.98</v>
+      </c>
+      <c r="AH206">
+        <v>1.77</v>
+      </c>
+      <c r="AI206">
+        <v>2.38</v>
+      </c>
+      <c r="AJ206">
+        <v>1.53</v>
+      </c>
+      <c r="AK206">
+        <v>1.09</v>
+      </c>
+      <c r="AL206">
+        <v>1.2</v>
+      </c>
+      <c r="AM206">
+        <v>2.8</v>
+      </c>
+      <c r="AN206">
+        <v>2.17</v>
+      </c>
+      <c r="AO206">
+        <v>0.42</v>
+      </c>
+      <c r="AP206">
+        <v>2.08</v>
+      </c>
+      <c r="AQ206">
+        <v>0.46</v>
+      </c>
+      <c r="AR206">
+        <v>1.62</v>
+      </c>
+      <c r="AS206">
+        <v>1.33</v>
+      </c>
+      <c r="AT206">
+        <v>2.95</v>
+      </c>
+      <c r="AU206">
+        <v>3</v>
+      </c>
+      <c r="AV206">
+        <v>7</v>
+      </c>
+      <c r="AW206">
+        <v>4</v>
+      </c>
+      <c r="AX206">
+        <v>6</v>
+      </c>
+      <c r="AY206">
+        <v>7</v>
+      </c>
+      <c r="AZ206">
+        <v>13</v>
+      </c>
+      <c r="BA206">
+        <v>3</v>
+      </c>
+      <c r="BB206">
+        <v>7</v>
+      </c>
+      <c r="BC206">
+        <v>10</v>
+      </c>
+      <c r="BD206">
+        <v>1.06</v>
+      </c>
+      <c r="BE206">
+        <v>12</v>
+      </c>
+      <c r="BF206">
+        <v>9.4</v>
+      </c>
+      <c r="BG206">
+        <v>1.31</v>
+      </c>
+      <c r="BH206">
+        <v>3.05</v>
+      </c>
+      <c r="BI206">
+        <v>1.58</v>
+      </c>
+      <c r="BJ206">
+        <v>2.2</v>
+      </c>
+      <c r="BK206">
+        <v>2.05</v>
+      </c>
+      <c r="BL206">
+        <v>1.68</v>
+      </c>
+      <c r="BM206">
+        <v>2.75</v>
+      </c>
+      <c r="BN206">
+        <v>1.39</v>
+      </c>
+      <c r="BO206">
+        <v>3.9</v>
+      </c>
+      <c r="BP206">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7486688</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45697.625</v>
+      </c>
+      <c r="F207">
+        <v>26</v>
+      </c>
+      <c r="G207" t="s">
+        <v>74</v>
+      </c>
+      <c r="H207" t="s">
+        <v>72</v>
+      </c>
+      <c r="I207">
+        <v>3</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>3</v>
+      </c>
+      <c r="L207">
+        <v>3</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="N207">
+        <v>3</v>
+      </c>
+      <c r="O207" t="s">
+        <v>212</v>
+      </c>
+      <c r="P207" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q207">
+        <v>2.2</v>
+      </c>
+      <c r="R207">
+        <v>2.2</v>
+      </c>
+      <c r="S207">
+        <v>6</v>
+      </c>
+      <c r="T207">
+        <v>1.4</v>
+      </c>
+      <c r="U207">
+        <v>2.75</v>
+      </c>
+      <c r="V207">
+        <v>3</v>
+      </c>
+      <c r="W207">
+        <v>1.36</v>
+      </c>
+      <c r="X207">
+        <v>8</v>
+      </c>
+      <c r="Y207">
+        <v>1.08</v>
+      </c>
+      <c r="Z207">
+        <v>1.59</v>
+      </c>
+      <c r="AA207">
+        <v>3.61</v>
+      </c>
+      <c r="AB207">
+        <v>6.2</v>
+      </c>
+      <c r="AC207">
+        <v>1.05</v>
+      </c>
+      <c r="AD207">
+        <v>8.5</v>
+      </c>
+      <c r="AE207">
+        <v>1.35</v>
+      </c>
+      <c r="AF207">
+        <v>3.05</v>
+      </c>
+      <c r="AG207">
+        <v>1.98</v>
+      </c>
+      <c r="AH207">
+        <v>1.77</v>
+      </c>
+      <c r="AI207">
+        <v>2</v>
+      </c>
+      <c r="AJ207">
+        <v>1.73</v>
+      </c>
+      <c r="AK207">
+        <v>1.17</v>
+      </c>
+      <c r="AL207">
+        <v>1.25</v>
+      </c>
+      <c r="AM207">
+        <v>2.15</v>
+      </c>
+      <c r="AN207">
+        <v>1.67</v>
+      </c>
+      <c r="AO207">
+        <v>1.08</v>
+      </c>
+      <c r="AP207">
+        <v>1.77</v>
+      </c>
+      <c r="AQ207">
+        <v>1</v>
+      </c>
+      <c r="AR207">
+        <v>2.04</v>
+      </c>
+      <c r="AS207">
+        <v>1.52</v>
+      </c>
+      <c r="AT207">
+        <v>3.56</v>
+      </c>
+      <c r="AU207">
+        <v>13</v>
+      </c>
+      <c r="AV207">
+        <v>4</v>
+      </c>
+      <c r="AW207">
+        <v>12</v>
+      </c>
+      <c r="AX207">
+        <v>4</v>
+      </c>
+      <c r="AY207">
+        <v>29</v>
+      </c>
+      <c r="AZ207">
+        <v>9</v>
+      </c>
+      <c r="BA207">
+        <v>10</v>
+      </c>
+      <c r="BB207">
+        <v>1</v>
+      </c>
+      <c r="BC207">
+        <v>11</v>
+      </c>
+      <c r="BD207">
+        <v>1.19</v>
+      </c>
+      <c r="BE207">
+        <v>9.4</v>
+      </c>
+      <c r="BF207">
+        <v>5.55</v>
+      </c>
+      <c r="BG207">
+        <v>1.26</v>
+      </c>
+      <c r="BH207">
+        <v>3.4</v>
+      </c>
+      <c r="BI207">
+        <v>1.49</v>
+      </c>
+      <c r="BJ207">
+        <v>2.42</v>
+      </c>
+      <c r="BK207">
+        <v>1.88</v>
+      </c>
+      <c r="BL207">
+        <v>1.8</v>
+      </c>
+      <c r="BM207">
+        <v>2.5</v>
+      </c>
+      <c r="BN207">
+        <v>1.46</v>
+      </c>
+      <c r="BO207">
+        <v>3.45</v>
+      </c>
+      <c r="BP207">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="300">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -655,6 +655,12 @@
     <t>['8', '15', '27']</t>
   </si>
   <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
+    <t>['75']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -868,9 +874,6 @@
     <t>['39']</t>
   </si>
   <si>
-    <t>['75']</t>
-  </si>
-  <si>
     <t>['18', '90+1']</t>
   </si>
   <si>
@@ -908,6 +911,9 @@
   </si>
   <si>
     <t>['90', '90+6']</t>
+  </si>
+  <si>
+    <t>['48', '52', '62', '89']</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP207"/>
+  <dimension ref="A1:BP209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1525,7 +1531,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1603,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -2221,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -2555,7 +2561,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2761,7 +2767,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3048,7 +3054,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ9">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3379,7 +3385,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3585,7 +3591,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3791,7 +3797,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3872,7 +3878,7 @@
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3997,7 +4003,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4203,7 +4209,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4409,7 +4415,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4821,7 +4827,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -5027,7 +5033,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5233,7 +5239,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5314,7 +5320,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ20">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR20">
         <v>1.45</v>
@@ -5645,7 +5651,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5723,7 +5729,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ22">
         <v>0.6899999999999999</v>
@@ -5851,7 +5857,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6135,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ24">
         <v>1.38</v>
@@ -6756,7 +6762,7 @@
         <v>2</v>
       </c>
       <c r="AQ27">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR27">
         <v>1</v>
@@ -6959,7 +6965,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ28">
         <v>0.46</v>
@@ -7293,7 +7299,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7499,7 +7505,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7705,7 +7711,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7911,7 +7917,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8117,7 +8123,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8323,7 +8329,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8401,7 +8407,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8735,7 +8741,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9353,7 +9359,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9559,7 +9565,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9765,7 +9771,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -9846,7 +9852,7 @@
         <v>2</v>
       </c>
       <c r="AQ42">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR42">
         <v>1.69</v>
@@ -10795,7 +10801,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -10873,7 +10879,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ47">
         <v>0.85</v>
@@ -11207,7 +11213,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -12237,7 +12243,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12443,7 +12449,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12521,7 +12527,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ55">
         <v>0.77</v>
@@ -12855,7 +12861,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13267,7 +13273,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13473,7 +13479,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13551,10 +13557,10 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ60">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR60">
         <v>1.71</v>
@@ -13885,7 +13891,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13966,7 +13972,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ62">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR62">
         <v>1.4</v>
@@ -14915,7 +14921,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15327,7 +15333,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15533,7 +15539,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15611,7 +15617,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ70">
         <v>0.85</v>
@@ -15739,7 +15745,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15945,7 +15951,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16026,7 +16032,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ72">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR72">
         <v>1.78</v>
@@ -16438,7 +16444,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ74">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR74">
         <v>1.37</v>
@@ -16563,7 +16569,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16769,7 +16775,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16847,7 +16853,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -16975,7 +16981,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17259,7 +17265,7 @@
         <v>0.75</v>
       </c>
       <c r="AP78">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ78">
         <v>0.46</v>
@@ -17387,7 +17393,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17799,7 +17805,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18211,7 +18217,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18829,7 +18835,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19319,7 +19325,7 @@
         <v>1.6</v>
       </c>
       <c r="AP88">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ88">
         <v>1.15</v>
@@ -19525,7 +19531,7 @@
         <v>0.67</v>
       </c>
       <c r="AP89">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ89">
         <v>1.46</v>
@@ -19653,7 +19659,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19859,7 +19865,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20065,7 +20071,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20271,7 +20277,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20683,7 +20689,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20764,7 +20770,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ95">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR95">
         <v>1.89</v>
@@ -21588,7 +21594,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ99">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR99">
         <v>1.24</v>
@@ -21919,7 +21925,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22537,7 +22543,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22821,10 +22827,10 @@
         <v>0.71</v>
       </c>
       <c r="AP105">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ105">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR105">
         <v>1.58</v>
@@ -23155,7 +23161,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23361,7 +23367,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23773,7 +23779,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23979,7 +23985,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24057,7 +24063,7 @@
         <v>1.29</v>
       </c>
       <c r="AP111">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ111">
         <v>1.46</v>
@@ -24185,7 +24191,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24266,7 +24272,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ112">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR112">
         <v>1.44</v>
@@ -24391,7 +24397,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24803,7 +24809,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -26039,7 +26045,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26120,7 +26126,7 @@
         <v>2</v>
       </c>
       <c r="AQ121">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR121">
         <v>1.14</v>
@@ -26245,7 +26251,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -27069,7 +27075,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27562,7 +27568,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ128">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR128">
         <v>1.38</v>
@@ -27974,7 +27980,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ130">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR130">
         <v>1.47</v>
@@ -28099,7 +28105,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28177,7 +28183,7 @@
         <v>1.25</v>
       </c>
       <c r="AP131">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ131">
         <v>1</v>
@@ -28305,7 +28311,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28511,7 +28517,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -29335,7 +29341,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29413,7 +29419,7 @@
         <v>1.13</v>
       </c>
       <c r="AP137">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ137">
         <v>1.46</v>
@@ -29953,7 +29959,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30365,7 +30371,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30571,7 +30577,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30652,7 +30658,7 @@
         <v>2</v>
       </c>
       <c r="AQ143">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR143">
         <v>1.8</v>
@@ -30777,7 +30783,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30983,7 +30989,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31395,7 +31401,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31601,7 +31607,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31807,7 +31813,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -31885,7 +31891,7 @@
         <v>1.11</v>
       </c>
       <c r="AP149">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ149">
         <v>1</v>
@@ -32013,7 +32019,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32631,7 +32637,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32712,7 +32718,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ153">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -32837,7 +32843,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33455,7 +33461,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33661,7 +33667,7 @@
         <v>187</v>
       </c>
       <c r="P158" t="s">
-        <v>284</v>
+        <v>214</v>
       </c>
       <c r="Q158">
         <v>2.63</v>
@@ -33948,7 +33954,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ159">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR159">
         <v>1.46</v>
@@ -34151,7 +34157,7 @@
         <v>1.67</v>
       </c>
       <c r="AP160">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ160">
         <v>1.77</v>
@@ -34360,7 +34366,7 @@
         <v>2</v>
       </c>
       <c r="AQ161">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR161">
         <v>1.54</v>
@@ -34897,7 +34903,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35309,7 +35315,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35799,7 +35805,7 @@
         <v>0.6</v>
       </c>
       <c r="AP168">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ168">
         <v>0.6899999999999999</v>
@@ -35927,7 +35933,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36133,7 +36139,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36339,7 +36345,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36545,7 +36551,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36626,7 +36632,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ172">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR172">
         <v>1.54</v>
@@ -37038,7 +37044,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ174">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR174">
         <v>1.61</v>
@@ -37447,7 +37453,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ176">
         <v>1.15</v>
@@ -37575,7 +37581,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -38193,7 +38199,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38811,7 +38817,7 @@
         <v>86</v>
       </c>
       <c r="P183" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q183">
         <v>5.2</v>
@@ -38889,7 +38895,7 @@
         <v>1.73</v>
       </c>
       <c r="AP183">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ183">
         <v>1.77</v>
@@ -39635,7 +39641,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -40047,7 +40053,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40128,7 +40134,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ189">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR189">
         <v>1.34</v>
@@ -40253,7 +40259,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40459,7 +40465,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40746,7 +40752,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ192">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR192">
         <v>2.13</v>
@@ -40871,7 +40877,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -40949,7 +40955,7 @@
         <v>1.27</v>
       </c>
       <c r="AP193">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ193">
         <v>1.15</v>
@@ -41077,7 +41083,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -42725,7 +42731,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -42931,7 +42937,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43343,7 +43349,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43549,7 +43555,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -43912,6 +43918,418 @@
       </c>
       <c r="BP207">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7486689</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45698.5</v>
+      </c>
+      <c r="F208">
+        <v>26</v>
+      </c>
+      <c r="G208" t="s">
+        <v>70</v>
+      </c>
+      <c r="H208" t="s">
+        <v>84</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>1</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="N208">
+        <v>1</v>
+      </c>
+      <c r="O208" t="s">
+        <v>213</v>
+      </c>
+      <c r="P208" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q208">
+        <v>2.5</v>
+      </c>
+      <c r="R208">
+        <v>2.1</v>
+      </c>
+      <c r="S208">
+        <v>4.75</v>
+      </c>
+      <c r="T208">
+        <v>1.44</v>
+      </c>
+      <c r="U208">
+        <v>2.63</v>
+      </c>
+      <c r="V208">
+        <v>3</v>
+      </c>
+      <c r="W208">
+        <v>1.36</v>
+      </c>
+      <c r="X208">
+        <v>9</v>
+      </c>
+      <c r="Y208">
+        <v>1.07</v>
+      </c>
+      <c r="Z208">
+        <v>1.71</v>
+      </c>
+      <c r="AA208">
+        <v>3.45</v>
+      </c>
+      <c r="AB208">
+        <v>5.2</v>
+      </c>
+      <c r="AC208">
+        <v>1.06</v>
+      </c>
+      <c r="AD208">
+        <v>8</v>
+      </c>
+      <c r="AE208">
+        <v>1.32</v>
+      </c>
+      <c r="AF208">
+        <v>3.2</v>
+      </c>
+      <c r="AG208">
+        <v>2.17</v>
+      </c>
+      <c r="AH208">
+        <v>1.62</v>
+      </c>
+      <c r="AI208">
+        <v>1.91</v>
+      </c>
+      <c r="AJ208">
+        <v>1.8</v>
+      </c>
+      <c r="AK208">
+        <v>1.21</v>
+      </c>
+      <c r="AL208">
+        <v>1.29</v>
+      </c>
+      <c r="AM208">
+        <v>1.9</v>
+      </c>
+      <c r="AN208">
+        <v>1.5</v>
+      </c>
+      <c r="AO208">
+        <v>0.42</v>
+      </c>
+      <c r="AP208">
+        <v>1.62</v>
+      </c>
+      <c r="AQ208">
+        <v>0.38</v>
+      </c>
+      <c r="AR208">
+        <v>1.66</v>
+      </c>
+      <c r="AS208">
+        <v>1.14</v>
+      </c>
+      <c r="AT208">
+        <v>2.8</v>
+      </c>
+      <c r="AU208">
+        <v>4</v>
+      </c>
+      <c r="AV208">
+        <v>2</v>
+      </c>
+      <c r="AW208">
+        <v>7</v>
+      </c>
+      <c r="AX208">
+        <v>4</v>
+      </c>
+      <c r="AY208">
+        <v>13</v>
+      </c>
+      <c r="AZ208">
+        <v>9</v>
+      </c>
+      <c r="BA208">
+        <v>9</v>
+      </c>
+      <c r="BB208">
+        <v>3</v>
+      </c>
+      <c r="BC208">
+        <v>12</v>
+      </c>
+      <c r="BD208">
+        <v>1.4</v>
+      </c>
+      <c r="BE208">
+        <v>7.7</v>
+      </c>
+      <c r="BF208">
+        <v>3.5</v>
+      </c>
+      <c r="BG208">
+        <v>1.22</v>
+      </c>
+      <c r="BH208">
+        <v>3.7</v>
+      </c>
+      <c r="BI208">
+        <v>1.43</v>
+      </c>
+      <c r="BJ208">
+        <v>2.6</v>
+      </c>
+      <c r="BK208">
+        <v>1.78</v>
+      </c>
+      <c r="BL208">
+        <v>1.92</v>
+      </c>
+      <c r="BM208">
+        <v>2.32</v>
+      </c>
+      <c r="BN208">
+        <v>1.52</v>
+      </c>
+      <c r="BO208">
+        <v>3.15</v>
+      </c>
+      <c r="BP208">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7486693</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45698.625</v>
+      </c>
+      <c r="F209">
+        <v>26</v>
+      </c>
+      <c r="G209" t="s">
+        <v>73</v>
+      </c>
+      <c r="H209" t="s">
+        <v>75</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209">
+        <v>4</v>
+      </c>
+      <c r="N209">
+        <v>5</v>
+      </c>
+      <c r="O209" t="s">
+        <v>214</v>
+      </c>
+      <c r="P209" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q209">
+        <v>4.75</v>
+      </c>
+      <c r="R209">
+        <v>2.1</v>
+      </c>
+      <c r="S209">
+        <v>2.6</v>
+      </c>
+      <c r="T209">
+        <v>1.44</v>
+      </c>
+      <c r="U209">
+        <v>2.63</v>
+      </c>
+      <c r="V209">
+        <v>3.25</v>
+      </c>
+      <c r="W209">
+        <v>1.33</v>
+      </c>
+      <c r="X209">
+        <v>10</v>
+      </c>
+      <c r="Y209">
+        <v>1.06</v>
+      </c>
+      <c r="Z209">
+        <v>3.5</v>
+      </c>
+      <c r="AA209">
+        <v>3.2</v>
+      </c>
+      <c r="AB209">
+        <v>2.12</v>
+      </c>
+      <c r="AC209">
+        <v>1.06</v>
+      </c>
+      <c r="AD209">
+        <v>8</v>
+      </c>
+      <c r="AE209">
+        <v>1.36</v>
+      </c>
+      <c r="AF209">
+        <v>2.95</v>
+      </c>
+      <c r="AG209">
+        <v>2</v>
+      </c>
+      <c r="AH209">
+        <v>1.67</v>
+      </c>
+      <c r="AI209">
+        <v>2</v>
+      </c>
+      <c r="AJ209">
+        <v>1.73</v>
+      </c>
+      <c r="AK209">
+        <v>1.87</v>
+      </c>
+      <c r="AL209">
+        <v>1.29</v>
+      </c>
+      <c r="AM209">
+        <v>1.23</v>
+      </c>
+      <c r="AN209">
+        <v>1.25</v>
+      </c>
+      <c r="AO209">
+        <v>1.58</v>
+      </c>
+      <c r="AP209">
+        <v>1.15</v>
+      </c>
+      <c r="AQ209">
+        <v>1.69</v>
+      </c>
+      <c r="AR209">
+        <v>1.6</v>
+      </c>
+      <c r="AS209">
+        <v>1.29</v>
+      </c>
+      <c r="AT209">
+        <v>2.89</v>
+      </c>
+      <c r="AU209">
+        <v>2</v>
+      </c>
+      <c r="AV209">
+        <v>9</v>
+      </c>
+      <c r="AW209">
+        <v>5</v>
+      </c>
+      <c r="AX209">
+        <v>14</v>
+      </c>
+      <c r="AY209">
+        <v>8</v>
+      </c>
+      <c r="AZ209">
+        <v>26</v>
+      </c>
+      <c r="BA209">
+        <v>7</v>
+      </c>
+      <c r="BB209">
+        <v>8</v>
+      </c>
+      <c r="BC209">
+        <v>15</v>
+      </c>
+      <c r="BD209">
+        <v>3.3</v>
+      </c>
+      <c r="BE209">
+        <v>6.3</v>
+      </c>
+      <c r="BF209">
+        <v>1.5</v>
+      </c>
+      <c r="BG209">
+        <v>1.28</v>
+      </c>
+      <c r="BH209">
+        <v>3.3</v>
+      </c>
+      <c r="BI209">
+        <v>1.52</v>
+      </c>
+      <c r="BJ209">
+        <v>2.32</v>
+      </c>
+      <c r="BK209">
+        <v>1.92</v>
+      </c>
+      <c r="BL209">
+        <v>1.75</v>
+      </c>
+      <c r="BM209">
+        <v>2.6</v>
+      </c>
+      <c r="BN209">
+        <v>1.43</v>
+      </c>
+      <c r="BO209">
+        <v>3.7</v>
+      </c>
+      <c r="BP209">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="304">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -661,6 +661,12 @@
     <t>['75']</t>
   </si>
   <si>
+    <t>['64', '75']</t>
+  </si>
+  <si>
+    <t>['54', '76']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -914,6 +920,12 @@
   </si>
   <si>
     <t>['48', '52', '62', '89']</t>
+  </si>
+  <si>
+    <t>['51', '53', '72']</t>
+  </si>
+  <si>
+    <t>['72']</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP209"/>
+  <dimension ref="A1:BP211"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1531,7 +1543,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -2021,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ4">
         <v>0.46</v>
@@ -2561,7 +2573,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2767,7 +2779,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2848,7 +2860,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3385,7 +3397,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3591,7 +3603,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3669,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ12">
         <v>1.15</v>
@@ -3797,7 +3809,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -4003,7 +4015,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4084,7 +4096,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ14">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4209,7 +4221,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4415,7 +4427,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4827,7 +4839,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -5033,7 +5045,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5114,7 +5126,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR19">
         <v>1.85</v>
@@ -5239,7 +5251,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5523,7 +5535,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ21">
         <v>1.46</v>
@@ -5651,7 +5663,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5857,7 +5869,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6556,7 +6568,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ26">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR26">
         <v>1.29</v>
@@ -7171,7 +7183,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ29">
         <v>1.15</v>
@@ -7299,7 +7311,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7505,7 +7517,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7711,7 +7723,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7917,7 +7929,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8123,7 +8135,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8329,7 +8341,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8410,7 +8422,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR35">
         <v>1.45</v>
@@ -8741,7 +8753,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -8819,7 +8831,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ37">
         <v>1.46</v>
@@ -9359,7 +9371,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9565,7 +9577,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9771,7 +9783,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -9849,7 +9861,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ42">
         <v>0.38</v>
@@ -10801,7 +10813,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -10882,7 +10894,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ47">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>1.66</v>
@@ -11088,7 +11100,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR48">
         <v>0.93</v>
@@ -11213,7 +11225,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11497,7 +11509,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -12243,7 +12255,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12449,7 +12461,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12861,7 +12873,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13145,7 +13157,7 @@
         <v>1.25</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -13273,7 +13285,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13479,7 +13491,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13891,7 +13903,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14381,7 +14393,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ64">
         <v>0.6899999999999999</v>
@@ -14796,7 +14808,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR66">
         <v>1.39</v>
@@ -14921,7 +14933,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15333,7 +15345,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15539,7 +15551,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15620,7 +15632,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ70">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -15745,7 +15757,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15951,7 +15963,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16569,7 +16581,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16775,7 +16787,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16981,7 +16993,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17393,7 +17405,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17680,7 +17692,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ80">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR80">
         <v>1.06</v>
@@ -17805,7 +17817,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18217,7 +18229,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18504,7 +18516,7 @@
         <v>2</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR84">
         <v>1.43</v>
@@ -18835,7 +18847,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -18913,7 +18925,7 @@
         <v>0.67</v>
       </c>
       <c r="AP86">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ86">
         <v>1.77</v>
@@ -19119,7 +19131,7 @@
         <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ87">
         <v>1</v>
@@ -19659,7 +19671,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19865,7 +19877,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20071,7 +20083,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20277,7 +20289,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20689,7 +20701,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20976,7 +20988,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ96">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR96">
         <v>1.35</v>
@@ -21182,7 +21194,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR97">
         <v>1.37</v>
@@ -21385,7 +21397,7 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ98">
         <v>1.15</v>
@@ -21797,7 +21809,7 @@
         <v>0.67</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ100">
         <v>0.6899999999999999</v>
@@ -21925,7 +21937,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22543,7 +22555,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -23161,7 +23173,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23367,7 +23379,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23779,7 +23791,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23985,7 +23997,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24191,7 +24203,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24397,7 +24409,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24475,7 +24487,7 @@
         <v>1.33</v>
       </c>
       <c r="AP113">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ113">
         <v>1.15</v>
@@ -24809,7 +24821,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24890,7 +24902,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR115">
         <v>1.47</v>
@@ -25299,7 +25311,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ117">
         <v>1.77</v>
@@ -25714,7 +25726,7 @@
         <v>2</v>
       </c>
       <c r="AQ119">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR119">
         <v>1.46</v>
@@ -26045,7 +26057,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26251,7 +26263,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26535,10 +26547,10 @@
         <v>0.14</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ123">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR123">
         <v>1.82</v>
@@ -27075,7 +27087,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27977,7 +27989,7 @@
         <v>0.63</v>
       </c>
       <c r="AP130">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ130">
         <v>0.38</v>
@@ -28105,7 +28117,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28186,7 +28198,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ131">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR131">
         <v>1.58</v>
@@ -28311,7 +28323,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28517,7 +28529,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -29341,7 +29353,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29959,7 +29971,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30040,7 +30052,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ140">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR140">
         <v>1.45</v>
@@ -30371,7 +30383,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30577,7 +30589,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30655,7 +30667,7 @@
         <v>1.86</v>
       </c>
       <c r="AP143">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ143">
         <v>1.69</v>
@@ -30783,7 +30795,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30989,7 +31001,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31273,7 +31285,7 @@
         <v>1.22</v>
       </c>
       <c r="AP146">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ146">
         <v>1</v>
@@ -31401,7 +31413,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31607,7 +31619,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31813,7 +31825,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32019,7 +32031,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32512,7 +32524,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ152">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR152">
         <v>1.23</v>
@@ -32637,7 +32649,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32843,7 +32855,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -32924,7 +32936,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ154">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR154">
         <v>1.64</v>
@@ -33461,7 +33473,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33539,7 +33551,7 @@
         <v>1.33</v>
       </c>
       <c r="AP157">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ157">
         <v>1</v>
@@ -34569,7 +34581,7 @@
         <v>1.6</v>
       </c>
       <c r="AP162">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ162">
         <v>1.38</v>
@@ -34903,7 +34915,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35315,7 +35327,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35396,7 +35408,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ166">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR166">
         <v>1.81</v>
@@ -35933,7 +35945,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36139,7 +36151,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36345,7 +36357,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36426,7 +36438,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ171">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR171">
         <v>2.04</v>
@@ -36551,7 +36563,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -37247,7 +37259,7 @@
         <v>1.4</v>
       </c>
       <c r="AP175">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ175">
         <v>1.46</v>
@@ -37581,7 +37593,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -38199,7 +38211,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38280,7 +38292,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ180">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR180">
         <v>1.37</v>
@@ -38689,10 +38701,10 @@
         <v>1.18</v>
       </c>
       <c r="AP182">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ182">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR182">
         <v>1.35</v>
@@ -38817,7 +38829,7 @@
         <v>86</v>
       </c>
       <c r="P183" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q183">
         <v>5.2</v>
@@ -39641,7 +39653,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -40053,7 +40065,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40259,7 +40271,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40465,7 +40477,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40543,7 +40555,7 @@
         <v>0.45</v>
       </c>
       <c r="AP191">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ191">
         <v>0.46</v>
@@ -40877,7 +40889,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -41083,7 +41095,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -41576,7 +41588,7 @@
         <v>2</v>
       </c>
       <c r="AQ196">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR196">
         <v>1.24</v>
@@ -41782,7 +41794,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ197">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR197">
         <v>1.86</v>
@@ -41985,7 +41997,7 @@
         <v>1.5</v>
       </c>
       <c r="AP198">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ198">
         <v>1.38</v>
@@ -42397,7 +42409,7 @@
         <v>0.83</v>
       </c>
       <c r="AP200">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ200">
         <v>0.77</v>
@@ -42731,7 +42743,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -42937,7 +42949,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43349,7 +43361,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43555,7 +43567,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -44173,7 +44185,7 @@
         <v>214</v>
       </c>
       <c r="P209" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q209">
         <v>4.75</v>
@@ -44330,6 +44342,418 @@
       </c>
       <c r="BP209">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7486695</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45702.5</v>
+      </c>
+      <c r="F210">
+        <v>27</v>
+      </c>
+      <c r="G210" t="s">
+        <v>72</v>
+      </c>
+      <c r="H210" t="s">
+        <v>71</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>2</v>
+      </c>
+      <c r="M210">
+        <v>3</v>
+      </c>
+      <c r="N210">
+        <v>5</v>
+      </c>
+      <c r="O210" t="s">
+        <v>215</v>
+      </c>
+      <c r="P210" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q210">
+        <v>2.8</v>
+      </c>
+      <c r="R210">
+        <v>1.96</v>
+      </c>
+      <c r="S210">
+        <v>4.2</v>
+      </c>
+      <c r="T210">
+        <v>1.53</v>
+      </c>
+      <c r="U210">
+        <v>2.36</v>
+      </c>
+      <c r="V210">
+        <v>3.3</v>
+      </c>
+      <c r="W210">
+        <v>1.28</v>
+      </c>
+      <c r="X210">
+        <v>10.5</v>
+      </c>
+      <c r="Y210">
+        <v>1.03</v>
+      </c>
+      <c r="Z210">
+        <v>2.17</v>
+      </c>
+      <c r="AA210">
+        <v>3.11</v>
+      </c>
+      <c r="AB210">
+        <v>3.5</v>
+      </c>
+      <c r="AC210">
+        <v>1.09</v>
+      </c>
+      <c r="AD210">
+        <v>6.5</v>
+      </c>
+      <c r="AE210">
+        <v>1.44</v>
+      </c>
+      <c r="AF210">
+        <v>2.65</v>
+      </c>
+      <c r="AG210">
+        <v>2.3</v>
+      </c>
+      <c r="AH210">
+        <v>1.5</v>
+      </c>
+      <c r="AI210">
+        <v>2.01</v>
+      </c>
+      <c r="AJ210">
+        <v>1.72</v>
+      </c>
+      <c r="AK210">
+        <v>1.28</v>
+      </c>
+      <c r="AL210">
+        <v>1.32</v>
+      </c>
+      <c r="AM210">
+        <v>1.63</v>
+      </c>
+      <c r="AN210">
+        <v>1.85</v>
+      </c>
+      <c r="AO210">
+        <v>0.85</v>
+      </c>
+      <c r="AP210">
+        <v>1.71</v>
+      </c>
+      <c r="AQ210">
+        <v>1</v>
+      </c>
+      <c r="AR210">
+        <v>1.42</v>
+      </c>
+      <c r="AS210">
+        <v>1.28</v>
+      </c>
+      <c r="AT210">
+        <v>2.7</v>
+      </c>
+      <c r="AU210">
+        <v>5</v>
+      </c>
+      <c r="AV210">
+        <v>4</v>
+      </c>
+      <c r="AW210">
+        <v>10</v>
+      </c>
+      <c r="AX210">
+        <v>4</v>
+      </c>
+      <c r="AY210">
+        <v>20</v>
+      </c>
+      <c r="AZ210">
+        <v>8</v>
+      </c>
+      <c r="BA210">
+        <v>7</v>
+      </c>
+      <c r="BB210">
+        <v>2</v>
+      </c>
+      <c r="BC210">
+        <v>9</v>
+      </c>
+      <c r="BD210">
+        <v>1.72</v>
+      </c>
+      <c r="BE210">
+        <v>6.1</v>
+      </c>
+      <c r="BF210">
+        <v>2.4</v>
+      </c>
+      <c r="BG210">
+        <v>1.52</v>
+      </c>
+      <c r="BH210">
+        <v>2.3</v>
+      </c>
+      <c r="BI210">
+        <v>1.87</v>
+      </c>
+      <c r="BJ210">
+        <v>1.79</v>
+      </c>
+      <c r="BK210">
+        <v>2.38</v>
+      </c>
+      <c r="BL210">
+        <v>1.48</v>
+      </c>
+      <c r="BM210">
+        <v>3.15</v>
+      </c>
+      <c r="BN210">
+        <v>1.29</v>
+      </c>
+      <c r="BO210">
+        <v>4.2</v>
+      </c>
+      <c r="BP210">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7486699</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45702.625</v>
+      </c>
+      <c r="F211">
+        <v>27</v>
+      </c>
+      <c r="G211" t="s">
+        <v>80</v>
+      </c>
+      <c r="H211" t="s">
+        <v>85</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>2</v>
+      </c>
+      <c r="M211">
+        <v>1</v>
+      </c>
+      <c r="N211">
+        <v>3</v>
+      </c>
+      <c r="O211" t="s">
+        <v>216</v>
+      </c>
+      <c r="P211" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q211">
+        <v>2.06</v>
+      </c>
+      <c r="R211">
+        <v>2.19</v>
+      </c>
+      <c r="S211">
+        <v>6.4</v>
+      </c>
+      <c r="T211">
+        <v>1.43</v>
+      </c>
+      <c r="U211">
+        <v>2.65</v>
+      </c>
+      <c r="V211">
+        <v>2.88</v>
+      </c>
+      <c r="W211">
+        <v>1.36</v>
+      </c>
+      <c r="X211">
+        <v>9</v>
+      </c>
+      <c r="Y211">
+        <v>1.04</v>
+      </c>
+      <c r="Z211">
+        <v>1.57</v>
+      </c>
+      <c r="AA211">
+        <v>3.62</v>
+      </c>
+      <c r="AB211">
+        <v>6.4</v>
+      </c>
+      <c r="AC211">
+        <v>1.07</v>
+      </c>
+      <c r="AD211">
+        <v>7.5</v>
+      </c>
+      <c r="AE211">
+        <v>1.36</v>
+      </c>
+      <c r="AF211">
+        <v>3</v>
+      </c>
+      <c r="AG211">
+        <v>1.95</v>
+      </c>
+      <c r="AH211">
+        <v>1.79</v>
+      </c>
+      <c r="AI211">
+        <v>2.13</v>
+      </c>
+      <c r="AJ211">
+        <v>1.64</v>
+      </c>
+      <c r="AK211">
+        <v>1.12</v>
+      </c>
+      <c r="AL211">
+        <v>1.23</v>
+      </c>
+      <c r="AM211">
+        <v>2.28</v>
+      </c>
+      <c r="AN211">
+        <v>2</v>
+      </c>
+      <c r="AO211">
+        <v>1</v>
+      </c>
+      <c r="AP211">
+        <v>2.07</v>
+      </c>
+      <c r="AQ211">
+        <v>0.93</v>
+      </c>
+      <c r="AR211">
+        <v>1.81</v>
+      </c>
+      <c r="AS211">
+        <v>1.3</v>
+      </c>
+      <c r="AT211">
+        <v>3.11</v>
+      </c>
+      <c r="AU211">
+        <v>6</v>
+      </c>
+      <c r="AV211">
+        <v>5</v>
+      </c>
+      <c r="AW211">
+        <v>10</v>
+      </c>
+      <c r="AX211">
+        <v>5</v>
+      </c>
+      <c r="AY211">
+        <v>19</v>
+      </c>
+      <c r="AZ211">
+        <v>12</v>
+      </c>
+      <c r="BA211">
+        <v>5</v>
+      </c>
+      <c r="BB211">
+        <v>3</v>
+      </c>
+      <c r="BC211">
+        <v>8</v>
+      </c>
+      <c r="BD211">
+        <v>1.41</v>
+      </c>
+      <c r="BE211">
+        <v>6.75</v>
+      </c>
+      <c r="BF211">
+        <v>3.3</v>
+      </c>
+      <c r="BG211">
+        <v>1.46</v>
+      </c>
+      <c r="BH211">
+        <v>2.45</v>
+      </c>
+      <c r="BI211">
+        <v>1.78</v>
+      </c>
+      <c r="BJ211">
+        <v>1.88</v>
+      </c>
+      <c r="BK211">
+        <v>2.25</v>
+      </c>
+      <c r="BL211">
+        <v>1.54</v>
+      </c>
+      <c r="BM211">
+        <v>2.9</v>
+      </c>
+      <c r="BN211">
+        <v>1.34</v>
+      </c>
+      <c r="BO211">
+        <v>3.9</v>
+      </c>
+      <c r="BP211">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="305">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -927,6 +927,9 @@
   <si>
     <t>['72']</t>
   </si>
+  <si>
+    <t>['24', '59']</t>
+  </si>
 </sst>
 </file>
 
@@ -1287,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP211"/>
+  <dimension ref="A1:BP213"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3063,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ9">
         <v>0.38</v>
@@ -3684,7 +3687,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ12">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4299,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ15">
         <v>1.15</v>
@@ -4714,7 +4717,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ17">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -6359,7 +6362,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6771,7 +6774,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ27">
         <v>0.38</v>
@@ -7598,7 +7601,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ31">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR31">
         <v>1</v>
@@ -8010,7 +8013,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ33">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR33">
         <v>2.11</v>
@@ -9243,7 +9246,7 @@
         <v>1.67</v>
       </c>
       <c r="AP39">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ39">
         <v>1.38</v>
@@ -10070,7 +10073,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ43">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR43">
         <v>1.6</v>
@@ -11097,7 +11100,7 @@
         <v>2.33</v>
       </c>
       <c r="AP48">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ48">
         <v>0.93</v>
@@ -11715,7 +11718,7 @@
         <v>2.33</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ51">
         <v>1.46</v>
@@ -12542,7 +12545,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ55">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR55">
         <v>1.71</v>
@@ -13778,7 +13781,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ61">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR61">
         <v>2.06</v>
@@ -14599,7 +14602,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -15011,10 +15014,10 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ67">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR67">
         <v>0.97</v>
@@ -17689,7 +17692,7 @@
         <v>0.25</v>
       </c>
       <c r="AP80">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ80">
         <v>1</v>
@@ -17895,7 +17898,7 @@
         <v>0.6</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ81">
         <v>0.6899999999999999</v>
@@ -18310,7 +18313,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ83">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR83">
         <v>1.79</v>
@@ -18722,7 +18725,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ85">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -21400,7 +21403,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ98">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR98">
         <v>1.57</v>
@@ -21603,7 +21606,7 @@
         <v>1.67</v>
       </c>
       <c r="AP99">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ99">
         <v>1.69</v>
@@ -22015,7 +22018,7 @@
         <v>1.25</v>
       </c>
       <c r="AP101">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ101">
         <v>1.77</v>
@@ -22430,7 +22433,7 @@
         <v>2</v>
       </c>
       <c r="AQ103">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR103">
         <v>1.37</v>
@@ -23045,7 +23048,7 @@
         <v>0.67</v>
       </c>
       <c r="AP106">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ106">
         <v>0.46</v>
@@ -24693,10 +24696,10 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ114">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR114">
         <v>1.16</v>
@@ -25108,7 +25111,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ116">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR116">
         <v>1.34</v>
@@ -26135,7 +26138,7 @@
         <v>1.8</v>
       </c>
       <c r="AP121">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ121">
         <v>1.69</v>
@@ -26756,7 +26759,7 @@
         <v>2</v>
       </c>
       <c r="AQ124">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR124">
         <v>1.43</v>
@@ -26962,7 +26965,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ125">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR125">
         <v>1.4</v>
@@ -29019,7 +29022,7 @@
         <v>1</v>
       </c>
       <c r="AP135">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ135">
         <v>1.46</v>
@@ -29640,7 +29643,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ138">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR138">
         <v>1.66</v>
@@ -30461,7 +30464,7 @@
         <v>1.38</v>
       </c>
       <c r="AP142">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ142">
         <v>1</v>
@@ -30876,7 +30879,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ144">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR144">
         <v>1.39</v>
@@ -31697,7 +31700,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ148">
         <v>1.46</v>
@@ -32112,7 +32115,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ150">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR150">
         <v>1.49</v>
@@ -33139,7 +33142,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP155">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ155">
         <v>0.46</v>
@@ -33348,7 +33351,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ156">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR156">
         <v>1.39</v>
@@ -34790,7 +34793,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ163">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR163">
         <v>1.24</v>
@@ -35199,7 +35202,7 @@
         <v>1.3</v>
       </c>
       <c r="AP165">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ165">
         <v>1</v>
@@ -35611,7 +35614,7 @@
         <v>1.1</v>
       </c>
       <c r="AP167">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ167">
         <v>1</v>
@@ -37468,7 +37471,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ176">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR176">
         <v>1.54</v>
@@ -38083,7 +38086,7 @@
         <v>1.55</v>
       </c>
       <c r="AP179">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ179">
         <v>1.38</v>
@@ -39113,7 +39116,7 @@
         <v>0.55</v>
       </c>
       <c r="AP184">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ184">
         <v>0.6899999999999999</v>
@@ -39322,7 +39325,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ185">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR185">
         <v>1.75</v>
@@ -39528,7 +39531,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ186">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR186">
         <v>1.23</v>
@@ -41585,7 +41588,7 @@
         <v>1.08</v>
       </c>
       <c r="AP196">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ196">
         <v>0.93</v>
@@ -42206,7 +42209,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ199">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR199">
         <v>1.46</v>
@@ -42412,7 +42415,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ200">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR200">
         <v>1.39</v>
@@ -42615,7 +42618,7 @@
         <v>1.83</v>
       </c>
       <c r="AP201">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ201">
         <v>1.77</v>
@@ -44754,6 +44757,418 @@
       </c>
       <c r="BP211">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7486700</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45703.41666666666</v>
+      </c>
+      <c r="F212">
+        <v>27</v>
+      </c>
+      <c r="G212" t="s">
+        <v>77</v>
+      </c>
+      <c r="H212" t="s">
+        <v>73</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>1</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="M212">
+        <v>1</v>
+      </c>
+      <c r="N212">
+        <v>1</v>
+      </c>
+      <c r="O212" t="s">
+        <v>86</v>
+      </c>
+      <c r="P212" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q212">
+        <v>2.7</v>
+      </c>
+      <c r="R212">
+        <v>2</v>
+      </c>
+      <c r="S212">
+        <v>4.3</v>
+      </c>
+      <c r="T212">
+        <v>1.5</v>
+      </c>
+      <c r="U212">
+        <v>2.4</v>
+      </c>
+      <c r="V212">
+        <v>3.28</v>
+      </c>
+      <c r="W212">
+        <v>1.3</v>
+      </c>
+      <c r="X212">
+        <v>8.4</v>
+      </c>
+      <c r="Y212">
+        <v>1.02</v>
+      </c>
+      <c r="Z212">
+        <v>2.11</v>
+      </c>
+      <c r="AA212">
+        <v>3.11</v>
+      </c>
+      <c r="AB212">
+        <v>3.64</v>
+      </c>
+      <c r="AC212">
+        <v>1.03</v>
+      </c>
+      <c r="AD212">
+        <v>7.6</v>
+      </c>
+      <c r="AE212">
+        <v>1.5</v>
+      </c>
+      <c r="AF212">
+        <v>2.4</v>
+      </c>
+      <c r="AG212">
+        <v>2.2</v>
+      </c>
+      <c r="AH212">
+        <v>1.55</v>
+      </c>
+      <c r="AI212">
+        <v>1.94</v>
+      </c>
+      <c r="AJ212">
+        <v>1.77</v>
+      </c>
+      <c r="AK212">
+        <v>1.26</v>
+      </c>
+      <c r="AL212">
+        <v>1.32</v>
+      </c>
+      <c r="AM212">
+        <v>1.66</v>
+      </c>
+      <c r="AN212">
+        <v>1.69</v>
+      </c>
+      <c r="AO212">
+        <v>1.15</v>
+      </c>
+      <c r="AP212">
+        <v>1.57</v>
+      </c>
+      <c r="AQ212">
+        <v>1.29</v>
+      </c>
+      <c r="AR212">
+        <v>1.27</v>
+      </c>
+      <c r="AS212">
+        <v>1.25</v>
+      </c>
+      <c r="AT212">
+        <v>2.52</v>
+      </c>
+      <c r="AU212">
+        <v>4</v>
+      </c>
+      <c r="AV212">
+        <v>5</v>
+      </c>
+      <c r="AW212">
+        <v>13</v>
+      </c>
+      <c r="AX212">
+        <v>5</v>
+      </c>
+      <c r="AY212">
+        <v>23</v>
+      </c>
+      <c r="AZ212">
+        <v>10</v>
+      </c>
+      <c r="BA212">
+        <v>6</v>
+      </c>
+      <c r="BB212">
+        <v>4</v>
+      </c>
+      <c r="BC212">
+        <v>10</v>
+      </c>
+      <c r="BD212">
+        <v>1.72</v>
+      </c>
+      <c r="BE212">
+        <v>6.1</v>
+      </c>
+      <c r="BF212">
+        <v>2.4</v>
+      </c>
+      <c r="BG212">
+        <v>1.49</v>
+      </c>
+      <c r="BH212">
+        <v>2.38</v>
+      </c>
+      <c r="BI212">
+        <v>1.82</v>
+      </c>
+      <c r="BJ212">
+        <v>1.84</v>
+      </c>
+      <c r="BK212">
+        <v>2.33</v>
+      </c>
+      <c r="BL212">
+        <v>1.5</v>
+      </c>
+      <c r="BM212">
+        <v>3.05</v>
+      </c>
+      <c r="BN212">
+        <v>1.3</v>
+      </c>
+      <c r="BO212">
+        <v>4.1</v>
+      </c>
+      <c r="BP212">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7486697</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45703.625</v>
+      </c>
+      <c r="F213">
+        <v>27</v>
+      </c>
+      <c r="G213" t="s">
+        <v>83</v>
+      </c>
+      <c r="H213" t="s">
+        <v>70</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>1</v>
+      </c>
+      <c r="K213">
+        <v>1</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213">
+        <v>2</v>
+      </c>
+      <c r="N213">
+        <v>2</v>
+      </c>
+      <c r="O213" t="s">
+        <v>86</v>
+      </c>
+      <c r="P213" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q213">
+        <v>2.65</v>
+      </c>
+      <c r="R213">
+        <v>1.99</v>
+      </c>
+      <c r="S213">
+        <v>4.5</v>
+      </c>
+      <c r="T213">
+        <v>1.52</v>
+      </c>
+      <c r="U213">
+        <v>2.4</v>
+      </c>
+      <c r="V213">
+        <v>3.4</v>
+      </c>
+      <c r="W213">
+        <v>1.28</v>
+      </c>
+      <c r="X213">
+        <v>9.4</v>
+      </c>
+      <c r="Y213">
+        <v>1.01</v>
+      </c>
+      <c r="Z213">
+        <v>1.99</v>
+      </c>
+      <c r="AA213">
+        <v>3.27</v>
+      </c>
+      <c r="AB213">
+        <v>3.83</v>
+      </c>
+      <c r="AC213">
+        <v>1.02</v>
+      </c>
+      <c r="AD213">
+        <v>7.7</v>
+      </c>
+      <c r="AE213">
+        <v>1.43</v>
+      </c>
+      <c r="AF213">
+        <v>2.7</v>
+      </c>
+      <c r="AG213">
+        <v>2.2</v>
+      </c>
+      <c r="AH213">
+        <v>1.55</v>
+      </c>
+      <c r="AI213">
+        <v>2.02</v>
+      </c>
+      <c r="AJ213">
+        <v>1.71</v>
+      </c>
+      <c r="AK213">
+        <v>1.25</v>
+      </c>
+      <c r="AL213">
+        <v>1.3</v>
+      </c>
+      <c r="AM213">
+        <v>1.73</v>
+      </c>
+      <c r="AN213">
+        <v>2</v>
+      </c>
+      <c r="AO213">
+        <v>0.77</v>
+      </c>
+      <c r="AP213">
+        <v>1.86</v>
+      </c>
+      <c r="AQ213">
+        <v>0.93</v>
+      </c>
+      <c r="AR213">
+        <v>1.24</v>
+      </c>
+      <c r="AS213">
+        <v>1.28</v>
+      </c>
+      <c r="AT213">
+        <v>2.52</v>
+      </c>
+      <c r="AU213">
+        <v>6</v>
+      </c>
+      <c r="AV213">
+        <v>4</v>
+      </c>
+      <c r="AW213">
+        <v>19</v>
+      </c>
+      <c r="AX213">
+        <v>6</v>
+      </c>
+      <c r="AY213">
+        <v>34</v>
+      </c>
+      <c r="AZ213">
+        <v>11</v>
+      </c>
+      <c r="BA213">
+        <v>13</v>
+      </c>
+      <c r="BB213">
+        <v>5</v>
+      </c>
+      <c r="BC213">
+        <v>18</v>
+      </c>
+      <c r="BD213">
+        <v>1.7</v>
+      </c>
+      <c r="BE213">
+        <v>6.1</v>
+      </c>
+      <c r="BF213">
+        <v>2.43</v>
+      </c>
+      <c r="BG213">
+        <v>1.5</v>
+      </c>
+      <c r="BH213">
+        <v>2.35</v>
+      </c>
+      <c r="BI213">
+        <v>1.85</v>
+      </c>
+      <c r="BJ213">
+        <v>1.82</v>
+      </c>
+      <c r="BK213">
+        <v>2.35</v>
+      </c>
+      <c r="BL213">
+        <v>1.5</v>
+      </c>
+      <c r="BM213">
+        <v>3.15</v>
+      </c>
+      <c r="BN213">
+        <v>1.29</v>
+      </c>
+      <c r="BO213">
+        <v>4.1</v>
+      </c>
+      <c r="BP213">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="306">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -667,6 +667,9 @@
     <t>['54', '76']</t>
   </si>
   <si>
+    <t>['63']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -898,9 +901,6 @@
     <t>['55', '75']</t>
   </si>
   <si>
-    <t>['63']</t>
-  </si>
-  <si>
     <t>['35', '82', '90+2']</t>
   </si>
   <si>
@@ -929,6 +929,9 @@
   </si>
   <si>
     <t>['24', '59']</t>
+  </si>
+  <si>
+    <t>['67', '73']</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP213"/>
+  <dimension ref="A1:BP215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1546,7 +1549,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -2576,7 +2579,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2782,7 +2785,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3272,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ10">
         <v>0.6899999999999999</v>
@@ -3400,7 +3403,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3481,7 +3484,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ11">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3606,7 +3609,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3812,7 +3815,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3893,7 +3896,7 @@
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4018,7 +4021,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4224,7 +4227,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4430,7 +4433,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4508,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -4842,7 +4845,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -5048,7 +5051,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5254,7 +5257,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5332,7 +5335,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ20">
         <v>0.38</v>
@@ -5666,7 +5669,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5872,7 +5875,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -7314,7 +7317,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7520,7 +7523,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7726,7 +7729,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7932,7 +7935,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8138,7 +8141,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8344,7 +8347,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8628,7 +8631,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8756,7 +8759,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9374,7 +9377,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9452,7 +9455,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ40">
         <v>1.46</v>
@@ -9580,7 +9583,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9786,7 +9789,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10816,7 +10819,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11228,7 +11231,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11306,7 +11309,7 @@
         <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ49">
         <v>1</v>
@@ -12133,7 +12136,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ53">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR53">
         <v>1.19</v>
@@ -12258,7 +12261,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12336,7 +12339,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ54">
         <v>1.38</v>
@@ -12464,7 +12467,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12876,7 +12879,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13288,7 +13291,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13494,7 +13497,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13575,7 +13578,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ60">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR60">
         <v>1.71</v>
@@ -13906,7 +13909,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14808,7 +14811,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ66">
         <v>0.93</v>
@@ -14936,7 +14939,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15220,7 +15223,7 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ68">
         <v>1.46</v>
@@ -15348,7 +15351,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15429,7 +15432,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ69">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR69">
         <v>1.9</v>
@@ -15554,7 +15557,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15760,7 +15763,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15966,7 +15969,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16459,7 +16462,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ74">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR74">
         <v>1.37</v>
@@ -16584,7 +16587,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16790,7 +16793,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16996,7 +16999,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17408,7 +17411,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17820,7 +17823,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18104,7 +18107,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ82">
         <v>1.38</v>
@@ -18232,7 +18235,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18722,7 +18725,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ85">
         <v>0.93</v>
@@ -18850,7 +18853,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -18931,7 +18934,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ86">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR86">
         <v>1.56</v>
@@ -19674,7 +19677,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19880,7 +19883,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20086,7 +20089,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20292,7 +20295,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20704,7 +20707,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20988,7 +20991,7 @@
         <v>0.2</v>
       </c>
       <c r="AP96">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21609,7 +21612,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ99">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR99">
         <v>1.24</v>
@@ -21940,7 +21943,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22021,7 +22024,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ101">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR101">
         <v>1.23</v>
@@ -22224,7 +22227,7 @@
         <v>1.17</v>
       </c>
       <c r="AP102">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22558,7 +22561,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -23176,7 +23179,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23382,7 +23385,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23794,7 +23797,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24000,7 +24003,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24206,7 +24209,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24284,10 +24287,10 @@
         <v>1.5</v>
       </c>
       <c r="AP112">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ112">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR112">
         <v>1.44</v>
@@ -24412,7 +24415,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24824,7 +24827,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24902,7 +24905,7 @@
         <v>1.43</v>
       </c>
       <c r="AP115">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ115">
         <v>0.93</v>
@@ -25317,7 +25320,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ117">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR117">
         <v>1.93</v>
@@ -26060,7 +26063,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26141,7 +26144,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ121">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR121">
         <v>1.14</v>
@@ -26266,7 +26269,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26344,7 +26347,7 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -27090,7 +27093,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27171,7 +27174,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ126">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR126">
         <v>1.38</v>
@@ -27374,7 +27377,7 @@
         <v>1.29</v>
       </c>
       <c r="AP127">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
         <v>1.15</v>
@@ -27583,7 +27586,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ128">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR128">
         <v>1.38</v>
@@ -27789,7 +27792,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ129">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR129">
         <v>1.77</v>
@@ -28120,7 +28123,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28326,7 +28329,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28532,7 +28535,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -29356,7 +29359,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29974,7 +29977,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30258,7 +30261,7 @@
         <v>0.63</v>
       </c>
       <c r="AP141">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ141">
         <v>0.46</v>
@@ -30386,7 +30389,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30592,7 +30595,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30673,7 +30676,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ143">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR143">
         <v>1.8</v>
@@ -30798,7 +30801,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -31004,7 +31007,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31085,7 +31088,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ145">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR145">
         <v>1.39</v>
@@ -31416,7 +31419,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31494,7 +31497,7 @@
         <v>1.22</v>
       </c>
       <c r="AP147">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ147">
         <v>1.46</v>
@@ -31622,7 +31625,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31828,7 +31831,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32034,7 +32037,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32112,7 +32115,7 @@
         <v>0.89</v>
       </c>
       <c r="AP150">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ150">
         <v>0.93</v>
@@ -32652,7 +32655,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32733,7 +32736,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ153">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -32858,7 +32861,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33476,7 +33479,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33969,7 +33972,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ159">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR159">
         <v>1.46</v>
@@ -34175,7 +34178,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ160">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR160">
         <v>1.52</v>
@@ -34918,7 +34921,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -34996,7 +34999,7 @@
         <v>1.3</v>
       </c>
       <c r="AP164">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ164">
         <v>1.46</v>
@@ -35330,7 +35333,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35948,7 +35951,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36026,10 +36029,10 @@
         <v>1.6</v>
       </c>
       <c r="AP169">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ169">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR169">
         <v>1.46</v>
@@ -36154,7 +36157,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36360,7 +36363,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36566,7 +36569,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -37059,7 +37062,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ174">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR174">
         <v>1.61</v>
@@ -37596,7 +37599,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -37880,7 +37883,7 @@
         <v>1.18</v>
       </c>
       <c r="AP178">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ178">
         <v>1</v>
@@ -38214,7 +38217,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38292,7 +38295,7 @@
         <v>0.73</v>
       </c>
       <c r="AP180">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ180">
         <v>1</v>
@@ -38832,7 +38835,7 @@
         <v>86</v>
       </c>
       <c r="P183" t="s">
-        <v>294</v>
+        <v>217</v>
       </c>
       <c r="Q183">
         <v>5.2</v>
@@ -38913,7 +38916,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ183">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR183">
         <v>1.63</v>
@@ -40068,7 +40071,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40274,7 +40277,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40767,7 +40770,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ192">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR192">
         <v>2.13</v>
@@ -41176,7 +41179,7 @@
         <v>0.5</v>
       </c>
       <c r="AP194">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ194">
         <v>0.6899999999999999</v>
@@ -42206,7 +42209,7 @@
         <v>1</v>
       </c>
       <c r="AP199">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ199">
         <v>1.29</v>
@@ -42621,7 +42624,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ201">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR201">
         <v>1.3</v>
@@ -43364,7 +43367,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -44269,7 +44272,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ209">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AR209">
         <v>1.6</v>
@@ -45169,6 +45172,418 @@
       </c>
       <c r="BP213">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7486701</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F214">
+        <v>27</v>
+      </c>
+      <c r="G214" t="s">
+        <v>78</v>
+      </c>
+      <c r="H214" t="s">
+        <v>75</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>1</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214">
+        <v>1</v>
+      </c>
+      <c r="M214">
+        <v>1</v>
+      </c>
+      <c r="N214">
+        <v>2</v>
+      </c>
+      <c r="O214" t="s">
+        <v>217</v>
+      </c>
+      <c r="P214" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q214">
+        <v>5.6</v>
+      </c>
+      <c r="R214">
+        <v>2.05</v>
+      </c>
+      <c r="S214">
+        <v>2.31</v>
+      </c>
+      <c r="T214">
+        <v>1.49</v>
+      </c>
+      <c r="U214">
+        <v>2.45</v>
+      </c>
+      <c r="V214">
+        <v>3.28</v>
+      </c>
+      <c r="W214">
+        <v>1.3</v>
+      </c>
+      <c r="X214">
+        <v>8.6</v>
+      </c>
+      <c r="Y214">
+        <v>1.02</v>
+      </c>
+      <c r="Z214">
+        <v>4.9</v>
+      </c>
+      <c r="AA214">
+        <v>3.52</v>
+      </c>
+      <c r="AB214">
+        <v>1.72</v>
+      </c>
+      <c r="AC214">
+        <v>1.03</v>
+      </c>
+      <c r="AD214">
+        <v>7.5</v>
+      </c>
+      <c r="AE214">
+        <v>1.42</v>
+      </c>
+      <c r="AF214">
+        <v>2.75</v>
+      </c>
+      <c r="AG214">
+        <v>2</v>
+      </c>
+      <c r="AH214">
+        <v>1.75</v>
+      </c>
+      <c r="AI214">
+        <v>2.14</v>
+      </c>
+      <c r="AJ214">
+        <v>1.63</v>
+      </c>
+      <c r="AK214">
+        <v>2</v>
+      </c>
+      <c r="AL214">
+        <v>1.26</v>
+      </c>
+      <c r="AM214">
+        <v>1.17</v>
+      </c>
+      <c r="AN214">
+        <v>1.31</v>
+      </c>
+      <c r="AO214">
+        <v>1.69</v>
+      </c>
+      <c r="AP214">
+        <v>1.29</v>
+      </c>
+      <c r="AQ214">
+        <v>1.64</v>
+      </c>
+      <c r="AR214">
+        <v>1.44</v>
+      </c>
+      <c r="AS214">
+        <v>1.38</v>
+      </c>
+      <c r="AT214">
+        <v>2.82</v>
+      </c>
+      <c r="AU214">
+        <v>7</v>
+      </c>
+      <c r="AV214">
+        <v>8</v>
+      </c>
+      <c r="AW214">
+        <v>4</v>
+      </c>
+      <c r="AX214">
+        <v>13</v>
+      </c>
+      <c r="AY214">
+        <v>14</v>
+      </c>
+      <c r="AZ214">
+        <v>23</v>
+      </c>
+      <c r="BA214">
+        <v>7</v>
+      </c>
+      <c r="BB214">
+        <v>4</v>
+      </c>
+      <c r="BC214">
+        <v>11</v>
+      </c>
+      <c r="BD214">
+        <v>2.9</v>
+      </c>
+      <c r="BE214">
+        <v>6.4</v>
+      </c>
+      <c r="BF214">
+        <v>1.52</v>
+      </c>
+      <c r="BG214">
+        <v>1.5</v>
+      </c>
+      <c r="BH214">
+        <v>2.35</v>
+      </c>
+      <c r="BI214">
+        <v>1.83</v>
+      </c>
+      <c r="BJ214">
+        <v>1.83</v>
+      </c>
+      <c r="BK214">
+        <v>2.35</v>
+      </c>
+      <c r="BL214">
+        <v>1.5</v>
+      </c>
+      <c r="BM214">
+        <v>3.05</v>
+      </c>
+      <c r="BN214">
+        <v>1.3</v>
+      </c>
+      <c r="BO214">
+        <v>4.1</v>
+      </c>
+      <c r="BP214">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7486696</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45704.65625</v>
+      </c>
+      <c r="F215">
+        <v>27</v>
+      </c>
+      <c r="G215" t="s">
+        <v>84</v>
+      </c>
+      <c r="H215" t="s">
+        <v>74</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>0</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+      <c r="M215">
+        <v>2</v>
+      </c>
+      <c r="N215">
+        <v>2</v>
+      </c>
+      <c r="O215" t="s">
+        <v>86</v>
+      </c>
+      <c r="P215" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q215">
+        <v>6.8</v>
+      </c>
+      <c r="R215">
+        <v>2.27</v>
+      </c>
+      <c r="S215">
+        <v>1.95</v>
+      </c>
+      <c r="T215">
+        <v>1.39</v>
+      </c>
+      <c r="U215">
+        <v>2.81</v>
+      </c>
+      <c r="V215">
+        <v>2.75</v>
+      </c>
+      <c r="W215">
+        <v>1.4</v>
+      </c>
+      <c r="X215">
+        <v>7.6</v>
+      </c>
+      <c r="Y215">
+        <v>1.03</v>
+      </c>
+      <c r="Z215">
+        <v>7.1</v>
+      </c>
+      <c r="AA215">
+        <v>4.2</v>
+      </c>
+      <c r="AB215">
+        <v>1.45</v>
+      </c>
+      <c r="AC215">
+        <v>1.01</v>
+      </c>
+      <c r="AD215">
+        <v>8.4</v>
+      </c>
+      <c r="AE215">
+        <v>1.32</v>
+      </c>
+      <c r="AF215">
+        <v>3.2</v>
+      </c>
+      <c r="AG215">
+        <v>1.98</v>
+      </c>
+      <c r="AH215">
+        <v>1.77</v>
+      </c>
+      <c r="AI215">
+        <v>2.13</v>
+      </c>
+      <c r="AJ215">
+        <v>1.64</v>
+      </c>
+      <c r="AK215">
+        <v>2.49</v>
+      </c>
+      <c r="AL215">
+        <v>1.19</v>
+      </c>
+      <c r="AM215">
+        <v>1.1</v>
+      </c>
+      <c r="AN215">
+        <v>1.08</v>
+      </c>
+      <c r="AO215">
+        <v>1.77</v>
+      </c>
+      <c r="AP215">
+        <v>1</v>
+      </c>
+      <c r="AQ215">
+        <v>1.86</v>
+      </c>
+      <c r="AR215">
+        <v>1.43</v>
+      </c>
+      <c r="AS215">
+        <v>1.59</v>
+      </c>
+      <c r="AT215">
+        <v>3.02</v>
+      </c>
+      <c r="AU215">
+        <v>3</v>
+      </c>
+      <c r="AV215">
+        <v>10</v>
+      </c>
+      <c r="AW215">
+        <v>4</v>
+      </c>
+      <c r="AX215">
+        <v>9</v>
+      </c>
+      <c r="AY215">
+        <v>7</v>
+      </c>
+      <c r="AZ215">
+        <v>21</v>
+      </c>
+      <c r="BA215">
+        <v>2</v>
+      </c>
+      <c r="BB215">
+        <v>4</v>
+      </c>
+      <c r="BC215">
+        <v>6</v>
+      </c>
+      <c r="BD215">
+        <v>3.45</v>
+      </c>
+      <c r="BE215">
+        <v>7</v>
+      </c>
+      <c r="BF215">
+        <v>1.37</v>
+      </c>
+      <c r="BG215">
+        <v>1.43</v>
+      </c>
+      <c r="BH215">
+        <v>2.55</v>
+      </c>
+      <c r="BI215">
+        <v>1.72</v>
+      </c>
+      <c r="BJ215">
+        <v>1.95</v>
+      </c>
+      <c r="BK215">
+        <v>2.17</v>
+      </c>
+      <c r="BL215">
+        <v>1.58</v>
+      </c>
+      <c r="BM215">
+        <v>2.8</v>
+      </c>
+      <c r="BN215">
+        <v>1.36</v>
+      </c>
+      <c r="BO215">
+        <v>3.8</v>
+      </c>
+      <c r="BP215">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="309">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -670,6 +670,12 @@
     <t>['63']</t>
   </si>
   <si>
+    <t>['22', '64', '81']</t>
+  </si>
+  <si>
+    <t>['37']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -932,6 +938,9 @@
   </si>
   <si>
     <t>['67', '73']</t>
+  </si>
+  <si>
+    <t>['23', '32']</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP215"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1549,7 +1558,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1630,7 +1639,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2579,7 +2588,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2785,7 +2794,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3278,7 +3287,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ10">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3403,7 +3412,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3609,7 +3618,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3815,7 +3824,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3893,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ13">
         <v>1.64</v>
@@ -4021,7 +4030,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4099,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -4227,7 +4236,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4433,7 +4442,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4845,7 +4854,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -4926,7 +4935,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR18">
         <v>0.84</v>
@@ -5051,7 +5060,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5257,7 +5266,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5669,7 +5678,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5750,7 +5759,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ22">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR22">
         <v>1.89</v>
@@ -5875,7 +5884,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -7317,7 +7326,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7523,7 +7532,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7729,7 +7738,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7807,7 +7816,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -7935,7 +7944,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8141,7 +8150,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8222,7 +8231,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ34">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR34">
         <v>1.21</v>
@@ -8347,7 +8356,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8759,7 +8768,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9046,7 +9055,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR38">
         <v>1.73</v>
@@ -9377,7 +9386,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9583,7 +9592,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9789,7 +9798,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10485,7 +10494,7 @@
         <v>0.67</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ45">
         <v>1.46</v>
@@ -10691,7 +10700,7 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -10819,7 +10828,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11231,7 +11240,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11518,7 +11527,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR50">
         <v>1.71</v>
@@ -11930,7 +11939,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ52">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR52">
         <v>1.69</v>
@@ -12261,7 +12270,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12467,7 +12476,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12879,7 +12888,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13291,7 +13300,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13497,7 +13506,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13909,7 +13918,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14193,7 +14202,7 @@
         <v>0.75</v>
       </c>
       <c r="AP63">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ63">
         <v>1.46</v>
@@ -14402,7 +14411,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ64">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -14608,7 +14617,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR65">
         <v>1.18</v>
@@ -14939,7 +14948,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15351,7 +15360,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15557,7 +15566,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15763,7 +15772,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15841,7 +15850,7 @@
         <v>1.8</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ71">
         <v>1.38</v>
@@ -15969,7 +15978,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16587,7 +16596,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16793,7 +16802,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16999,7 +17008,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17077,7 +17086,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ77">
         <v>1.46</v>
@@ -17411,7 +17420,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17823,7 +17832,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -17904,7 +17913,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ81">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR81">
         <v>1.21</v>
@@ -18235,7 +18244,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18519,7 +18528,7 @@
         <v>1.8</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ84">
         <v>0.93</v>
@@ -18853,7 +18862,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19140,7 +19149,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ87">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR87">
         <v>1.94</v>
@@ -19677,7 +19686,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19883,7 +19892,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20089,7 +20098,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20295,7 +20304,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20707,7 +20716,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -21197,7 +21206,7 @@
         <v>1.67</v>
       </c>
       <c r="AP97">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ97">
         <v>0.93</v>
@@ -21818,7 +21827,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ100">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR100">
         <v>1.91</v>
@@ -21943,7 +21952,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22230,7 +22239,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR102">
         <v>1.5</v>
@@ -22433,7 +22442,7 @@
         <v>0.6</v>
       </c>
       <c r="AP103">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ103">
         <v>0.93</v>
@@ -22561,7 +22570,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -23179,7 +23188,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23385,7 +23394,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23466,7 +23475,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR108">
         <v>1.42</v>
@@ -23797,7 +23806,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24003,7 +24012,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24209,7 +24218,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24415,7 +24424,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24827,7 +24836,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -25111,7 +25120,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ116">
         <v>0.93</v>
@@ -25526,7 +25535,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ118">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR118">
         <v>1.37</v>
@@ -25729,7 +25738,7 @@
         <v>0.17</v>
       </c>
       <c r="AP119">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ119">
         <v>1</v>
@@ -25938,7 +25947,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ120">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR120">
         <v>1.36</v>
@@ -26063,7 +26072,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26269,7 +26278,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26759,7 +26768,7 @@
         <v>0.86</v>
       </c>
       <c r="AP124">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ124">
         <v>1.29</v>
@@ -27093,7 +27102,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27171,7 +27180,7 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ126">
         <v>1.86</v>
@@ -28123,7 +28132,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28329,7 +28338,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28535,7 +28544,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28822,7 +28831,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ134">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR134">
         <v>2.06</v>
@@ -29359,7 +29368,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29849,7 +29858,7 @@
         <v>1.5</v>
       </c>
       <c r="AP139">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ139">
         <v>1.15</v>
@@ -29977,7 +29986,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30389,7 +30398,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30595,7 +30604,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30801,7 +30810,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30879,7 +30888,7 @@
         <v>0.75</v>
       </c>
       <c r="AP144">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ144">
         <v>1.29</v>
@@ -31007,7 +31016,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31419,7 +31428,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31625,7 +31634,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31831,7 +31840,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -31912,7 +31921,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ149">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR149">
         <v>1.6</v>
@@ -32037,7 +32046,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32324,7 +32333,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ151">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR151">
         <v>2.01</v>
@@ -32655,7 +32664,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32733,7 +32742,7 @@
         <v>2</v>
       </c>
       <c r="AP153">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ153">
         <v>1.64</v>
@@ -32861,7 +32870,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33479,7 +33488,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33763,7 +33772,7 @@
         <v>1.44</v>
       </c>
       <c r="AP158">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ158">
         <v>1.15</v>
@@ -34381,7 +34390,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP161">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ161">
         <v>0.38</v>
@@ -34921,7 +34930,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35208,7 +35217,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ165">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR165">
         <v>1.27</v>
@@ -35333,7 +35342,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35826,7 +35835,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ168">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR168">
         <v>1.63</v>
@@ -35951,7 +35960,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36157,7 +36166,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36363,7 +36372,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36569,7 +36578,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36647,7 +36656,7 @@
         <v>0.5</v>
       </c>
       <c r="AP172">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ172">
         <v>0.38</v>
@@ -37599,7 +37608,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -37677,7 +37686,7 @@
         <v>0.5</v>
       </c>
       <c r="AP177">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ177">
         <v>0.46</v>
@@ -37886,7 +37895,7 @@
         <v>1</v>
       </c>
       <c r="AQ178">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR178">
         <v>1.45</v>
@@ -38217,7 +38226,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38501,7 +38510,7 @@
         <v>1.45</v>
       </c>
       <c r="AP181">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ181">
         <v>1.46</v>
@@ -39122,7 +39131,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ184">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR184">
         <v>1.32</v>
@@ -39659,7 +39668,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -40071,7 +40080,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40277,7 +40286,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40355,7 +40364,7 @@
         <v>1.09</v>
       </c>
       <c r="AP190">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ190">
         <v>1</v>
@@ -40483,7 +40492,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40895,7 +40904,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -41101,7 +41110,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -41182,7 +41191,7 @@
         <v>1</v>
       </c>
       <c r="AQ194">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR194">
         <v>1.47</v>
@@ -41385,10 +41394,10 @@
         <v>1.08</v>
       </c>
       <c r="AP195">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ195">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR195">
         <v>1.63</v>
@@ -42749,7 +42758,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -42955,7 +42964,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43367,7 +43376,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43573,7 +43582,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -43651,7 +43660,7 @@
         <v>0.42</v>
       </c>
       <c r="AP206">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ206">
         <v>0.46</v>
@@ -44191,7 +44200,7 @@
         <v>214</v>
       </c>
       <c r="P209" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q209">
         <v>4.75</v>
@@ -44397,7 +44406,7 @@
         <v>215</v>
       </c>
       <c r="P210" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q210">
         <v>2.8</v>
@@ -44603,7 +44612,7 @@
         <v>216</v>
       </c>
       <c r="P211" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q211">
         <v>2.06</v>
@@ -45015,7 +45024,7 @@
         <v>86</v>
       </c>
       <c r="P213" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q213">
         <v>2.65</v>
@@ -45427,7 +45436,7 @@
         <v>86</v>
       </c>
       <c r="P215" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q215">
         <v>6.8</v>
@@ -45584,6 +45593,418 @@
       </c>
       <c r="BP215">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7486991</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45705.5</v>
+      </c>
+      <c r="F216">
+        <v>27</v>
+      </c>
+      <c r="G216" t="s">
+        <v>82</v>
+      </c>
+      <c r="H216" t="s">
+        <v>79</v>
+      </c>
+      <c r="I216">
+        <v>1</v>
+      </c>
+      <c r="J216">
+        <v>2</v>
+      </c>
+      <c r="K216">
+        <v>3</v>
+      </c>
+      <c r="L216">
+        <v>3</v>
+      </c>
+      <c r="M216">
+        <v>2</v>
+      </c>
+      <c r="N216">
+        <v>5</v>
+      </c>
+      <c r="O216" t="s">
+        <v>218</v>
+      </c>
+      <c r="P216" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q216">
+        <v>1.91</v>
+      </c>
+      <c r="R216">
+        <v>2.28</v>
+      </c>
+      <c r="S216">
+        <v>6.6</v>
+      </c>
+      <c r="T216">
+        <v>1.41</v>
+      </c>
+      <c r="U216">
+        <v>2.7</v>
+      </c>
+      <c r="V216">
+        <v>2.8</v>
+      </c>
+      <c r="W216">
+        <v>1.38</v>
+      </c>
+      <c r="X216">
+        <v>7.4</v>
+      </c>
+      <c r="Y216">
+        <v>1.04</v>
+      </c>
+      <c r="Z216">
+        <v>1.54</v>
+      </c>
+      <c r="AA216">
+        <v>3.78</v>
+      </c>
+      <c r="AB216">
+        <v>6.5</v>
+      </c>
+      <c r="AC216">
+        <v>1.01</v>
+      </c>
+      <c r="AD216">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE216">
+        <v>1.33</v>
+      </c>
+      <c r="AF216">
+        <v>3.15</v>
+      </c>
+      <c r="AG216">
+        <v>1.98</v>
+      </c>
+      <c r="AH216">
+        <v>1.77</v>
+      </c>
+      <c r="AI216">
+        <v>2.23</v>
+      </c>
+      <c r="AJ216">
+        <v>1.58</v>
+      </c>
+      <c r="AK216">
+        <v>1.09</v>
+      </c>
+      <c r="AL216">
+        <v>1.18</v>
+      </c>
+      <c r="AM216">
+        <v>2.6</v>
+      </c>
+      <c r="AN216">
+        <v>2.08</v>
+      </c>
+      <c r="AO216">
+        <v>1</v>
+      </c>
+      <c r="AP216">
+        <v>2.14</v>
+      </c>
+      <c r="AQ216">
+        <v>0.93</v>
+      </c>
+      <c r="AR216">
+        <v>1.57</v>
+      </c>
+      <c r="AS216">
+        <v>1.31</v>
+      </c>
+      <c r="AT216">
+        <v>2.88</v>
+      </c>
+      <c r="AU216">
+        <v>8</v>
+      </c>
+      <c r="AV216">
+        <v>6</v>
+      </c>
+      <c r="AW216">
+        <v>15</v>
+      </c>
+      <c r="AX216">
+        <v>4</v>
+      </c>
+      <c r="AY216">
+        <v>25</v>
+      </c>
+      <c r="AZ216">
+        <v>10</v>
+      </c>
+      <c r="BA216">
+        <v>10</v>
+      </c>
+      <c r="BB216">
+        <v>5</v>
+      </c>
+      <c r="BC216">
+        <v>15</v>
+      </c>
+      <c r="BD216">
+        <v>1.32</v>
+      </c>
+      <c r="BE216">
+        <v>7</v>
+      </c>
+      <c r="BF216">
+        <v>3.8</v>
+      </c>
+      <c r="BG216">
+        <v>1.47</v>
+      </c>
+      <c r="BH216">
+        <v>2.43</v>
+      </c>
+      <c r="BI216">
+        <v>1.78</v>
+      </c>
+      <c r="BJ216">
+        <v>1.88</v>
+      </c>
+      <c r="BK216">
+        <v>2.28</v>
+      </c>
+      <c r="BL216">
+        <v>1.53</v>
+      </c>
+      <c r="BM216">
+        <v>2.95</v>
+      </c>
+      <c r="BN216">
+        <v>1.33</v>
+      </c>
+      <c r="BO216">
+        <v>3.9</v>
+      </c>
+      <c r="BP216">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7486698</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45705.625</v>
+      </c>
+      <c r="F217">
+        <v>27</v>
+      </c>
+      <c r="G217" t="s">
+        <v>81</v>
+      </c>
+      <c r="H217" t="s">
+        <v>76</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>1</v>
+      </c>
+      <c r="L217">
+        <v>1</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
+      </c>
+      <c r="N217">
+        <v>1</v>
+      </c>
+      <c r="O217" t="s">
+        <v>219</v>
+      </c>
+      <c r="P217" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q217">
+        <v>2.13</v>
+      </c>
+      <c r="R217">
+        <v>2.15</v>
+      </c>
+      <c r="S217">
+        <v>6</v>
+      </c>
+      <c r="T217">
+        <v>1.44</v>
+      </c>
+      <c r="U217">
+        <v>2.6</v>
+      </c>
+      <c r="V217">
+        <v>2.75</v>
+      </c>
+      <c r="W217">
+        <v>1.4</v>
+      </c>
+      <c r="X217">
+        <v>8.4</v>
+      </c>
+      <c r="Y217">
+        <v>1.02</v>
+      </c>
+      <c r="Z217">
+        <v>1.61</v>
+      </c>
+      <c r="AA217">
+        <v>3.57</v>
+      </c>
+      <c r="AB217">
+        <v>5.9</v>
+      </c>
+      <c r="AC217">
+        <v>1.01</v>
+      </c>
+      <c r="AD217">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE217">
+        <v>1.37</v>
+      </c>
+      <c r="AF217">
+        <v>2.95</v>
+      </c>
+      <c r="AG217">
+        <v>1.98</v>
+      </c>
+      <c r="AH217">
+        <v>1.77</v>
+      </c>
+      <c r="AI217">
+        <v>2.13</v>
+      </c>
+      <c r="AJ217">
+        <v>1.64</v>
+      </c>
+      <c r="AK217">
+        <v>1.13</v>
+      </c>
+      <c r="AL217">
+        <v>1.22</v>
+      </c>
+      <c r="AM217">
+        <v>2.23</v>
+      </c>
+      <c r="AN217">
+        <v>2</v>
+      </c>
+      <c r="AO217">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP217">
+        <v>2.07</v>
+      </c>
+      <c r="AQ217">
+        <v>0.64</v>
+      </c>
+      <c r="AR217">
+        <v>1.78</v>
+      </c>
+      <c r="AS217">
+        <v>1.3</v>
+      </c>
+      <c r="AT217">
+        <v>3.08</v>
+      </c>
+      <c r="AU217">
+        <v>2</v>
+      </c>
+      <c r="AV217">
+        <v>3</v>
+      </c>
+      <c r="AW217">
+        <v>6</v>
+      </c>
+      <c r="AX217">
+        <v>1</v>
+      </c>
+      <c r="AY217">
+        <v>8</v>
+      </c>
+      <c r="AZ217">
+        <v>4</v>
+      </c>
+      <c r="BA217">
+        <v>6</v>
+      </c>
+      <c r="BB217">
+        <v>3</v>
+      </c>
+      <c r="BC217">
+        <v>9</v>
+      </c>
+      <c r="BD217">
+        <v>1.4</v>
+      </c>
+      <c r="BE217">
+        <v>6.75</v>
+      </c>
+      <c r="BF217">
+        <v>3.4</v>
+      </c>
+      <c r="BG217">
+        <v>1.5</v>
+      </c>
+      <c r="BH217">
+        <v>2.33</v>
+      </c>
+      <c r="BI217">
+        <v>1.85</v>
+      </c>
+      <c r="BJ217">
+        <v>1.81</v>
+      </c>
+      <c r="BK217">
+        <v>2.38</v>
+      </c>
+      <c r="BL217">
+        <v>1.49</v>
+      </c>
+      <c r="BM217">
+        <v>3.1</v>
+      </c>
+      <c r="BN217">
+        <v>1.3</v>
+      </c>
+      <c r="BO217">
+        <v>4.1</v>
+      </c>
+      <c r="BP217">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="311">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -676,6 +676,9 @@
     <t>['37']</t>
   </si>
   <si>
+    <t>['11', '81']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -941,6 +944,9 @@
   </si>
   <si>
     <t>['23', '32']</t>
+  </si>
+  <si>
+    <t>['9']</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP219"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1558,7 +1564,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1842,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ3">
         <v>1.46</v>
@@ -2463,7 +2469,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ6">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2588,7 +2594,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2794,7 +2800,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3081,7 +3087,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ9">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3412,7 +3418,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3618,7 +3624,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3824,7 +3830,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -4030,7 +4036,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4236,7 +4242,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4442,7 +4448,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4726,7 +4732,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ17">
         <v>0.93</v>
@@ -4854,7 +4860,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -4932,7 +4938,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ18">
         <v>0.93</v>
@@ -5060,7 +5066,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5266,7 +5272,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5347,7 +5353,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ20">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR20">
         <v>1.45</v>
@@ -5678,7 +5684,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5884,7 +5890,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6171,7 +6177,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ24">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR24">
         <v>1.56</v>
@@ -6580,7 +6586,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ26">
         <v>1</v>
@@ -6789,7 +6795,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ27">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR27">
         <v>1</v>
@@ -7326,7 +7332,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7407,7 +7413,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ30">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
         <v>1.69</v>
@@ -7532,7 +7538,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7738,7 +7744,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7944,7 +7950,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8150,7 +8156,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8228,7 +8234,7 @@
         <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ34">
         <v>0.64</v>
@@ -8356,7 +8362,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8768,7 +8774,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9261,7 +9267,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ39">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR39">
         <v>0.8100000000000001</v>
@@ -9386,7 +9392,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9592,7 +9598,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9798,7 +9804,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -9879,7 +9885,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ42">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR42">
         <v>1.69</v>
@@ -10828,7 +10834,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11240,7 +11246,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -12142,7 +12148,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ53">
         <v>1.86</v>
@@ -12270,7 +12276,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12351,7 +12357,7 @@
         <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR54">
         <v>1.5</v>
@@ -12476,7 +12482,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12760,7 +12766,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ56">
         <v>1</v>
@@ -12888,7 +12894,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -12966,7 +12972,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ57">
         <v>0.46</v>
@@ -13300,7 +13306,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13506,7 +13512,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13918,7 +13924,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13999,7 +14005,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ62">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR62">
         <v>1.4</v>
@@ -14948,7 +14954,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15360,7 +15366,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15566,7 +15572,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15772,7 +15778,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15853,7 +15859,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ71">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR71">
         <v>1.35</v>
@@ -15978,7 +15984,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16059,7 +16065,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ72">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR72">
         <v>1.78</v>
@@ -16262,7 +16268,7 @@
         <v>0.6</v>
       </c>
       <c r="AP73">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ73">
         <v>1.46</v>
@@ -16468,7 +16474,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ74">
         <v>1.64</v>
@@ -16596,7 +16602,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16802,7 +16808,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17008,7 +17014,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17420,7 +17426,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17832,7 +17838,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18119,7 +18125,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ82">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR82">
         <v>1.61</v>
@@ -18244,7 +18250,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18862,7 +18868,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19686,7 +19692,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19767,7 +19773,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ90">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR90">
         <v>1.38</v>
@@ -19892,7 +19898,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20098,7 +20104,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20176,7 +20182,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ92">
         <v>1.46</v>
@@ -20304,7 +20310,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20382,7 +20388,7 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ93">
         <v>1</v>
@@ -20716,7 +20722,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20797,7 +20803,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ95">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR95">
         <v>1.89</v>
@@ -21952,7 +21958,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22570,7 +22576,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22857,7 +22863,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ105">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR105">
         <v>1.58</v>
@@ -23188,7 +23194,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23266,7 +23272,7 @@
         <v>0.71</v>
       </c>
       <c r="AP107">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ107">
         <v>1.46</v>
@@ -23394,7 +23400,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23472,7 +23478,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ108">
         <v>0.93</v>
@@ -23806,7 +23812,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23887,7 +23893,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ110">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR110">
         <v>1.9</v>
@@ -24012,7 +24018,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24218,7 +24224,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24424,7 +24430,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24836,7 +24842,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -25944,7 +25950,7 @@
         <v>0.63</v>
       </c>
       <c r="AP120">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ120">
         <v>0.64</v>
@@ -26072,7 +26078,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26278,7 +26284,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -27102,7 +27108,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27592,7 +27598,7 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ128">
         <v>1.64</v>
@@ -28007,7 +28013,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ130">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR130">
         <v>1.47</v>
@@ -28132,7 +28138,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28338,7 +28344,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28416,10 +28422,10 @@
         <v>1.78</v>
       </c>
       <c r="AP132">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ132">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR132">
         <v>1.25</v>
@@ -28544,7 +28550,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -29368,7 +29374,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29986,7 +29992,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30398,7 +30404,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30604,7 +30610,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30810,7 +30816,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -31016,7 +31022,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31094,7 +31100,7 @@
         <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ145">
         <v>1.86</v>
@@ -31428,7 +31434,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31634,7 +31640,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31840,7 +31846,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32046,7 +32052,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32536,7 +32542,7 @@
         <v>1.44</v>
       </c>
       <c r="AP152">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ152">
         <v>0.93</v>
@@ -32664,7 +32670,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32870,7 +32876,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33360,7 +33366,7 @@
         <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ156">
         <v>1.29</v>
@@ -33488,7 +33494,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -34393,7 +34399,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ161">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR161">
         <v>1.54</v>
@@ -34599,7 +34605,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ162">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR162">
         <v>1.45</v>
@@ -34802,7 +34808,7 @@
         <v>0.9</v>
       </c>
       <c r="AP163">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ163">
         <v>0.93</v>
@@ -34930,7 +34936,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35342,7 +35348,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35960,7 +35966,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36166,7 +36172,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36372,7 +36378,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36578,7 +36584,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36659,7 +36665,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ172">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR172">
         <v>1.54</v>
@@ -36862,7 +36868,7 @@
         <v>1.3</v>
       </c>
       <c r="AP173">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ173">
         <v>1.15</v>
@@ -37608,7 +37614,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -38101,7 +38107,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ179">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR179">
         <v>1.24</v>
@@ -38226,7 +38232,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -39540,7 +39546,7 @@
         <v>1</v>
       </c>
       <c r="AP186">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ186">
         <v>1.29</v>
@@ -39668,7 +39674,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -40080,7 +40086,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40158,10 +40164,10 @@
         <v>0.45</v>
       </c>
       <c r="AP189">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ189">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR189">
         <v>1.34</v>
@@ -40286,7 +40292,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40492,7 +40498,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40904,7 +40910,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -41110,7 +41116,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -42015,7 +42021,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ198">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR198">
         <v>1.82</v>
@@ -42758,7 +42764,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -42964,7 +42970,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43248,7 +43254,7 @@
         <v>1</v>
       </c>
       <c r="AP204">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ204">
         <v>1</v>
@@ -43376,7 +43382,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43454,7 +43460,7 @@
         <v>1.17</v>
       </c>
       <c r="AP205">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ205">
         <v>1.15</v>
@@ -43582,7 +43588,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -44075,7 +44081,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ208">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR208">
         <v>1.66</v>
@@ -44200,7 +44206,7 @@
         <v>214</v>
       </c>
       <c r="P209" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q209">
         <v>4.75</v>
@@ -44406,7 +44412,7 @@
         <v>215</v>
       </c>
       <c r="P210" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q210">
         <v>2.8</v>
@@ -44612,7 +44618,7 @@
         <v>216</v>
       </c>
       <c r="P211" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q211">
         <v>2.06</v>
@@ -45024,7 +45030,7 @@
         <v>86</v>
       </c>
       <c r="P213" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q213">
         <v>2.65</v>
@@ -45436,7 +45442,7 @@
         <v>86</v>
       </c>
       <c r="P215" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q215">
         <v>6.8</v>
@@ -45642,7 +45648,7 @@
         <v>218</v>
       </c>
       <c r="P216" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q216">
         <v>1.91</v>
@@ -46005,6 +46011,418 @@
       </c>
       <c r="BP217">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7486992</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45709.5</v>
+      </c>
+      <c r="F218">
+        <v>28</v>
+      </c>
+      <c r="G218" t="s">
+        <v>71</v>
+      </c>
+      <c r="H218" t="s">
+        <v>84</v>
+      </c>
+      <c r="I218">
+        <v>1</v>
+      </c>
+      <c r="J218">
+        <v>1</v>
+      </c>
+      <c r="K218">
+        <v>2</v>
+      </c>
+      <c r="L218">
+        <v>2</v>
+      </c>
+      <c r="M218">
+        <v>1</v>
+      </c>
+      <c r="N218">
+        <v>3</v>
+      </c>
+      <c r="O218" t="s">
+        <v>220</v>
+      </c>
+      <c r="P218" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q218">
+        <v>2.18</v>
+      </c>
+      <c r="R218">
+        <v>2.14</v>
+      </c>
+      <c r="S218">
+        <v>5.8</v>
+      </c>
+      <c r="T218">
+        <v>1.44</v>
+      </c>
+      <c r="U218">
+        <v>2.6</v>
+      </c>
+      <c r="V218">
+        <v>2.88</v>
+      </c>
+      <c r="W218">
+        <v>1.36</v>
+      </c>
+      <c r="X218">
+        <v>8.4</v>
+      </c>
+      <c r="Y218">
+        <v>1.05</v>
+      </c>
+      <c r="Z218">
+        <v>1.7</v>
+      </c>
+      <c r="AA218">
+        <v>3.37</v>
+      </c>
+      <c r="AB218">
+        <v>5.4</v>
+      </c>
+      <c r="AC218">
+        <v>1.07</v>
+      </c>
+      <c r="AD218">
+        <v>7.5</v>
+      </c>
+      <c r="AE218">
+        <v>1.37</v>
+      </c>
+      <c r="AF218">
+        <v>2.95</v>
+      </c>
+      <c r="AG218">
+        <v>2.15</v>
+      </c>
+      <c r="AH218">
+        <v>1.57</v>
+      </c>
+      <c r="AI218">
+        <v>2.05</v>
+      </c>
+      <c r="AJ218">
+        <v>1.69</v>
+      </c>
+      <c r="AK218">
+        <v>1.14</v>
+      </c>
+      <c r="AL218">
+        <v>1.26</v>
+      </c>
+      <c r="AM218">
+        <v>2.07</v>
+      </c>
+      <c r="AN218">
+        <v>1.62</v>
+      </c>
+      <c r="AO218">
+        <v>0.38</v>
+      </c>
+      <c r="AP218">
+        <v>1.71</v>
+      </c>
+      <c r="AQ218">
+        <v>0.36</v>
+      </c>
+      <c r="AR218">
+        <v>1.24</v>
+      </c>
+      <c r="AS218">
+        <v>1.12</v>
+      </c>
+      <c r="AT218">
+        <v>2.36</v>
+      </c>
+      <c r="AU218">
+        <v>6</v>
+      </c>
+      <c r="AV218">
+        <v>5</v>
+      </c>
+      <c r="AW218">
+        <v>9</v>
+      </c>
+      <c r="AX218">
+        <v>7</v>
+      </c>
+      <c r="AY218">
+        <v>18</v>
+      </c>
+      <c r="AZ218">
+        <v>16</v>
+      </c>
+      <c r="BA218">
+        <v>8</v>
+      </c>
+      <c r="BB218">
+        <v>0</v>
+      </c>
+      <c r="BC218">
+        <v>8</v>
+      </c>
+      <c r="BD218">
+        <v>1.63</v>
+      </c>
+      <c r="BE218">
+        <v>6.4</v>
+      </c>
+      <c r="BF218">
+        <v>2.55</v>
+      </c>
+      <c r="BG218">
+        <v>1.48</v>
+      </c>
+      <c r="BH218">
+        <v>2.38</v>
+      </c>
+      <c r="BI218">
+        <v>1.8</v>
+      </c>
+      <c r="BJ218">
+        <v>1.86</v>
+      </c>
+      <c r="BK218">
+        <v>2.3</v>
+      </c>
+      <c r="BL218">
+        <v>1.52</v>
+      </c>
+      <c r="BM218">
+        <v>3.05</v>
+      </c>
+      <c r="BN218">
+        <v>1.3</v>
+      </c>
+      <c r="BO218">
+        <v>4.1</v>
+      </c>
+      <c r="BP218">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7486994</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45709.625</v>
+      </c>
+      <c r="F219">
+        <v>28</v>
+      </c>
+      <c r="G219" t="s">
+        <v>85</v>
+      </c>
+      <c r="H219" t="s">
+        <v>82</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+      <c r="J219">
+        <v>1</v>
+      </c>
+      <c r="K219">
+        <v>1</v>
+      </c>
+      <c r="L219">
+        <v>0</v>
+      </c>
+      <c r="M219">
+        <v>1</v>
+      </c>
+      <c r="N219">
+        <v>1</v>
+      </c>
+      <c r="O219" t="s">
+        <v>86</v>
+      </c>
+      <c r="P219" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q219">
+        <v>4.1</v>
+      </c>
+      <c r="R219">
+        <v>1.97</v>
+      </c>
+      <c r="S219">
+        <v>2.85</v>
+      </c>
+      <c r="T219">
+        <v>1.52</v>
+      </c>
+      <c r="U219">
+        <v>2.39</v>
+      </c>
+      <c r="V219">
+        <v>3.3</v>
+      </c>
+      <c r="W219">
+        <v>1.28</v>
+      </c>
+      <c r="X219">
+        <v>8</v>
+      </c>
+      <c r="Y219">
+        <v>1.04</v>
+      </c>
+      <c r="Z219">
+        <v>3.26</v>
+      </c>
+      <c r="AA219">
+        <v>3.23</v>
+      </c>
+      <c r="AB219">
+        <v>2.2</v>
+      </c>
+      <c r="AC219">
+        <v>1.07</v>
+      </c>
+      <c r="AD219">
+        <v>7.5</v>
+      </c>
+      <c r="AE219">
+        <v>1.48</v>
+      </c>
+      <c r="AF219">
+        <v>2.37</v>
+      </c>
+      <c r="AG219">
+        <v>2.52</v>
+      </c>
+      <c r="AH219">
+        <v>1.46</v>
+      </c>
+      <c r="AI219">
+        <v>1.99</v>
+      </c>
+      <c r="AJ219">
+        <v>1.74</v>
+      </c>
+      <c r="AK219">
+        <v>1.63</v>
+      </c>
+      <c r="AL219">
+        <v>1.3</v>
+      </c>
+      <c r="AM219">
+        <v>1.3</v>
+      </c>
+      <c r="AN219">
+        <v>1.23</v>
+      </c>
+      <c r="AO219">
+        <v>1.38</v>
+      </c>
+      <c r="AP219">
+        <v>1.14</v>
+      </c>
+      <c r="AQ219">
+        <v>1.5</v>
+      </c>
+      <c r="AR219">
+        <v>1.36</v>
+      </c>
+      <c r="AS219">
+        <v>1.44</v>
+      </c>
+      <c r="AT219">
+        <v>2.8</v>
+      </c>
+      <c r="AU219">
+        <v>0</v>
+      </c>
+      <c r="AV219">
+        <v>4</v>
+      </c>
+      <c r="AW219">
+        <v>10</v>
+      </c>
+      <c r="AX219">
+        <v>6</v>
+      </c>
+      <c r="AY219">
+        <v>11</v>
+      </c>
+      <c r="AZ219">
+        <v>11</v>
+      </c>
+      <c r="BA219">
+        <v>1</v>
+      </c>
+      <c r="BB219">
+        <v>2</v>
+      </c>
+      <c r="BC219">
+        <v>3</v>
+      </c>
+      <c r="BD219">
+        <v>2.35</v>
+      </c>
+      <c r="BE219">
+        <v>6.25</v>
+      </c>
+      <c r="BF219">
+        <v>1.74</v>
+      </c>
+      <c r="BG219">
+        <v>1.49</v>
+      </c>
+      <c r="BH219">
+        <v>2.38</v>
+      </c>
+      <c r="BI219">
+        <v>1.84</v>
+      </c>
+      <c r="BJ219">
+        <v>1.83</v>
+      </c>
+      <c r="BK219">
+        <v>2.33</v>
+      </c>
+      <c r="BL219">
+        <v>1.5</v>
+      </c>
+      <c r="BM219">
+        <v>3.05</v>
+      </c>
+      <c r="BN219">
+        <v>1.3</v>
+      </c>
+      <c r="BO219">
+        <v>4.1</v>
+      </c>
+      <c r="BP219">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="313">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -679,6 +679,9 @@
     <t>['11', '81']</t>
   </si>
   <si>
+    <t>['34', '90+3']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -947,6 +950,9 @@
   </si>
   <si>
     <t>['9']</t>
+  </si>
+  <si>
+    <t>['38', '65']</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1564,7 +1570,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1851,7 +1857,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ3">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2594,7 +2600,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2672,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ7">
         <v>1.46</v>
@@ -2800,7 +2806,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2878,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ8">
         <v>0.93</v>
@@ -3418,7 +3424,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3624,7 +3630,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3830,7 +3836,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -4036,7 +4042,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4242,7 +4248,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4323,7 +4329,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ15">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4448,7 +4454,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4860,7 +4866,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -5066,7 +5072,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5272,7 +5278,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5684,7 +5690,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5890,7 +5896,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -5968,10 +5974,10 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ23">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR23">
         <v>2</v>
@@ -7207,7 +7213,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ29">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR29">
         <v>2.09</v>
@@ -7332,7 +7338,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7410,7 +7416,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ30">
         <v>1.5</v>
@@ -7538,7 +7544,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7744,7 +7750,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7950,7 +7956,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8156,7 +8162,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8362,7 +8368,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8774,7 +8780,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -8855,7 +8861,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ37">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR37">
         <v>1.39</v>
@@ -9058,7 +9064,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ38">
         <v>0.93</v>
@@ -9392,7 +9398,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9598,7 +9604,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9679,7 +9685,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ41">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR41">
         <v>1.24</v>
@@ -9804,7 +9810,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10088,7 +10094,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ43">
         <v>1.29</v>
@@ -10834,7 +10840,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11246,7 +11252,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11739,7 +11745,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ51">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR51">
         <v>1.33</v>
@@ -11942,7 +11948,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ52">
         <v>0.64</v>
@@ -12276,7 +12282,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12482,7 +12488,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12894,7 +12900,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13306,7 +13312,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13384,10 +13390,10 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ59">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR59">
         <v>1.8</v>
@@ -13512,7 +13518,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13924,7 +13930,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14954,7 +14960,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15241,7 +15247,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ68">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR68">
         <v>1.66</v>
@@ -15366,7 +15372,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15444,7 +15450,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ69">
         <v>1.86</v>
@@ -15572,7 +15578,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15778,7 +15784,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15984,7 +15990,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16062,7 +16068,7 @@
         <v>0.8</v>
       </c>
       <c r="AP72">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ72">
         <v>0.36</v>
@@ -16602,7 +16608,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16683,7 +16689,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ75">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR75">
         <v>2.05</v>
@@ -16808,7 +16814,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17014,7 +17020,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17095,7 +17101,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ77">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR77">
         <v>1.36</v>
@@ -17426,7 +17432,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17838,7 +17844,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18250,7 +18256,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18328,7 +18334,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ83">
         <v>1.29</v>
@@ -18868,7 +18874,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19361,7 +19367,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ88">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR88">
         <v>1.66</v>
@@ -19692,7 +19698,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19898,7 +19904,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -19976,7 +19982,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ91">
         <v>0.46</v>
@@ -20104,7 +20110,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20185,7 +20191,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ92">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR92">
         <v>1.5</v>
@@ -20310,7 +20316,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20594,7 +20600,7 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20722,7 +20728,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -21958,7 +21964,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22576,7 +22582,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22654,7 +22660,7 @@
         <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ104">
         <v>1</v>
@@ -23194,7 +23200,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23400,7 +23406,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23812,7 +23818,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23890,7 +23896,7 @@
         <v>1.63</v>
       </c>
       <c r="AP110">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ110">
         <v>1.5</v>
@@ -24018,7 +24024,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24099,7 +24105,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ111">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR111">
         <v>1.65</v>
@@ -24224,7 +24230,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24430,7 +24436,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24511,7 +24517,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ113">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR113">
         <v>1.54</v>
@@ -24842,7 +24848,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -26078,7 +26084,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26284,7 +26290,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -27108,7 +27114,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27395,7 +27401,7 @@
         <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR127">
         <v>1.4</v>
@@ -27804,7 +27810,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ129">
         <v>1.86</v>
@@ -28138,7 +28144,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28344,7 +28350,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28550,7 +28556,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28628,7 +28634,7 @@
         <v>1.25</v>
       </c>
       <c r="AP133">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ133">
         <v>1</v>
@@ -29246,7 +29252,7 @@
         <v>0.57</v>
       </c>
       <c r="AP136">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ136">
         <v>0.46</v>
@@ -29374,7 +29380,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29455,7 +29461,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ137">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR137">
         <v>1.59</v>
@@ -29658,7 +29664,7 @@
         <v>0.88</v>
       </c>
       <c r="AP138">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ138">
         <v>0.93</v>
@@ -29867,7 +29873,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ139">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR139">
         <v>1.55</v>
@@ -29992,7 +29998,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30404,7 +30410,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30610,7 +30616,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30816,7 +30822,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -31022,7 +31028,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31434,7 +31440,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31640,7 +31646,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31721,7 +31727,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ148">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR148">
         <v>1.32</v>
@@ -31846,7 +31852,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32052,7 +32058,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32670,7 +32676,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32876,7 +32882,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -32954,7 +32960,7 @@
         <v>0.44</v>
       </c>
       <c r="AP154">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ154">
         <v>1</v>
@@ -33494,7 +33500,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33781,7 +33787,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ158">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR158">
         <v>1.5</v>
@@ -34936,7 +34942,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35017,7 +35023,7 @@
         <v>1</v>
       </c>
       <c r="AQ164">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR164">
         <v>1.45</v>
@@ -35348,7 +35354,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35426,7 +35432,7 @@
         <v>1.3</v>
       </c>
       <c r="AP166">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ166">
         <v>0.93</v>
@@ -35966,7 +35972,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36172,7 +36178,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36378,7 +36384,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36584,7 +36590,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36871,7 +36877,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ173">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR173">
         <v>1.4</v>
@@ -37074,7 +37080,7 @@
         <v>1.7</v>
       </c>
       <c r="AP174">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ174">
         <v>1.64</v>
@@ -37614,7 +37620,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -38232,7 +38238,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38519,7 +38525,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ181">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR181">
         <v>1.62</v>
@@ -39340,7 +39346,7 @@
         <v>0.91</v>
       </c>
       <c r="AP185">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ185">
         <v>0.93</v>
@@ -39674,7 +39680,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -39958,7 +39964,7 @@
         <v>1.09</v>
       </c>
       <c r="AP188">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ188">
         <v>1</v>
@@ -40086,7 +40092,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40292,7 +40298,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40498,7 +40504,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40910,7 +40916,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -40991,7 +40997,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ193">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR193">
         <v>1.72</v>
@@ -41116,7 +41122,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -41812,7 +41818,7 @@
         <v>0.92</v>
       </c>
       <c r="AP197">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ197">
         <v>1</v>
@@ -42764,7 +42770,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -42842,7 +42848,7 @@
         <v>1.5</v>
       </c>
       <c r="AP202">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ202">
         <v>1.46</v>
@@ -42970,7 +42976,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43051,7 +43057,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ203">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AR203">
         <v>1.35</v>
@@ -43382,7 +43388,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43463,7 +43469,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ205">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR205">
         <v>1.24</v>
@@ -43588,7 +43594,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -44206,7 +44212,7 @@
         <v>214</v>
       </c>
       <c r="P209" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q209">
         <v>4.75</v>
@@ -44412,7 +44418,7 @@
         <v>215</v>
       </c>
       <c r="P210" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q210">
         <v>2.8</v>
@@ -44618,7 +44624,7 @@
         <v>216</v>
       </c>
       <c r="P211" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q211">
         <v>2.06</v>
@@ -45030,7 +45036,7 @@
         <v>86</v>
       </c>
       <c r="P213" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q213">
         <v>2.65</v>
@@ -45442,7 +45448,7 @@
         <v>86</v>
       </c>
       <c r="P215" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q215">
         <v>6.8</v>
@@ -45648,7 +45654,7 @@
         <v>218</v>
       </c>
       <c r="P216" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q216">
         <v>1.91</v>
@@ -46060,7 +46066,7 @@
         <v>220</v>
       </c>
       <c r="P218" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q218">
         <v>2.18</v>
@@ -46422,6 +46428,418 @@
         <v>4.1</v>
       </c>
       <c r="BP219">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7486704</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45710.54166666666</v>
+      </c>
+      <c r="F220">
+        <v>28</v>
+      </c>
+      <c r="G220" t="s">
+        <v>76</v>
+      </c>
+      <c r="H220" t="s">
+        <v>80</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220">
+        <v>1</v>
+      </c>
+      <c r="K220">
+        <v>2</v>
+      </c>
+      <c r="L220">
+        <v>2</v>
+      </c>
+      <c r="M220">
+        <v>2</v>
+      </c>
+      <c r="N220">
+        <v>4</v>
+      </c>
+      <c r="O220" t="s">
+        <v>221</v>
+      </c>
+      <c r="P220" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q220">
+        <v>4.3</v>
+      </c>
+      <c r="R220">
+        <v>2.06</v>
+      </c>
+      <c r="S220">
+        <v>2.6</v>
+      </c>
+      <c r="T220">
+        <v>1.46</v>
+      </c>
+      <c r="U220">
+        <v>2.55</v>
+      </c>
+      <c r="V220">
+        <v>3.05</v>
+      </c>
+      <c r="W220">
+        <v>1.32</v>
+      </c>
+      <c r="X220">
+        <v>7.5</v>
+      </c>
+      <c r="Y220">
+        <v>1.05</v>
+      </c>
+      <c r="Z220">
+        <v>3.76</v>
+      </c>
+      <c r="AA220">
+        <v>3.11</v>
+      </c>
+      <c r="AB220">
+        <v>2.07</v>
+      </c>
+      <c r="AC220">
+        <v>1.04</v>
+      </c>
+      <c r="AD220">
+        <v>9.5</v>
+      </c>
+      <c r="AE220">
+        <v>1.36</v>
+      </c>
+      <c r="AF220">
+        <v>3</v>
+      </c>
+      <c r="AG220">
+        <v>1.92</v>
+      </c>
+      <c r="AH220">
+        <v>1.82</v>
+      </c>
+      <c r="AI220">
+        <v>1.86</v>
+      </c>
+      <c r="AJ220">
+        <v>1.84</v>
+      </c>
+      <c r="AK220">
+        <v>1.69</v>
+      </c>
+      <c r="AL220">
+        <v>1.32</v>
+      </c>
+      <c r="AM220">
+        <v>1.25</v>
+      </c>
+      <c r="AN220">
+        <v>1.15</v>
+      </c>
+      <c r="AO220">
+        <v>1.46</v>
+      </c>
+      <c r="AP220">
+        <v>1.14</v>
+      </c>
+      <c r="AQ220">
+        <v>1.43</v>
+      </c>
+      <c r="AR220">
+        <v>1.73</v>
+      </c>
+      <c r="AS220">
+        <v>1.58</v>
+      </c>
+      <c r="AT220">
+        <v>3.31</v>
+      </c>
+      <c r="AU220">
+        <v>7</v>
+      </c>
+      <c r="AV220">
+        <v>6</v>
+      </c>
+      <c r="AW220">
+        <v>6</v>
+      </c>
+      <c r="AX220">
+        <v>7</v>
+      </c>
+      <c r="AY220">
+        <v>13</v>
+      </c>
+      <c r="AZ220">
+        <v>13</v>
+      </c>
+      <c r="BA220">
+        <v>4</v>
+      </c>
+      <c r="BB220">
+        <v>2</v>
+      </c>
+      <c r="BC220">
+        <v>6</v>
+      </c>
+      <c r="BD220">
+        <v>2.4</v>
+      </c>
+      <c r="BE220">
+        <v>6.25</v>
+      </c>
+      <c r="BF220">
+        <v>1.71</v>
+      </c>
+      <c r="BG220">
+        <v>1.43</v>
+      </c>
+      <c r="BH220">
+        <v>2.55</v>
+      </c>
+      <c r="BI220">
+        <v>1.75</v>
+      </c>
+      <c r="BJ220">
+        <v>1.92</v>
+      </c>
+      <c r="BK220">
+        <v>2.23</v>
+      </c>
+      <c r="BL220">
+        <v>1.56</v>
+      </c>
+      <c r="BM220">
+        <v>2.9</v>
+      </c>
+      <c r="BN220">
+        <v>1.34</v>
+      </c>
+      <c r="BO220">
+        <v>3.9</v>
+      </c>
+      <c r="BP220">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7486705</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45710.64583333334</v>
+      </c>
+      <c r="F221">
+        <v>28</v>
+      </c>
+      <c r="G221" t="s">
+        <v>75</v>
+      </c>
+      <c r="H221" t="s">
+        <v>77</v>
+      </c>
+      <c r="I221">
+        <v>0</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>0</v>
+      </c>
+      <c r="L221">
+        <v>2</v>
+      </c>
+      <c r="M221">
+        <v>0</v>
+      </c>
+      <c r="N221">
+        <v>2</v>
+      </c>
+      <c r="O221" t="s">
+        <v>167</v>
+      </c>
+      <c r="P221" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q221">
+        <v>2</v>
+      </c>
+      <c r="R221">
+        <v>2.28</v>
+      </c>
+      <c r="S221">
+        <v>6.1</v>
+      </c>
+      <c r="T221">
+        <v>1.38</v>
+      </c>
+      <c r="U221">
+        <v>2.75</v>
+      </c>
+      <c r="V221">
+        <v>2.9</v>
+      </c>
+      <c r="W221">
+        <v>1.38</v>
+      </c>
+      <c r="X221">
+        <v>6.75</v>
+      </c>
+      <c r="Y221">
+        <v>1.06</v>
+      </c>
+      <c r="Z221">
+        <v>1.73</v>
+      </c>
+      <c r="AA221">
+        <v>3.45</v>
+      </c>
+      <c r="AB221">
+        <v>5</v>
+      </c>
+      <c r="AC221">
+        <v>1.02</v>
+      </c>
+      <c r="AD221">
+        <v>11.5</v>
+      </c>
+      <c r="AE221">
+        <v>1.3</v>
+      </c>
+      <c r="AF221">
+        <v>3.3</v>
+      </c>
+      <c r="AG221">
+        <v>1.95</v>
+      </c>
+      <c r="AH221">
+        <v>1.79</v>
+      </c>
+      <c r="AI221">
+        <v>2.18</v>
+      </c>
+      <c r="AJ221">
+        <v>1.58</v>
+      </c>
+      <c r="AK221">
+        <v>1.12</v>
+      </c>
+      <c r="AL221">
+        <v>1.2</v>
+      </c>
+      <c r="AM221">
+        <v>2.4</v>
+      </c>
+      <c r="AN221">
+        <v>1.85</v>
+      </c>
+      <c r="AO221">
+        <v>1.15</v>
+      </c>
+      <c r="AP221">
+        <v>1.93</v>
+      </c>
+      <c r="AQ221">
+        <v>1.07</v>
+      </c>
+      <c r="AR221">
+        <v>1.82</v>
+      </c>
+      <c r="AS221">
+        <v>1.34</v>
+      </c>
+      <c r="AT221">
+        <v>3.16</v>
+      </c>
+      <c r="AU221">
+        <v>8</v>
+      </c>
+      <c r="AV221">
+        <v>2</v>
+      </c>
+      <c r="AW221">
+        <v>8</v>
+      </c>
+      <c r="AX221">
+        <v>7</v>
+      </c>
+      <c r="AY221">
+        <v>18</v>
+      </c>
+      <c r="AZ221">
+        <v>11</v>
+      </c>
+      <c r="BA221">
+        <v>8</v>
+      </c>
+      <c r="BB221">
+        <v>3</v>
+      </c>
+      <c r="BC221">
+        <v>11</v>
+      </c>
+      <c r="BD221">
+        <v>1.38</v>
+      </c>
+      <c r="BE221">
+        <v>6.75</v>
+      </c>
+      <c r="BF221">
+        <v>3.45</v>
+      </c>
+      <c r="BG221">
+        <v>1.49</v>
+      </c>
+      <c r="BH221">
+        <v>2.38</v>
+      </c>
+      <c r="BI221">
+        <v>1.82</v>
+      </c>
+      <c r="BJ221">
+        <v>1.84</v>
+      </c>
+      <c r="BK221">
+        <v>2.3</v>
+      </c>
+      <c r="BL221">
+        <v>1.52</v>
+      </c>
+      <c r="BM221">
+        <v>3</v>
+      </c>
+      <c r="BN221">
+        <v>1.32</v>
+      </c>
+      <c r="BO221">
+        <v>3.95</v>
+      </c>
+      <c r="BP221">
         <v>1.18</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="314">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -682,6 +682,9 @@
     <t>['34', '90+3']</t>
   </si>
   <si>
+    <t>['20', '57']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -1314,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP221"/>
+  <dimension ref="A1:BP223"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1570,7 +1573,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -2063,7 +2066,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ4">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2472,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6">
         <v>1.5</v>
@@ -2600,7 +2603,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2681,7 +2684,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ7">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2806,7 +2809,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3424,7 +3427,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3502,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ11">
         <v>1.86</v>
@@ -3630,7 +3633,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3836,7 +3839,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -4042,7 +4045,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4248,7 +4251,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4454,7 +4457,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4866,7 +4869,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -5072,7 +5075,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5150,7 +5153,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ19">
         <v>0.93</v>
@@ -5278,7 +5281,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5565,7 +5568,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ21">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -5690,7 +5693,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5896,7 +5899,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -7007,7 +7010,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ28">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -7338,7 +7341,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7544,7 +7547,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7622,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ31">
         <v>1.29</v>
@@ -7750,7 +7753,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7956,7 +7959,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8034,7 +8037,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ33">
         <v>0.93</v>
@@ -8162,7 +8165,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8368,7 +8371,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8780,7 +8783,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9398,7 +9401,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9479,7 +9482,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ40">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9604,7 +9607,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9682,7 +9685,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ41">
         <v>1.07</v>
@@ -9810,7 +9813,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10300,10 +10303,10 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ44">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR44">
         <v>2.23</v>
@@ -10509,7 +10512,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ45">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR45">
         <v>1.51</v>
@@ -10840,7 +10843,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11252,7 +11255,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -12282,7 +12285,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12488,7 +12491,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12900,7 +12903,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -12981,7 +12984,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ57">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR57">
         <v>1.23</v>
@@ -13312,7 +13315,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13518,7 +13521,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13802,7 +13805,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ61">
         <v>1.29</v>
@@ -13930,7 +13933,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14008,7 +14011,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ62">
         <v>0.36</v>
@@ -14217,7 +14220,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ63">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -14960,7 +14963,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15372,7 +15375,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15578,7 +15581,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15784,7 +15787,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15990,7 +15993,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16277,7 +16280,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ73">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR73">
         <v>1.51</v>
@@ -16608,7 +16611,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16686,7 +16689,7 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ75">
         <v>1.07</v>
@@ -16814,7 +16817,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17020,7 +17023,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17307,7 +17310,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ78">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR78">
         <v>1.54</v>
@@ -17432,7 +17435,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17510,7 +17513,7 @@
         <v>1.2</v>
       </c>
       <c r="AP79">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -17844,7 +17847,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18256,7 +18259,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18874,7 +18877,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19573,7 +19576,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ89">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR89">
         <v>1.6</v>
@@ -19698,7 +19701,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19776,7 +19779,7 @@
         <v>1.71</v>
       </c>
       <c r="AP90">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ90">
         <v>1.5</v>
@@ -19904,7 +19907,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -19985,7 +19988,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ91">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR91">
         <v>1.87</v>
@@ -20110,7 +20113,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20316,7 +20319,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20728,7 +20731,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20806,7 +20809,7 @@
         <v>0.83</v>
       </c>
       <c r="AP95">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ95">
         <v>0.36</v>
@@ -21964,7 +21967,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22582,7 +22585,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -23075,7 +23078,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ106">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR106">
         <v>1.16</v>
@@ -23200,7 +23203,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23281,7 +23284,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ107">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR107">
         <v>1.21</v>
@@ -23406,7 +23409,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23690,7 +23693,7 @@
         <v>1.29</v>
       </c>
       <c r="AP109">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -23818,7 +23821,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24024,7 +24027,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24230,7 +24233,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24436,7 +24439,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24848,7 +24851,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -25544,7 +25547,7 @@
         <v>0.71</v>
       </c>
       <c r="AP118">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ118">
         <v>0.64</v>
@@ -26084,7 +26087,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26290,7 +26293,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26986,7 +26989,7 @@
         <v>0.57</v>
       </c>
       <c r="AP125">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ125">
         <v>0.93</v>
@@ -27114,7 +27117,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -28144,7 +28147,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28350,7 +28353,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28556,7 +28559,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28840,7 +28843,7 @@
         <v>1.25</v>
       </c>
       <c r="AP134">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ134">
         <v>0.93</v>
@@ -29049,7 +29052,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ135">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR135">
         <v>1.36</v>
@@ -29255,7 +29258,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ136">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR136">
         <v>1.72</v>
@@ -29380,7 +29383,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29998,7 +30001,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30076,7 +30079,7 @@
         <v>0.13</v>
       </c>
       <c r="AP140">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ140">
         <v>1</v>
@@ -30285,7 +30288,7 @@
         <v>1</v>
       </c>
       <c r="AQ141">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR141">
         <v>1.41</v>
@@ -30410,7 +30413,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30616,7 +30619,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30822,7 +30825,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -31028,7 +31031,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31440,7 +31443,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31521,7 +31524,7 @@
         <v>1</v>
       </c>
       <c r="AQ147">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR147">
         <v>1.41</v>
@@ -31646,7 +31649,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31852,7 +31855,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32058,7 +32061,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32342,7 +32345,7 @@
         <v>0.67</v>
       </c>
       <c r="AP151">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ151">
         <v>0.64</v>
@@ -32676,7 +32679,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32882,7 +32885,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33169,7 +33172,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ155">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR155">
         <v>1.16</v>
@@ -33500,7 +33503,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33990,7 +33993,7 @@
         <v>1.78</v>
       </c>
       <c r="AP159">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ159">
         <v>1.64</v>
@@ -34942,7 +34945,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35354,7 +35357,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35972,7 +35975,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36178,7 +36181,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36256,7 +36259,7 @@
         <v>1.2</v>
       </c>
       <c r="AP170">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36384,7 +36387,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36462,7 +36465,7 @@
         <v>0.7</v>
       </c>
       <c r="AP171">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ171">
         <v>1</v>
@@ -36590,7 +36593,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -37289,7 +37292,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ175">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR175">
         <v>1.78</v>
@@ -37620,7 +37623,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -37701,7 +37704,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ177">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR177">
         <v>1.54</v>
@@ -38238,7 +38241,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -39680,7 +39683,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -39758,10 +39761,10 @@
         <v>1.36</v>
       </c>
       <c r="AP187">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ187">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR187">
         <v>1.38</v>
@@ -40092,7 +40095,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40298,7 +40301,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40504,7 +40507,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40585,7 +40588,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ191">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR191">
         <v>1.78</v>
@@ -40788,7 +40791,7 @@
         <v>1.64</v>
       </c>
       <c r="AP192">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ192">
         <v>1.64</v>
@@ -40916,7 +40919,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -41122,7 +41125,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -42770,7 +42773,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -42851,7 +42854,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ202">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR202">
         <v>1.75</v>
@@ -42976,7 +42979,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43054,7 +43057,7 @@
         <v>1.33</v>
       </c>
       <c r="AP203">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ203">
         <v>1.43</v>
@@ -43388,7 +43391,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43594,7 +43597,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -43675,7 +43678,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ206">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR206">
         <v>1.62</v>
@@ -43878,7 +43881,7 @@
         <v>1.08</v>
       </c>
       <c r="AP207">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ207">
         <v>1</v>
@@ -44212,7 +44215,7 @@
         <v>214</v>
       </c>
       <c r="P209" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q209">
         <v>4.75</v>
@@ -44418,7 +44421,7 @@
         <v>215</v>
       </c>
       <c r="P210" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q210">
         <v>2.8</v>
@@ -44624,7 +44627,7 @@
         <v>216</v>
       </c>
       <c r="P211" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q211">
         <v>2.06</v>
@@ -45036,7 +45039,7 @@
         <v>86</v>
       </c>
       <c r="P213" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q213">
         <v>2.65</v>
@@ -45448,7 +45451,7 @@
         <v>86</v>
       </c>
       <c r="P215" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q215">
         <v>6.8</v>
@@ -45654,7 +45657,7 @@
         <v>218</v>
       </c>
       <c r="P216" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q216">
         <v>1.91</v>
@@ -46066,7 +46069,7 @@
         <v>220</v>
       </c>
       <c r="P218" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q218">
         <v>2.18</v>
@@ -46478,7 +46481,7 @@
         <v>221</v>
       </c>
       <c r="P220" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q220">
         <v>4.3</v>
@@ -46783,16 +46786,16 @@
         <v>2</v>
       </c>
       <c r="AW221">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX221">
         <v>7</v>
       </c>
       <c r="AY221">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ221">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA221">
         <v>8</v>
@@ -46841,6 +46844,418 @@
       </c>
       <c r="BP221">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7486706</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45711.41666666666</v>
+      </c>
+      <c r="F222">
+        <v>28</v>
+      </c>
+      <c r="G222" t="s">
+        <v>79</v>
+      </c>
+      <c r="H222" t="s">
+        <v>78</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>0</v>
+      </c>
+      <c r="N222">
+        <v>0</v>
+      </c>
+      <c r="O222" t="s">
+        <v>86</v>
+      </c>
+      <c r="P222" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q222">
+        <v>3.15</v>
+      </c>
+      <c r="R222">
+        <v>1.94</v>
+      </c>
+      <c r="S222">
+        <v>3.7</v>
+      </c>
+      <c r="T222">
+        <v>1.54</v>
+      </c>
+      <c r="U222">
+        <v>2.34</v>
+      </c>
+      <c r="V222">
+        <v>3.3</v>
+      </c>
+      <c r="W222">
+        <v>1.27</v>
+      </c>
+      <c r="X222">
+        <v>8</v>
+      </c>
+      <c r="Y222">
+        <v>1.04</v>
+      </c>
+      <c r="Z222">
+        <v>2.45</v>
+      </c>
+      <c r="AA222">
+        <v>3.12</v>
+      </c>
+      <c r="AB222">
+        <v>2.93</v>
+      </c>
+      <c r="AC222">
+        <v>1.07</v>
+      </c>
+      <c r="AD222">
+        <v>7</v>
+      </c>
+      <c r="AE222">
+        <v>1.45</v>
+      </c>
+      <c r="AF222">
+        <v>2.65</v>
+      </c>
+      <c r="AG222">
+        <v>2.1</v>
+      </c>
+      <c r="AH222">
+        <v>1.6</v>
+      </c>
+      <c r="AI222">
+        <v>1.99</v>
+      </c>
+      <c r="AJ222">
+        <v>1.73</v>
+      </c>
+      <c r="AK222">
+        <v>1.37</v>
+      </c>
+      <c r="AL222">
+        <v>1.32</v>
+      </c>
+      <c r="AM222">
+        <v>1.5</v>
+      </c>
+      <c r="AN222">
+        <v>0.92</v>
+      </c>
+      <c r="AO222">
+        <v>0.46</v>
+      </c>
+      <c r="AP222">
+        <v>0.93</v>
+      </c>
+      <c r="AQ222">
+        <v>0.5</v>
+      </c>
+      <c r="AR222">
+        <v>1.35</v>
+      </c>
+      <c r="AS222">
+        <v>1.35</v>
+      </c>
+      <c r="AT222">
+        <v>2.7</v>
+      </c>
+      <c r="AU222">
+        <v>4</v>
+      </c>
+      <c r="AV222">
+        <v>5</v>
+      </c>
+      <c r="AW222">
+        <v>13</v>
+      </c>
+      <c r="AX222">
+        <v>5</v>
+      </c>
+      <c r="AY222">
+        <v>20</v>
+      </c>
+      <c r="AZ222">
+        <v>13</v>
+      </c>
+      <c r="BA222">
+        <v>3</v>
+      </c>
+      <c r="BB222">
+        <v>3</v>
+      </c>
+      <c r="BC222">
+        <v>6</v>
+      </c>
+      <c r="BD222">
+        <v>1.85</v>
+      </c>
+      <c r="BE222">
+        <v>6.1</v>
+      </c>
+      <c r="BF222">
+        <v>2.18</v>
+      </c>
+      <c r="BG222">
+        <v>1.5</v>
+      </c>
+      <c r="BH222">
+        <v>2.35</v>
+      </c>
+      <c r="BI222">
+        <v>1.85</v>
+      </c>
+      <c r="BJ222">
+        <v>1.81</v>
+      </c>
+      <c r="BK222">
+        <v>2.35</v>
+      </c>
+      <c r="BL222">
+        <v>1.5</v>
+      </c>
+      <c r="BM222">
+        <v>3.05</v>
+      </c>
+      <c r="BN222">
+        <v>1.3</v>
+      </c>
+      <c r="BO222">
+        <v>4.1</v>
+      </c>
+      <c r="BP222">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7486993</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45711.625</v>
+      </c>
+      <c r="F223">
+        <v>28</v>
+      </c>
+      <c r="G223" t="s">
+        <v>74</v>
+      </c>
+      <c r="H223" t="s">
+        <v>83</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="J223">
+        <v>1</v>
+      </c>
+      <c r="K223">
+        <v>2</v>
+      </c>
+      <c r="L223">
+        <v>2</v>
+      </c>
+      <c r="M223">
+        <v>1</v>
+      </c>
+      <c r="N223">
+        <v>3</v>
+      </c>
+      <c r="O223" t="s">
+        <v>222</v>
+      </c>
+      <c r="P223" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q223">
+        <v>2.31</v>
+      </c>
+      <c r="R223">
+        <v>2.06</v>
+      </c>
+      <c r="S223">
+        <v>5.4</v>
+      </c>
+      <c r="T223">
+        <v>1.49</v>
+      </c>
+      <c r="U223">
+        <v>2.45</v>
+      </c>
+      <c r="V223">
+        <v>2.75</v>
+      </c>
+      <c r="W223">
+        <v>1.4</v>
+      </c>
+      <c r="X223">
+        <v>7.5</v>
+      </c>
+      <c r="Y223">
+        <v>1.05</v>
+      </c>
+      <c r="Z223">
+        <v>1.84</v>
+      </c>
+      <c r="AA223">
+        <v>3.41</v>
+      </c>
+      <c r="AB223">
+        <v>4.3</v>
+      </c>
+      <c r="AC223">
+        <v>1.04</v>
+      </c>
+      <c r="AD223">
+        <v>9.5</v>
+      </c>
+      <c r="AE223">
+        <v>1.41</v>
+      </c>
+      <c r="AF223">
+        <v>2.75</v>
+      </c>
+      <c r="AG223">
+        <v>1.92</v>
+      </c>
+      <c r="AH223">
+        <v>1.82</v>
+      </c>
+      <c r="AI223">
+        <v>2.11</v>
+      </c>
+      <c r="AJ223">
+        <v>1.65</v>
+      </c>
+      <c r="AK223">
+        <v>1.17</v>
+      </c>
+      <c r="AL223">
+        <v>1.27</v>
+      </c>
+      <c r="AM223">
+        <v>1.99</v>
+      </c>
+      <c r="AN223">
+        <v>1.77</v>
+      </c>
+      <c r="AO223">
+        <v>1.46</v>
+      </c>
+      <c r="AP223">
+        <v>1.86</v>
+      </c>
+      <c r="AQ223">
+        <v>1.36</v>
+      </c>
+      <c r="AR223">
+        <v>2.11</v>
+      </c>
+      <c r="AS223">
+        <v>1.16</v>
+      </c>
+      <c r="AT223">
+        <v>3.27</v>
+      </c>
+      <c r="AU223">
+        <v>5</v>
+      </c>
+      <c r="AV223">
+        <v>5</v>
+      </c>
+      <c r="AW223">
+        <v>6</v>
+      </c>
+      <c r="AX223">
+        <v>7</v>
+      </c>
+      <c r="AY223">
+        <v>13</v>
+      </c>
+      <c r="AZ223">
+        <v>13</v>
+      </c>
+      <c r="BA223">
+        <v>4</v>
+      </c>
+      <c r="BB223">
+        <v>4</v>
+      </c>
+      <c r="BC223">
+        <v>8</v>
+      </c>
+      <c r="BD223">
+        <v>1.5</v>
+      </c>
+      <c r="BE223">
+        <v>6.5</v>
+      </c>
+      <c r="BF223">
+        <v>2.9</v>
+      </c>
+      <c r="BG223">
+        <v>1.49</v>
+      </c>
+      <c r="BH223">
+        <v>2.38</v>
+      </c>
+      <c r="BI223">
+        <v>1.82</v>
+      </c>
+      <c r="BJ223">
+        <v>1.84</v>
+      </c>
+      <c r="BK223">
+        <v>2.3</v>
+      </c>
+      <c r="BL223">
+        <v>1.52</v>
+      </c>
+      <c r="BM223">
+        <v>3.05</v>
+      </c>
+      <c r="BN223">
+        <v>1.3</v>
+      </c>
+      <c r="BO223">
+        <v>4.1</v>
+      </c>
+      <c r="BP223">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="317">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -685,6 +685,9 @@
     <t>['20', '57']</t>
   </si>
   <si>
+    <t>['59']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -956,6 +959,12 @@
   </si>
   <si>
     <t>['38', '65']</t>
+  </si>
+  <si>
+    <t>['37', '62']</t>
+  </si>
+  <si>
+    <t>['8', '39', '69']</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP223"/>
+  <dimension ref="A1:BP225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1573,7 +1582,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1651,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AQ2">
         <v>0.93</v>
@@ -1857,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ3">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2063,10 +2072,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2269,10 +2278,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2478,7 +2487,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2603,7 +2612,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2681,10 +2690,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AQ7">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2809,7 +2818,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2887,10 +2896,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ8">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3093,10 +3102,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ9">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3299,19 +3308,19 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="AQ10">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AU10">
         <v>6</v>
@@ -3427,7 +3436,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3499,10 +3508,10 @@
         <v>1.13</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP11">
         <v>0.93</v>
@@ -3511,13 +3520,13 @@
         <v>1.86</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AU11">
         <v>5</v>
@@ -3633,7 +3642,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3705,25 +3714,25 @@
         <v>2.1</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP12">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AQ12">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AU12">
         <v>9</v>
@@ -3839,7 +3848,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3911,25 +3920,25 @@
         <v>1.4</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP13">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ13">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU13">
         <v>8</v>
@@ -4045,7 +4054,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4117,25 +4126,25 @@
         <v>1.72</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP14">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AU14">
         <v>7</v>
@@ -4251,7 +4260,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4326,22 +4335,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ15">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AU15">
         <v>5</v>
@@ -4457,7 +4466,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4529,25 +4538,25 @@
         <v>1.3</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AU16">
         <v>7</v>
@@ -4735,25 +4744,25 @@
         <v>1.55</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ17">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AU17">
         <v>3</v>
@@ -4869,7 +4878,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -4941,25 +4950,25 @@
         <v>1.8</v>
       </c>
       <c r="AN18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP18">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ18">
         <v>0.93</v>
       </c>
       <c r="AR18">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="AS18">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="AT18">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AU18">
         <v>2</v>
@@ -5075,7 +5084,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5150,22 +5159,22 @@
         <v>1</v>
       </c>
       <c r="AO19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP19">
         <v>1.86</v>
       </c>
       <c r="AQ19">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR19">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AS19">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="AT19">
-        <v>3.54</v>
+        <v>3</v>
       </c>
       <c r="AU19">
         <v>8</v>
@@ -5281,7 +5290,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5353,25 +5362,25 @@
         <v>1.6</v>
       </c>
       <c r="AN20">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO20">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP20">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="AQ20">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR20">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AS20">
-        <v>0.71</v>
+        <v>1.19</v>
       </c>
       <c r="AT20">
-        <v>2.16</v>
+        <v>2.83</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5562,22 +5571,22 @@
         <v>3</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP21">
+        <v>1.43</v>
+      </c>
+      <c r="AQ21">
+        <v>1.61</v>
+      </c>
+      <c r="AR21">
         <v>1.71</v>
       </c>
-      <c r="AQ21">
-        <v>1.36</v>
-      </c>
-      <c r="AR21">
-        <v>1.66</v>
-      </c>
       <c r="AS21">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AT21">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="AU21">
         <v>2</v>
@@ -5693,7 +5702,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5765,25 +5774,25 @@
         <v>2.35</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AQ22">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR22">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AS22">
-        <v>0.77</v>
+        <v>1.18</v>
       </c>
       <c r="AT22">
-        <v>2.66</v>
+        <v>2.97</v>
       </c>
       <c r="AU22">
         <v>2</v>
@@ -5899,7 +5908,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -5971,25 +5980,25 @@
         <v>1.95</v>
       </c>
       <c r="AN23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP23">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AQ23">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AR23">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AS23">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AT23">
-        <v>4.23</v>
+        <v>3.77</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -6177,25 +6186,25 @@
         <v>1.36</v>
       </c>
       <c r="AN24">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AR24">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AS24">
-        <v>0.54</v>
+        <v>1.06</v>
       </c>
       <c r="AT24">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="AU24">
         <v>5</v>
@@ -6383,25 +6392,25 @@
         <v>1.26</v>
       </c>
       <c r="AN25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO25">
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="AR25">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="AS25">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AT25">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6589,25 +6598,25 @@
         <v>1.63</v>
       </c>
       <c r="AN26">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AP26">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR26">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AS26">
-        <v>0.91</v>
+        <v>1.11</v>
       </c>
       <c r="AT26">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AU26">
         <v>5</v>
@@ -6795,25 +6804,25 @@
         <v>1.75</v>
       </c>
       <c r="AN27">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO27">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AP27">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ27">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR27">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AS27">
-        <v>0.99</v>
+        <v>1.22</v>
       </c>
       <c r="AT27">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -7001,25 +7010,25 @@
         <v>2.25</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AQ28">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR28">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AS28">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AT28">
-        <v>3.56</v>
+        <v>3.31</v>
       </c>
       <c r="AU28">
         <v>6</v>
@@ -7207,25 +7216,25 @@
         <v>2.35</v>
       </c>
       <c r="AN29">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP29">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AQ29">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR29">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="AS29">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="AT29">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AU29">
         <v>0</v>
@@ -7341,7 +7350,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7413,25 +7422,25 @@
         <v>1.66</v>
       </c>
       <c r="AN30">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AO30">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP30">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AR30">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AS30">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="AT30">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="AU30">
         <v>7</v>
@@ -7547,7 +7556,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7619,25 +7628,25 @@
         <v>1.45</v>
       </c>
       <c r="AN31">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AP31">
         <v>0.93</v>
       </c>
       <c r="AQ31">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR31">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AS31">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AT31">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="AU31">
         <v>3</v>
@@ -7753,7 +7762,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7825,25 +7834,25 @@
         <v>1.72</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO32">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AP32">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR32">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AS32">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AT32">
-        <v>3.44</v>
+        <v>3.16</v>
       </c>
       <c r="AU32">
         <v>5</v>
@@ -7959,7 +7968,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8031,7 +8040,7 @@
         <v>2</v>
       </c>
       <c r="AN33">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO33">
         <v>1</v>
@@ -8040,16 +8049,16 @@
         <v>1.86</v>
       </c>
       <c r="AQ33">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR33">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AS33">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AT33">
-        <v>3.79</v>
+        <v>3.46</v>
       </c>
       <c r="AU33">
         <v>9</v>
@@ -8165,7 +8174,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8237,25 +8246,25 @@
         <v>1.68</v>
       </c>
       <c r="AN34">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO34">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ34">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR34">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AS34">
-        <v>0.9</v>
+        <v>1.13</v>
       </c>
       <c r="AT34">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AU34">
         <v>3</v>
@@ -8371,7 +8380,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8443,25 +8452,25 @@
         <v>1.47</v>
       </c>
       <c r="AN35">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO35">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP35">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AQ35">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR35">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AS35">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT35">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="AU35">
         <v>8</v>
@@ -8649,25 +8658,25 @@
         <v>1.25</v>
       </c>
       <c r="AN36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO36">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="AR36">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AS36">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AT36">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="AU36">
         <v>4</v>
@@ -8783,7 +8792,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -8861,19 +8870,19 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AQ37">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AR37">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AS37">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AT37">
-        <v>3.17</v>
+        <v>3.39</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -9064,22 +9073,22 @@
         <v>1</v>
       </c>
       <c r="AO38">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AP38">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AQ38">
         <v>0.93</v>
       </c>
       <c r="AR38">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AS38">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="AT38">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="AU38">
         <v>7</v>
@@ -9267,25 +9276,25 @@
         <v>1.34</v>
       </c>
       <c r="AN39">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AO39">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ39">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AR39">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="AS39">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AT39">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9401,7 +9410,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9473,25 +9482,25 @@
         <v>1.44</v>
       </c>
       <c r="AN40">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AO40">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP40">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="AQ40">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR40">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AS40">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AT40">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AU40">
         <v>7</v>
@@ -9607,7 +9616,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9679,25 +9688,25 @@
         <v>1.57</v>
       </c>
       <c r="AN41">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO41">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="AP41">
         <v>0.93</v>
       </c>
       <c r="AQ41">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR41">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AS41">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AT41">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AU41">
         <v>7</v>
@@ -9813,7 +9822,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -9885,25 +9894,25 @@
         <v>2.35</v>
       </c>
       <c r="AN42">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AO42">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AQ42">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR42">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AS42">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AT42">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="AU42">
         <v>12</v>
@@ -10091,25 +10100,25 @@
         <v>1.7</v>
       </c>
       <c r="AN43">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AO43">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AP43">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ43">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR43">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="AS43">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="AT43">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AU43">
         <v>4</v>
@@ -10297,25 +10306,25 @@
         <v>2.6</v>
       </c>
       <c r="AN44">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AO44">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AP44">
         <v>1.86</v>
       </c>
       <c r="AQ44">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR44">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="AS44">
         <v>1.49</v>
       </c>
       <c r="AT44">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="AU44">
         <v>3</v>
@@ -10503,25 +10512,25 @@
         <v>2</v>
       </c>
       <c r="AN45">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AO45">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="AP45">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ45">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR45">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AS45">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AT45">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="AU45">
         <v>4</v>
@@ -10709,25 +10718,25 @@
         <v>1.62</v>
       </c>
       <c r="AN46">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AO46">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP46">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR46">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AS46">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AT46">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="AU46">
         <v>8</v>
@@ -10843,7 +10852,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -10915,25 +10924,25 @@
         <v>2.02</v>
       </c>
       <c r="AN47">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AO47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR47">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS47">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AT47">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -11121,25 +11130,25 @@
         <v>1.45</v>
       </c>
       <c r="AN48">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO48">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AP48">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ48">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR48">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="AS48">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AT48">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -11255,7 +11264,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11327,25 +11336,25 @@
         <v>1.36</v>
       </c>
       <c r="AN49">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO49">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AP49">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="AR49">
+        <v>1.44</v>
+      </c>
+      <c r="AS49">
         <v>1.48</v>
       </c>
-      <c r="AS49">
-        <v>1.61</v>
-      </c>
       <c r="AT49">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="AU49">
         <v>9</v>
@@ -11536,22 +11545,22 @@
         <v>1.33</v>
       </c>
       <c r="AO50">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AP50">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AQ50">
         <v>0.93</v>
       </c>
       <c r="AR50">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AS50">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AT50">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11739,25 +11748,25 @@
         <v>1.4</v>
       </c>
       <c r="AN51">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO51">
         <v>2.33</v>
       </c>
       <c r="AP51">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ51">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AR51">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AS51">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="AT51">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="AU51">
         <v>3</v>
@@ -11945,25 +11954,25 @@
         <v>2.49</v>
       </c>
       <c r="AN52">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO52">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP52">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AQ52">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR52">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AS52">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AT52">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="AU52">
         <v>12</v>
@@ -12151,25 +12160,25 @@
         <v>1.2</v>
       </c>
       <c r="AN53">
-        <v>1.67</v>
+        <v>0.83</v>
       </c>
       <c r="AO53">
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ53">
         <v>1.86</v>
       </c>
       <c r="AR53">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AS53">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="AT53">
-        <v>2.36</v>
+        <v>3.01</v>
       </c>
       <c r="AU53">
         <v>6</v>
@@ -12285,7 +12294,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12357,25 +12366,25 @@
         <v>1.24</v>
       </c>
       <c r="AN54">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="AO54">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP54">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ54">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AR54">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AS54">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AT54">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="AU54">
         <v>4</v>
@@ -12491,7 +12500,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12566,19 +12575,19 @@
         <v>1</v>
       </c>
       <c r="AO55">
-        <v>0.5</v>
+        <v>1.17</v>
       </c>
       <c r="AP55">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AQ55">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR55">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="AS55">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="AT55">
         <v>3.05</v>
@@ -12772,22 +12781,22 @@
         <v>2</v>
       </c>
       <c r="AO56">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AP56">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR56">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AS56">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AT56">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12903,7 +12912,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -12975,25 +12984,25 @@
         <v>1.68</v>
       </c>
       <c r="AN57">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="AO57">
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ57">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR57">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AS57">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AT57">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AU57">
         <v>8</v>
@@ -13181,25 +13190,25 @@
         <v>1.68</v>
       </c>
       <c r="AN58">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO58">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AP58">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="AR58">
-        <v>2.03</v>
+        <v>1.74</v>
       </c>
       <c r="AS58">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AT58">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13315,7 +13324,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13387,25 +13396,25 @@
         <v>1.46</v>
       </c>
       <c r="AN59">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO59">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP59">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ59">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR59">
-        <v>1.8</v>
+        <v>1.18</v>
       </c>
       <c r="AS59">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AT59">
-        <v>3.1</v>
+        <v>2.29</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13521,7 +13530,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13593,25 +13602,25 @@
         <v>1.45</v>
       </c>
       <c r="AN60">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AO60">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP60">
+        <v>1.21</v>
+      </c>
+      <c r="AQ60">
+        <v>1.79</v>
+      </c>
+      <c r="AR60">
         <v>1.62</v>
       </c>
-      <c r="AQ60">
-        <v>1.64</v>
-      </c>
-      <c r="AR60">
-        <v>1.71</v>
-      </c>
       <c r="AS60">
-        <v>1.23</v>
+        <v>1.78</v>
       </c>
       <c r="AT60">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13799,7 +13808,7 @@
         <v>2.6</v>
       </c>
       <c r="AN61">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AO61">
         <v>1</v>
@@ -13808,13 +13817,13 @@
         <v>1.86</v>
       </c>
       <c r="AQ61">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR61">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="AS61">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AT61">
         <v>3.27</v>
@@ -13933,7 +13942,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14005,25 +14014,25 @@
         <v>1.71</v>
       </c>
       <c r="AN62">
-        <v>0.33</v>
+        <v>1.14</v>
       </c>
       <c r="AO62">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="AP62">
         <v>0.93</v>
       </c>
       <c r="AQ62">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR62">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AS62">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AT62">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -14211,25 +14220,25 @@
         <v>1.94</v>
       </c>
       <c r="AN63">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="AO63">
-        <v>0.75</v>
+        <v>1.71</v>
       </c>
       <c r="AP63">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ63">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR63">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="AS63">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AT63">
-        <v>2.67</v>
+        <v>2.37</v>
       </c>
       <c r="AU63">
         <v>3</v>
@@ -14420,22 +14429,22 @@
         <v>1</v>
       </c>
       <c r="AO64">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="AP64">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AQ64">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR64">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AS64">
-        <v>0.88</v>
+        <v>1.26</v>
       </c>
       <c r="AT64">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14623,25 +14632,25 @@
         <v>1.95</v>
       </c>
       <c r="AN65">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO65">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AP65">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ65">
         <v>0.93</v>
       </c>
       <c r="AR65">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AS65">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AT65">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14829,25 +14838,25 @@
         <v>1.25</v>
       </c>
       <c r="AN66">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="AO66">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ66">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR66">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AS66">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AT66">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="AU66">
         <v>3</v>
@@ -14963,7 +14972,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15035,25 +15044,25 @@
         <v>1.4</v>
       </c>
       <c r="AN67">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AO67">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP67">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ67">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR67">
-        <v>0.97</v>
+        <v>1.18</v>
       </c>
       <c r="AS67">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AT67">
-        <v>2.47</v>
+        <v>2.78</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -15241,25 +15250,25 @@
         <v>1.25</v>
       </c>
       <c r="AN68">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO68">
+        <v>1.88</v>
+      </c>
+      <c r="AP68">
+        <v>0.89</v>
+      </c>
+      <c r="AQ68">
         <v>1.75</v>
       </c>
-      <c r="AP68">
-        <v>1.29</v>
-      </c>
-      <c r="AQ68">
-        <v>1.43</v>
-      </c>
       <c r="AR68">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AS68">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AT68">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="AU68">
         <v>6</v>
@@ -15375,7 +15384,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15447,25 +15456,25 @@
         <v>1.57</v>
       </c>
       <c r="AN69">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AO69">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="AP69">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AQ69">
         <v>1.86</v>
       </c>
       <c r="AR69">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AS69">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AT69">
-        <v>3.32</v>
+        <v>3.59</v>
       </c>
       <c r="AU69">
         <v>6</v>
@@ -15581,7 +15590,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15653,25 +15662,25 @@
         <v>1.5</v>
       </c>
       <c r="AN70">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO70">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AP70">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR70">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AS70">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AT70">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="AU70">
         <v>3</v>
@@ -15787,7 +15796,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15859,25 +15868,25 @@
         <v>1.78</v>
       </c>
       <c r="AN71">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AO71">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AP71">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AR71">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AS71">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AT71">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="AU71">
         <v>4</v>
@@ -15993,7 +16002,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16065,25 +16074,25 @@
         <v>1.8</v>
       </c>
       <c r="AN72">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO72">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP72">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ72">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR72">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="AS72">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AT72">
-        <v>2.91</v>
+        <v>2.57</v>
       </c>
       <c r="AU72">
         <v>8</v>
@@ -16271,25 +16280,25 @@
         <v>1.62</v>
       </c>
       <c r="AN73">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO73">
-        <v>0.6</v>
+        <v>1.67</v>
       </c>
       <c r="AP73">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ73">
+        <v>1.61</v>
+      </c>
+      <c r="AR73">
         <v>1.36</v>
       </c>
-      <c r="AR73">
-        <v>1.51</v>
-      </c>
       <c r="AS73">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AT73">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16477,25 +16486,25 @@
         <v>1.25</v>
       </c>
       <c r="AN74">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AO74">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP74">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ74">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AR74">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AS74">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AT74">
-        <v>2.66</v>
+        <v>3.02</v>
       </c>
       <c r="AU74">
         <v>2</v>
@@ -16611,7 +16620,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16683,25 +16692,25 @@
         <v>2.45</v>
       </c>
       <c r="AN75">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AO75">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AP75">
         <v>1.86</v>
       </c>
       <c r="AQ75">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR75">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AS75">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AT75">
-        <v>3.43</v>
+        <v>3.03</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16817,7 +16826,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16889,25 +16898,25 @@
         <v>1.62</v>
       </c>
       <c r="AN76">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AO76">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AP76">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AQ76">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR76">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AS76">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AT76">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -17023,7 +17032,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17095,25 +17104,25 @@
         <v>1.53</v>
       </c>
       <c r="AN77">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO77">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AP77">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ77">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AR77">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AS77">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AT77">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="AU77">
         <v>5</v>
@@ -17301,25 +17310,25 @@
         <v>1.71</v>
       </c>
       <c r="AN78">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AO78">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="AP78">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AQ78">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR78">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AS78">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AT78">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="AU78">
         <v>9</v>
@@ -17435,7 +17444,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17507,25 +17516,25 @@
         <v>1.22</v>
       </c>
       <c r="AN79">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AO79">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP79">
         <v>0.93</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="AR79">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AS79">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AT79">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AU79">
         <v>3</v>
@@ -17713,25 +17722,25 @@
         <v>1.57</v>
       </c>
       <c r="AN80">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO80">
-        <v>0.25</v>
+        <v>1.3</v>
       </c>
       <c r="AP80">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ80">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR80">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AS80">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AT80">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AU80">
         <v>10</v>
@@ -17847,7 +17856,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -17919,25 +17928,25 @@
         <v>1.9</v>
       </c>
       <c r="AN81">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="AO81">
-        <v>0.6</v>
+        <v>0.78</v>
       </c>
       <c r="AP81">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ81">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR81">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AS81">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AT81">
-        <v>2.29</v>
+        <v>2.58</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -18125,25 +18134,25 @@
         <v>1.3</v>
       </c>
       <c r="AN82">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AO82">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AP82">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="AQ82">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AR82">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AS82">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AT82">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AU82">
         <v>2</v>
@@ -18259,7 +18268,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18334,22 +18343,22 @@
         <v>1.67</v>
       </c>
       <c r="AO83">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="AP83">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AQ83">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR83">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AS83">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AT83">
-        <v>2.98</v>
+        <v>3.21</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18537,25 +18546,25 @@
         <v>1.95</v>
       </c>
       <c r="AN84">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AO84">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AP84">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ84">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR84">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AS84">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AT84">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AU84">
         <v>2</v>
@@ -18743,25 +18752,25 @@
         <v>1.25</v>
       </c>
       <c r="AN85">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AO85">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AP85">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ85">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR85">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AS85">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AT85">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AU85">
         <v>5</v>
@@ -18877,7 +18886,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -18949,25 +18958,25 @@
         <v>1.44</v>
       </c>
       <c r="AN86">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AO86">
-        <v>0.67</v>
+        <v>1.11</v>
       </c>
       <c r="AP86">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AQ86">
         <v>1.86</v>
       </c>
       <c r="AR86">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AS86">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AT86">
-        <v>2.99</v>
+        <v>3.39</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -19155,25 +19164,25 @@
         <v>2.9</v>
       </c>
       <c r="AN87">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AO87">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AP87">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AQ87">
         <v>0.93</v>
       </c>
       <c r="AR87">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="AS87">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AT87">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AU87">
         <v>8</v>
@@ -19361,25 +19370,25 @@
         <v>1.52</v>
       </c>
       <c r="AN88">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AO88">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AP88">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AQ88">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR88">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AS88">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT88">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU88">
         <v>5</v>
@@ -19567,22 +19576,22 @@
         <v>1.86</v>
       </c>
       <c r="AN89">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="AO89">
-        <v>0.67</v>
+        <v>1.55</v>
       </c>
       <c r="AP89">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AQ89">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR89">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AS89">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AT89">
         <v>2.69</v>
@@ -19701,7 +19710,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19773,25 +19782,25 @@
         <v>1.24</v>
       </c>
       <c r="AN90">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AO90">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AP90">
         <v>0.93</v>
       </c>
       <c r="AQ90">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AR90">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS90">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AT90">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="AU90">
         <v>4</v>
@@ -19907,7 +19916,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -19979,25 +19988,25 @@
         <v>2.7</v>
       </c>
       <c r="AN91">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AO91">
-        <v>0.8</v>
+        <v>1.27</v>
       </c>
       <c r="AP91">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AQ91">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR91">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AS91">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AT91">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20113,7 +20122,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20185,25 +20194,25 @@
         <v>1.37</v>
       </c>
       <c r="AN92">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AO92">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AP92">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ92">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AR92">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AS92">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AT92">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AU92">
         <v>3</v>
@@ -20319,7 +20328,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20391,25 +20400,25 @@
         <v>1.44</v>
       </c>
       <c r="AN93">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="AO93">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ93">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR93">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AS93">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AT93">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AU93">
         <v>3</v>
@@ -20597,25 +20606,25 @@
         <v>1.29</v>
       </c>
       <c r="AN94">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AO94">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AP94">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="AR94">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AS94">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AT94">
-        <v>3.34</v>
+        <v>2.85</v>
       </c>
       <c r="AU94">
         <v>8</v>
@@ -20731,7 +20740,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20803,25 +20812,25 @@
         <v>3.15</v>
       </c>
       <c r="AN95">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AO95">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="AP95">
         <v>1.86</v>
       </c>
       <c r="AQ95">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR95">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="AS95">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AT95">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="AU95">
         <v>9</v>
@@ -21009,25 +21018,25 @@
         <v>1.42</v>
       </c>
       <c r="AN96">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AO96">
-        <v>0.2</v>
+        <v>1.08</v>
       </c>
       <c r="AP96">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR96">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AS96">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AT96">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="AU96">
         <v>9</v>
@@ -21215,25 +21224,25 @@
         <v>1.78</v>
       </c>
       <c r="AN97">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="AO97">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AP97">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ97">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR97">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AS97">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AT97">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AU97">
         <v>5</v>
@@ -21424,22 +21433,22 @@
         <v>1.17</v>
       </c>
       <c r="AO98">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AQ98">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR98">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AS98">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AT98">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21627,25 +21636,25 @@
         <v>1.15</v>
       </c>
       <c r="AN99">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO99">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AP99">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ99">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AR99">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AS99">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AT99">
-        <v>2.86</v>
+        <v>3.07</v>
       </c>
       <c r="AU99">
         <v>0</v>
@@ -21833,25 +21842,25 @@
         <v>2.85</v>
       </c>
       <c r="AN100">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AO100">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP100">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AQ100">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR100">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AS100">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="AT100">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21967,7 +21976,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22039,25 +22048,25 @@
         <v>1.2</v>
       </c>
       <c r="AN101">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO101">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AP101">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ101">
         <v>1.86</v>
       </c>
       <c r="AR101">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AS101">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="AT101">
-        <v>2.58</v>
+        <v>2.91</v>
       </c>
       <c r="AU101">
         <v>2</v>
@@ -22245,25 +22254,25 @@
         <v>1.87</v>
       </c>
       <c r="AN102">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AO102">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="AQ102">
         <v>0.93</v>
       </c>
       <c r="AR102">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AS102">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AT102">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22451,25 +22460,25 @@
         <v>1.72</v>
       </c>
       <c r="AN103">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="AO103">
-        <v>0.6</v>
+        <v>1.08</v>
       </c>
       <c r="AP103">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ103">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR103">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AS103">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AT103">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="AU103">
         <v>8</v>
@@ -22585,7 +22594,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22657,25 +22666,25 @@
         <v>1.95</v>
       </c>
       <c r="AN104">
+        <v>1.58</v>
+      </c>
+      <c r="AO104">
+        <v>1.31</v>
+      </c>
+      <c r="AP104">
+        <v>1.79</v>
+      </c>
+      <c r="AQ104">
+        <v>1.43</v>
+      </c>
+      <c r="AR104">
+        <v>1.68</v>
+      </c>
+      <c r="AS104">
         <v>1.63</v>
       </c>
-      <c r="AO104">
-        <v>1.17</v>
-      </c>
-      <c r="AP104">
-        <v>1.93</v>
-      </c>
-      <c r="AQ104">
-        <v>1</v>
-      </c>
-      <c r="AR104">
-        <v>1.78</v>
-      </c>
-      <c r="AS104">
-        <v>1.74</v>
-      </c>
       <c r="AT104">
-        <v>3.52</v>
+        <v>3.31</v>
       </c>
       <c r="AU104">
         <v>9</v>
@@ -22863,25 +22872,25 @@
         <v>1.95</v>
       </c>
       <c r="AN105">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AO105">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AP105">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AQ105">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR105">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AS105">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AT105">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AU105">
         <v>6</v>
@@ -23069,25 +23078,25 @@
         <v>1.66</v>
       </c>
       <c r="AN106">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AO106">
-        <v>0.67</v>
+        <v>1.31</v>
       </c>
       <c r="AP106">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ106">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR106">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AS106">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AT106">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="AU106">
         <v>11</v>
@@ -23203,7 +23212,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23275,25 +23284,25 @@
         <v>1.55</v>
       </c>
       <c r="AN107">
-        <v>1.71</v>
+        <v>1</v>
       </c>
       <c r="AO107">
-        <v>0.71</v>
+        <v>1.38</v>
       </c>
       <c r="AP107">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ107">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR107">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AS107">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AT107">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AU107">
         <v>4</v>
@@ -23409,7 +23418,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23481,25 +23490,25 @@
         <v>1.97</v>
       </c>
       <c r="AN108">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AO108">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP108">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ108">
         <v>0.93</v>
       </c>
       <c r="AR108">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AS108">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AT108">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="AU108">
         <v>0</v>
@@ -23687,25 +23696,25 @@
         <v>2</v>
       </c>
       <c r="AN109">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AO109">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AP109">
         <v>1.86</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="AR109">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AS109">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AT109">
-        <v>3.51</v>
+        <v>3.21</v>
       </c>
       <c r="AU109">
         <v>7</v>
@@ -23821,7 +23830,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23893,25 +23902,25 @@
         <v>1.32</v>
       </c>
       <c r="AN110">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO110">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AP110">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ110">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AR110">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="AS110">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AT110">
-        <v>3.09</v>
+        <v>2.7</v>
       </c>
       <c r="AU110">
         <v>3</v>
@@ -24027,7 +24036,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24099,25 +24108,25 @@
         <v>1.34</v>
       </c>
       <c r="AN111">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AO111">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AP111">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AQ111">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AR111">
+        <v>1.49</v>
+      </c>
+      <c r="AS111">
         <v>1.65</v>
       </c>
-      <c r="AS111">
-        <v>1.42</v>
-      </c>
       <c r="AT111">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="AU111">
         <v>5</v>
@@ -24233,7 +24242,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24305,25 +24314,25 @@
         <v>1.08</v>
       </c>
       <c r="AN112">
-        <v>1.33</v>
+        <v>0.93</v>
       </c>
       <c r="AO112">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AP112">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ112">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AR112">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AS112">
-        <v>1.49</v>
+        <v>1.74</v>
       </c>
       <c r="AT112">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="AU112">
         <v>3</v>
@@ -24439,7 +24448,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24511,25 +24520,25 @@
         <v>1.8</v>
       </c>
       <c r="AN113">
+        <v>1.29</v>
+      </c>
+      <c r="AO113">
+        <v>1.57</v>
+      </c>
+      <c r="AP113">
         <v>1.43</v>
       </c>
-      <c r="AO113">
-        <v>1.33</v>
-      </c>
-      <c r="AP113">
-        <v>1.71</v>
-      </c>
       <c r="AQ113">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR113">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AS113">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AT113">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AU113">
         <v>5</v>
@@ -24717,25 +24726,25 @@
         <v>1.8</v>
       </c>
       <c r="AN114">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="AO114">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AP114">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ114">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR114">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AS114">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AT114">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="AU114">
         <v>4</v>
@@ -24851,7 +24860,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24923,25 +24932,25 @@
         <v>1.42</v>
       </c>
       <c r="AN115">
-        <v>1.86</v>
+        <v>1.21</v>
       </c>
       <c r="AO115">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AP115">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="AQ115">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR115">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AS115">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AT115">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AU115">
         <v>7</v>
@@ -25129,25 +25138,25 @@
         <v>1.9</v>
       </c>
       <c r="AN116">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="AO116">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="AP116">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ116">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR116">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AS116">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AT116">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AU116">
         <v>4</v>
@@ -25335,25 +25344,25 @@
         <v>1.62</v>
       </c>
       <c r="AN117">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO117">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AP117">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AQ117">
         <v>1.86</v>
       </c>
       <c r="AR117">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AS117">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="AT117">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AU117">
         <v>4</v>
@@ -25541,25 +25550,25 @@
         <v>1.5</v>
       </c>
       <c r="AN118">
-        <v>0.83</v>
+        <v>1.07</v>
       </c>
       <c r="AO118">
-        <v>0.71</v>
+        <v>0.92</v>
       </c>
       <c r="AP118">
         <v>0.93</v>
       </c>
       <c r="AQ118">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR118">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AS118">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AT118">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25747,25 +25756,25 @@
         <v>2.2</v>
       </c>
       <c r="AN119">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AO119">
-        <v>0.17</v>
+        <v>0.93</v>
       </c>
       <c r="AP119">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ119">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR119">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AS119">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AT119">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="AU119">
         <v>5</v>
@@ -25953,25 +25962,25 @@
         <v>1.76</v>
       </c>
       <c r="AN120">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AO120">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="AP120">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ120">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR120">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AS120">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AT120">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -26087,7 +26096,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26159,25 +26168,25 @@
         <v>1.36</v>
       </c>
       <c r="AN121">
-        <v>2.29</v>
+        <v>1.6</v>
       </c>
       <c r="AO121">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AP121">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ121">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AR121">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AS121">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AT121">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AU121">
         <v>5</v>
@@ -26293,7 +26302,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26365,25 +26374,25 @@
         <v>1.36</v>
       </c>
       <c r="AN122">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO122">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AP122">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="AQ122">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR122">
+        <v>1.49</v>
+      </c>
+      <c r="AS122">
         <v>1.54</v>
       </c>
-      <c r="AS122">
-        <v>1.62</v>
-      </c>
       <c r="AT122">
-        <v>3.16</v>
+        <v>3.03</v>
       </c>
       <c r="AU122">
         <v>3</v>
@@ -26571,25 +26580,25 @@
         <v>2.2</v>
       </c>
       <c r="AN123">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="AO123">
-        <v>0.14</v>
+        <v>0.87</v>
       </c>
       <c r="AP123">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AQ123">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR123">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AS123">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AT123">
-        <v>3.27</v>
+        <v>3.01</v>
       </c>
       <c r="AU123">
         <v>8</v>
@@ -26777,25 +26786,25 @@
         <v>1.99</v>
       </c>
       <c r="AN124">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AO124">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AP124">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ124">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR124">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AS124">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AT124">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AU124">
         <v>13</v>
@@ -26983,25 +26992,25 @@
         <v>1.44</v>
       </c>
       <c r="AN125">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AO125">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="AP125">
         <v>0.93</v>
       </c>
       <c r="AQ125">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR125">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AS125">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AT125">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -27117,7 +27126,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27189,25 +27198,25 @@
         <v>1.41</v>
       </c>
       <c r="AN126">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO126">
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ126">
         <v>1.86</v>
       </c>
       <c r="AR126">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS126">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="AT126">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27395,25 +27404,25 @@
         <v>1.36</v>
       </c>
       <c r="AN127">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="AO127">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ127">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR127">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AS127">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AT127">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27601,25 +27610,25 @@
         <v>1.33</v>
       </c>
       <c r="AN128">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AO128">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AP128">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ128">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AR128">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS128">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="AT128">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="AU128">
         <v>3</v>
@@ -27807,25 +27816,25 @@
         <v>1.17</v>
       </c>
       <c r="AN129">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AO129">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AP129">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ129">
         <v>1.86</v>
       </c>
       <c r="AR129">
-        <v>1.77</v>
+        <v>1.42</v>
       </c>
       <c r="AS129">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="AT129">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="AU129">
         <v>5</v>
@@ -28016,22 +28025,22 @@
         <v>1.38</v>
       </c>
       <c r="AO130">
-        <v>0.63</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP130">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AQ130">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR130">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AS130">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AT130">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="AU130">
         <v>6</v>
@@ -28147,7 +28156,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28219,25 +28228,25 @@
         <v>1.56</v>
       </c>
       <c r="AN131">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AO131">
         <v>1.25</v>
       </c>
       <c r="AP131">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AQ131">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR131">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AS131">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AT131">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="AU131">
         <v>0</v>
@@ -28353,7 +28362,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28425,25 +28434,25 @@
         <v>1.28</v>
       </c>
       <c r="AN132">
-        <v>1.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AO132">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AP132">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ132">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AR132">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AS132">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AT132">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="AU132">
         <v>5</v>
@@ -28559,7 +28568,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28631,25 +28640,25 @@
         <v>1.7</v>
       </c>
       <c r="AN133">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AO133">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AP133">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AQ133">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="AR133">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AS133">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AT133">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
       <c r="AU133">
         <v>3</v>
@@ -28840,7 +28849,7 @@
         <v>1.5</v>
       </c>
       <c r="AO134">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AP134">
         <v>1.86</v>
@@ -28849,13 +28858,13 @@
         <v>0.93</v>
       </c>
       <c r="AR134">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AS134">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AT134">
-        <v>3.33</v>
+        <v>3.09</v>
       </c>
       <c r="AU134">
         <v>8</v>
@@ -29043,25 +29052,25 @@
         <v>1.62</v>
       </c>
       <c r="AN135">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AO135">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AP135">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ135">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR135">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AS135">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AT135">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AU135">
         <v>4</v>
@@ -29249,25 +29258,25 @@
         <v>1.46</v>
       </c>
       <c r="AN136">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AO136">
-        <v>0.57</v>
+        <v>1.25</v>
       </c>
       <c r="AP136">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ136">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR136">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AS136">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AT136">
-        <v>3.17</v>
+        <v>2.89</v>
       </c>
       <c r="AU136">
         <v>4</v>
@@ -29383,7 +29392,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29455,25 +29464,25 @@
         <v>1.25</v>
       </c>
       <c r="AN137">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AO137">
-        <v>1.13</v>
+        <v>1.56</v>
       </c>
       <c r="AP137">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AQ137">
+        <v>1.75</v>
+      </c>
+      <c r="AR137">
         <v>1.43</v>
       </c>
-      <c r="AR137">
-        <v>1.59</v>
-      </c>
       <c r="AS137">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AT137">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AU137">
         <v>6</v>
@@ -29661,25 +29670,25 @@
         <v>1.34</v>
       </c>
       <c r="AN138">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AO138">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="AP138">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ138">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR138">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="AS138">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AT138">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="AU138">
         <v>4</v>
@@ -29867,25 +29876,25 @@
         <v>1.72</v>
       </c>
       <c r="AN139">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AO139">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AP139">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ139">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR139">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AS139">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AT139">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="AU139">
         <v>6</v>
@@ -30001,7 +30010,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30073,25 +30082,25 @@
         <v>1.37</v>
       </c>
       <c r="AN140">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AO140">
-        <v>0.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP140">
         <v>0.93</v>
       </c>
       <c r="AQ140">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR140">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AS140">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT140">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="AU140">
         <v>7</v>
@@ -30279,25 +30288,25 @@
         <v>1.42</v>
       </c>
       <c r="AN141">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AO141">
-        <v>0.63</v>
+        <v>1.24</v>
       </c>
       <c r="AP141">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ141">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR141">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AS141">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AT141">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="AU141">
         <v>7</v>
@@ -30413,7 +30422,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30485,25 +30494,25 @@
         <v>1.47</v>
       </c>
       <c r="AN142">
-        <v>2.13</v>
+        <v>1.65</v>
       </c>
       <c r="AO142">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AP142">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ142">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR142">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AS142">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AT142">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AU142">
         <v>4</v>
@@ -30619,7 +30628,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30691,25 +30700,25 @@
         <v>1.42</v>
       </c>
       <c r="AN143">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AO143">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AP143">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AQ143">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AR143">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AS143">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="AT143">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="AU143">
         <v>6</v>
@@ -30825,7 +30834,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30897,25 +30906,25 @@
         <v>1.83</v>
       </c>
       <c r="AN144">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AO144">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="AP144">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ144">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR144">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AS144">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AT144">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="AU144">
         <v>8</v>
@@ -31031,7 +31040,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31103,25 +31112,25 @@
         <v>1.21</v>
       </c>
       <c r="AN145">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AO145">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AP145">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ145">
         <v>1.86</v>
       </c>
       <c r="AR145">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AS145">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="AT145">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AU145">
         <v>4</v>
@@ -31309,25 +31318,25 @@
         <v>1.41</v>
       </c>
       <c r="AN146">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AO146">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AP146">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AQ146">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="AR146">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AS146">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AT146">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="AU146">
         <v>5</v>
@@ -31443,7 +31452,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31515,25 +31524,25 @@
         <v>1.32</v>
       </c>
       <c r="AN147">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AO147">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="AP147">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ147">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR147">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AS147">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AT147">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AU147">
         <v>4</v>
@@ -31649,7 +31658,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31721,25 +31730,25 @@
         <v>1.27</v>
       </c>
       <c r="AN148">
+        <v>1.5</v>
+      </c>
+      <c r="AO148">
         <v>1.56</v>
       </c>
-      <c r="AO148">
-        <v>1.33</v>
-      </c>
       <c r="AP148">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ148">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AR148">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AS148">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AT148">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="AU148">
         <v>4</v>
@@ -31855,7 +31864,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -31927,25 +31936,25 @@
         <v>1.64</v>
       </c>
       <c r="AN149">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO149">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP149">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AQ149">
         <v>0.93</v>
       </c>
       <c r="AR149">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AS149">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AT149">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="AU149">
         <v>7</v>
@@ -32061,7 +32070,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32133,25 +32142,25 @@
         <v>1.42</v>
       </c>
       <c r="AN150">
-        <v>1.78</v>
+        <v>1.17</v>
       </c>
       <c r="AO150">
+        <v>1.17</v>
+      </c>
+      <c r="AP150">
         <v>0.89</v>
       </c>
-      <c r="AP150">
-        <v>1.29</v>
-      </c>
       <c r="AQ150">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR150">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AS150">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AT150">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="AU150">
         <v>5</v>
@@ -32342,22 +32351,22 @@
         <v>1.67</v>
       </c>
       <c r="AO151">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP151">
         <v>1.86</v>
       </c>
       <c r="AQ151">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR151">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AS151">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AT151">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="AU151">
         <v>9</v>
@@ -32545,25 +32554,25 @@
         <v>1.38</v>
       </c>
       <c r="AN152">
-        <v>1.67</v>
+        <v>1.06</v>
       </c>
       <c r="AO152">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AP152">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ152">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR152">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AS152">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AT152">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="AU152">
         <v>5</v>
@@ -32679,7 +32688,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32751,25 +32760,25 @@
         <v>1.35</v>
       </c>
       <c r="AN153">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AO153">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AP153">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ153">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AR153">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AS153">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AT153">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AU153">
         <v>6</v>
@@ -32885,7 +32894,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -32957,25 +32966,25 @@
         <v>1.44</v>
       </c>
       <c r="AN154">
-        <v>1.33</v>
+        <v>0.95</v>
       </c>
       <c r="AO154">
-        <v>0.44</v>
+        <v>1.16</v>
       </c>
       <c r="AP154">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ154">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR154">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="AS154">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AT154">
-        <v>2.99</v>
+        <v>2.67</v>
       </c>
       <c r="AU154">
         <v>5</v>
@@ -33163,25 +33172,25 @@
         <v>1.78</v>
       </c>
       <c r="AN155">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AO155">
-        <v>0.5600000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="AP155">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ155">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR155">
         <v>1.16</v>
       </c>
       <c r="AS155">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AT155">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AU155">
         <v>8</v>
@@ -33369,25 +33378,25 @@
         <v>1.66</v>
       </c>
       <c r="AN156">
+        <v>1.21</v>
+      </c>
+      <c r="AO156">
         <v>1.11</v>
       </c>
-      <c r="AO156">
-        <v>1</v>
-      </c>
       <c r="AP156">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ156">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR156">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AS156">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="AT156">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="AU156">
         <v>4</v>
@@ -33503,7 +33512,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33575,25 +33584,25 @@
         <v>1.68</v>
       </c>
       <c r="AN157">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AO157">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AP157">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AQ157">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR157">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AS157">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AT157">
-        <v>3.31</v>
+        <v>3.16</v>
       </c>
       <c r="AU157">
         <v>7</v>
@@ -33781,25 +33790,25 @@
         <v>1.65</v>
       </c>
       <c r="AN158">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AO158">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AP158">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ158">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR158">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AS158">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AT158">
-        <v>2.87</v>
+        <v>2.71</v>
       </c>
       <c r="AU158">
         <v>7</v>
@@ -33987,25 +33996,25 @@
         <v>1.17</v>
       </c>
       <c r="AN159">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AO159">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AP159">
         <v>0.93</v>
       </c>
       <c r="AQ159">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AR159">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AS159">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AT159">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="AU159">
         <v>3</v>
@@ -34193,25 +34202,25 @@
         <v>1.27</v>
       </c>
       <c r="AN160">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AO160">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AP160">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AQ160">
         <v>1.86</v>
       </c>
       <c r="AR160">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AS160">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AT160">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="AU160">
         <v>7</v>
@@ -34399,25 +34408,25 @@
         <v>2.29</v>
       </c>
       <c r="AN161">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AO161">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="AP161">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ161">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR161">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AS161">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AT161">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AU161">
         <v>6</v>
@@ -34605,25 +34614,25 @@
         <v>1.43</v>
       </c>
       <c r="AN162">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AO162">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AP162">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AQ162">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AR162">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AS162">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AT162">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AU162">
         <v>0</v>
@@ -34811,25 +34820,25 @@
         <v>1.55</v>
       </c>
       <c r="AN163">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AO163">
-        <v>0.9</v>
+        <v>1.15</v>
       </c>
       <c r="AP163">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ163">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR163">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AS163">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AT163">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="AU163">
         <v>3</v>
@@ -34945,7 +34954,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35017,25 +35026,25 @@
         <v>1.16</v>
       </c>
       <c r="AN164">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AO164">
+        <v>1.6</v>
+      </c>
+      <c r="AP164">
+        <v>0.68</v>
+      </c>
+      <c r="AQ164">
+        <v>1.75</v>
+      </c>
+      <c r="AR164">
         <v>1.3</v>
       </c>
-      <c r="AP164">
-        <v>1</v>
-      </c>
-      <c r="AQ164">
-        <v>1.43</v>
-      </c>
-      <c r="AR164">
-        <v>1.45</v>
-      </c>
       <c r="AS164">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AT164">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="AU164">
         <v>5</v>
@@ -35223,25 +35232,25 @@
         <v>1.8</v>
       </c>
       <c r="AN165">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO165">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AP165">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ165">
         <v>0.93</v>
       </c>
       <c r="AR165">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AS165">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AT165">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="AU165">
         <v>8</v>
@@ -35357,7 +35366,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35429,25 +35438,25 @@
         <v>1.94</v>
       </c>
       <c r="AN166">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AO166">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AP166">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AQ166">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR166">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AS166">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AT166">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU166">
         <v>5</v>
@@ -35635,25 +35644,25 @@
         <v>1.37</v>
       </c>
       <c r="AN167">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AO167">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AP167">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ167">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="AR167">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AS167">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AT167">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AU167">
         <v>5</v>
@@ -35841,25 +35850,25 @@
         <v>1.59</v>
       </c>
       <c r="AN168">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AO168">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AP168">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AQ168">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR168">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AS168">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AT168">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AU168">
         <v>7</v>
@@ -35975,7 +35984,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36047,25 +36056,25 @@
         <v>1.19</v>
       </c>
       <c r="AN169">
+        <v>1.1</v>
+      </c>
+      <c r="AO169">
         <v>1.7</v>
       </c>
-      <c r="AO169">
-        <v>1.6</v>
-      </c>
       <c r="AP169">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="AQ169">
         <v>1.86</v>
       </c>
       <c r="AR169">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AS169">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AT169">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="AU169">
         <v>0</v>
@@ -36181,7 +36190,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36253,25 +36262,25 @@
         <v>1.3</v>
       </c>
       <c r="AN170">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AO170">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AP170">
         <v>0.93</v>
       </c>
       <c r="AQ170">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR170">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS170">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AT170">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="AU170">
         <v>5</v>
@@ -36387,7 +36396,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36459,25 +36468,25 @@
         <v>2.34</v>
       </c>
       <c r="AN171">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AO171">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="AP171">
         <v>1.86</v>
       </c>
       <c r="AQ171">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR171">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AS171">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AT171">
-        <v>3.37</v>
+        <v>3.08</v>
       </c>
       <c r="AU171">
         <v>9</v>
@@ -36593,7 +36602,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36665,25 +36674,25 @@
         <v>2.08</v>
       </c>
       <c r="AN172">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AO172">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AP172">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ172">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR172">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AS172">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AT172">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="AU172">
         <v>11</v>
@@ -36871,25 +36880,25 @@
         <v>1.42</v>
       </c>
       <c r="AN173">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AO173">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AP173">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ173">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR173">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AS173">
         <v>1.33</v>
       </c>
       <c r="AT173">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="AU173">
         <v>2</v>
@@ -37077,25 +37086,25 @@
         <v>1.2</v>
       </c>
       <c r="AN174">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AO174">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AP174">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ174">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AR174">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AS174">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AT174">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="AU174">
         <v>8</v>
@@ -37283,25 +37292,25 @@
         <v>1.88</v>
       </c>
       <c r="AN175">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AO175">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AP175">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AQ175">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR175">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AS175">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AT175">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="AU175">
         <v>8</v>
@@ -37489,25 +37498,25 @@
         <v>1.62</v>
       </c>
       <c r="AN176">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AO176">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AP176">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AQ176">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR176">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS176">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AT176">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="AU176">
         <v>11</v>
@@ -37623,7 +37632,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -37695,25 +37704,25 @@
         <v>2.11</v>
       </c>
       <c r="AN177">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AO177">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="AP177">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ177">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR177">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AS177">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AT177">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="AU177">
         <v>8</v>
@@ -37901,25 +37910,25 @@
         <v>1.45</v>
       </c>
       <c r="AN178">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AO178">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AP178">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ178">
         <v>0.93</v>
       </c>
       <c r="AR178">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AS178">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AT178">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="AU178">
         <v>6</v>
@@ -38107,25 +38116,25 @@
         <v>1.43</v>
       </c>
       <c r="AN179">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AO179">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AP179">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ179">
+        <v>1.82</v>
+      </c>
+      <c r="AR179">
+        <v>1.19</v>
+      </c>
+      <c r="AS179">
         <v>1.5</v>
       </c>
-      <c r="AR179">
-        <v>1.24</v>
-      </c>
-      <c r="AS179">
-        <v>1.37</v>
-      </c>
       <c r="AT179">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="AU179">
         <v>4</v>
@@ -38241,7 +38250,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38313,25 +38322,25 @@
         <v>1.47</v>
       </c>
       <c r="AN180">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="AO180">
-        <v>0.73</v>
+        <v>1.23</v>
       </c>
       <c r="AP180">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="AQ180">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR180">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AS180">
         <v>1.24</v>
       </c>
       <c r="AT180">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AU180">
         <v>5</v>
@@ -38519,25 +38528,25 @@
         <v>1.47</v>
       </c>
       <c r="AN181">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="AO181">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AP181">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ181">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AR181">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AS181">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AT181">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="AU181">
         <v>5</v>
@@ -38725,25 +38734,25 @@
         <v>1.95</v>
       </c>
       <c r="AN182">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AO182">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AP182">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AQ182">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR182">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AS182">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AT182">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="AU182">
         <v>8</v>
@@ -38931,25 +38940,25 @@
         <v>1.17</v>
       </c>
       <c r="AN183">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AO183">
         <v>1.73</v>
       </c>
       <c r="AP183">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AQ183">
         <v>1.86</v>
       </c>
       <c r="AR183">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AS183">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AT183">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="AU183">
         <v>3</v>
@@ -39137,25 +39146,25 @@
         <v>1.69</v>
       </c>
       <c r="AN184">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AO184">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AP184">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ184">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR184">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AS184">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AT184">
-        <v>2.49</v>
+        <v>2.76</v>
       </c>
       <c r="AU184">
         <v>5</v>
@@ -39346,22 +39355,22 @@
         <v>1.64</v>
       </c>
       <c r="AO185">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="AP185">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AQ185">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR185">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AS185">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AT185">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="AU185">
         <v>11</v>
@@ -39549,25 +39558,25 @@
         <v>1.53</v>
       </c>
       <c r="AN186">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AO186">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP186">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ186">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR186">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AS186">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AT186">
-        <v>2.43</v>
+        <v>2.68</v>
       </c>
       <c r="AU186">
         <v>2</v>
@@ -39683,7 +39692,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -39758,22 +39767,22 @@
         <v>1.09</v>
       </c>
       <c r="AO187">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AP187">
         <v>0.93</v>
       </c>
       <c r="AQ187">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR187">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AS187">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AT187">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="AU187">
         <v>4</v>
@@ -39961,25 +39970,25 @@
         <v>1.34</v>
       </c>
       <c r="AN188">
-        <v>1.18</v>
+        <v>0.83</v>
       </c>
       <c r="AO188">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="AP188">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ188">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR188">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AS188">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AT188">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AU188">
         <v>10</v>
@@ -40095,7 +40104,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40170,22 +40179,22 @@
         <v>1.09</v>
       </c>
       <c r="AO189">
-        <v>0.45</v>
+        <v>0.83</v>
       </c>
       <c r="AP189">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ189">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR189">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AS189">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AT189">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="AU189">
         <v>8</v>
@@ -40301,7 +40310,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40373,25 +40382,25 @@
         <v>1.45</v>
       </c>
       <c r="AN190">
-        <v>2.09</v>
+        <v>1.78</v>
       </c>
       <c r="AO190">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AP190">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ190">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="AR190">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AS190">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AT190">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="AU190">
         <v>6</v>
@@ -40507,7 +40516,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40579,25 +40588,25 @@
         <v>2.55</v>
       </c>
       <c r="AN191">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AO191">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
       <c r="AP191">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AQ191">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR191">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS191">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AT191">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AU191">
         <v>8</v>
@@ -40785,25 +40794,25 @@
         <v>1.67</v>
       </c>
       <c r="AN192">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AO192">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AP192">
         <v>1.86</v>
       </c>
       <c r="AQ192">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AR192">
-        <v>2.13</v>
+        <v>1.84</v>
       </c>
       <c r="AS192">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="AT192">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="AU192">
         <v>4</v>
@@ -40919,7 +40928,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -40991,25 +41000,25 @@
         <v>1.49</v>
       </c>
       <c r="AN193">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AO193">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AP193">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AQ193">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR193">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="AS193">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AT193">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AU193">
         <v>3</v>
@@ -41125,7 +41134,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -41197,25 +41206,25 @@
         <v>1.47</v>
       </c>
       <c r="AN194">
-        <v>1.17</v>
+        <v>0.79</v>
       </c>
       <c r="AO194">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="AP194">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ194">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR194">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AS194">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="AT194">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="AU194">
         <v>2</v>
@@ -41403,25 +41412,25 @@
         <v>2.43</v>
       </c>
       <c r="AN195">
-        <v>1.92</v>
+        <v>1.46</v>
       </c>
       <c r="AO195">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AP195">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ195">
         <v>0.93</v>
       </c>
       <c r="AR195">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AS195">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AT195">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="AU195">
         <v>12</v>
@@ -41609,25 +41618,25 @@
         <v>1.96</v>
       </c>
       <c r="AN196">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="AO196">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AP196">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ196">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR196">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AS196">
         <v>1.36</v>
       </c>
       <c r="AT196">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AU196">
         <v>5</v>
@@ -41815,25 +41824,25 @@
         <v>2.09</v>
       </c>
       <c r="AN197">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AO197">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AP197">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AQ197">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR197">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AS197">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AT197">
-        <v>3.17</v>
+        <v>2.85</v>
       </c>
       <c r="AU197">
         <v>2</v>
@@ -42021,25 +42030,25 @@
         <v>1.56</v>
       </c>
       <c r="AN198">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AO198">
+        <v>1.83</v>
+      </c>
+      <c r="AP198">
+        <v>1.75</v>
+      </c>
+      <c r="AQ198">
+        <v>1.82</v>
+      </c>
+      <c r="AR198">
+        <v>1.68</v>
+      </c>
+      <c r="AS198">
         <v>1.5</v>
       </c>
-      <c r="AP198">
-        <v>2.07</v>
-      </c>
-      <c r="AQ198">
-        <v>1.5</v>
-      </c>
-      <c r="AR198">
-        <v>1.82</v>
-      </c>
-      <c r="AS198">
-        <v>1.38</v>
-      </c>
       <c r="AT198">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AU198">
         <v>6</v>
@@ -42227,25 +42236,25 @@
         <v>1.49</v>
       </c>
       <c r="AN199">
-        <v>1.42</v>
+        <v>0.92</v>
       </c>
       <c r="AO199">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP199">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="AQ199">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR199">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AS199">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="AT199">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="AU199">
         <v>2</v>
@@ -42433,25 +42442,25 @@
         <v>1.66</v>
       </c>
       <c r="AN200">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AO200">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="AP200">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AQ200">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR200">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AS200">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AT200">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="AU200">
         <v>5</v>
@@ -42639,25 +42648,25 @@
         <v>1.21</v>
       </c>
       <c r="AN201">
+        <v>1.46</v>
+      </c>
+      <c r="AO201">
         <v>1.75</v>
       </c>
-      <c r="AO201">
-        <v>1.83</v>
-      </c>
       <c r="AP201">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ201">
         <v>1.86</v>
       </c>
       <c r="AR201">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AS201">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AT201">
-        <v>2.87</v>
+        <v>3.12</v>
       </c>
       <c r="AU201">
         <v>0</v>
@@ -42773,7 +42782,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -42845,25 +42854,25 @@
         <v>1.29</v>
       </c>
       <c r="AN202">
-        <v>1.17</v>
+        <v>0.92</v>
       </c>
       <c r="AO202">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AP202">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ202">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR202">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AS202">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AT202">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="AU202">
         <v>4</v>
@@ -42979,7 +42988,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43054,22 +43063,22 @@
         <v>1</v>
       </c>
       <c r="AO203">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AP203">
         <v>0.93</v>
       </c>
       <c r="AQ203">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AR203">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AS203">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AT203">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="AU203">
         <v>2</v>
@@ -43257,25 +43266,25 @@
         <v>0</v>
       </c>
       <c r="AN204">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AO204">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AP204">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ204">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="AR204">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AS204">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AT204">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="AU204">
         <v>4</v>
@@ -43391,7 +43400,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43463,25 +43472,25 @@
         <v>1.58</v>
       </c>
       <c r="AN205">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AO205">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AP205">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ205">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR205">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AS205">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AT205">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="AU205">
         <v>3</v>
@@ -43597,7 +43606,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -43669,25 +43678,25 @@
         <v>2.8</v>
       </c>
       <c r="AN206">
-        <v>2.17</v>
+        <v>1.76</v>
       </c>
       <c r="AO206">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AP206">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ206">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR206">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AS206">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AT206">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="AU206">
         <v>3</v>
@@ -43875,25 +43884,25 @@
         <v>2.15</v>
       </c>
       <c r="AN207">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AO207">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="AP207">
         <v>1.86</v>
       </c>
       <c r="AQ207">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AR207">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AS207">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AT207">
-        <v>3.56</v>
+        <v>3.27</v>
       </c>
       <c r="AU207">
         <v>13</v>
@@ -44081,25 +44090,25 @@
         <v>1.9</v>
       </c>
       <c r="AN208">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="AO208">
-        <v>0.42</v>
+        <v>0.76</v>
       </c>
       <c r="AP208">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AQ208">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR208">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AS208">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AT208">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AU208">
         <v>4</v>
@@ -44215,7 +44224,7 @@
         <v>214</v>
       </c>
       <c r="P209" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q209">
         <v>4.75</v>
@@ -44287,25 +44296,25 @@
         <v>1.23</v>
       </c>
       <c r="AN209">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AO209">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AP209">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AQ209">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AR209">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AS209">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AT209">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="AU209">
         <v>2</v>
@@ -44421,7 +44430,7 @@
         <v>215</v>
       </c>
       <c r="P210" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q210">
         <v>2.8</v>
@@ -44493,25 +44502,25 @@
         <v>1.63</v>
       </c>
       <c r="AN210">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AO210">
-        <v>0.85</v>
+        <v>1.23</v>
       </c>
       <c r="AP210">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AQ210">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR210">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AS210">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AT210">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AU210">
         <v>5</v>
@@ -44627,7 +44636,7 @@
         <v>216</v>
       </c>
       <c r="P211" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q211">
         <v>2.06</v>
@@ -44699,25 +44708,25 @@
         <v>2.28</v>
       </c>
       <c r="AN211">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AO211">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AP211">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AQ211">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AR211">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AS211">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AT211">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="AU211">
         <v>6</v>
@@ -44905,25 +44914,25 @@
         <v>1.66</v>
       </c>
       <c r="AN212">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="AO212">
         <v>1.15</v>
       </c>
       <c r="AP212">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AQ212">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR212">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AS212">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AT212">
-        <v>2.52</v>
+        <v>2.71</v>
       </c>
       <c r="AU212">
         <v>4</v>
@@ -45039,7 +45048,7 @@
         <v>86</v>
       </c>
       <c r="P213" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q213">
         <v>2.65</v>
@@ -45111,25 +45120,25 @@
         <v>1.73</v>
       </c>
       <c r="AN213">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AO213">
-        <v>0.77</v>
+        <v>1.19</v>
       </c>
       <c r="AP213">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ213">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AR213">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AS213">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AT213">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="AU213">
         <v>6</v>
@@ -45317,25 +45326,25 @@
         <v>1.17</v>
       </c>
       <c r="AN214">
-        <v>1.31</v>
+        <v>0.88</v>
       </c>
       <c r="AO214">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AP214">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="AQ214">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AR214">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AS214">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AT214">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="AU214">
         <v>7</v>
@@ -45451,7 +45460,7 @@
         <v>86</v>
       </c>
       <c r="P215" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q215">
         <v>6.8</v>
@@ -45523,25 +45532,25 @@
         <v>1.1</v>
       </c>
       <c r="AN215">
-        <v>1.08</v>
+        <v>0.73</v>
       </c>
       <c r="AO215">
         <v>1.77</v>
       </c>
       <c r="AP215">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ215">
         <v>1.86</v>
       </c>
       <c r="AR215">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AS215">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AT215">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="AU215">
         <v>3</v>
@@ -45657,7 +45666,7 @@
         <v>218</v>
       </c>
       <c r="P216" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q216">
         <v>1.91</v>
@@ -45729,25 +45738,25 @@
         <v>2.6</v>
       </c>
       <c r="AN216">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="AO216">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AP216">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AQ216">
         <v>0.93</v>
       </c>
       <c r="AR216">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AS216">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AT216">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AU216">
         <v>8</v>
@@ -45935,25 +45944,25 @@
         <v>2.23</v>
       </c>
       <c r="AN217">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO217">
-        <v>0.6899999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="AP217">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AQ217">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AR217">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AS217">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="AT217">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="AU217">
         <v>2</v>
@@ -46069,7 +46078,7 @@
         <v>220</v>
       </c>
       <c r="P218" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q218">
         <v>2.18</v>
@@ -46141,25 +46150,25 @@
         <v>2.07</v>
       </c>
       <c r="AN218">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AO218">
-        <v>0.38</v>
+        <v>0.7</v>
       </c>
       <c r="AP218">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ218">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR218">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AS218">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AT218">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="AU218">
         <v>6</v>
@@ -46347,25 +46356,25 @@
         <v>1.3</v>
       </c>
       <c r="AN219">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AO219">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AP219">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AQ219">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AR219">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AS219">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AT219">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AU219">
         <v>0</v>
@@ -46481,7 +46490,7 @@
         <v>221</v>
       </c>
       <c r="P220" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q220">
         <v>4.3</v>
@@ -46553,25 +46562,25 @@
         <v>1.25</v>
       </c>
       <c r="AN220">
-        <v>1.15</v>
+        <v>0.89</v>
       </c>
       <c r="AO220">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AP220">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="AQ220">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AR220">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AS220">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AT220">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="AU220">
         <v>7</v>
@@ -46759,25 +46768,25 @@
         <v>2.4</v>
       </c>
       <c r="AN221">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AO221">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AP221">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AQ221">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AR221">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AS221">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AT221">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="AU221">
         <v>8</v>
@@ -46965,25 +46974,25 @@
         <v>1.5</v>
       </c>
       <c r="AN222">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AO222">
-        <v>0.46</v>
+        <v>0.89</v>
       </c>
       <c r="AP222">
         <v>0.93</v>
       </c>
       <c r="AQ222">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR222">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AS222">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AT222">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AU222">
         <v>4</v>
@@ -47171,25 +47180,25 @@
         <v>1.99</v>
       </c>
       <c r="AN223">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AO223">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AP223">
         <v>1.86</v>
       </c>
       <c r="AQ223">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR223">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AS223">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AT223">
-        <v>3.27</v>
+        <v>3.14</v>
       </c>
       <c r="AU223">
         <v>5</v>
@@ -47256,6 +47265,418 @@
       </c>
       <c r="BP223">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7486702</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45712.5</v>
+      </c>
+      <c r="F224">
+        <v>28</v>
+      </c>
+      <c r="G224" t="s">
+        <v>73</v>
+      </c>
+      <c r="H224" t="s">
+        <v>72</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>1</v>
+      </c>
+      <c r="K224">
+        <v>1</v>
+      </c>
+      <c r="L224">
+        <v>1</v>
+      </c>
+      <c r="M224">
+        <v>2</v>
+      </c>
+      <c r="N224">
+        <v>3</v>
+      </c>
+      <c r="O224" t="s">
+        <v>223</v>
+      </c>
+      <c r="P224" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q224">
+        <v>3.5</v>
+      </c>
+      <c r="R224">
+        <v>2</v>
+      </c>
+      <c r="S224">
+        <v>3.4</v>
+      </c>
+      <c r="T224">
+        <v>1.5</v>
+      </c>
+      <c r="U224">
+        <v>2.5</v>
+      </c>
+      <c r="V224">
+        <v>3.4</v>
+      </c>
+      <c r="W224">
+        <v>1.3</v>
+      </c>
+      <c r="X224">
+        <v>10</v>
+      </c>
+      <c r="Y224">
+        <v>1.06</v>
+      </c>
+      <c r="Z224">
+        <v>2.7</v>
+      </c>
+      <c r="AA224">
+        <v>3</v>
+      </c>
+      <c r="AB224">
+        <v>2.6</v>
+      </c>
+      <c r="AC224">
+        <v>1.08</v>
+      </c>
+      <c r="AD224">
+        <v>7</v>
+      </c>
+      <c r="AE224">
+        <v>1.39</v>
+      </c>
+      <c r="AF224">
+        <v>2.85</v>
+      </c>
+      <c r="AG224">
+        <v>2.25</v>
+      </c>
+      <c r="AH224">
+        <v>1.62</v>
+      </c>
+      <c r="AI224">
+        <v>1.83</v>
+      </c>
+      <c r="AJ224">
+        <v>1.83</v>
+      </c>
+      <c r="AK224">
+        <v>1.43</v>
+      </c>
+      <c r="AL224">
+        <v>1.33</v>
+      </c>
+      <c r="AM224">
+        <v>1.43</v>
+      </c>
+      <c r="AN224">
+        <v>1.22</v>
+      </c>
+      <c r="AO224">
+        <v>1.37</v>
+      </c>
+      <c r="AP224">
+        <v>1.18</v>
+      </c>
+      <c r="AQ224">
+        <v>1.43</v>
+      </c>
+      <c r="AR224">
+        <v>1.39</v>
+      </c>
+      <c r="AS224">
+        <v>1.46</v>
+      </c>
+      <c r="AT224">
+        <v>2.85</v>
+      </c>
+      <c r="AU224">
+        <v>5</v>
+      </c>
+      <c r="AV224">
+        <v>4</v>
+      </c>
+      <c r="AW224">
+        <v>11</v>
+      </c>
+      <c r="AX224">
+        <v>2</v>
+      </c>
+      <c r="AY224">
+        <v>21</v>
+      </c>
+      <c r="AZ224">
+        <v>7</v>
+      </c>
+      <c r="BA224">
+        <v>3</v>
+      </c>
+      <c r="BB224">
+        <v>5</v>
+      </c>
+      <c r="BC224">
+        <v>8</v>
+      </c>
+      <c r="BD224">
+        <v>1.98</v>
+      </c>
+      <c r="BE224">
+        <v>6.75</v>
+      </c>
+      <c r="BF224">
+        <v>1.98</v>
+      </c>
+      <c r="BG224">
+        <v>1.22</v>
+      </c>
+      <c r="BH224">
+        <v>3.65</v>
+      </c>
+      <c r="BI224">
+        <v>1.4</v>
+      </c>
+      <c r="BJ224">
+        <v>2.65</v>
+      </c>
+      <c r="BK224">
+        <v>1.65</v>
+      </c>
+      <c r="BL224">
+        <v>2.05</v>
+      </c>
+      <c r="BM224">
+        <v>2.02</v>
+      </c>
+      <c r="BN224">
+        <v>1.68</v>
+      </c>
+      <c r="BO224">
+        <v>2.55</v>
+      </c>
+      <c r="BP224">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7486703</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45712.625</v>
+      </c>
+      <c r="F225">
+        <v>28</v>
+      </c>
+      <c r="G225" t="s">
+        <v>70</v>
+      </c>
+      <c r="H225" t="s">
+        <v>81</v>
+      </c>
+      <c r="I225">
+        <v>1</v>
+      </c>
+      <c r="J225">
+        <v>2</v>
+      </c>
+      <c r="K225">
+        <v>3</v>
+      </c>
+      <c r="L225">
+        <v>1</v>
+      </c>
+      <c r="M225">
+        <v>3</v>
+      </c>
+      <c r="N225">
+        <v>4</v>
+      </c>
+      <c r="O225" t="s">
+        <v>209</v>
+      </c>
+      <c r="P225" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q225">
+        <v>3.6</v>
+      </c>
+      <c r="R225">
+        <v>2.05</v>
+      </c>
+      <c r="S225">
+        <v>3.2</v>
+      </c>
+      <c r="T225">
+        <v>1.44</v>
+      </c>
+      <c r="U225">
+        <v>2.63</v>
+      </c>
+      <c r="V225">
+        <v>3.4</v>
+      </c>
+      <c r="W225">
+        <v>1.3</v>
+      </c>
+      <c r="X225">
+        <v>10</v>
+      </c>
+      <c r="Y225">
+        <v>1.06</v>
+      </c>
+      <c r="Z225">
+        <v>2.93</v>
+      </c>
+      <c r="AA225">
+        <v>3.19</v>
+      </c>
+      <c r="AB225">
+        <v>2.41</v>
+      </c>
+      <c r="AC225">
+        <v>1.07</v>
+      </c>
+      <c r="AD225">
+        <v>7.5</v>
+      </c>
+      <c r="AE225">
+        <v>1.38</v>
+      </c>
+      <c r="AF225">
+        <v>2.9</v>
+      </c>
+      <c r="AG225">
+        <v>1.95</v>
+      </c>
+      <c r="AH225">
+        <v>1.79</v>
+      </c>
+      <c r="AI225">
+        <v>1.83</v>
+      </c>
+      <c r="AJ225">
+        <v>1.83</v>
+      </c>
+      <c r="AK225">
+        <v>1.5</v>
+      </c>
+      <c r="AL225">
+        <v>1.32</v>
+      </c>
+      <c r="AM225">
+        <v>1.38</v>
+      </c>
+      <c r="AN225">
+        <v>1.26</v>
+      </c>
+      <c r="AO225">
+        <v>1.56</v>
+      </c>
+      <c r="AP225">
+        <v>1.21</v>
+      </c>
+      <c r="AQ225">
+        <v>1.61</v>
+      </c>
+      <c r="AR225">
+        <v>1.46</v>
+      </c>
+      <c r="AS225">
+        <v>1.59</v>
+      </c>
+      <c r="AT225">
+        <v>3.05</v>
+      </c>
+      <c r="AU225">
+        <v>5</v>
+      </c>
+      <c r="AV225">
+        <v>6</v>
+      </c>
+      <c r="AW225">
+        <v>15</v>
+      </c>
+      <c r="AX225">
+        <v>8</v>
+      </c>
+      <c r="AY225">
+        <v>22</v>
+      </c>
+      <c r="AZ225">
+        <v>16</v>
+      </c>
+      <c r="BA225">
+        <v>3</v>
+      </c>
+      <c r="BB225">
+        <v>6</v>
+      </c>
+      <c r="BC225">
+        <v>9</v>
+      </c>
+      <c r="BD225">
+        <v>2.2</v>
+      </c>
+      <c r="BE225">
+        <v>8</v>
+      </c>
+      <c r="BF225">
+        <v>1.91</v>
+      </c>
+      <c r="BG225">
+        <v>1.28</v>
+      </c>
+      <c r="BH225">
+        <v>3.25</v>
+      </c>
+      <c r="BI225">
+        <v>1.52</v>
+      </c>
+      <c r="BJ225">
+        <v>2.37</v>
+      </c>
+      <c r="BK225">
+        <v>1.87</v>
+      </c>
+      <c r="BL225">
+        <v>1.87</v>
+      </c>
+      <c r="BM225">
+        <v>2.38</v>
+      </c>
+      <c r="BN225">
+        <v>1.54</v>
+      </c>
+      <c r="BO225">
+        <v>3.12</v>
+      </c>
+      <c r="BP225">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -1660,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
         <v>0.93</v>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ3">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2072,10 +2072,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AQ4">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2278,10 +2278,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ5">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2487,7 +2487,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2690,10 +2690,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AQ7">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2896,10 +2896,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ8">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3102,10 +3102,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ9">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3308,19 +3308,19 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AQ10">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="AR10">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AU10">
         <v>6</v>
@@ -3508,10 +3508,10 @@
         <v>1.13</v>
       </c>
       <c r="AN11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP11">
         <v>0.93</v>
@@ -3520,13 +3520,13 @@
         <v>1.86</v>
       </c>
       <c r="AR11">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>5</v>
@@ -3714,25 +3714,25 @@
         <v>2.1</v>
       </c>
       <c r="AN12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AQ12">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR12">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>9</v>
@@ -3920,25 +3920,25 @@
         <v>1.4</v>
       </c>
       <c r="AN13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AQ13">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AR13">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>8</v>
@@ -4126,25 +4126,25 @@
         <v>1.72</v>
       </c>
       <c r="AN14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AQ14">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR14">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AU14">
         <v>7</v>
@@ -4335,22 +4335,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ15">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR15">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AU15">
         <v>5</v>
@@ -4538,25 +4538,25 @@
         <v>1.3</v>
       </c>
       <c r="AN16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR16">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AU16">
         <v>7</v>
@@ -4744,25 +4744,25 @@
         <v>1.55</v>
       </c>
       <c r="AN17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AQ17">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR17">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AU17">
         <v>3</v>
@@ -4950,25 +4950,25 @@
         <v>1.8</v>
       </c>
       <c r="AN18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ18">
         <v>0.93</v>
       </c>
       <c r="AR18">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="AS18">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AT18">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AU18">
         <v>2</v>
@@ -5159,22 +5159,22 @@
         <v>1</v>
       </c>
       <c r="AO19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP19">
         <v>1.86</v>
       </c>
       <c r="AQ19">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR19">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="AS19">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="AT19">
-        <v>3</v>
+        <v>3.54</v>
       </c>
       <c r="AU19">
         <v>8</v>
@@ -5362,25 +5362,25 @@
         <v>1.6</v>
       </c>
       <c r="AN20">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP20">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AQ20">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR20">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AS20">
-        <v>1.19</v>
+        <v>0.71</v>
       </c>
       <c r="AT20">
-        <v>2.83</v>
+        <v>2.16</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5571,22 +5571,22 @@
         <v>3</v>
       </c>
       <c r="AO21">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AQ21">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR21">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AS21">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="AT21">
-        <v>2.64</v>
+        <v>2.51</v>
       </c>
       <c r="AU21">
         <v>2</v>
@@ -5774,25 +5774,25 @@
         <v>2.35</v>
       </c>
       <c r="AN22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="AR22">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AS22">
-        <v>1.18</v>
+        <v>0.77</v>
       </c>
       <c r="AT22">
-        <v>2.97</v>
+        <v>2.66</v>
       </c>
       <c r="AU22">
         <v>2</v>
@@ -5980,25 +5980,25 @@
         <v>1.95</v>
       </c>
       <c r="AN23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AQ23">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AR23">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AS23">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AT23">
-        <v>3.77</v>
+        <v>4.23</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -6186,25 +6186,25 @@
         <v>1.36</v>
       </c>
       <c r="AN24">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ24">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AR24">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AS24">
-        <v>1.06</v>
+        <v>0.54</v>
       </c>
       <c r="AT24">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="AU24">
         <v>5</v>
@@ -6392,25 +6392,25 @@
         <v>1.26</v>
       </c>
       <c r="AN25">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO25">
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ25">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="AR25">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="AS25">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AT25">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6598,25 +6598,25 @@
         <v>1.63</v>
       </c>
       <c r="AN26">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AO26">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AQ26">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR26">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AS26">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="AT26">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AU26">
         <v>5</v>
@@ -6804,25 +6804,25 @@
         <v>1.75</v>
       </c>
       <c r="AN27">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO27">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AP27">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ27">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR27">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AS27">
-        <v>1.22</v>
+        <v>0.99</v>
       </c>
       <c r="AT27">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -7010,25 +7010,25 @@
         <v>2.25</v>
       </c>
       <c r="AN28">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AQ28">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR28">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AS28">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AT28">
-        <v>3.31</v>
+        <v>3.56</v>
       </c>
       <c r="AU28">
         <v>6</v>
@@ -7216,25 +7216,25 @@
         <v>2.35</v>
       </c>
       <c r="AN29">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO29">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AQ29">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR29">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="AS29">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="AT29">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AU29">
         <v>0</v>
@@ -7422,25 +7422,25 @@
         <v>1.66</v>
       </c>
       <c r="AN30">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AO30">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AQ30">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AS30">
-        <v>1.09</v>
+        <v>0.84</v>
       </c>
       <c r="AT30">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="AU30">
         <v>7</v>
@@ -7628,25 +7628,25 @@
         <v>1.45</v>
       </c>
       <c r="AN31">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AO31">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AP31">
         <v>0.93</v>
       </c>
       <c r="AQ31">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR31">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AS31">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AT31">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="AU31">
         <v>3</v>
@@ -7834,25 +7834,25 @@
         <v>1.72</v>
       </c>
       <c r="AN32">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO32">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AQ32">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR32">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AS32">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AT32">
-        <v>3.16</v>
+        <v>3.44</v>
       </c>
       <c r="AU32">
         <v>5</v>
@@ -8040,7 +8040,7 @@
         <v>2</v>
       </c>
       <c r="AN33">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AO33">
         <v>1</v>
@@ -8049,16 +8049,16 @@
         <v>1.86</v>
       </c>
       <c r="AQ33">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR33">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AS33">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AT33">
-        <v>3.46</v>
+        <v>3.79</v>
       </c>
       <c r="AU33">
         <v>9</v>
@@ -8246,25 +8246,25 @@
         <v>1.68</v>
       </c>
       <c r="AN34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO34">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ34">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="AR34">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AS34">
-        <v>1.13</v>
+        <v>0.9</v>
       </c>
       <c r="AT34">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AU34">
         <v>3</v>
@@ -8452,25 +8452,25 @@
         <v>1.47</v>
       </c>
       <c r="AN35">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO35">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ35">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR35">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AS35">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT35">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="AU35">
         <v>8</v>
@@ -8658,25 +8658,25 @@
         <v>1.25</v>
       </c>
       <c r="AN36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO36">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ36">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="AR36">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AS36">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AT36">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="AU36">
         <v>4</v>
@@ -8870,19 +8870,19 @@
         <v>2</v>
       </c>
       <c r="AP37">
+        <v>1.71</v>
+      </c>
+      <c r="AQ37">
         <v>1.43</v>
       </c>
-      <c r="AQ37">
-        <v>1.75</v>
-      </c>
       <c r="AR37">
-        <v>1.66</v>
+        <v>1.39</v>
       </c>
       <c r="AS37">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AT37">
-        <v>3.39</v>
+        <v>3.17</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -9073,22 +9073,22 @@
         <v>1</v>
       </c>
       <c r="AO38">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AQ38">
         <v>0.93</v>
       </c>
       <c r="AR38">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AS38">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="AT38">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="AU38">
         <v>7</v>
@@ -9276,25 +9276,25 @@
         <v>1.34</v>
       </c>
       <c r="AN39">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AO39">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP39">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ39">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AR39">
-        <v>0.97</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS39">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AT39">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9482,25 +9482,25 @@
         <v>1.44</v>
       </c>
       <c r="AN40">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO40">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP40">
+        <v>1.29</v>
+      </c>
+      <c r="AQ40">
+        <v>1.36</v>
+      </c>
+      <c r="AR40">
+        <v>1.48</v>
+      </c>
+      <c r="AS40">
         <v>0.89</v>
       </c>
-      <c r="AQ40">
-        <v>1.61</v>
-      </c>
-      <c r="AR40">
-        <v>1.49</v>
-      </c>
-      <c r="AS40">
-        <v>1.11</v>
-      </c>
       <c r="AT40">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AU40">
         <v>7</v>
@@ -9688,25 +9688,25 @@
         <v>1.57</v>
       </c>
       <c r="AN41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO41">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="AP41">
         <v>0.93</v>
       </c>
       <c r="AQ41">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR41">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AS41">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AT41">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="AU41">
         <v>7</v>
@@ -9894,25 +9894,25 @@
         <v>2.35</v>
       </c>
       <c r="AN42">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AO42">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AQ42">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR42">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AS42">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AT42">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="AU42">
         <v>12</v>
@@ -10100,25 +10100,25 @@
         <v>1.7</v>
       </c>
       <c r="AN43">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AO43">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ43">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR43">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="AS43">
-        <v>1.49</v>
+        <v>1.14</v>
       </c>
       <c r="AT43">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="AU43">
         <v>4</v>
@@ -10306,25 +10306,25 @@
         <v>2.6</v>
       </c>
       <c r="AN44">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AP44">
         <v>1.86</v>
       </c>
       <c r="AQ44">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR44">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="AS44">
         <v>1.49</v>
       </c>
       <c r="AT44">
-        <v>3.45</v>
+        <v>3.72</v>
       </c>
       <c r="AU44">
         <v>3</v>
@@ -10512,25 +10512,25 @@
         <v>2</v>
       </c>
       <c r="AN45">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AO45">
-        <v>1.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP45">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AQ45">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR45">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AS45">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AT45">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="AU45">
         <v>4</v>
@@ -10718,25 +10718,25 @@
         <v>1.62</v>
       </c>
       <c r="AN46">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AO46">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP46">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AQ46">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR46">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AS46">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AT46">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="AU46">
         <v>8</v>
@@ -10924,25 +10924,25 @@
         <v>2.02</v>
       </c>
       <c r="AN47">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AO47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR47">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AS47">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AT47">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -11130,25 +11130,25 @@
         <v>1.45</v>
       </c>
       <c r="AN48">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO48">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AP48">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ48">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR48">
-        <v>1.12</v>
+        <v>0.93</v>
       </c>
       <c r="AS48">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AT48">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -11336,25 +11336,25 @@
         <v>1.36</v>
       </c>
       <c r="AN49">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO49">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AQ49">
+        <v>1.14</v>
+      </c>
+      <c r="AR49">
+        <v>1.48</v>
+      </c>
+      <c r="AS49">
         <v>1.61</v>
       </c>
-      <c r="AR49">
-        <v>1.44</v>
-      </c>
-      <c r="AS49">
-        <v>1.48</v>
-      </c>
       <c r="AT49">
-        <v>2.92</v>
+        <v>3.09</v>
       </c>
       <c r="AU49">
         <v>9</v>
@@ -11545,22 +11545,22 @@
         <v>1.33</v>
       </c>
       <c r="AO50">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AQ50">
         <v>0.93</v>
       </c>
       <c r="AR50">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AS50">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AT50">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11748,25 +11748,25 @@
         <v>1.4</v>
       </c>
       <c r="AN51">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO51">
         <v>2.33</v>
       </c>
       <c r="AP51">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ51">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AR51">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AS51">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="AT51">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AU51">
         <v>3</v>
@@ -11954,25 +11954,25 @@
         <v>2.49</v>
       </c>
       <c r="AN52">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO52">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AQ52">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="AR52">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AS52">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="AT52">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="AU52">
         <v>12</v>
@@ -12160,25 +12160,25 @@
         <v>1.2</v>
       </c>
       <c r="AN53">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO53">
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ53">
         <v>1.86</v>
       </c>
       <c r="AR53">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AS53">
-        <v>1.88</v>
+        <v>1.17</v>
       </c>
       <c r="AT53">
-        <v>3.01</v>
+        <v>2.36</v>
       </c>
       <c r="AU53">
         <v>6</v>
@@ -12366,25 +12366,25 @@
         <v>1.24</v>
       </c>
       <c r="AN54">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="AO54">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AR54">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AS54">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AT54">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="AU54">
         <v>4</v>
@@ -12575,19 +12575,19 @@
         <v>1</v>
       </c>
       <c r="AO55">
-        <v>1.17</v>
+        <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ55">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR55">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AS55">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="AT55">
         <v>3.05</v>
@@ -12781,22 +12781,22 @@
         <v>2</v>
       </c>
       <c r="AO56">
+        <v>1.33</v>
+      </c>
+      <c r="AP56">
         <v>1.14</v>
       </c>
-      <c r="AP56">
-        <v>1.04</v>
-      </c>
       <c r="AQ56">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR56">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AS56">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AT56">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12984,25 +12984,25 @@
         <v>1.68</v>
       </c>
       <c r="AN57">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="AO57">
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ57">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR57">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AS57">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT57">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AU57">
         <v>8</v>
@@ -13190,25 +13190,25 @@
         <v>1.68</v>
       </c>
       <c r="AN58">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO58">
+        <v>1.25</v>
+      </c>
+      <c r="AP58">
+        <v>2.07</v>
+      </c>
+      <c r="AQ58">
         <v>1.14</v>
       </c>
-      <c r="AP58">
-        <v>1.75</v>
-      </c>
-      <c r="AQ58">
-        <v>1.61</v>
-      </c>
       <c r="AR58">
-        <v>1.74</v>
+        <v>2.03</v>
       </c>
       <c r="AS58">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AT58">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13396,25 +13396,25 @@
         <v>1.46</v>
       </c>
       <c r="AN59">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO59">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ59">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR59">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="AS59">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AT59">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13602,25 +13602,25 @@
         <v>1.45</v>
       </c>
       <c r="AN60">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AO60">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AQ60">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AR60">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AS60">
-        <v>1.78</v>
+        <v>1.23</v>
       </c>
       <c r="AT60">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13808,7 +13808,7 @@
         <v>2.6</v>
       </c>
       <c r="AN61">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AO61">
         <v>1</v>
@@ -13817,13 +13817,13 @@
         <v>1.86</v>
       </c>
       <c r="AQ61">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR61">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="AS61">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AT61">
         <v>3.27</v>
@@ -14014,25 +14014,25 @@
         <v>1.71</v>
       </c>
       <c r="AN62">
-        <v>1.14</v>
+        <v>0.33</v>
       </c>
       <c r="AO62">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AP62">
         <v>0.93</v>
       </c>
       <c r="AQ62">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR62">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AS62">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AT62">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -14220,25 +14220,25 @@
         <v>1.94</v>
       </c>
       <c r="AN63">
+        <v>3</v>
+      </c>
+      <c r="AO63">
+        <v>0.75</v>
+      </c>
+      <c r="AP63">
         <v>2.14</v>
       </c>
-      <c r="AO63">
-        <v>1.71</v>
-      </c>
-      <c r="AP63">
-        <v>1.82</v>
-      </c>
       <c r="AQ63">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR63">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="AS63">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT63">
-        <v>2.37</v>
+        <v>2.67</v>
       </c>
       <c r="AU63">
         <v>3</v>
@@ -14429,22 +14429,22 @@
         <v>1</v>
       </c>
       <c r="AO64">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP64">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AQ64">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="AR64">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AS64">
-        <v>1.26</v>
+        <v>0.88</v>
       </c>
       <c r="AT64">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14632,25 +14632,25 @@
         <v>1.95</v>
       </c>
       <c r="AN65">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO65">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ65">
         <v>0.93</v>
       </c>
       <c r="AR65">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AS65">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AT65">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14838,25 +14838,25 @@
         <v>1.25</v>
       </c>
       <c r="AN66">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="AO66">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AP66">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ66">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR66">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AS66">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AT66">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="AU66">
         <v>3</v>
@@ -15044,25 +15044,25 @@
         <v>1.4</v>
       </c>
       <c r="AN67">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AO67">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ67">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR67">
-        <v>1.18</v>
+        <v>0.97</v>
       </c>
       <c r="AS67">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AT67">
-        <v>2.78</v>
+        <v>2.47</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -15250,25 +15250,25 @@
         <v>1.25</v>
       </c>
       <c r="AN68">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO68">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AQ68">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AR68">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AS68">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AT68">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="AU68">
         <v>6</v>
@@ -15456,25 +15456,25 @@
         <v>1.57</v>
       </c>
       <c r="AN69">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AO69">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AQ69">
         <v>1.86</v>
       </c>
       <c r="AR69">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AS69">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AT69">
-        <v>3.59</v>
+        <v>3.32</v>
       </c>
       <c r="AU69">
         <v>6</v>
@@ -15662,25 +15662,25 @@
         <v>1.5</v>
       </c>
       <c r="AN70">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO70">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ70">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR70">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AS70">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AT70">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="AU70">
         <v>3</v>
@@ -15868,25 +15868,25 @@
         <v>1.78</v>
       </c>
       <c r="AN71">
+        <v>1</v>
+      </c>
+      <c r="AO71">
+        <v>1.8</v>
+      </c>
+      <c r="AP71">
+        <v>2.07</v>
+      </c>
+      <c r="AQ71">
+        <v>1.5</v>
+      </c>
+      <c r="AR71">
+        <v>1.35</v>
+      </c>
+      <c r="AS71">
         <v>1.13</v>
       </c>
-      <c r="AO71">
-        <v>2.25</v>
-      </c>
-      <c r="AP71">
-        <v>1.61</v>
-      </c>
-      <c r="AQ71">
-        <v>1.82</v>
-      </c>
-      <c r="AR71">
-        <v>1.37</v>
-      </c>
-      <c r="AS71">
-        <v>1.22</v>
-      </c>
       <c r="AT71">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="AU71">
         <v>4</v>
@@ -16074,25 +16074,25 @@
         <v>1.8</v>
       </c>
       <c r="AN72">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO72">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AP72">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ72">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR72">
-        <v>1.34</v>
+        <v>1.78</v>
       </c>
       <c r="AS72">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AT72">
-        <v>2.57</v>
+        <v>2.91</v>
       </c>
       <c r="AU72">
         <v>8</v>
@@ -16280,25 +16280,25 @@
         <v>1.62</v>
       </c>
       <c r="AN73">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO73">
-        <v>1.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP73">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AQ73">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR73">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AS73">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AT73">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16486,25 +16486,25 @@
         <v>1.25</v>
       </c>
       <c r="AN74">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AO74">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ74">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AR74">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AS74">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AT74">
-        <v>3.02</v>
+        <v>2.66</v>
       </c>
       <c r="AU74">
         <v>2</v>
@@ -16692,25 +16692,25 @@
         <v>2.45</v>
       </c>
       <c r="AN75">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AO75">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AP75">
         <v>1.86</v>
       </c>
       <c r="AQ75">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR75">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AS75">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AT75">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16898,25 +16898,25 @@
         <v>1.62</v>
       </c>
       <c r="AN76">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AO76">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AQ76">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR76">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AS76">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AT76">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -17104,25 +17104,25 @@
         <v>1.53</v>
       </c>
       <c r="AN77">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO77">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AQ77">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AR77">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AS77">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AT77">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AU77">
         <v>5</v>
@@ -17310,25 +17310,25 @@
         <v>1.71</v>
       </c>
       <c r="AN78">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AO78">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="AP78">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ78">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR78">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AS78">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AT78">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="AU78">
         <v>9</v>
@@ -17516,25 +17516,25 @@
         <v>1.22</v>
       </c>
       <c r="AN79">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AO79">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP79">
         <v>0.93</v>
       </c>
       <c r="AQ79">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="AR79">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AS79">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AT79">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="AU79">
         <v>3</v>
@@ -17722,25 +17722,25 @@
         <v>1.57</v>
       </c>
       <c r="AN80">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO80">
-        <v>1.3</v>
+        <v>0.25</v>
       </c>
       <c r="AP80">
+        <v>1.57</v>
+      </c>
+      <c r="AQ80">
+        <v>1</v>
+      </c>
+      <c r="AR80">
+        <v>1.06</v>
+      </c>
+      <c r="AS80">
         <v>1.32</v>
       </c>
-      <c r="AQ80">
-        <v>1.36</v>
-      </c>
-      <c r="AR80">
-        <v>1.23</v>
-      </c>
-      <c r="AS80">
-        <v>1.28</v>
-      </c>
       <c r="AT80">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AU80">
         <v>10</v>
@@ -17928,25 +17928,25 @@
         <v>1.9</v>
       </c>
       <c r="AN81">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="AO81">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="AP81">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ81">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="AR81">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AS81">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AT81">
-        <v>2.58</v>
+        <v>2.29</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -18134,25 +18134,25 @@
         <v>1.3</v>
       </c>
       <c r="AN82">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AO82">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AQ82">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AR82">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AS82">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AT82">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AU82">
         <v>2</v>
@@ -18343,22 +18343,22 @@
         <v>1.67</v>
       </c>
       <c r="AO83">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="AP83">
+        <v>1.93</v>
+      </c>
+      <c r="AQ83">
+        <v>1.29</v>
+      </c>
+      <c r="AR83">
         <v>1.79</v>
       </c>
-      <c r="AQ83">
-        <v>1.18</v>
-      </c>
-      <c r="AR83">
-        <v>1.74</v>
-      </c>
       <c r="AS83">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AT83">
-        <v>3.21</v>
+        <v>2.98</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18546,25 +18546,25 @@
         <v>1.95</v>
       </c>
       <c r="AN84">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="AO84">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AP84">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AQ84">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR84">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AS84">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AT84">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AU84">
         <v>2</v>
@@ -18752,25 +18752,25 @@
         <v>1.25</v>
       </c>
       <c r="AN85">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AO85">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ85">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR85">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AS85">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AT85">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AU85">
         <v>5</v>
@@ -18958,25 +18958,25 @@
         <v>1.44</v>
       </c>
       <c r="AN86">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AO86">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="AP86">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AQ86">
         <v>1.86</v>
       </c>
       <c r="AR86">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AS86">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="AT86">
-        <v>3.39</v>
+        <v>2.99</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -19164,25 +19164,25 @@
         <v>2.9</v>
       </c>
       <c r="AN87">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AO87">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AQ87">
         <v>0.93</v>
       </c>
       <c r="AR87">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AS87">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AT87">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AU87">
         <v>8</v>
@@ -19370,25 +19370,25 @@
         <v>1.52</v>
       </c>
       <c r="AN88">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AO88">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AP88">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ88">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR88">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="AS88">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AT88">
-        <v>2.79</v>
+        <v>3.05</v>
       </c>
       <c r="AU88">
         <v>5</v>
@@ -19576,22 +19576,22 @@
         <v>1.86</v>
       </c>
       <c r="AN89">
+        <v>1.5</v>
+      </c>
+      <c r="AO89">
+        <v>0.67</v>
+      </c>
+      <c r="AP89">
+        <v>1.5</v>
+      </c>
+      <c r="AQ89">
+        <v>1.36</v>
+      </c>
+      <c r="AR89">
+        <v>1.6</v>
+      </c>
+      <c r="AS89">
         <v>1.09</v>
-      </c>
-      <c r="AO89">
-        <v>1.55</v>
-      </c>
-      <c r="AP89">
-        <v>1.21</v>
-      </c>
-      <c r="AQ89">
-        <v>1.61</v>
-      </c>
-      <c r="AR89">
-        <v>1.53</v>
-      </c>
-      <c r="AS89">
-        <v>1.16</v>
       </c>
       <c r="AT89">
         <v>2.69</v>
@@ -19782,25 +19782,25 @@
         <v>1.24</v>
       </c>
       <c r="AN90">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AO90">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AP90">
         <v>0.93</v>
       </c>
       <c r="AQ90">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AR90">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS90">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AT90">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="AU90">
         <v>4</v>
@@ -19988,25 +19988,25 @@
         <v>2.7</v>
       </c>
       <c r="AN91">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AO91">
-        <v>1.27</v>
+        <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AQ91">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR91">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AS91">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AT91">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20194,25 +20194,25 @@
         <v>1.37</v>
       </c>
       <c r="AN92">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AO92">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AQ92">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AR92">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AS92">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AT92">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AU92">
         <v>3</v>
@@ -20400,25 +20400,25 @@
         <v>1.44</v>
       </c>
       <c r="AN93">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="AO93">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ93">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR93">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AS93">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AT93">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AU93">
         <v>3</v>
@@ -20606,25 +20606,25 @@
         <v>1.29</v>
       </c>
       <c r="AN94">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AO94">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ94">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="AR94">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AS94">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AT94">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="AU94">
         <v>8</v>
@@ -20812,25 +20812,25 @@
         <v>3.15</v>
       </c>
       <c r="AN95">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AO95">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP95">
         <v>1.86</v>
       </c>
       <c r="AQ95">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR95">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AS95">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AT95">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="AU95">
         <v>9</v>
@@ -21018,25 +21018,25 @@
         <v>1.42</v>
       </c>
       <c r="AN96">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AO96">
-        <v>1.08</v>
+        <v>0.2</v>
       </c>
       <c r="AP96">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR96">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AS96">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AT96">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="AU96">
         <v>9</v>
@@ -21224,25 +21224,25 @@
         <v>1.78</v>
       </c>
       <c r="AN97">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="AO97">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AP97">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AQ97">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR97">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AS97">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AT97">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="AU97">
         <v>5</v>
@@ -21433,22 +21433,22 @@
         <v>1.17</v>
       </c>
       <c r="AO98">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AQ98">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR98">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AS98">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="AT98">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21636,25 +21636,25 @@
         <v>1.15</v>
       </c>
       <c r="AN99">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO99">
+        <v>1.67</v>
+      </c>
+      <c r="AP99">
+        <v>1.57</v>
+      </c>
+      <c r="AQ99">
         <v>1.64</v>
       </c>
-      <c r="AP99">
-        <v>1.32</v>
-      </c>
-      <c r="AQ99">
-        <v>1.79</v>
-      </c>
       <c r="AR99">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AS99">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AT99">
-        <v>3.07</v>
+        <v>2.86</v>
       </c>
       <c r="AU99">
         <v>0</v>
@@ -21842,25 +21842,25 @@
         <v>2.85</v>
       </c>
       <c r="AN100">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AO100">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP100">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AQ100">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="AR100">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AS100">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="AT100">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -22048,25 +22048,25 @@
         <v>1.2</v>
       </c>
       <c r="AN101">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AO101">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AP101">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ101">
         <v>1.86</v>
       </c>
       <c r="AR101">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AS101">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="AT101">
-        <v>2.91</v>
+        <v>2.58</v>
       </c>
       <c r="AU101">
         <v>2</v>
@@ -22254,25 +22254,25 @@
         <v>1.87</v>
       </c>
       <c r="AN102">
+        <v>1.67</v>
+      </c>
+      <c r="AO102">
         <v>1.17</v>
       </c>
-      <c r="AO102">
-        <v>1</v>
-      </c>
       <c r="AP102">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AQ102">
         <v>0.93</v>
       </c>
       <c r="AR102">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AS102">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AT102">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22460,25 +22460,25 @@
         <v>1.72</v>
       </c>
       <c r="AN103">
-        <v>1.08</v>
+        <v>0.8</v>
       </c>
       <c r="AO103">
-        <v>1.08</v>
+        <v>0.6</v>
       </c>
       <c r="AP103">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AQ103">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR103">
+        <v>1.37</v>
+      </c>
+      <c r="AS103">
         <v>1.44</v>
       </c>
-      <c r="AS103">
-        <v>1.56</v>
-      </c>
       <c r="AT103">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AU103">
         <v>8</v>
@@ -22666,25 +22666,25 @@
         <v>1.95</v>
       </c>
       <c r="AN104">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AO104">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AQ104">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR104">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AS104">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AT104">
-        <v>3.31</v>
+        <v>3.52</v>
       </c>
       <c r="AU104">
         <v>9</v>
@@ -22872,25 +22872,25 @@
         <v>1.95</v>
       </c>
       <c r="AN105">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AO105">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="AP105">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ105">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR105">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AS105">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AT105">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AU105">
         <v>6</v>
@@ -23078,25 +23078,25 @@
         <v>1.66</v>
       </c>
       <c r="AN106">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AO106">
-        <v>1.31</v>
+        <v>0.67</v>
       </c>
       <c r="AP106">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ106">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR106">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AS106">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AT106">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AU106">
         <v>11</v>
@@ -23284,25 +23284,25 @@
         <v>1.55</v>
       </c>
       <c r="AN107">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="AO107">
-        <v>1.38</v>
+        <v>0.71</v>
       </c>
       <c r="AP107">
+        <v>1.71</v>
+      </c>
+      <c r="AQ107">
         <v>1.36</v>
       </c>
-      <c r="AQ107">
-        <v>1.61</v>
-      </c>
       <c r="AR107">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AS107">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AT107">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AU107">
         <v>4</v>
@@ -23490,25 +23490,25 @@
         <v>1.97</v>
       </c>
       <c r="AN108">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AO108">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AQ108">
         <v>0.93</v>
       </c>
       <c r="AR108">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AS108">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AT108">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="AU108">
         <v>0</v>
@@ -23696,25 +23696,25 @@
         <v>2</v>
       </c>
       <c r="AN109">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AO109">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AP109">
         <v>1.86</v>
       </c>
       <c r="AQ109">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="AR109">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AS109">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AT109">
-        <v>3.21</v>
+        <v>3.51</v>
       </c>
       <c r="AU109">
         <v>7</v>
@@ -23902,25 +23902,25 @@
         <v>1.32</v>
       </c>
       <c r="AN110">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO110">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AP110">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ110">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AR110">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="AS110">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AT110">
-        <v>2.7</v>
+        <v>3.09</v>
       </c>
       <c r="AU110">
         <v>3</v>
@@ -24108,25 +24108,25 @@
         <v>1.34</v>
       </c>
       <c r="AN111">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AO111">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AP111">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AR111">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AS111">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AT111">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="AU111">
         <v>5</v>
@@ -24314,25 +24314,25 @@
         <v>1.08</v>
       </c>
       <c r="AN112">
-        <v>0.93</v>
+        <v>1.33</v>
       </c>
       <c r="AO112">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AP112">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ112">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AR112">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AS112">
-        <v>1.74</v>
+        <v>1.49</v>
       </c>
       <c r="AT112">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="AU112">
         <v>3</v>
@@ -24520,25 +24520,25 @@
         <v>1.8</v>
       </c>
       <c r="AN113">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AO113">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AP113">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AQ113">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR113">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AS113">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AT113">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AU113">
         <v>5</v>
@@ -24726,25 +24726,25 @@
         <v>1.8</v>
       </c>
       <c r="AN114">
-        <v>1.5</v>
+        <v>2.17</v>
       </c>
       <c r="AO114">
+        <v>1</v>
+      </c>
+      <c r="AP114">
+        <v>1.86</v>
+      </c>
+      <c r="AQ114">
         <v>1.29</v>
       </c>
-      <c r="AP114">
-        <v>1.61</v>
-      </c>
-      <c r="AQ114">
-        <v>1.18</v>
-      </c>
       <c r="AR114">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AS114">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AT114">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="AU114">
         <v>4</v>
@@ -24932,25 +24932,25 @@
         <v>1.42</v>
       </c>
       <c r="AN115">
-        <v>1.21</v>
+        <v>1.86</v>
       </c>
       <c r="AO115">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AP115">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AQ115">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR115">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AS115">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AT115">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AU115">
         <v>7</v>
@@ -25138,25 +25138,25 @@
         <v>1.9</v>
       </c>
       <c r="AN116">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="AO116">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AQ116">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR116">
+        <v>1.34</v>
+      </c>
+      <c r="AS116">
         <v>1.3</v>
       </c>
-      <c r="AS116">
-        <v>1.46</v>
-      </c>
       <c r="AT116">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AU116">
         <v>4</v>
@@ -25344,25 +25344,25 @@
         <v>1.62</v>
       </c>
       <c r="AN117">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO117">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AQ117">
         <v>1.86</v>
       </c>
       <c r="AR117">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AS117">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="AT117">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AU117">
         <v>4</v>
@@ -25550,25 +25550,25 @@
         <v>1.5</v>
       </c>
       <c r="AN118">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="AO118">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="AP118">
         <v>0.93</v>
       </c>
       <c r="AQ118">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="AR118">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AS118">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AT118">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25756,25 +25756,25 @@
         <v>2.2</v>
       </c>
       <c r="AN119">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AO119">
-        <v>0.93</v>
+        <v>0.17</v>
       </c>
       <c r="AP119">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AQ119">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR119">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AS119">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AT119">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="AU119">
         <v>5</v>
@@ -25962,25 +25962,25 @@
         <v>1.76</v>
       </c>
       <c r="AN120">
+        <v>1.5</v>
+      </c>
+      <c r="AO120">
+        <v>0.63</v>
+      </c>
+      <c r="AP120">
+        <v>1.14</v>
+      </c>
+      <c r="AQ120">
+        <v>0.64</v>
+      </c>
+      <c r="AR120">
         <v>1.36</v>
       </c>
-      <c r="AO120">
-        <v>0.86</v>
-      </c>
-      <c r="AP120">
-        <v>1.04</v>
-      </c>
-      <c r="AQ120">
-        <v>0.89</v>
-      </c>
-      <c r="AR120">
-        <v>1.32</v>
-      </c>
       <c r="AS120">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AT120">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -26168,25 +26168,25 @@
         <v>1.36</v>
       </c>
       <c r="AN121">
-        <v>1.6</v>
+        <v>2.29</v>
       </c>
       <c r="AO121">
+        <v>1.8</v>
+      </c>
+      <c r="AP121">
+        <v>1.86</v>
+      </c>
+      <c r="AQ121">
         <v>1.64</v>
       </c>
-      <c r="AP121">
-        <v>1.61</v>
-      </c>
-      <c r="AQ121">
-        <v>1.79</v>
-      </c>
       <c r="AR121">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AS121">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="AT121">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="AU121">
         <v>5</v>
@@ -26374,25 +26374,25 @@
         <v>1.36</v>
       </c>
       <c r="AN122">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO122">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AQ122">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR122">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AS122">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AT122">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="AU122">
         <v>3</v>
@@ -26580,25 +26580,25 @@
         <v>2.2</v>
       </c>
       <c r="AN123">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="AO123">
-        <v>0.87</v>
+        <v>0.14</v>
       </c>
       <c r="AP123">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AQ123">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR123">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AS123">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AT123">
-        <v>3.01</v>
+        <v>3.27</v>
       </c>
       <c r="AU123">
         <v>8</v>
@@ -26786,25 +26786,25 @@
         <v>1.99</v>
       </c>
       <c r="AN124">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AO124">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AP124">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AQ124">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR124">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AS124">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AT124">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AU124">
         <v>13</v>
@@ -26992,25 +26992,25 @@
         <v>1.44</v>
       </c>
       <c r="AN125">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AO125">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="AP125">
         <v>0.93</v>
       </c>
       <c r="AQ125">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR125">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AS125">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AT125">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -27198,25 +27198,25 @@
         <v>1.41</v>
       </c>
       <c r="AN126">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO126">
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AQ126">
         <v>1.86</v>
       </c>
       <c r="AR126">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS126">
-        <v>1.77</v>
+        <v>1.38</v>
       </c>
       <c r="AT126">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27404,25 +27404,25 @@
         <v>1.36</v>
       </c>
       <c r="AN127">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="AO127">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AP127">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR127">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AS127">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AT127">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27610,25 +27610,25 @@
         <v>1.33</v>
       </c>
       <c r="AN128">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AO128">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AQ128">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AR128">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS128">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="AT128">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="AU128">
         <v>3</v>
@@ -27816,25 +27816,25 @@
         <v>1.17</v>
       </c>
       <c r="AN129">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AO129">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ129">
         <v>1.86</v>
       </c>
       <c r="AR129">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="AS129">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="AT129">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="AU129">
         <v>5</v>
@@ -28025,22 +28025,22 @@
         <v>1.38</v>
       </c>
       <c r="AO130">
-        <v>0.8100000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="AP130">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AQ130">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR130">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AS130">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AT130">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="AU130">
         <v>6</v>
@@ -28228,25 +28228,25 @@
         <v>1.56</v>
       </c>
       <c r="AN131">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AO131">
         <v>1.25</v>
       </c>
       <c r="AP131">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AQ131">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR131">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AS131">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AT131">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="AU131">
         <v>0</v>
@@ -28434,25 +28434,25 @@
         <v>1.28</v>
       </c>
       <c r="AN132">
-        <v>0.8100000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="AO132">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AP132">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ132">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AR132">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AS132">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AT132">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="AU132">
         <v>5</v>
@@ -28640,25 +28640,25 @@
         <v>1.7</v>
       </c>
       <c r="AN133">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AO133">
+        <v>1.25</v>
+      </c>
+      <c r="AP133">
+        <v>1.93</v>
+      </c>
+      <c r="AQ133">
+        <v>1.14</v>
+      </c>
+      <c r="AR133">
+        <v>1.85</v>
+      </c>
+      <c r="AS133">
         <v>1.44</v>
       </c>
-      <c r="AP133">
-        <v>1.79</v>
-      </c>
-      <c r="AQ133">
-        <v>1.61</v>
-      </c>
-      <c r="AR133">
-        <v>1.6</v>
-      </c>
-      <c r="AS133">
-        <v>1.49</v>
-      </c>
       <c r="AT133">
-        <v>3.09</v>
+        <v>3.29</v>
       </c>
       <c r="AU133">
         <v>3</v>
@@ -28849,7 +28849,7 @@
         <v>1.5</v>
       </c>
       <c r="AO134">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AP134">
         <v>1.86</v>
@@ -28858,13 +28858,13 @@
         <v>0.93</v>
       </c>
       <c r="AR134">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="AS134">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AT134">
-        <v>3.09</v>
+        <v>3.33</v>
       </c>
       <c r="AU134">
         <v>8</v>
@@ -29052,25 +29052,25 @@
         <v>1.62</v>
       </c>
       <c r="AN135">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO135">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AP135">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ135">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR135">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AS135">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AT135">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AU135">
         <v>4</v>
@@ -29258,25 +29258,25 @@
         <v>1.46</v>
       </c>
       <c r="AN136">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AO136">
-        <v>1.25</v>
+        <v>0.57</v>
       </c>
       <c r="AP136">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ136">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR136">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AS136">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AT136">
-        <v>2.89</v>
+        <v>3.17</v>
       </c>
       <c r="AU136">
         <v>4</v>
@@ -29464,25 +29464,25 @@
         <v>1.25</v>
       </c>
       <c r="AN137">
+        <v>1.5</v>
+      </c>
+      <c r="AO137">
         <v>1.13</v>
       </c>
-      <c r="AO137">
-        <v>1.56</v>
-      </c>
       <c r="AP137">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ137">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AR137">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AS137">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AT137">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AU137">
         <v>6</v>
@@ -29670,25 +29670,25 @@
         <v>1.34</v>
       </c>
       <c r="AN138">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AO138">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="AP138">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ138">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR138">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AS138">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT138">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="AU138">
         <v>4</v>
@@ -29876,25 +29876,25 @@
         <v>1.72</v>
       </c>
       <c r="AN139">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AO139">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AP139">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AQ139">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR139">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AS139">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AT139">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="AU139">
         <v>6</v>
@@ -30082,25 +30082,25 @@
         <v>1.37</v>
       </c>
       <c r="AN140">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AO140">
-        <v>0.9399999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="AP140">
         <v>0.93</v>
       </c>
       <c r="AQ140">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR140">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AS140">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AT140">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="AU140">
         <v>7</v>
@@ -30288,25 +30288,25 @@
         <v>1.42</v>
       </c>
       <c r="AN141">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AO141">
-        <v>1.24</v>
+        <v>0.63</v>
       </c>
       <c r="AP141">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ141">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR141">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AS141">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AT141">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AU141">
         <v>7</v>
@@ -30494,25 +30494,25 @@
         <v>1.47</v>
       </c>
       <c r="AN142">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="AO142">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AP142">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ142">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR142">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AS142">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AT142">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AU142">
         <v>4</v>
@@ -30700,25 +30700,25 @@
         <v>1.42</v>
       </c>
       <c r="AN143">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AO143">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AP143">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AQ143">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AR143">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AS143">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="AT143">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="AU143">
         <v>6</v>
@@ -30906,25 +30906,25 @@
         <v>1.83</v>
       </c>
       <c r="AN144">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AO144">
-        <v>1.06</v>
+        <v>0.75</v>
       </c>
       <c r="AP144">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AQ144">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR144">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AS144">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AT144">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="AU144">
         <v>8</v>
@@ -31112,25 +31112,25 @@
         <v>1.21</v>
       </c>
       <c r="AN145">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AO145">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AQ145">
         <v>1.86</v>
       </c>
       <c r="AR145">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AS145">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="AT145">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AU145">
         <v>4</v>
@@ -31318,25 +31318,25 @@
         <v>1.41</v>
       </c>
       <c r="AN146">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AO146">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AP146">
+        <v>1.71</v>
+      </c>
+      <c r="AQ146">
+        <v>1.14</v>
+      </c>
+      <c r="AR146">
+        <v>1.46</v>
+      </c>
+      <c r="AS146">
         <v>1.43</v>
       </c>
-      <c r="AQ146">
-        <v>1.61</v>
-      </c>
-      <c r="AR146">
-        <v>1.49</v>
-      </c>
-      <c r="AS146">
-        <v>1.49</v>
-      </c>
       <c r="AT146">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="AU146">
         <v>5</v>
@@ -31524,25 +31524,25 @@
         <v>1.32</v>
       </c>
       <c r="AN147">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO147">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AP147">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ147">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR147">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AS147">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AT147">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AU147">
         <v>4</v>
@@ -31730,25 +31730,25 @@
         <v>1.27</v>
       </c>
       <c r="AN148">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AO148">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AP148">
+        <v>1.57</v>
+      </c>
+      <c r="AQ148">
+        <v>1.43</v>
+      </c>
+      <c r="AR148">
         <v>1.32</v>
       </c>
-      <c r="AQ148">
-        <v>1.75</v>
-      </c>
-      <c r="AR148">
-        <v>1.35</v>
-      </c>
       <c r="AS148">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT148">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="AU148">
         <v>4</v>
@@ -31936,25 +31936,25 @@
         <v>1.64</v>
       </c>
       <c r="AN149">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO149">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP149">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ149">
         <v>0.93</v>
       </c>
       <c r="AR149">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AS149">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AT149">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="AU149">
         <v>7</v>
@@ -32142,25 +32142,25 @@
         <v>1.42</v>
       </c>
       <c r="AN150">
-        <v>1.17</v>
+        <v>1.78</v>
       </c>
       <c r="AO150">
-        <v>1.17</v>
+        <v>0.89</v>
       </c>
       <c r="AP150">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AQ150">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR150">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AS150">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT150">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="AU150">
         <v>5</v>
@@ -32351,22 +32351,22 @@
         <v>1.67</v>
       </c>
       <c r="AO151">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP151">
         <v>1.86</v>
       </c>
       <c r="AQ151">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="AR151">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AS151">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AT151">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="AU151">
         <v>9</v>
@@ -32554,25 +32554,25 @@
         <v>1.38</v>
       </c>
       <c r="AN152">
-        <v>1.06</v>
+        <v>1.67</v>
       </c>
       <c r="AO152">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AP152">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ152">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR152">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AS152">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AT152">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="AU152">
         <v>5</v>
@@ -32760,25 +32760,25 @@
         <v>1.35</v>
       </c>
       <c r="AN153">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AO153">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AP153">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AQ153">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AR153">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AS153">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="AT153">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="AU153">
         <v>6</v>
@@ -32966,25 +32966,25 @@
         <v>1.44</v>
       </c>
       <c r="AN154">
-        <v>0.95</v>
+        <v>1.33</v>
       </c>
       <c r="AO154">
-        <v>1.16</v>
+        <v>0.44</v>
       </c>
       <c r="AP154">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ154">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR154">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="AS154">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AT154">
-        <v>2.67</v>
+        <v>2.99</v>
       </c>
       <c r="AU154">
         <v>5</v>
@@ -33172,25 +33172,25 @@
         <v>1.78</v>
       </c>
       <c r="AN155">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AO155">
-        <v>1.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP155">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ155">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR155">
         <v>1.16</v>
       </c>
       <c r="AS155">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AT155">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AU155">
         <v>8</v>
@@ -33378,25 +33378,25 @@
         <v>1.66</v>
       </c>
       <c r="AN156">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AO156">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AQ156">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR156">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AS156">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AT156">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="AU156">
         <v>4</v>
@@ -33584,25 +33584,25 @@
         <v>1.68</v>
       </c>
       <c r="AN157">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AO157">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AP157">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AQ157">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR157">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AS157">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AT157">
-        <v>3.16</v>
+        <v>3.31</v>
       </c>
       <c r="AU157">
         <v>7</v>
@@ -33790,25 +33790,25 @@
         <v>1.65</v>
       </c>
       <c r="AN158">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AO158">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AP158">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AQ158">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR158">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AS158">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AT158">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="AU158">
         <v>7</v>
@@ -33996,25 +33996,25 @@
         <v>1.17</v>
       </c>
       <c r="AN159">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AO159">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AP159">
         <v>0.93</v>
       </c>
       <c r="AQ159">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AR159">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AS159">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AT159">
-        <v>2.91</v>
+        <v>2.68</v>
       </c>
       <c r="AU159">
         <v>3</v>
@@ -34202,25 +34202,25 @@
         <v>1.27</v>
       </c>
       <c r="AN160">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="AO160">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AP160">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AQ160">
         <v>1.86</v>
       </c>
       <c r="AR160">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AS160">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="AT160">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="AU160">
         <v>7</v>
@@ -34408,25 +34408,25 @@
         <v>2.29</v>
       </c>
       <c r="AN161">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AO161">
-        <v>0.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP161">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AQ161">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR161">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AS161">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AT161">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AU161">
         <v>6</v>
@@ -34614,25 +34614,25 @@
         <v>1.43</v>
       </c>
       <c r="AN162">
+        <v>1.7</v>
+      </c>
+      <c r="AO162">
+        <v>1.6</v>
+      </c>
+      <c r="AP162">
+        <v>1.71</v>
+      </c>
+      <c r="AQ162">
+        <v>1.5</v>
+      </c>
+      <c r="AR162">
         <v>1.45</v>
       </c>
-      <c r="AO162">
-        <v>1.8</v>
-      </c>
-      <c r="AP162">
-        <v>1.43</v>
-      </c>
-      <c r="AQ162">
-        <v>1.82</v>
-      </c>
-      <c r="AR162">
-        <v>1.47</v>
-      </c>
       <c r="AS162">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT162">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="AU162">
         <v>0</v>
@@ -34820,25 +34820,25 @@
         <v>1.55</v>
       </c>
       <c r="AN163">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AO163">
-        <v>1.15</v>
+        <v>0.9</v>
       </c>
       <c r="AP163">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ163">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR163">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AS163">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AT163">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="AU163">
         <v>3</v>
@@ -35026,25 +35026,25 @@
         <v>1.16</v>
       </c>
       <c r="AN164">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="AO164">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AP164">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ164">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AR164">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AS164">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AT164">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="AU164">
         <v>5</v>
@@ -35232,25 +35232,25 @@
         <v>1.8</v>
       </c>
       <c r="AN165">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO165">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AP165">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ165">
         <v>0.93</v>
       </c>
       <c r="AR165">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AS165">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AT165">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AU165">
         <v>8</v>
@@ -35438,25 +35438,25 @@
         <v>1.94</v>
       </c>
       <c r="AN166">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO166">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AP166">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AQ166">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR166">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AS166">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AT166">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="AU166">
         <v>5</v>
@@ -35644,25 +35644,25 @@
         <v>1.37</v>
       </c>
       <c r="AN167">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AO167">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AP167">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ167">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="AR167">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AS167">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AT167">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AU167">
         <v>5</v>
@@ -35850,25 +35850,25 @@
         <v>1.59</v>
       </c>
       <c r="AN168">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AO168">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="AP168">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ168">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="AR168">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AS168">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AT168">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="AU168">
         <v>7</v>
@@ -36056,25 +36056,25 @@
         <v>1.19</v>
       </c>
       <c r="AN169">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="AO169">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AP169">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AQ169">
         <v>1.86</v>
       </c>
       <c r="AR169">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AS169">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AT169">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="AU169">
         <v>0</v>
@@ -36262,25 +36262,25 @@
         <v>1.3</v>
       </c>
       <c r="AN170">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="AO170">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AP170">
         <v>0.93</v>
       </c>
       <c r="AQ170">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR170">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS170">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AT170">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="AU170">
         <v>5</v>
@@ -36468,25 +36468,25 @@
         <v>2.34</v>
       </c>
       <c r="AN171">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AO171">
-        <v>1.24</v>
+        <v>0.7</v>
       </c>
       <c r="AP171">
         <v>1.86</v>
       </c>
       <c r="AQ171">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR171">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AS171">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AT171">
-        <v>3.08</v>
+        <v>3.37</v>
       </c>
       <c r="AU171">
         <v>9</v>
@@ -36674,25 +36674,25 @@
         <v>2.08</v>
       </c>
       <c r="AN172">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AO172">
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="AP172">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AQ172">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR172">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AS172">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AT172">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="AU172">
         <v>11</v>
@@ -36880,25 +36880,25 @@
         <v>1.42</v>
       </c>
       <c r="AN173">
+        <v>1.1</v>
+      </c>
+      <c r="AO173">
+        <v>1.3</v>
+      </c>
+      <c r="AP173">
         <v>1.14</v>
       </c>
-      <c r="AO173">
-        <v>1.48</v>
-      </c>
-      <c r="AP173">
-        <v>1.04</v>
-      </c>
       <c r="AQ173">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR173">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AS173">
         <v>1.33</v>
       </c>
       <c r="AT173">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="AU173">
         <v>2</v>
@@ -37086,25 +37086,25 @@
         <v>1.2</v>
       </c>
       <c r="AN174">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AO174">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AP174">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ174">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AR174">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AS174">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AT174">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="AU174">
         <v>8</v>
@@ -37292,25 +37292,25 @@
         <v>1.88</v>
       </c>
       <c r="AN175">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AO175">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AP175">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AQ175">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR175">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AS175">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AT175">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="AU175">
         <v>8</v>
@@ -37498,25 +37498,25 @@
         <v>1.62</v>
       </c>
       <c r="AN176">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AO176">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AQ176">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR176">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AS176">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AT176">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="AU176">
         <v>11</v>
@@ -37704,25 +37704,25 @@
         <v>2.11</v>
       </c>
       <c r="AN177">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AO177">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AP177">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AQ177">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR177">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AS177">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AT177">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="AU177">
         <v>8</v>
@@ -37910,25 +37910,25 @@
         <v>1.45</v>
       </c>
       <c r="AN178">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AO178">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AP178">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ178">
         <v>0.93</v>
       </c>
       <c r="AR178">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AS178">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AT178">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="AU178">
         <v>6</v>
@@ -38116,25 +38116,25 @@
         <v>1.43</v>
       </c>
       <c r="AN179">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AO179">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AP179">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ179">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AR179">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AS179">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AT179">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="AU179">
         <v>4</v>
@@ -38322,25 +38322,25 @@
         <v>1.47</v>
       </c>
       <c r="AN180">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="AO180">
-        <v>1.23</v>
+        <v>0.73</v>
       </c>
       <c r="AP180">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AQ180">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR180">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AS180">
         <v>1.24</v>
       </c>
       <c r="AT180">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AU180">
         <v>5</v>
@@ -38528,25 +38528,25 @@
         <v>1.47</v>
       </c>
       <c r="AN181">
+        <v>1.82</v>
+      </c>
+      <c r="AO181">
         <v>1.45</v>
       </c>
-      <c r="AO181">
-        <v>1.64</v>
-      </c>
       <c r="AP181">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AQ181">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AR181">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AS181">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AT181">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="AU181">
         <v>5</v>
@@ -38734,25 +38734,25 @@
         <v>1.95</v>
       </c>
       <c r="AN182">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AO182">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AP182">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AQ182">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR182">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AS182">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AT182">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="AU182">
         <v>8</v>
@@ -38940,25 +38940,25 @@
         <v>1.17</v>
       </c>
       <c r="AN183">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AO183">
         <v>1.73</v>
       </c>
       <c r="AP183">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ183">
         <v>1.86</v>
       </c>
       <c r="AR183">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AS183">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AT183">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="AU183">
         <v>3</v>
@@ -39146,25 +39146,25 @@
         <v>1.69</v>
       </c>
       <c r="AN184">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AO184">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AP184">
+        <v>1.57</v>
+      </c>
+      <c r="AQ184">
+        <v>0.64</v>
+      </c>
+      <c r="AR184">
         <v>1.32</v>
       </c>
-      <c r="AQ184">
-        <v>0.89</v>
-      </c>
-      <c r="AR184">
-        <v>1.33</v>
-      </c>
       <c r="AS184">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AT184">
-        <v>2.76</v>
+        <v>2.49</v>
       </c>
       <c r="AU184">
         <v>5</v>
@@ -39355,22 +39355,22 @@
         <v>1.64</v>
       </c>
       <c r="AO185">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AP185">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AQ185">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR185">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AS185">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AT185">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AU185">
         <v>11</v>
@@ -39558,25 +39558,25 @@
         <v>1.53</v>
       </c>
       <c r="AN186">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AO186">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP186">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ186">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR186">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AS186">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AT186">
-        <v>2.68</v>
+        <v>2.43</v>
       </c>
       <c r="AU186">
         <v>2</v>
@@ -39767,22 +39767,22 @@
         <v>1.09</v>
       </c>
       <c r="AO187">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AP187">
         <v>0.93</v>
       </c>
       <c r="AQ187">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR187">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AS187">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AT187">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="AU187">
         <v>4</v>
@@ -39970,25 +39970,25 @@
         <v>1.34</v>
       </c>
       <c r="AN188">
-        <v>0.83</v>
+        <v>1.18</v>
       </c>
       <c r="AO188">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AP188">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ188">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR188">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="AS188">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AT188">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AU188">
         <v>10</v>
@@ -40179,22 +40179,22 @@
         <v>1.09</v>
       </c>
       <c r="AO189">
-        <v>0.83</v>
+        <v>0.45</v>
       </c>
       <c r="AP189">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AQ189">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR189">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AS189">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AT189">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="AU189">
         <v>8</v>
@@ -40382,25 +40382,25 @@
         <v>1.45</v>
       </c>
       <c r="AN190">
-        <v>1.78</v>
+        <v>2.09</v>
       </c>
       <c r="AO190">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="AP190">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AQ190">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="AR190">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AS190">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AT190">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="AU190">
         <v>6</v>
@@ -40588,25 +40588,25 @@
         <v>2.55</v>
       </c>
       <c r="AN191">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AO191">
-        <v>0.96</v>
+        <v>0.45</v>
       </c>
       <c r="AP191">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AQ191">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR191">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AS191">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AT191">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU191">
         <v>8</v>
@@ -40794,25 +40794,25 @@
         <v>1.67</v>
       </c>
       <c r="AN192">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AO192">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AP192">
         <v>1.86</v>
       </c>
       <c r="AQ192">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AR192">
-        <v>1.84</v>
+        <v>2.13</v>
       </c>
       <c r="AS192">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="AT192">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="AU192">
         <v>4</v>
@@ -41000,25 +41000,25 @@
         <v>1.49</v>
       </c>
       <c r="AN193">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AO193">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AP193">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AQ193">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR193">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="AS193">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AT193">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AU193">
         <v>3</v>
@@ -41206,25 +41206,25 @@
         <v>1.47</v>
       </c>
       <c r="AN194">
-        <v>0.79</v>
+        <v>1.17</v>
       </c>
       <c r="AO194">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="AP194">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ194">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="AR194">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AS194">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AT194">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="AU194">
         <v>2</v>
@@ -41412,25 +41412,25 @@
         <v>2.43</v>
       </c>
       <c r="AN195">
-        <v>1.46</v>
+        <v>1.92</v>
       </c>
       <c r="AO195">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AP195">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AQ195">
         <v>0.93</v>
       </c>
       <c r="AR195">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AS195">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AT195">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="AU195">
         <v>12</v>
@@ -41618,25 +41618,25 @@
         <v>1.96</v>
       </c>
       <c r="AN196">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AO196">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AP196">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ196">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR196">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AS196">
         <v>1.36</v>
       </c>
       <c r="AT196">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AU196">
         <v>5</v>
@@ -41824,25 +41824,25 @@
         <v>2.09</v>
       </c>
       <c r="AN197">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AO197">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AP197">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AQ197">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR197">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AS197">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AT197">
-        <v>2.85</v>
+        <v>3.17</v>
       </c>
       <c r="AU197">
         <v>2</v>
@@ -42030,25 +42030,25 @@
         <v>1.56</v>
       </c>
       <c r="AN198">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AO198">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AP198">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AQ198">
+        <v>1.5</v>
+      </c>
+      <c r="AR198">
         <v>1.82</v>
       </c>
-      <c r="AR198">
-        <v>1.68</v>
-      </c>
       <c r="AS198">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AT198">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AU198">
         <v>6</v>
@@ -42236,25 +42236,25 @@
         <v>1.49</v>
       </c>
       <c r="AN199">
-        <v>0.92</v>
+        <v>1.42</v>
       </c>
       <c r="AO199">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP199">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AQ199">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR199">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AS199">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AT199">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="AU199">
         <v>2</v>
@@ -42442,25 +42442,25 @@
         <v>1.66</v>
       </c>
       <c r="AN200">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AO200">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="AP200">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AQ200">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR200">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AS200">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AT200">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AU200">
         <v>5</v>
@@ -42648,25 +42648,25 @@
         <v>1.21</v>
       </c>
       <c r="AN201">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AO201">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AP201">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ201">
         <v>1.86</v>
       </c>
       <c r="AR201">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AS201">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AT201">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="AU201">
         <v>0</v>
@@ -42854,25 +42854,25 @@
         <v>1.29</v>
       </c>
       <c r="AN202">
-        <v>0.92</v>
+        <v>1.17</v>
       </c>
       <c r="AO202">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AP202">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ202">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR202">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AS202">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AT202">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="AU202">
         <v>4</v>
@@ -43063,22 +43063,22 @@
         <v>1</v>
       </c>
       <c r="AO203">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AP203">
         <v>0.93</v>
       </c>
       <c r="AQ203">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AR203">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AS203">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AT203">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="AU203">
         <v>2</v>
@@ -43266,25 +43266,25 @@
         <v>0</v>
       </c>
       <c r="AN204">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AO204">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="AP204">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AQ204">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="AR204">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AS204">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AT204">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="AU204">
         <v>4</v>
@@ -43472,25 +43472,25 @@
         <v>1.58</v>
       </c>
       <c r="AN205">
+        <v>1.67</v>
+      </c>
+      <c r="AO205">
+        <v>1.17</v>
+      </c>
+      <c r="AP205">
+        <v>1.71</v>
+      </c>
+      <c r="AQ205">
+        <v>1.07</v>
+      </c>
+      <c r="AR205">
         <v>1.24</v>
       </c>
-      <c r="AO205">
-        <v>1.44</v>
-      </c>
-      <c r="AP205">
-        <v>1.36</v>
-      </c>
-      <c r="AQ205">
-        <v>1.32</v>
-      </c>
-      <c r="AR205">
-        <v>1.26</v>
-      </c>
       <c r="AS205">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AT205">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AU205">
         <v>3</v>
@@ -43678,25 +43678,25 @@
         <v>2.8</v>
       </c>
       <c r="AN206">
-        <v>1.76</v>
+        <v>2.17</v>
       </c>
       <c r="AO206">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="AP206">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AQ206">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR206">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AS206">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AT206">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AU206">
         <v>3</v>
@@ -43884,25 +43884,25 @@
         <v>2.15</v>
       </c>
       <c r="AN207">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AO207">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="AP207">
         <v>1.86</v>
       </c>
       <c r="AQ207">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR207">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AS207">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AT207">
-        <v>3.27</v>
+        <v>3.56</v>
       </c>
       <c r="AU207">
         <v>13</v>
@@ -44090,25 +44090,25 @@
         <v>1.9</v>
       </c>
       <c r="AN208">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="AO208">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="AP208">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AQ208">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR208">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AS208">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AT208">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AU208">
         <v>4</v>
@@ -44296,25 +44296,25 @@
         <v>1.23</v>
       </c>
       <c r="AN209">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AO209">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AP209">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ209">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AR209">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AS209">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AT209">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="AU209">
         <v>2</v>
@@ -44502,25 +44502,25 @@
         <v>1.63</v>
       </c>
       <c r="AN210">
+        <v>1.85</v>
+      </c>
+      <c r="AO210">
+        <v>0.85</v>
+      </c>
+      <c r="AP210">
+        <v>1.71</v>
+      </c>
+      <c r="AQ210">
+        <v>1</v>
+      </c>
+      <c r="AR210">
         <v>1.42</v>
       </c>
-      <c r="AO210">
-        <v>1.23</v>
-      </c>
-      <c r="AP210">
-        <v>1.43</v>
-      </c>
-      <c r="AQ210">
-        <v>1.36</v>
-      </c>
-      <c r="AR210">
-        <v>1.45</v>
-      </c>
       <c r="AS210">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AT210">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AU210">
         <v>5</v>
@@ -44708,25 +44708,25 @@
         <v>2.28</v>
       </c>
       <c r="AN211">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AO211">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AP211">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AQ211">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AR211">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AS211">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AT211">
-        <v>3.03</v>
+        <v>3.11</v>
       </c>
       <c r="AU211">
         <v>6</v>
@@ -44914,25 +44914,25 @@
         <v>1.66</v>
       </c>
       <c r="AN212">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AO212">
         <v>1.15</v>
       </c>
       <c r="AP212">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ212">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR212">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AS212">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AT212">
-        <v>2.71</v>
+        <v>2.52</v>
       </c>
       <c r="AU212">
         <v>4</v>
@@ -45120,25 +45120,25 @@
         <v>1.73</v>
       </c>
       <c r="AN213">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AO213">
-        <v>1.19</v>
+        <v>0.77</v>
       </c>
       <c r="AP213">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ213">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AR213">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AS213">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AT213">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="AU213">
         <v>6</v>
@@ -45326,25 +45326,25 @@
         <v>1.17</v>
       </c>
       <c r="AN214">
-        <v>0.88</v>
+        <v>1.31</v>
       </c>
       <c r="AO214">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AP214">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AQ214">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AR214">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AS214">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AT214">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="AU214">
         <v>7</v>
@@ -45532,25 +45532,25 @@
         <v>1.1</v>
       </c>
       <c r="AN215">
-        <v>0.73</v>
+        <v>1.08</v>
       </c>
       <c r="AO215">
         <v>1.77</v>
       </c>
       <c r="AP215">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ215">
         <v>1.86</v>
       </c>
       <c r="AR215">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AS215">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AT215">
-        <v>3.13</v>
+        <v>3.02</v>
       </c>
       <c r="AU215">
         <v>3</v>
@@ -45738,25 +45738,25 @@
         <v>2.6</v>
       </c>
       <c r="AN216">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="AO216">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AP216">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AQ216">
         <v>0.93</v>
       </c>
       <c r="AR216">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AS216">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AT216">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AU216">
         <v>8</v>
@@ -45944,25 +45944,25 @@
         <v>2.23</v>
       </c>
       <c r="AN217">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO217">
-        <v>0.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP217">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AQ217">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="AR217">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AS217">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AT217">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="AU217">
         <v>2</v>
@@ -46150,25 +46150,25 @@
         <v>2.07</v>
       </c>
       <c r="AN218">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AO218">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="AP218">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ218">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR218">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AS218">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AT218">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="AU218">
         <v>6</v>
@@ -46356,25 +46356,25 @@
         <v>1.3</v>
       </c>
       <c r="AN219">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AO219">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="AP219">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AQ219">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AR219">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AS219">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AT219">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="AU219">
         <v>0</v>
@@ -46562,25 +46562,25 @@
         <v>1.25</v>
       </c>
       <c r="AN220">
-        <v>0.89</v>
+        <v>1.15</v>
       </c>
       <c r="AO220">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AP220">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="AQ220">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AR220">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AS220">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AT220">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="AU220">
         <v>7</v>
@@ -46768,25 +46768,25 @@
         <v>2.4</v>
       </c>
       <c r="AN221">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AO221">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AP221">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AQ221">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR221">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AS221">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AT221">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="AU221">
         <v>8</v>
@@ -46974,25 +46974,25 @@
         <v>1.5</v>
       </c>
       <c r="AN222">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AO222">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
       <c r="AP222">
         <v>0.93</v>
       </c>
       <c r="AQ222">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="AR222">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AS222">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AT222">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AU222">
         <v>4</v>
@@ -47180,25 +47180,25 @@
         <v>1.99</v>
       </c>
       <c r="AN223">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AO223">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AP223">
         <v>1.86</v>
       </c>
       <c r="AQ223">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR223">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AS223">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AT223">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="AU223">
         <v>5</v>
@@ -47386,25 +47386,25 @@
         <v>1.43</v>
       </c>
       <c r="AN224">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AO224">
-        <v>1.37</v>
+        <v>1</v>
       </c>
       <c r="AP224">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ224">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AR224">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AS224">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AT224">
-        <v>2.85</v>
+        <v>3.03</v>
       </c>
       <c r="AU224">
         <v>5</v>
@@ -47592,25 +47592,25 @@
         <v>1.38</v>
       </c>
       <c r="AN225">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="AO225">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AP225">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AQ225">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="AR225">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AS225">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AT225">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="AU225">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="317">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1326,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP225"/>
+  <dimension ref="A1:BP227"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4">
         <v>0.5</v>
@@ -2899,7 +2899,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ8">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ11">
         <v>1.86</v>
@@ -3929,7 +3929,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ13">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ19">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR19">
         <v>1.85</v>
@@ -5574,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ21">
         <v>1.36</v>
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ31">
         <v>1.29</v>
@@ -8461,7 +8461,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ35">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR35">
         <v>1.45</v>
@@ -8870,7 +8870,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ37">
         <v>1.43</v>
@@ -9694,7 +9694,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ41">
         <v>1.07</v>
@@ -11139,7 +11139,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ48">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR48">
         <v>0.93</v>
@@ -11548,7 +11548,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ50">
         <v>0.93</v>
@@ -13611,7 +13611,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ60">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR60">
         <v>1.71</v>
@@ -14020,7 +14020,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ62">
         <v>0.36</v>
@@ -14432,7 +14432,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ64">
         <v>0.64</v>
@@ -14847,7 +14847,7 @@
         <v>1</v>
       </c>
       <c r="AQ66">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR66">
         <v>1.39</v>
@@ -16495,7 +16495,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ74">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR74">
         <v>1.37</v>
@@ -17522,7 +17522,7 @@
         <v>1.2</v>
       </c>
       <c r="AP79">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ79">
         <v>1.14</v>
@@ -18555,7 +18555,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ84">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR84">
         <v>1.43</v>
@@ -18964,7 +18964,7 @@
         <v>0.67</v>
       </c>
       <c r="AP86">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ86">
         <v>1.86</v>
@@ -19788,7 +19788,7 @@
         <v>1.71</v>
       </c>
       <c r="AP90">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ90">
         <v>1.5</v>
@@ -21233,7 +21233,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ97">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR97">
         <v>1.37</v>
@@ -21436,7 +21436,7 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ98">
         <v>1.29</v>
@@ -21645,7 +21645,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ99">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR99">
         <v>1.24</v>
@@ -24323,7 +24323,7 @@
         <v>1</v>
       </c>
       <c r="AQ112">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR112">
         <v>1.44</v>
@@ -24526,7 +24526,7 @@
         <v>1.33</v>
       </c>
       <c r="AP113">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ113">
         <v>1.07</v>
@@ -24941,7 +24941,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ115">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR115">
         <v>1.47</v>
@@ -25556,7 +25556,7 @@
         <v>0.71</v>
       </c>
       <c r="AP118">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ118">
         <v>0.64</v>
@@ -26177,7 +26177,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ121">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR121">
         <v>1.14</v>
@@ -26998,7 +26998,7 @@
         <v>0.57</v>
       </c>
       <c r="AP125">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ125">
         <v>0.93</v>
@@ -27619,7 +27619,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ128">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR128">
         <v>1.38</v>
@@ -28028,7 +28028,7 @@
         <v>0.63</v>
       </c>
       <c r="AP130">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ130">
         <v>0.36</v>
@@ -28237,7 +28237,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ131">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR131">
         <v>1.58</v>
@@ -30088,7 +30088,7 @@
         <v>0.13</v>
       </c>
       <c r="AP140">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ140">
         <v>1</v>
@@ -30709,7 +30709,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ143">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR143">
         <v>1.8</v>
@@ -31324,7 +31324,7 @@
         <v>1.22</v>
       </c>
       <c r="AP146">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ146">
         <v>1.14</v>
@@ -32563,7 +32563,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ152">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR152">
         <v>1.23</v>
@@ -32769,7 +32769,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ153">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -34002,10 +34002,10 @@
         <v>1.78</v>
       </c>
       <c r="AP159">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ159">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR159">
         <v>1.46</v>
@@ -34620,7 +34620,7 @@
         <v>1.6</v>
       </c>
       <c r="AP162">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ162">
         <v>1.5</v>
@@ -35447,7 +35447,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ166">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR166">
         <v>1.81</v>
@@ -36268,7 +36268,7 @@
         <v>1.2</v>
       </c>
       <c r="AP170">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ170">
         <v>1.14</v>
@@ -37095,7 +37095,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ174">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR174">
         <v>1.61</v>
@@ -38740,10 +38740,10 @@
         <v>1.18</v>
       </c>
       <c r="AP182">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ182">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR182">
         <v>1.35</v>
@@ -39770,7 +39770,7 @@
         <v>1.36</v>
       </c>
       <c r="AP187">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ187">
         <v>1.36</v>
@@ -40803,7 +40803,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ192">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR192">
         <v>2.13</v>
@@ -41627,7 +41627,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ196">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR196">
         <v>1.24</v>
@@ -42448,7 +42448,7 @@
         <v>0.83</v>
       </c>
       <c r="AP200">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ200">
         <v>0.93</v>
@@ -43066,7 +43066,7 @@
         <v>1.33</v>
       </c>
       <c r="AP203">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ203">
         <v>1.43</v>
@@ -44305,7 +44305,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ209">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR209">
         <v>1.6</v>
@@ -44508,7 +44508,7 @@
         <v>0.85</v>
       </c>
       <c r="AP210">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ210">
         <v>1</v>
@@ -44717,7 +44717,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ211">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR211">
         <v>1.81</v>
@@ -45335,7 +45335,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ214">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR214">
         <v>1.44</v>
@@ -46980,7 +46980,7 @@
         <v>0.46</v>
       </c>
       <c r="AP222">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ222">
         <v>0.5</v>
@@ -47677,6 +47677,418 @@
       </c>
       <c r="BP225">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7486712</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45716.5</v>
+      </c>
+      <c r="F226">
+        <v>29</v>
+      </c>
+      <c r="G226" t="s">
+        <v>79</v>
+      </c>
+      <c r="H226" t="s">
+        <v>85</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+      <c r="N226">
+        <v>1</v>
+      </c>
+      <c r="O226" t="s">
+        <v>86</v>
+      </c>
+      <c r="P226" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q226">
+        <v>3.75</v>
+      </c>
+      <c r="R226">
+        <v>1.88</v>
+      </c>
+      <c r="S226">
+        <v>3.25</v>
+      </c>
+      <c r="T226">
+        <v>1.6</v>
+      </c>
+      <c r="U226">
+        <v>2.22</v>
+      </c>
+      <c r="V226">
+        <v>3.74</v>
+      </c>
+      <c r="W226">
+        <v>1.22</v>
+      </c>
+      <c r="X226">
+        <v>9</v>
+      </c>
+      <c r="Y226">
+        <v>1.04</v>
+      </c>
+      <c r="Z226">
+        <v>2.63</v>
+      </c>
+      <c r="AA226">
+        <v>3.09</v>
+      </c>
+      <c r="AB226">
+        <v>2.73</v>
+      </c>
+      <c r="AC226">
+        <v>1.1</v>
+      </c>
+      <c r="AD226">
+        <v>6.4</v>
+      </c>
+      <c r="AE226">
+        <v>1.5</v>
+      </c>
+      <c r="AF226">
+        <v>2.3</v>
+      </c>
+      <c r="AG226">
+        <v>2.7</v>
+      </c>
+      <c r="AH226">
+        <v>1.41</v>
+      </c>
+      <c r="AI226">
+        <v>2.12</v>
+      </c>
+      <c r="AJ226">
+        <v>1.65</v>
+      </c>
+      <c r="AK226">
+        <v>1.48</v>
+      </c>
+      <c r="AL226">
+        <v>1.33</v>
+      </c>
+      <c r="AM226">
+        <v>1.38</v>
+      </c>
+      <c r="AN226">
+        <v>0.93</v>
+      </c>
+      <c r="AO226">
+        <v>0.93</v>
+      </c>
+      <c r="AP226">
+        <v>0.87</v>
+      </c>
+      <c r="AQ226">
+        <v>1.07</v>
+      </c>
+      <c r="AR226">
+        <v>1.38</v>
+      </c>
+      <c r="AS226">
+        <v>1.3</v>
+      </c>
+      <c r="AT226">
+        <v>2.68</v>
+      </c>
+      <c r="AU226">
+        <v>7</v>
+      </c>
+      <c r="AV226">
+        <v>4</v>
+      </c>
+      <c r="AW226">
+        <v>22</v>
+      </c>
+      <c r="AX226">
+        <v>9</v>
+      </c>
+      <c r="AY226">
+        <v>34</v>
+      </c>
+      <c r="AZ226">
+        <v>17</v>
+      </c>
+      <c r="BA226">
+        <v>10</v>
+      </c>
+      <c r="BB226">
+        <v>1</v>
+      </c>
+      <c r="BC226">
+        <v>11</v>
+      </c>
+      <c r="BD226">
+        <v>2.07</v>
+      </c>
+      <c r="BE226">
+        <v>6.25</v>
+      </c>
+      <c r="BF226">
+        <v>1.95</v>
+      </c>
+      <c r="BG226">
+        <v>1.52</v>
+      </c>
+      <c r="BH226">
+        <v>2.3</v>
+      </c>
+      <c r="BI226">
+        <v>1.86</v>
+      </c>
+      <c r="BJ226">
+        <v>1.8</v>
+      </c>
+      <c r="BK226">
+        <v>2.4</v>
+      </c>
+      <c r="BL226">
+        <v>1.48</v>
+      </c>
+      <c r="BM226">
+        <v>3.15</v>
+      </c>
+      <c r="BN226">
+        <v>1.29</v>
+      </c>
+      <c r="BO226">
+        <v>4.35</v>
+      </c>
+      <c r="BP226">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7486707</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45716.625</v>
+      </c>
+      <c r="F227">
+        <v>29</v>
+      </c>
+      <c r="G227" t="s">
+        <v>72</v>
+      </c>
+      <c r="H227" t="s">
+        <v>75</v>
+      </c>
+      <c r="I227">
+        <v>1</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227">
+        <v>1</v>
+      </c>
+      <c r="L227">
+        <v>1</v>
+      </c>
+      <c r="M227">
+        <v>1</v>
+      </c>
+      <c r="N227">
+        <v>2</v>
+      </c>
+      <c r="O227" t="s">
+        <v>156</v>
+      </c>
+      <c r="P227" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q227">
+        <v>3.75</v>
+      </c>
+      <c r="R227">
+        <v>2.06</v>
+      </c>
+      <c r="S227">
+        <v>2.8</v>
+      </c>
+      <c r="T227">
+        <v>1.46</v>
+      </c>
+      <c r="U227">
+        <v>2.55</v>
+      </c>
+      <c r="V227">
+        <v>2.99</v>
+      </c>
+      <c r="W227">
+        <v>1.35</v>
+      </c>
+      <c r="X227">
+        <v>7.2</v>
+      </c>
+      <c r="Y227">
+        <v>1.04</v>
+      </c>
+      <c r="Z227">
+        <v>3.17</v>
+      </c>
+      <c r="AA227">
+        <v>3.18</v>
+      </c>
+      <c r="AB227">
+        <v>2.27</v>
+      </c>
+      <c r="AC227">
+        <v>1.02</v>
+      </c>
+      <c r="AD227">
+        <v>8</v>
+      </c>
+      <c r="AE227">
+        <v>1.34</v>
+      </c>
+      <c r="AF227">
+        <v>3.1</v>
+      </c>
+      <c r="AG227">
+        <v>1.95</v>
+      </c>
+      <c r="AH227">
+        <v>1.7</v>
+      </c>
+      <c r="AI227">
+        <v>1.8</v>
+      </c>
+      <c r="AJ227">
+        <v>1.9</v>
+      </c>
+      <c r="AK227">
+        <v>1.58</v>
+      </c>
+      <c r="AL227">
+        <v>1.31</v>
+      </c>
+      <c r="AM227">
+        <v>1.33</v>
+      </c>
+      <c r="AN227">
+        <v>1.71</v>
+      </c>
+      <c r="AO227">
+        <v>1.64</v>
+      </c>
+      <c r="AP227">
+        <v>1.67</v>
+      </c>
+      <c r="AQ227">
+        <v>1.6</v>
+      </c>
+      <c r="AR227">
+        <v>1.44</v>
+      </c>
+      <c r="AS227">
+        <v>1.44</v>
+      </c>
+      <c r="AT227">
+        <v>2.88</v>
+      </c>
+      <c r="AU227">
+        <v>7</v>
+      </c>
+      <c r="AV227">
+        <v>7</v>
+      </c>
+      <c r="AW227">
+        <v>7</v>
+      </c>
+      <c r="AX227">
+        <v>14</v>
+      </c>
+      <c r="AY227">
+        <v>17</v>
+      </c>
+      <c r="AZ227">
+        <v>25</v>
+      </c>
+      <c r="BA227">
+        <v>5</v>
+      </c>
+      <c r="BB227">
+        <v>1</v>
+      </c>
+      <c r="BC227">
+        <v>6</v>
+      </c>
+      <c r="BD227">
+        <v>2.28</v>
+      </c>
+      <c r="BE227">
+        <v>6.25</v>
+      </c>
+      <c r="BF227">
+        <v>1.78</v>
+      </c>
+      <c r="BG227">
+        <v>1.42</v>
+      </c>
+      <c r="BH227">
+        <v>2.55</v>
+      </c>
+      <c r="BI227">
+        <v>1.72</v>
+      </c>
+      <c r="BJ227">
+        <v>1.95</v>
+      </c>
+      <c r="BK227">
+        <v>2.18</v>
+      </c>
+      <c r="BL227">
+        <v>1.58</v>
+      </c>
+      <c r="BM227">
+        <v>2.8</v>
+      </c>
+      <c r="BN227">
+        <v>1.36</v>
+      </c>
+      <c r="BO227">
+        <v>3.8</v>
+      </c>
+      <c r="BP227">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -966,6 +966,9 @@
   <si>
     <t>['8', '39', '69']</t>
   </si>
+  <si>
+    <t>['80']</t>
+  </si>
 </sst>
 </file>
 
@@ -1326,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP227"/>
+  <dimension ref="A1:BP229"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3311,7 +3314,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ10">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3720,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ12">
         <v>1.29</v>
@@ -4132,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -4753,7 +4756,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ17">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5783,7 +5786,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR22">
         <v>1.89</v>
@@ -7222,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ29">
         <v>1.07</v>
@@ -8049,7 +8052,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ33">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR33">
         <v>2.11</v>
@@ -8255,7 +8258,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ34">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR34">
         <v>1.21</v>
@@ -9900,7 +9903,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ42">
         <v>0.36</v>
@@ -10724,7 +10727,7 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>1.14</v>
@@ -11963,7 +11966,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ52">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR52">
         <v>1.69</v>
@@ -12581,7 +12584,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ55">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR55">
         <v>1.71</v>
@@ -13196,7 +13199,7 @@
         <v>1.25</v>
       </c>
       <c r="AP58">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ58">
         <v>1.14</v>
@@ -14226,7 +14229,7 @@
         <v>0.75</v>
       </c>
       <c r="AP63">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ63">
         <v>1.36</v>
@@ -14435,7 +14438,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ64">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -15053,7 +15056,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ67">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR67">
         <v>0.97</v>
@@ -17110,7 +17113,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
         <v>1.43</v>
@@ -17937,7 +17940,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ81">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR81">
         <v>1.21</v>
@@ -18761,7 +18764,7 @@
         <v>1</v>
       </c>
       <c r="AQ85">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -19170,7 +19173,7 @@
         <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ87">
         <v>0.93</v>
@@ -21230,7 +21233,7 @@
         <v>1.67</v>
       </c>
       <c r="AP97">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
         <v>1.07</v>
@@ -21848,10 +21851,10 @@
         <v>0.67</v>
       </c>
       <c r="AP100">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ100">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR100">
         <v>1.91</v>
@@ -22469,7 +22472,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ103">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR103">
         <v>1.37</v>
@@ -25144,10 +25147,10 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ116">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR116">
         <v>1.34</v>
@@ -25350,7 +25353,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ117">
         <v>1.86</v>
@@ -25559,7 +25562,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ118">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR118">
         <v>1.37</v>
@@ -25971,7 +25974,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ120">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR120">
         <v>1.36</v>
@@ -26586,7 +26589,7 @@
         <v>0.14</v>
       </c>
       <c r="AP123">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ123">
         <v>1</v>
@@ -27001,7 +27004,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ125">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR125">
         <v>1.4</v>
@@ -27204,7 +27207,7 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ126">
         <v>1.86</v>
@@ -29679,7 +29682,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ138">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR138">
         <v>1.66</v>
@@ -30706,7 +30709,7 @@
         <v>1.86</v>
       </c>
       <c r="AP143">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ143">
         <v>1.6</v>
@@ -30912,7 +30915,7 @@
         <v>0.75</v>
       </c>
       <c r="AP144">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ144">
         <v>1.29</v>
@@ -32151,7 +32154,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ150">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR150">
         <v>1.49</v>
@@ -32357,7 +32360,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ151">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR151">
         <v>2.01</v>
@@ -32766,7 +32769,7 @@
         <v>2</v>
       </c>
       <c r="AP153">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ153">
         <v>1.6</v>
@@ -33590,7 +33593,7 @@
         <v>1.33</v>
       </c>
       <c r="AP157">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ157">
         <v>1.14</v>
@@ -33796,7 +33799,7 @@
         <v>1.44</v>
       </c>
       <c r="AP158">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ158">
         <v>1.07</v>
@@ -34829,7 +34832,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ163">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR163">
         <v>1.24</v>
@@ -35859,7 +35862,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ168">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR168">
         <v>1.63</v>
@@ -36680,7 +36683,7 @@
         <v>0.5</v>
       </c>
       <c r="AP172">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ172">
         <v>0.36</v>
@@ -37298,7 +37301,7 @@
         <v>1.4</v>
       </c>
       <c r="AP175">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ175">
         <v>1.36</v>
@@ -39155,7 +39158,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ184">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR184">
         <v>1.32</v>
@@ -39361,7 +39364,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ185">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR185">
         <v>1.75</v>
@@ -40388,7 +40391,7 @@
         <v>1.09</v>
       </c>
       <c r="AP190">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ190">
         <v>1.14</v>
@@ -40594,7 +40597,7 @@
         <v>0.45</v>
       </c>
       <c r="AP191">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ191">
         <v>0.5</v>
@@ -41215,7 +41218,7 @@
         <v>1</v>
       </c>
       <c r="AQ194">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR194">
         <v>1.47</v>
@@ -42036,7 +42039,7 @@
         <v>1.5</v>
       </c>
       <c r="AP198">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ198">
         <v>1.5</v>
@@ -42451,7 +42454,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ200">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR200">
         <v>1.39</v>
@@ -43684,7 +43687,7 @@
         <v>0.42</v>
       </c>
       <c r="AP206">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ206">
         <v>0.5</v>
@@ -44714,7 +44717,7 @@
         <v>1</v>
       </c>
       <c r="AP211">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ211">
         <v>1.07</v>
@@ -45129,7 +45132,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ213">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR213">
         <v>1.24</v>
@@ -45744,7 +45747,7 @@
         <v>1</v>
       </c>
       <c r="AP216">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ216">
         <v>0.93</v>
@@ -45953,7 +45956,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ217">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR217">
         <v>1.78</v>
@@ -48089,6 +48092,418 @@
       </c>
       <c r="BP227">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7486995</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45717.45833333334</v>
+      </c>
+      <c r="F228">
+        <v>29</v>
+      </c>
+      <c r="G228" t="s">
+        <v>82</v>
+      </c>
+      <c r="H228" t="s">
+        <v>76</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>0</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+      <c r="M228">
+        <v>1</v>
+      </c>
+      <c r="N228">
+        <v>1</v>
+      </c>
+      <c r="O228" t="s">
+        <v>86</v>
+      </c>
+      <c r="P228" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q228">
+        <v>2.24</v>
+      </c>
+      <c r="R228">
+        <v>2.05</v>
+      </c>
+      <c r="S228">
+        <v>5.85</v>
+      </c>
+      <c r="T228">
+        <v>1.45</v>
+      </c>
+      <c r="U228">
+        <v>2.59</v>
+      </c>
+      <c r="V228">
+        <v>3.22</v>
+      </c>
+      <c r="W228">
+        <v>1.31</v>
+      </c>
+      <c r="X228">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y228">
+        <v>1.01</v>
+      </c>
+      <c r="Z228">
+        <v>1.62</v>
+      </c>
+      <c r="AA228">
+        <v>3.75</v>
+      </c>
+      <c r="AB228">
+        <v>5.4</v>
+      </c>
+      <c r="AC228">
+        <v>1.01</v>
+      </c>
+      <c r="AD228">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE228">
+        <v>1.34</v>
+      </c>
+      <c r="AF228">
+        <v>2.79</v>
+      </c>
+      <c r="AG228">
+        <v>2.15</v>
+      </c>
+      <c r="AH228">
+        <v>1.57</v>
+      </c>
+      <c r="AI228">
+        <v>2.11</v>
+      </c>
+      <c r="AJ228">
+        <v>1.65</v>
+      </c>
+      <c r="AK228">
+        <v>1.14</v>
+      </c>
+      <c r="AL228">
+        <v>1.25</v>
+      </c>
+      <c r="AM228">
+        <v>2.12</v>
+      </c>
+      <c r="AN228">
+        <v>2.14</v>
+      </c>
+      <c r="AO228">
+        <v>0.64</v>
+      </c>
+      <c r="AP228">
+        <v>2</v>
+      </c>
+      <c r="AQ228">
+        <v>0.8</v>
+      </c>
+      <c r="AR228">
+        <v>1.64</v>
+      </c>
+      <c r="AS228">
+        <v>1.26</v>
+      </c>
+      <c r="AT228">
+        <v>2.9</v>
+      </c>
+      <c r="AU228">
+        <v>3</v>
+      </c>
+      <c r="AV228">
+        <v>2</v>
+      </c>
+      <c r="AW228">
+        <v>12</v>
+      </c>
+      <c r="AX228">
+        <v>5</v>
+      </c>
+      <c r="AY228">
+        <v>19</v>
+      </c>
+      <c r="AZ228">
+        <v>9</v>
+      </c>
+      <c r="BA228">
+        <v>9</v>
+      </c>
+      <c r="BB228">
+        <v>6</v>
+      </c>
+      <c r="BC228">
+        <v>15</v>
+      </c>
+      <c r="BD228">
+        <v>1.5</v>
+      </c>
+      <c r="BE228">
+        <v>6.5</v>
+      </c>
+      <c r="BF228">
+        <v>2.9</v>
+      </c>
+      <c r="BG228">
+        <v>1.47</v>
+      </c>
+      <c r="BH228">
+        <v>2.43</v>
+      </c>
+      <c r="BI228">
+        <v>1.78</v>
+      </c>
+      <c r="BJ228">
+        <v>1.88</v>
+      </c>
+      <c r="BK228">
+        <v>2.28</v>
+      </c>
+      <c r="BL228">
+        <v>1.53</v>
+      </c>
+      <c r="BM228">
+        <v>2.95</v>
+      </c>
+      <c r="BN228">
+        <v>1.33</v>
+      </c>
+      <c r="BO228">
+        <v>3.95</v>
+      </c>
+      <c r="BP228">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7486711</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45717.58333333334</v>
+      </c>
+      <c r="F229">
+        <v>29</v>
+      </c>
+      <c r="G229" t="s">
+        <v>80</v>
+      </c>
+      <c r="H229" t="s">
+        <v>70</v>
+      </c>
+      <c r="I229">
+        <v>1</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>1</v>
+      </c>
+      <c r="L229">
+        <v>1</v>
+      </c>
+      <c r="M229">
+        <v>0</v>
+      </c>
+      <c r="N229">
+        <v>1</v>
+      </c>
+      <c r="O229" t="s">
+        <v>152</v>
+      </c>
+      <c r="P229" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q229">
+        <v>1.93</v>
+      </c>
+      <c r="R229">
+        <v>2.42</v>
+      </c>
+      <c r="S229">
+        <v>6</v>
+      </c>
+      <c r="T229">
+        <v>1.33</v>
+      </c>
+      <c r="U229">
+        <v>3.15</v>
+      </c>
+      <c r="V229">
+        <v>2.4</v>
+      </c>
+      <c r="W229">
+        <v>1.51</v>
+      </c>
+      <c r="X229">
+        <v>5.8</v>
+      </c>
+      <c r="Y229">
+        <v>1.09</v>
+      </c>
+      <c r="Z229">
+        <v>1.57</v>
+      </c>
+      <c r="AA229">
+        <v>3.64</v>
+      </c>
+      <c r="AB229">
+        <v>6.3</v>
+      </c>
+      <c r="AC229">
+        <v>1.01</v>
+      </c>
+      <c r="AD229">
+        <v>11</v>
+      </c>
+      <c r="AE229">
+        <v>1.22</v>
+      </c>
+      <c r="AF229">
+        <v>3.95</v>
+      </c>
+      <c r="AG229">
+        <v>1.95</v>
+      </c>
+      <c r="AH229">
+        <v>1.79</v>
+      </c>
+      <c r="AI229">
+        <v>1.81</v>
+      </c>
+      <c r="AJ229">
+        <v>1.88</v>
+      </c>
+      <c r="AK229">
+        <v>1.12</v>
+      </c>
+      <c r="AL229">
+        <v>1.19</v>
+      </c>
+      <c r="AM229">
+        <v>2.43</v>
+      </c>
+      <c r="AN229">
+        <v>2.07</v>
+      </c>
+      <c r="AO229">
+        <v>0.93</v>
+      </c>
+      <c r="AP229">
+        <v>2.13</v>
+      </c>
+      <c r="AQ229">
+        <v>0.87</v>
+      </c>
+      <c r="AR229">
+        <v>1.81</v>
+      </c>
+      <c r="AS229">
+        <v>1.27</v>
+      </c>
+      <c r="AT229">
+        <v>3.08</v>
+      </c>
+      <c r="AU229">
+        <v>6</v>
+      </c>
+      <c r="AV229">
+        <v>0</v>
+      </c>
+      <c r="AW229">
+        <v>13</v>
+      </c>
+      <c r="AX229">
+        <v>3</v>
+      </c>
+      <c r="AY229">
+        <v>27</v>
+      </c>
+      <c r="AZ229">
+        <v>3</v>
+      </c>
+      <c r="BA229">
+        <v>9</v>
+      </c>
+      <c r="BB229">
+        <v>3</v>
+      </c>
+      <c r="BC229">
+        <v>12</v>
+      </c>
+      <c r="BD229">
+        <v>1.38</v>
+      </c>
+      <c r="BE229">
+        <v>7</v>
+      </c>
+      <c r="BF229">
+        <v>3.4</v>
+      </c>
+      <c r="BG229">
+        <v>1.4</v>
+      </c>
+      <c r="BH229">
+        <v>2.65</v>
+      </c>
+      <c r="BI229">
+        <v>1.68</v>
+      </c>
+      <c r="BJ229">
+        <v>2.02</v>
+      </c>
+      <c r="BK229">
+        <v>2.08</v>
+      </c>
+      <c r="BL229">
+        <v>1.63</v>
+      </c>
+      <c r="BM229">
+        <v>2.65</v>
+      </c>
+      <c r="BN229">
+        <v>1.4</v>
+      </c>
+      <c r="BO229">
+        <v>3.55</v>
+      </c>
+      <c r="BP229">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -688,6 +688,9 @@
     <t>['59']</t>
   </si>
   <si>
+    <t>['45+3']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -740,9 +743,6 @@
   </si>
   <si>
     <t>['5', '43']</t>
-  </si>
-  <si>
-    <t>['45+3']</t>
   </si>
   <si>
     <t>['13']</t>
@@ -1329,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP229"/>
+  <dimension ref="A1:BP230"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1585,7 +1585,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -2615,7 +2615,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2821,7 +2821,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3311,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ10">
         <v>0.8</v>
@@ -3439,7 +3439,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3645,7 +3645,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3851,7 +3851,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -4057,7 +4057,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4263,7 +4263,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4344,7 +4344,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ15">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4469,7 +4469,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4881,7 +4881,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -5087,7 +5087,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5293,7 +5293,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5371,7 +5371,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ20">
         <v>0.36</v>
@@ -5705,7 +5705,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5911,7 +5911,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -7228,7 +7228,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ29">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>2.09</v>
@@ -7353,7 +7353,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7559,7 +7559,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7765,7 +7765,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7971,7 +7971,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8177,7 +8177,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -9491,7 +9491,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ40">
         <v>1.36</v>
@@ -9700,7 +9700,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ41">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR41">
         <v>1.24</v>
@@ -11345,7 +11345,7 @@
         <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ49">
         <v>1.14</v>
@@ -13408,7 +13408,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ59">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR59">
         <v>1.8</v>
@@ -15259,7 +15259,7 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ68">
         <v>1.43</v>
@@ -16704,7 +16704,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ75">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR75">
         <v>2.05</v>
@@ -18143,7 +18143,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ82">
         <v>1.5</v>
@@ -19382,7 +19382,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ88">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>1.66</v>
@@ -22263,7 +22263,7 @@
         <v>1.17</v>
       </c>
       <c r="AP102">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ102">
         <v>0.93</v>
@@ -24532,7 +24532,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ113">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR113">
         <v>1.54</v>
@@ -24941,7 +24941,7 @@
         <v>1.43</v>
       </c>
       <c r="AP115">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ115">
         <v>1.07</v>
@@ -26383,7 +26383,7 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ122">
         <v>1.14</v>
@@ -27416,7 +27416,7 @@
         <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR127">
         <v>1.4</v>
@@ -29888,7 +29888,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ139">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR139">
         <v>1.55</v>
@@ -31661,7 +31661,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -32151,7 +32151,7 @@
         <v>0.89</v>
       </c>
       <c r="AP150">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ150">
         <v>0.87</v>
@@ -33802,7 +33802,7 @@
         <v>2</v>
       </c>
       <c r="AQ158">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR158">
         <v>1.5</v>
@@ -36065,7 +36065,7 @@
         <v>1.6</v>
       </c>
       <c r="AP169">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ169">
         <v>1.86</v>
@@ -36892,7 +36892,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ173">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR173">
         <v>1.4</v>
@@ -38331,7 +38331,7 @@
         <v>0.73</v>
       </c>
       <c r="AP180">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ180">
         <v>1</v>
@@ -41012,7 +41012,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ193">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR193">
         <v>1.72</v>
@@ -42245,7 +42245,7 @@
         <v>1</v>
       </c>
       <c r="AP199">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ199">
         <v>1.29</v>
@@ -43484,7 +43484,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ205">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR205">
         <v>1.24</v>
@@ -45335,7 +45335,7 @@
         <v>1.69</v>
       </c>
       <c r="AP214">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ214">
         <v>1.6</v>
@@ -46780,7 +46780,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ221">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR221">
         <v>1.82</v>
@@ -48504,6 +48504,212 @@
       </c>
       <c r="BP229">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7486713</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45718.41666666666</v>
+      </c>
+      <c r="F230">
+        <v>29</v>
+      </c>
+      <c r="G230" t="s">
+        <v>78</v>
+      </c>
+      <c r="H230" t="s">
+        <v>77</v>
+      </c>
+      <c r="I230">
+        <v>1</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>1</v>
+      </c>
+      <c r="L230">
+        <v>1</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
+      </c>
+      <c r="N230">
+        <v>1</v>
+      </c>
+      <c r="O230" t="s">
+        <v>224</v>
+      </c>
+      <c r="P230" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q230">
+        <v>3.75</v>
+      </c>
+      <c r="R230">
+        <v>1.91</v>
+      </c>
+      <c r="S230">
+        <v>3.4</v>
+      </c>
+      <c r="T230">
+        <v>1.57</v>
+      </c>
+      <c r="U230">
+        <v>2.25</v>
+      </c>
+      <c r="V230">
+        <v>3.75</v>
+      </c>
+      <c r="W230">
+        <v>1.25</v>
+      </c>
+      <c r="X230">
+        <v>13</v>
+      </c>
+      <c r="Y230">
+        <v>1.04</v>
+      </c>
+      <c r="Z230">
+        <v>3</v>
+      </c>
+      <c r="AA230">
+        <v>2.8</v>
+      </c>
+      <c r="AB230">
+        <v>2.45</v>
+      </c>
+      <c r="AC230">
+        <v>1.1</v>
+      </c>
+      <c r="AD230">
+        <v>6.4</v>
+      </c>
+      <c r="AE230">
+        <v>1.5</v>
+      </c>
+      <c r="AF230">
+        <v>2.4</v>
+      </c>
+      <c r="AG230">
+        <v>2.37</v>
+      </c>
+      <c r="AH230">
+        <v>1.48</v>
+      </c>
+      <c r="AI230">
+        <v>2.1</v>
+      </c>
+      <c r="AJ230">
+        <v>1.67</v>
+      </c>
+      <c r="AK230">
+        <v>1.49</v>
+      </c>
+      <c r="AL230">
+        <v>1.35</v>
+      </c>
+      <c r="AM230">
+        <v>1.36</v>
+      </c>
+      <c r="AN230">
+        <v>1.29</v>
+      </c>
+      <c r="AO230">
+        <v>1.07</v>
+      </c>
+      <c r="AP230">
+        <v>1.4</v>
+      </c>
+      <c r="AQ230">
+        <v>1</v>
+      </c>
+      <c r="AR230">
+        <v>1.44</v>
+      </c>
+      <c r="AS230">
+        <v>1.31</v>
+      </c>
+      <c r="AT230">
+        <v>2.75</v>
+      </c>
+      <c r="AU230">
+        <v>-1</v>
+      </c>
+      <c r="AV230">
+        <v>-1</v>
+      </c>
+      <c r="AW230">
+        <v>-1</v>
+      </c>
+      <c r="AX230">
+        <v>-1</v>
+      </c>
+      <c r="AY230">
+        <v>-1</v>
+      </c>
+      <c r="AZ230">
+        <v>-1</v>
+      </c>
+      <c r="BA230">
+        <v>-1</v>
+      </c>
+      <c r="BB230">
+        <v>-1</v>
+      </c>
+      <c r="BC230">
+        <v>-1</v>
+      </c>
+      <c r="BD230">
+        <v>2.17</v>
+      </c>
+      <c r="BE230">
+        <v>5.8</v>
+      </c>
+      <c r="BF230">
+        <v>1.88</v>
+      </c>
+      <c r="BG230">
+        <v>1.55</v>
+      </c>
+      <c r="BH230">
+        <v>2.25</v>
+      </c>
+      <c r="BI230">
+        <v>1.91</v>
+      </c>
+      <c r="BJ230">
+        <v>1.76</v>
+      </c>
+      <c r="BK230">
+        <v>2.48</v>
+      </c>
+      <c r="BL230">
+        <v>1.45</v>
+      </c>
+      <c r="BM230">
+        <v>3.3</v>
+      </c>
+      <c r="BN230">
+        <v>1.27</v>
+      </c>
+      <c r="BO230">
+        <v>4.35</v>
+      </c>
+      <c r="BP230">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -48646,31 +48646,31 @@
         <v>2.75</v>
       </c>
       <c r="AU230">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV230">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AW230">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AX230">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AY230">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AZ230">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="BA230">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB230">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC230">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD230">
         <v>2.17</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1329,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP230"/>
+  <dimension ref="A1:BP231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1663,10 +1663,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ2">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ3">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2075,10 +2075,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ5">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2487,10 +2487,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2693,10 +2693,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AQ7">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2899,10 +2899,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ8">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3105,10 +3105,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AQ9">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3311,19 +3311,19 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ10">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AU10">
         <v>6</v>
@@ -3511,25 +3511,25 @@
         <v>1.13</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP11">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AQ11">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AU11">
         <v>5</v>
@@ -3717,25 +3717,25 @@
         <v>2.1</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP12">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ12">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AU12">
         <v>9</v>
@@ -3923,25 +3923,25 @@
         <v>1.4</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP13">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ13">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU13">
         <v>8</v>
@@ -4129,25 +4129,25 @@
         <v>1.72</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AU14">
         <v>7</v>
@@ -4338,22 +4338,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP15">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AU15">
         <v>5</v>
@@ -4541,25 +4541,25 @@
         <v>1.3</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ16">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AU16">
         <v>7</v>
@@ -4747,25 +4747,25 @@
         <v>1.55</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AQ17">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AU17">
         <v>3</v>
@@ -4953,25 +4953,25 @@
         <v>1.8</v>
       </c>
       <c r="AN18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP18">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ18">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR18">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="AS18">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="AT18">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AU18">
         <v>2</v>
@@ -5162,22 +5162,22 @@
         <v>1</v>
       </c>
       <c r="AO19">
+        <v>2</v>
+      </c>
+      <c r="AP19">
+        <v>1.83</v>
+      </c>
+      <c r="AQ19">
+        <v>1.1</v>
+      </c>
+      <c r="AR19">
+        <v>1.51</v>
+      </c>
+      <c r="AS19">
+        <v>1.49</v>
+      </c>
+      <c r="AT19">
         <v>3</v>
-      </c>
-      <c r="AP19">
-        <v>1.86</v>
-      </c>
-      <c r="AQ19">
-        <v>1.07</v>
-      </c>
-      <c r="AR19">
-        <v>1.85</v>
-      </c>
-      <c r="AS19">
-        <v>1.69</v>
-      </c>
-      <c r="AT19">
-        <v>3.54</v>
       </c>
       <c r="AU19">
         <v>8</v>
@@ -5365,25 +5365,25 @@
         <v>1.6</v>
       </c>
       <c r="AN20">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO20">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP20">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ20">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR20">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AS20">
-        <v>0.71</v>
+        <v>1.19</v>
       </c>
       <c r="AT20">
-        <v>2.16</v>
+        <v>2.83</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5574,22 +5574,22 @@
         <v>3</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP21">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ21">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR21">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AS21">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AT21">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="AU21">
         <v>2</v>
@@ -5777,25 +5777,25 @@
         <v>2.35</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ22">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR22">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AS22">
-        <v>0.77</v>
+        <v>1.18</v>
       </c>
       <c r="AT22">
-        <v>2.66</v>
+        <v>2.97</v>
       </c>
       <c r="AU22">
         <v>2</v>
@@ -5983,25 +5983,25 @@
         <v>1.95</v>
       </c>
       <c r="AN23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP23">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AQ23">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AR23">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AS23">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AT23">
-        <v>4.23</v>
+        <v>3.77</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -6189,25 +6189,25 @@
         <v>1.36</v>
       </c>
       <c r="AN24">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AR24">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AS24">
-        <v>0.54</v>
+        <v>1.06</v>
       </c>
       <c r="AT24">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="AU24">
         <v>5</v>
@@ -6395,25 +6395,25 @@
         <v>1.26</v>
       </c>
       <c r="AN25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO25">
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AQ25">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR25">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="AS25">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AT25">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6601,25 +6601,25 @@
         <v>1.63</v>
       </c>
       <c r="AN26">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AP26">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR26">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AS26">
-        <v>0.91</v>
+        <v>1.11</v>
       </c>
       <c r="AT26">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AU26">
         <v>5</v>
@@ -6807,25 +6807,25 @@
         <v>1.75</v>
       </c>
       <c r="AN27">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO27">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AP27">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ27">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR27">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AS27">
-        <v>0.99</v>
+        <v>1.22</v>
       </c>
       <c r="AT27">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -7013,25 +7013,25 @@
         <v>2.25</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ28">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR28">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AS28">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AT28">
-        <v>3.56</v>
+        <v>3.31</v>
       </c>
       <c r="AU28">
         <v>6</v>
@@ -7219,25 +7219,25 @@
         <v>2.35</v>
       </c>
       <c r="AN29">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP29">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ29">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR29">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="AS29">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="AT29">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AU29">
         <v>0</v>
@@ -7425,25 +7425,25 @@
         <v>1.66</v>
       </c>
       <c r="AN30">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AO30">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP30">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AR30">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AS30">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="AT30">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="AU30">
         <v>7</v>
@@ -7631,25 +7631,25 @@
         <v>1.45</v>
       </c>
       <c r="AN31">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AP31">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AQ31">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR31">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AS31">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AT31">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="AU31">
         <v>3</v>
@@ -7837,25 +7837,25 @@
         <v>1.72</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO32">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AP32">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ32">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AR32">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AS32">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AT32">
-        <v>3.44</v>
+        <v>3.16</v>
       </c>
       <c r="AU32">
         <v>5</v>
@@ -8043,25 +8043,25 @@
         <v>2</v>
       </c>
       <c r="AN33">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO33">
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AQ33">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR33">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AS33">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AT33">
-        <v>3.79</v>
+        <v>3.46</v>
       </c>
       <c r="AU33">
         <v>9</v>
@@ -8249,25 +8249,25 @@
         <v>1.68</v>
       </c>
       <c r="AN34">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO34">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ34">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR34">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AS34">
-        <v>0.9</v>
+        <v>1.13</v>
       </c>
       <c r="AT34">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AU34">
         <v>3</v>
@@ -8455,25 +8455,25 @@
         <v>1.47</v>
       </c>
       <c r="AN35">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO35">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP35">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ35">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR35">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AS35">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT35">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="AU35">
         <v>8</v>
@@ -8661,25 +8661,25 @@
         <v>1.25</v>
       </c>
       <c r="AN36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO36">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ36">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR36">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AS36">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AT36">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="AU36">
         <v>4</v>
@@ -8873,19 +8873,19 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ37">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AR37">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AS37">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AT37">
-        <v>3.17</v>
+        <v>3.39</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -9076,22 +9076,22 @@
         <v>1</v>
       </c>
       <c r="AO38">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AP38">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AQ38">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR38">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AS38">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="AT38">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="AU38">
         <v>7</v>
@@ -9279,25 +9279,25 @@
         <v>1.34</v>
       </c>
       <c r="AN39">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AO39">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AQ39">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AR39">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="AS39">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AT39">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9485,25 +9485,25 @@
         <v>1.44</v>
       </c>
       <c r="AN40">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AO40">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP40">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ40">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR40">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AS40">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AT40">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AU40">
         <v>7</v>
@@ -9691,25 +9691,25 @@
         <v>1.57</v>
       </c>
       <c r="AN41">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO41">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="AP41">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR41">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AS41">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AT41">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AU41">
         <v>7</v>
@@ -9897,25 +9897,25 @@
         <v>2.35</v>
       </c>
       <c r="AN42">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AO42">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ42">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR42">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AS42">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AT42">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="AU42">
         <v>12</v>
@@ -10103,25 +10103,25 @@
         <v>1.7</v>
       </c>
       <c r="AN43">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AO43">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AP43">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ43">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR43">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="AS43">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="AT43">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AU43">
         <v>4</v>
@@ -10309,25 +10309,25 @@
         <v>2.6</v>
       </c>
       <c r="AN44">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AO44">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AP44">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AQ44">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR44">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="AS44">
         <v>1.49</v>
       </c>
       <c r="AT44">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="AU44">
         <v>3</v>
@@ -10515,25 +10515,25 @@
         <v>2</v>
       </c>
       <c r="AN45">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AO45">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="AP45">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ45">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR45">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AS45">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AT45">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="AU45">
         <v>4</v>
@@ -10721,25 +10721,25 @@
         <v>1.62</v>
       </c>
       <c r="AN46">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AO46">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ46">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AR46">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AS46">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AT46">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="AU46">
         <v>8</v>
@@ -10927,25 +10927,25 @@
         <v>2.02</v>
       </c>
       <c r="AN47">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AO47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR47">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS47">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AT47">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -11133,25 +11133,25 @@
         <v>1.45</v>
       </c>
       <c r="AN48">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO48">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AP48">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AQ48">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR48">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="AS48">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AT48">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -11339,25 +11339,25 @@
         <v>1.36</v>
       </c>
       <c r="AN49">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO49">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AP49">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ49">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR49">
+        <v>1.44</v>
+      </c>
+      <c r="AS49">
         <v>1.48</v>
       </c>
-      <c r="AS49">
-        <v>1.61</v>
-      </c>
       <c r="AT49">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="AU49">
         <v>9</v>
@@ -11548,22 +11548,22 @@
         <v>1.33</v>
       </c>
       <c r="AO50">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AP50">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ50">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR50">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AS50">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AT50">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11751,25 +11751,25 @@
         <v>1.4</v>
       </c>
       <c r="AN51">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO51">
         <v>2.33</v>
       </c>
       <c r="AP51">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ51">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AR51">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AS51">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="AT51">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="AU51">
         <v>3</v>
@@ -11957,25 +11957,25 @@
         <v>2.49</v>
       </c>
       <c r="AN52">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO52">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP52">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AQ52">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR52">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AS52">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AT52">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="AU52">
         <v>12</v>
@@ -12163,25 +12163,25 @@
         <v>1.2</v>
       </c>
       <c r="AN53">
-        <v>1.67</v>
+        <v>0.83</v>
       </c>
       <c r="AO53">
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ53">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR53">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AS53">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="AT53">
-        <v>2.36</v>
+        <v>3.01</v>
       </c>
       <c r="AU53">
         <v>6</v>
@@ -12369,25 +12369,25 @@
         <v>1.24</v>
       </c>
       <c r="AN54">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="AO54">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP54">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ54">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AR54">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AS54">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AT54">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="AU54">
         <v>4</v>
@@ -12578,19 +12578,19 @@
         <v>1</v>
       </c>
       <c r="AO55">
-        <v>0.5</v>
+        <v>1.17</v>
       </c>
       <c r="AP55">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ55">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR55">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="AS55">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="AT55">
         <v>3.05</v>
@@ -12784,22 +12784,22 @@
         <v>2</v>
       </c>
       <c r="AO56">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AP56">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AQ56">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AR56">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AS56">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AT56">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12987,25 +12987,25 @@
         <v>1.68</v>
       </c>
       <c r="AN57">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="AO57">
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ57">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR57">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AS57">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AT57">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AU57">
         <v>8</v>
@@ -13193,25 +13193,25 @@
         <v>1.68</v>
       </c>
       <c r="AN58">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO58">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AP58">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ58">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR58">
-        <v>2.03</v>
+        <v>1.74</v>
       </c>
       <c r="AS58">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AT58">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13399,25 +13399,25 @@
         <v>1.46</v>
       </c>
       <c r="AN59">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO59">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP59">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR59">
-        <v>1.8</v>
+        <v>1.18</v>
       </c>
       <c r="AS59">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AT59">
-        <v>3.1</v>
+        <v>2.29</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13605,25 +13605,25 @@
         <v>1.45</v>
       </c>
       <c r="AN60">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AO60">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP60">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ60">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR60">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AS60">
-        <v>1.23</v>
+        <v>1.78</v>
       </c>
       <c r="AT60">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13811,22 +13811,22 @@
         <v>2.6</v>
       </c>
       <c r="AN61">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AO61">
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AQ61">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR61">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="AS61">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AT61">
         <v>3.27</v>
@@ -14017,25 +14017,25 @@
         <v>1.71</v>
       </c>
       <c r="AN62">
-        <v>0.33</v>
+        <v>1.14</v>
       </c>
       <c r="AO62">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="AP62">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AQ62">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR62">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AS62">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AT62">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -14223,25 +14223,25 @@
         <v>1.94</v>
       </c>
       <c r="AN63">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="AO63">
-        <v>0.75</v>
+        <v>1.71</v>
       </c>
       <c r="AP63">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ63">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR63">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="AS63">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AT63">
-        <v>2.67</v>
+        <v>2.37</v>
       </c>
       <c r="AU63">
         <v>3</v>
@@ -14432,22 +14432,22 @@
         <v>1</v>
       </c>
       <c r="AO64">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="AP64">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ64">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR64">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AS64">
-        <v>0.88</v>
+        <v>1.26</v>
       </c>
       <c r="AT64">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14635,25 +14635,25 @@
         <v>1.95</v>
       </c>
       <c r="AN65">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO65">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AP65">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ65">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR65">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AS65">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AT65">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14841,25 +14841,25 @@
         <v>1.25</v>
       </c>
       <c r="AN66">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="AO66">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ66">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR66">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AS66">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AT66">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="AU66">
         <v>3</v>
@@ -15047,25 +15047,25 @@
         <v>1.4</v>
       </c>
       <c r="AN67">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AO67">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP67">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AQ67">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR67">
-        <v>0.97</v>
+        <v>1.18</v>
       </c>
       <c r="AS67">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AT67">
-        <v>2.47</v>
+        <v>2.78</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -15253,25 +15253,25 @@
         <v>1.25</v>
       </c>
       <c r="AN68">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO68">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AP68">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ68">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AR68">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AS68">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AT68">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="AU68">
         <v>6</v>
@@ -15459,25 +15459,25 @@
         <v>1.57</v>
       </c>
       <c r="AN69">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AO69">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="AP69">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AQ69">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR69">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AS69">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AT69">
-        <v>3.32</v>
+        <v>3.59</v>
       </c>
       <c r="AU69">
         <v>6</v>
@@ -15665,25 +15665,25 @@
         <v>1.5</v>
       </c>
       <c r="AN70">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO70">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AP70">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR70">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AS70">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AT70">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="AU70">
         <v>3</v>
@@ -15871,25 +15871,25 @@
         <v>1.78</v>
       </c>
       <c r="AN71">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AO71">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AP71">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AR71">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AS71">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AT71">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="AU71">
         <v>4</v>
@@ -16077,25 +16077,25 @@
         <v>1.8</v>
       </c>
       <c r="AN72">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO72">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP72">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ72">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR72">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="AS72">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AT72">
-        <v>2.91</v>
+        <v>2.57</v>
       </c>
       <c r="AU72">
         <v>8</v>
@@ -16283,25 +16283,25 @@
         <v>1.62</v>
       </c>
       <c r="AN73">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO73">
-        <v>0.6</v>
+        <v>1.67</v>
       </c>
       <c r="AP73">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AQ73">
+        <v>1.61</v>
+      </c>
+      <c r="AR73">
         <v>1.36</v>
       </c>
-      <c r="AR73">
-        <v>1.51</v>
-      </c>
       <c r="AS73">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AT73">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16489,25 +16489,25 @@
         <v>1.25</v>
       </c>
       <c r="AN74">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AO74">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP74">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ74">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR74">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AS74">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AT74">
-        <v>2.66</v>
+        <v>3.02</v>
       </c>
       <c r="AU74">
         <v>2</v>
@@ -16695,25 +16695,25 @@
         <v>2.45</v>
       </c>
       <c r="AN75">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AO75">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AP75">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR75">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AS75">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AT75">
-        <v>3.43</v>
+        <v>3.03</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16901,25 +16901,25 @@
         <v>1.62</v>
       </c>
       <c r="AN76">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AO76">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AP76">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ76">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AR76">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AS76">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AT76">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -17107,25 +17107,25 @@
         <v>1.53</v>
       </c>
       <c r="AN77">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO77">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ77">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AR77">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AS77">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AT77">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="AU77">
         <v>5</v>
@@ -17313,25 +17313,25 @@
         <v>1.71</v>
       </c>
       <c r="AN78">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AO78">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="AP78">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ78">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR78">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AS78">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AT78">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="AU78">
         <v>9</v>
@@ -17519,25 +17519,25 @@
         <v>1.22</v>
       </c>
       <c r="AN79">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AO79">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP79">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AQ79">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR79">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AS79">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AT79">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AU79">
         <v>3</v>
@@ -17725,25 +17725,25 @@
         <v>1.57</v>
       </c>
       <c r="AN80">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO80">
-        <v>0.25</v>
+        <v>1.3</v>
       </c>
       <c r="AP80">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AQ80">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR80">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AS80">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AT80">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AU80">
         <v>10</v>
@@ -17931,25 +17931,25 @@
         <v>1.9</v>
       </c>
       <c r="AN81">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="AO81">
-        <v>0.6</v>
+        <v>0.78</v>
       </c>
       <c r="AP81">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ81">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR81">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AS81">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AT81">
-        <v>2.29</v>
+        <v>2.58</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -18137,25 +18137,25 @@
         <v>1.3</v>
       </c>
       <c r="AN82">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AO82">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AP82">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ82">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AR82">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AS82">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AT82">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AU82">
         <v>2</v>
@@ -18346,22 +18346,22 @@
         <v>1.67</v>
       </c>
       <c r="AO83">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="AP83">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AQ83">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR83">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AS83">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AT83">
-        <v>2.98</v>
+        <v>3.21</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18549,25 +18549,25 @@
         <v>1.95</v>
       </c>
       <c r="AN84">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AO84">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AP84">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ84">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR84">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AS84">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AT84">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AU84">
         <v>2</v>
@@ -18755,25 +18755,25 @@
         <v>1.25</v>
       </c>
       <c r="AN85">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AO85">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AP85">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ85">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR85">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AS85">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AT85">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AU85">
         <v>5</v>
@@ -18961,25 +18961,25 @@
         <v>1.44</v>
       </c>
       <c r="AN86">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AO86">
-        <v>0.67</v>
+        <v>1.11</v>
       </c>
       <c r="AP86">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ86">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR86">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AS86">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AT86">
-        <v>2.99</v>
+        <v>3.39</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -19167,25 +19167,25 @@
         <v>2.9</v>
       </c>
       <c r="AN87">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AO87">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AP87">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ87">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR87">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="AS87">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AT87">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AU87">
         <v>8</v>
@@ -19373,25 +19373,25 @@
         <v>1.52</v>
       </c>
       <c r="AN88">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AO88">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AP88">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR88">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AS88">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT88">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU88">
         <v>5</v>
@@ -19579,22 +19579,22 @@
         <v>1.86</v>
       </c>
       <c r="AN89">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="AO89">
-        <v>0.67</v>
+        <v>1.55</v>
       </c>
       <c r="AP89">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ89">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR89">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AS89">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AT89">
         <v>2.69</v>
@@ -19785,25 +19785,25 @@
         <v>1.24</v>
       </c>
       <c r="AN90">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AO90">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AP90">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AQ90">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AR90">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS90">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AT90">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="AU90">
         <v>4</v>
@@ -19991,25 +19991,25 @@
         <v>2.7</v>
       </c>
       <c r="AN91">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AO91">
-        <v>0.8</v>
+        <v>1.27</v>
       </c>
       <c r="AP91">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AQ91">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR91">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AS91">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AT91">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20197,25 +20197,25 @@
         <v>1.37</v>
       </c>
       <c r="AN92">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AO92">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AP92">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AQ92">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AR92">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AS92">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AT92">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AU92">
         <v>3</v>
@@ -20403,25 +20403,25 @@
         <v>1.44</v>
       </c>
       <c r="AN93">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="AO93">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ93">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AR93">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AS93">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AT93">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AU93">
         <v>3</v>
@@ -20609,25 +20609,25 @@
         <v>1.29</v>
       </c>
       <c r="AN94">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AO94">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AP94">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ94">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR94">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AS94">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AT94">
-        <v>3.34</v>
+        <v>2.85</v>
       </c>
       <c r="AU94">
         <v>8</v>
@@ -20815,25 +20815,25 @@
         <v>3.15</v>
       </c>
       <c r="AN95">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AO95">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="AP95">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AQ95">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR95">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="AS95">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AT95">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="AU95">
         <v>9</v>
@@ -21021,25 +21021,25 @@
         <v>1.42</v>
       </c>
       <c r="AN96">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AO96">
-        <v>0.2</v>
+        <v>1.08</v>
       </c>
       <c r="AP96">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR96">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AS96">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AT96">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="AU96">
         <v>9</v>
@@ -21227,25 +21227,25 @@
         <v>1.78</v>
       </c>
       <c r="AN97">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="AO97">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ97">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR97">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AS97">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AT97">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AU97">
         <v>5</v>
@@ -21436,22 +21436,22 @@
         <v>1.17</v>
       </c>
       <c r="AO98">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ98">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR98">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AS98">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AT98">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21639,25 +21639,25 @@
         <v>1.15</v>
       </c>
       <c r="AN99">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO99">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AP99">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AQ99">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR99">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AS99">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AT99">
-        <v>2.86</v>
+        <v>3.07</v>
       </c>
       <c r="AU99">
         <v>0</v>
@@ -21845,25 +21845,25 @@
         <v>2.85</v>
       </c>
       <c r="AN100">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AO100">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP100">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ100">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR100">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AS100">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="AT100">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -22051,25 +22051,25 @@
         <v>1.2</v>
       </c>
       <c r="AN101">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO101">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AP101">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ101">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR101">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AS101">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="AT101">
-        <v>2.58</v>
+        <v>2.91</v>
       </c>
       <c r="AU101">
         <v>2</v>
@@ -22257,25 +22257,25 @@
         <v>1.87</v>
       </c>
       <c r="AN102">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AO102">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ102">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR102">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AS102">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AT102">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22463,25 +22463,25 @@
         <v>1.72</v>
       </c>
       <c r="AN103">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="AO103">
-        <v>0.6</v>
+        <v>1.08</v>
       </c>
       <c r="AP103">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ103">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR103">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AS103">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AT103">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="AU103">
         <v>8</v>
@@ -22669,25 +22669,25 @@
         <v>1.95</v>
       </c>
       <c r="AN104">
+        <v>1.58</v>
+      </c>
+      <c r="AO104">
+        <v>1.31</v>
+      </c>
+      <c r="AP104">
+        <v>1.76</v>
+      </c>
+      <c r="AQ104">
+        <v>1.41</v>
+      </c>
+      <c r="AR104">
+        <v>1.68</v>
+      </c>
+      <c r="AS104">
         <v>1.63</v>
       </c>
-      <c r="AO104">
-        <v>1.17</v>
-      </c>
-      <c r="AP104">
-        <v>1.93</v>
-      </c>
-      <c r="AQ104">
-        <v>1.14</v>
-      </c>
-      <c r="AR104">
-        <v>1.78</v>
-      </c>
-      <c r="AS104">
-        <v>1.74</v>
-      </c>
       <c r="AT104">
-        <v>3.52</v>
+        <v>3.31</v>
       </c>
       <c r="AU104">
         <v>9</v>
@@ -22875,25 +22875,25 @@
         <v>1.95</v>
       </c>
       <c r="AN105">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AO105">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AP105">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ105">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR105">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AS105">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AT105">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AU105">
         <v>6</v>
@@ -23081,25 +23081,25 @@
         <v>1.66</v>
       </c>
       <c r="AN106">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AO106">
-        <v>0.67</v>
+        <v>1.31</v>
       </c>
       <c r="AP106">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AQ106">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR106">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AS106">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AT106">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="AU106">
         <v>11</v>
@@ -23287,25 +23287,25 @@
         <v>1.55</v>
       </c>
       <c r="AN107">
-        <v>1.71</v>
+        <v>1</v>
       </c>
       <c r="AO107">
-        <v>0.71</v>
+        <v>1.38</v>
       </c>
       <c r="AP107">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ107">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR107">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AS107">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AT107">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AU107">
         <v>4</v>
@@ -23493,25 +23493,25 @@
         <v>1.97</v>
       </c>
       <c r="AN108">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AO108">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP108">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AQ108">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR108">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AS108">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AT108">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="AU108">
         <v>0</v>
@@ -23699,25 +23699,25 @@
         <v>2</v>
       </c>
       <c r="AN109">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AO109">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AP109">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AQ109">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR109">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AS109">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AT109">
-        <v>3.51</v>
+        <v>3.21</v>
       </c>
       <c r="AU109">
         <v>7</v>
@@ -23905,25 +23905,25 @@
         <v>1.32</v>
       </c>
       <c r="AN110">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO110">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AP110">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ110">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AR110">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="AS110">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AT110">
-        <v>3.09</v>
+        <v>2.7</v>
       </c>
       <c r="AU110">
         <v>3</v>
@@ -24111,25 +24111,25 @@
         <v>1.34</v>
       </c>
       <c r="AN111">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AO111">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AP111">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ111">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AR111">
+        <v>1.49</v>
+      </c>
+      <c r="AS111">
         <v>1.65</v>
       </c>
-      <c r="AS111">
-        <v>1.42</v>
-      </c>
       <c r="AT111">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="AU111">
         <v>5</v>
@@ -24317,25 +24317,25 @@
         <v>1.08</v>
       </c>
       <c r="AN112">
-        <v>1.33</v>
+        <v>0.93</v>
       </c>
       <c r="AO112">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AP112">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ112">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR112">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AS112">
-        <v>1.49</v>
+        <v>1.74</v>
       </c>
       <c r="AT112">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="AU112">
         <v>3</v>
@@ -24523,25 +24523,25 @@
         <v>1.8</v>
       </c>
       <c r="AN113">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AO113">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AP113">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ113">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR113">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AS113">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AT113">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AU113">
         <v>5</v>
@@ -24729,25 +24729,25 @@
         <v>1.8</v>
       </c>
       <c r="AN114">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="AO114">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AP114">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ114">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR114">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AS114">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AT114">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="AU114">
         <v>4</v>
@@ -24935,25 +24935,25 @@
         <v>1.42</v>
       </c>
       <c r="AN115">
-        <v>1.86</v>
+        <v>1.21</v>
       </c>
       <c r="AO115">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AP115">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ115">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR115">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AS115">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AT115">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AU115">
         <v>7</v>
@@ -25141,25 +25141,25 @@
         <v>1.9</v>
       </c>
       <c r="AN116">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="AO116">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ116">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR116">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AS116">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AT116">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AU116">
         <v>4</v>
@@ -25347,25 +25347,25 @@
         <v>1.62</v>
       </c>
       <c r="AN117">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO117">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AP117">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ117">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR117">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AS117">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="AT117">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AU117">
         <v>4</v>
@@ -25553,25 +25553,25 @@
         <v>1.5</v>
       </c>
       <c r="AN118">
-        <v>0.83</v>
+        <v>1.07</v>
       </c>
       <c r="AO118">
-        <v>0.71</v>
+        <v>0.92</v>
       </c>
       <c r="AP118">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AQ118">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR118">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AS118">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AT118">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25759,25 +25759,25 @@
         <v>2.2</v>
       </c>
       <c r="AN119">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AO119">
-        <v>0.17</v>
+        <v>0.93</v>
       </c>
       <c r="AP119">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ119">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR119">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AS119">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AT119">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="AU119">
         <v>5</v>
@@ -25965,25 +25965,25 @@
         <v>1.76</v>
       </c>
       <c r="AN120">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AO120">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="AP120">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AQ120">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR120">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AS120">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AT120">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -26171,25 +26171,25 @@
         <v>1.36</v>
       </c>
       <c r="AN121">
-        <v>2.29</v>
+        <v>1.6</v>
       </c>
       <c r="AO121">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AP121">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ121">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR121">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AS121">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AT121">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AU121">
         <v>5</v>
@@ -26377,25 +26377,25 @@
         <v>1.36</v>
       </c>
       <c r="AN122">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO122">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AP122">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ122">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AR122">
+        <v>1.49</v>
+      </c>
+      <c r="AS122">
         <v>1.54</v>
       </c>
-      <c r="AS122">
-        <v>1.62</v>
-      </c>
       <c r="AT122">
-        <v>3.16</v>
+        <v>3.03</v>
       </c>
       <c r="AU122">
         <v>3</v>
@@ -26583,25 +26583,25 @@
         <v>2.2</v>
       </c>
       <c r="AN123">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="AO123">
-        <v>0.14</v>
+        <v>0.87</v>
       </c>
       <c r="AP123">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ123">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR123">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AS123">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AT123">
-        <v>3.27</v>
+        <v>3.01</v>
       </c>
       <c r="AU123">
         <v>8</v>
@@ -26789,25 +26789,25 @@
         <v>1.99</v>
       </c>
       <c r="AN124">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AO124">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AP124">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ124">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR124">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AS124">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AT124">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AU124">
         <v>13</v>
@@ -26995,25 +26995,25 @@
         <v>1.44</v>
       </c>
       <c r="AN125">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AO125">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="AP125">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AQ125">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR125">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AS125">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AT125">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -27201,25 +27201,25 @@
         <v>1.41</v>
       </c>
       <c r="AN126">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO126">
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ126">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR126">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS126">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="AT126">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27407,25 +27407,25 @@
         <v>1.36</v>
       </c>
       <c r="AN127">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="AO127">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ127">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR127">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AS127">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AT127">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27613,25 +27613,25 @@
         <v>1.33</v>
       </c>
       <c r="AN128">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AO128">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AP128">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AQ128">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR128">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS128">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="AT128">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="AU128">
         <v>3</v>
@@ -27819,25 +27819,25 @@
         <v>1.17</v>
       </c>
       <c r="AN129">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AO129">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AP129">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ129">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR129">
-        <v>1.77</v>
+        <v>1.42</v>
       </c>
       <c r="AS129">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="AT129">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="AU129">
         <v>5</v>
@@ -28028,22 +28028,22 @@
         <v>1.38</v>
       </c>
       <c r="AO130">
-        <v>0.63</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP130">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ130">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR130">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AS130">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AT130">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="AU130">
         <v>6</v>
@@ -28231,25 +28231,25 @@
         <v>1.56</v>
       </c>
       <c r="AN131">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AO131">
         <v>1.25</v>
       </c>
       <c r="AP131">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ131">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR131">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AS131">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AT131">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="AU131">
         <v>0</v>
@@ -28437,25 +28437,25 @@
         <v>1.28</v>
       </c>
       <c r="AN132">
-        <v>1.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AO132">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AP132">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ132">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AR132">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AS132">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AT132">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="AU132">
         <v>5</v>
@@ -28643,25 +28643,25 @@
         <v>1.7</v>
       </c>
       <c r="AN133">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AO133">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AP133">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AQ133">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR133">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AS133">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AT133">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
       <c r="AU133">
         <v>3</v>
@@ -28852,22 +28852,22 @@
         <v>1.5</v>
       </c>
       <c r="AO134">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AP134">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AQ134">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR134">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AS134">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AT134">
-        <v>3.33</v>
+        <v>3.09</v>
       </c>
       <c r="AU134">
         <v>8</v>
@@ -29055,25 +29055,25 @@
         <v>1.62</v>
       </c>
       <c r="AN135">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AO135">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AP135">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AQ135">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR135">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AS135">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AT135">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AU135">
         <v>4</v>
@@ -29261,25 +29261,25 @@
         <v>1.46</v>
       </c>
       <c r="AN136">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AO136">
-        <v>0.57</v>
+        <v>1.25</v>
       </c>
       <c r="AP136">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ136">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR136">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AS136">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AT136">
-        <v>3.17</v>
+        <v>2.89</v>
       </c>
       <c r="AU136">
         <v>4</v>
@@ -29467,25 +29467,25 @@
         <v>1.25</v>
       </c>
       <c r="AN137">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AO137">
-        <v>1.13</v>
+        <v>1.56</v>
       </c>
       <c r="AP137">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ137">
+        <v>1.79</v>
+      </c>
+      <c r="AR137">
         <v>1.43</v>
       </c>
-      <c r="AR137">
-        <v>1.59</v>
-      </c>
       <c r="AS137">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AT137">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AU137">
         <v>6</v>
@@ -29673,25 +29673,25 @@
         <v>1.34</v>
       </c>
       <c r="AN138">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AO138">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="AP138">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ138">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR138">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="AS138">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AT138">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="AU138">
         <v>4</v>
@@ -29879,25 +29879,25 @@
         <v>1.72</v>
       </c>
       <c r="AN139">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AO139">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AP139">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ139">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR139">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AS139">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AT139">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="AU139">
         <v>6</v>
@@ -30085,25 +30085,25 @@
         <v>1.37</v>
       </c>
       <c r="AN140">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AO140">
-        <v>0.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP140">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AQ140">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR140">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AS140">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT140">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="AU140">
         <v>7</v>
@@ -30291,25 +30291,25 @@
         <v>1.42</v>
       </c>
       <c r="AN141">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AO141">
-        <v>0.63</v>
+        <v>1.24</v>
       </c>
       <c r="AP141">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ141">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR141">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AS141">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AT141">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="AU141">
         <v>7</v>
@@ -30497,25 +30497,25 @@
         <v>1.47</v>
       </c>
       <c r="AN142">
-        <v>2.13</v>
+        <v>1.65</v>
       </c>
       <c r="AO142">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AP142">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ142">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AR142">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AS142">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AT142">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AU142">
         <v>4</v>
@@ -30703,25 +30703,25 @@
         <v>1.42</v>
       </c>
       <c r="AN143">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AO143">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AP143">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ143">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR143">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AS143">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="AT143">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="AU143">
         <v>6</v>
@@ -30909,25 +30909,25 @@
         <v>1.83</v>
       </c>
       <c r="AN144">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AO144">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="AP144">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ144">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR144">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AS144">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AT144">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="AU144">
         <v>8</v>
@@ -31115,25 +31115,25 @@
         <v>1.21</v>
       </c>
       <c r="AN145">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AO145">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AP145">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AQ145">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR145">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AS145">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="AT145">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AU145">
         <v>4</v>
@@ -31321,25 +31321,25 @@
         <v>1.41</v>
       </c>
       <c r="AN146">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AO146">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AP146">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ146">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR146">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AS146">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AT146">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="AU146">
         <v>5</v>
@@ -31527,25 +31527,25 @@
         <v>1.32</v>
       </c>
       <c r="AN147">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AO147">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="AP147">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ147">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR147">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AS147">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AT147">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AU147">
         <v>4</v>
@@ -31733,25 +31733,25 @@
         <v>1.27</v>
       </c>
       <c r="AN148">
+        <v>1.5</v>
+      </c>
+      <c r="AO148">
         <v>1.56</v>
       </c>
-      <c r="AO148">
-        <v>1.33</v>
-      </c>
       <c r="AP148">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AQ148">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AR148">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AS148">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AT148">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="AU148">
         <v>4</v>
@@ -31939,25 +31939,25 @@
         <v>1.64</v>
       </c>
       <c r="AN149">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO149">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP149">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ149">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR149">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AS149">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AT149">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="AU149">
         <v>7</v>
@@ -32145,25 +32145,25 @@
         <v>1.42</v>
       </c>
       <c r="AN150">
-        <v>1.78</v>
+        <v>1.17</v>
       </c>
       <c r="AO150">
-        <v>0.89</v>
+        <v>1.17</v>
       </c>
       <c r="AP150">
+        <v>0.97</v>
+      </c>
+      <c r="AQ150">
+        <v>1.17</v>
+      </c>
+      <c r="AR150">
+        <v>1.45</v>
+      </c>
+      <c r="AS150">
         <v>1.4</v>
       </c>
-      <c r="AQ150">
-        <v>0.87</v>
-      </c>
-      <c r="AR150">
-        <v>1.49</v>
-      </c>
-      <c r="AS150">
-        <v>1.27</v>
-      </c>
       <c r="AT150">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="AU150">
         <v>5</v>
@@ -32354,22 +32354,22 @@
         <v>1.67</v>
       </c>
       <c r="AO151">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP151">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AQ151">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR151">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AS151">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AT151">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="AU151">
         <v>9</v>
@@ -32557,25 +32557,25 @@
         <v>1.38</v>
       </c>
       <c r="AN152">
-        <v>1.67</v>
+        <v>1.06</v>
       </c>
       <c r="AO152">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AP152">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ152">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR152">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AS152">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AT152">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="AU152">
         <v>5</v>
@@ -32763,25 +32763,25 @@
         <v>1.35</v>
       </c>
       <c r="AN153">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AO153">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AP153">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ153">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR153">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AS153">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AT153">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AU153">
         <v>6</v>
@@ -32969,25 +32969,25 @@
         <v>1.44</v>
       </c>
       <c r="AN154">
-        <v>1.33</v>
+        <v>0.95</v>
       </c>
       <c r="AO154">
-        <v>0.44</v>
+        <v>1.16</v>
       </c>
       <c r="AP154">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ154">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR154">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="AS154">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AT154">
-        <v>2.99</v>
+        <v>2.67</v>
       </c>
       <c r="AU154">
         <v>5</v>
@@ -33175,25 +33175,25 @@
         <v>1.78</v>
       </c>
       <c r="AN155">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AO155">
-        <v>0.5600000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="AP155">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ155">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR155">
         <v>1.16</v>
       </c>
       <c r="AS155">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AT155">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AU155">
         <v>8</v>
@@ -33381,25 +33381,25 @@
         <v>1.66</v>
       </c>
       <c r="AN156">
+        <v>1.21</v>
+      </c>
+      <c r="AO156">
         <v>1.11</v>
       </c>
-      <c r="AO156">
-        <v>1</v>
-      </c>
       <c r="AP156">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AQ156">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR156">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AS156">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="AT156">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="AU156">
         <v>4</v>
@@ -33587,25 +33587,25 @@
         <v>1.68</v>
       </c>
       <c r="AN157">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AO157">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AP157">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ157">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AR157">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AS157">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AT157">
-        <v>3.31</v>
+        <v>3.16</v>
       </c>
       <c r="AU157">
         <v>7</v>
@@ -33793,25 +33793,25 @@
         <v>1.65</v>
       </c>
       <c r="AN158">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AO158">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AP158">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ158">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR158">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AS158">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AT158">
-        <v>2.87</v>
+        <v>2.71</v>
       </c>
       <c r="AU158">
         <v>7</v>
@@ -33999,25 +33999,25 @@
         <v>1.17</v>
       </c>
       <c r="AN159">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AO159">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AP159">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AQ159">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR159">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AS159">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AT159">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="AU159">
         <v>3</v>
@@ -34205,25 +34205,25 @@
         <v>1.27</v>
       </c>
       <c r="AN160">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AO160">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AP160">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ160">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR160">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AS160">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AT160">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="AU160">
         <v>7</v>
@@ -34411,25 +34411,25 @@
         <v>2.29</v>
       </c>
       <c r="AN161">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AO161">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="AP161">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ161">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR161">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AS161">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AT161">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AU161">
         <v>6</v>
@@ -34617,25 +34617,25 @@
         <v>1.43</v>
       </c>
       <c r="AN162">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AO162">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AP162">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ162">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AR162">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AS162">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AT162">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AU162">
         <v>0</v>
@@ -34823,25 +34823,25 @@
         <v>1.55</v>
       </c>
       <c r="AN163">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AO163">
-        <v>0.9</v>
+        <v>1.15</v>
       </c>
       <c r="AP163">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ163">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR163">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AS163">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AT163">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="AU163">
         <v>3</v>
@@ -35029,25 +35029,25 @@
         <v>1.16</v>
       </c>
       <c r="AN164">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AO164">
+        <v>1.6</v>
+      </c>
+      <c r="AP164">
+        <v>0.68</v>
+      </c>
+      <c r="AQ164">
+        <v>1.79</v>
+      </c>
+      <c r="AR164">
         <v>1.3</v>
       </c>
-      <c r="AP164">
-        <v>1</v>
-      </c>
-      <c r="AQ164">
-        <v>1.43</v>
-      </c>
-      <c r="AR164">
-        <v>1.45</v>
-      </c>
       <c r="AS164">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AT164">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="AU164">
         <v>5</v>
@@ -35235,25 +35235,25 @@
         <v>1.8</v>
       </c>
       <c r="AN165">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO165">
+        <v>1.1</v>
+      </c>
+      <c r="AP165">
+        <v>1.28</v>
+      </c>
+      <c r="AQ165">
+        <v>0.9</v>
+      </c>
+      <c r="AR165">
         <v>1.3</v>
       </c>
-      <c r="AP165">
-        <v>1.57</v>
-      </c>
-      <c r="AQ165">
-        <v>0.93</v>
-      </c>
-      <c r="AR165">
-        <v>1.27</v>
-      </c>
       <c r="AS165">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AT165">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="AU165">
         <v>8</v>
@@ -35441,25 +35441,25 @@
         <v>1.94</v>
       </c>
       <c r="AN166">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AO166">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AP166">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AQ166">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR166">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AS166">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AT166">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU166">
         <v>5</v>
@@ -35647,25 +35647,25 @@
         <v>1.37</v>
       </c>
       <c r="AN167">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AO167">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AP167">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ167">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR167">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AS167">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AT167">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AU167">
         <v>5</v>
@@ -35853,25 +35853,25 @@
         <v>1.59</v>
       </c>
       <c r="AN168">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AO168">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AP168">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ168">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR168">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AS168">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AT168">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AU168">
         <v>7</v>
@@ -36059,25 +36059,25 @@
         <v>1.19</v>
       </c>
       <c r="AN169">
+        <v>1.1</v>
+      </c>
+      <c r="AO169">
         <v>1.7</v>
       </c>
-      <c r="AO169">
-        <v>1.6</v>
-      </c>
       <c r="AP169">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ169">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR169">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AS169">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AT169">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="AU169">
         <v>0</v>
@@ -36265,25 +36265,25 @@
         <v>1.3</v>
       </c>
       <c r="AN170">
+        <v>1.05</v>
+      </c>
+      <c r="AO170">
+        <v>1.43</v>
+      </c>
+      <c r="AP170">
         <v>0.9</v>
       </c>
-      <c r="AO170">
-        <v>1.2</v>
-      </c>
-      <c r="AP170">
-        <v>0.87</v>
-      </c>
       <c r="AQ170">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AR170">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS170">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AT170">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="AU170">
         <v>5</v>
@@ -36471,25 +36471,25 @@
         <v>2.34</v>
       </c>
       <c r="AN171">
+        <v>1.76</v>
+      </c>
+      <c r="AO171">
+        <v>1.24</v>
+      </c>
+      <c r="AP171">
+        <v>1.83</v>
+      </c>
+      <c r="AQ171">
+        <v>1.36</v>
+      </c>
+      <c r="AR171">
         <v>1.8</v>
       </c>
-      <c r="AO171">
-        <v>0.7</v>
-      </c>
-      <c r="AP171">
-        <v>1.86</v>
-      </c>
-      <c r="AQ171">
-        <v>1</v>
-      </c>
-      <c r="AR171">
-        <v>2.04</v>
-      </c>
       <c r="AS171">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AT171">
-        <v>3.37</v>
+        <v>3.08</v>
       </c>
       <c r="AU171">
         <v>9</v>
@@ -36677,25 +36677,25 @@
         <v>2.08</v>
       </c>
       <c r="AN172">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AO172">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AP172">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ172">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR172">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AS172">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AT172">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="AU172">
         <v>11</v>
@@ -36883,25 +36883,25 @@
         <v>1.42</v>
       </c>
       <c r="AN173">
+        <v>1.14</v>
+      </c>
+      <c r="AO173">
+        <v>1.48</v>
+      </c>
+      <c r="AP173">
         <v>1.1</v>
       </c>
-      <c r="AO173">
-        <v>1.3</v>
-      </c>
-      <c r="AP173">
-        <v>1.14</v>
-      </c>
       <c r="AQ173">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR173">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AS173">
         <v>1.33</v>
       </c>
       <c r="AT173">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="AU173">
         <v>2</v>
@@ -37089,25 +37089,25 @@
         <v>1.2</v>
       </c>
       <c r="AN174">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AO174">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AP174">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ174">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR174">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AS174">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AT174">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="AU174">
         <v>8</v>
@@ -37295,25 +37295,25 @@
         <v>1.88</v>
       </c>
       <c r="AN175">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AO175">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AP175">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ175">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR175">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AS175">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AT175">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="AU175">
         <v>8</v>
@@ -37501,25 +37501,25 @@
         <v>1.62</v>
       </c>
       <c r="AN176">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AO176">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AP176">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ176">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR176">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS176">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AT176">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="AU176">
         <v>11</v>
@@ -37707,25 +37707,25 @@
         <v>2.11</v>
       </c>
       <c r="AN177">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AO177">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="AP177">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ177">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR177">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AS177">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AT177">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="AU177">
         <v>8</v>
@@ -37913,25 +37913,25 @@
         <v>1.45</v>
       </c>
       <c r="AN178">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AO178">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AP178">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ178">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR178">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AS178">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AT178">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="AU178">
         <v>6</v>
@@ -38119,25 +38119,25 @@
         <v>1.43</v>
       </c>
       <c r="AN179">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AO179">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AP179">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ179">
+        <v>1.76</v>
+      </c>
+      <c r="AR179">
+        <v>1.19</v>
+      </c>
+      <c r="AS179">
         <v>1.5</v>
       </c>
-      <c r="AR179">
-        <v>1.24</v>
-      </c>
-      <c r="AS179">
-        <v>1.37</v>
-      </c>
       <c r="AT179">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="AU179">
         <v>4</v>
@@ -38325,25 +38325,25 @@
         <v>1.47</v>
       </c>
       <c r="AN180">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="AO180">
-        <v>0.73</v>
+        <v>1.23</v>
       </c>
       <c r="AP180">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ180">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR180">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AS180">
         <v>1.24</v>
       </c>
       <c r="AT180">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AU180">
         <v>5</v>
@@ -38531,25 +38531,25 @@
         <v>1.47</v>
       </c>
       <c r="AN181">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="AO181">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AP181">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ181">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AR181">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AS181">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AT181">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="AU181">
         <v>5</v>
@@ -38737,25 +38737,25 @@
         <v>1.95</v>
       </c>
       <c r="AN182">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AO182">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AP182">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ182">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR182">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AS182">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AT182">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="AU182">
         <v>8</v>
@@ -38943,25 +38943,25 @@
         <v>1.17</v>
       </c>
       <c r="AN183">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AO183">
         <v>1.73</v>
       </c>
       <c r="AP183">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ183">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR183">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AS183">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AT183">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="AU183">
         <v>3</v>
@@ -39149,25 +39149,25 @@
         <v>1.69</v>
       </c>
       <c r="AN184">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AO184">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AP184">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AQ184">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR184">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AS184">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AT184">
-        <v>2.49</v>
+        <v>2.76</v>
       </c>
       <c r="AU184">
         <v>5</v>
@@ -39358,22 +39358,22 @@
         <v>1.64</v>
       </c>
       <c r="AO185">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="AP185">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AQ185">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR185">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AS185">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AT185">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="AU185">
         <v>11</v>
@@ -39561,25 +39561,25 @@
         <v>1.53</v>
       </c>
       <c r="AN186">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AO186">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP186">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ186">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR186">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AS186">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AT186">
-        <v>2.43</v>
+        <v>2.68</v>
       </c>
       <c r="AU186">
         <v>2</v>
@@ -39770,22 +39770,22 @@
         <v>1.09</v>
       </c>
       <c r="AO187">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AP187">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AQ187">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR187">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AS187">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AT187">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="AU187">
         <v>4</v>
@@ -39973,25 +39973,25 @@
         <v>1.34</v>
       </c>
       <c r="AN188">
-        <v>1.18</v>
+        <v>0.83</v>
       </c>
       <c r="AO188">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="AP188">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ188">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AR188">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AS188">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AT188">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AU188">
         <v>10</v>
@@ -40182,22 +40182,22 @@
         <v>1.09</v>
       </c>
       <c r="AO189">
-        <v>0.45</v>
+        <v>0.83</v>
       </c>
       <c r="AP189">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AQ189">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR189">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AS189">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AT189">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="AU189">
         <v>8</v>
@@ -40385,25 +40385,25 @@
         <v>1.45</v>
       </c>
       <c r="AN190">
-        <v>2.09</v>
+        <v>1.78</v>
       </c>
       <c r="AO190">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="AP190">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ190">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR190">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AS190">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AT190">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="AU190">
         <v>6</v>
@@ -40591,25 +40591,25 @@
         <v>2.55</v>
       </c>
       <c r="AN191">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AO191">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
       <c r="AP191">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ191">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR191">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS191">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AT191">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AU191">
         <v>8</v>
@@ -40797,25 +40797,25 @@
         <v>1.67</v>
       </c>
       <c r="AN192">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AO192">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AP192">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AQ192">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR192">
-        <v>2.13</v>
+        <v>1.84</v>
       </c>
       <c r="AS192">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="AT192">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="AU192">
         <v>4</v>
@@ -41003,25 +41003,25 @@
         <v>1.49</v>
       </c>
       <c r="AN193">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AO193">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AP193">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ193">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR193">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="AS193">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AT193">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AU193">
         <v>3</v>
@@ -41209,25 +41209,25 @@
         <v>1.47</v>
       </c>
       <c r="AN194">
-        <v>1.17</v>
+        <v>0.79</v>
       </c>
       <c r="AO194">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="AP194">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ194">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR194">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AS194">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="AT194">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="AU194">
         <v>2</v>
@@ -41415,25 +41415,25 @@
         <v>2.43</v>
       </c>
       <c r="AN195">
-        <v>1.92</v>
+        <v>1.46</v>
       </c>
       <c r="AO195">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AP195">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ195">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR195">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AS195">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AT195">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="AU195">
         <v>12</v>
@@ -41621,25 +41621,25 @@
         <v>1.96</v>
       </c>
       <c r="AN196">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="AO196">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AP196">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ196">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR196">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AS196">
         <v>1.36</v>
       </c>
       <c r="AT196">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AU196">
         <v>5</v>
@@ -41827,25 +41827,25 @@
         <v>2.09</v>
       </c>
       <c r="AN197">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AO197">
-        <v>0.92</v>
+        <v>1.29</v>
       </c>
       <c r="AP197">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AQ197">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR197">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AS197">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AT197">
-        <v>3.17</v>
+        <v>2.85</v>
       </c>
       <c r="AU197">
         <v>2</v>
@@ -42033,25 +42033,25 @@
         <v>1.56</v>
       </c>
       <c r="AN198">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AO198">
+        <v>1.83</v>
+      </c>
+      <c r="AP198">
+        <v>1.79</v>
+      </c>
+      <c r="AQ198">
+        <v>1.76</v>
+      </c>
+      <c r="AR198">
+        <v>1.68</v>
+      </c>
+      <c r="AS198">
         <v>1.5</v>
       </c>
-      <c r="AP198">
-        <v>2.13</v>
-      </c>
-      <c r="AQ198">
-        <v>1.5</v>
-      </c>
-      <c r="AR198">
-        <v>1.82</v>
-      </c>
-      <c r="AS198">
-        <v>1.38</v>
-      </c>
       <c r="AT198">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AU198">
         <v>6</v>
@@ -42239,25 +42239,25 @@
         <v>1.49</v>
       </c>
       <c r="AN199">
-        <v>1.42</v>
+        <v>0.92</v>
       </c>
       <c r="AO199">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP199">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ199">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR199">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AS199">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="AT199">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="AU199">
         <v>2</v>
@@ -42445,25 +42445,25 @@
         <v>1.66</v>
       </c>
       <c r="AN200">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AO200">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="AP200">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ200">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR200">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AS200">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AT200">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="AU200">
         <v>5</v>
@@ -42651,25 +42651,25 @@
         <v>1.21</v>
       </c>
       <c r="AN201">
+        <v>1.46</v>
+      </c>
+      <c r="AO201">
         <v>1.75</v>
       </c>
-      <c r="AO201">
+      <c r="AP201">
+        <v>1.28</v>
+      </c>
+      <c r="AQ201">
         <v>1.83</v>
       </c>
-      <c r="AP201">
-        <v>1.57</v>
-      </c>
-      <c r="AQ201">
-        <v>1.86</v>
-      </c>
       <c r="AR201">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AS201">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AT201">
-        <v>2.87</v>
+        <v>3.12</v>
       </c>
       <c r="AU201">
         <v>0</v>
@@ -42857,25 +42857,25 @@
         <v>1.29</v>
       </c>
       <c r="AN202">
-        <v>1.17</v>
+        <v>0.92</v>
       </c>
       <c r="AO202">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AP202">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ202">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR202">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AS202">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AT202">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="AU202">
         <v>4</v>
@@ -43066,22 +43066,22 @@
         <v>1</v>
       </c>
       <c r="AO203">
+        <v>1.68</v>
+      </c>
+      <c r="AP203">
+        <v>0.9</v>
+      </c>
+      <c r="AQ203">
+        <v>1.79</v>
+      </c>
+      <c r="AR203">
         <v>1.33</v>
       </c>
-      <c r="AP203">
-        <v>0.87</v>
-      </c>
-      <c r="AQ203">
-        <v>1.43</v>
-      </c>
-      <c r="AR203">
-        <v>1.35</v>
-      </c>
       <c r="AS203">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AT203">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="AU203">
         <v>2</v>
@@ -43269,25 +43269,25 @@
         <v>0</v>
       </c>
       <c r="AN204">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AO204">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AP204">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AQ204">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR204">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AS204">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AT204">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="AU204">
         <v>4</v>
@@ -43475,25 +43475,25 @@
         <v>1.58</v>
       </c>
       <c r="AN205">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AO205">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AP205">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ205">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR205">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AS205">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AT205">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="AU205">
         <v>3</v>
@@ -43681,25 +43681,25 @@
         <v>2.8</v>
       </c>
       <c r="AN206">
-        <v>2.17</v>
+        <v>1.76</v>
       </c>
       <c r="AO206">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="AP206">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ206">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR206">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AS206">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AT206">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="AU206">
         <v>3</v>
@@ -43887,25 +43887,25 @@
         <v>2.15</v>
       </c>
       <c r="AN207">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AO207">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="AP207">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AQ207">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AR207">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AS207">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AT207">
-        <v>3.56</v>
+        <v>3.27</v>
       </c>
       <c r="AU207">
         <v>13</v>
@@ -44093,25 +44093,25 @@
         <v>1.9</v>
       </c>
       <c r="AN208">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="AO208">
-        <v>0.42</v>
+        <v>0.76</v>
       </c>
       <c r="AP208">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ208">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR208">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AS208">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AT208">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AU208">
         <v>4</v>
@@ -44299,25 +44299,25 @@
         <v>1.23</v>
       </c>
       <c r="AN209">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AO209">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AP209">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ209">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR209">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AS209">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AT209">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="AU209">
         <v>2</v>
@@ -44505,25 +44505,25 @@
         <v>1.63</v>
       </c>
       <c r="AN210">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AO210">
-        <v>0.85</v>
+        <v>1.23</v>
       </c>
       <c r="AP210">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ210">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AR210">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AS210">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AT210">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AU210">
         <v>5</v>
@@ -44711,25 +44711,25 @@
         <v>2.28</v>
       </c>
       <c r="AN211">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AO211">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AP211">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ211">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR211">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AS211">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AT211">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="AU211">
         <v>6</v>
@@ -44917,25 +44917,25 @@
         <v>1.66</v>
       </c>
       <c r="AN212">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="AO212">
         <v>1.15</v>
       </c>
       <c r="AP212">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AQ212">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AR212">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AS212">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AT212">
-        <v>2.52</v>
+        <v>2.71</v>
       </c>
       <c r="AU212">
         <v>4</v>
@@ -45123,25 +45123,25 @@
         <v>1.73</v>
       </c>
       <c r="AN213">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AO213">
-        <v>0.77</v>
+        <v>1.19</v>
       </c>
       <c r="AP213">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AQ213">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR213">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AS213">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AT213">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="AU213">
         <v>6</v>
@@ -45329,25 +45329,25 @@
         <v>1.17</v>
       </c>
       <c r="AN214">
-        <v>1.31</v>
+        <v>0.88</v>
       </c>
       <c r="AO214">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AP214">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ214">
+        <v>1.76</v>
+      </c>
+      <c r="AR214">
+        <v>1.39</v>
+      </c>
+      <c r="AS214">
         <v>1.6</v>
       </c>
-      <c r="AR214">
-        <v>1.44</v>
-      </c>
-      <c r="AS214">
-        <v>1.38</v>
-      </c>
       <c r="AT214">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="AU214">
         <v>7</v>
@@ -45535,25 +45535,25 @@
         <v>1.1</v>
       </c>
       <c r="AN215">
-        <v>1.08</v>
+        <v>0.73</v>
       </c>
       <c r="AO215">
         <v>1.77</v>
       </c>
       <c r="AP215">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="AQ215">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AR215">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AS215">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AT215">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="AU215">
         <v>3</v>
@@ -45741,25 +45741,25 @@
         <v>2.6</v>
       </c>
       <c r="AN216">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="AO216">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AP216">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ216">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AR216">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AS216">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AT216">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AU216">
         <v>8</v>
@@ -45947,25 +45947,25 @@
         <v>2.23</v>
       </c>
       <c r="AN217">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO217">
-        <v>0.6899999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="AP217">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AQ217">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR217">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AS217">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="AT217">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="AU217">
         <v>2</v>
@@ -46153,25 +46153,25 @@
         <v>2.07</v>
       </c>
       <c r="AN218">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AO218">
-        <v>0.38</v>
+        <v>0.7</v>
       </c>
       <c r="AP218">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AQ218">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="AR218">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AS218">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AT218">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="AU218">
         <v>6</v>
@@ -46359,25 +46359,25 @@
         <v>1.3</v>
       </c>
       <c r="AN219">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AO219">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AP219">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AQ219">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AR219">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AS219">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AT219">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AU219">
         <v>0</v>
@@ -46565,25 +46565,25 @@
         <v>1.25</v>
       </c>
       <c r="AN220">
-        <v>1.15</v>
+        <v>0.89</v>
       </c>
       <c r="AO220">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AP220">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="AQ220">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AR220">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AS220">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AT220">
-        <v>3.31</v>
+        <v>3.19</v>
       </c>
       <c r="AU220">
         <v>7</v>
@@ -46771,25 +46771,25 @@
         <v>2.4</v>
       </c>
       <c r="AN221">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AO221">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AP221">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AQ221">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR221">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AS221">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AT221">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="AU221">
         <v>8</v>
@@ -46977,25 +46977,25 @@
         <v>1.5</v>
       </c>
       <c r="AN222">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AO222">
-        <v>0.46</v>
+        <v>0.89</v>
       </c>
       <c r="AP222">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AQ222">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="AR222">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AS222">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AT222">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AU222">
         <v>4</v>
@@ -47183,25 +47183,25 @@
         <v>1.99</v>
       </c>
       <c r="AN223">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AO223">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AP223">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AQ223">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AR223">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AS223">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AT223">
-        <v>3.27</v>
+        <v>3.14</v>
       </c>
       <c r="AU223">
         <v>5</v>
@@ -47389,25 +47389,25 @@
         <v>1.43</v>
       </c>
       <c r="AN224">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AO224">
-        <v>1</v>
+        <v>1.37</v>
       </c>
       <c r="AP224">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AQ224">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AR224">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AS224">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AT224">
-        <v>3.03</v>
+        <v>2.85</v>
       </c>
       <c r="AU224">
         <v>5</v>
@@ -47595,25 +47595,25 @@
         <v>1.38</v>
       </c>
       <c r="AN225">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="AO225">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AP225">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AQ225">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AR225">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AS225">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AT225">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="AU225">
         <v>5</v>
@@ -47804,22 +47804,22 @@
         <v>0.93</v>
       </c>
       <c r="AO226">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="AP226">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AQ226">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AR226">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AS226">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AT226">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="AU226">
         <v>7</v>
@@ -48007,25 +48007,25 @@
         <v>1.33</v>
       </c>
       <c r="AN227">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AO227">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AP227">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AQ227">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AR227">
         <v>1.44</v>
       </c>
       <c r="AS227">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AT227">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AU227">
         <v>7</v>
@@ -48213,25 +48213,25 @@
         <v>2.12</v>
       </c>
       <c r="AN228">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AO228">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="AP228">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ228">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="AR228">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AS228">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AT228">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="AU228">
         <v>3</v>
@@ -48419,25 +48419,25 @@
         <v>2.43</v>
       </c>
       <c r="AN229">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AO229">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="AP229">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ229">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AR229">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AS229">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AT229">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="AU229">
         <v>6</v>
@@ -48625,25 +48625,25 @@
         <v>1.36</v>
       </c>
       <c r="AN230">
-        <v>1.29</v>
+        <v>0.89</v>
       </c>
       <c r="AO230">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AP230">
-        <v>1.4</v>
+        <v>0.97</v>
       </c>
       <c r="AQ230">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AR230">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AS230">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AT230">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AU230">
         <v>5</v>
@@ -48710,6 +48710,212 @@
       </c>
       <c r="BP230">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7486710</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45718.625</v>
+      </c>
+      <c r="F231">
+        <v>29</v>
+      </c>
+      <c r="G231" t="s">
+        <v>81</v>
+      </c>
+      <c r="H231" t="s">
+        <v>74</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>0</v>
+      </c>
+      <c r="L231">
+        <v>0</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>0</v>
+      </c>
+      <c r="O231" t="s">
+        <v>86</v>
+      </c>
+      <c r="P231" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q231">
+        <v>3.5</v>
+      </c>
+      <c r="R231">
+        <v>2.1</v>
+      </c>
+      <c r="S231">
+        <v>3.2</v>
+      </c>
+      <c r="T231">
+        <v>1.44</v>
+      </c>
+      <c r="U231">
+        <v>2.63</v>
+      </c>
+      <c r="V231">
+        <v>3.25</v>
+      </c>
+      <c r="W231">
+        <v>1.33</v>
+      </c>
+      <c r="X231">
+        <v>9</v>
+      </c>
+      <c r="Y231">
+        <v>1.07</v>
+      </c>
+      <c r="Z231">
+        <v>2.69</v>
+      </c>
+      <c r="AA231">
+        <v>3.13</v>
+      </c>
+      <c r="AB231">
+        <v>2.64</v>
+      </c>
+      <c r="AC231">
+        <v>1.02</v>
+      </c>
+      <c r="AD231">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE231">
+        <v>1.33</v>
+      </c>
+      <c r="AF231">
+        <v>3.15</v>
+      </c>
+      <c r="AG231">
+        <v>1.98</v>
+      </c>
+      <c r="AH231">
+        <v>1.77</v>
+      </c>
+      <c r="AI231">
+        <v>1.8</v>
+      </c>
+      <c r="AJ231">
+        <v>1.91</v>
+      </c>
+      <c r="AK231">
+        <v>1.51</v>
+      </c>
+      <c r="AL231">
+        <v>1.31</v>
+      </c>
+      <c r="AM231">
+        <v>1.38</v>
+      </c>
+      <c r="AN231">
+        <v>1.61</v>
+      </c>
+      <c r="AO231">
+        <v>1.86</v>
+      </c>
+      <c r="AP231">
+        <v>1.59</v>
+      </c>
+      <c r="AQ231">
+        <v>1.83</v>
+      </c>
+      <c r="AR231">
+        <v>1.6</v>
+      </c>
+      <c r="AS231">
+        <v>1.85</v>
+      </c>
+      <c r="AT231">
+        <v>3.45</v>
+      </c>
+      <c r="AU231">
+        <v>3</v>
+      </c>
+      <c r="AV231">
+        <v>5</v>
+      </c>
+      <c r="AW231">
+        <v>9</v>
+      </c>
+      <c r="AX231">
+        <v>7</v>
+      </c>
+      <c r="AY231">
+        <v>14</v>
+      </c>
+      <c r="AZ231">
+        <v>13</v>
+      </c>
+      <c r="BA231">
+        <v>8</v>
+      </c>
+      <c r="BB231">
+        <v>2</v>
+      </c>
+      <c r="BC231">
+        <v>10</v>
+      </c>
+      <c r="BD231">
+        <v>2.12</v>
+      </c>
+      <c r="BE231">
+        <v>6.4</v>
+      </c>
+      <c r="BF231">
+        <v>1.88</v>
+      </c>
+      <c r="BG231">
+        <v>1.4</v>
+      </c>
+      <c r="BH231">
+        <v>2.65</v>
+      </c>
+      <c r="BI231">
+        <v>1.68</v>
+      </c>
+      <c r="BJ231">
+        <v>2.02</v>
+      </c>
+      <c r="BK231">
+        <v>2.1</v>
+      </c>
+      <c r="BL231">
+        <v>1.63</v>
+      </c>
+      <c r="BM231">
+        <v>2.65</v>
+      </c>
+      <c r="BN231">
+        <v>1.4</v>
+      </c>
+      <c r="BO231">
+        <v>3.55</v>
+      </c>
+      <c r="BP231">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1329,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP231"/>
+  <dimension ref="A1:BP232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1663,10 +1663,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ3">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2075,10 +2075,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ5">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2487,10 +2487,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2693,10 +2693,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AQ7">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2899,10 +2899,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ8">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3105,10 +3105,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ9">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3311,19 +3311,19 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ10">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR10">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AU10">
         <v>6</v>
@@ -3511,25 +3511,25 @@
         <v>1.13</v>
       </c>
       <c r="AN11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ11">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR11">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>5</v>
@@ -3717,25 +3717,25 @@
         <v>2.1</v>
       </c>
       <c r="AN12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ12">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR12">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>9</v>
@@ -3923,25 +3923,25 @@
         <v>1.4</v>
       </c>
       <c r="AN13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR13">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>8</v>
@@ -4129,25 +4129,25 @@
         <v>1.72</v>
       </c>
       <c r="AN14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR14">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AU14">
         <v>7</v>
@@ -4338,22 +4338,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ15">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AR15">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AU15">
         <v>5</v>
@@ -4541,25 +4541,25 @@
         <v>1.3</v>
       </c>
       <c r="AN16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AR16">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AU16">
         <v>7</v>
@@ -4747,25 +4747,25 @@
         <v>1.55</v>
       </c>
       <c r="AN17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ17">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR17">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AU17">
         <v>3</v>
@@ -4953,25 +4953,25 @@
         <v>1.8</v>
       </c>
       <c r="AN18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ18">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR18">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="AS18">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AT18">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AU18">
         <v>2</v>
@@ -5162,22 +5162,22 @@
         <v>1</v>
       </c>
       <c r="AO19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ19">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR19">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="AS19">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="AT19">
-        <v>3</v>
+        <v>3.54</v>
       </c>
       <c r="AU19">
         <v>8</v>
@@ -5365,25 +5365,25 @@
         <v>1.6</v>
       </c>
       <c r="AN20">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP20">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ20">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR20">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AS20">
-        <v>1.19</v>
+        <v>0.71</v>
       </c>
       <c r="AT20">
-        <v>2.83</v>
+        <v>2.16</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5574,22 +5574,22 @@
         <v>3</v>
       </c>
       <c r="AO21">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AQ21">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR21">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AS21">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="AT21">
-        <v>2.64</v>
+        <v>2.51</v>
       </c>
       <c r="AU21">
         <v>2</v>
@@ -5777,25 +5777,25 @@
         <v>2.35</v>
       </c>
       <c r="AN22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR22">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AS22">
-        <v>1.18</v>
+        <v>0.77</v>
       </c>
       <c r="AT22">
-        <v>2.97</v>
+        <v>2.66</v>
       </c>
       <c r="AU22">
         <v>2</v>
@@ -5983,25 +5983,25 @@
         <v>1.95</v>
       </c>
       <c r="AN23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AQ23">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR23">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AS23">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AT23">
-        <v>3.77</v>
+        <v>4.23</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -6189,25 +6189,25 @@
         <v>1.36</v>
       </c>
       <c r="AN24">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ24">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AR24">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AS24">
-        <v>1.06</v>
+        <v>0.54</v>
       </c>
       <c r="AT24">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="AU24">
         <v>5</v>
@@ -6395,25 +6395,25 @@
         <v>1.26</v>
       </c>
       <c r="AN25">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO25">
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ25">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="AR25">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="AS25">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AT25">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6601,25 +6601,25 @@
         <v>1.63</v>
       </c>
       <c r="AN26">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AO26">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ26">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR26">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AS26">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="AT26">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AU26">
         <v>5</v>
@@ -6807,25 +6807,25 @@
         <v>1.75</v>
       </c>
       <c r="AN27">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO27">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AP27">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ27">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR27">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AS27">
-        <v>1.22</v>
+        <v>0.99</v>
       </c>
       <c r="AT27">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -7013,25 +7013,25 @@
         <v>2.25</v>
       </c>
       <c r="AN28">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AQ28">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR28">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AS28">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AT28">
-        <v>3.31</v>
+        <v>3.56</v>
       </c>
       <c r="AU28">
         <v>6</v>
@@ -7219,25 +7219,25 @@
         <v>2.35</v>
       </c>
       <c r="AN29">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO29">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ29">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AR29">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="AS29">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="AT29">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AU29">
         <v>0</v>
@@ -7425,25 +7425,25 @@
         <v>1.66</v>
       </c>
       <c r="AN30">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AO30">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AQ30">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AS30">
-        <v>1.09</v>
+        <v>0.84</v>
       </c>
       <c r="AT30">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="AU30">
         <v>7</v>
@@ -7631,25 +7631,25 @@
         <v>1.45</v>
       </c>
       <c r="AN31">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AO31">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AP31">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ31">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR31">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AS31">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AT31">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="AU31">
         <v>3</v>
@@ -7837,25 +7837,25 @@
         <v>1.72</v>
       </c>
       <c r="AN32">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO32">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ32">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AR32">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AS32">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AT32">
-        <v>3.16</v>
+        <v>3.44</v>
       </c>
       <c r="AU32">
         <v>5</v>
@@ -8043,25 +8043,25 @@
         <v>2</v>
       </c>
       <c r="AN33">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AO33">
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ33">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR33">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AS33">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AT33">
-        <v>3.46</v>
+        <v>3.79</v>
       </c>
       <c r="AU33">
         <v>9</v>
@@ -8249,25 +8249,25 @@
         <v>1.68</v>
       </c>
       <c r="AN34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO34">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ34">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR34">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AS34">
-        <v>1.13</v>
+        <v>0.9</v>
       </c>
       <c r="AT34">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AU34">
         <v>3</v>
@@ -8455,25 +8455,25 @@
         <v>1.47</v>
       </c>
       <c r="AN35">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO35">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ35">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR35">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AS35">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT35">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="AU35">
         <v>8</v>
@@ -8661,25 +8661,25 @@
         <v>1.25</v>
       </c>
       <c r="AN36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO36">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ36">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="AR36">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AS36">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AT36">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="AU36">
         <v>4</v>
@@ -8873,19 +8873,19 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AQ37">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR37">
-        <v>1.66</v>
+        <v>1.39</v>
       </c>
       <c r="AS37">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AT37">
-        <v>3.39</v>
+        <v>3.17</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -9076,22 +9076,22 @@
         <v>1</v>
       </c>
       <c r="AO38">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AQ38">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR38">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AS38">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="AT38">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="AU38">
         <v>7</v>
@@ -9279,25 +9279,25 @@
         <v>1.34</v>
       </c>
       <c r="AN39">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AO39">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP39">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ39">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AR39">
-        <v>0.97</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS39">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AT39">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9485,25 +9485,25 @@
         <v>1.44</v>
       </c>
       <c r="AN40">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO40">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ40">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR40">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AS40">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AT40">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AU40">
         <v>7</v>
@@ -9691,25 +9691,25 @@
         <v>1.57</v>
       </c>
       <c r="AN41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO41">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ41">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AR41">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AS41">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AT41">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="AU41">
         <v>7</v>
@@ -9897,25 +9897,25 @@
         <v>2.35</v>
       </c>
       <c r="AN42">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AO42">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ42">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR42">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AS42">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AT42">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="AU42">
         <v>12</v>
@@ -10103,25 +10103,25 @@
         <v>1.7</v>
       </c>
       <c r="AN43">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AO43">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ43">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR43">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="AS43">
-        <v>1.49</v>
+        <v>1.14</v>
       </c>
       <c r="AT43">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="AU43">
         <v>4</v>
@@ -10309,25 +10309,25 @@
         <v>2.6</v>
       </c>
       <c r="AN44">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ44">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR44">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="AS44">
         <v>1.49</v>
       </c>
       <c r="AT44">
-        <v>3.45</v>
+        <v>3.72</v>
       </c>
       <c r="AU44">
         <v>3</v>
@@ -10515,25 +10515,25 @@
         <v>2</v>
       </c>
       <c r="AN45">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AO45">
-        <v>1.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP45">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR45">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AS45">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AT45">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="AU45">
         <v>4</v>
@@ -10721,25 +10721,25 @@
         <v>1.62</v>
       </c>
       <c r="AN46">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AO46">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP46">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AR46">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AS46">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AT46">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="AU46">
         <v>8</v>
@@ -10927,25 +10927,25 @@
         <v>2.02</v>
       </c>
       <c r="AN47">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AO47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR47">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AS47">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AT47">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -11133,25 +11133,25 @@
         <v>1.45</v>
       </c>
       <c r="AN48">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO48">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AP48">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ48">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR48">
-        <v>1.12</v>
+        <v>0.93</v>
       </c>
       <c r="AS48">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AT48">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -11339,25 +11339,25 @@
         <v>1.36</v>
       </c>
       <c r="AN49">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO49">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ49">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="AR49">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AS49">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AT49">
-        <v>2.92</v>
+        <v>3.09</v>
       </c>
       <c r="AU49">
         <v>9</v>
@@ -11548,22 +11548,22 @@
         <v>1.33</v>
       </c>
       <c r="AO50">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AQ50">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR50">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AS50">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AT50">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11751,25 +11751,25 @@
         <v>1.4</v>
       </c>
       <c r="AN51">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO51">
         <v>2.33</v>
       </c>
       <c r="AP51">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ51">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR51">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AS51">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="AT51">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AU51">
         <v>3</v>
@@ -11957,25 +11957,25 @@
         <v>2.49</v>
       </c>
       <c r="AN52">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO52">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AQ52">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR52">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AS52">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="AT52">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="AU52">
         <v>12</v>
@@ -12163,25 +12163,25 @@
         <v>1.2</v>
       </c>
       <c r="AN53">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO53">
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ53">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR53">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AS53">
-        <v>1.88</v>
+        <v>1.17</v>
       </c>
       <c r="AT53">
-        <v>3.01</v>
+        <v>2.36</v>
       </c>
       <c r="AU53">
         <v>6</v>
@@ -12369,25 +12369,25 @@
         <v>1.24</v>
       </c>
       <c r="AN54">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="AO54">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AR54">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AS54">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AT54">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="AU54">
         <v>4</v>
@@ -12578,19 +12578,19 @@
         <v>1</v>
       </c>
       <c r="AO55">
-        <v>1.17</v>
+        <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ55">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR55">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AS55">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="AT55">
         <v>3.05</v>
@@ -12784,22 +12784,22 @@
         <v>2</v>
       </c>
       <c r="AO56">
+        <v>1.33</v>
+      </c>
+      <c r="AP56">
         <v>1.14</v>
       </c>
-      <c r="AP56">
-        <v>1.1</v>
-      </c>
       <c r="AQ56">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AR56">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AS56">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AT56">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12987,25 +12987,25 @@
         <v>1.68</v>
       </c>
       <c r="AN57">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="AO57">
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ57">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR57">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AS57">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT57">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AU57">
         <v>8</v>
@@ -13193,25 +13193,25 @@
         <v>1.68</v>
       </c>
       <c r="AN58">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO58">
+        <v>1.25</v>
+      </c>
+      <c r="AP58">
+        <v>2.13</v>
+      </c>
+      <c r="AQ58">
         <v>1.14</v>
       </c>
-      <c r="AP58">
-        <v>1.79</v>
-      </c>
-      <c r="AQ58">
-        <v>1.59</v>
-      </c>
       <c r="AR58">
-        <v>1.74</v>
+        <v>2.03</v>
       </c>
       <c r="AS58">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AT58">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13399,25 +13399,25 @@
         <v>1.46</v>
       </c>
       <c r="AN59">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO59">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ59">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AR59">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="AS59">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AT59">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13605,25 +13605,25 @@
         <v>1.45</v>
       </c>
       <c r="AN60">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AO60">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AQ60">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR60">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AS60">
-        <v>1.78</v>
+        <v>1.23</v>
       </c>
       <c r="AT60">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13811,22 +13811,22 @@
         <v>2.6</v>
       </c>
       <c r="AN61">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AO61">
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ61">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR61">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="AS61">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AT61">
         <v>3.27</v>
@@ -14017,25 +14017,25 @@
         <v>1.71</v>
       </c>
       <c r="AN62">
-        <v>1.14</v>
+        <v>0.33</v>
       </c>
       <c r="AO62">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AP62">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ62">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR62">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AS62">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AT62">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -14223,25 +14223,25 @@
         <v>1.94</v>
       </c>
       <c r="AN63">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AO63">
-        <v>1.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP63">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ63">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR63">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="AS63">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT63">
-        <v>2.37</v>
+        <v>2.67</v>
       </c>
       <c r="AU63">
         <v>3</v>
@@ -14432,22 +14432,22 @@
         <v>1</v>
       </c>
       <c r="AO64">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP64">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AQ64">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR64">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AS64">
-        <v>1.26</v>
+        <v>0.88</v>
       </c>
       <c r="AT64">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14635,25 +14635,25 @@
         <v>1.95</v>
       </c>
       <c r="AN65">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO65">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ65">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR65">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AS65">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AT65">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14841,25 +14841,25 @@
         <v>1.25</v>
       </c>
       <c r="AN66">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="AO66">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AP66">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ66">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR66">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AS66">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AT66">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="AU66">
         <v>3</v>
@@ -15047,25 +15047,25 @@
         <v>1.4</v>
       </c>
       <c r="AN67">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AO67">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ67">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR67">
-        <v>1.18</v>
+        <v>0.97</v>
       </c>
       <c r="AS67">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AT67">
-        <v>2.78</v>
+        <v>2.47</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -15253,25 +15253,25 @@
         <v>1.25</v>
       </c>
       <c r="AN68">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO68">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ68">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR68">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AS68">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AT68">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="AU68">
         <v>6</v>
@@ -15459,25 +15459,25 @@
         <v>1.57</v>
       </c>
       <c r="AN69">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AO69">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AQ69">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR69">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AS69">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AT69">
-        <v>3.59</v>
+        <v>3.32</v>
       </c>
       <c r="AU69">
         <v>6</v>
@@ -15665,25 +15665,25 @@
         <v>1.5</v>
       </c>
       <c r="AN70">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO70">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ70">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR70">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AS70">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AT70">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="AU70">
         <v>3</v>
@@ -15871,25 +15871,25 @@
         <v>1.78</v>
       </c>
       <c r="AN71">
+        <v>1</v>
+      </c>
+      <c r="AO71">
+        <v>1.8</v>
+      </c>
+      <c r="AP71">
+        <v>2</v>
+      </c>
+      <c r="AQ71">
+        <v>1.5</v>
+      </c>
+      <c r="AR71">
+        <v>1.35</v>
+      </c>
+      <c r="AS71">
         <v>1.13</v>
       </c>
-      <c r="AO71">
-        <v>2.25</v>
-      </c>
-      <c r="AP71">
-        <v>1.59</v>
-      </c>
-      <c r="AQ71">
-        <v>1.76</v>
-      </c>
-      <c r="AR71">
-        <v>1.37</v>
-      </c>
-      <c r="AS71">
-        <v>1.22</v>
-      </c>
       <c r="AT71">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="AU71">
         <v>4</v>
@@ -16077,25 +16077,25 @@
         <v>1.8</v>
       </c>
       <c r="AN72">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO72">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AP72">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ72">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR72">
-        <v>1.34</v>
+        <v>1.78</v>
       </c>
       <c r="AS72">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AT72">
-        <v>2.57</v>
+        <v>2.91</v>
       </c>
       <c r="AU72">
         <v>8</v>
@@ -16283,25 +16283,25 @@
         <v>1.62</v>
       </c>
       <c r="AN73">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO73">
-        <v>1.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP73">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ73">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR73">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AS73">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AT73">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16489,25 +16489,25 @@
         <v>1.25</v>
       </c>
       <c r="AN74">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AO74">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ74">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR74">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AS74">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AT74">
-        <v>3.02</v>
+        <v>2.66</v>
       </c>
       <c r="AU74">
         <v>2</v>
@@ -16695,25 +16695,25 @@
         <v>2.45</v>
       </c>
       <c r="AN75">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AO75">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ75">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AR75">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AS75">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AT75">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16901,25 +16901,25 @@
         <v>1.62</v>
       </c>
       <c r="AN76">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AO76">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AQ76">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AR76">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AS76">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AT76">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -17107,25 +17107,25 @@
         <v>1.53</v>
       </c>
       <c r="AN77">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO77">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR77">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AS77">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AT77">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AU77">
         <v>5</v>
@@ -17313,25 +17313,25 @@
         <v>1.71</v>
       </c>
       <c r="AN78">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AO78">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="AP78">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ78">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR78">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AS78">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AT78">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="AU78">
         <v>9</v>
@@ -17519,25 +17519,25 @@
         <v>1.22</v>
       </c>
       <c r="AN79">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AO79">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP79">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ79">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="AR79">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AS79">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AT79">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="AU79">
         <v>3</v>
@@ -17725,25 +17725,25 @@
         <v>1.57</v>
       </c>
       <c r="AN80">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO80">
-        <v>1.3</v>
+        <v>0.25</v>
       </c>
       <c r="AP80">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ80">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR80">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AS80">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AT80">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AU80">
         <v>10</v>
@@ -17931,25 +17931,25 @@
         <v>1.9</v>
       </c>
       <c r="AN81">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="AO81">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="AP81">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ81">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR81">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AS81">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AT81">
-        <v>2.58</v>
+        <v>2.29</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -18137,25 +18137,25 @@
         <v>1.3</v>
       </c>
       <c r="AN82">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AO82">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ82">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AR82">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AS82">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AT82">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AU82">
         <v>2</v>
@@ -18346,22 +18346,22 @@
         <v>1.67</v>
       </c>
       <c r="AO83">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AQ83">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR83">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AS83">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AT83">
-        <v>3.21</v>
+        <v>2.98</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18549,25 +18549,25 @@
         <v>1.95</v>
       </c>
       <c r="AN84">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="AO84">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AP84">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR84">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AS84">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AT84">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AU84">
         <v>2</v>
@@ -18755,25 +18755,25 @@
         <v>1.25</v>
       </c>
       <c r="AN85">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AO85">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ85">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR85">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AS85">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AT85">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AU85">
         <v>5</v>
@@ -18961,25 +18961,25 @@
         <v>1.44</v>
       </c>
       <c r="AN86">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AO86">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="AP86">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AQ86">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR86">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AS86">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="AT86">
-        <v>3.39</v>
+        <v>2.99</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -19167,25 +19167,25 @@
         <v>2.9</v>
       </c>
       <c r="AN87">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AO87">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ87">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR87">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AS87">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AT87">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AU87">
         <v>8</v>
@@ -19373,25 +19373,25 @@
         <v>1.52</v>
       </c>
       <c r="AN88">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AO88">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AP88">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ88">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AR88">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="AS88">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AT88">
-        <v>2.79</v>
+        <v>3.05</v>
       </c>
       <c r="AU88">
         <v>5</v>
@@ -19579,22 +19579,22 @@
         <v>1.86</v>
       </c>
       <c r="AN89">
+        <v>1.5</v>
+      </c>
+      <c r="AO89">
+        <v>0.67</v>
+      </c>
+      <c r="AP89">
+        <v>1.5</v>
+      </c>
+      <c r="AQ89">
+        <v>1.36</v>
+      </c>
+      <c r="AR89">
+        <v>1.6</v>
+      </c>
+      <c r="AS89">
         <v>1.09</v>
-      </c>
-      <c r="AO89">
-        <v>1.55</v>
-      </c>
-      <c r="AP89">
-        <v>1.17</v>
-      </c>
-      <c r="AQ89">
-        <v>1.61</v>
-      </c>
-      <c r="AR89">
-        <v>1.53</v>
-      </c>
-      <c r="AS89">
-        <v>1.16</v>
       </c>
       <c r="AT89">
         <v>2.69</v>
@@ -19785,25 +19785,25 @@
         <v>1.24</v>
       </c>
       <c r="AN90">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AO90">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AP90">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ90">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AR90">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS90">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AT90">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="AU90">
         <v>4</v>
@@ -19991,25 +19991,25 @@
         <v>2.7</v>
       </c>
       <c r="AN91">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AO91">
-        <v>1.27</v>
+        <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AQ91">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR91">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AS91">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AT91">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20197,25 +20197,25 @@
         <v>1.37</v>
       </c>
       <c r="AN92">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AO92">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ92">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR92">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AS92">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AT92">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AU92">
         <v>3</v>
@@ -20403,25 +20403,25 @@
         <v>1.44</v>
       </c>
       <c r="AN93">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="AO93">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ93">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AR93">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AS93">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AT93">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AU93">
         <v>3</v>
@@ -20609,25 +20609,25 @@
         <v>1.29</v>
       </c>
       <c r="AN94">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AO94">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ94">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="AR94">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AS94">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AT94">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="AU94">
         <v>8</v>
@@ -20815,25 +20815,25 @@
         <v>3.15</v>
       </c>
       <c r="AN95">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AO95">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP95">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ95">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR95">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AS95">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AT95">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="AU95">
         <v>9</v>
@@ -21021,25 +21021,25 @@
         <v>1.42</v>
       </c>
       <c r="AN96">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AO96">
-        <v>1.08</v>
+        <v>0.2</v>
       </c>
       <c r="AP96">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR96">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AS96">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AT96">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="AU96">
         <v>9</v>
@@ -21227,25 +21227,25 @@
         <v>1.78</v>
       </c>
       <c r="AN97">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="AO97">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AP97">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR97">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AS97">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AT97">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="AU97">
         <v>5</v>
@@ -21436,22 +21436,22 @@
         <v>1.17</v>
       </c>
       <c r="AO98">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AQ98">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR98">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AS98">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="AT98">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21639,25 +21639,25 @@
         <v>1.15</v>
       </c>
       <c r="AN99">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO99">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AP99">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ99">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR99">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AS99">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AT99">
-        <v>3.07</v>
+        <v>2.86</v>
       </c>
       <c r="AU99">
         <v>0</v>
@@ -21845,25 +21845,25 @@
         <v>2.85</v>
       </c>
       <c r="AN100">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AO100">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP100">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ100">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR100">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AS100">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="AT100">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -22051,25 +22051,25 @@
         <v>1.2</v>
       </c>
       <c r="AN101">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AO101">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AP101">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ101">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR101">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AS101">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="AT101">
-        <v>2.91</v>
+        <v>2.58</v>
       </c>
       <c r="AU101">
         <v>2</v>
@@ -22257,25 +22257,25 @@
         <v>1.87</v>
       </c>
       <c r="AN102">
+        <v>1.67</v>
+      </c>
+      <c r="AO102">
         <v>1.17</v>
       </c>
-      <c r="AO102">
-        <v>1</v>
-      </c>
       <c r="AP102">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ102">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR102">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AS102">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AT102">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22463,25 +22463,25 @@
         <v>1.72</v>
       </c>
       <c r="AN103">
-        <v>1.08</v>
+        <v>0.8</v>
       </c>
       <c r="AO103">
-        <v>1.08</v>
+        <v>0.6</v>
       </c>
       <c r="AP103">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ103">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR103">
+        <v>1.37</v>
+      </c>
+      <c r="AS103">
         <v>1.44</v>
       </c>
-      <c r="AS103">
-        <v>1.56</v>
-      </c>
       <c r="AT103">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AU103">
         <v>8</v>
@@ -22669,25 +22669,25 @@
         <v>1.95</v>
       </c>
       <c r="AN104">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AO104">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AQ104">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AR104">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AS104">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AT104">
-        <v>3.31</v>
+        <v>3.52</v>
       </c>
       <c r="AU104">
         <v>9</v>
@@ -22875,25 +22875,25 @@
         <v>1.95</v>
       </c>
       <c r="AN105">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AO105">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="AP105">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ105">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR105">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AS105">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AT105">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AU105">
         <v>6</v>
@@ -23081,25 +23081,25 @@
         <v>1.66</v>
       </c>
       <c r="AN106">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AO106">
-        <v>1.31</v>
+        <v>0.67</v>
       </c>
       <c r="AP106">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ106">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR106">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AS106">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AT106">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AU106">
         <v>11</v>
@@ -23287,25 +23287,25 @@
         <v>1.55</v>
       </c>
       <c r="AN107">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="AO107">
-        <v>1.38</v>
+        <v>0.71</v>
       </c>
       <c r="AP107">
+        <v>1.71</v>
+      </c>
+      <c r="AQ107">
         <v>1.36</v>
       </c>
-      <c r="AQ107">
-        <v>1.61</v>
-      </c>
       <c r="AR107">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AS107">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AT107">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AU107">
         <v>4</v>
@@ -23493,25 +23493,25 @@
         <v>1.97</v>
       </c>
       <c r="AN108">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AO108">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ108">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR108">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AS108">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AT108">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="AU108">
         <v>0</v>
@@ -23699,25 +23699,25 @@
         <v>2</v>
       </c>
       <c r="AN109">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AO109">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AP109">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ109">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="AR109">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AS109">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AT109">
-        <v>3.21</v>
+        <v>3.51</v>
       </c>
       <c r="AU109">
         <v>7</v>
@@ -23905,25 +23905,25 @@
         <v>1.32</v>
       </c>
       <c r="AN110">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO110">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AP110">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ110">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AR110">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="AS110">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AT110">
-        <v>2.7</v>
+        <v>3.09</v>
       </c>
       <c r="AU110">
         <v>3</v>
@@ -24111,25 +24111,25 @@
         <v>1.34</v>
       </c>
       <c r="AN111">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AO111">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AP111">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR111">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AS111">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AT111">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="AU111">
         <v>5</v>
@@ -24317,25 +24317,25 @@
         <v>1.08</v>
       </c>
       <c r="AN112">
-        <v>0.93</v>
+        <v>1.33</v>
       </c>
       <c r="AO112">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AP112">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ112">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR112">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AS112">
-        <v>1.74</v>
+        <v>1.49</v>
       </c>
       <c r="AT112">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="AU112">
         <v>3</v>
@@ -24523,25 +24523,25 @@
         <v>1.8</v>
       </c>
       <c r="AN113">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AO113">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AP113">
+        <v>1.67</v>
+      </c>
+      <c r="AQ113">
+        <v>1</v>
+      </c>
+      <c r="AR113">
+        <v>1.54</v>
+      </c>
+      <c r="AS113">
         <v>1.41</v>
       </c>
-      <c r="AQ113">
-        <v>1.28</v>
-      </c>
-      <c r="AR113">
-        <v>1.58</v>
-      </c>
-      <c r="AS113">
-        <v>1.38</v>
-      </c>
       <c r="AT113">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AU113">
         <v>5</v>
@@ -24729,25 +24729,25 @@
         <v>1.8</v>
       </c>
       <c r="AN114">
-        <v>1.5</v>
+        <v>2.17</v>
       </c>
       <c r="AO114">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AP114">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ114">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR114">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AS114">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AT114">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="AU114">
         <v>4</v>
@@ -24935,25 +24935,25 @@
         <v>1.42</v>
       </c>
       <c r="AN115">
-        <v>1.21</v>
+        <v>1.86</v>
       </c>
       <c r="AO115">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AP115">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ115">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR115">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AS115">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AT115">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AU115">
         <v>7</v>
@@ -25141,25 +25141,25 @@
         <v>1.9</v>
       </c>
       <c r="AN116">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="AO116">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ116">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR116">
+        <v>1.34</v>
+      </c>
+      <c r="AS116">
         <v>1.3</v>
       </c>
-      <c r="AS116">
-        <v>1.46</v>
-      </c>
       <c r="AT116">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AU116">
         <v>4</v>
@@ -25347,25 +25347,25 @@
         <v>1.62</v>
       </c>
       <c r="AN117">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO117">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ117">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR117">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AS117">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="AT117">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AU117">
         <v>4</v>
@@ -25553,25 +25553,25 @@
         <v>1.5</v>
       </c>
       <c r="AN118">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="AO118">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="AP118">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ118">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR118">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AS118">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AT118">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25759,25 +25759,25 @@
         <v>2.2</v>
       </c>
       <c r="AN119">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AO119">
-        <v>0.93</v>
+        <v>0.17</v>
       </c>
       <c r="AP119">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ119">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR119">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AS119">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AT119">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="AU119">
         <v>5</v>
@@ -25965,25 +25965,25 @@
         <v>1.76</v>
       </c>
       <c r="AN120">
+        <v>1.5</v>
+      </c>
+      <c r="AO120">
+        <v>0.63</v>
+      </c>
+      <c r="AP120">
+        <v>1.14</v>
+      </c>
+      <c r="AQ120">
+        <v>0.8</v>
+      </c>
+      <c r="AR120">
         <v>1.36</v>
       </c>
-      <c r="AO120">
-        <v>0.86</v>
-      </c>
-      <c r="AP120">
-        <v>1.1</v>
-      </c>
-      <c r="AQ120">
-        <v>0.97</v>
-      </c>
-      <c r="AR120">
-        <v>1.32</v>
-      </c>
       <c r="AS120">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AT120">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -26171,25 +26171,25 @@
         <v>1.36</v>
       </c>
       <c r="AN121">
+        <v>2.29</v>
+      </c>
+      <c r="AO121">
+        <v>1.8</v>
+      </c>
+      <c r="AP121">
+        <v>1.86</v>
+      </c>
+      <c r="AQ121">
         <v>1.6</v>
       </c>
-      <c r="AO121">
-        <v>1.64</v>
-      </c>
-      <c r="AP121">
-        <v>1.61</v>
-      </c>
-      <c r="AQ121">
-        <v>1.76</v>
-      </c>
       <c r="AR121">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AS121">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="AT121">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="AU121">
         <v>5</v>
@@ -26377,25 +26377,25 @@
         <v>1.36</v>
       </c>
       <c r="AN122">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO122">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ122">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AR122">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AS122">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AT122">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="AU122">
         <v>3</v>
@@ -26583,25 +26583,25 @@
         <v>2.2</v>
       </c>
       <c r="AN123">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="AO123">
-        <v>0.87</v>
+        <v>0.14</v>
       </c>
       <c r="AP123">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ123">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR123">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AS123">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AT123">
-        <v>3.01</v>
+        <v>3.27</v>
       </c>
       <c r="AU123">
         <v>8</v>
@@ -26789,25 +26789,25 @@
         <v>1.99</v>
       </c>
       <c r="AN124">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AO124">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AP124">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ124">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR124">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AS124">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AT124">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AU124">
         <v>13</v>
@@ -26995,25 +26995,25 @@
         <v>1.44</v>
       </c>
       <c r="AN125">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AO125">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="AP125">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ125">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR125">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AS125">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AT125">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -27201,25 +27201,25 @@
         <v>1.41</v>
       </c>
       <c r="AN126">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO126">
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ126">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR126">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS126">
-        <v>1.77</v>
+        <v>1.38</v>
       </c>
       <c r="AT126">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27407,25 +27407,25 @@
         <v>1.36</v>
       </c>
       <c r="AN127">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="AO127">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AP127">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AR127">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AS127">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AT127">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27613,25 +27613,25 @@
         <v>1.33</v>
       </c>
       <c r="AN128">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AO128">
+        <v>1.67</v>
+      </c>
+      <c r="AP128">
+        <v>1.14</v>
+      </c>
+      <c r="AQ128">
         <v>1.6</v>
       </c>
-      <c r="AP128">
-        <v>1.1</v>
-      </c>
-      <c r="AQ128">
-        <v>1.76</v>
-      </c>
       <c r="AR128">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS128">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="AT128">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="AU128">
         <v>3</v>
@@ -27819,25 +27819,25 @@
         <v>1.17</v>
       </c>
       <c r="AN129">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AO129">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ129">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR129">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="AS129">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="AT129">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="AU129">
         <v>5</v>
@@ -28028,22 +28028,22 @@
         <v>1.38</v>
       </c>
       <c r="AO130">
-        <v>0.8100000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="AP130">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AQ130">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR130">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AS130">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AT130">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="AU130">
         <v>6</v>
@@ -28231,25 +28231,25 @@
         <v>1.56</v>
       </c>
       <c r="AN131">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AO131">
         <v>1.25</v>
       </c>
       <c r="AP131">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AQ131">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR131">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AS131">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AT131">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="AU131">
         <v>0</v>
@@ -28437,25 +28437,25 @@
         <v>1.28</v>
       </c>
       <c r="AN132">
-        <v>0.8100000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="AO132">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AP132">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ132">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AR132">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AS132">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AT132">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="AU132">
         <v>5</v>
@@ -28643,25 +28643,25 @@
         <v>1.7</v>
       </c>
       <c r="AN133">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AO133">
+        <v>1.25</v>
+      </c>
+      <c r="AP133">
+        <v>1.93</v>
+      </c>
+      <c r="AQ133">
+        <v>1.14</v>
+      </c>
+      <c r="AR133">
+        <v>1.85</v>
+      </c>
+      <c r="AS133">
         <v>1.44</v>
       </c>
-      <c r="AP133">
-        <v>1.76</v>
-      </c>
-      <c r="AQ133">
-        <v>1.59</v>
-      </c>
-      <c r="AR133">
-        <v>1.6</v>
-      </c>
-      <c r="AS133">
-        <v>1.49</v>
-      </c>
       <c r="AT133">
-        <v>3.09</v>
+        <v>3.29</v>
       </c>
       <c r="AU133">
         <v>3</v>
@@ -28852,22 +28852,22 @@
         <v>1.5</v>
       </c>
       <c r="AO134">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AP134">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ134">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR134">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="AS134">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AT134">
-        <v>3.09</v>
+        <v>3.33</v>
       </c>
       <c r="AU134">
         <v>8</v>
@@ -29055,25 +29055,25 @@
         <v>1.62</v>
       </c>
       <c r="AN135">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO135">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AP135">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ135">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR135">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AS135">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AT135">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AU135">
         <v>4</v>
@@ -29261,25 +29261,25 @@
         <v>1.46</v>
       </c>
       <c r="AN136">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AO136">
-        <v>1.25</v>
+        <v>0.57</v>
       </c>
       <c r="AP136">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ136">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR136">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AS136">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AT136">
-        <v>2.89</v>
+        <v>3.17</v>
       </c>
       <c r="AU136">
         <v>4</v>
@@ -29467,25 +29467,25 @@
         <v>1.25</v>
       </c>
       <c r="AN137">
+        <v>1.5</v>
+      </c>
+      <c r="AO137">
         <v>1.13</v>
       </c>
-      <c r="AO137">
-        <v>1.56</v>
-      </c>
       <c r="AP137">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ137">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR137">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AS137">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AT137">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AU137">
         <v>6</v>
@@ -29673,25 +29673,25 @@
         <v>1.34</v>
       </c>
       <c r="AN138">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AO138">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="AP138">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ138">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR138">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AS138">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT138">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="AU138">
         <v>4</v>
@@ -29879,25 +29879,25 @@
         <v>1.72</v>
       </c>
       <c r="AN139">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AO139">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AP139">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ139">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AR139">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AS139">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AT139">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="AU139">
         <v>6</v>
@@ -30085,25 +30085,25 @@
         <v>1.37</v>
       </c>
       <c r="AN140">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AO140">
-        <v>0.9399999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="AP140">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ140">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR140">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AS140">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AT140">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="AU140">
         <v>7</v>
@@ -30291,25 +30291,25 @@
         <v>1.42</v>
       </c>
       <c r="AN141">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AO141">
-        <v>1.24</v>
+        <v>0.63</v>
       </c>
       <c r="AP141">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ141">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR141">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AS141">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AT141">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AU141">
         <v>7</v>
@@ -30497,25 +30497,25 @@
         <v>1.47</v>
       </c>
       <c r="AN142">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="AO142">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AP142">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ142">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AR142">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AS142">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AT142">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AU142">
         <v>4</v>
@@ -30703,25 +30703,25 @@
         <v>1.42</v>
       </c>
       <c r="AN143">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AO143">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AP143">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ143">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR143">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AS143">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="AT143">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="AU143">
         <v>6</v>
@@ -30909,25 +30909,25 @@
         <v>1.83</v>
       </c>
       <c r="AN144">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AO144">
-        <v>1.06</v>
+        <v>0.75</v>
       </c>
       <c r="AP144">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ144">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR144">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AS144">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AT144">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="AU144">
         <v>8</v>
@@ -31115,25 +31115,25 @@
         <v>1.21</v>
       </c>
       <c r="AN145">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AO145">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ145">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR145">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AS145">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="AT145">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AU145">
         <v>4</v>
@@ -31321,25 +31321,25 @@
         <v>1.41</v>
       </c>
       <c r="AN146">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AO146">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AP146">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AQ146">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="AR146">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AS146">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AT146">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="AU146">
         <v>5</v>
@@ -31527,25 +31527,25 @@
         <v>1.32</v>
       </c>
       <c r="AN147">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO147">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AP147">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ147">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR147">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AS147">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AT147">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AU147">
         <v>4</v>
@@ -31733,25 +31733,25 @@
         <v>1.27</v>
       </c>
       <c r="AN148">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AO148">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ148">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR148">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AS148">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT148">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="AU148">
         <v>4</v>
@@ -31939,25 +31939,25 @@
         <v>1.64</v>
       </c>
       <c r="AN149">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO149">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP149">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ149">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR149">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AS149">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AT149">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="AU149">
         <v>7</v>
@@ -32145,25 +32145,25 @@
         <v>1.42</v>
       </c>
       <c r="AN150">
-        <v>1.17</v>
+        <v>1.78</v>
       </c>
       <c r="AO150">
-        <v>1.17</v>
+        <v>0.89</v>
       </c>
       <c r="AP150">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ150">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR150">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AS150">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT150">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="AU150">
         <v>5</v>
@@ -32354,22 +32354,22 @@
         <v>1.67</v>
       </c>
       <c r="AO151">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP151">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ151">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR151">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AS151">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AT151">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="AU151">
         <v>9</v>
@@ -32557,25 +32557,25 @@
         <v>1.38</v>
       </c>
       <c r="AN152">
-        <v>1.06</v>
+        <v>1.67</v>
       </c>
       <c r="AO152">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AP152">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ152">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR152">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AS152">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AT152">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="AU152">
         <v>5</v>
@@ -32763,25 +32763,25 @@
         <v>1.35</v>
       </c>
       <c r="AN153">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AO153">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AP153">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ153">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR153">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AS153">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="AT153">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="AU153">
         <v>6</v>
@@ -32969,25 +32969,25 @@
         <v>1.44</v>
       </c>
       <c r="AN154">
-        <v>0.95</v>
+        <v>1.33</v>
       </c>
       <c r="AO154">
-        <v>1.16</v>
+        <v>0.44</v>
       </c>
       <c r="AP154">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ154">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR154">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="AS154">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AT154">
-        <v>2.67</v>
+        <v>2.99</v>
       </c>
       <c r="AU154">
         <v>5</v>
@@ -33175,25 +33175,25 @@
         <v>1.78</v>
       </c>
       <c r="AN155">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AO155">
-        <v>1.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP155">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ155">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR155">
         <v>1.16</v>
       </c>
       <c r="AS155">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AT155">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AU155">
         <v>8</v>
@@ -33381,25 +33381,25 @@
         <v>1.66</v>
       </c>
       <c r="AN156">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AO156">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ156">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR156">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AS156">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AT156">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="AU156">
         <v>4</v>
@@ -33587,25 +33587,25 @@
         <v>1.68</v>
       </c>
       <c r="AN157">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AO157">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AP157">
+        <v>2.13</v>
+      </c>
+      <c r="AQ157">
+        <v>1.14</v>
+      </c>
+      <c r="AR157">
         <v>1.79</v>
       </c>
-      <c r="AQ157">
-        <v>1.41</v>
-      </c>
-      <c r="AR157">
-        <v>1.68</v>
-      </c>
       <c r="AS157">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AT157">
-        <v>3.16</v>
+        <v>3.31</v>
       </c>
       <c r="AU157">
         <v>7</v>
@@ -33793,25 +33793,25 @@
         <v>1.65</v>
       </c>
       <c r="AN158">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AO158">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AP158">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ158">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AR158">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AS158">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AT158">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="AU158">
         <v>7</v>
@@ -33999,25 +33999,25 @@
         <v>1.17</v>
       </c>
       <c r="AN159">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AO159">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AP159">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ159">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR159">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AS159">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AT159">
-        <v>2.91</v>
+        <v>2.68</v>
       </c>
       <c r="AU159">
         <v>3</v>
@@ -34205,25 +34205,25 @@
         <v>1.27</v>
       </c>
       <c r="AN160">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="AO160">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AP160">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AQ160">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR160">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AS160">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="AT160">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="AU160">
         <v>7</v>
@@ -34411,25 +34411,25 @@
         <v>2.29</v>
       </c>
       <c r="AN161">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AO161">
-        <v>0.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP161">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ161">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR161">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AS161">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AT161">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AU161">
         <v>6</v>
@@ -34617,25 +34617,25 @@
         <v>1.43</v>
       </c>
       <c r="AN162">
+        <v>1.7</v>
+      </c>
+      <c r="AO162">
+        <v>1.6</v>
+      </c>
+      <c r="AP162">
+        <v>1.67</v>
+      </c>
+      <c r="AQ162">
+        <v>1.5</v>
+      </c>
+      <c r="AR162">
         <v>1.45</v>
       </c>
-      <c r="AO162">
-        <v>1.8</v>
-      </c>
-      <c r="AP162">
-        <v>1.41</v>
-      </c>
-      <c r="AQ162">
-        <v>1.76</v>
-      </c>
-      <c r="AR162">
-        <v>1.47</v>
-      </c>
       <c r="AS162">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT162">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="AU162">
         <v>0</v>
@@ -34823,25 +34823,25 @@
         <v>1.55</v>
       </c>
       <c r="AN163">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AO163">
-        <v>1.15</v>
+        <v>0.9</v>
       </c>
       <c r="AP163">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ163">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR163">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AS163">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AT163">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="AU163">
         <v>3</v>
@@ -35029,25 +35029,25 @@
         <v>1.16</v>
       </c>
       <c r="AN164">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="AO164">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AP164">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ164">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR164">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AS164">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AT164">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="AU164">
         <v>5</v>
@@ -35235,25 +35235,25 @@
         <v>1.8</v>
       </c>
       <c r="AN165">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO165">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AP165">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ165">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR165">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AS165">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AT165">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AU165">
         <v>8</v>
@@ -35441,25 +35441,25 @@
         <v>1.94</v>
       </c>
       <c r="AN166">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO166">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AP166">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AQ166">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR166">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AS166">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AT166">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="AU166">
         <v>5</v>
@@ -35647,25 +35647,25 @@
         <v>1.37</v>
       </c>
       <c r="AN167">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AO167">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AP167">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ167">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="AR167">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AS167">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AT167">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AU167">
         <v>5</v>
@@ -35853,25 +35853,25 @@
         <v>1.59</v>
       </c>
       <c r="AN168">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AO168">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="AP168">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ168">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR168">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AS168">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AT168">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="AU168">
         <v>7</v>
@@ -36059,25 +36059,25 @@
         <v>1.19</v>
       </c>
       <c r="AN169">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="AO169">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AP169">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ169">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR169">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AS169">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AT169">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="AU169">
         <v>0</v>
@@ -36265,25 +36265,25 @@
         <v>1.3</v>
       </c>
       <c r="AN170">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="AO170">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AP170">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ170">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AR170">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS170">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AT170">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="AU170">
         <v>5</v>
@@ -36471,25 +36471,25 @@
         <v>2.34</v>
       </c>
       <c r="AN171">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AO171">
-        <v>1.24</v>
+        <v>0.7</v>
       </c>
       <c r="AP171">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ171">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR171">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AS171">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AT171">
-        <v>3.08</v>
+        <v>3.37</v>
       </c>
       <c r="AU171">
         <v>9</v>
@@ -36677,25 +36677,25 @@
         <v>2.08</v>
       </c>
       <c r="AN172">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AO172">
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="AP172">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ172">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR172">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AS172">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AT172">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="AU172">
         <v>11</v>
@@ -36883,25 +36883,25 @@
         <v>1.42</v>
       </c>
       <c r="AN173">
+        <v>1.1</v>
+      </c>
+      <c r="AO173">
+        <v>1.3</v>
+      </c>
+      <c r="AP173">
         <v>1.14</v>
       </c>
-      <c r="AO173">
-        <v>1.48</v>
-      </c>
-      <c r="AP173">
-        <v>1.1</v>
-      </c>
       <c r="AQ173">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AR173">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AS173">
         <v>1.33</v>
       </c>
       <c r="AT173">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="AU173">
         <v>2</v>
@@ -37089,25 +37089,25 @@
         <v>1.2</v>
       </c>
       <c r="AN174">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AO174">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AP174">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ174">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR174">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AS174">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AT174">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="AU174">
         <v>8</v>
@@ -37295,25 +37295,25 @@
         <v>1.88</v>
       </c>
       <c r="AN175">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AO175">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AP175">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ175">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR175">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AS175">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AT175">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="AU175">
         <v>8</v>
@@ -37501,25 +37501,25 @@
         <v>1.62</v>
       </c>
       <c r="AN176">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AO176">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AQ176">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR176">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AS176">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AT176">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="AU176">
         <v>11</v>
@@ -37707,25 +37707,25 @@
         <v>2.11</v>
       </c>
       <c r="AN177">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AO177">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AP177">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ177">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR177">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AS177">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AT177">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="AU177">
         <v>8</v>
@@ -37913,25 +37913,25 @@
         <v>1.45</v>
       </c>
       <c r="AN178">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AO178">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AP178">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ178">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR178">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AS178">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AT178">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="AU178">
         <v>6</v>
@@ -38119,25 +38119,25 @@
         <v>1.43</v>
       </c>
       <c r="AN179">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AO179">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AP179">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ179">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AR179">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AS179">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AT179">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="AU179">
         <v>4</v>
@@ -38325,25 +38325,25 @@
         <v>1.47</v>
       </c>
       <c r="AN180">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="AO180">
-        <v>1.23</v>
+        <v>0.73</v>
       </c>
       <c r="AP180">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ180">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR180">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AS180">
         <v>1.24</v>
       </c>
       <c r="AT180">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AU180">
         <v>5</v>
@@ -38531,25 +38531,25 @@
         <v>1.47</v>
       </c>
       <c r="AN181">
+        <v>1.82</v>
+      </c>
+      <c r="AO181">
         <v>1.45</v>
       </c>
-      <c r="AO181">
-        <v>1.64</v>
-      </c>
       <c r="AP181">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ181">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR181">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AS181">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AT181">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="AU181">
         <v>5</v>
@@ -38737,25 +38737,25 @@
         <v>1.95</v>
       </c>
       <c r="AN182">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AO182">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AP182">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AQ182">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR182">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AS182">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AT182">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="AU182">
         <v>8</v>
@@ -38943,25 +38943,25 @@
         <v>1.17</v>
       </c>
       <c r="AN183">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AO183">
         <v>1.73</v>
       </c>
       <c r="AP183">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ183">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR183">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AS183">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AT183">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="AU183">
         <v>3</v>
@@ -39149,25 +39149,25 @@
         <v>1.69</v>
       </c>
       <c r="AN184">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AO184">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AP184">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ184">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR184">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AS184">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AT184">
-        <v>2.76</v>
+        <v>2.49</v>
       </c>
       <c r="AU184">
         <v>5</v>
@@ -39358,22 +39358,22 @@
         <v>1.64</v>
       </c>
       <c r="AO185">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AP185">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AQ185">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR185">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AS185">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AT185">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AU185">
         <v>11</v>
@@ -39561,25 +39561,25 @@
         <v>1.53</v>
       </c>
       <c r="AN186">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AO186">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP186">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ186">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR186">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AS186">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AT186">
-        <v>2.68</v>
+        <v>2.43</v>
       </c>
       <c r="AU186">
         <v>2</v>
@@ -39770,22 +39770,22 @@
         <v>1.09</v>
       </c>
       <c r="AO187">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AP187">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ187">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR187">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AS187">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AT187">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="AU187">
         <v>4</v>
@@ -39973,25 +39973,25 @@
         <v>1.34</v>
       </c>
       <c r="AN188">
-        <v>0.83</v>
+        <v>1.18</v>
       </c>
       <c r="AO188">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AP188">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ188">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AR188">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="AS188">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AT188">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AU188">
         <v>10</v>
@@ -40182,22 +40182,22 @@
         <v>1.09</v>
       </c>
       <c r="AO189">
-        <v>0.83</v>
+        <v>0.45</v>
       </c>
       <c r="AP189">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ189">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR189">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AS189">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AT189">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="AU189">
         <v>8</v>
@@ -40385,25 +40385,25 @@
         <v>1.45</v>
       </c>
       <c r="AN190">
-        <v>1.78</v>
+        <v>2.09</v>
       </c>
       <c r="AO190">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="AP190">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ190">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="AR190">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AS190">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AT190">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="AU190">
         <v>6</v>
@@ -40591,25 +40591,25 @@
         <v>2.55</v>
       </c>
       <c r="AN191">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AO191">
-        <v>0.96</v>
+        <v>0.45</v>
       </c>
       <c r="AP191">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ191">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR191">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AS191">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AT191">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU191">
         <v>8</v>
@@ -40797,25 +40797,25 @@
         <v>1.67</v>
       </c>
       <c r="AN192">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AO192">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AP192">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ192">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR192">
-        <v>1.84</v>
+        <v>2.13</v>
       </c>
       <c r="AS192">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="AT192">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="AU192">
         <v>4</v>
@@ -41003,25 +41003,25 @@
         <v>1.49</v>
       </c>
       <c r="AN193">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AO193">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AP193">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AQ193">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AR193">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="AS193">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AT193">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AU193">
         <v>3</v>
@@ -41209,25 +41209,25 @@
         <v>1.47</v>
       </c>
       <c r="AN194">
-        <v>0.79</v>
+        <v>1.17</v>
       </c>
       <c r="AO194">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="AP194">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ194">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR194">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AS194">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AT194">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="AU194">
         <v>2</v>
@@ -41415,25 +41415,25 @@
         <v>2.43</v>
       </c>
       <c r="AN195">
-        <v>1.46</v>
+        <v>1.92</v>
       </c>
       <c r="AO195">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AP195">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ195">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR195">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AS195">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AT195">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="AU195">
         <v>12</v>
@@ -41621,25 +41621,25 @@
         <v>1.96</v>
       </c>
       <c r="AN196">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AO196">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AP196">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ196">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR196">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AS196">
         <v>1.36</v>
       </c>
       <c r="AT196">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AU196">
         <v>5</v>
@@ -41827,25 +41827,25 @@
         <v>2.09</v>
       </c>
       <c r="AN197">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AO197">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="AP197">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AQ197">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AR197">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AS197">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AT197">
-        <v>2.85</v>
+        <v>3.17</v>
       </c>
       <c r="AU197">
         <v>2</v>
@@ -42033,25 +42033,25 @@
         <v>1.56</v>
       </c>
       <c r="AN198">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AO198">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AP198">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ198">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AR198">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AS198">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AT198">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AU198">
         <v>6</v>
@@ -42239,25 +42239,25 @@
         <v>1.49</v>
       </c>
       <c r="AN199">
-        <v>0.92</v>
+        <v>1.42</v>
       </c>
       <c r="AO199">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP199">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ199">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR199">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AS199">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AT199">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="AU199">
         <v>2</v>
@@ -42445,25 +42445,25 @@
         <v>1.66</v>
       </c>
       <c r="AN200">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AO200">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="AP200">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AQ200">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR200">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AS200">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AT200">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AU200">
         <v>5</v>
@@ -42651,25 +42651,25 @@
         <v>1.21</v>
       </c>
       <c r="AN201">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AO201">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AP201">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ201">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR201">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AS201">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AT201">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="AU201">
         <v>0</v>
@@ -42857,25 +42857,25 @@
         <v>1.29</v>
       </c>
       <c r="AN202">
-        <v>0.92</v>
+        <v>1.17</v>
       </c>
       <c r="AO202">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AP202">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ202">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR202">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AS202">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AT202">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="AU202">
         <v>4</v>
@@ -43066,22 +43066,22 @@
         <v>1</v>
       </c>
       <c r="AO203">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AP203">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ203">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR203">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AS203">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AT203">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="AU203">
         <v>2</v>
@@ -43269,25 +43269,25 @@
         <v>0</v>
       </c>
       <c r="AN204">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AO204">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="AP204">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ204">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="AR204">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AS204">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AT204">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="AU204">
         <v>4</v>
@@ -43475,25 +43475,25 @@
         <v>1.58</v>
       </c>
       <c r="AN205">
+        <v>1.67</v>
+      </c>
+      <c r="AO205">
+        <v>1.17</v>
+      </c>
+      <c r="AP205">
+        <v>1.71</v>
+      </c>
+      <c r="AQ205">
+        <v>1</v>
+      </c>
+      <c r="AR205">
         <v>1.24</v>
       </c>
-      <c r="AO205">
-        <v>1.44</v>
-      </c>
-      <c r="AP205">
-        <v>1.36</v>
-      </c>
-      <c r="AQ205">
-        <v>1.28</v>
-      </c>
-      <c r="AR205">
-        <v>1.26</v>
-      </c>
       <c r="AS205">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AT205">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AU205">
         <v>3</v>
@@ -43681,25 +43681,25 @@
         <v>2.8</v>
       </c>
       <c r="AN206">
-        <v>1.76</v>
+        <v>2.17</v>
       </c>
       <c r="AO206">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="AP206">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ206">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR206">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AS206">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AT206">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AU206">
         <v>3</v>
@@ -43887,25 +43887,25 @@
         <v>2.15</v>
       </c>
       <c r="AN207">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AO207">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="AP207">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ207">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AR207">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AS207">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AT207">
-        <v>3.27</v>
+        <v>3.56</v>
       </c>
       <c r="AU207">
         <v>13</v>
@@ -44093,25 +44093,25 @@
         <v>1.9</v>
       </c>
       <c r="AN208">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="AO208">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="AP208">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AQ208">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR208">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AS208">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AT208">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AU208">
         <v>4</v>
@@ -44299,25 +44299,25 @@
         <v>1.23</v>
       </c>
       <c r="AN209">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AO209">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AP209">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ209">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR209">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AS209">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AT209">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="AU209">
         <v>2</v>
@@ -44505,25 +44505,25 @@
         <v>1.63</v>
       </c>
       <c r="AN210">
+        <v>1.85</v>
+      </c>
+      <c r="AO210">
+        <v>0.85</v>
+      </c>
+      <c r="AP210">
+        <v>1.67</v>
+      </c>
+      <c r="AQ210">
+        <v>1</v>
+      </c>
+      <c r="AR210">
         <v>1.42</v>
       </c>
-      <c r="AO210">
-        <v>1.23</v>
-      </c>
-      <c r="AP210">
-        <v>1.41</v>
-      </c>
-      <c r="AQ210">
-        <v>1.36</v>
-      </c>
-      <c r="AR210">
-        <v>1.45</v>
-      </c>
       <c r="AS210">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AT210">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AU210">
         <v>5</v>
@@ -44711,25 +44711,25 @@
         <v>2.28</v>
       </c>
       <c r="AN211">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AO211">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AP211">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ211">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR211">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AS211">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AT211">
-        <v>3.03</v>
+        <v>3.11</v>
       </c>
       <c r="AU211">
         <v>6</v>
@@ -44917,25 +44917,25 @@
         <v>1.66</v>
       </c>
       <c r="AN212">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AO212">
         <v>1.15</v>
       </c>
       <c r="AP212">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AQ212">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AR212">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AS212">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AT212">
-        <v>2.71</v>
+        <v>2.52</v>
       </c>
       <c r="AU212">
         <v>4</v>
@@ -45123,25 +45123,25 @@
         <v>1.73</v>
       </c>
       <c r="AN213">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AO213">
-        <v>1.19</v>
+        <v>0.77</v>
       </c>
       <c r="AP213">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AQ213">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR213">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AS213">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AT213">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="AU213">
         <v>6</v>
@@ -45329,25 +45329,25 @@
         <v>1.17</v>
       </c>
       <c r="AN214">
-        <v>0.88</v>
+        <v>1.31</v>
       </c>
       <c r="AO214">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AP214">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ214">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR214">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AS214">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AT214">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="AU214">
         <v>7</v>
@@ -45535,25 +45535,25 @@
         <v>1.1</v>
       </c>
       <c r="AN215">
-        <v>0.73</v>
+        <v>1.08</v>
       </c>
       <c r="AO215">
         <v>1.77</v>
       </c>
       <c r="AP215">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="AQ215">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR215">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AS215">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AT215">
-        <v>3.13</v>
+        <v>3.02</v>
       </c>
       <c r="AU215">
         <v>3</v>
@@ -45741,25 +45741,25 @@
         <v>2.6</v>
       </c>
       <c r="AN216">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="AO216">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AP216">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ216">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AR216">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AS216">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AT216">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AU216">
         <v>8</v>
@@ -45947,25 +45947,25 @@
         <v>2.23</v>
       </c>
       <c r="AN217">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO217">
-        <v>0.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP217">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ217">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR217">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AS217">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AT217">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="AU217">
         <v>2</v>
@@ -46153,43 +46153,43 @@
         <v>2.07</v>
       </c>
       <c r="AN218">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AO218">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="AP218">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AQ218">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="AR218">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AS218">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AT218">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="AU218">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AV218">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AW218">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="AX218">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="AY218">
-        <v>18</v>
+        <v>-1</v>
       </c>
       <c r="AZ218">
-        <v>16</v>
+        <v>-1</v>
       </c>
       <c r="BA218">
         <v>8</v>
@@ -46359,43 +46359,43 @@
         <v>1.3</v>
       </c>
       <c r="AN219">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AO219">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="AP219">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ219">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AR219">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AS219">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AT219">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="AU219">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AV219">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="AW219">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="AX219">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AY219">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="AZ219">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="BA219">
         <v>1</v>
@@ -46565,43 +46565,43 @@
         <v>1.25</v>
       </c>
       <c r="AN220">
-        <v>0.89</v>
+        <v>1.15</v>
       </c>
       <c r="AO220">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AP220">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="AQ220">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AR220">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AS220">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AT220">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="AU220">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="AV220">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AW220">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AX220">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="AY220">
-        <v>13</v>
+        <v>-1</v>
       </c>
       <c r="AZ220">
-        <v>13</v>
+        <v>-1</v>
       </c>
       <c r="BA220">
         <v>4</v>
@@ -46771,43 +46771,43 @@
         <v>2.4</v>
       </c>
       <c r="AN221">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AO221">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AP221">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AQ221">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AR221">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AS221">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AT221">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="AU221">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="AV221">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AW221">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AX221">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="AY221">
-        <v>16</v>
+        <v>-1</v>
       </c>
       <c r="AZ221">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="BA221">
         <v>8</v>
@@ -46977,43 +46977,43 @@
         <v>1.5</v>
       </c>
       <c r="AN222">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AO222">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
       <c r="AP222">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ222">
-        <v>0.97</v>
+        <v>0.5</v>
       </c>
       <c r="AR222">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AS222">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AT222">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AU222">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="AV222">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AW222">
-        <v>13</v>
+        <v>-1</v>
       </c>
       <c r="AX222">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AY222">
-        <v>20</v>
+        <v>-1</v>
       </c>
       <c r="AZ222">
-        <v>13</v>
+        <v>-1</v>
       </c>
       <c r="BA222">
         <v>3</v>
@@ -47183,43 +47183,43 @@
         <v>1.99</v>
       </c>
       <c r="AN223">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AO223">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AP223">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ223">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AR223">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AS223">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AT223">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="AU223">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AV223">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AW223">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AX223">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="AY223">
-        <v>13</v>
+        <v>-1</v>
       </c>
       <c r="AZ223">
-        <v>13</v>
+        <v>-1</v>
       </c>
       <c r="BA223">
         <v>4</v>
@@ -47389,25 +47389,25 @@
         <v>1.43</v>
       </c>
       <c r="AN224">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AO224">
-        <v>1.37</v>
+        <v>1</v>
       </c>
       <c r="AP224">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AQ224">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AR224">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AS224">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AT224">
-        <v>2.85</v>
+        <v>3.03</v>
       </c>
       <c r="AU224">
         <v>5</v>
@@ -47595,25 +47595,25 @@
         <v>1.38</v>
       </c>
       <c r="AN225">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="AO225">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AP225">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AQ225">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="AR225">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AS225">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AT225">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="AU225">
         <v>5</v>
@@ -47804,19 +47804,19 @@
         <v>0.93</v>
       </c>
       <c r="AO226">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="AP226">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AQ226">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AR226">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AS226">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AT226">
         <v>2.65</v>
@@ -48007,25 +48007,25 @@
         <v>1.33</v>
       </c>
       <c r="AN227">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AO227">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AP227">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AQ227">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR227">
         <v>1.44</v>
       </c>
       <c r="AS227">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AT227">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="AU227">
         <v>7</v>
@@ -48213,25 +48213,25 @@
         <v>2.12</v>
       </c>
       <c r="AN228">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AO228">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="AP228">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AQ228">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="AR228">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AS228">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AT228">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="AU228">
         <v>3</v>
@@ -48419,25 +48419,25 @@
         <v>2.43</v>
       </c>
       <c r="AN229">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AO229">
-        <v>1.21</v>
+        <v>0.93</v>
       </c>
       <c r="AP229">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ229">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AR229">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AS229">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AT229">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="AU229">
         <v>6</v>
@@ -48625,25 +48625,25 @@
         <v>1.36</v>
       </c>
       <c r="AN230">
-        <v>0.89</v>
+        <v>1.29</v>
       </c>
       <c r="AO230">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AP230">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="AQ230">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="AR230">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AS230">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AT230">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="AU230">
         <v>5</v>
@@ -48831,25 +48831,25 @@
         <v>1.38</v>
       </c>
       <c r="AN231">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AO231">
         <v>1.86</v>
       </c>
       <c r="AP231">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AQ231">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR231">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AS231">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AT231">
-        <v>3.45</v>
+        <v>3.39</v>
       </c>
       <c r="AU231">
         <v>3</v>
@@ -48916,6 +48916,212 @@
       </c>
       <c r="BP231">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7486708</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45719.5</v>
+      </c>
+      <c r="F232">
+        <v>29</v>
+      </c>
+      <c r="G232" t="s">
+        <v>84</v>
+      </c>
+      <c r="H232" t="s">
+        <v>73</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>0</v>
+      </c>
+      <c r="L232">
+        <v>1</v>
+      </c>
+      <c r="M232">
+        <v>1</v>
+      </c>
+      <c r="N232">
+        <v>2</v>
+      </c>
+      <c r="O232" t="s">
+        <v>98</v>
+      </c>
+      <c r="P232" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q232">
+        <v>3.4</v>
+      </c>
+      <c r="R232">
+        <v>1.91</v>
+      </c>
+      <c r="S232">
+        <v>3.75</v>
+      </c>
+      <c r="T232">
+        <v>1.57</v>
+      </c>
+      <c r="U232">
+        <v>2.25</v>
+      </c>
+      <c r="V232">
+        <v>3.75</v>
+      </c>
+      <c r="W232">
+        <v>1.25</v>
+      </c>
+      <c r="X232">
+        <v>13</v>
+      </c>
+      <c r="Y232">
+        <v>1.04</v>
+      </c>
+      <c r="Z232">
+        <v>2.66</v>
+      </c>
+      <c r="AA232">
+        <v>3.04</v>
+      </c>
+      <c r="AB232">
+        <v>2.74</v>
+      </c>
+      <c r="AC232">
+        <v>1.04</v>
+      </c>
+      <c r="AD232">
+        <v>6.75</v>
+      </c>
+      <c r="AE232">
+        <v>1.5</v>
+      </c>
+      <c r="AF232">
+        <v>2.3</v>
+      </c>
+      <c r="AG232">
+        <v>2.38</v>
+      </c>
+      <c r="AH232">
+        <v>1.47</v>
+      </c>
+      <c r="AI232">
+        <v>2.2</v>
+      </c>
+      <c r="AJ232">
+        <v>1.62</v>
+      </c>
+      <c r="AK232">
+        <v>1.38</v>
+      </c>
+      <c r="AL232">
+        <v>1.35</v>
+      </c>
+      <c r="AM232">
+        <v>1.46</v>
+      </c>
+      <c r="AN232">
+        <v>1</v>
+      </c>
+      <c r="AO232">
+        <v>1.29</v>
+      </c>
+      <c r="AP232">
+        <v>1</v>
+      </c>
+      <c r="AQ232">
+        <v>1.27</v>
+      </c>
+      <c r="AR232">
+        <v>1.4</v>
+      </c>
+      <c r="AS232">
+        <v>1.25</v>
+      </c>
+      <c r="AT232">
+        <v>2.65</v>
+      </c>
+      <c r="AU232">
+        <v>8</v>
+      </c>
+      <c r="AV232">
+        <v>6</v>
+      </c>
+      <c r="AW232">
+        <v>7</v>
+      </c>
+      <c r="AX232">
+        <v>9</v>
+      </c>
+      <c r="AY232">
+        <v>16</v>
+      </c>
+      <c r="AZ232">
+        <v>16</v>
+      </c>
+      <c r="BA232">
+        <v>7</v>
+      </c>
+      <c r="BB232">
+        <v>3</v>
+      </c>
+      <c r="BC232">
+        <v>10</v>
+      </c>
+      <c r="BD232">
+        <v>1.98</v>
+      </c>
+      <c r="BE232">
+        <v>6.1</v>
+      </c>
+      <c r="BF232">
+        <v>2.02</v>
+      </c>
+      <c r="BG232">
+        <v>1.52</v>
+      </c>
+      <c r="BH232">
+        <v>2.32</v>
+      </c>
+      <c r="BI232">
+        <v>1.87</v>
+      </c>
+      <c r="BJ232">
+        <v>1.79</v>
+      </c>
+      <c r="BK232">
+        <v>2.4</v>
+      </c>
+      <c r="BL232">
+        <v>1.48</v>
+      </c>
+      <c r="BM232">
+        <v>3.2</v>
+      </c>
+      <c r="BN232">
+        <v>1.28</v>
+      </c>
+      <c r="BO232">
+        <v>4.3</v>
+      </c>
+      <c r="BP232">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="319">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -691,6 +691,9 @@
     <t>['45+3']</t>
   </si>
   <si>
+    <t>['47', '65']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -1329,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP232"/>
+  <dimension ref="A1:BP233"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1585,7 +1588,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -2615,7 +2618,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2821,7 +2824,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3439,7 +3442,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3645,7 +3648,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3851,7 +3854,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -4057,7 +4060,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4138,7 +4141,7 @@
         <v>2</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4263,7 +4266,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4341,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4469,7 +4472,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4881,7 +4884,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -5087,7 +5090,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5293,7 +5296,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5705,7 +5708,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5911,7 +5914,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6610,7 +6613,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR26">
         <v>1.29</v>
@@ -6813,7 +6816,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ27">
         <v>0.36</v>
@@ -7353,7 +7356,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7559,7 +7562,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7765,7 +7768,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7971,7 +7974,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8383,7 +8386,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8795,7 +8798,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9413,7 +9416,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9619,7 +9622,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9825,7 +9828,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10855,7 +10858,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -10936,7 +10939,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR47">
         <v>1.66</v>
@@ -11267,7 +11270,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11757,7 +11760,7 @@
         <v>2.33</v>
       </c>
       <c r="AP51">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ51">
         <v>1.43</v>
@@ -12297,7 +12300,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12503,7 +12506,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12915,7 +12918,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13327,7 +13330,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13533,7 +13536,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13945,7 +13948,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14641,7 +14644,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ65">
         <v>0.93</v>
@@ -14975,7 +14978,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15387,7 +15390,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15593,7 +15596,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15674,7 +15677,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -15799,7 +15802,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -16005,7 +16008,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16623,7 +16626,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16829,7 +16832,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17035,7 +17038,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17447,7 +17450,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17734,7 +17737,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ80">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR80">
         <v>1.06</v>
@@ -17859,7 +17862,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -17937,7 +17940,7 @@
         <v>0.6</v>
       </c>
       <c r="AP81">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ81">
         <v>0.8</v>
@@ -18271,7 +18274,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18889,7 +18892,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19713,7 +19716,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19919,7 +19922,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20125,7 +20128,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20331,7 +20334,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20743,7 +20746,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -21030,7 +21033,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR96">
         <v>1.35</v>
@@ -21979,7 +21982,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22057,7 +22060,7 @@
         <v>1.25</v>
       </c>
       <c r="AP101">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ101">
         <v>1.8</v>
@@ -22597,7 +22600,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -23215,7 +23218,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23421,7 +23424,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23833,7 +23836,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24039,7 +24042,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24245,7 +24248,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24451,7 +24454,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24735,7 +24738,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ114">
         <v>1.27</v>
@@ -24863,7 +24866,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -25768,7 +25771,7 @@
         <v>2</v>
       </c>
       <c r="AQ119">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR119">
         <v>1.46</v>
@@ -26099,7 +26102,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26177,7 +26180,7 @@
         <v>1.8</v>
       </c>
       <c r="AP121">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ121">
         <v>1.6</v>
@@ -26305,7 +26308,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26592,7 +26595,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ123">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR123">
         <v>1.82</v>
@@ -27129,7 +27132,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -28159,7 +28162,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28365,7 +28368,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28571,7 +28574,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -29395,7 +29398,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -30013,7 +30016,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30094,7 +30097,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ140">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR140">
         <v>1.45</v>
@@ -30425,7 +30428,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30503,7 +30506,7 @@
         <v>1.38</v>
       </c>
       <c r="AP142">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ142">
         <v>1.14</v>
@@ -30631,7 +30634,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30837,7 +30840,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -31043,7 +31046,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31455,7 +31458,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31661,7 +31664,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31867,7 +31870,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32073,7 +32076,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32691,7 +32694,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32897,7 +32900,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -32978,7 +32981,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ154">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR154">
         <v>1.64</v>
@@ -33181,7 +33184,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP155">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ155">
         <v>0.5</v>
@@ -33515,7 +33518,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -34957,7 +34960,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35369,7 +35372,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35653,7 +35656,7 @@
         <v>1.1</v>
       </c>
       <c r="AP167">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ167">
         <v>1.14</v>
@@ -35987,7 +35990,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36193,7 +36196,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36399,7 +36402,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36480,7 +36483,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ171">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR171">
         <v>2.04</v>
@@ -36605,7 +36608,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -37635,7 +37638,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -38125,7 +38128,7 @@
         <v>1.55</v>
       </c>
       <c r="AP179">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ179">
         <v>1.5</v>
@@ -38253,7 +38256,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38334,7 +38337,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ180">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR180">
         <v>1.37</v>
@@ -39695,7 +39698,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -40107,7 +40110,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40313,7 +40316,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40519,7 +40522,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40931,7 +40934,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -41137,7 +41140,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -41627,7 +41630,7 @@
         <v>1.08</v>
       </c>
       <c r="AP196">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ196">
         <v>1.07</v>
@@ -41836,7 +41839,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ197">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR197">
         <v>1.86</v>
@@ -42785,7 +42788,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -42991,7 +42994,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43403,7 +43406,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43609,7 +43612,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -44227,7 +44230,7 @@
         <v>214</v>
       </c>
       <c r="P209" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q209">
         <v>4.75</v>
@@ -44433,7 +44436,7 @@
         <v>215</v>
       </c>
       <c r="P210" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q210">
         <v>2.8</v>
@@ -44514,7 +44517,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ210">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR210">
         <v>1.42</v>
@@ -44639,7 +44642,7 @@
         <v>216</v>
       </c>
       <c r="P211" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q211">
         <v>2.06</v>
@@ -45051,7 +45054,7 @@
         <v>86</v>
       </c>
       <c r="P213" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q213">
         <v>2.65</v>
@@ -45129,7 +45132,7 @@
         <v>0.77</v>
       </c>
       <c r="AP213">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ213">
         <v>0.87</v>
@@ -45463,7 +45466,7 @@
         <v>86</v>
       </c>
       <c r="P215" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q215">
         <v>6.8</v>
@@ -45669,7 +45672,7 @@
         <v>218</v>
       </c>
       <c r="P216" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q216">
         <v>1.91</v>
@@ -46081,7 +46084,7 @@
         <v>220</v>
       </c>
       <c r="P218" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q218">
         <v>2.18</v>
@@ -46493,7 +46496,7 @@
         <v>221</v>
       </c>
       <c r="P220" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q220">
         <v>4.3</v>
@@ -47317,7 +47320,7 @@
         <v>223</v>
       </c>
       <c r="P224" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q224">
         <v>3.5</v>
@@ -47523,7 +47526,7 @@
         <v>209</v>
       </c>
       <c r="P225" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q225">
         <v>3.6</v>
@@ -47935,7 +47938,7 @@
         <v>156</v>
       </c>
       <c r="P227" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q227">
         <v>3.75</v>
@@ -48141,7 +48144,7 @@
         <v>86</v>
       </c>
       <c r="P228" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q228">
         <v>2.24</v>
@@ -49070,10 +49073,10 @@
         <v>9</v>
       </c>
       <c r="AY232">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ232">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA232">
         <v>7</v>
@@ -49122,6 +49125,212 @@
       </c>
       <c r="BP232">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7486709</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45719.625</v>
+      </c>
+      <c r="F233">
+        <v>29</v>
+      </c>
+      <c r="G233" t="s">
+        <v>83</v>
+      </c>
+      <c r="H233" t="s">
+        <v>71</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>0</v>
+      </c>
+      <c r="L233">
+        <v>2</v>
+      </c>
+      <c r="M233">
+        <v>0</v>
+      </c>
+      <c r="N233">
+        <v>2</v>
+      </c>
+      <c r="O233" t="s">
+        <v>225</v>
+      </c>
+      <c r="P233" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q233">
+        <v>2.5</v>
+      </c>
+      <c r="R233">
+        <v>2</v>
+      </c>
+      <c r="S233">
+        <v>5.5</v>
+      </c>
+      <c r="T233">
+        <v>1.53</v>
+      </c>
+      <c r="U233">
+        <v>2.38</v>
+      </c>
+      <c r="V233">
+        <v>3.5</v>
+      </c>
+      <c r="W233">
+        <v>1.29</v>
+      </c>
+      <c r="X233">
+        <v>11</v>
+      </c>
+      <c r="Y233">
+        <v>1.05</v>
+      </c>
+      <c r="Z233">
+        <v>1.97</v>
+      </c>
+      <c r="AA233">
+        <v>3.15</v>
+      </c>
+      <c r="AB233">
+        <v>4.1</v>
+      </c>
+      <c r="AC233">
+        <v>1.03</v>
+      </c>
+      <c r="AD233">
+        <v>7.2</v>
+      </c>
+      <c r="AE233">
+        <v>1.39</v>
+      </c>
+      <c r="AF233">
+        <v>2.6</v>
+      </c>
+      <c r="AG233">
+        <v>2.25</v>
+      </c>
+      <c r="AH233">
+        <v>1.53</v>
+      </c>
+      <c r="AI233">
+        <v>2.2</v>
+      </c>
+      <c r="AJ233">
+        <v>1.62</v>
+      </c>
+      <c r="AK233">
+        <v>1.19</v>
+      </c>
+      <c r="AL233">
+        <v>1.29</v>
+      </c>
+      <c r="AM233">
+        <v>1.87</v>
+      </c>
+      <c r="AN233">
+        <v>1.86</v>
+      </c>
+      <c r="AO233">
+        <v>1</v>
+      </c>
+      <c r="AP233">
+        <v>1.93</v>
+      </c>
+      <c r="AQ233">
+        <v>0.93</v>
+      </c>
+      <c r="AR233">
+        <v>1.34</v>
+      </c>
+      <c r="AS233">
+        <v>1.26</v>
+      </c>
+      <c r="AT233">
+        <v>2.6</v>
+      </c>
+      <c r="AU233">
+        <v>6</v>
+      </c>
+      <c r="AV233">
+        <v>6</v>
+      </c>
+      <c r="AW233">
+        <v>7</v>
+      </c>
+      <c r="AX233">
+        <v>8</v>
+      </c>
+      <c r="AY233">
+        <v>15</v>
+      </c>
+      <c r="AZ233">
+        <v>17</v>
+      </c>
+      <c r="BA233">
+        <v>6</v>
+      </c>
+      <c r="BB233">
+        <v>3</v>
+      </c>
+      <c r="BC233">
+        <v>9</v>
+      </c>
+      <c r="BD233">
+        <v>1.6</v>
+      </c>
+      <c r="BE233">
+        <v>6.25</v>
+      </c>
+      <c r="BF233">
+        <v>2.65</v>
+      </c>
+      <c r="BG233">
+        <v>1.49</v>
+      </c>
+      <c r="BH233">
+        <v>2.38</v>
+      </c>
+      <c r="BI233">
+        <v>1.83</v>
+      </c>
+      <c r="BJ233">
+        <v>1.83</v>
+      </c>
+      <c r="BK233">
+        <v>2.32</v>
+      </c>
+      <c r="BL233">
+        <v>1.52</v>
+      </c>
+      <c r="BM233">
+        <v>3.05</v>
+      </c>
+      <c r="BN233">
+        <v>1.3</v>
+      </c>
+      <c r="BO233">
+        <v>4.1</v>
+      </c>
+      <c r="BP233">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="321">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -694,6 +694,9 @@
     <t>['47', '65']</t>
   </si>
   <si>
+    <t>['17', '27']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -971,6 +974,9 @@
   </si>
   <si>
     <t>['80']</t>
+  </si>
+  <si>
+    <t>['38', '39', '90+6']</t>
   </si>
 </sst>
 </file>
@@ -1332,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP233"/>
+  <dimension ref="A1:BP234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1588,7 +1594,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -2081,7 +2087,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2618,7 +2624,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2824,7 +2830,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3442,7 +3448,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3648,7 +3654,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3854,7 +3860,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -4060,7 +4066,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4266,7 +4272,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4472,7 +4478,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4756,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ17">
         <v>0.87</v>
@@ -4884,7 +4890,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -5090,7 +5096,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5296,7 +5302,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5708,7 +5714,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5914,7 +5920,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6610,7 +6616,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ26">
         <v>0.93</v>
@@ -7025,7 +7031,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ28">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -7356,7 +7362,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7562,7 +7568,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7768,7 +7774,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7974,7 +7980,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8386,7 +8392,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8798,7 +8804,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9416,7 +9422,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9622,7 +9628,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9828,7 +9834,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10321,7 +10327,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ44">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR44">
         <v>2.23</v>
@@ -10858,7 +10864,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11270,7 +11276,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -12300,7 +12306,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12506,7 +12512,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12790,7 +12796,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ56">
         <v>1.14</v>
@@ -12918,7 +12924,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -12999,7 +13005,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ57">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR57">
         <v>1.23</v>
@@ -13330,7 +13336,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13536,7 +13542,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13948,7 +13954,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14978,7 +14984,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15390,7 +15396,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15596,7 +15602,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15802,7 +15808,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -16008,7 +16014,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16292,7 +16298,7 @@
         <v>0.6</v>
       </c>
       <c r="AP73">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ73">
         <v>1.36</v>
@@ -16626,7 +16632,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16832,7 +16838,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17038,7 +17044,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17325,7 +17331,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ78">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR78">
         <v>1.54</v>
@@ -17450,7 +17456,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17862,7 +17868,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18274,7 +18280,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18892,7 +18898,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19716,7 +19722,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19922,7 +19928,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20003,7 +20009,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ91">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR91">
         <v>1.87</v>
@@ -20128,7 +20134,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20206,7 +20212,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ92">
         <v>1.43</v>
@@ -20334,7 +20340,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20746,7 +20752,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -21982,7 +21988,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22600,7 +22606,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -23093,7 +23099,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ106">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR106">
         <v>1.16</v>
@@ -23218,7 +23224,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23424,7 +23430,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23502,7 +23508,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ108">
         <v>0.93</v>
@@ -23836,7 +23842,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24042,7 +24048,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24248,7 +24254,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24454,7 +24460,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24866,7 +24872,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -25974,7 +25980,7 @@
         <v>0.63</v>
       </c>
       <c r="AP120">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ120">
         <v>0.8</v>
@@ -26102,7 +26108,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26308,7 +26314,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -27132,7 +27138,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27622,7 +27628,7 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ128">
         <v>1.6</v>
@@ -28162,7 +28168,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28368,7 +28374,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28574,7 +28580,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -29273,7 +29279,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ136">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR136">
         <v>1.72</v>
@@ -29398,7 +29404,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -30016,7 +30022,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30303,7 +30309,7 @@
         <v>1</v>
       </c>
       <c r="AQ141">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR141">
         <v>1.41</v>
@@ -30428,7 +30434,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30634,7 +30640,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30840,7 +30846,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -31046,7 +31052,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31124,7 +31130,7 @@
         <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ145">
         <v>1.8</v>
@@ -31458,7 +31464,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31664,7 +31670,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31870,7 +31876,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32076,7 +32082,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32694,7 +32700,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32900,7 +32906,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33187,7 +33193,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ155">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR155">
         <v>1.16</v>
@@ -33390,7 +33396,7 @@
         <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ156">
         <v>1.27</v>
@@ -33518,7 +33524,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -34960,7 +34966,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35372,7 +35378,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35990,7 +35996,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36196,7 +36202,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36402,7 +36408,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36608,7 +36614,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36892,7 +36898,7 @@
         <v>1.3</v>
       </c>
       <c r="AP173">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ173">
         <v>1</v>
@@ -37638,7 +37644,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -37719,7 +37725,7 @@
         <v>2</v>
       </c>
       <c r="AQ177">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR177">
         <v>1.54</v>
@@ -38256,7 +38262,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -39698,7 +39704,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -40110,7 +40116,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40188,7 +40194,7 @@
         <v>0.45</v>
       </c>
       <c r="AP189">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ189">
         <v>0.36</v>
@@ -40316,7 +40322,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40522,7 +40528,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40603,7 +40609,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ191">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR191">
         <v>1.78</v>
@@ -40934,7 +40940,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -41140,7 +41146,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -42788,7 +42794,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -42994,7 +43000,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43278,7 +43284,7 @@
         <v>1</v>
       </c>
       <c r="AP204">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ204">
         <v>1.14</v>
@@ -43406,7 +43412,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43612,7 +43618,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -43693,7 +43699,7 @@
         <v>2</v>
       </c>
       <c r="AQ206">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR206">
         <v>1.62</v>
@@ -44230,7 +44236,7 @@
         <v>214</v>
       </c>
       <c r="P209" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q209">
         <v>4.75</v>
@@ -44436,7 +44442,7 @@
         <v>215</v>
       </c>
       <c r="P210" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q210">
         <v>2.8</v>
@@ -44642,7 +44648,7 @@
         <v>216</v>
       </c>
       <c r="P211" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q211">
         <v>2.06</v>
@@ -45054,7 +45060,7 @@
         <v>86</v>
       </c>
       <c r="P213" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q213">
         <v>2.65</v>
@@ -45466,7 +45472,7 @@
         <v>86</v>
       </c>
       <c r="P215" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q215">
         <v>6.8</v>
@@ -45672,7 +45678,7 @@
         <v>218</v>
       </c>
       <c r="P216" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q216">
         <v>1.91</v>
@@ -46084,7 +46090,7 @@
         <v>220</v>
       </c>
       <c r="P218" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q218">
         <v>2.18</v>
@@ -46368,7 +46374,7 @@
         <v>1.38</v>
       </c>
       <c r="AP219">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ219">
         <v>1.5</v>
@@ -46496,7 +46502,7 @@
         <v>221</v>
       </c>
       <c r="P220" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q220">
         <v>4.3</v>
@@ -46989,7 +46995,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ222">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR222">
         <v>1.35</v>
@@ -47320,7 +47326,7 @@
         <v>223</v>
       </c>
       <c r="P224" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q224">
         <v>3.5</v>
@@ -47526,7 +47532,7 @@
         <v>209</v>
       </c>
       <c r="P225" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q225">
         <v>3.6</v>
@@ -47938,7 +47944,7 @@
         <v>156</v>
       </c>
       <c r="P227" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q227">
         <v>3.75</v>
@@ -48144,7 +48150,7 @@
         <v>86</v>
       </c>
       <c r="P228" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q228">
         <v>2.24</v>
@@ -49331,6 +49337,212 @@
       </c>
       <c r="BP233">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7486719</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45723.5</v>
+      </c>
+      <c r="F234">
+        <v>30</v>
+      </c>
+      <c r="G234" t="s">
+        <v>85</v>
+      </c>
+      <c r="H234" t="s">
+        <v>78</v>
+      </c>
+      <c r="I234">
+        <v>2</v>
+      </c>
+      <c r="J234">
+        <v>2</v>
+      </c>
+      <c r="K234">
+        <v>4</v>
+      </c>
+      <c r="L234">
+        <v>2</v>
+      </c>
+      <c r="M234">
+        <v>3</v>
+      </c>
+      <c r="N234">
+        <v>5</v>
+      </c>
+      <c r="O234" t="s">
+        <v>226</v>
+      </c>
+      <c r="P234" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q234">
+        <v>2.88</v>
+      </c>
+      <c r="R234">
+        <v>1.98</v>
+      </c>
+      <c r="S234">
+        <v>3.8</v>
+      </c>
+      <c r="T234">
+        <v>1.5</v>
+      </c>
+      <c r="U234">
+        <v>2.48</v>
+      </c>
+      <c r="V234">
+        <v>3.4</v>
+      </c>
+      <c r="W234">
+        <v>1.29</v>
+      </c>
+      <c r="X234">
+        <v>8</v>
+      </c>
+      <c r="Y234">
+        <v>1.04</v>
+      </c>
+      <c r="Z234">
+        <v>1.89</v>
+      </c>
+      <c r="AA234">
+        <v>3.28</v>
+      </c>
+      <c r="AB234">
+        <v>4.2</v>
+      </c>
+      <c r="AC234">
+        <v>0</v>
+      </c>
+      <c r="AD234">
+        <v>0</v>
+      </c>
+      <c r="AE234">
+        <v>1.5</v>
+      </c>
+      <c r="AF234">
+        <v>2.4</v>
+      </c>
+      <c r="AG234">
+        <v>2.37</v>
+      </c>
+      <c r="AH234">
+        <v>1.48</v>
+      </c>
+      <c r="AI234">
+        <v>1.98</v>
+      </c>
+      <c r="AJ234">
+        <v>1.72</v>
+      </c>
+      <c r="AK234">
+        <v>1.28</v>
+      </c>
+      <c r="AL234">
+        <v>1.31</v>
+      </c>
+      <c r="AM234">
+        <v>1.58</v>
+      </c>
+      <c r="AN234">
+        <v>1.14</v>
+      </c>
+      <c r="AO234">
+        <v>0.5</v>
+      </c>
+      <c r="AP234">
+        <v>1.07</v>
+      </c>
+      <c r="AQ234">
+        <v>0.67</v>
+      </c>
+      <c r="AR234">
+        <v>1.36</v>
+      </c>
+      <c r="AS234">
+        <v>1.35</v>
+      </c>
+      <c r="AT234">
+        <v>2.71</v>
+      </c>
+      <c r="AU234">
+        <v>14</v>
+      </c>
+      <c r="AV234">
+        <v>8</v>
+      </c>
+      <c r="AW234">
+        <v>10</v>
+      </c>
+      <c r="AX234">
+        <v>7</v>
+      </c>
+      <c r="AY234">
+        <v>25</v>
+      </c>
+      <c r="AZ234">
+        <v>16</v>
+      </c>
+      <c r="BA234">
+        <v>10</v>
+      </c>
+      <c r="BB234">
+        <v>6</v>
+      </c>
+      <c r="BC234">
+        <v>16</v>
+      </c>
+      <c r="BD234">
+        <v>1.74</v>
+      </c>
+      <c r="BE234">
+        <v>6.25</v>
+      </c>
+      <c r="BF234">
+        <v>2.33</v>
+      </c>
+      <c r="BG234">
+        <v>1.5</v>
+      </c>
+      <c r="BH234">
+        <v>2.33</v>
+      </c>
+      <c r="BI234">
+        <v>1.85</v>
+      </c>
+      <c r="BJ234">
+        <v>1.81</v>
+      </c>
+      <c r="BK234">
+        <v>2.38</v>
+      </c>
+      <c r="BL234">
+        <v>1.49</v>
+      </c>
+      <c r="BM234">
+        <v>3.15</v>
+      </c>
+      <c r="BN234">
+        <v>1.29</v>
+      </c>
+      <c r="BO234">
+        <v>4.3</v>
+      </c>
+      <c r="BP234">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="322">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -697,6 +697,12 @@
     <t>['17', '27']</t>
   </si>
   <si>
+    <t>['72']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -773,9 +779,6 @@
   </si>
   <si>
     <t>['27', '43']</t>
-  </si>
-  <si>
-    <t>['90+5']</t>
   </si>
   <si>
     <t>['45+3', '82']</t>
@@ -949,9 +952,6 @@
     <t>['51', '53', '72']</t>
   </si>
   <si>
-    <t>['72']</t>
-  </si>
-  <si>
     <t>['24', '59']</t>
   </si>
   <si>
@@ -977,6 +977,9 @@
   </si>
   <si>
     <t>['38', '39', '90+6']</t>
+  </si>
+  <si>
+    <t>['8']</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP234"/>
+  <dimension ref="A1:BP237"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1594,7 +1597,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1672,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ2">
         <v>0.93</v>
@@ -1878,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ3">
         <v>1.43</v>
@@ -2293,7 +2296,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ5">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2499,7 +2502,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2624,7 +2627,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2830,7 +2833,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3114,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ9">
         <v>0.36</v>
@@ -3448,7 +3451,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3654,7 +3657,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3860,7 +3863,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -4066,7 +4069,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4272,7 +4275,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4478,7 +4481,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4559,7 +4562,7 @@
         <v>1</v>
       </c>
       <c r="AQ16">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4890,7 +4893,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -4968,7 +4971,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ18">
         <v>0.93</v>
@@ -5096,7 +5099,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5302,7 +5305,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5714,7 +5717,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5792,7 +5795,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ22">
         <v>0.8</v>
@@ -5920,7 +5923,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6207,7 +6210,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ24">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR24">
         <v>1.56</v>
@@ -6410,10 +6413,10 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ25">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR25">
         <v>0.95</v>
@@ -7028,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ28">
         <v>0.67</v>
@@ -7362,7 +7365,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7443,7 +7446,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR30">
         <v>1.69</v>
@@ -7568,7 +7571,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7774,7 +7777,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7855,7 +7858,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR32">
         <v>1.69</v>
@@ -7980,7 +7983,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8264,7 +8267,7 @@
         <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ34">
         <v>0.8</v>
@@ -8392,7 +8395,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8679,7 +8682,7 @@
         <v>1</v>
       </c>
       <c r="AQ36">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR36">
         <v>1.67</v>
@@ -8804,7 +8807,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9294,10 +9297,10 @@
         <v>1.67</v>
       </c>
       <c r="AP39">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ39">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR39">
         <v>0.8100000000000001</v>
@@ -9422,7 +9425,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9628,7 +9631,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9834,7 +9837,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10739,7 +10742,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR46">
         <v>1.57</v>
@@ -10864,7 +10867,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -10942,7 +10945,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ47">
         <v>0.93</v>
@@ -11148,7 +11151,7 @@
         <v>2.33</v>
       </c>
       <c r="AP48">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ48">
         <v>1.07</v>
@@ -11276,7 +11279,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11357,7 +11360,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ49">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR49">
         <v>1.48</v>
@@ -12178,7 +12181,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ53">
         <v>1.8</v>
@@ -12306,7 +12309,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12387,7 +12390,7 @@
         <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR54">
         <v>1.5</v>
@@ -12512,7 +12515,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12799,7 +12802,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ56">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR56">
         <v>1.46</v>
@@ -12924,7 +12927,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13002,7 +13005,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ57">
         <v>0.67</v>
@@ -13211,7 +13214,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ58">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR58">
         <v>2.03</v>
@@ -13336,7 +13339,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13542,7 +13545,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13620,7 +13623,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ60">
         <v>1.6</v>
@@ -13954,7 +13957,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14984,7 +14987,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15062,7 +15065,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ67">
         <v>0.87</v>
@@ -15396,7 +15399,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15602,7 +15605,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15808,7 +15811,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15889,7 +15892,7 @@
         <v>2</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR71">
         <v>1.35</v>
@@ -16014,7 +16017,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16504,7 +16507,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ74">
         <v>1.6</v>
@@ -16632,7 +16635,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16838,7 +16841,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16916,10 +16919,10 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ76">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR76">
         <v>1.67</v>
@@ -17044,7 +17047,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17456,7 +17459,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17537,7 +17540,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ79">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR79">
         <v>1.52</v>
@@ -17740,7 +17743,7 @@
         <v>0.25</v>
       </c>
       <c r="AP80">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ80">
         <v>0.93</v>
@@ -17868,7 +17871,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18155,7 +18158,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ82">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR82">
         <v>1.61</v>
@@ -18280,7 +18283,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18898,7 +18901,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19594,7 +19597,7 @@
         <v>0.67</v>
       </c>
       <c r="AP89">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ89">
         <v>1.36</v>
@@ -19722,7 +19725,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19803,7 +19806,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ90">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR90">
         <v>1.38</v>
@@ -19928,7 +19931,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20134,7 +20137,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20340,7 +20343,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20418,10 +20421,10 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ93">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR93">
         <v>1.25</v>
@@ -20627,7 +20630,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ94">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR94">
         <v>1.89</v>
@@ -20752,7 +20755,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -21654,7 +21657,7 @@
         <v>1.67</v>
       </c>
       <c r="AP99">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ99">
         <v>1.6</v>
@@ -21988,7 +21991,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22606,7 +22609,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22687,7 +22690,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ104">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR104">
         <v>1.78</v>
@@ -23096,7 +23099,7 @@
         <v>0.67</v>
       </c>
       <c r="AP106">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ106">
         <v>0.67</v>
@@ -23224,7 +23227,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23302,7 +23305,7 @@
         <v>0.71</v>
       </c>
       <c r="AP107">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ107">
         <v>1.36</v>
@@ -23430,7 +23433,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23717,7 +23720,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ109">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR109">
         <v>2.02</v>
@@ -23842,7 +23845,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23923,7 +23926,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ110">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR110">
         <v>1.9</v>
@@ -24048,7 +24051,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24126,7 +24129,7 @@
         <v>1.29</v>
       </c>
       <c r="AP111">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ111">
         <v>1.43</v>
@@ -24254,7 +24257,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24460,7 +24463,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24872,7 +24875,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -26108,7 +26111,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26314,7 +26317,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26395,7 +26398,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ122">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR122">
         <v>1.54</v>
@@ -27138,7 +27141,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -28168,7 +28171,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28246,7 +28249,7 @@
         <v>1.25</v>
       </c>
       <c r="AP131">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ131">
         <v>1.07</v>
@@ -28374,7 +28377,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28452,10 +28455,10 @@
         <v>1.78</v>
       </c>
       <c r="AP132">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ132">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR132">
         <v>1.25</v>
@@ -28580,7 +28583,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28661,7 +28664,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ133">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR133">
         <v>1.85</v>
@@ -29070,7 +29073,7 @@
         <v>1</v>
       </c>
       <c r="AP135">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ135">
         <v>1.36</v>
@@ -29404,7 +29407,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -30022,7 +30025,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30434,7 +30437,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30515,7 +30518,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ142">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR142">
         <v>1.14</v>
@@ -30640,7 +30643,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30846,7 +30849,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -31052,7 +31055,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31339,7 +31342,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ146">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR146">
         <v>1.46</v>
@@ -31464,7 +31467,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31670,7 +31673,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31748,7 +31751,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ148">
         <v>1.43</v>
@@ -31876,7 +31879,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32082,7 +32085,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32572,7 +32575,7 @@
         <v>1.44</v>
       </c>
       <c r="AP152">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ152">
         <v>1.07</v>
@@ -32700,7 +32703,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32906,7 +32909,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33524,7 +33527,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33605,7 +33608,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ157">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR157">
         <v>1.79</v>
@@ -34220,7 +34223,7 @@
         <v>1.67</v>
       </c>
       <c r="AP160">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ160">
         <v>1.8</v>
@@ -34635,7 +34638,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ162">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR162">
         <v>1.45</v>
@@ -34838,7 +34841,7 @@
         <v>0.9</v>
       </c>
       <c r="AP163">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ163">
         <v>0.87</v>
@@ -34966,7 +34969,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35250,7 +35253,7 @@
         <v>1.3</v>
       </c>
       <c r="AP165">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ165">
         <v>0.93</v>
@@ -35378,7 +35381,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35665,7 +35668,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ167">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR167">
         <v>1.24</v>
@@ -35996,7 +35999,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36202,7 +36205,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36283,7 +36286,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ170">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR170">
         <v>1.38</v>
@@ -36408,7 +36411,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36614,7 +36617,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -37516,7 +37519,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ176">
         <v>1.27</v>
@@ -37644,7 +37647,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -38137,7 +38140,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ179">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR179">
         <v>1.24</v>
@@ -38262,7 +38265,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -39164,7 +39167,7 @@
         <v>0.55</v>
       </c>
       <c r="AP184">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ184">
         <v>0.8</v>
@@ -39576,7 +39579,7 @@
         <v>1</v>
       </c>
       <c r="AP186">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ186">
         <v>1.27</v>
@@ -39704,7 +39707,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -39991,7 +39994,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ188">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR188">
         <v>1.69</v>
@@ -40116,7 +40119,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40322,7 +40325,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40403,7 +40406,7 @@
         <v>2</v>
       </c>
       <c r="AQ190">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR190">
         <v>1.64</v>
@@ -40528,7 +40531,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40940,7 +40943,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -41018,7 +41021,7 @@
         <v>1.27</v>
       </c>
       <c r="AP193">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ193">
         <v>1</v>
@@ -41146,7 +41149,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -42051,7 +42054,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ198">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR198">
         <v>1.82</v>
@@ -42666,7 +42669,7 @@
         <v>1.83</v>
       </c>
       <c r="AP201">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ201">
         <v>1.8</v>
@@ -42794,7 +42797,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -43000,7 +43003,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43287,7 +43290,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ204">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR204">
         <v>1.36</v>
@@ -43412,7 +43415,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43490,7 +43493,7 @@
         <v>1.17</v>
       </c>
       <c r="AP205">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ205">
         <v>1</v>
@@ -43618,7 +43621,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -43905,7 +43908,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ207">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR207">
         <v>2.04</v>
@@ -44108,7 +44111,7 @@
         <v>0.42</v>
       </c>
       <c r="AP208">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ208">
         <v>0.36</v>
@@ -44236,7 +44239,7 @@
         <v>214</v>
       </c>
       <c r="P209" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q209">
         <v>4.75</v>
@@ -44442,7 +44445,7 @@
         <v>215</v>
       </c>
       <c r="P210" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q210">
         <v>2.8</v>
@@ -44648,7 +44651,7 @@
         <v>216</v>
       </c>
       <c r="P211" t="s">
-        <v>311</v>
+        <v>227</v>
       </c>
       <c r="Q211">
         <v>2.06</v>
@@ -44932,7 +44935,7 @@
         <v>1.15</v>
       </c>
       <c r="AP212">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ212">
         <v>1.27</v>
@@ -46168,7 +46171,7 @@
         <v>0.38</v>
       </c>
       <c r="AP218">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ218">
         <v>0.36</v>
@@ -46377,7 +46380,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ219">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR219">
         <v>1.36</v>
@@ -47407,7 +47410,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ224">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR224">
         <v>1.55</v>
@@ -47610,10 +47613,10 @@
         <v>1</v>
       </c>
       <c r="AP225">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ225">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR225">
         <v>1.67</v>
@@ -47944,7 +47947,7 @@
         <v>156</v>
       </c>
       <c r="P227" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q227">
         <v>3.75</v>
@@ -49543,6 +49546,624 @@
       </c>
       <c r="BP234">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7486718</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45723.625</v>
+      </c>
+      <c r="F235">
+        <v>30</v>
+      </c>
+      <c r="G235" t="s">
+        <v>70</v>
+      </c>
+      <c r="H235" t="s">
+        <v>82</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>1</v>
+      </c>
+      <c r="K235">
+        <v>1</v>
+      </c>
+      <c r="L235">
+        <v>1</v>
+      </c>
+      <c r="M235">
+        <v>1</v>
+      </c>
+      <c r="N235">
+        <v>2</v>
+      </c>
+      <c r="O235" t="s">
+        <v>214</v>
+      </c>
+      <c r="P235" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q235">
+        <v>3.65</v>
+      </c>
+      <c r="R235">
+        <v>2.12</v>
+      </c>
+      <c r="S235">
+        <v>2.75</v>
+      </c>
+      <c r="T235">
+        <v>1.41</v>
+      </c>
+      <c r="U235">
+        <v>2.8</v>
+      </c>
+      <c r="V235">
+        <v>2.85</v>
+      </c>
+      <c r="W235">
+        <v>1.36</v>
+      </c>
+      <c r="X235">
+        <v>6.75</v>
+      </c>
+      <c r="Y235">
+        <v>1.06</v>
+      </c>
+      <c r="Z235">
+        <v>3.07</v>
+      </c>
+      <c r="AA235">
+        <v>3.21</v>
+      </c>
+      <c r="AB235">
+        <v>2.31</v>
+      </c>
+      <c r="AC235">
+        <v>0</v>
+      </c>
+      <c r="AD235">
+        <v>0</v>
+      </c>
+      <c r="AE235">
+        <v>0</v>
+      </c>
+      <c r="AF235">
+        <v>0</v>
+      </c>
+      <c r="AG235">
+        <v>2.1</v>
+      </c>
+      <c r="AH235">
+        <v>1.61</v>
+      </c>
+      <c r="AI235">
+        <v>1.77</v>
+      </c>
+      <c r="AJ235">
+        <v>1.91</v>
+      </c>
+      <c r="AK235">
+        <v>1.51</v>
+      </c>
+      <c r="AL235">
+        <v>1.31</v>
+      </c>
+      <c r="AM235">
+        <v>1.32</v>
+      </c>
+      <c r="AN235">
+        <v>1.5</v>
+      </c>
+      <c r="AO235">
+        <v>1.5</v>
+      </c>
+      <c r="AP235">
+        <v>1.47</v>
+      </c>
+      <c r="AQ235">
+        <v>1.47</v>
+      </c>
+      <c r="AR235">
+        <v>1.69</v>
+      </c>
+      <c r="AS235">
+        <v>1.44</v>
+      </c>
+      <c r="AT235">
+        <v>3.13</v>
+      </c>
+      <c r="AU235">
+        <v>7</v>
+      </c>
+      <c r="AV235">
+        <v>7</v>
+      </c>
+      <c r="AW235">
+        <v>6</v>
+      </c>
+      <c r="AX235">
+        <v>8</v>
+      </c>
+      <c r="AY235">
+        <v>13</v>
+      </c>
+      <c r="AZ235">
+        <v>16</v>
+      </c>
+      <c r="BA235">
+        <v>3</v>
+      </c>
+      <c r="BB235">
+        <v>2</v>
+      </c>
+      <c r="BC235">
+        <v>5</v>
+      </c>
+      <c r="BD235">
+        <v>2.25</v>
+      </c>
+      <c r="BE235">
+        <v>6.25</v>
+      </c>
+      <c r="BF235">
+        <v>1.79</v>
+      </c>
+      <c r="BG235">
+        <v>1.42</v>
+      </c>
+      <c r="BH235">
+        <v>2.55</v>
+      </c>
+      <c r="BI235">
+        <v>1.72</v>
+      </c>
+      <c r="BJ235">
+        <v>1.96</v>
+      </c>
+      <c r="BK235">
+        <v>2.16</v>
+      </c>
+      <c r="BL235">
+        <v>1.58</v>
+      </c>
+      <c r="BM235">
+        <v>2.8</v>
+      </c>
+      <c r="BN235">
+        <v>1.36</v>
+      </c>
+      <c r="BO235">
+        <v>3.7</v>
+      </c>
+      <c r="BP235">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7486996</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45724.54166666666</v>
+      </c>
+      <c r="F236">
+        <v>30</v>
+      </c>
+      <c r="G236" t="s">
+        <v>77</v>
+      </c>
+      <c r="H236" t="s">
+        <v>72</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>0</v>
+      </c>
+      <c r="L236">
+        <v>1</v>
+      </c>
+      <c r="M236">
+        <v>0</v>
+      </c>
+      <c r="N236">
+        <v>1</v>
+      </c>
+      <c r="O236" t="s">
+        <v>227</v>
+      </c>
+      <c r="P236" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q236">
+        <v>3.39</v>
+      </c>
+      <c r="R236">
+        <v>1.92</v>
+      </c>
+      <c r="S236">
+        <v>3.92</v>
+      </c>
+      <c r="T236">
+        <v>1.57</v>
+      </c>
+      <c r="U236">
+        <v>2.33</v>
+      </c>
+      <c r="V236">
+        <v>4</v>
+      </c>
+      <c r="W236">
+        <v>1.22</v>
+      </c>
+      <c r="X236">
+        <v>13</v>
+      </c>
+      <c r="Y236">
+        <v>1.04</v>
+      </c>
+      <c r="Z236">
+        <v>2.6</v>
+      </c>
+      <c r="AA236">
+        <v>3.14</v>
+      </c>
+      <c r="AB236">
+        <v>2.73</v>
+      </c>
+      <c r="AC236">
+        <v>0</v>
+      </c>
+      <c r="AD236">
+        <v>0</v>
+      </c>
+      <c r="AE236">
+        <v>1.5</v>
+      </c>
+      <c r="AF236">
+        <v>2.3</v>
+      </c>
+      <c r="AG236">
+        <v>2.56</v>
+      </c>
+      <c r="AH236">
+        <v>1.45</v>
+      </c>
+      <c r="AI236">
+        <v>2.2</v>
+      </c>
+      <c r="AJ236">
+        <v>1.62</v>
+      </c>
+      <c r="AK236">
+        <v>1.39</v>
+      </c>
+      <c r="AL236">
+        <v>1.31</v>
+      </c>
+      <c r="AM236">
+        <v>1.43</v>
+      </c>
+      <c r="AN236">
+        <v>1.57</v>
+      </c>
+      <c r="AO236">
+        <v>1.14</v>
+      </c>
+      <c r="AP236">
+        <v>1.67</v>
+      </c>
+      <c r="AQ236">
+        <v>1.07</v>
+      </c>
+      <c r="AR236">
+        <v>1.33</v>
+      </c>
+      <c r="AS236">
+        <v>1.44</v>
+      </c>
+      <c r="AT236">
+        <v>2.77</v>
+      </c>
+      <c r="AU236">
+        <v>7</v>
+      </c>
+      <c r="AV236">
+        <v>4</v>
+      </c>
+      <c r="AW236">
+        <v>9</v>
+      </c>
+      <c r="AX236">
+        <v>1</v>
+      </c>
+      <c r="AY236">
+        <v>21</v>
+      </c>
+      <c r="AZ236">
+        <v>6</v>
+      </c>
+      <c r="BA236">
+        <v>5</v>
+      </c>
+      <c r="BB236">
+        <v>1</v>
+      </c>
+      <c r="BC236">
+        <v>6</v>
+      </c>
+      <c r="BD236">
+        <v>0</v>
+      </c>
+      <c r="BE236">
+        <v>0</v>
+      </c>
+      <c r="BF236">
+        <v>0</v>
+      </c>
+      <c r="BG236">
+        <v>0</v>
+      </c>
+      <c r="BH236">
+        <v>0</v>
+      </c>
+      <c r="BI236">
+        <v>0</v>
+      </c>
+      <c r="BJ236">
+        <v>0</v>
+      </c>
+      <c r="BK236">
+        <v>0</v>
+      </c>
+      <c r="BL236">
+        <v>0</v>
+      </c>
+      <c r="BM236">
+        <v>0</v>
+      </c>
+      <c r="BN236">
+        <v>0</v>
+      </c>
+      <c r="BO236">
+        <v>0</v>
+      </c>
+      <c r="BP236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7486716</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45724.64583333334</v>
+      </c>
+      <c r="F237">
+        <v>30</v>
+      </c>
+      <c r="G237" t="s">
+        <v>71</v>
+      </c>
+      <c r="H237" t="s">
+        <v>81</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>1</v>
+      </c>
+      <c r="M237">
+        <v>0</v>
+      </c>
+      <c r="N237">
+        <v>1</v>
+      </c>
+      <c r="O237" t="s">
+        <v>228</v>
+      </c>
+      <c r="P237" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q237">
+        <v>3.45</v>
+      </c>
+      <c r="R237">
+        <v>2.11</v>
+      </c>
+      <c r="S237">
+        <v>3.32</v>
+      </c>
+      <c r="T237">
+        <v>1.42</v>
+      </c>
+      <c r="U237">
+        <v>2.69</v>
+      </c>
+      <c r="V237">
+        <v>3.19</v>
+      </c>
+      <c r="W237">
+        <v>1.32</v>
+      </c>
+      <c r="X237">
+        <v>10</v>
+      </c>
+      <c r="Y237">
+        <v>1.06</v>
+      </c>
+      <c r="Z237">
+        <v>3.25</v>
+      </c>
+      <c r="AA237">
+        <v>3.25</v>
+      </c>
+      <c r="AB237">
+        <v>2.2</v>
+      </c>
+      <c r="AC237">
+        <v>3.45</v>
+      </c>
+      <c r="AD237">
+        <v>1.31</v>
+      </c>
+      <c r="AE237">
+        <v>0</v>
+      </c>
+      <c r="AF237">
+        <v>0</v>
+      </c>
+      <c r="AG237">
+        <v>2.05</v>
+      </c>
+      <c r="AH237">
+        <v>1.61</v>
+      </c>
+      <c r="AI237">
+        <v>1.83</v>
+      </c>
+      <c r="AJ237">
+        <v>1.83</v>
+      </c>
+      <c r="AK237">
+        <v>0</v>
+      </c>
+      <c r="AL237">
+        <v>0</v>
+      </c>
+      <c r="AM237">
+        <v>0</v>
+      </c>
+      <c r="AN237">
+        <v>1.71</v>
+      </c>
+      <c r="AO237">
+        <v>1.14</v>
+      </c>
+      <c r="AP237">
+        <v>1.8</v>
+      </c>
+      <c r="AQ237">
+        <v>1.07</v>
+      </c>
+      <c r="AR237">
+        <v>1.24</v>
+      </c>
+      <c r="AS237">
+        <v>1.46</v>
+      </c>
+      <c r="AT237">
+        <v>2.7</v>
+      </c>
+      <c r="AU237">
+        <v>8</v>
+      </c>
+      <c r="AV237">
+        <v>0</v>
+      </c>
+      <c r="AW237">
+        <v>3</v>
+      </c>
+      <c r="AX237">
+        <v>15</v>
+      </c>
+      <c r="AY237">
+        <v>11</v>
+      </c>
+      <c r="AZ237">
+        <v>17</v>
+      </c>
+      <c r="BA237">
+        <v>3</v>
+      </c>
+      <c r="BB237">
+        <v>4</v>
+      </c>
+      <c r="BC237">
+        <v>7</v>
+      </c>
+      <c r="BD237">
+        <v>0</v>
+      </c>
+      <c r="BE237">
+        <v>0</v>
+      </c>
+      <c r="BF237">
+        <v>0</v>
+      </c>
+      <c r="BG237">
+        <v>0</v>
+      </c>
+      <c r="BH237">
+        <v>0</v>
+      </c>
+      <c r="BI237">
+        <v>0</v>
+      </c>
+      <c r="BJ237">
+        <v>0</v>
+      </c>
+      <c r="BK237">
+        <v>0</v>
+      </c>
+      <c r="BL237">
+        <v>0</v>
+      </c>
+      <c r="BM237">
+        <v>0</v>
+      </c>
+      <c r="BN237">
+        <v>0</v>
+      </c>
+      <c r="BO237">
+        <v>0</v>
+      </c>
+      <c r="BP237">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="323">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -703,6 +703,9 @@
     <t>['90+5']</t>
   </si>
   <si>
+    <t>['4', '7', '20', '48', '72', '77']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -1341,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP237"/>
+  <dimension ref="A1:BP239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1597,7 +1600,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1884,7 +1887,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ3">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2499,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ6">
         <v>1.47</v>
@@ -2627,7 +2630,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2705,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>1.36</v>
@@ -2833,7 +2836,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3120,7 +3123,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ9">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3451,7 +3454,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3657,7 +3660,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3863,7 +3866,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -4069,7 +4072,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4275,7 +4278,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4481,7 +4484,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4893,7 +4896,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -5099,7 +5102,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5177,7 +5180,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ19">
         <v>1.07</v>
@@ -5305,7 +5308,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5386,7 +5389,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ20">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR20">
         <v>1.45</v>
@@ -5717,7 +5720,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5923,7 +5926,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6001,10 +6004,10 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR23">
         <v>2</v>
@@ -6828,7 +6831,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ27">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR27">
         <v>1</v>
@@ -7365,7 +7368,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7443,7 +7446,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
         <v>1.47</v>
@@ -7571,7 +7574,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7777,7 +7780,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7983,7 +7986,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8061,7 +8064,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ33">
         <v>0.87</v>
@@ -8395,7 +8398,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8807,7 +8810,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -8888,7 +8891,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ37">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR37">
         <v>1.39</v>
@@ -9091,7 +9094,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
         <v>0.93</v>
@@ -9425,7 +9428,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9631,7 +9634,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9837,7 +9840,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -9918,7 +9921,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ42">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR42">
         <v>1.69</v>
@@ -10327,7 +10330,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ44">
         <v>0.67</v>
@@ -10867,7 +10870,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11279,7 +11282,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11772,7 +11775,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ51">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR51">
         <v>1.33</v>
@@ -11975,7 +11978,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
         <v>0.8</v>
@@ -12309,7 +12312,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12927,7 +12930,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13339,7 +13342,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13545,7 +13548,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13829,7 +13832,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ61">
         <v>1.27</v>
@@ -13957,7 +13960,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14038,7 +14041,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ62">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR62">
         <v>1.4</v>
@@ -14987,7 +14990,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15274,7 +15277,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ68">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR68">
         <v>1.66</v>
@@ -15399,7 +15402,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15477,7 +15480,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>1.8</v>
@@ -15605,7 +15608,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15811,7 +15814,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -16017,7 +16020,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16098,7 +16101,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ72">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR72">
         <v>1.78</v>
@@ -16635,7 +16638,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16713,7 +16716,7 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -16841,7 +16844,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17047,7 +17050,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17128,7 +17131,7 @@
         <v>2</v>
       </c>
       <c r="AQ77">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR77">
         <v>1.36</v>
@@ -17459,7 +17462,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17871,7 +17874,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18283,7 +18286,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18361,7 +18364,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ83">
         <v>1.27</v>
@@ -18901,7 +18904,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19725,7 +19728,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19931,7 +19934,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20009,7 +20012,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ91">
         <v>0.67</v>
@@ -20137,7 +20140,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20218,7 +20221,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ92">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR92">
         <v>1.5</v>
@@ -20343,7 +20346,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20755,7 +20758,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20833,10 +20836,10 @@
         <v>0.83</v>
       </c>
       <c r="AP95">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ95">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR95">
         <v>1.89</v>
@@ -21991,7 +21994,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22609,7 +22612,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22687,7 +22690,7 @@
         <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ104">
         <v>1.07</v>
@@ -22896,7 +22899,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ105">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR105">
         <v>1.58</v>
@@ -23227,7 +23230,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23433,7 +23436,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23717,7 +23720,7 @@
         <v>1.29</v>
       </c>
       <c r="AP109">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ109">
         <v>1.07</v>
@@ -23845,7 +23848,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24051,7 +24054,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24132,7 +24135,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ111">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR111">
         <v>1.65</v>
@@ -24257,7 +24260,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24463,7 +24466,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24875,7 +24878,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -26111,7 +26114,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26317,7 +26320,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -27141,7 +27144,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -28046,7 +28049,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ130">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR130">
         <v>1.47</v>
@@ -28377,7 +28380,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28583,7 +28586,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28661,7 +28664,7 @@
         <v>1.25</v>
       </c>
       <c r="AP133">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ133">
         <v>1.07</v>
@@ -28867,7 +28870,7 @@
         <v>1.25</v>
       </c>
       <c r="AP134">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ134">
         <v>0.93</v>
@@ -29407,7 +29410,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29488,7 +29491,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ137">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR137">
         <v>1.59</v>
@@ -30025,7 +30028,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30437,7 +30440,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30643,7 +30646,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30849,7 +30852,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -31055,7 +31058,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31467,7 +31470,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31673,7 +31676,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31754,7 +31757,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ148">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR148">
         <v>1.32</v>
@@ -31879,7 +31882,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32085,7 +32088,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32369,7 +32372,7 @@
         <v>0.67</v>
       </c>
       <c r="AP151">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ151">
         <v>0.8</v>
@@ -32703,7 +32706,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32909,7 +32912,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33527,7 +33530,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -34432,7 +34435,7 @@
         <v>2</v>
       </c>
       <c r="AQ161">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR161">
         <v>1.54</v>
@@ -34969,7 +34972,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35050,7 +35053,7 @@
         <v>1</v>
       </c>
       <c r="AQ164">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR164">
         <v>1.45</v>
@@ -35381,7 +35384,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35459,7 +35462,7 @@
         <v>1.3</v>
       </c>
       <c r="AP166">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ166">
         <v>1.07</v>
@@ -35999,7 +36002,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36205,7 +36208,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36411,7 +36414,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36489,7 +36492,7 @@
         <v>0.7</v>
       </c>
       <c r="AP171">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ171">
         <v>0.93</v>
@@ -36617,7 +36620,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36698,7 +36701,7 @@
         <v>2</v>
       </c>
       <c r="AQ172">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR172">
         <v>1.54</v>
@@ -37647,7 +37650,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -38265,7 +38268,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38552,7 +38555,7 @@
         <v>2</v>
       </c>
       <c r="AQ181">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR181">
         <v>1.62</v>
@@ -39373,7 +39376,7 @@
         <v>0.91</v>
       </c>
       <c r="AP185">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ185">
         <v>0.87</v>
@@ -39707,7 +39710,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -40119,7 +40122,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40200,7 +40203,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ189">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR189">
         <v>1.34</v>
@@ -40325,7 +40328,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40531,7 +40534,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40815,7 +40818,7 @@
         <v>1.64</v>
       </c>
       <c r="AP192">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ192">
         <v>1.6</v>
@@ -40943,7 +40946,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -41149,7 +41152,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -41845,7 +41848,7 @@
         <v>0.92</v>
       </c>
       <c r="AP197">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ197">
         <v>0.93</v>
@@ -42797,7 +42800,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -43003,7 +43006,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43084,7 +43087,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ203">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR203">
         <v>1.35</v>
@@ -43415,7 +43418,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43621,7 +43624,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -43905,7 +43908,7 @@
         <v>1.08</v>
       </c>
       <c r="AP207">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ207">
         <v>1.07</v>
@@ -44114,7 +44117,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ208">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR208">
         <v>1.66</v>
@@ -44239,7 +44242,7 @@
         <v>214</v>
       </c>
       <c r="P209" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q209">
         <v>4.75</v>
@@ -44445,7 +44448,7 @@
         <v>215</v>
       </c>
       <c r="P210" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q210">
         <v>2.8</v>
@@ -45063,7 +45066,7 @@
         <v>86</v>
       </c>
       <c r="P213" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q213">
         <v>2.65</v>
@@ -45475,7 +45478,7 @@
         <v>86</v>
       </c>
       <c r="P215" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q215">
         <v>6.8</v>
@@ -45681,7 +45684,7 @@
         <v>218</v>
       </c>
       <c r="P216" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q216">
         <v>1.91</v>
@@ -46093,7 +46096,7 @@
         <v>220</v>
       </c>
       <c r="P218" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q218">
         <v>2.18</v>
@@ -46174,7 +46177,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ218">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR218">
         <v>1.24</v>
@@ -46505,7 +46508,7 @@
         <v>221</v>
       </c>
       <c r="P220" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q220">
         <v>4.3</v>
@@ -46586,7 +46589,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ220">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR220">
         <v>1.73</v>
@@ -46789,7 +46792,7 @@
         <v>1.15</v>
       </c>
       <c r="AP221">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ221">
         <v>1</v>
@@ -47201,7 +47204,7 @@
         <v>1.46</v>
       </c>
       <c r="AP223">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ223">
         <v>1.36</v>
@@ -47329,7 +47332,7 @@
         <v>223</v>
       </c>
       <c r="P224" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q224">
         <v>3.5</v>
@@ -47535,7 +47538,7 @@
         <v>209</v>
       </c>
       <c r="P225" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q225">
         <v>3.6</v>
@@ -47947,7 +47950,7 @@
         <v>156</v>
       </c>
       <c r="P227" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q227">
         <v>3.75</v>
@@ -48153,7 +48156,7 @@
         <v>86</v>
       </c>
       <c r="P228" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q228">
         <v>2.24</v>
@@ -49389,7 +49392,7 @@
         <v>226</v>
       </c>
       <c r="P234" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -49595,7 +49598,7 @@
         <v>214</v>
       </c>
       <c r="P235" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q235">
         <v>3.65</v>
@@ -50164,6 +50167,418 @@
       </c>
       <c r="BP237">
         <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7486714</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45725.41666666666</v>
+      </c>
+      <c r="F238">
+        <v>30</v>
+      </c>
+      <c r="G238" t="s">
+        <v>75</v>
+      </c>
+      <c r="H238" t="s">
+        <v>84</v>
+      </c>
+      <c r="I238">
+        <v>3</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>3</v>
+      </c>
+      <c r="L238">
+        <v>6</v>
+      </c>
+      <c r="M238">
+        <v>0</v>
+      </c>
+      <c r="N238">
+        <v>6</v>
+      </c>
+      <c r="O238" t="s">
+        <v>229</v>
+      </c>
+      <c r="P238" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q238">
+        <v>1.8</v>
+      </c>
+      <c r="R238">
+        <v>2.4</v>
+      </c>
+      <c r="S238">
+        <v>10</v>
+      </c>
+      <c r="T238">
+        <v>1.36</v>
+      </c>
+      <c r="U238">
+        <v>3</v>
+      </c>
+      <c r="V238">
+        <v>2.75</v>
+      </c>
+      <c r="W238">
+        <v>1.4</v>
+      </c>
+      <c r="X238">
+        <v>7</v>
+      </c>
+      <c r="Y238">
+        <v>1.1</v>
+      </c>
+      <c r="Z238">
+        <v>1.27</v>
+      </c>
+      <c r="AA238">
+        <v>5.4</v>
+      </c>
+      <c r="AB238">
+        <v>10</v>
+      </c>
+      <c r="AC238">
+        <v>0</v>
+      </c>
+      <c r="AD238">
+        <v>0</v>
+      </c>
+      <c r="AE238">
+        <v>0</v>
+      </c>
+      <c r="AF238">
+        <v>0</v>
+      </c>
+      <c r="AG238">
+        <v>1.8</v>
+      </c>
+      <c r="AH238">
+        <v>1.94</v>
+      </c>
+      <c r="AI238">
+        <v>2.5</v>
+      </c>
+      <c r="AJ238">
+        <v>1.5</v>
+      </c>
+      <c r="AK238">
+        <v>1.06</v>
+      </c>
+      <c r="AL238">
+        <v>1.16</v>
+      </c>
+      <c r="AM238">
+        <v>2.65</v>
+      </c>
+      <c r="AN238">
+        <v>1.93</v>
+      </c>
+      <c r="AO238">
+        <v>0.36</v>
+      </c>
+      <c r="AP238">
+        <v>2</v>
+      </c>
+      <c r="AQ238">
+        <v>0.33</v>
+      </c>
+      <c r="AR238">
+        <v>1.82</v>
+      </c>
+      <c r="AS238">
+        <v>1.12</v>
+      </c>
+      <c r="AT238">
+        <v>2.94</v>
+      </c>
+      <c r="AU238">
+        <v>9</v>
+      </c>
+      <c r="AV238">
+        <v>3</v>
+      </c>
+      <c r="AW238">
+        <v>15</v>
+      </c>
+      <c r="AX238">
+        <v>7</v>
+      </c>
+      <c r="AY238">
+        <v>31</v>
+      </c>
+      <c r="AZ238">
+        <v>11</v>
+      </c>
+      <c r="BA238">
+        <v>3</v>
+      </c>
+      <c r="BB238">
+        <v>1</v>
+      </c>
+      <c r="BC238">
+        <v>4</v>
+      </c>
+      <c r="BD238">
+        <v>0</v>
+      </c>
+      <c r="BE238">
+        <v>0</v>
+      </c>
+      <c r="BF238">
+        <v>0</v>
+      </c>
+      <c r="BG238">
+        <v>0</v>
+      </c>
+      <c r="BH238">
+        <v>0</v>
+      </c>
+      <c r="BI238">
+        <v>0</v>
+      </c>
+      <c r="BJ238">
+        <v>0</v>
+      </c>
+      <c r="BK238">
+        <v>0</v>
+      </c>
+      <c r="BL238">
+        <v>0</v>
+      </c>
+      <c r="BM238">
+        <v>0</v>
+      </c>
+      <c r="BN238">
+        <v>0</v>
+      </c>
+      <c r="BO238">
+        <v>0</v>
+      </c>
+      <c r="BP238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7486717</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45725.625</v>
+      </c>
+      <c r="F239">
+        <v>30</v>
+      </c>
+      <c r="G239" t="s">
+        <v>74</v>
+      </c>
+      <c r="H239" t="s">
+        <v>80</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>1</v>
+      </c>
+      <c r="L239">
+        <v>1</v>
+      </c>
+      <c r="M239">
+        <v>0</v>
+      </c>
+      <c r="N239">
+        <v>1</v>
+      </c>
+      <c r="O239" t="s">
+        <v>99</v>
+      </c>
+      <c r="P239" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q239">
+        <v>2.8</v>
+      </c>
+      <c r="R239">
+        <v>2.09</v>
+      </c>
+      <c r="S239">
+        <v>4.31</v>
+      </c>
+      <c r="T239">
+        <v>1.46</v>
+      </c>
+      <c r="U239">
+        <v>2.64</v>
+      </c>
+      <c r="V239">
+        <v>3.34</v>
+      </c>
+      <c r="W239">
+        <v>1.31</v>
+      </c>
+      <c r="X239">
+        <v>10</v>
+      </c>
+      <c r="Y239">
+        <v>1.06</v>
+      </c>
+      <c r="Z239">
+        <v>2.11</v>
+      </c>
+      <c r="AA239">
+        <v>3.2</v>
+      </c>
+      <c r="AB239">
+        <v>3.53</v>
+      </c>
+      <c r="AC239">
+        <v>1.08</v>
+      </c>
+      <c r="AD239">
+        <v>7</v>
+      </c>
+      <c r="AE239">
+        <v>1.4</v>
+      </c>
+      <c r="AF239">
+        <v>2.7</v>
+      </c>
+      <c r="AG239">
+        <v>2.15</v>
+      </c>
+      <c r="AH239">
+        <v>1.57</v>
+      </c>
+      <c r="AI239">
+        <v>1.91</v>
+      </c>
+      <c r="AJ239">
+        <v>1.8</v>
+      </c>
+      <c r="AK239">
+        <v>1.32</v>
+      </c>
+      <c r="AL239">
+        <v>1.31</v>
+      </c>
+      <c r="AM239">
+        <v>1.51</v>
+      </c>
+      <c r="AN239">
+        <v>1.86</v>
+      </c>
+      <c r="AO239">
+        <v>1.43</v>
+      </c>
+      <c r="AP239">
+        <v>1.93</v>
+      </c>
+      <c r="AQ239">
+        <v>1.33</v>
+      </c>
+      <c r="AR239">
+        <v>2.11</v>
+      </c>
+      <c r="AS239">
+        <v>1.58</v>
+      </c>
+      <c r="AT239">
+        <v>3.69</v>
+      </c>
+      <c r="AU239">
+        <v>5</v>
+      </c>
+      <c r="AV239">
+        <v>2</v>
+      </c>
+      <c r="AW239">
+        <v>9</v>
+      </c>
+      <c r="AX239">
+        <v>8</v>
+      </c>
+      <c r="AY239">
+        <v>16</v>
+      </c>
+      <c r="AZ239">
+        <v>10</v>
+      </c>
+      <c r="BA239">
+        <v>9</v>
+      </c>
+      <c r="BB239">
+        <v>8</v>
+      </c>
+      <c r="BC239">
+        <v>17</v>
+      </c>
+      <c r="BD239">
+        <v>1.47</v>
+      </c>
+      <c r="BE239">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF239">
+        <v>3.22</v>
+      </c>
+      <c r="BG239">
+        <v>1.26</v>
+      </c>
+      <c r="BH239">
+        <v>3.22</v>
+      </c>
+      <c r="BI239">
+        <v>1.5</v>
+      </c>
+      <c r="BJ239">
+        <v>2.35</v>
+      </c>
+      <c r="BK239">
+        <v>1.8</v>
+      </c>
+      <c r="BL239">
+        <v>1.91</v>
+      </c>
+      <c r="BM239">
+        <v>2.42</v>
+      </c>
+      <c r="BN239">
+        <v>1.47</v>
+      </c>
+      <c r="BO239">
+        <v>3.2</v>
+      </c>
+      <c r="BP239">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="324">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -984,6 +984,9 @@
   <si>
     <t>['8']</t>
   </si>
+  <si>
+    <t>['45+1', '87']</t>
+  </si>
 </sst>
 </file>
 
@@ -1344,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP239"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1681,7 +1684,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ2">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2296,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
         <v>1.07</v>
@@ -2711,7 +2714,7 @@
         <v>2</v>
       </c>
       <c r="AQ7">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2914,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ8">
         <v>1.07</v>
@@ -4977,7 +4980,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ18">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR18">
         <v>0.84</v>
@@ -5595,7 +5598,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ21">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -6210,7 +6213,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ24">
         <v>1.47</v>
@@ -8476,7 +8479,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ35">
         <v>1.07</v>
@@ -9097,7 +9100,7 @@
         <v>2</v>
       </c>
       <c r="AQ38">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR38">
         <v>1.73</v>
@@ -9509,7 +9512,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ40">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -10124,7 +10127,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ43">
         <v>1.27</v>
@@ -10539,7 +10542,7 @@
         <v>2</v>
       </c>
       <c r="AQ45">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR45">
         <v>1.51</v>
@@ -11569,7 +11572,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ50">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR50">
         <v>1.71</v>
@@ -12596,7 +12599,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ55">
         <v>0.87</v>
@@ -13420,7 +13423,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -14247,7 +14250,7 @@
         <v>2</v>
       </c>
       <c r="AQ63">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -14659,7 +14662,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ65">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR65">
         <v>1.18</v>
@@ -15686,7 +15689,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ70">
         <v>0.93</v>
@@ -16098,7 +16101,7 @@
         <v>0.8</v>
       </c>
       <c r="AP72">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ72">
         <v>0.33</v>
@@ -16307,7 +16310,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ73">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR73">
         <v>1.51</v>
@@ -17334,7 +17337,7 @@
         <v>0.75</v>
       </c>
       <c r="AP78">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ78">
         <v>0.67</v>
@@ -19191,7 +19194,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ87">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR87">
         <v>1.94</v>
@@ -19394,7 +19397,7 @@
         <v>1.6</v>
       </c>
       <c r="AP88">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ88">
         <v>1</v>
@@ -19603,7 +19606,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ89">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR89">
         <v>1.6</v>
@@ -20630,7 +20633,7 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ94">
         <v>1.07</v>
@@ -22281,7 +22284,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ102">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR102">
         <v>1.5</v>
@@ -22896,7 +22899,7 @@
         <v>0.71</v>
       </c>
       <c r="AP105">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ105">
         <v>0.33</v>
@@ -23311,7 +23314,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ107">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR107">
         <v>1.21</v>
@@ -23517,7 +23520,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ108">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR108">
         <v>1.42</v>
@@ -23926,7 +23929,7 @@
         <v>1.63</v>
       </c>
       <c r="AP110">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ110">
         <v>1.47</v>
@@ -27840,7 +27843,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ129">
         <v>1.8</v>
@@ -28873,7 +28876,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ134">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR134">
         <v>2.06</v>
@@ -29079,7 +29082,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ135">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR135">
         <v>1.36</v>
@@ -29282,7 +29285,7 @@
         <v>0.57</v>
       </c>
       <c r="AP136">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ136">
         <v>0.67</v>
@@ -29488,7 +29491,7 @@
         <v>1.13</v>
       </c>
       <c r="AP137">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ137">
         <v>1.33</v>
@@ -29694,7 +29697,7 @@
         <v>0.88</v>
       </c>
       <c r="AP138">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ138">
         <v>0.87</v>
@@ -31551,7 +31554,7 @@
         <v>1</v>
       </c>
       <c r="AQ147">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR147">
         <v>1.41</v>
@@ -31960,10 +31963,10 @@
         <v>1.11</v>
       </c>
       <c r="AP149">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ149">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR149">
         <v>1.6</v>
@@ -32990,7 +32993,7 @@
         <v>0.44</v>
       </c>
       <c r="AP154">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ154">
         <v>0.93</v>
@@ -35259,7 +35262,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ165">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR165">
         <v>1.27</v>
@@ -35874,7 +35877,7 @@
         <v>0.6</v>
       </c>
       <c r="AP168">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ168">
         <v>0.8</v>
@@ -37110,7 +37113,7 @@
         <v>1.7</v>
       </c>
       <c r="AP174">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ174">
         <v>1.6</v>
@@ -37319,7 +37322,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ175">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR175">
         <v>1.78</v>
@@ -37937,7 +37940,7 @@
         <v>1</v>
       </c>
       <c r="AQ178">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR178">
         <v>1.45</v>
@@ -38964,7 +38967,7 @@
         <v>1.73</v>
       </c>
       <c r="AP183">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ183">
         <v>1.8</v>
@@ -39791,7 +39794,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ187">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR187">
         <v>1.38</v>
@@ -39994,7 +39997,7 @@
         <v>1.09</v>
       </c>
       <c r="AP188">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ188">
         <v>1.07</v>
@@ -41439,7 +41442,7 @@
         <v>2</v>
       </c>
       <c r="AQ195">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR195">
         <v>1.63</v>
@@ -42878,10 +42881,10 @@
         <v>1.5</v>
       </c>
       <c r="AP202">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ202">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR202">
         <v>1.75</v>
@@ -44320,7 +44323,7 @@
         <v>1.58</v>
       </c>
       <c r="AP209">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ209">
         <v>1.6</v>
@@ -45765,7 +45768,7 @@
         <v>2</v>
       </c>
       <c r="AQ216">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR216">
         <v>1.57</v>
@@ -46586,7 +46589,7 @@
         <v>1.46</v>
       </c>
       <c r="AP220">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ220">
         <v>1.33</v>
@@ -47207,7 +47210,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ223">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR223">
         <v>2.11</v>
@@ -47410,7 +47413,7 @@
         <v>1</v>
       </c>
       <c r="AP224">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ224">
         <v>1.07</v>
@@ -50579,6 +50582,418 @@
       </c>
       <c r="BP239">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7486997</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45726.5</v>
+      </c>
+      <c r="F240">
+        <v>30</v>
+      </c>
+      <c r="G240" t="s">
+        <v>76</v>
+      </c>
+      <c r="H240" t="s">
+        <v>79</v>
+      </c>
+      <c r="I240">
+        <v>1</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>1</v>
+      </c>
+      <c r="L240">
+        <v>1</v>
+      </c>
+      <c r="M240">
+        <v>0</v>
+      </c>
+      <c r="N240">
+        <v>1</v>
+      </c>
+      <c r="O240" t="s">
+        <v>87</v>
+      </c>
+      <c r="P240" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q240">
+        <v>2.6</v>
+      </c>
+      <c r="R240">
+        <v>2.05</v>
+      </c>
+      <c r="S240">
+        <v>5</v>
+      </c>
+      <c r="T240">
+        <v>1.5</v>
+      </c>
+      <c r="U240">
+        <v>2.5</v>
+      </c>
+      <c r="V240">
+        <v>3.4</v>
+      </c>
+      <c r="W240">
+        <v>1.3</v>
+      </c>
+      <c r="X240">
+        <v>10</v>
+      </c>
+      <c r="Y240">
+        <v>1.06</v>
+      </c>
+      <c r="Z240">
+        <v>2.08</v>
+      </c>
+      <c r="AA240">
+        <v>3.16</v>
+      </c>
+      <c r="AB240">
+        <v>3.66</v>
+      </c>
+      <c r="AC240">
+        <v>1.07</v>
+      </c>
+      <c r="AD240">
+        <v>7.5</v>
+      </c>
+      <c r="AE240">
+        <v>1.4</v>
+      </c>
+      <c r="AF240">
+        <v>2.8</v>
+      </c>
+      <c r="AG240">
+        <v>2.15</v>
+      </c>
+      <c r="AH240">
+        <v>1.57</v>
+      </c>
+      <c r="AI240">
+        <v>2</v>
+      </c>
+      <c r="AJ240">
+        <v>1.73</v>
+      </c>
+      <c r="AK240">
+        <v>1.19</v>
+      </c>
+      <c r="AL240">
+        <v>1.28</v>
+      </c>
+      <c r="AM240">
+        <v>2</v>
+      </c>
+      <c r="AN240">
+        <v>1.14</v>
+      </c>
+      <c r="AO240">
+        <v>0.93</v>
+      </c>
+      <c r="AP240">
+        <v>1.27</v>
+      </c>
+      <c r="AQ240">
+        <v>0.87</v>
+      </c>
+      <c r="AR240">
+        <v>1.73</v>
+      </c>
+      <c r="AS240">
+        <v>1.31</v>
+      </c>
+      <c r="AT240">
+        <v>3.04</v>
+      </c>
+      <c r="AU240">
+        <v>9</v>
+      </c>
+      <c r="AV240">
+        <v>2</v>
+      </c>
+      <c r="AW240">
+        <v>20</v>
+      </c>
+      <c r="AX240">
+        <v>5</v>
+      </c>
+      <c r="AY240">
+        <v>35</v>
+      </c>
+      <c r="AZ240">
+        <v>8</v>
+      </c>
+      <c r="BA240">
+        <v>13</v>
+      </c>
+      <c r="BB240">
+        <v>1</v>
+      </c>
+      <c r="BC240">
+        <v>14</v>
+      </c>
+      <c r="BD240">
+        <v>1.4</v>
+      </c>
+      <c r="BE240">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF240">
+        <v>3.54</v>
+      </c>
+      <c r="BG240">
+        <v>1.22</v>
+      </c>
+      <c r="BH240">
+        <v>3.48</v>
+      </c>
+      <c r="BI240">
+        <v>1.44</v>
+      </c>
+      <c r="BJ240">
+        <v>2.5</v>
+      </c>
+      <c r="BK240">
+        <v>1.8</v>
+      </c>
+      <c r="BL240">
+        <v>1.9</v>
+      </c>
+      <c r="BM240">
+        <v>2.28</v>
+      </c>
+      <c r="BN240">
+        <v>1.53</v>
+      </c>
+      <c r="BO240">
+        <v>3.04</v>
+      </c>
+      <c r="BP240">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7486715</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45726.625</v>
+      </c>
+      <c r="F241">
+        <v>30</v>
+      </c>
+      <c r="G241" t="s">
+        <v>73</v>
+      </c>
+      <c r="H241" t="s">
+        <v>83</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+      <c r="J241">
+        <v>1</v>
+      </c>
+      <c r="K241">
+        <v>1</v>
+      </c>
+      <c r="L241">
+        <v>0</v>
+      </c>
+      <c r="M241">
+        <v>2</v>
+      </c>
+      <c r="N241">
+        <v>2</v>
+      </c>
+      <c r="O241" t="s">
+        <v>86</v>
+      </c>
+      <c r="P241" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q241">
+        <v>4</v>
+      </c>
+      <c r="R241">
+        <v>2</v>
+      </c>
+      <c r="S241">
+        <v>3.1</v>
+      </c>
+      <c r="T241">
+        <v>1.53</v>
+      </c>
+      <c r="U241">
+        <v>2.38</v>
+      </c>
+      <c r="V241">
+        <v>3.5</v>
+      </c>
+      <c r="W241">
+        <v>1.29</v>
+      </c>
+      <c r="X241">
+        <v>11</v>
+      </c>
+      <c r="Y241">
+        <v>1.05</v>
+      </c>
+      <c r="Z241">
+        <v>3.25</v>
+      </c>
+      <c r="AA241">
+        <v>3.1</v>
+      </c>
+      <c r="AB241">
+        <v>2.25</v>
+      </c>
+      <c r="AC241">
+        <v>1.08</v>
+      </c>
+      <c r="AD241">
+        <v>7</v>
+      </c>
+      <c r="AE241">
+        <v>1.44</v>
+      </c>
+      <c r="AF241">
+        <v>2.65</v>
+      </c>
+      <c r="AG241">
+        <v>2.35</v>
+      </c>
+      <c r="AH241">
+        <v>1.57</v>
+      </c>
+      <c r="AI241">
+        <v>2</v>
+      </c>
+      <c r="AJ241">
+        <v>1.73</v>
+      </c>
+      <c r="AK241">
+        <v>1.66</v>
+      </c>
+      <c r="AL241">
+        <v>1.34</v>
+      </c>
+      <c r="AM241">
+        <v>1.29</v>
+      </c>
+      <c r="AN241">
+        <v>1.07</v>
+      </c>
+      <c r="AO241">
+        <v>1.36</v>
+      </c>
+      <c r="AP241">
+        <v>1</v>
+      </c>
+      <c r="AQ241">
+        <v>1.47</v>
+      </c>
+      <c r="AR241">
+        <v>1.56</v>
+      </c>
+      <c r="AS241">
+        <v>1.16</v>
+      </c>
+      <c r="AT241">
+        <v>2.72</v>
+      </c>
+      <c r="AU241">
+        <v>3</v>
+      </c>
+      <c r="AV241">
+        <v>7</v>
+      </c>
+      <c r="AW241">
+        <v>12</v>
+      </c>
+      <c r="AX241">
+        <v>15</v>
+      </c>
+      <c r="AY241">
+        <v>20</v>
+      </c>
+      <c r="AZ241">
+        <v>25</v>
+      </c>
+      <c r="BA241">
+        <v>3</v>
+      </c>
+      <c r="BB241">
+        <v>5</v>
+      </c>
+      <c r="BC241">
+        <v>8</v>
+      </c>
+      <c r="BD241">
+        <v>2.32</v>
+      </c>
+      <c r="BE241">
+        <v>6.3</v>
+      </c>
+      <c r="BF241">
+        <v>1.94</v>
+      </c>
+      <c r="BG241">
+        <v>1.28</v>
+      </c>
+      <c r="BH241">
+        <v>3.05</v>
+      </c>
+      <c r="BI241">
+        <v>1.55</v>
+      </c>
+      <c r="BJ241">
+        <v>2.23</v>
+      </c>
+      <c r="BK241">
+        <v>1.96</v>
+      </c>
+      <c r="BL241">
+        <v>1.75</v>
+      </c>
+      <c r="BM241">
+        <v>2.57</v>
+      </c>
+      <c r="BN241">
+        <v>1.42</v>
+      </c>
+      <c r="BO241">
+        <v>3.5</v>
+      </c>
+      <c r="BP241">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="331">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -721,6 +721,9 @@
     <t>['29', '55', '90+3']</t>
   </si>
   <si>
+    <t>['40']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -746,9 +749,6 @@
   </si>
   <si>
     <t>['12', '30']</t>
-  </si>
-  <si>
-    <t>['40']</t>
   </si>
   <si>
     <t>['44', '59']</t>
@@ -1004,6 +1004,9 @@
   </si>
   <si>
     <t>['40', '70', '83']</t>
+  </si>
+  <si>
+    <t>['18', '46']</t>
   </si>
 </sst>
 </file>
@@ -1365,7 +1368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP248"/>
+  <dimension ref="A1:BP249"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1621,7 +1624,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -2111,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ4">
         <v>0.6899999999999999</v>
@@ -2651,7 +2654,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2857,7 +2860,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3144,7 +3147,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ9">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3475,7 +3478,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3681,7 +3684,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3887,7 +3890,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -4093,7 +4096,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4299,7 +4302,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4505,7 +4508,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4917,7 +4920,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -5410,7 +5413,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ20">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR20">
         <v>1.45</v>
@@ -5613,7 +5616,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ21">
         <v>1.38</v>
@@ -6852,7 +6855,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ27">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR27">
         <v>1</v>
@@ -8909,7 +8912,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ37">
         <v>1.33</v>
@@ -9942,7 +9945,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ42">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR42">
         <v>1.69</v>
@@ -11587,7 +11590,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ50">
         <v>0.88</v>
@@ -14062,7 +14065,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ62">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR62">
         <v>1.4</v>
@@ -14471,7 +14474,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ64">
         <v>0.9399999999999999</v>
@@ -16122,7 +16125,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ72">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR72">
         <v>1.78</v>
@@ -19003,7 +19006,7 @@
         <v>0.67</v>
       </c>
       <c r="AP86">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ86">
         <v>1.8</v>
@@ -20860,7 +20863,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ95">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR95">
         <v>1.89</v>
@@ -21475,7 +21478,7 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ98">
         <v>1.27</v>
@@ -22920,7 +22923,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ105">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR105">
         <v>1.58</v>
@@ -24565,7 +24568,7 @@
         <v>1.33</v>
       </c>
       <c r="AP113">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ113">
         <v>1</v>
@@ -28067,10 +28070,10 @@
         <v>0.63</v>
       </c>
       <c r="AP130">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ130">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR130">
         <v>1.47</v>
@@ -31363,7 +31366,7 @@
         <v>1.22</v>
       </c>
       <c r="AP146">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ146">
         <v>1.06</v>
@@ -34456,7 +34459,7 @@
         <v>2</v>
       </c>
       <c r="AQ161">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR161">
         <v>1.54</v>
@@ -34659,7 +34662,7 @@
         <v>1.6</v>
       </c>
       <c r="AP162">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ162">
         <v>1.38</v>
@@ -36722,7 +36725,7 @@
         <v>2</v>
       </c>
       <c r="AQ172">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR172">
         <v>1.54</v>
@@ -38779,7 +38782,7 @@
         <v>1.18</v>
       </c>
       <c r="AP182">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ182">
         <v>1</v>
@@ -40224,7 +40227,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ189">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR189">
         <v>1.34</v>
@@ -42487,7 +42490,7 @@
         <v>0.83</v>
       </c>
       <c r="AP200">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ200">
         <v>0.87</v>
@@ -44138,7 +44141,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ208">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR208">
         <v>1.66</v>
@@ -44547,7 +44550,7 @@
         <v>0.85</v>
       </c>
       <c r="AP210">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ210">
         <v>0.93</v>
@@ -46198,7 +46201,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ218">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR218">
         <v>1.24</v>
@@ -48049,7 +48052,7 @@
         <v>1.64</v>
       </c>
       <c r="AP227">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ227">
         <v>1.6</v>
@@ -50318,7 +50321,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ238">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR238">
         <v>1.86</v>
@@ -51999,10 +52002,10 @@
         <v>3</v>
       </c>
       <c r="BB246">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC246">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD246">
         <v>1.36</v>
@@ -52454,6 +52457,212 @@
       </c>
       <c r="BP248">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7856868</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45733.625</v>
+      </c>
+      <c r="F249">
+        <v>1</v>
+      </c>
+      <c r="G249" t="s">
+        <v>72</v>
+      </c>
+      <c r="H249" t="s">
+        <v>84</v>
+      </c>
+      <c r="I249">
+        <v>1</v>
+      </c>
+      <c r="J249">
+        <v>1</v>
+      </c>
+      <c r="K249">
+        <v>2</v>
+      </c>
+      <c r="L249">
+        <v>1</v>
+      </c>
+      <c r="M249">
+        <v>2</v>
+      </c>
+      <c r="N249">
+        <v>3</v>
+      </c>
+      <c r="O249" t="s">
+        <v>235</v>
+      </c>
+      <c r="P249" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q249">
+        <v>2.05</v>
+      </c>
+      <c r="R249">
+        <v>2.27</v>
+      </c>
+      <c r="S249">
+        <v>5.98</v>
+      </c>
+      <c r="T249">
+        <v>1.36</v>
+      </c>
+      <c r="U249">
+        <v>2.89</v>
+      </c>
+      <c r="V249">
+        <v>2.73</v>
+      </c>
+      <c r="W249">
+        <v>1.4</v>
+      </c>
+      <c r="X249">
+        <v>6.6</v>
+      </c>
+      <c r="Y249">
+        <v>1.05</v>
+      </c>
+      <c r="Z249">
+        <v>1.42</v>
+      </c>
+      <c r="AA249">
+        <v>4.5</v>
+      </c>
+      <c r="AB249">
+        <v>7</v>
+      </c>
+      <c r="AC249">
+        <v>1.01</v>
+      </c>
+      <c r="AD249">
+        <v>12.5</v>
+      </c>
+      <c r="AE249">
+        <v>1.24</v>
+      </c>
+      <c r="AF249">
+        <v>3.36</v>
+      </c>
+      <c r="AG249">
+        <v>1.87</v>
+      </c>
+      <c r="AH249">
+        <v>1.87</v>
+      </c>
+      <c r="AI249">
+        <v>1.94</v>
+      </c>
+      <c r="AJ249">
+        <v>1.76</v>
+      </c>
+      <c r="AK249">
+        <v>1.14</v>
+      </c>
+      <c r="AL249">
+        <v>1.21</v>
+      </c>
+      <c r="AM249">
+        <v>2.48</v>
+      </c>
+      <c r="AN249">
+        <v>1.67</v>
+      </c>
+      <c r="AO249">
+        <v>0.33</v>
+      </c>
+      <c r="AP249">
+        <v>1.56</v>
+      </c>
+      <c r="AQ249">
+        <v>0.5</v>
+      </c>
+      <c r="AR249">
+        <v>1.45</v>
+      </c>
+      <c r="AS249">
+        <v>1.13</v>
+      </c>
+      <c r="AT249">
+        <v>2.58</v>
+      </c>
+      <c r="AU249">
+        <v>-1</v>
+      </c>
+      <c r="AV249">
+        <v>-1</v>
+      </c>
+      <c r="AW249">
+        <v>-1</v>
+      </c>
+      <c r="AX249">
+        <v>-1</v>
+      </c>
+      <c r="AY249">
+        <v>-1</v>
+      </c>
+      <c r="AZ249">
+        <v>-1</v>
+      </c>
+      <c r="BA249">
+        <v>-1</v>
+      </c>
+      <c r="BB249">
+        <v>-1</v>
+      </c>
+      <c r="BC249">
+        <v>-1</v>
+      </c>
+      <c r="BD249">
+        <v>1.38</v>
+      </c>
+      <c r="BE249">
+        <v>7</v>
+      </c>
+      <c r="BF249">
+        <v>3.4</v>
+      </c>
+      <c r="BG249">
+        <v>1.36</v>
+      </c>
+      <c r="BH249">
+        <v>2.8</v>
+      </c>
+      <c r="BI249">
+        <v>1.6</v>
+      </c>
+      <c r="BJ249">
+        <v>2.14</v>
+      </c>
+      <c r="BK249">
+        <v>1.96</v>
+      </c>
+      <c r="BL249">
+        <v>1.71</v>
+      </c>
+      <c r="BM249">
+        <v>2.5</v>
+      </c>
+      <c r="BN249">
+        <v>1.44</v>
+      </c>
+      <c r="BO249">
+        <v>3.35</v>
+      </c>
+      <c r="BP249">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -52599,31 +52599,31 @@
         <v>2.58</v>
       </c>
       <c r="AU249">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV249">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW249">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX249">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY249">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AZ249">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BA249">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BB249">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC249">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD249">
         <v>1.38</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="332">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1008,6 +1008,9 @@
   <si>
     <t>['18', '46']</t>
   </si>
+  <si>
+    <t>['23', '45+2']</t>
+  </si>
 </sst>
 </file>
 
@@ -1368,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP249"/>
+  <dimension ref="A1:BP251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2114,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ4">
         <v>0.6899999999999999</v>
@@ -3556,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ11">
         <v>1.8</v>
@@ -4177,7 +4180,7 @@
         <v>2</v>
       </c>
       <c r="AQ14">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -5616,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ21">
         <v>1.38</v>
@@ -6649,7 +6652,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ26">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR26">
         <v>1.29</v>
@@ -7676,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ31">
         <v>1.27</v>
@@ -8912,7 +8915,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ37">
         <v>1.33</v>
@@ -9736,7 +9739,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -10975,7 +10978,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ47">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR47">
         <v>1.66</v>
@@ -11590,7 +11593,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ50">
         <v>0.88</v>
@@ -14062,7 +14065,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ62">
         <v>0.5</v>
@@ -14474,7 +14477,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ64">
         <v>0.9399999999999999</v>
@@ -15713,7 +15716,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ70">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -17564,7 +17567,7 @@
         <v>1.2</v>
       </c>
       <c r="AP79">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ79">
         <v>1.06</v>
@@ -17773,7 +17776,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ80">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR80">
         <v>1.06</v>
@@ -19006,7 +19009,7 @@
         <v>0.67</v>
       </c>
       <c r="AP86">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ86">
         <v>1.8</v>
@@ -19830,7 +19833,7 @@
         <v>1.71</v>
       </c>
       <c r="AP90">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ90">
         <v>1.38</v>
@@ -21069,7 +21072,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR96">
         <v>1.35</v>
@@ -21478,7 +21481,7 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ98">
         <v>1.27</v>
@@ -24568,7 +24571,7 @@
         <v>1.33</v>
       </c>
       <c r="AP113">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ113">
         <v>1</v>
@@ -25598,7 +25601,7 @@
         <v>0.71</v>
       </c>
       <c r="AP118">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ118">
         <v>0.9399999999999999</v>
@@ -25807,7 +25810,7 @@
         <v>2</v>
       </c>
       <c r="AQ119">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR119">
         <v>1.46</v>
@@ -26631,7 +26634,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ123">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR123">
         <v>1.82</v>
@@ -27040,7 +27043,7 @@
         <v>0.57</v>
       </c>
       <c r="AP125">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ125">
         <v>0.87</v>
@@ -28070,7 +28073,7 @@
         <v>0.63</v>
       </c>
       <c r="AP130">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ130">
         <v>0.5</v>
@@ -30130,10 +30133,10 @@
         <v>0.13</v>
       </c>
       <c r="AP140">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ140">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR140">
         <v>1.45</v>
@@ -31366,7 +31369,7 @@
         <v>1.22</v>
       </c>
       <c r="AP146">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ146">
         <v>1.06</v>
@@ -33017,7 +33020,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ154">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR154">
         <v>1.64</v>
@@ -34044,7 +34047,7 @@
         <v>1.78</v>
       </c>
       <c r="AP159">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ159">
         <v>1.6</v>
@@ -34662,7 +34665,7 @@
         <v>1.6</v>
       </c>
       <c r="AP162">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ162">
         <v>1.38</v>
@@ -36310,7 +36313,7 @@
         <v>1.2</v>
       </c>
       <c r="AP170">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ170">
         <v>1.07</v>
@@ -36519,7 +36522,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ171">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR171">
         <v>2.04</v>
@@ -38373,7 +38376,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ180">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR180">
         <v>1.37</v>
@@ -38782,7 +38785,7 @@
         <v>1.18</v>
       </c>
       <c r="AP182">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ182">
         <v>1</v>
@@ -39812,7 +39815,7 @@
         <v>1.36</v>
       </c>
       <c r="AP187">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ187">
         <v>1.38</v>
@@ -41875,7 +41878,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ197">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR197">
         <v>1.86</v>
@@ -42490,7 +42493,7 @@
         <v>0.83</v>
       </c>
       <c r="AP200">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ200">
         <v>0.87</v>
@@ -43108,7 +43111,7 @@
         <v>1.33</v>
       </c>
       <c r="AP203">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ203">
         <v>1.33</v>
@@ -44550,10 +44553,10 @@
         <v>0.85</v>
       </c>
       <c r="AP210">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ210">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR210">
         <v>1.42</v>
@@ -47022,7 +47025,7 @@
         <v>0.46</v>
       </c>
       <c r="AP222">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ222">
         <v>0.6899999999999999</v>
@@ -47846,7 +47849,7 @@
         <v>0.93</v>
       </c>
       <c r="AP226">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ226">
         <v>1</v>
@@ -48052,7 +48055,7 @@
         <v>1.64</v>
       </c>
       <c r="AP227">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ227">
         <v>1.6</v>
@@ -49291,7 +49294,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ233">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR233">
         <v>1.34</v>
@@ -52584,7 +52587,7 @@
         <v>0.33</v>
       </c>
       <c r="AP249">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ249">
         <v>0.5</v>
@@ -52663,6 +52666,418 @@
       </c>
       <c r="BP249">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7856869</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45744.52083333334</v>
+      </c>
+      <c r="F250">
+        <v>2</v>
+      </c>
+      <c r="G250" t="s">
+        <v>79</v>
+      </c>
+      <c r="H250" t="s">
+        <v>77</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>0</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+      <c r="M250">
+        <v>0</v>
+      </c>
+      <c r="N250">
+        <v>0</v>
+      </c>
+      <c r="O250" t="s">
+        <v>86</v>
+      </c>
+      <c r="P250" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q250">
+        <v>3.4</v>
+      </c>
+      <c r="R250">
+        <v>1.85</v>
+      </c>
+      <c r="S250">
+        <v>3.45</v>
+      </c>
+      <c r="T250">
+        <v>1.55</v>
+      </c>
+      <c r="U250">
+        <v>2.3</v>
+      </c>
+      <c r="V250">
+        <v>3.55</v>
+      </c>
+      <c r="W250">
+        <v>1.25</v>
+      </c>
+      <c r="X250">
+        <v>9</v>
+      </c>
+      <c r="Y250">
+        <v>1.04</v>
+      </c>
+      <c r="Z250">
+        <v>2.7</v>
+      </c>
+      <c r="AA250">
+        <v>3.02</v>
+      </c>
+      <c r="AB250">
+        <v>2.71</v>
+      </c>
+      <c r="AC250">
+        <v>1.1</v>
+      </c>
+      <c r="AD250">
+        <v>6.25</v>
+      </c>
+      <c r="AE250">
+        <v>1.5</v>
+      </c>
+      <c r="AF250">
+        <v>2.3</v>
+      </c>
+      <c r="AG250">
+        <v>2.56</v>
+      </c>
+      <c r="AH250">
+        <v>1.45</v>
+      </c>
+      <c r="AI250">
+        <v>2.05</v>
+      </c>
+      <c r="AJ250">
+        <v>1.65</v>
+      </c>
+      <c r="AK250">
+        <v>1.44</v>
+      </c>
+      <c r="AL250">
+        <v>1.3</v>
+      </c>
+      <c r="AM250">
+        <v>1.44</v>
+      </c>
+      <c r="AN250">
+        <v>0.87</v>
+      </c>
+      <c r="AO250">
+        <v>1</v>
+      </c>
+      <c r="AP250">
+        <v>0.88</v>
+      </c>
+      <c r="AQ250">
+        <v>1</v>
+      </c>
+      <c r="AR250">
+        <v>1.45</v>
+      </c>
+      <c r="AS250">
+        <v>1.38</v>
+      </c>
+      <c r="AT250">
+        <v>2.83</v>
+      </c>
+      <c r="AU250">
+        <v>0</v>
+      </c>
+      <c r="AV250">
+        <v>2</v>
+      </c>
+      <c r="AW250">
+        <v>15</v>
+      </c>
+      <c r="AX250">
+        <v>8</v>
+      </c>
+      <c r="AY250">
+        <v>17</v>
+      </c>
+      <c r="AZ250">
+        <v>10</v>
+      </c>
+      <c r="BA250">
+        <v>12</v>
+      </c>
+      <c r="BB250">
+        <v>2</v>
+      </c>
+      <c r="BC250">
+        <v>14</v>
+      </c>
+      <c r="BD250">
+        <v>2.05</v>
+      </c>
+      <c r="BE250">
+        <v>6.4</v>
+      </c>
+      <c r="BF250">
+        <v>1.95</v>
+      </c>
+      <c r="BG250">
+        <v>1.43</v>
+      </c>
+      <c r="BH250">
+        <v>2.55</v>
+      </c>
+      <c r="BI250">
+        <v>1.71</v>
+      </c>
+      <c r="BJ250">
+        <v>1.96</v>
+      </c>
+      <c r="BK250">
+        <v>2.14</v>
+      </c>
+      <c r="BL250">
+        <v>1.6</v>
+      </c>
+      <c r="BM250">
+        <v>2.8</v>
+      </c>
+      <c r="BN250">
+        <v>1.36</v>
+      </c>
+      <c r="BO250">
+        <v>3.7</v>
+      </c>
+      <c r="BP250">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7856870</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45744.64583333334</v>
+      </c>
+      <c r="F251">
+        <v>2</v>
+      </c>
+      <c r="G251" t="s">
+        <v>72</v>
+      </c>
+      <c r="H251" t="s">
+        <v>71</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251">
+        <v>2</v>
+      </c>
+      <c r="K251">
+        <v>2</v>
+      </c>
+      <c r="L251">
+        <v>0</v>
+      </c>
+      <c r="M251">
+        <v>2</v>
+      </c>
+      <c r="N251">
+        <v>2</v>
+      </c>
+      <c r="O251" t="s">
+        <v>86</v>
+      </c>
+      <c r="P251" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q251">
+        <v>2.8</v>
+      </c>
+      <c r="R251">
+        <v>2</v>
+      </c>
+      <c r="S251">
+        <v>3.8</v>
+      </c>
+      <c r="T251">
+        <v>1.45</v>
+      </c>
+      <c r="U251">
+        <v>2.55</v>
+      </c>
+      <c r="V251">
+        <v>3.1</v>
+      </c>
+      <c r="W251">
+        <v>1.33</v>
+      </c>
+      <c r="X251">
+        <v>7</v>
+      </c>
+      <c r="Y251">
+        <v>1.06</v>
+      </c>
+      <c r="Z251">
+        <v>2.24</v>
+      </c>
+      <c r="AA251">
+        <v>3.18</v>
+      </c>
+      <c r="AB251">
+        <v>3.23</v>
+      </c>
+      <c r="AC251">
+        <v>1.07</v>
+      </c>
+      <c r="AD251">
+        <v>7.5</v>
+      </c>
+      <c r="AE251">
+        <v>1.4</v>
+      </c>
+      <c r="AF251">
+        <v>2.8</v>
+      </c>
+      <c r="AG251">
+        <v>2.1</v>
+      </c>
+      <c r="AH251">
+        <v>1.6</v>
+      </c>
+      <c r="AI251">
+        <v>1.85</v>
+      </c>
+      <c r="AJ251">
+        <v>1.8</v>
+      </c>
+      <c r="AK251">
+        <v>1.3</v>
+      </c>
+      <c r="AL251">
+        <v>1.28</v>
+      </c>
+      <c r="AM251">
+        <v>1.65</v>
+      </c>
+      <c r="AN251">
+        <v>1.56</v>
+      </c>
+      <c r="AO251">
+        <v>0.93</v>
+      </c>
+      <c r="AP251">
+        <v>1.47</v>
+      </c>
+      <c r="AQ251">
+        <v>1.06</v>
+      </c>
+      <c r="AR251">
+        <v>1.48</v>
+      </c>
+      <c r="AS251">
+        <v>1.31</v>
+      </c>
+      <c r="AT251">
+        <v>2.79</v>
+      </c>
+      <c r="AU251">
+        <v>5</v>
+      </c>
+      <c r="AV251">
+        <v>9</v>
+      </c>
+      <c r="AW251">
+        <v>13</v>
+      </c>
+      <c r="AX251">
+        <v>2</v>
+      </c>
+      <c r="AY251">
+        <v>24</v>
+      </c>
+      <c r="AZ251">
+        <v>12</v>
+      </c>
+      <c r="BA251">
+        <v>9</v>
+      </c>
+      <c r="BB251">
+        <v>2</v>
+      </c>
+      <c r="BC251">
+        <v>11</v>
+      </c>
+      <c r="BD251">
+        <v>1.64</v>
+      </c>
+      <c r="BE251">
+        <v>6.4</v>
+      </c>
+      <c r="BF251">
+        <v>2.55</v>
+      </c>
+      <c r="BG251">
+        <v>1.42</v>
+      </c>
+      <c r="BH251">
+        <v>2.55</v>
+      </c>
+      <c r="BI251">
+        <v>1.71</v>
+      </c>
+      <c r="BJ251">
+        <v>1.97</v>
+      </c>
+      <c r="BK251">
+        <v>2.15</v>
+      </c>
+      <c r="BL251">
+        <v>1.58</v>
+      </c>
+      <c r="BM251">
+        <v>2.8</v>
+      </c>
+      <c r="BN251">
+        <v>1.36</v>
+      </c>
+      <c r="BO251">
+        <v>3.8</v>
+      </c>
+      <c r="BP251">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="337">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -724,6 +724,15 @@
     <t>['40']</t>
   </si>
   <si>
+    <t>['10', '16', '49', '77']</t>
+  </si>
+  <si>
+    <t>['55']</t>
+  </si>
+  <si>
+    <t>['4', '29', '44', '81']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -1010,6 +1019,12 @@
   </si>
   <si>
     <t>['23', '45+2']</t>
+  </si>
+  <si>
+    <t>['63', '71', '82']</t>
+  </si>
+  <si>
+    <t>['18', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP251"/>
+  <dimension ref="A1:BP254"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1627,7 +1642,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1914,7 +1929,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ3">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2657,7 +2672,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2863,7 +2878,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2941,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -3353,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10">
         <v>0.9399999999999999</v>
@@ -3481,7 +3496,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3687,7 +3702,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3768,7 +3783,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ12">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3893,7 +3908,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3971,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ13">
         <v>1.6</v>
@@ -4099,7 +4114,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4305,7 +4320,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4511,7 +4526,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4798,7 +4813,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ17">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5129,7 +5144,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5335,7 +5350,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5413,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20">
         <v>0.5</v>
@@ -5747,7 +5762,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5953,7 +5968,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6034,7 +6049,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ23">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR23">
         <v>2</v>
@@ -7395,7 +7410,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7601,7 +7616,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7682,7 +7697,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ31">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR31">
         <v>1</v>
@@ -7807,7 +7822,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7885,7 +7900,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ32">
         <v>1.07</v>
@@ -8013,7 +8028,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8094,7 +8109,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ33">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR33">
         <v>2.11</v>
@@ -8425,7 +8440,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8837,7 +8852,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -8918,7 +8933,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR37">
         <v>1.39</v>
@@ -9455,7 +9470,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9533,7 +9548,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ40">
         <v>1.38</v>
@@ -9661,7 +9676,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9867,7 +9882,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10151,10 +10166,10 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ43">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR43">
         <v>1.6</v>
@@ -10563,7 +10578,7 @@
         <v>0.67</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ45">
         <v>1.38</v>
@@ -10897,7 +10912,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11309,7 +11324,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11387,7 +11402,7 @@
         <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ49">
         <v>1.06</v>
@@ -11802,7 +11817,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ51">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR51">
         <v>1.33</v>
@@ -12339,7 +12354,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12626,7 +12641,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ55">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR55">
         <v>1.71</v>
@@ -12957,7 +12972,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13369,7 +13384,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13447,7 +13462,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13575,7 +13590,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13862,7 +13877,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ61">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR61">
         <v>2.06</v>
@@ -13987,7 +14002,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -15017,7 +15032,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15098,7 +15113,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ67">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR67">
         <v>0.97</v>
@@ -15301,10 +15316,10 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ68">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR68">
         <v>1.66</v>
@@ -15429,7 +15444,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15841,7 +15856,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15919,7 +15934,7 @@
         <v>1.8</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ71">
         <v>1.38</v>
@@ -16047,7 +16062,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16125,7 +16140,7 @@
         <v>0.8</v>
       </c>
       <c r="AP72">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ72">
         <v>0.5</v>
@@ -16665,7 +16680,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16871,7 +16886,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17077,7 +17092,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17158,7 +17173,7 @@
         <v>2</v>
       </c>
       <c r="AQ77">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR77">
         <v>1.36</v>
@@ -17489,7 +17504,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17901,7 +17916,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18185,7 +18200,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ82">
         <v>1.38</v>
@@ -18313,7 +18328,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18394,7 +18409,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ83">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR83">
         <v>1.79</v>
@@ -18597,7 +18612,7 @@
         <v>1.8</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18806,7 +18821,7 @@
         <v>1</v>
       </c>
       <c r="AQ85">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18931,7 +18946,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19755,7 +19770,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19961,7 +19976,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20167,7 +20182,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20248,7 +20263,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ92">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR92">
         <v>1.5</v>
@@ -20373,7 +20388,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20657,7 +20672,7 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ94">
         <v>1.06</v>
@@ -20785,7 +20800,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -21484,7 +21499,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ98">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR98">
         <v>1.57</v>
@@ -22021,7 +22036,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22305,7 +22320,7 @@
         <v>1.17</v>
       </c>
       <c r="AP102">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ102">
         <v>0.88</v>
@@ -22511,10 +22526,10 @@
         <v>0.6</v>
       </c>
       <c r="AP103">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ103">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR103">
         <v>1.37</v>
@@ -22639,7 +22654,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -23257,7 +23272,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23463,7 +23478,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23875,7 +23890,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23953,7 +23968,7 @@
         <v>1.63</v>
       </c>
       <c r="AP110">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ110">
         <v>1.38</v>
@@ -24081,7 +24096,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24162,7 +24177,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ111">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR111">
         <v>1.65</v>
@@ -24287,7 +24302,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24493,7 +24508,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24780,7 +24795,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ114">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR114">
         <v>1.16</v>
@@ -24905,7 +24920,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24983,7 +24998,7 @@
         <v>1.43</v>
       </c>
       <c r="AP115">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ115">
         <v>1</v>
@@ -25192,7 +25207,7 @@
         <v>2</v>
       </c>
       <c r="AQ116">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR116">
         <v>1.34</v>
@@ -25807,7 +25822,7 @@
         <v>0.17</v>
       </c>
       <c r="AP119">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ119">
         <v>1.06</v>
@@ -26141,7 +26156,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26347,7 +26362,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26425,7 +26440,7 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ122">
         <v>1.07</v>
@@ -26837,10 +26852,10 @@
         <v>0.86</v>
       </c>
       <c r="AP124">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ124">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR124">
         <v>1.43</v>
@@ -27046,7 +27061,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ125">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR125">
         <v>1.4</v>
@@ -27171,7 +27186,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27867,7 +27882,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ129">
         <v>1.8</v>
@@ -28407,7 +28422,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28613,7 +28628,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -29309,7 +29324,7 @@
         <v>0.57</v>
       </c>
       <c r="AP136">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ136">
         <v>0.6899999999999999</v>
@@ -29437,7 +29452,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29518,7 +29533,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ137">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR137">
         <v>1.59</v>
@@ -29721,10 +29736,10 @@
         <v>0.88</v>
       </c>
       <c r="AP138">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ138">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR138">
         <v>1.66</v>
@@ -29927,7 +29942,7 @@
         <v>1.5</v>
       </c>
       <c r="AP139">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ139">
         <v>1</v>
@@ -30055,7 +30070,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30467,7 +30482,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30673,7 +30688,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30879,7 +30894,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30960,7 +30975,7 @@
         <v>2</v>
       </c>
       <c r="AQ144">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR144">
         <v>1.39</v>
@@ -31085,7 +31100,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31497,7 +31512,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31703,7 +31718,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31784,7 +31799,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ148">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR148">
         <v>1.32</v>
@@ -31909,7 +31924,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32115,7 +32130,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32193,10 +32208,10 @@
         <v>0.89</v>
       </c>
       <c r="AP150">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ150">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR150">
         <v>1.49</v>
@@ -32733,7 +32748,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32939,7 +32954,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33017,7 +33032,7 @@
         <v>0.44</v>
       </c>
       <c r="AP154">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ154">
         <v>1.06</v>
@@ -33432,7 +33447,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ156">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR156">
         <v>1.39</v>
@@ -33557,7 +33572,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -34459,7 +34474,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP161">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ161">
         <v>0.5</v>
@@ -34874,7 +34889,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ163">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR163">
         <v>1.24</v>
@@ -34999,7 +35014,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35080,7 +35095,7 @@
         <v>1</v>
       </c>
       <c r="AQ164">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR164">
         <v>1.45</v>
@@ -35411,7 +35426,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -36029,7 +36044,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36107,7 +36122,7 @@
         <v>1.6</v>
       </c>
       <c r="AP169">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ169">
         <v>1.8</v>
@@ -36235,7 +36250,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36441,7 +36456,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36647,7 +36662,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -37137,7 +37152,7 @@
         <v>1.7</v>
       </c>
       <c r="AP174">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ174">
         <v>1.6</v>
@@ -37552,7 +37567,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ176">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR176">
         <v>1.54</v>
@@ -37677,7 +37692,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -37755,7 +37770,7 @@
         <v>0.5</v>
       </c>
       <c r="AP177">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ177">
         <v>0.6899999999999999</v>
@@ -38295,7 +38310,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38373,7 +38388,7 @@
         <v>0.73</v>
       </c>
       <c r="AP180">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ180">
         <v>1.06</v>
@@ -38579,10 +38594,10 @@
         <v>1.45</v>
       </c>
       <c r="AP181">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ181">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR181">
         <v>1.62</v>
@@ -39406,7 +39421,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ185">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR185">
         <v>1.75</v>
@@ -39612,7 +39627,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ186">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR186">
         <v>1.23</v>
@@ -39737,7 +39752,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -40021,7 +40036,7 @@
         <v>1.09</v>
       </c>
       <c r="AP188">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ188">
         <v>1.07</v>
@@ -40149,7 +40164,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40355,7 +40370,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40561,7 +40576,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40973,7 +40988,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -41179,7 +41194,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -41463,7 +41478,7 @@
         <v>1.08</v>
       </c>
       <c r="AP195">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ195">
         <v>0.88</v>
@@ -42287,10 +42302,10 @@
         <v>1</v>
       </c>
       <c r="AP199">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ199">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR199">
         <v>1.46</v>
@@ -42496,7 +42511,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ200">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR200">
         <v>1.39</v>
@@ -42827,7 +42842,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -42905,7 +42920,7 @@
         <v>1.5</v>
       </c>
       <c r="AP202">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ202">
         <v>1.38</v>
@@ -43033,7 +43048,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43114,7 +43129,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ203">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR203">
         <v>1.35</v>
@@ -43445,7 +43460,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43651,7 +43666,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -44269,7 +44284,7 @@
         <v>214</v>
       </c>
       <c r="P209" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q209">
         <v>4.75</v>
@@ -44475,7 +44490,7 @@
         <v>215</v>
       </c>
       <c r="P210" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q210">
         <v>2.8</v>
@@ -44968,7 +44983,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ212">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR212">
         <v>1.27</v>
@@ -45093,7 +45108,7 @@
         <v>86</v>
       </c>
       <c r="P213" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q213">
         <v>2.65</v>
@@ -45174,7 +45189,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ213">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR213">
         <v>1.24</v>
@@ -45377,7 +45392,7 @@
         <v>1.69</v>
       </c>
       <c r="AP214">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ214">
         <v>1.6</v>
@@ -45505,7 +45520,7 @@
         <v>86</v>
       </c>
       <c r="P215" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q215">
         <v>6.8</v>
@@ -45711,7 +45726,7 @@
         <v>218</v>
       </c>
       <c r="P216" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q216">
         <v>1.91</v>
@@ -45995,7 +46010,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP217">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ217">
         <v>0.9399999999999999</v>
@@ -46123,7 +46138,7 @@
         <v>220</v>
       </c>
       <c r="P218" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q218">
         <v>2.18</v>
@@ -46535,7 +46550,7 @@
         <v>221</v>
       </c>
       <c r="P220" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q220">
         <v>4.3</v>
@@ -46613,10 +46628,10 @@
         <v>1.46</v>
       </c>
       <c r="AP220">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ220">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR220">
         <v>1.73</v>
@@ -47359,7 +47374,7 @@
         <v>223</v>
       </c>
       <c r="P224" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q224">
         <v>3.5</v>
@@ -47565,7 +47580,7 @@
         <v>209</v>
       </c>
       <c r="P225" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q225">
         <v>3.6</v>
@@ -47977,7 +47992,7 @@
         <v>156</v>
       </c>
       <c r="P227" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q227">
         <v>3.75</v>
@@ -48183,7 +48198,7 @@
         <v>86</v>
       </c>
       <c r="P228" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q228">
         <v>2.24</v>
@@ -48470,7 +48485,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ229">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR229">
         <v>1.81</v>
@@ -48673,7 +48688,7 @@
         <v>1.07</v>
       </c>
       <c r="AP230">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ230">
         <v>1</v>
@@ -48879,7 +48894,7 @@
         <v>1.86</v>
       </c>
       <c r="AP231">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ231">
         <v>1.8</v>
@@ -49088,7 +49103,7 @@
         <v>1</v>
       </c>
       <c r="AQ232">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR232">
         <v>1.4</v>
@@ -49419,7 +49434,7 @@
         <v>226</v>
       </c>
       <c r="P234" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -49625,7 +49640,7 @@
         <v>214</v>
       </c>
       <c r="P235" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q235">
         <v>3.65</v>
@@ -50530,7 +50545,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ239">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR239">
         <v>2.11</v>
@@ -50733,7 +50748,7 @@
         <v>0.93</v>
       </c>
       <c r="AP240">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AQ240">
         <v>0.88</v>
@@ -50861,7 +50876,7 @@
         <v>86</v>
       </c>
       <c r="P241" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q241">
         <v>4</v>
@@ -51067,7 +51082,7 @@
         <v>86</v>
       </c>
       <c r="P242" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51685,7 +51700,7 @@
         <v>231</v>
       </c>
       <c r="P245" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q245">
         <v>2.3</v>
@@ -52303,7 +52318,7 @@
         <v>234</v>
       </c>
       <c r="P248" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q248">
         <v>2.6</v>
@@ -52509,7 +52524,7 @@
         <v>235</v>
       </c>
       <c r="P249" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q249">
         <v>2.05</v>
@@ -52921,7 +52936,7 @@
         <v>86</v>
       </c>
       <c r="P251" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q251">
         <v>2.8</v>
@@ -53078,6 +53093,624 @@
       </c>
       <c r="BP251">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7856871</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45745.39583333334</v>
+      </c>
+      <c r="F252">
+        <v>2</v>
+      </c>
+      <c r="G252" t="s">
+        <v>76</v>
+      </c>
+      <c r="H252" t="s">
+        <v>70</v>
+      </c>
+      <c r="I252">
+        <v>2</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>2</v>
+      </c>
+      <c r="L252">
+        <v>4</v>
+      </c>
+      <c r="M252">
+        <v>3</v>
+      </c>
+      <c r="N252">
+        <v>7</v>
+      </c>
+      <c r="O252" t="s">
+        <v>236</v>
+      </c>
+      <c r="P252" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q252">
+        <v>2.8</v>
+      </c>
+      <c r="R252">
+        <v>1.95</v>
+      </c>
+      <c r="S252">
+        <v>4</v>
+      </c>
+      <c r="T252">
+        <v>1.48</v>
+      </c>
+      <c r="U252">
+        <v>2.45</v>
+      </c>
+      <c r="V252">
+        <v>3.2</v>
+      </c>
+      <c r="W252">
+        <v>1.3</v>
+      </c>
+      <c r="X252">
+        <v>7.5</v>
+      </c>
+      <c r="Y252">
+        <v>1.05</v>
+      </c>
+      <c r="Z252">
+        <v>2.51</v>
+      </c>
+      <c r="AA252">
+        <v>3.12</v>
+      </c>
+      <c r="AB252">
+        <v>2.85</v>
+      </c>
+      <c r="AC252">
+        <v>1.08</v>
+      </c>
+      <c r="AD252">
+        <v>7</v>
+      </c>
+      <c r="AE252">
+        <v>1.42</v>
+      </c>
+      <c r="AF252">
+        <v>2.75</v>
+      </c>
+      <c r="AG252">
+        <v>2.15</v>
+      </c>
+      <c r="AH252">
+        <v>1.57</v>
+      </c>
+      <c r="AI252">
+        <v>1.9</v>
+      </c>
+      <c r="AJ252">
+        <v>1.75</v>
+      </c>
+      <c r="AK252">
+        <v>1.28</v>
+      </c>
+      <c r="AL252">
+        <v>1.3</v>
+      </c>
+      <c r="AM252">
+        <v>1.67</v>
+      </c>
+      <c r="AN252">
+        <v>1.27</v>
+      </c>
+      <c r="AO252">
+        <v>0.87</v>
+      </c>
+      <c r="AP252">
+        <v>1.38</v>
+      </c>
+      <c r="AQ252">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AR252">
+        <v>1.82</v>
+      </c>
+      <c r="AS252">
+        <v>1.21</v>
+      </c>
+      <c r="AT252">
+        <v>3.03</v>
+      </c>
+      <c r="AU252">
+        <v>8</v>
+      </c>
+      <c r="AV252">
+        <v>7</v>
+      </c>
+      <c r="AW252">
+        <v>17</v>
+      </c>
+      <c r="AX252">
+        <v>8</v>
+      </c>
+      <c r="AY252">
+        <v>35</v>
+      </c>
+      <c r="AZ252">
+        <v>17</v>
+      </c>
+      <c r="BA252">
+        <v>6</v>
+      </c>
+      <c r="BB252">
+        <v>2</v>
+      </c>
+      <c r="BC252">
+        <v>8</v>
+      </c>
+      <c r="BD252">
+        <v>1.65</v>
+      </c>
+      <c r="BE252">
+        <v>6.5</v>
+      </c>
+      <c r="BF252">
+        <v>2.5</v>
+      </c>
+      <c r="BG252">
+        <v>1.33</v>
+      </c>
+      <c r="BH252">
+        <v>2.95</v>
+      </c>
+      <c r="BI252">
+        <v>1.56</v>
+      </c>
+      <c r="BJ252">
+        <v>2.23</v>
+      </c>
+      <c r="BK252">
+        <v>1.9</v>
+      </c>
+      <c r="BL252">
+        <v>1.76</v>
+      </c>
+      <c r="BM252">
+        <v>2.43</v>
+      </c>
+      <c r="BN252">
+        <v>1.47</v>
+      </c>
+      <c r="BO252">
+        <v>3.15</v>
+      </c>
+      <c r="BP252">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7856872</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45745.625</v>
+      </c>
+      <c r="F253">
+        <v>2</v>
+      </c>
+      <c r="G253" t="s">
+        <v>81</v>
+      </c>
+      <c r="H253" t="s">
+        <v>80</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253">
+        <v>1</v>
+      </c>
+      <c r="K253">
+        <v>1</v>
+      </c>
+      <c r="L253">
+        <v>1</v>
+      </c>
+      <c r="M253">
+        <v>2</v>
+      </c>
+      <c r="N253">
+        <v>3</v>
+      </c>
+      <c r="O253" t="s">
+        <v>237</v>
+      </c>
+      <c r="P253" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q253">
+        <v>2.95</v>
+      </c>
+      <c r="R253">
+        <v>2.17</v>
+      </c>
+      <c r="S253">
+        <v>3.3</v>
+      </c>
+      <c r="T253">
+        <v>1.36</v>
+      </c>
+      <c r="U253">
+        <v>2.8</v>
+      </c>
+      <c r="V253">
+        <v>2.7</v>
+      </c>
+      <c r="W253">
+        <v>1.38</v>
+      </c>
+      <c r="X253">
+        <v>6.5</v>
+      </c>
+      <c r="Y253">
+        <v>1.07</v>
+      </c>
+      <c r="Z253">
+        <v>2.3</v>
+      </c>
+      <c r="AA253">
+        <v>3.1</v>
+      </c>
+      <c r="AB253">
+        <v>2.95</v>
+      </c>
+      <c r="AC253">
+        <v>1.02</v>
+      </c>
+      <c r="AD253">
+        <v>11.5</v>
+      </c>
+      <c r="AE253">
+        <v>1.28</v>
+      </c>
+      <c r="AF253">
+        <v>3.55</v>
+      </c>
+      <c r="AG253">
+        <v>1.95</v>
+      </c>
+      <c r="AH253">
+        <v>1.7</v>
+      </c>
+      <c r="AI253">
+        <v>1.72</v>
+      </c>
+      <c r="AJ253">
+        <v>1.98</v>
+      </c>
+      <c r="AK253">
+        <v>1.43</v>
+      </c>
+      <c r="AL253">
+        <v>1.29</v>
+      </c>
+      <c r="AM253">
+        <v>1.57</v>
+      </c>
+      <c r="AN253">
+        <v>2</v>
+      </c>
+      <c r="AO253">
+        <v>1.33</v>
+      </c>
+      <c r="AP253">
+        <v>1.88</v>
+      </c>
+      <c r="AQ253">
+        <v>1.44</v>
+      </c>
+      <c r="AR253">
+        <v>1.7</v>
+      </c>
+      <c r="AS253">
+        <v>1.54</v>
+      </c>
+      <c r="AT253">
+        <v>3.24</v>
+      </c>
+      <c r="AU253">
+        <v>7</v>
+      </c>
+      <c r="AV253">
+        <v>10</v>
+      </c>
+      <c r="AW253">
+        <v>9</v>
+      </c>
+      <c r="AX253">
+        <v>5</v>
+      </c>
+      <c r="AY253">
+        <v>18</v>
+      </c>
+      <c r="AZ253">
+        <v>15</v>
+      </c>
+      <c r="BA253">
+        <v>6</v>
+      </c>
+      <c r="BB253">
+        <v>3</v>
+      </c>
+      <c r="BC253">
+        <v>9</v>
+      </c>
+      <c r="BD253">
+        <v>1.74</v>
+      </c>
+      <c r="BE253">
+        <v>6.4</v>
+      </c>
+      <c r="BF253">
+        <v>2.33</v>
+      </c>
+      <c r="BG253">
+        <v>1.4</v>
+      </c>
+      <c r="BH253">
+        <v>2.65</v>
+      </c>
+      <c r="BI253">
+        <v>1.68</v>
+      </c>
+      <c r="BJ253">
+        <v>2</v>
+      </c>
+      <c r="BK253">
+        <v>2.12</v>
+      </c>
+      <c r="BL253">
+        <v>1.61</v>
+      </c>
+      <c r="BM253">
+        <v>2.7</v>
+      </c>
+      <c r="BN253">
+        <v>1.38</v>
+      </c>
+      <c r="BO253">
+        <v>3.65</v>
+      </c>
+      <c r="BP253">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="254" spans="1:68">
+      <c r="A254" s="1">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>7856873</v>
+      </c>
+      <c r="C254" t="s">
+        <v>68</v>
+      </c>
+      <c r="D254" t="s">
+        <v>69</v>
+      </c>
+      <c r="E254" s="2">
+        <v>45746.375</v>
+      </c>
+      <c r="F254">
+        <v>2</v>
+      </c>
+      <c r="G254" t="s">
+        <v>78</v>
+      </c>
+      <c r="H254" t="s">
+        <v>73</v>
+      </c>
+      <c r="I254">
+        <v>3</v>
+      </c>
+      <c r="J254">
+        <v>0</v>
+      </c>
+      <c r="K254">
+        <v>3</v>
+      </c>
+      <c r="L254">
+        <v>4</v>
+      </c>
+      <c r="M254">
+        <v>0</v>
+      </c>
+      <c r="N254">
+        <v>4</v>
+      </c>
+      <c r="O254" t="s">
+        <v>238</v>
+      </c>
+      <c r="P254" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q254">
+        <v>3</v>
+      </c>
+      <c r="R254">
+        <v>2.08</v>
+      </c>
+      <c r="S254">
+        <v>3.4</v>
+      </c>
+      <c r="T254">
+        <v>1.44</v>
+      </c>
+      <c r="U254">
+        <v>2.65</v>
+      </c>
+      <c r="V254">
+        <v>3.05</v>
+      </c>
+      <c r="W254">
+        <v>1.34</v>
+      </c>
+      <c r="X254">
+        <v>7</v>
+      </c>
+      <c r="Y254">
+        <v>1.05</v>
+      </c>
+      <c r="Z254">
+        <v>2.55</v>
+      </c>
+      <c r="AA254">
+        <v>3.12</v>
+      </c>
+      <c r="AB254">
+        <v>2.8</v>
+      </c>
+      <c r="AC254">
+        <v>1.04</v>
+      </c>
+      <c r="AD254">
+        <v>9.5</v>
+      </c>
+      <c r="AE254">
+        <v>1.34</v>
+      </c>
+      <c r="AF254">
+        <v>3.15</v>
+      </c>
+      <c r="AG254">
+        <v>2.05</v>
+      </c>
+      <c r="AH254">
+        <v>1.61</v>
+      </c>
+      <c r="AI254">
+        <v>1.84</v>
+      </c>
+      <c r="AJ254">
+        <v>1.84</v>
+      </c>
+      <c r="AK254">
+        <v>1.42</v>
+      </c>
+      <c r="AL254">
+        <v>1.3</v>
+      </c>
+      <c r="AM254">
+        <v>1.56</v>
+      </c>
+      <c r="AN254">
+        <v>1.4</v>
+      </c>
+      <c r="AO254">
+        <v>1.27</v>
+      </c>
+      <c r="AP254">
+        <v>1.5</v>
+      </c>
+      <c r="AQ254">
+        <v>1.19</v>
+      </c>
+      <c r="AR254">
+        <v>1.44</v>
+      </c>
+      <c r="AS254">
+        <v>1.29</v>
+      </c>
+      <c r="AT254">
+        <v>2.73</v>
+      </c>
+      <c r="AU254">
+        <v>10</v>
+      </c>
+      <c r="AV254">
+        <v>9</v>
+      </c>
+      <c r="AW254">
+        <v>5</v>
+      </c>
+      <c r="AX254">
+        <v>16</v>
+      </c>
+      <c r="AY254">
+        <v>17</v>
+      </c>
+      <c r="AZ254">
+        <v>32</v>
+      </c>
+      <c r="BA254">
+        <v>2</v>
+      </c>
+      <c r="BB254">
+        <v>7</v>
+      </c>
+      <c r="BC254">
+        <v>9</v>
+      </c>
+      <c r="BD254">
+        <v>1.78</v>
+      </c>
+      <c r="BE254">
+        <v>6.4</v>
+      </c>
+      <c r="BF254">
+        <v>2.25</v>
+      </c>
+      <c r="BG254">
+        <v>1.34</v>
+      </c>
+      <c r="BH254">
+        <v>2.9</v>
+      </c>
+      <c r="BI254">
+        <v>1.58</v>
+      </c>
+      <c r="BJ254">
+        <v>2.18</v>
+      </c>
+      <c r="BK254">
+        <v>1.94</v>
+      </c>
+      <c r="BL254">
+        <v>1.73</v>
+      </c>
+      <c r="BM254">
+        <v>2.48</v>
+      </c>
+      <c r="BN254">
+        <v>1.45</v>
+      </c>
+      <c r="BO254">
+        <v>3.2</v>
+      </c>
+      <c r="BP254">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="338">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1026,6 +1026,9 @@
   <si>
     <t>['18', '90+4']</t>
   </si>
+  <si>
+    <t>['44', '85']</t>
+  </si>
 </sst>
 </file>
 
@@ -1386,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP254"/>
+  <dimension ref="A1:BP255"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3577,7 +3580,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ11">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4398,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -6870,7 +6873,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ27">
         <v>0.5</v>
@@ -11814,7 +11817,7 @@
         <v>2.33</v>
       </c>
       <c r="AP51">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ51">
         <v>1.44</v>
@@ -12229,7 +12232,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ53">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR53">
         <v>1.19</v>
@@ -14698,7 +14701,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ65">
         <v>0.88</v>
@@ -15525,7 +15528,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ69">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR69">
         <v>1.9</v>
@@ -17994,7 +17997,7 @@
         <v>0.6</v>
       </c>
       <c r="AP81">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ81">
         <v>0.9399999999999999</v>
@@ -19027,7 +19030,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ86">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR86">
         <v>1.56</v>
@@ -22114,10 +22117,10 @@
         <v>1.25</v>
       </c>
       <c r="AP101">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ101">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR101">
         <v>1.23</v>
@@ -24792,7 +24795,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ114">
         <v>1.19</v>
@@ -25413,7 +25416,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ117">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR117">
         <v>1.93</v>
@@ -26234,7 +26237,7 @@
         <v>1.8</v>
       </c>
       <c r="AP121">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ121">
         <v>1.6</v>
@@ -27267,7 +27270,7 @@
         <v>2</v>
       </c>
       <c r="AQ126">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR126">
         <v>1.38</v>
@@ -27885,7 +27888,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ129">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR129">
         <v>1.77</v>
@@ -30560,7 +30563,7 @@
         <v>1.38</v>
       </c>
       <c r="AP142">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ142">
         <v>1.07</v>
@@ -31181,7 +31184,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ145">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR145">
         <v>1.39</v>
@@ -33238,7 +33241,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP155">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ155">
         <v>0.6899999999999999</v>
@@ -34271,7 +34274,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ160">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR160">
         <v>1.52</v>
@@ -35710,7 +35713,7 @@
         <v>1.1</v>
       </c>
       <c r="AP167">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ167">
         <v>1.06</v>
@@ -36125,7 +36128,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ169">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR169">
         <v>1.46</v>
@@ -38182,7 +38185,7 @@
         <v>1.55</v>
       </c>
       <c r="AP179">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ179">
         <v>1.38</v>
@@ -39009,7 +39012,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ183">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR183">
         <v>1.63</v>
@@ -41684,7 +41687,7 @@
         <v>1.08</v>
       </c>
       <c r="AP196">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ196">
         <v>1</v>
@@ -42717,7 +42720,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ201">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR201">
         <v>1.3</v>
@@ -45186,7 +45189,7 @@
         <v>0.77</v>
       </c>
       <c r="AP213">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ213">
         <v>0.8100000000000001</v>
@@ -45601,7 +45604,7 @@
         <v>1</v>
       </c>
       <c r="AQ215">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR215">
         <v>1.43</v>
@@ -48897,7 +48900,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ231">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR231">
         <v>1.73</v>
@@ -49306,7 +49309,7 @@
         <v>1</v>
       </c>
       <c r="AP233">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ233">
         <v>1.06</v>
@@ -53711,6 +53714,212 @@
       </c>
       <c r="BP254">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="255" spans="1:68">
+      <c r="A255" s="1">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>7856874</v>
+      </c>
+      <c r="C255" t="s">
+        <v>68</v>
+      </c>
+      <c r="D255" t="s">
+        <v>69</v>
+      </c>
+      <c r="E255" s="2">
+        <v>45746.60416666666</v>
+      </c>
+      <c r="F255">
+        <v>2</v>
+      </c>
+      <c r="G255" t="s">
+        <v>83</v>
+      </c>
+      <c r="H255" t="s">
+        <v>74</v>
+      </c>
+      <c r="I255">
+        <v>1</v>
+      </c>
+      <c r="J255">
+        <v>1</v>
+      </c>
+      <c r="K255">
+        <v>2</v>
+      </c>
+      <c r="L255">
+        <v>1</v>
+      </c>
+      <c r="M255">
+        <v>2</v>
+      </c>
+      <c r="N255">
+        <v>3</v>
+      </c>
+      <c r="O255" t="s">
+        <v>153</v>
+      </c>
+      <c r="P255" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q255">
+        <v>4.1</v>
+      </c>
+      <c r="R255">
+        <v>1.98</v>
+      </c>
+      <c r="S255">
+        <v>2.7</v>
+      </c>
+      <c r="T255">
+        <v>1.49</v>
+      </c>
+      <c r="U255">
+        <v>2.43</v>
+      </c>
+      <c r="V255">
+        <v>3.3</v>
+      </c>
+      <c r="W255">
+        <v>1.27</v>
+      </c>
+      <c r="X255">
+        <v>8.5</v>
+      </c>
+      <c r="Y255">
+        <v>1.04</v>
+      </c>
+      <c r="Z255">
+        <v>3.75</v>
+      </c>
+      <c r="AA255">
+        <v>3.35</v>
+      </c>
+      <c r="AB255">
+        <v>1.98</v>
+      </c>
+      <c r="AC255">
+        <v>1.1</v>
+      </c>
+      <c r="AD255">
+        <v>6.62</v>
+      </c>
+      <c r="AE255">
+        <v>1.46</v>
+      </c>
+      <c r="AF255">
+        <v>2.67</v>
+      </c>
+      <c r="AG255">
+        <v>2.3</v>
+      </c>
+      <c r="AH255">
+        <v>1.5</v>
+      </c>
+      <c r="AI255">
+        <v>2</v>
+      </c>
+      <c r="AJ255">
+        <v>1.7</v>
+      </c>
+      <c r="AK255">
+        <v>1.76</v>
+      </c>
+      <c r="AL255">
+        <v>1.3</v>
+      </c>
+      <c r="AM255">
+        <v>1.29</v>
+      </c>
+      <c r="AN255">
+        <v>1.93</v>
+      </c>
+      <c r="AO255">
+        <v>1.8</v>
+      </c>
+      <c r="AP255">
+        <v>1.81</v>
+      </c>
+      <c r="AQ255">
+        <v>1.88</v>
+      </c>
+      <c r="AR255">
+        <v>1.36</v>
+      </c>
+      <c r="AS255">
+        <v>1.64</v>
+      </c>
+      <c r="AT255">
+        <v>3</v>
+      </c>
+      <c r="AU255">
+        <v>3</v>
+      </c>
+      <c r="AV255">
+        <v>5</v>
+      </c>
+      <c r="AW255">
+        <v>4</v>
+      </c>
+      <c r="AX255">
+        <v>12</v>
+      </c>
+      <c r="AY255">
+        <v>9</v>
+      </c>
+      <c r="AZ255">
+        <v>20</v>
+      </c>
+      <c r="BA255">
+        <v>4</v>
+      </c>
+      <c r="BB255">
+        <v>10</v>
+      </c>
+      <c r="BC255">
+        <v>14</v>
+      </c>
+      <c r="BD255">
+        <v>2.55</v>
+      </c>
+      <c r="BE255">
+        <v>6.4</v>
+      </c>
+      <c r="BF255">
+        <v>1.63</v>
+      </c>
+      <c r="BG255">
+        <v>1.4</v>
+      </c>
+      <c r="BH255">
+        <v>2.63</v>
+      </c>
+      <c r="BI255">
+        <v>1.7</v>
+      </c>
+      <c r="BJ255">
+        <v>2</v>
+      </c>
+      <c r="BK255">
+        <v>2.1</v>
+      </c>
+      <c r="BL255">
+        <v>1.62</v>
+      </c>
+      <c r="BM255">
+        <v>2.7</v>
+      </c>
+      <c r="BN255">
+        <v>1.38</v>
+      </c>
+      <c r="BO255">
+        <v>3.55</v>
+      </c>
+      <c r="BP255">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="339">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1029,6 +1029,9 @@
   <si>
     <t>['44', '85']</t>
   </si>
+  <si>
+    <t>['12', '16']</t>
+  </si>
 </sst>
 </file>
 
@@ -1389,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP255"/>
+  <dimension ref="A1:BP257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2962,7 +2965,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ8">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3992,7 +3995,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ13">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4195,7 +4198,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ14">
         <v>1.06</v>
@@ -4607,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ16">
         <v>1.07</v>
@@ -5228,7 +5231,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR19">
         <v>1.85</v>
@@ -8524,7 +8527,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR35">
         <v>1.45</v>
@@ -8727,7 +8730,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ36">
         <v>1.06</v>
@@ -10787,7 +10790,7 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ46">
         <v>1.07</v>
@@ -11202,7 +11205,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR48">
         <v>0.93</v>
@@ -12435,7 +12438,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ54">
         <v>1.38</v>
@@ -13674,7 +13677,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ60">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR60">
         <v>1.71</v>
@@ -14289,7 +14292,7 @@
         <v>0.75</v>
       </c>
       <c r="AP63">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ63">
         <v>1.38</v>
@@ -14907,10 +14910,10 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR66">
         <v>1.39</v>
@@ -16558,7 +16561,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ74">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR74">
         <v>1.37</v>
@@ -17173,7 +17176,7 @@
         <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ77">
         <v>1.44</v>
@@ -18618,7 +18621,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR84">
         <v>1.43</v>
@@ -18821,7 +18824,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ85">
         <v>0.8100000000000001</v>
@@ -21087,7 +21090,7 @@
         <v>0.2</v>
       </c>
       <c r="AP96">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ96">
         <v>1.06</v>
@@ -21293,10 +21296,10 @@
         <v>1.67</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR97">
         <v>1.37</v>
@@ -21708,7 +21711,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ99">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR99">
         <v>1.24</v>
@@ -24383,10 +24386,10 @@
         <v>1.5</v>
       </c>
       <c r="AP112">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ112">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR112">
         <v>1.44</v>
@@ -25004,7 +25007,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR115">
         <v>1.47</v>
@@ -25207,7 +25210,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ116">
         <v>0.8100000000000001</v>
@@ -26240,7 +26243,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ121">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR121">
         <v>1.14</v>
@@ -27267,7 +27270,7 @@
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ126">
         <v>1.88</v>
@@ -27473,7 +27476,7 @@
         <v>1.29</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ127">
         <v>1</v>
@@ -27682,7 +27685,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ128">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR128">
         <v>1.38</v>
@@ -28300,7 +28303,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ131">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR131">
         <v>1.58</v>
@@ -30357,7 +30360,7 @@
         <v>0.63</v>
       </c>
       <c r="AP141">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ141">
         <v>0.6899999999999999</v>
@@ -30772,7 +30775,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ143">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR143">
         <v>1.8</v>
@@ -30975,7 +30978,7 @@
         <v>0.75</v>
       </c>
       <c r="AP144">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ144">
         <v>1.19</v>
@@ -31593,7 +31596,7 @@
         <v>1.22</v>
       </c>
       <c r="AP147">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ147">
         <v>1.38</v>
@@ -32626,7 +32629,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ152">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR152">
         <v>1.23</v>
@@ -32829,10 +32832,10 @@
         <v>2</v>
       </c>
       <c r="AP153">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ153">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -33859,7 +33862,7 @@
         <v>1.44</v>
       </c>
       <c r="AP158">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ158">
         <v>1</v>
@@ -34068,7 +34071,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ159">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR159">
         <v>1.46</v>
@@ -35095,7 +35098,7 @@
         <v>1.3</v>
       </c>
       <c r="AP164">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ164">
         <v>1.44</v>
@@ -35510,7 +35513,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ166">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR166">
         <v>1.81</v>
@@ -36743,7 +36746,7 @@
         <v>0.5</v>
       </c>
       <c r="AP172">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ172">
         <v>0.5</v>
@@ -37158,7 +37161,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ174">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR174">
         <v>1.61</v>
@@ -37979,7 +37982,7 @@
         <v>1.18</v>
       </c>
       <c r="AP178">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ178">
         <v>0.88</v>
@@ -38806,7 +38809,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ182">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR182">
         <v>1.35</v>
@@ -40451,7 +40454,7 @@
         <v>1.09</v>
       </c>
       <c r="AP190">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ190">
         <v>1.06</v>
@@ -40866,7 +40869,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ192">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR192">
         <v>2.13</v>
@@ -41275,7 +41278,7 @@
         <v>0.5</v>
       </c>
       <c r="AP194">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ194">
         <v>0.9399999999999999</v>
@@ -41690,7 +41693,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ196">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR196">
         <v>1.24</v>
@@ -43747,7 +43750,7 @@
         <v>0.42</v>
       </c>
       <c r="AP206">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ206">
         <v>0.6899999999999999</v>
@@ -44368,7 +44371,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ209">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR209">
         <v>1.6</v>
@@ -44780,7 +44783,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ211">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR211">
         <v>1.81</v>
@@ -45398,7 +45401,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ214">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR214">
         <v>1.44</v>
@@ -45601,7 +45604,7 @@
         <v>1.77</v>
       </c>
       <c r="AP215">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ215">
         <v>1.88</v>
@@ -45807,7 +45810,7 @@
         <v>1</v>
       </c>
       <c r="AP216">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ216">
         <v>0.88</v>
@@ -47870,7 +47873,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ226">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR226">
         <v>1.35</v>
@@ -48076,7 +48079,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ227">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR227">
         <v>1.44</v>
@@ -48279,7 +48282,7 @@
         <v>0.64</v>
       </c>
       <c r="AP228">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ228">
         <v>0.9399999999999999</v>
@@ -49103,7 +49106,7 @@
         <v>1.29</v>
       </c>
       <c r="AP232">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ232">
         <v>1.19</v>
@@ -52196,7 +52199,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ247">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR247">
         <v>1.55</v>
@@ -53920,6 +53923,418 @@
       </c>
       <c r="BP255">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="256" spans="1:68">
+      <c r="A256" s="1">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>7856875</v>
+      </c>
+      <c r="C256" t="s">
+        <v>68</v>
+      </c>
+      <c r="D256" t="s">
+        <v>69</v>
+      </c>
+      <c r="E256" s="2">
+        <v>45747.47916666666</v>
+      </c>
+      <c r="F256">
+        <v>2</v>
+      </c>
+      <c r="G256" t="s">
+        <v>84</v>
+      </c>
+      <c r="H256" t="s">
+        <v>85</v>
+      </c>
+      <c r="I256">
+        <v>0</v>
+      </c>
+      <c r="J256">
+        <v>2</v>
+      </c>
+      <c r="K256">
+        <v>2</v>
+      </c>
+      <c r="L256">
+        <v>0</v>
+      </c>
+      <c r="M256">
+        <v>2</v>
+      </c>
+      <c r="N256">
+        <v>2</v>
+      </c>
+      <c r="O256" t="s">
+        <v>86</v>
+      </c>
+      <c r="P256" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q256">
+        <v>3.65</v>
+      </c>
+      <c r="R256">
+        <v>1.96</v>
+      </c>
+      <c r="S256">
+        <v>3.15</v>
+      </c>
+      <c r="T256">
+        <v>1.55</v>
+      </c>
+      <c r="U256">
+        <v>2.35</v>
+      </c>
+      <c r="V256">
+        <v>3.7</v>
+      </c>
+      <c r="W256">
+        <v>1.25</v>
+      </c>
+      <c r="X256">
+        <v>9.5</v>
+      </c>
+      <c r="Y256">
+        <v>1.03</v>
+      </c>
+      <c r="Z256">
+        <v>2.99</v>
+      </c>
+      <c r="AA256">
+        <v>3.02</v>
+      </c>
+      <c r="AB256">
+        <v>2.48</v>
+      </c>
+      <c r="AC256">
+        <v>1.08</v>
+      </c>
+      <c r="AD256">
+        <v>7.5</v>
+      </c>
+      <c r="AE256">
+        <v>1.48</v>
+      </c>
+      <c r="AF256">
+        <v>2.37</v>
+      </c>
+      <c r="AG256">
+        <v>2.56</v>
+      </c>
+      <c r="AH256">
+        <v>1.45</v>
+      </c>
+      <c r="AI256">
+        <v>2.15</v>
+      </c>
+      <c r="AJ256">
+        <v>1.61</v>
+      </c>
+      <c r="AK256">
+        <v>1.52</v>
+      </c>
+      <c r="AL256">
+        <v>1.35</v>
+      </c>
+      <c r="AM256">
+        <v>1.38</v>
+      </c>
+      <c r="AN256">
+        <v>1</v>
+      </c>
+      <c r="AO256">
+        <v>1</v>
+      </c>
+      <c r="AP256">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AQ256">
+        <v>1.12</v>
+      </c>
+      <c r="AR256">
+        <v>1.45</v>
+      </c>
+      <c r="AS256">
+        <v>1.29</v>
+      </c>
+      <c r="AT256">
+        <v>2.74</v>
+      </c>
+      <c r="AU256">
+        <v>5</v>
+      </c>
+      <c r="AV256">
+        <v>5</v>
+      </c>
+      <c r="AW256">
+        <v>5</v>
+      </c>
+      <c r="AX256">
+        <v>7</v>
+      </c>
+      <c r="AY256">
+        <v>12</v>
+      </c>
+      <c r="AZ256">
+        <v>16</v>
+      </c>
+      <c r="BA256">
+        <v>5</v>
+      </c>
+      <c r="BB256">
+        <v>6</v>
+      </c>
+      <c r="BC256">
+        <v>11</v>
+      </c>
+      <c r="BD256">
+        <v>2</v>
+      </c>
+      <c r="BE256">
+        <v>6.25</v>
+      </c>
+      <c r="BF256">
+        <v>1.98</v>
+      </c>
+      <c r="BG256">
+        <v>1.49</v>
+      </c>
+      <c r="BH256">
+        <v>2.38</v>
+      </c>
+      <c r="BI256">
+        <v>1.82</v>
+      </c>
+      <c r="BJ256">
+        <v>1.84</v>
+      </c>
+      <c r="BK256">
+        <v>2.33</v>
+      </c>
+      <c r="BL256">
+        <v>1.5</v>
+      </c>
+      <c r="BM256">
+        <v>3.05</v>
+      </c>
+      <c r="BN256">
+        <v>1.3</v>
+      </c>
+      <c r="BO256">
+        <v>4.1</v>
+      </c>
+      <c r="BP256">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="257" spans="1:68">
+      <c r="A257" s="1">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>7856876</v>
+      </c>
+      <c r="C257" t="s">
+        <v>68</v>
+      </c>
+      <c r="D257" t="s">
+        <v>69</v>
+      </c>
+      <c r="E257" s="2">
+        <v>45747.60416666666</v>
+      </c>
+      <c r="F257">
+        <v>2</v>
+      </c>
+      <c r="G257" t="s">
+        <v>82</v>
+      </c>
+      <c r="H257" t="s">
+        <v>75</v>
+      </c>
+      <c r="I257">
+        <v>1</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257">
+        <v>1</v>
+      </c>
+      <c r="L257">
+        <v>1</v>
+      </c>
+      <c r="M257">
+        <v>0</v>
+      </c>
+      <c r="N257">
+        <v>1</v>
+      </c>
+      <c r="O257" t="s">
+        <v>201</v>
+      </c>
+      <c r="P257" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q257">
+        <v>3.8</v>
+      </c>
+      <c r="R257">
+        <v>1.97</v>
+      </c>
+      <c r="S257">
+        <v>2.95</v>
+      </c>
+      <c r="T257">
+        <v>1.52</v>
+      </c>
+      <c r="U257">
+        <v>2.4</v>
+      </c>
+      <c r="V257">
+        <v>3.4</v>
+      </c>
+      <c r="W257">
+        <v>1.26</v>
+      </c>
+      <c r="X257">
+        <v>8.5</v>
+      </c>
+      <c r="Y257">
+        <v>1.04</v>
+      </c>
+      <c r="Z257">
+        <v>2.69</v>
+      </c>
+      <c r="AA257">
+        <v>3.26</v>
+      </c>
+      <c r="AB257">
+        <v>2.55</v>
+      </c>
+      <c r="AC257">
+        <v>1.08</v>
+      </c>
+      <c r="AD257">
+        <v>6.2</v>
+      </c>
+      <c r="AE257">
+        <v>1.5</v>
+      </c>
+      <c r="AF257">
+        <v>2.4</v>
+      </c>
+      <c r="AG257">
+        <v>2.37</v>
+      </c>
+      <c r="AH257">
+        <v>1.48</v>
+      </c>
+      <c r="AI257">
+        <v>1.98</v>
+      </c>
+      <c r="AJ257">
+        <v>1.71</v>
+      </c>
+      <c r="AK257">
+        <v>1.58</v>
+      </c>
+      <c r="AL257">
+        <v>1.36</v>
+      </c>
+      <c r="AM257">
+        <v>1.33</v>
+      </c>
+      <c r="AN257">
+        <v>2</v>
+      </c>
+      <c r="AO257">
+        <v>1.6</v>
+      </c>
+      <c r="AP257">
+        <v>2.06</v>
+      </c>
+      <c r="AQ257">
+        <v>1.5</v>
+      </c>
+      <c r="AR257">
+        <v>1.65</v>
+      </c>
+      <c r="AS257">
+        <v>1.5</v>
+      </c>
+      <c r="AT257">
+        <v>3.15</v>
+      </c>
+      <c r="AU257">
+        <v>2</v>
+      </c>
+      <c r="AV257">
+        <v>7</v>
+      </c>
+      <c r="AW257">
+        <v>2</v>
+      </c>
+      <c r="AX257">
+        <v>14</v>
+      </c>
+      <c r="AY257">
+        <v>5</v>
+      </c>
+      <c r="AZ257">
+        <v>23</v>
+      </c>
+      <c r="BA257">
+        <v>4</v>
+      </c>
+      <c r="BB257">
+        <v>5</v>
+      </c>
+      <c r="BC257">
+        <v>9</v>
+      </c>
+      <c r="BD257">
+        <v>1.95</v>
+      </c>
+      <c r="BE257">
+        <v>6.4</v>
+      </c>
+      <c r="BF257">
+        <v>2.05</v>
+      </c>
+      <c r="BG257">
+        <v>1.3</v>
+      </c>
+      <c r="BH257">
+        <v>3.05</v>
+      </c>
+      <c r="BI257">
+        <v>1.54</v>
+      </c>
+      <c r="BJ257">
+        <v>2.25</v>
+      </c>
+      <c r="BK257">
+        <v>1.86</v>
+      </c>
+      <c r="BL257">
+        <v>1.8</v>
+      </c>
+      <c r="BM257">
+        <v>2.35</v>
+      </c>
+      <c r="BN257">
+        <v>1.5</v>
+      </c>
+      <c r="BO257">
+        <v>3.05</v>
+      </c>
+      <c r="BP257">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="341">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -733,6 +733,9 @@
     <t>['4', '29', '44', '81']</t>
   </si>
   <si>
+    <t>['10', '38']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -1031,6 +1034,9 @@
   </si>
   <si>
     <t>['12', '16']</t>
+  </si>
+  <si>
+    <t>['1']</t>
   </si>
 </sst>
 </file>
@@ -1392,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP257"/>
+  <dimension ref="A1:BP258"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1648,7 +1654,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -2678,7 +2684,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2884,7 +2890,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3168,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ9">
         <v>0.5</v>
@@ -3502,7 +3508,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3708,7 +3714,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3914,7 +3920,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -4120,7 +4126,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4326,7 +4332,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4532,7 +4538,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4613,7 +4619,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ16">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5150,7 +5156,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5356,7 +5362,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5768,7 +5774,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5974,7 +5980,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6464,7 +6470,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ25">
         <v>1.06</v>
@@ -7416,7 +7422,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7622,7 +7628,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7828,7 +7834,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7909,7 +7915,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ32">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.69</v>
@@ -8034,7 +8040,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8446,7 +8452,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8858,7 +8864,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9348,7 +9354,7 @@
         <v>1.67</v>
       </c>
       <c r="AP39">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ39">
         <v>1.38</v>
@@ -9476,7 +9482,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9682,7 +9688,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9888,7 +9894,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10793,7 +10799,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ46">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR46">
         <v>1.57</v>
@@ -10918,7 +10924,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11202,7 +11208,7 @@
         <v>2.33</v>
       </c>
       <c r="AP48">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ48">
         <v>1.12</v>
@@ -11330,7 +11336,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -12360,7 +12366,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12853,7 +12859,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ56">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>1.46</v>
@@ -12978,7 +12984,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13390,7 +13396,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13596,7 +13602,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -14008,7 +14014,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -15038,7 +15044,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15116,7 +15122,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ67">
         <v>0.8100000000000001</v>
@@ -15450,7 +15456,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15862,7 +15868,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -16068,7 +16074,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16686,7 +16692,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16892,7 +16898,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16973,7 +16979,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ76">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR76">
         <v>1.67</v>
@@ -17098,7 +17104,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17510,7 +17516,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17794,7 +17800,7 @@
         <v>0.25</v>
       </c>
       <c r="AP80">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ80">
         <v>1.06</v>
@@ -17922,7 +17928,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18334,7 +18340,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18952,7 +18958,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19776,7 +19782,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19982,7 +19988,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20188,7 +20194,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20394,7 +20400,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20475,7 +20481,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ93">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>1.25</v>
@@ -20806,7 +20812,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -21708,7 +21714,7 @@
         <v>1.67</v>
       </c>
       <c r="AP99">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ99">
         <v>1.5</v>
@@ -22042,7 +22048,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22660,7 +22666,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22741,7 +22747,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ104">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR104">
         <v>1.78</v>
@@ -23150,7 +23156,7 @@
         <v>0.67</v>
       </c>
       <c r="AP106">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ106">
         <v>0.6899999999999999</v>
@@ -23278,7 +23284,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23484,7 +23490,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23896,7 +23902,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24102,7 +24108,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24308,7 +24314,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24514,7 +24520,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24926,7 +24932,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -26162,7 +26168,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26368,7 +26374,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26449,7 +26455,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ122">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR122">
         <v>1.54</v>
@@ -27192,7 +27198,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -28428,7 +28434,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28634,7 +28640,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -29124,7 +29130,7 @@
         <v>1</v>
       </c>
       <c r="AP135">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ135">
         <v>1.38</v>
@@ -29458,7 +29464,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -30076,7 +30082,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30488,7 +30494,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30569,7 +30575,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ142">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR142">
         <v>1.14</v>
@@ -30694,7 +30700,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30900,7 +30906,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -31106,7 +31112,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31518,7 +31524,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31724,7 +31730,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31802,7 +31808,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ148">
         <v>1.44</v>
@@ -31930,7 +31936,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32136,7 +32142,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32754,7 +32760,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32960,7 +32966,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33578,7 +33584,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33659,7 +33665,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ157">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR157">
         <v>1.79</v>
@@ -35020,7 +35026,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35304,7 +35310,7 @@
         <v>1.3</v>
       </c>
       <c r="AP165">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ165">
         <v>0.88</v>
@@ -35432,7 +35438,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -36050,7 +36056,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36256,7 +36262,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36337,7 +36343,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ170">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR170">
         <v>1.38</v>
@@ -36462,7 +36468,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36668,7 +36674,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -37698,7 +37704,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -38316,7 +38322,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -39218,7 +39224,7 @@
         <v>0.55</v>
       </c>
       <c r="AP184">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ184">
         <v>0.9399999999999999</v>
@@ -39758,7 +39764,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -40045,7 +40051,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ188">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR188">
         <v>1.69</v>
@@ -40170,7 +40176,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40376,7 +40382,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40582,7 +40588,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -40994,7 +41000,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -41200,7 +41206,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -42720,7 +42726,7 @@
         <v>1.83</v>
       </c>
       <c r="AP201">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ201">
         <v>1.88</v>
@@ -42848,7 +42854,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -43054,7 +43060,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43466,7 +43472,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43672,7 +43678,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -43959,7 +43965,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ207">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR207">
         <v>2.04</v>
@@ -44290,7 +44296,7 @@
         <v>214</v>
       </c>
       <c r="P209" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q209">
         <v>4.75</v>
@@ -44496,7 +44502,7 @@
         <v>215</v>
       </c>
       <c r="P210" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q210">
         <v>2.8</v>
@@ -44986,7 +44992,7 @@
         <v>1.15</v>
       </c>
       <c r="AP212">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ212">
         <v>1.19</v>
@@ -45114,7 +45120,7 @@
         <v>86</v>
       </c>
       <c r="P213" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q213">
         <v>2.65</v>
@@ -45526,7 +45532,7 @@
         <v>86</v>
       </c>
       <c r="P215" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q215">
         <v>6.8</v>
@@ -45732,7 +45738,7 @@
         <v>218</v>
       </c>
       <c r="P216" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q216">
         <v>1.91</v>
@@ -46144,7 +46150,7 @@
         <v>220</v>
       </c>
       <c r="P218" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q218">
         <v>2.18</v>
@@ -46556,7 +46562,7 @@
         <v>221</v>
       </c>
       <c r="P220" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q220">
         <v>4.3</v>
@@ -47380,7 +47386,7 @@
         <v>223</v>
       </c>
       <c r="P224" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q224">
         <v>3.5</v>
@@ -47461,7 +47467,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ224">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR224">
         <v>1.55</v>
@@ -47586,7 +47592,7 @@
         <v>209</v>
       </c>
       <c r="P225" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q225">
         <v>3.6</v>
@@ -47998,7 +48004,7 @@
         <v>156</v>
       </c>
       <c r="P227" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q227">
         <v>3.75</v>
@@ -48204,7 +48210,7 @@
         <v>86</v>
       </c>
       <c r="P228" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q228">
         <v>2.24</v>
@@ -49440,7 +49446,7 @@
         <v>226</v>
       </c>
       <c r="P234" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -49646,7 +49652,7 @@
         <v>214</v>
       </c>
       <c r="P235" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q235">
         <v>3.65</v>
@@ -49930,10 +49936,10 @@
         <v>1.14</v>
       </c>
       <c r="AP236">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ236">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR236">
         <v>1.33</v>
@@ -50882,7 +50888,7 @@
         <v>86</v>
       </c>
       <c r="P241" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q241">
         <v>4</v>
@@ -51088,7 +51094,7 @@
         <v>86</v>
       </c>
       <c r="P242" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51166,7 +51172,7 @@
         <v>0.8</v>
       </c>
       <c r="AP242">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ242">
         <v>0.9399999999999999</v>
@@ -51706,7 +51712,7 @@
         <v>231</v>
       </c>
       <c r="P245" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q245">
         <v>2.3</v>
@@ -52324,7 +52330,7 @@
         <v>234</v>
       </c>
       <c r="P248" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q248">
         <v>2.6</v>
@@ -52530,7 +52536,7 @@
         <v>235</v>
       </c>
       <c r="P249" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q249">
         <v>2.05</v>
@@ -52942,7 +52948,7 @@
         <v>86</v>
       </c>
       <c r="P251" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q251">
         <v>2.8</v>
@@ -53148,7 +53154,7 @@
         <v>236</v>
       </c>
       <c r="P252" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q252">
         <v>2.8</v>
@@ -53354,7 +53360,7 @@
         <v>237</v>
       </c>
       <c r="P253" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q253">
         <v>2.95</v>
@@ -53766,7 +53772,7 @@
         <v>153</v>
       </c>
       <c r="P255" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q255">
         <v>4.1</v>
@@ -53972,7 +53978,7 @@
         <v>86</v>
       </c>
       <c r="P256" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q256">
         <v>3.65</v>
@@ -54335,6 +54341,212 @@
       </c>
       <c r="BP257">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:68">
+      <c r="A258" s="1">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>7856881</v>
+      </c>
+      <c r="C258" t="s">
+        <v>68</v>
+      </c>
+      <c r="D258" t="s">
+        <v>69</v>
+      </c>
+      <c r="E258" s="2">
+        <v>45751.60416666666</v>
+      </c>
+      <c r="F258">
+        <v>3</v>
+      </c>
+      <c r="G258" t="s">
+        <v>77</v>
+      </c>
+      <c r="H258" t="s">
+        <v>72</v>
+      </c>
+      <c r="I258">
+        <v>2</v>
+      </c>
+      <c r="J258">
+        <v>1</v>
+      </c>
+      <c r="K258">
+        <v>3</v>
+      </c>
+      <c r="L258">
+        <v>2</v>
+      </c>
+      <c r="M258">
+        <v>1</v>
+      </c>
+      <c r="N258">
+        <v>3</v>
+      </c>
+      <c r="O258" t="s">
+        <v>239</v>
+      </c>
+      <c r="P258" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q258">
+        <v>3.76</v>
+      </c>
+      <c r="R258">
+        <v>1.97</v>
+      </c>
+      <c r="S258">
+        <v>3.32</v>
+      </c>
+      <c r="T258">
+        <v>1.5</v>
+      </c>
+      <c r="U258">
+        <v>2.4</v>
+      </c>
+      <c r="V258">
+        <v>3.25</v>
+      </c>
+      <c r="W258">
+        <v>1.28</v>
+      </c>
+      <c r="X258">
+        <v>7.85</v>
+      </c>
+      <c r="Y258">
+        <v>1.05</v>
+      </c>
+      <c r="Z258">
+        <v>2.87</v>
+      </c>
+      <c r="AA258">
+        <v>3.03</v>
+      </c>
+      <c r="AB258">
+        <v>2.56</v>
+      </c>
+      <c r="AC258">
+        <v>1.09</v>
+      </c>
+      <c r="AD258">
+        <v>6.5</v>
+      </c>
+      <c r="AE258">
+        <v>1.43</v>
+      </c>
+      <c r="AF258">
+        <v>2.62</v>
+      </c>
+      <c r="AG258">
+        <v>2.37</v>
+      </c>
+      <c r="AH258">
+        <v>1.48</v>
+      </c>
+      <c r="AI258">
+        <v>1.93</v>
+      </c>
+      <c r="AJ258">
+        <v>1.73</v>
+      </c>
+      <c r="AK258">
+        <v>1.48</v>
+      </c>
+      <c r="AL258">
+        <v>1.33</v>
+      </c>
+      <c r="AM258">
+        <v>1.4</v>
+      </c>
+      <c r="AN258">
+        <v>1.56</v>
+      </c>
+      <c r="AO258">
+        <v>1.07</v>
+      </c>
+      <c r="AP258">
+        <v>1.65</v>
+      </c>
+      <c r="AQ258">
+        <v>1</v>
+      </c>
+      <c r="AR258">
+        <v>1.35</v>
+      </c>
+      <c r="AS258">
+        <v>1.41</v>
+      </c>
+      <c r="AT258">
+        <v>2.76</v>
+      </c>
+      <c r="AU258">
+        <v>-1</v>
+      </c>
+      <c r="AV258">
+        <v>-1</v>
+      </c>
+      <c r="AW258">
+        <v>-1</v>
+      </c>
+      <c r="AX258">
+        <v>-1</v>
+      </c>
+      <c r="AY258">
+        <v>-1</v>
+      </c>
+      <c r="AZ258">
+        <v>-1</v>
+      </c>
+      <c r="BA258">
+        <v>-1</v>
+      </c>
+      <c r="BB258">
+        <v>-1</v>
+      </c>
+      <c r="BC258">
+        <v>-1</v>
+      </c>
+      <c r="BD258">
+        <v>1.92</v>
+      </c>
+      <c r="BE258">
+        <v>6.4</v>
+      </c>
+      <c r="BF258">
+        <v>2.08</v>
+      </c>
+      <c r="BG258">
+        <v>1.4</v>
+      </c>
+      <c r="BH258">
+        <v>2.63</v>
+      </c>
+      <c r="BI258">
+        <v>1.7</v>
+      </c>
+      <c r="BJ258">
+        <v>2</v>
+      </c>
+      <c r="BK258">
+        <v>2.12</v>
+      </c>
+      <c r="BL258">
+        <v>1.61</v>
+      </c>
+      <c r="BM258">
+        <v>2.7</v>
+      </c>
+      <c r="BN258">
+        <v>1.38</v>
+      </c>
+      <c r="BO258">
+        <v>3.65</v>
+      </c>
+      <c r="BP258">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -54483,31 +54483,31 @@
         <v>2.76</v>
       </c>
       <c r="AU258">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV258">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AW258">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AX258">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AY258">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AZ258">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="BA258">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB258">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC258">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD258">
         <v>1.92</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="341">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -733,7 +733,13 @@
     <t>['4', '29', '44', '81']</t>
   </si>
   <si>
+    <t>['35']</t>
+  </si>
+  <si>
     <t>['10', '38']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
   </si>
   <si>
     <t>['19']</t>
@@ -836,9 +842,6 @@
   </si>
   <si>
     <t>['90+4']</t>
-  </si>
-  <si>
-    <t>['90+2']</t>
   </si>
   <si>
     <t>['68']</t>
@@ -947,9 +950,6 @@
   </si>
   <si>
     <t>['51', '69']</t>
-  </si>
-  <si>
-    <t>['35']</t>
   </si>
   <si>
     <t>['55', '75']</t>
@@ -1398,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP258"/>
+  <dimension ref="A1:BP261"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1654,7 +1654,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -2147,7 +2147,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ4">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ5">
         <v>1.06</v>
@@ -2556,10 +2556,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ6">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2890,7 +2890,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3383,7 +3383,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ10">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3714,7 +3714,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3920,7 +3920,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -4126,7 +4126,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4332,7 +4332,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4538,7 +4538,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4822,7 +4822,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ17">
         <v>0.8100000000000001</v>
@@ -5156,7 +5156,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5234,7 +5234,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ19">
         <v>1.12</v>
@@ -5362,7 +5362,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5774,7 +5774,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5855,7 +5855,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ22">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR22">
         <v>1.89</v>
@@ -5980,7 +5980,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6264,10 +6264,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ24">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR24">
         <v>1.56</v>
@@ -6676,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ26">
         <v>1.06</v>
@@ -7091,7 +7091,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ28">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -7422,7 +7422,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7503,7 +7503,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ30">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR30">
         <v>1.69</v>
@@ -7628,7 +7628,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7834,7 +7834,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -8040,7 +8040,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8118,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ33">
         <v>0.8100000000000001</v>
@@ -8327,7 +8327,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ34">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR34">
         <v>1.21</v>
@@ -8452,7 +8452,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8530,7 +8530,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ35">
         <v>1.12</v>
@@ -8864,7 +8864,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9357,7 +9357,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ39">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR39">
         <v>0.8100000000000001</v>
@@ -9482,7 +9482,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9688,7 +9688,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9894,7 +9894,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10384,10 +10384,10 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ44">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR44">
         <v>2.23</v>
@@ -10924,7 +10924,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11336,7 +11336,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -12035,7 +12035,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ52">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR52">
         <v>1.69</v>
@@ -12366,7 +12366,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12447,7 +12447,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ54">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR54">
         <v>1.5</v>
@@ -12650,7 +12650,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ55">
         <v>0.8100000000000001</v>
@@ -12856,7 +12856,7 @@
         <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ56">
         <v>1</v>
@@ -12984,7 +12984,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13065,7 +13065,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ57">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR57">
         <v>1.23</v>
@@ -13396,7 +13396,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13602,7 +13602,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13886,7 +13886,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ61">
         <v>1.19</v>
@@ -14014,7 +14014,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14507,7 +14507,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ64">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -15044,7 +15044,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15456,7 +15456,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15740,7 +15740,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ70">
         <v>1.06</v>
@@ -15868,7 +15868,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15949,7 +15949,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ71">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR71">
         <v>1.35</v>
@@ -16074,7 +16074,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16358,7 +16358,7 @@
         <v>0.6</v>
       </c>
       <c r="AP73">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ73">
         <v>1.38</v>
@@ -16692,7 +16692,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16770,7 +16770,7 @@
         <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -16898,7 +16898,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -17104,7 +17104,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17388,10 +17388,10 @@
         <v>0.75</v>
       </c>
       <c r="AP78">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ78">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR78">
         <v>1.54</v>
@@ -17516,7 +17516,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17928,7 +17928,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18009,7 +18009,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ81">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR81">
         <v>1.21</v>
@@ -18215,7 +18215,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ82">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR82">
         <v>1.61</v>
@@ -18340,7 +18340,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18958,7 +18958,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19448,7 +19448,7 @@
         <v>1.6</v>
       </c>
       <c r="AP88">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ88">
         <v>1</v>
@@ -19782,7 +19782,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19863,7 +19863,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ90">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR90">
         <v>1.38</v>
@@ -19988,7 +19988,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20069,7 +20069,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ91">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR91">
         <v>1.87</v>
@@ -20194,7 +20194,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20272,7 +20272,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ92">
         <v>1.44</v>
@@ -20400,7 +20400,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20812,7 +20812,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20890,7 +20890,7 @@
         <v>0.83</v>
       </c>
       <c r="AP95">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ95">
         <v>0.5</v>
@@ -21923,7 +21923,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ100">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR100">
         <v>1.91</v>
@@ -22048,7 +22048,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22666,7 +22666,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22950,7 +22950,7 @@
         <v>0.71</v>
       </c>
       <c r="AP105">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ105">
         <v>0.5</v>
@@ -23159,7 +23159,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ106">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR106">
         <v>1.16</v>
@@ -23284,7 +23284,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23490,7 +23490,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23568,7 +23568,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ108">
         <v>0.88</v>
@@ -23774,7 +23774,7 @@
         <v>1.29</v>
       </c>
       <c r="AP109">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ109">
         <v>1.06</v>
@@ -23902,7 +23902,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23983,7 +23983,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ110">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR110">
         <v>1.9</v>
@@ -24108,7 +24108,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24314,7 +24314,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24520,7 +24520,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24932,7 +24932,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -25631,7 +25631,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ118">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR118">
         <v>1.37</v>
@@ -26040,10 +26040,10 @@
         <v>0.63</v>
       </c>
       <c r="AP120">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ120">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR120">
         <v>1.36</v>
@@ -26168,7 +26168,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26374,7 +26374,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -27198,7 +27198,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27688,7 +27688,7 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ128">
         <v>1.5</v>
@@ -28434,7 +28434,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28515,7 +28515,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ132">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR132">
         <v>1.25</v>
@@ -28640,7 +28640,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28924,7 +28924,7 @@
         <v>1.25</v>
       </c>
       <c r="AP134">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ134">
         <v>0.88</v>
@@ -29339,7 +29339,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ136">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR136">
         <v>1.72</v>
@@ -29464,7 +29464,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29542,7 +29542,7 @@
         <v>1.13</v>
       </c>
       <c r="AP137">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ137">
         <v>1.44</v>
@@ -30082,7 +30082,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30369,7 +30369,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ141">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR141">
         <v>1.41</v>
@@ -30494,7 +30494,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30700,7 +30700,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30906,7 +30906,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -31112,7 +31112,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31190,7 +31190,7 @@
         <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ145">
         <v>1.88</v>
@@ -31524,7 +31524,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31730,7 +31730,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31936,7 +31936,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32014,7 +32014,7 @@
         <v>1.11</v>
       </c>
       <c r="AP149">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ149">
         <v>0.88</v>
@@ -32142,7 +32142,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32426,10 +32426,10 @@
         <v>0.67</v>
       </c>
       <c r="AP151">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ151">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR151">
         <v>2.01</v>
@@ -32760,7 +32760,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32966,7 +32966,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33253,7 +33253,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ155">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR155">
         <v>1.16</v>
@@ -33456,7 +33456,7 @@
         <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ156">
         <v>1.19</v>
@@ -33584,7 +33584,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -34695,7 +34695,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ162">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR162">
         <v>1.45</v>
@@ -35026,7 +35026,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35438,7 +35438,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35928,10 +35928,10 @@
         <v>0.6</v>
       </c>
       <c r="AP168">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ168">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR168">
         <v>1.63</v>
@@ -36056,7 +36056,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36262,7 +36262,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36468,7 +36468,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36546,7 +36546,7 @@
         <v>0.7</v>
       </c>
       <c r="AP171">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ171">
         <v>1.06</v>
@@ -36674,7 +36674,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>311</v>
+        <v>239</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36958,7 +36958,7 @@
         <v>1.3</v>
       </c>
       <c r="AP173">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ173">
         <v>1</v>
@@ -37704,7 +37704,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>311</v>
+        <v>239</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -37785,7 +37785,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ177">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR177">
         <v>1.54</v>
@@ -38197,7 +38197,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ179">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR179">
         <v>1.24</v>
@@ -39018,7 +39018,7 @@
         <v>1.73</v>
       </c>
       <c r="AP183">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ183">
         <v>1.88</v>
@@ -39227,7 +39227,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ184">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR184">
         <v>1.32</v>
@@ -40176,7 +40176,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40254,7 +40254,7 @@
         <v>0.45</v>
       </c>
       <c r="AP189">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ189">
         <v>0.5</v>
@@ -40382,7 +40382,7 @@
         <v>203</v>
       </c>
       <c r="P190" t="s">
-        <v>311</v>
+        <v>239</v>
       </c>
       <c r="Q190">
         <v>3</v>
@@ -40669,7 +40669,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ191">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR191">
         <v>1.78</v>
@@ -40872,7 +40872,7 @@
         <v>1.64</v>
       </c>
       <c r="AP192">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ192">
         <v>1.5</v>
@@ -41287,7 +41287,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ194">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR194">
         <v>1.47</v>
@@ -42111,7 +42111,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ198">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR198">
         <v>1.82</v>
@@ -43344,7 +43344,7 @@
         <v>1</v>
       </c>
       <c r="AP204">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ204">
         <v>1.06</v>
@@ -43472,7 +43472,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43759,7 +43759,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ206">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR206">
         <v>1.62</v>
@@ -43962,7 +43962,7 @@
         <v>1.08</v>
       </c>
       <c r="AP207">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ207">
         <v>1</v>
@@ -44374,7 +44374,7 @@
         <v>1.58</v>
       </c>
       <c r="AP209">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ209">
         <v>1.5</v>
@@ -46025,7 +46025,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ217">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR217">
         <v>1.78</v>
@@ -46434,10 +46434,10 @@
         <v>1.38</v>
       </c>
       <c r="AP219">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ219">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR219">
         <v>1.36</v>
@@ -47055,7 +47055,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ222">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR222">
         <v>1.35</v>
@@ -47258,7 +47258,7 @@
         <v>1.46</v>
       </c>
       <c r="AP223">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ223">
         <v>1.38</v>
@@ -47464,7 +47464,7 @@
         <v>1</v>
       </c>
       <c r="AP224">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ224">
         <v>1</v>
@@ -48004,7 +48004,7 @@
         <v>156</v>
       </c>
       <c r="P227" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q227">
         <v>3.75</v>
@@ -48291,7 +48291,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ228">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR228">
         <v>1.64</v>
@@ -49524,10 +49524,10 @@
         <v>0.5</v>
       </c>
       <c r="AP234">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ234">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR234">
         <v>1.36</v>
@@ -49733,7 +49733,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ235">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR235">
         <v>1.69</v>
@@ -50554,7 +50554,7 @@
         <v>1.43</v>
       </c>
       <c r="AP239">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ239">
         <v>1.44</v>
@@ -50966,7 +50966,7 @@
         <v>1.36</v>
       </c>
       <c r="AP241">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ241">
         <v>1.38</v>
@@ -51175,7 +51175,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ242">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AR242">
         <v>1.36</v>
@@ -51381,7 +51381,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ243">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR243">
         <v>1.83</v>
@@ -51587,7 +51587,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ244">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AR244">
         <v>1.69</v>
@@ -51712,7 +51712,7 @@
         <v>231</v>
       </c>
       <c r="P245" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q245">
         <v>2.3</v>
@@ -52202,7 +52202,7 @@
         <v>1.07</v>
       </c>
       <c r="AP247">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ247">
         <v>1.12</v>
@@ -52408,7 +52408,7 @@
         <v>1.07</v>
       </c>
       <c r="AP248">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ248">
         <v>1.06</v>
@@ -54348,7 +54348,7 @@
         <v>257</v>
       </c>
       <c r="B258">
-        <v>7856881</v>
+        <v>7856884</v>
       </c>
       <c r="C258" t="s">
         <v>68</v>
@@ -54357,49 +54357,49 @@
         <v>69</v>
       </c>
       <c r="E258" s="2">
-        <v>45751.60416666666</v>
+        <v>45751.47916666666</v>
       </c>
       <c r="F258">
         <v>3</v>
       </c>
       <c r="G258" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H258" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I258">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K258">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L258">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N258">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O258" t="s">
         <v>239</v>
       </c>
       <c r="P258" t="s">
-        <v>340</v>
+        <v>86</v>
       </c>
       <c r="Q258">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="R258">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="S258">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="T258">
         <v>1.5</v>
@@ -54408,25 +54408,25 @@
         <v>2.4</v>
       </c>
       <c r="V258">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="W258">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X258">
-        <v>7.85</v>
+        <v>9.6</v>
       </c>
       <c r="Y258">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Z258">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="AA258">
-        <v>3.03</v>
+        <v>3.09</v>
       </c>
       <c r="AB258">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="AC258">
         <v>1.09</v>
@@ -54435,16 +54435,16 @@
         <v>6.5</v>
       </c>
       <c r="AE258">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AF258">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AG258">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AH258">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI258">
         <v>1.93</v>
@@ -54453,100 +54453,718 @@
         <v>1.73</v>
       </c>
       <c r="AK258">
+        <v>1.33</v>
+      </c>
+      <c r="AL258">
+        <v>1.3</v>
+      </c>
+      <c r="AM258">
+        <v>1.57</v>
+      </c>
+      <c r="AN258">
+        <v>1.07</v>
+      </c>
+      <c r="AO258">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP258">
+        <v>1.19</v>
+      </c>
+      <c r="AQ258">
+        <v>0.65</v>
+      </c>
+      <c r="AR258">
         <v>1.48</v>
       </c>
-      <c r="AL258">
-        <v>1.33</v>
-      </c>
-      <c r="AM258">
-        <v>1.4</v>
-      </c>
-      <c r="AN258">
-        <v>1.56</v>
-      </c>
-      <c r="AO258">
-        <v>1.07</v>
-      </c>
-      <c r="AP258">
-        <v>1.65</v>
-      </c>
-      <c r="AQ258">
-        <v>1</v>
-      </c>
-      <c r="AR258">
+      <c r="AS258">
         <v>1.35</v>
       </c>
-      <c r="AS258">
-        <v>1.41</v>
-      </c>
       <c r="AT258">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="AU258">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV258">
+        <v>3</v>
+      </c>
+      <c r="AW258">
         <v>9</v>
       </c>
-      <c r="AW258">
-        <v>2</v>
-      </c>
       <c r="AX258">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY258">
+        <v>16</v>
+      </c>
+      <c r="AZ258">
+        <v>11</v>
+      </c>
+      <c r="BA258">
+        <v>8</v>
+      </c>
+      <c r="BB258">
+        <v>1</v>
+      </c>
+      <c r="BC258">
         <v>9</v>
       </c>
-      <c r="AZ258">
-        <v>18</v>
-      </c>
-      <c r="BA258">
-        <v>2</v>
-      </c>
-      <c r="BB258">
-        <v>6</v>
-      </c>
-      <c r="BC258">
-        <v>8</v>
-      </c>
       <c r="BD258">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="BE258">
         <v>6.4</v>
       </c>
       <c r="BF258">
+        <v>2.23</v>
+      </c>
+      <c r="BG258">
+        <v>1.47</v>
+      </c>
+      <c r="BH258">
+        <v>2.4</v>
+      </c>
+      <c r="BI258">
+        <v>1.8</v>
+      </c>
+      <c r="BJ258">
+        <v>1.86</v>
+      </c>
+      <c r="BK258">
+        <v>2.28</v>
+      </c>
+      <c r="BL258">
+        <v>1.53</v>
+      </c>
+      <c r="BM258">
+        <v>2.95</v>
+      </c>
+      <c r="BN258">
+        <v>1.33</v>
+      </c>
+      <c r="BO258">
+        <v>3.95</v>
+      </c>
+      <c r="BP258">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="259" spans="1:68">
+      <c r="A259" s="1">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>7856881</v>
+      </c>
+      <c r="C259" t="s">
+        <v>68</v>
+      </c>
+      <c r="D259" t="s">
+        <v>69</v>
+      </c>
+      <c r="E259" s="2">
+        <v>45751.60416666666</v>
+      </c>
+      <c r="F259">
+        <v>3</v>
+      </c>
+      <c r="G259" t="s">
+        <v>77</v>
+      </c>
+      <c r="H259" t="s">
+        <v>72</v>
+      </c>
+      <c r="I259">
+        <v>2</v>
+      </c>
+      <c r="J259">
+        <v>1</v>
+      </c>
+      <c r="K259">
+        <v>3</v>
+      </c>
+      <c r="L259">
+        <v>2</v>
+      </c>
+      <c r="M259">
+        <v>1</v>
+      </c>
+      <c r="N259">
+        <v>3</v>
+      </c>
+      <c r="O259" t="s">
+        <v>240</v>
+      </c>
+      <c r="P259" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q259">
+        <v>3.76</v>
+      </c>
+      <c r="R259">
+        <v>1.97</v>
+      </c>
+      <c r="S259">
+        <v>3.32</v>
+      </c>
+      <c r="T259">
+        <v>1.5</v>
+      </c>
+      <c r="U259">
+        <v>2.4</v>
+      </c>
+      <c r="V259">
+        <v>3.25</v>
+      </c>
+      <c r="W259">
+        <v>1.28</v>
+      </c>
+      <c r="X259">
+        <v>7.85</v>
+      </c>
+      <c r="Y259">
+        <v>1.05</v>
+      </c>
+      <c r="Z259">
+        <v>2.87</v>
+      </c>
+      <c r="AA259">
+        <v>3.03</v>
+      </c>
+      <c r="AB259">
+        <v>2.56</v>
+      </c>
+      <c r="AC259">
+        <v>1.09</v>
+      </c>
+      <c r="AD259">
+        <v>6.5</v>
+      </c>
+      <c r="AE259">
+        <v>1.43</v>
+      </c>
+      <c r="AF259">
+        <v>2.62</v>
+      </c>
+      <c r="AG259">
+        <v>2.37</v>
+      </c>
+      <c r="AH259">
+        <v>1.48</v>
+      </c>
+      <c r="AI259">
+        <v>1.93</v>
+      </c>
+      <c r="AJ259">
+        <v>1.73</v>
+      </c>
+      <c r="AK259">
+        <v>1.48</v>
+      </c>
+      <c r="AL259">
+        <v>1.33</v>
+      </c>
+      <c r="AM259">
+        <v>1.4</v>
+      </c>
+      <c r="AN259">
+        <v>1.56</v>
+      </c>
+      <c r="AO259">
+        <v>1.07</v>
+      </c>
+      <c r="AP259">
+        <v>1.65</v>
+      </c>
+      <c r="AQ259">
+        <v>1</v>
+      </c>
+      <c r="AR259">
+        <v>1.35</v>
+      </c>
+      <c r="AS259">
+        <v>1.41</v>
+      </c>
+      <c r="AT259">
+        <v>2.76</v>
+      </c>
+      <c r="AU259">
+        <v>6</v>
+      </c>
+      <c r="AV259">
+        <v>9</v>
+      </c>
+      <c r="AW259">
+        <v>2</v>
+      </c>
+      <c r="AX259">
+        <v>6</v>
+      </c>
+      <c r="AY259">
+        <v>9</v>
+      </c>
+      <c r="AZ259">
+        <v>18</v>
+      </c>
+      <c r="BA259">
+        <v>2</v>
+      </c>
+      <c r="BB259">
+        <v>6</v>
+      </c>
+      <c r="BC259">
+        <v>8</v>
+      </c>
+      <c r="BD259">
+        <v>1.92</v>
+      </c>
+      <c r="BE259">
+        <v>6.4</v>
+      </c>
+      <c r="BF259">
         <v>2.08</v>
       </c>
-      <c r="BG258">
+      <c r="BG259">
         <v>1.4</v>
       </c>
-      <c r="BH258">
+      <c r="BH259">
         <v>2.63</v>
       </c>
-      <c r="BI258">
+      <c r="BI259">
         <v>1.7</v>
       </c>
-      <c r="BJ258">
-        <v>2</v>
-      </c>
-      <c r="BK258">
+      <c r="BJ259">
+        <v>2</v>
+      </c>
+      <c r="BK259">
         <v>2.12</v>
       </c>
-      <c r="BL258">
+      <c r="BL259">
         <v>1.61</v>
       </c>
-      <c r="BM258">
+      <c r="BM259">
         <v>2.7</v>
       </c>
-      <c r="BN258">
+      <c r="BN259">
         <v>1.38</v>
       </c>
-      <c r="BO258">
+      <c r="BO259">
         <v>3.65</v>
       </c>
-      <c r="BP258">
+      <c r="BP259">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="260" spans="1:68">
+      <c r="A260" s="1">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>7856883</v>
+      </c>
+      <c r="C260" t="s">
+        <v>68</v>
+      </c>
+      <c r="D260" t="s">
+        <v>69</v>
+      </c>
+      <c r="E260" s="2">
+        <v>45752.44791666666</v>
+      </c>
+      <c r="F260">
+        <v>3</v>
+      </c>
+      <c r="G260" t="s">
+        <v>73</v>
+      </c>
+      <c r="H260" t="s">
+        <v>76</v>
+      </c>
+      <c r="I260">
+        <v>0</v>
+      </c>
+      <c r="J260">
+        <v>0</v>
+      </c>
+      <c r="K260">
+        <v>0</v>
+      </c>
+      <c r="L260">
+        <v>1</v>
+      </c>
+      <c r="M260">
+        <v>0</v>
+      </c>
+      <c r="N260">
+        <v>1</v>
+      </c>
+      <c r="O260" t="s">
+        <v>241</v>
+      </c>
+      <c r="P260" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q260">
+        <v>3.6</v>
+      </c>
+      <c r="R260">
+        <v>2</v>
+      </c>
+      <c r="S260">
+        <v>3.25</v>
+      </c>
+      <c r="T260">
+        <v>1.5</v>
+      </c>
+      <c r="U260">
+        <v>2.5</v>
+      </c>
+      <c r="V260">
+        <v>3.5</v>
+      </c>
+      <c r="W260">
+        <v>1.29</v>
+      </c>
+      <c r="X260">
+        <v>10</v>
+      </c>
+      <c r="Y260">
+        <v>1.06</v>
+      </c>
+      <c r="Z260">
+        <v>2.1</v>
+      </c>
+      <c r="AA260">
+        <v>3.2</v>
+      </c>
+      <c r="AB260">
+        <v>3.3</v>
+      </c>
+      <c r="AC260">
+        <v>1.07</v>
+      </c>
+      <c r="AD260">
+        <v>7.5</v>
+      </c>
+      <c r="AE260">
+        <v>1.42</v>
+      </c>
+      <c r="AF260">
+        <v>2.75</v>
+      </c>
+      <c r="AG260">
+        <v>2.1</v>
+      </c>
+      <c r="AH260">
+        <v>1.6</v>
+      </c>
+      <c r="AI260">
+        <v>1.91</v>
+      </c>
+      <c r="AJ260">
+        <v>1.8</v>
+      </c>
+      <c r="AK260">
+        <v>1.55</v>
+      </c>
+      <c r="AL260">
+        <v>1.33</v>
+      </c>
+      <c r="AM260">
+        <v>1.38</v>
+      </c>
+      <c r="AN260">
+        <v>1.13</v>
+      </c>
+      <c r="AO260">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AP260">
+        <v>1.24</v>
+      </c>
+      <c r="AQ260">
+        <v>0.88</v>
+      </c>
+      <c r="AR260">
+        <v>1.55</v>
+      </c>
+      <c r="AS260">
+        <v>1.27</v>
+      </c>
+      <c r="AT260">
+        <v>2.82</v>
+      </c>
+      <c r="AU260">
+        <v>5</v>
+      </c>
+      <c r="AV260">
+        <v>2</v>
+      </c>
+      <c r="AW260">
+        <v>5</v>
+      </c>
+      <c r="AX260">
+        <v>6</v>
+      </c>
+      <c r="AY260">
+        <v>12</v>
+      </c>
+      <c r="AZ260">
+        <v>8</v>
+      </c>
+      <c r="BA260">
+        <v>7</v>
+      </c>
+      <c r="BB260">
+        <v>2</v>
+      </c>
+      <c r="BC260">
+        <v>9</v>
+      </c>
+      <c r="BD260">
+        <v>2.28</v>
+      </c>
+      <c r="BE260">
+        <v>6.3</v>
+      </c>
+      <c r="BF260">
+        <v>1.97</v>
+      </c>
+      <c r="BG260">
+        <v>1.27</v>
+      </c>
+      <c r="BH260">
+        <v>3.14</v>
+      </c>
+      <c r="BI260">
+        <v>1.53</v>
+      </c>
+      <c r="BJ260">
+        <v>2.28</v>
+      </c>
+      <c r="BK260">
+        <v>1.93</v>
+      </c>
+      <c r="BL260">
+        <v>1.78</v>
+      </c>
+      <c r="BM260">
+        <v>2.51</v>
+      </c>
+      <c r="BN260">
+        <v>1.44</v>
+      </c>
+      <c r="BO260">
+        <v>3.34</v>
+      </c>
+      <c r="BP260">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="261" spans="1:68">
+      <c r="A261" s="1">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>7856877</v>
+      </c>
+      <c r="C261" t="s">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>69</v>
+      </c>
+      <c r="E261" s="2">
+        <v>45752.63541666666</v>
+      </c>
+      <c r="F261">
+        <v>3</v>
+      </c>
+      <c r="G261" t="s">
+        <v>74</v>
+      </c>
+      <c r="H261" t="s">
+        <v>82</v>
+      </c>
+      <c r="I261">
+        <v>0</v>
+      </c>
+      <c r="J261">
+        <v>0</v>
+      </c>
+      <c r="K261">
+        <v>0</v>
+      </c>
+      <c r="L261">
+        <v>1</v>
+      </c>
+      <c r="M261">
+        <v>0</v>
+      </c>
+      <c r="N261">
+        <v>1</v>
+      </c>
+      <c r="O261" t="s">
+        <v>223</v>
+      </c>
+      <c r="P261" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q261">
+        <v>2.4</v>
+      </c>
+      <c r="R261">
+        <v>2</v>
+      </c>
+      <c r="S261">
+        <v>6</v>
+      </c>
+      <c r="T261">
+        <v>1.53</v>
+      </c>
+      <c r="U261">
+        <v>2.38</v>
+      </c>
+      <c r="V261">
+        <v>3.5</v>
+      </c>
+      <c r="W261">
+        <v>1.29</v>
+      </c>
+      <c r="X261">
+        <v>11</v>
+      </c>
+      <c r="Y261">
+        <v>1.05</v>
+      </c>
+      <c r="Z261">
+        <v>1.74</v>
+      </c>
+      <c r="AA261">
+        <v>3.3</v>
+      </c>
+      <c r="AB261">
+        <v>4.7</v>
+      </c>
+      <c r="AC261">
+        <v>1.07</v>
+      </c>
+      <c r="AD261">
+        <v>7.5</v>
+      </c>
+      <c r="AE261">
+        <v>1.42</v>
+      </c>
+      <c r="AF261">
+        <v>2.75</v>
+      </c>
+      <c r="AG261">
+        <v>2.05</v>
+      </c>
+      <c r="AH261">
+        <v>1.61</v>
+      </c>
+      <c r="AI261">
+        <v>2.25</v>
+      </c>
+      <c r="AJ261">
+        <v>1.57</v>
+      </c>
+      <c r="AK261">
+        <v>1.16</v>
+      </c>
+      <c r="AL261">
+        <v>1.29</v>
+      </c>
+      <c r="AM261">
+        <v>2.05</v>
+      </c>
+      <c r="AN261">
+        <v>1.88</v>
+      </c>
+      <c r="AO261">
+        <v>1.38</v>
+      </c>
+      <c r="AP261">
+        <v>1.94</v>
+      </c>
+      <c r="AQ261">
+        <v>1.29</v>
+      </c>
+      <c r="AR261">
+        <v>2.07</v>
+      </c>
+      <c r="AS261">
+        <v>1.5</v>
+      </c>
+      <c r="AT261">
+        <v>3.57</v>
+      </c>
+      <c r="AU261">
+        <v>5</v>
+      </c>
+      <c r="AV261">
+        <v>3</v>
+      </c>
+      <c r="AW261">
+        <v>9</v>
+      </c>
+      <c r="AX261">
+        <v>0</v>
+      </c>
+      <c r="AY261">
+        <v>19</v>
+      </c>
+      <c r="AZ261">
+        <v>3</v>
+      </c>
+      <c r="BA261">
+        <v>3</v>
+      </c>
+      <c r="BB261">
+        <v>0</v>
+      </c>
+      <c r="BC261">
+        <v>3</v>
+      </c>
+      <c r="BD261">
+        <v>1.48</v>
+      </c>
+      <c r="BE261">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF261">
+        <v>3.18</v>
+      </c>
+      <c r="BG261">
+        <v>1.26</v>
+      </c>
+      <c r="BH261">
+        <v>3.22</v>
+      </c>
+      <c r="BI261">
+        <v>1.51</v>
+      </c>
+      <c r="BJ261">
+        <v>2.32</v>
+      </c>
+      <c r="BK261">
+        <v>1.89</v>
+      </c>
+      <c r="BL261">
+        <v>1.81</v>
+      </c>
+      <c r="BM261">
+        <v>2.45</v>
+      </c>
+      <c r="BN261">
+        <v>1.46</v>
+      </c>
+      <c r="BO261">
+        <v>3.28</v>
+      </c>
+      <c r="BP261">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="341">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1398,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP261"/>
+  <dimension ref="A1:BP262"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2765,7 +2765,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ7">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3998,7 +3998,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ13">
         <v>1.5</v>
@@ -5649,7 +5649,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ21">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -7912,7 +7912,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -9563,7 +9563,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ40">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -10590,10 +10590,10 @@
         <v>0.67</v>
       </c>
       <c r="AP45">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ45">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR45">
         <v>1.51</v>
@@ -14301,7 +14301,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ63">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -15946,7 +15946,7 @@
         <v>1.8</v>
       </c>
       <c r="AP71">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ71">
         <v>1.29</v>
@@ -16361,7 +16361,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ73">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR73">
         <v>1.51</v>
@@ -18624,7 +18624,7 @@
         <v>1.8</v>
       </c>
       <c r="AP84">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ84">
         <v>1.12</v>
@@ -19657,7 +19657,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ89">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR89">
         <v>1.6</v>
@@ -22538,7 +22538,7 @@
         <v>0.6</v>
       </c>
       <c r="AP103">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ103">
         <v>0.8100000000000001</v>
@@ -23365,7 +23365,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ107">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR107">
         <v>1.21</v>
@@ -25834,7 +25834,7 @@
         <v>0.17</v>
       </c>
       <c r="AP119">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ119">
         <v>1.06</v>
@@ -26864,7 +26864,7 @@
         <v>0.86</v>
       </c>
       <c r="AP124">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ124">
         <v>1.19</v>
@@ -29133,7 +29133,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ135">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR135">
         <v>1.36</v>
@@ -29954,7 +29954,7 @@
         <v>1.5</v>
       </c>
       <c r="AP139">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ139">
         <v>1</v>
@@ -31605,7 +31605,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ147">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR147">
         <v>1.41</v>
@@ -34486,7 +34486,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP161">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ161">
         <v>0.5</v>
@@ -37373,7 +37373,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ175">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR175">
         <v>1.78</v>
@@ -37782,7 +37782,7 @@
         <v>0.5</v>
       </c>
       <c r="AP177">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ177">
         <v>0.65</v>
@@ -38606,7 +38606,7 @@
         <v>1.45</v>
       </c>
       <c r="AP181">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ181">
         <v>1.44</v>
@@ -39845,7 +39845,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ187">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR187">
         <v>1.38</v>
@@ -41490,7 +41490,7 @@
         <v>1.08</v>
       </c>
       <c r="AP195">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ195">
         <v>0.88</v>
@@ -42935,7 +42935,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ202">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR202">
         <v>1.75</v>
@@ -46022,7 +46022,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP217">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ217">
         <v>0.88</v>
@@ -47261,7 +47261,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ223">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR223">
         <v>2.11</v>
@@ -48906,7 +48906,7 @@
         <v>1.86</v>
       </c>
       <c r="AP231">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ231">
         <v>1.88</v>
@@ -50969,7 +50969,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ241">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR241">
         <v>1.56</v>
@@ -51793,7 +51793,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ245">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR245">
         <v>1.92</v>
@@ -53438,7 +53438,7 @@
         <v>1.33</v>
       </c>
       <c r="AP253">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ253">
         <v>1.44</v>
@@ -55165,6 +55165,212 @@
       </c>
       <c r="BP261">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="262" spans="1:68">
+      <c r="A262" s="1">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>7856879</v>
+      </c>
+      <c r="C262" t="s">
+        <v>68</v>
+      </c>
+      <c r="D262" t="s">
+        <v>69</v>
+      </c>
+      <c r="E262" s="2">
+        <v>45753.625</v>
+      </c>
+      <c r="F262">
+        <v>3</v>
+      </c>
+      <c r="G262" t="s">
+        <v>81</v>
+      </c>
+      <c r="H262" t="s">
+        <v>83</v>
+      </c>
+      <c r="I262">
+        <v>1</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>1</v>
+      </c>
+      <c r="L262">
+        <v>1</v>
+      </c>
+      <c r="M262">
+        <v>0</v>
+      </c>
+      <c r="N262">
+        <v>1</v>
+      </c>
+      <c r="O262" t="s">
+        <v>100</v>
+      </c>
+      <c r="P262" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q262">
+        <v>2.87</v>
+      </c>
+      <c r="R262">
+        <v>2.05</v>
+      </c>
+      <c r="S262">
+        <v>3.86</v>
+      </c>
+      <c r="T262">
+        <v>1.4</v>
+      </c>
+      <c r="U262">
+        <v>2.73</v>
+      </c>
+      <c r="V262">
+        <v>2.99</v>
+      </c>
+      <c r="W262">
+        <v>1.34</v>
+      </c>
+      <c r="X262">
+        <v>7.9</v>
+      </c>
+      <c r="Y262">
+        <v>1.02</v>
+      </c>
+      <c r="Z262">
+        <v>2.22</v>
+      </c>
+      <c r="AA262">
+        <v>3.15</v>
+      </c>
+      <c r="AB262">
+        <v>3.3</v>
+      </c>
+      <c r="AC262">
+        <v>1.05</v>
+      </c>
+      <c r="AD262">
+        <v>8</v>
+      </c>
+      <c r="AE262">
+        <v>1.29</v>
+      </c>
+      <c r="AF262">
+        <v>3.3</v>
+      </c>
+      <c r="AG262">
+        <v>2</v>
+      </c>
+      <c r="AH262">
+        <v>1.75</v>
+      </c>
+      <c r="AI262">
+        <v>1.8</v>
+      </c>
+      <c r="AJ262">
+        <v>2</v>
+      </c>
+      <c r="AK262">
+        <v>1.27</v>
+      </c>
+      <c r="AL262">
+        <v>1.32</v>
+      </c>
+      <c r="AM262">
+        <v>1.6</v>
+      </c>
+      <c r="AN262">
+        <v>1.88</v>
+      </c>
+      <c r="AO262">
+        <v>1.38</v>
+      </c>
+      <c r="AP262">
+        <v>1.94</v>
+      </c>
+      <c r="AQ262">
+        <v>1.29</v>
+      </c>
+      <c r="AR262">
+        <v>1.71</v>
+      </c>
+      <c r="AS262">
+        <v>1.24</v>
+      </c>
+      <c r="AT262">
+        <v>2.95</v>
+      </c>
+      <c r="AU262">
+        <v>5</v>
+      </c>
+      <c r="AV262">
+        <v>6</v>
+      </c>
+      <c r="AW262">
+        <v>10</v>
+      </c>
+      <c r="AX262">
+        <v>6</v>
+      </c>
+      <c r="AY262">
+        <v>19</v>
+      </c>
+      <c r="AZ262">
+        <v>12</v>
+      </c>
+      <c r="BA262">
+        <v>8</v>
+      </c>
+      <c r="BB262">
+        <v>3</v>
+      </c>
+      <c r="BC262">
+        <v>11</v>
+      </c>
+      <c r="BD262">
+        <v>1.63</v>
+      </c>
+      <c r="BE262">
+        <v>6.4</v>
+      </c>
+      <c r="BF262">
+        <v>2.55</v>
+      </c>
+      <c r="BG262">
+        <v>1.46</v>
+      </c>
+      <c r="BH262">
+        <v>2.45</v>
+      </c>
+      <c r="BI262">
+        <v>1.77</v>
+      </c>
+      <c r="BJ262">
+        <v>1.89</v>
+      </c>
+      <c r="BK262">
+        <v>2.23</v>
+      </c>
+      <c r="BL262">
+        <v>1.56</v>
+      </c>
+      <c r="BM262">
+        <v>2.9</v>
+      </c>
+      <c r="BN262">
+        <v>1.34</v>
+      </c>
+      <c r="BO262">
+        <v>3.8</v>
+      </c>
+      <c r="BP262">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="344">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -742,6 +742,12 @@
     <t>['90+2']</t>
   </si>
   <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['22', '44']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -1037,6 +1043,9 @@
   </si>
   <si>
     <t>['1']</t>
+  </si>
+  <si>
+    <t>['10', '45+1']</t>
   </si>
 </sst>
 </file>
@@ -1398,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP262"/>
+  <dimension ref="A1:BP265"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1654,7 +1663,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1732,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ2">
         <v>0.88</v>
@@ -1938,10 +1947,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ3">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2684,7 +2693,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2762,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ7">
         <v>1.29</v>
@@ -2890,7 +2899,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3177,7 +3186,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ9">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3508,7 +3517,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3714,7 +3723,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3920,7 +3929,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -4126,7 +4135,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4332,7 +4341,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4538,7 +4547,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -5028,7 +5037,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ18">
         <v>0.88</v>
@@ -5156,7 +5165,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5362,7 +5371,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5443,7 +5452,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ20">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR20">
         <v>1.45</v>
@@ -5774,7 +5783,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5852,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ22">
         <v>0.88</v>
@@ -5980,7 +5989,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6058,10 +6067,10 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ23">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR23">
         <v>2</v>
@@ -6885,7 +6894,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ27">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR27">
         <v>1</v>
@@ -7088,7 +7097,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ28">
         <v>0.65</v>
@@ -7422,7 +7431,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7500,7 +7509,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ30">
         <v>1.29</v>
@@ -7628,7 +7637,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7834,7 +7843,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -8040,7 +8049,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8324,7 +8333,7 @@
         <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ34">
         <v>0.88</v>
@@ -8452,7 +8461,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8864,7 +8873,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -8945,7 +8954,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ37">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR37">
         <v>1.39</v>
@@ -9148,7 +9157,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ38">
         <v>0.88</v>
@@ -9482,7 +9491,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9688,7 +9697,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9894,7 +9903,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -9975,7 +9984,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ42">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR42">
         <v>1.69</v>
@@ -10924,7 +10933,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11002,7 +11011,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ47">
         <v>1.06</v>
@@ -11336,7 +11345,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11829,7 +11838,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ51">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR51">
         <v>1.33</v>
@@ -12032,7 +12041,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ52">
         <v>0.88</v>
@@ -12238,7 +12247,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ53">
         <v>1.88</v>
@@ -12366,7 +12375,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12984,7 +12993,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13062,7 +13071,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ57">
         <v>0.65</v>
@@ -13396,7 +13405,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13602,7 +13611,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13680,7 +13689,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ60">
         <v>1.5</v>
@@ -14014,7 +14023,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14095,7 +14104,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ62">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR62">
         <v>1.4</v>
@@ -15044,7 +15053,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15331,7 +15340,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ68">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR68">
         <v>1.66</v>
@@ -15456,7 +15465,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15534,7 +15543,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ69">
         <v>1.88</v>
@@ -15868,7 +15877,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -16074,7 +16083,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16155,7 +16164,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ72">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR72">
         <v>1.78</v>
@@ -16564,7 +16573,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ74">
         <v>1.5</v>
@@ -16692,7 +16701,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16976,7 +16985,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -17104,7 +17113,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17185,7 +17194,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ77">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR77">
         <v>1.36</v>
@@ -17516,7 +17525,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17928,7 +17937,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18340,7 +18349,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18418,7 +18427,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ83">
         <v>1.19</v>
@@ -18958,7 +18967,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19654,7 +19663,7 @@
         <v>0.67</v>
       </c>
       <c r="AP89">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ89">
         <v>1.29</v>
@@ -19782,7 +19791,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19988,7 +19997,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20066,7 +20075,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ91">
         <v>0.65</v>
@@ -20194,7 +20203,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20275,7 +20284,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ92">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR92">
         <v>1.5</v>
@@ -20400,7 +20409,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20478,7 +20487,7 @@
         <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ93">
         <v>1</v>
@@ -20812,7 +20821,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20893,7 +20902,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ95">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR95">
         <v>1.89</v>
@@ -22048,7 +22057,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22666,7 +22675,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22744,7 +22753,7 @@
         <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ104">
         <v>1</v>
@@ -22953,7 +22962,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ105">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR105">
         <v>1.58</v>
@@ -23284,7 +23293,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23362,7 +23371,7 @@
         <v>0.71</v>
       </c>
       <c r="AP107">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ107">
         <v>1.29</v>
@@ -23490,7 +23499,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23902,7 +23911,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -24108,7 +24117,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24186,10 +24195,10 @@
         <v>1.29</v>
       </c>
       <c r="AP111">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ111">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR111">
         <v>1.65</v>
@@ -24314,7 +24323,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24520,7 +24529,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24932,7 +24941,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -26168,7 +26177,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26374,7 +26383,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -27198,7 +27207,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -28103,7 +28112,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ130">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR130">
         <v>1.47</v>
@@ -28306,7 +28315,7 @@
         <v>1.25</v>
       </c>
       <c r="AP131">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ131">
         <v>1.12</v>
@@ -28512,7 +28521,7 @@
         <v>1.78</v>
       </c>
       <c r="AP132">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ132">
         <v>1.29</v>
@@ -28640,7 +28649,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28718,7 +28727,7 @@
         <v>1.25</v>
       </c>
       <c r="AP133">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ133">
         <v>1.06</v>
@@ -29464,7 +29473,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29545,7 +29554,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ137">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR137">
         <v>1.59</v>
@@ -30082,7 +30091,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30494,7 +30503,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30700,7 +30709,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30906,7 +30915,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -31112,7 +31121,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31524,7 +31533,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31730,7 +31739,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31811,7 +31820,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ148">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR148">
         <v>1.32</v>
@@ -31936,7 +31945,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -32142,7 +32151,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32632,7 +32641,7 @@
         <v>1.44</v>
       </c>
       <c r="AP152">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ152">
         <v>1.12</v>
@@ -32760,7 +32769,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32966,7 +32975,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33584,7 +33593,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -34280,7 +34289,7 @@
         <v>1.67</v>
       </c>
       <c r="AP160">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ160">
         <v>1.88</v>
@@ -34489,7 +34498,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ161">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR161">
         <v>1.54</v>
@@ -34898,7 +34907,7 @@
         <v>0.9</v>
       </c>
       <c r="AP163">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ163">
         <v>0.8100000000000001</v>
@@ -35026,7 +35035,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35107,7 +35116,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ164">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR164">
         <v>1.45</v>
@@ -35438,7 +35447,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35516,7 +35525,7 @@
         <v>1.3</v>
       </c>
       <c r="AP166">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ166">
         <v>1.12</v>
@@ -36056,7 +36065,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36262,7 +36271,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36468,7 +36477,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36755,7 +36764,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ172">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR172">
         <v>1.54</v>
@@ -37576,7 +37585,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ176">
         <v>1.19</v>
@@ -38322,7 +38331,7 @@
         <v>86</v>
       </c>
       <c r="P180" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q180">
         <v>3.05</v>
@@ -38609,7 +38618,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ181">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR181">
         <v>1.62</v>
@@ -39430,7 +39439,7 @@
         <v>0.91</v>
       </c>
       <c r="AP185">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ185">
         <v>0.8100000000000001</v>
@@ -39636,7 +39645,7 @@
         <v>1</v>
       </c>
       <c r="AP186">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ186">
         <v>1.19</v>
@@ -39764,7 +39773,7 @@
         <v>201</v>
       </c>
       <c r="P187" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q187">
         <v>3.85</v>
@@ -40176,7 +40185,7 @@
         <v>202</v>
       </c>
       <c r="P189" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q189">
         <v>2.7</v>
@@ -40257,7 +40266,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ189">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR189">
         <v>1.34</v>
@@ -40588,7 +40597,7 @@
         <v>204</v>
       </c>
       <c r="P191" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q191">
         <v>1.91</v>
@@ -41000,7 +41009,7 @@
         <v>206</v>
       </c>
       <c r="P193" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q193">
         <v>3.25</v>
@@ -41078,7 +41087,7 @@
         <v>1.27</v>
       </c>
       <c r="AP193">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ193">
         <v>1</v>
@@ -41206,7 +41215,7 @@
         <v>86</v>
       </c>
       <c r="P194" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q194">
         <v>3.15</v>
@@ -41902,7 +41911,7 @@
         <v>0.92</v>
       </c>
       <c r="AP197">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ197">
         <v>1.06</v>
@@ -42854,7 +42863,7 @@
         <v>210</v>
       </c>
       <c r="P202" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q202">
         <v>3.75</v>
@@ -43060,7 +43069,7 @@
         <v>86</v>
       </c>
       <c r="P203" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q203">
         <v>6</v>
@@ -43141,7 +43150,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ203">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR203">
         <v>1.35</v>
@@ -43472,7 +43481,7 @@
         <v>130</v>
       </c>
       <c r="P205" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q205">
         <v>3.1</v>
@@ -43550,7 +43559,7 @@
         <v>1.17</v>
       </c>
       <c r="AP205">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ205">
         <v>1</v>
@@ -43678,7 +43687,7 @@
         <v>211</v>
       </c>
       <c r="P206" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q206">
         <v>1.91</v>
@@ -44168,10 +44177,10 @@
         <v>0.42</v>
       </c>
       <c r="AP208">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ208">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR208">
         <v>1.66</v>
@@ -44296,7 +44305,7 @@
         <v>214</v>
       </c>
       <c r="P209" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q209">
         <v>4.75</v>
@@ -44502,7 +44511,7 @@
         <v>215</v>
       </c>
       <c r="P210" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q210">
         <v>2.8</v>
@@ -45120,7 +45129,7 @@
         <v>86</v>
       </c>
       <c r="P213" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q213">
         <v>2.65</v>
@@ -45532,7 +45541,7 @@
         <v>86</v>
       </c>
       <c r="P215" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q215">
         <v>6.8</v>
@@ -45738,7 +45747,7 @@
         <v>218</v>
       </c>
       <c r="P216" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q216">
         <v>1.91</v>
@@ -46150,7 +46159,7 @@
         <v>220</v>
       </c>
       <c r="P218" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q218">
         <v>2.18</v>
@@ -46228,10 +46237,10 @@
         <v>0.38</v>
       </c>
       <c r="AP218">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ218">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR218">
         <v>1.24</v>
@@ -46562,7 +46571,7 @@
         <v>221</v>
       </c>
       <c r="P220" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q220">
         <v>4.3</v>
@@ -46643,7 +46652,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ220">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR220">
         <v>1.73</v>
@@ -46846,7 +46855,7 @@
         <v>1.15</v>
       </c>
       <c r="AP221">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ221">
         <v>1</v>
@@ -47386,7 +47395,7 @@
         <v>223</v>
       </c>
       <c r="P224" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q224">
         <v>3.5</v>
@@ -47592,7 +47601,7 @@
         <v>209</v>
       </c>
       <c r="P225" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q225">
         <v>3.6</v>
@@ -47670,7 +47679,7 @@
         <v>1</v>
       </c>
       <c r="AP225">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ225">
         <v>1.06</v>
@@ -48004,7 +48013,7 @@
         <v>156</v>
       </c>
       <c r="P227" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q227">
         <v>3.75</v>
@@ -48210,7 +48219,7 @@
         <v>86</v>
       </c>
       <c r="P228" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q228">
         <v>2.24</v>
@@ -49446,7 +49455,7 @@
         <v>226</v>
       </c>
       <c r="P234" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -49652,7 +49661,7 @@
         <v>214</v>
       </c>
       <c r="P235" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q235">
         <v>3.65</v>
@@ -49730,7 +49739,7 @@
         <v>1.5</v>
       </c>
       <c r="AP235">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ235">
         <v>1.29</v>
@@ -50142,7 +50151,7 @@
         <v>1.14</v>
       </c>
       <c r="AP237">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ237">
         <v>1.06</v>
@@ -50348,10 +50357,10 @@
         <v>0.36</v>
       </c>
       <c r="AP238">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ238">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR238">
         <v>1.86</v>
@@ -50557,7 +50566,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ239">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR239">
         <v>2.11</v>
@@ -50888,7 +50897,7 @@
         <v>86</v>
       </c>
       <c r="P241" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q241">
         <v>4</v>
@@ -51094,7 +51103,7 @@
         <v>86</v>
       </c>
       <c r="P242" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51584,7 +51593,7 @@
         <v>0.67</v>
       </c>
       <c r="AP244">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AQ244">
         <v>0.65</v>
@@ -51712,7 +51721,7 @@
         <v>231</v>
       </c>
       <c r="P245" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q245">
         <v>2.3</v>
@@ -51790,7 +51799,7 @@
         <v>1.47</v>
       </c>
       <c r="AP245">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ245">
         <v>1.29</v>
@@ -51996,7 +52005,7 @@
         <v>0.87</v>
       </c>
       <c r="AP246">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AQ246">
         <v>0.88</v>
@@ -52330,7 +52339,7 @@
         <v>234</v>
       </c>
       <c r="P248" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q248">
         <v>2.6</v>
@@ -52536,7 +52545,7 @@
         <v>235</v>
       </c>
       <c r="P249" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q249">
         <v>2.05</v>
@@ -52617,7 +52626,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ249">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="AR249">
         <v>1.45</v>
@@ -52948,7 +52957,7 @@
         <v>86</v>
       </c>
       <c r="P251" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q251">
         <v>2.8</v>
@@ -53154,7 +53163,7 @@
         <v>236</v>
       </c>
       <c r="P252" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q252">
         <v>2.8</v>
@@ -53360,7 +53369,7 @@
         <v>237</v>
       </c>
       <c r="P253" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q253">
         <v>2.95</v>
@@ -53441,7 +53450,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ253">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR253">
         <v>1.7</v>
@@ -53772,7 +53781,7 @@
         <v>153</v>
       </c>
       <c r="P255" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q255">
         <v>4.1</v>
@@ -53978,7 +53987,7 @@
         <v>86</v>
       </c>
       <c r="P256" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q256">
         <v>3.65</v>
@@ -54596,7 +54605,7 @@
         <v>240</v>
       </c>
       <c r="P259" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q259">
         <v>3.76</v>
@@ -55172,7 +55181,7 @@
         <v>261</v>
       </c>
       <c r="B262">
-        <v>7856879</v>
+        <v>7856880</v>
       </c>
       <c r="C262" t="s">
         <v>68</v>
@@ -55181,196 +55190,814 @@
         <v>69</v>
       </c>
       <c r="E262" s="2">
-        <v>45753.625</v>
+        <v>45753.3125</v>
       </c>
       <c r="F262">
         <v>3</v>
       </c>
       <c r="G262" t="s">
+        <v>71</v>
+      </c>
+      <c r="H262" t="s">
+        <v>84</v>
+      </c>
+      <c r="I262">
+        <v>0</v>
+      </c>
+      <c r="J262">
+        <v>2</v>
+      </c>
+      <c r="K262">
+        <v>2</v>
+      </c>
+      <c r="L262">
+        <v>0</v>
+      </c>
+      <c r="M262">
+        <v>2</v>
+      </c>
+      <c r="N262">
+        <v>2</v>
+      </c>
+      <c r="O262" t="s">
+        <v>86</v>
+      </c>
+      <c r="P262" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q262">
+        <v>1.85</v>
+      </c>
+      <c r="R262">
+        <v>2.35</v>
+      </c>
+      <c r="S262">
+        <v>6.5</v>
+      </c>
+      <c r="T262">
+        <v>1.35</v>
+      </c>
+      <c r="U262">
+        <v>2.95</v>
+      </c>
+      <c r="V262">
+        <v>2.65</v>
+      </c>
+      <c r="W262">
+        <v>1.42</v>
+      </c>
+      <c r="X262">
+        <v>7.2</v>
+      </c>
+      <c r="Y262">
+        <v>1.03</v>
+      </c>
+      <c r="Z262">
+        <v>1.49</v>
+      </c>
+      <c r="AA262">
+        <v>4.1</v>
+      </c>
+      <c r="AB262">
+        <v>6.5</v>
+      </c>
+      <c r="AC262">
+        <v>1.04</v>
+      </c>
+      <c r="AD262">
+        <v>9</v>
+      </c>
+      <c r="AE262">
+        <v>1.28</v>
+      </c>
+      <c r="AF262">
+        <v>3.5</v>
+      </c>
+      <c r="AG262">
+        <v>1.98</v>
+      </c>
+      <c r="AH262">
+        <v>1.77</v>
+      </c>
+      <c r="AI262">
+        <v>2.1</v>
+      </c>
+      <c r="AJ262">
+        <v>1.6</v>
+      </c>
+      <c r="AK262">
+        <v>1.04</v>
+      </c>
+      <c r="AL262">
+        <v>1.15</v>
+      </c>
+      <c r="AM262">
+        <v>2.9</v>
+      </c>
+      <c r="AN262">
+        <v>1.75</v>
+      </c>
+      <c r="AO262">
+        <v>0.5</v>
+      </c>
+      <c r="AP262">
+        <v>1.65</v>
+      </c>
+      <c r="AQ262">
+        <v>0.65</v>
+      </c>
+      <c r="AR262">
+        <v>1.32</v>
+      </c>
+      <c r="AS262">
+        <v>1.12</v>
+      </c>
+      <c r="AT262">
+        <v>2.44</v>
+      </c>
+      <c r="AU262">
+        <v>8</v>
+      </c>
+      <c r="AV262">
+        <v>4</v>
+      </c>
+      <c r="AW262">
+        <v>11</v>
+      </c>
+      <c r="AX262">
+        <v>1</v>
+      </c>
+      <c r="AY262">
+        <v>22</v>
+      </c>
+      <c r="AZ262">
+        <v>5</v>
+      </c>
+      <c r="BA262">
+        <v>7</v>
+      </c>
+      <c r="BB262">
+        <v>0</v>
+      </c>
+      <c r="BC262">
+        <v>7</v>
+      </c>
+      <c r="BD262">
+        <v>1.41</v>
+      </c>
+      <c r="BE262">
+        <v>6.75</v>
+      </c>
+      <c r="BF262">
+        <v>3.3</v>
+      </c>
+      <c r="BG262">
+        <v>1.47</v>
+      </c>
+      <c r="BH262">
+        <v>2.43</v>
+      </c>
+      <c r="BI262">
+        <v>1.78</v>
+      </c>
+      <c r="BJ262">
+        <v>1.88</v>
+      </c>
+      <c r="BK262">
+        <v>2.25</v>
+      </c>
+      <c r="BL262">
+        <v>1.53</v>
+      </c>
+      <c r="BM262">
+        <v>2.95</v>
+      </c>
+      <c r="BN262">
+        <v>1.33</v>
+      </c>
+      <c r="BO262">
+        <v>3.95</v>
+      </c>
+      <c r="BP262">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="263" spans="1:68">
+      <c r="A263" s="1">
+        <v>262</v>
+      </c>
+      <c r="B263">
+        <v>7856879</v>
+      </c>
+      <c r="C263" t="s">
+        <v>68</v>
+      </c>
+      <c r="D263" t="s">
+        <v>69</v>
+      </c>
+      <c r="E263" s="2">
+        <v>45753.625</v>
+      </c>
+      <c r="F263">
+        <v>3</v>
+      </c>
+      <c r="G263" t="s">
         <v>81</v>
       </c>
-      <c r="H262" t="s">
+      <c r="H263" t="s">
         <v>83</v>
       </c>
-      <c r="I262">
-        <v>1</v>
-      </c>
-      <c r="J262">
-        <v>0</v>
-      </c>
-      <c r="K262">
-        <v>1</v>
-      </c>
-      <c r="L262">
-        <v>1</v>
-      </c>
-      <c r="M262">
-        <v>0</v>
-      </c>
-      <c r="N262">
-        <v>1</v>
-      </c>
-      <c r="O262" t="s">
+      <c r="I263">
+        <v>1</v>
+      </c>
+      <c r="J263">
+        <v>0</v>
+      </c>
+      <c r="K263">
+        <v>1</v>
+      </c>
+      <c r="L263">
+        <v>1</v>
+      </c>
+      <c r="M263">
+        <v>0</v>
+      </c>
+      <c r="N263">
+        <v>1</v>
+      </c>
+      <c r="O263" t="s">
         <v>100</v>
       </c>
-      <c r="P262" t="s">
+      <c r="P263" t="s">
         <v>86</v>
       </c>
-      <c r="Q262">
+      <c r="Q263">
         <v>2.87</v>
       </c>
-      <c r="R262">
+      <c r="R263">
         <v>2.05</v>
       </c>
-      <c r="S262">
+      <c r="S263">
         <v>3.86</v>
       </c>
-      <c r="T262">
+      <c r="T263">
         <v>1.4</v>
       </c>
-      <c r="U262">
+      <c r="U263">
         <v>2.73</v>
       </c>
-      <c r="V262">
+      <c r="V263">
         <v>2.99</v>
       </c>
-      <c r="W262">
+      <c r="W263">
         <v>1.34</v>
       </c>
-      <c r="X262">
+      <c r="X263">
         <v>7.9</v>
       </c>
-      <c r="Y262">
+      <c r="Y263">
         <v>1.02</v>
       </c>
-      <c r="Z262">
+      <c r="Z263">
         <v>2.22</v>
       </c>
-      <c r="AA262">
+      <c r="AA263">
         <v>3.15</v>
       </c>
-      <c r="AB262">
+      <c r="AB263">
         <v>3.3</v>
       </c>
-      <c r="AC262">
+      <c r="AC263">
         <v>1.05</v>
       </c>
-      <c r="AD262">
+      <c r="AD263">
         <v>8</v>
       </c>
-      <c r="AE262">
+      <c r="AE263">
         <v>1.29</v>
       </c>
-      <c r="AF262">
+      <c r="AF263">
         <v>3.3</v>
       </c>
-      <c r="AG262">
-        <v>2</v>
-      </c>
-      <c r="AH262">
+      <c r="AG263">
+        <v>2</v>
+      </c>
+      <c r="AH263">
         <v>1.75</v>
       </c>
-      <c r="AI262">
+      <c r="AI263">
         <v>1.8</v>
       </c>
-      <c r="AJ262">
-        <v>2</v>
-      </c>
-      <c r="AK262">
+      <c r="AJ263">
+        <v>2</v>
+      </c>
+      <c r="AK263">
         <v>1.27</v>
       </c>
-      <c r="AL262">
+      <c r="AL263">
         <v>1.32</v>
       </c>
-      <c r="AM262">
+      <c r="AM263">
         <v>1.6</v>
       </c>
-      <c r="AN262">
+      <c r="AN263">
         <v>1.88</v>
       </c>
-      <c r="AO262">
+      <c r="AO263">
         <v>1.38</v>
       </c>
-      <c r="AP262">
+      <c r="AP263">
         <v>1.94</v>
       </c>
-      <c r="AQ262">
+      <c r="AQ263">
         <v>1.29</v>
       </c>
-      <c r="AR262">
+      <c r="AR263">
         <v>1.71</v>
       </c>
-      <c r="AS262">
+      <c r="AS263">
         <v>1.24</v>
       </c>
-      <c r="AT262">
+      <c r="AT263">
         <v>2.95</v>
       </c>
-      <c r="AU262">
+      <c r="AU263">
         <v>5</v>
       </c>
-      <c r="AV262">
+      <c r="AV263">
         <v>6</v>
       </c>
-      <c r="AW262">
+      <c r="AW263">
         <v>10</v>
       </c>
-      <c r="AX262">
+      <c r="AX263">
         <v>6</v>
       </c>
-      <c r="AY262">
+      <c r="AY263">
         <v>19</v>
       </c>
-      <c r="AZ262">
+      <c r="AZ263">
         <v>12</v>
       </c>
-      <c r="BA262">
+      <c r="BA263">
         <v>8</v>
       </c>
-      <c r="BB262">
+      <c r="BB263">
         <v>3</v>
       </c>
-      <c r="BC262">
+      <c r="BC263">
         <v>11</v>
       </c>
-      <c r="BD262">
+      <c r="BD263">
         <v>1.63</v>
       </c>
-      <c r="BE262">
+      <c r="BE263">
         <v>6.4</v>
       </c>
-      <c r="BF262">
+      <c r="BF263">
         <v>2.55</v>
       </c>
-      <c r="BG262">
+      <c r="BG263">
         <v>1.46</v>
       </c>
-      <c r="BH262">
+      <c r="BH263">
         <v>2.45</v>
       </c>
-      <c r="BI262">
+      <c r="BI263">
         <v>1.77</v>
       </c>
-      <c r="BJ262">
+      <c r="BJ263">
         <v>1.89</v>
       </c>
-      <c r="BK262">
+      <c r="BK263">
         <v>2.23</v>
       </c>
-      <c r="BL262">
+      <c r="BL263">
         <v>1.56</v>
       </c>
-      <c r="BM262">
+      <c r="BM263">
         <v>2.9</v>
       </c>
-      <c r="BN262">
+      <c r="BN263">
         <v>1.34</v>
       </c>
-      <c r="BO262">
+      <c r="BO263">
         <v>3.8</v>
       </c>
-      <c r="BP262">
+      <c r="BP263">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="264" spans="1:68">
+      <c r="A264" s="1">
+        <v>263</v>
+      </c>
+      <c r="B264">
+        <v>7856882</v>
+      </c>
+      <c r="C264" t="s">
+        <v>68</v>
+      </c>
+      <c r="D264" t="s">
+        <v>69</v>
+      </c>
+      <c r="E264" s="2">
+        <v>45754.47916666666</v>
+      </c>
+      <c r="F264">
+        <v>3</v>
+      </c>
+      <c r="G264" t="s">
+        <v>70</v>
+      </c>
+      <c r="H264" t="s">
+        <v>79</v>
+      </c>
+      <c r="I264">
+        <v>1</v>
+      </c>
+      <c r="J264">
+        <v>0</v>
+      </c>
+      <c r="K264">
+        <v>1</v>
+      </c>
+      <c r="L264">
+        <v>1</v>
+      </c>
+      <c r="M264">
+        <v>1</v>
+      </c>
+      <c r="N264">
+        <v>2</v>
+      </c>
+      <c r="O264" t="s">
+        <v>242</v>
+      </c>
+      <c r="P264" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q264">
+        <v>2.1</v>
+      </c>
+      <c r="R264">
+        <v>2.1</v>
+      </c>
+      <c r="S264">
+        <v>6</v>
+      </c>
+      <c r="T264">
+        <v>1.41</v>
+      </c>
+      <c r="U264">
+        <v>2.81</v>
+      </c>
+      <c r="V264">
+        <v>3.08</v>
+      </c>
+      <c r="W264">
+        <v>1.35</v>
+      </c>
+      <c r="X264">
+        <v>7.5</v>
+      </c>
+      <c r="Y264">
+        <v>1.03</v>
+      </c>
+      <c r="Z264">
+        <v>1.71</v>
+      </c>
+      <c r="AA264">
+        <v>3.55</v>
+      </c>
+      <c r="AB264">
+        <v>4.9</v>
+      </c>
+      <c r="AC264">
+        <v>1.03</v>
+      </c>
+      <c r="AD264">
+        <v>9</v>
+      </c>
+      <c r="AE264">
+        <v>1.29</v>
+      </c>
+      <c r="AF264">
+        <v>3.3</v>
+      </c>
+      <c r="AG264">
+        <v>2</v>
+      </c>
+      <c r="AH264">
+        <v>1.67</v>
+      </c>
+      <c r="AI264">
+        <v>2.05</v>
+      </c>
+      <c r="AJ264">
+        <v>1.75</v>
+      </c>
+      <c r="AK264">
+        <v>1.12</v>
+      </c>
+      <c r="AL264">
+        <v>1.25</v>
+      </c>
+      <c r="AM264">
+        <v>2.32</v>
+      </c>
+      <c r="AN264">
+        <v>1.44</v>
+      </c>
+      <c r="AO264">
+        <v>0.88</v>
+      </c>
+      <c r="AP264">
+        <v>1.41</v>
+      </c>
+      <c r="AQ264">
+        <v>0.88</v>
+      </c>
+      <c r="AR264">
+        <v>1.7</v>
+      </c>
+      <c r="AS264">
+        <v>1.29</v>
+      </c>
+      <c r="AT264">
+        <v>2.99</v>
+      </c>
+      <c r="AU264">
+        <v>7</v>
+      </c>
+      <c r="AV264">
+        <v>4</v>
+      </c>
+      <c r="AW264">
+        <v>8</v>
+      </c>
+      <c r="AX264">
+        <v>12</v>
+      </c>
+      <c r="AY264">
+        <v>16</v>
+      </c>
+      <c r="AZ264">
+        <v>17</v>
+      </c>
+      <c r="BA264">
+        <v>6</v>
+      </c>
+      <c r="BB264">
+        <v>2</v>
+      </c>
+      <c r="BC264">
+        <v>8</v>
+      </c>
+      <c r="BD264">
+        <v>1.38</v>
+      </c>
+      <c r="BE264">
+        <v>7</v>
+      </c>
+      <c r="BF264">
+        <v>3.3</v>
+      </c>
+      <c r="BG264">
+        <v>1.3</v>
+      </c>
+      <c r="BH264">
+        <v>3.05</v>
+      </c>
+      <c r="BI264">
+        <v>1.52</v>
+      </c>
+      <c r="BJ264">
+        <v>2.3</v>
+      </c>
+      <c r="BK264">
+        <v>1.83</v>
+      </c>
+      <c r="BL264">
+        <v>1.83</v>
+      </c>
+      <c r="BM264">
+        <v>2.28</v>
+      </c>
+      <c r="BN264">
+        <v>1.52</v>
+      </c>
+      <c r="BO264">
+        <v>2.95</v>
+      </c>
+      <c r="BP264">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="265" spans="1:68">
+      <c r="A265" s="1">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>7856878</v>
+      </c>
+      <c r="C265" t="s">
+        <v>68</v>
+      </c>
+      <c r="D265" t="s">
+        <v>69</v>
+      </c>
+      <c r="E265" s="2">
+        <v>45754.60416666666</v>
+      </c>
+      <c r="F265">
+        <v>3</v>
+      </c>
+      <c r="G265" t="s">
+        <v>75</v>
+      </c>
+      <c r="H265" t="s">
+        <v>80</v>
+      </c>
+      <c r="I265">
+        <v>2</v>
+      </c>
+      <c r="J265">
+        <v>0</v>
+      </c>
+      <c r="K265">
+        <v>2</v>
+      </c>
+      <c r="L265">
+        <v>2</v>
+      </c>
+      <c r="M265">
+        <v>0</v>
+      </c>
+      <c r="N265">
+        <v>2</v>
+      </c>
+      <c r="O265" t="s">
+        <v>243</v>
+      </c>
+      <c r="P265" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q265">
+        <v>2.62</v>
+      </c>
+      <c r="R265">
+        <v>2.05</v>
+      </c>
+      <c r="S265">
+        <v>4.33</v>
+      </c>
+      <c r="T265">
+        <v>1.42</v>
+      </c>
+      <c r="U265">
+        <v>2.62</v>
+      </c>
+      <c r="V265">
+        <v>2.88</v>
+      </c>
+      <c r="W265">
+        <v>1.33</v>
+      </c>
+      <c r="X265">
+        <v>8</v>
+      </c>
+      <c r="Y265">
+        <v>1.05</v>
+      </c>
+      <c r="Z265">
+        <v>2.34</v>
+      </c>
+      <c r="AA265">
+        <v>3.19</v>
+      </c>
+      <c r="AB265">
+        <v>3.04</v>
+      </c>
+      <c r="AC265">
+        <v>1.07</v>
+      </c>
+      <c r="AD265">
+        <v>7</v>
+      </c>
+      <c r="AE265">
+        <v>1.38</v>
+      </c>
+      <c r="AF265">
+        <v>2.8</v>
+      </c>
+      <c r="AG265">
+        <v>1.92</v>
+      </c>
+      <c r="AH265">
+        <v>1.82</v>
+      </c>
+      <c r="AI265">
+        <v>1.91</v>
+      </c>
+      <c r="AJ265">
+        <v>1.8</v>
+      </c>
+      <c r="AK265">
+        <v>1.25</v>
+      </c>
+      <c r="AL265">
+        <v>1.35</v>
+      </c>
+      <c r="AM265">
+        <v>1.78</v>
+      </c>
+      <c r="AN265">
+        <v>2.06</v>
+      </c>
+      <c r="AO265">
+        <v>1.44</v>
+      </c>
+      <c r="AP265">
+        <v>2.12</v>
+      </c>
+      <c r="AQ265">
+        <v>1.35</v>
+      </c>
+      <c r="AR265">
+        <v>1.89</v>
+      </c>
+      <c r="AS265">
+        <v>1.56</v>
+      </c>
+      <c r="AT265">
+        <v>3.45</v>
+      </c>
+      <c r="AU265">
+        <v>8</v>
+      </c>
+      <c r="AV265">
+        <v>3</v>
+      </c>
+      <c r="AW265">
+        <v>4</v>
+      </c>
+      <c r="AX265">
+        <v>4</v>
+      </c>
+      <c r="AY265">
+        <v>15</v>
+      </c>
+      <c r="AZ265">
+        <v>7</v>
+      </c>
+      <c r="BA265">
+        <v>5</v>
+      </c>
+      <c r="BB265">
+        <v>5</v>
+      </c>
+      <c r="BC265">
+        <v>10</v>
+      </c>
+      <c r="BD265">
+        <v>1.74</v>
+      </c>
+      <c r="BE265">
+        <v>6.4</v>
+      </c>
+      <c r="BF265">
+        <v>2.33</v>
+      </c>
+      <c r="BG265">
+        <v>1.3</v>
+      </c>
+      <c r="BH265">
+        <v>3.05</v>
+      </c>
+      <c r="BI265">
+        <v>1.53</v>
+      </c>
+      <c r="BJ265">
+        <v>2.28</v>
+      </c>
+      <c r="BK265">
+        <v>1.88</v>
+      </c>
+      <c r="BL265">
+        <v>1.78</v>
+      </c>
+      <c r="BM265">
+        <v>2.35</v>
+      </c>
+      <c r="BN265">
+        <v>1.49</v>
+      </c>
+      <c r="BO265">
+        <v>3.05</v>
+      </c>
+      <c r="BP265">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Romania Liga I_20242025.xlsx
@@ -1882,10 +1882,10 @@
         <v>4</v>
       </c>
       <c r="AY2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA2">
         <v>8</v>
@@ -2088,10 +2088,10 @@
         <v>3</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA3">
         <v>0</v>
@@ -2294,10 +2294,10 @@
         <v>10</v>
       </c>
       <c r="AY4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA4">
         <v>4</v>
@@ -2500,10 +2500,10 @@
         <v>6</v>
       </c>
       <c r="AY5">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ5">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA5">
         <v>5</v>
@@ -2706,10 +2706,10 @@
         <v>0</v>
       </c>
       <c r="AY6">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA6">
         <v>6</v>
@@ -2912,10 +2912,10 @@
         <v>4</v>
       </c>
       <c r="AY7">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA7">
         <v>7</v>
@@ -3118,10 +3118,10 @@
         <v>4</v>
       </c>
       <c r="AY8">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA8">
         <v>7</v>
@@ -3324,10 +3324,10 @@
         <v>2</v>
       </c>
       <c r="AY9">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AZ9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA9">
         <v>5</v>
@@ -3530,10 +3530,10 @@
         <v>2</v>
       </c>
       <c r="AY10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA10">
         <v>5</v>
@@ -3736,10 +3736,10 @@
         <v>4</v>
       </c>
       <c r="AY11">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ11">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA11">
         <v>4</v>
@@ -3942,7 +3942,7 @@
         <v>2</v>
       </c>
       <c r="AY12">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ12">
         <v>8</v>
@@ -4148,10 +4148,10 @@
         <v>7</v>
       </c>
       <c r="AY13">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ13">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA13">
         <v>5</v>
@@ -4354,10 +4354,10 @@
         <v>3</v>
       </c>
       <c r="AY14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA14">
         <v>3</v>
@@ -4560,10 +4560,10 @@
         <v>2</v>
       </c>
       <c r="AY15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA15">
         <v>5</v>
@@ -4766,10 +4766,10 @@
         <v>4</v>
       </c>
       <c r="AY16">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ16">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA16">
         <v>7</v>
@@ -4972,10 +4972,10 @@
         <v>10</v>
       </c>
       <c r="AY17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ17">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BA17">
         <v>8</v>
@@ -5178,10 +5178,10 @@
         <v>11</v>
       </c>
       <c r="AY18">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ18">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA18">
         <v>5</v>
@@ -5384,10 +5384,10 @@
         <v>1</v>
       </c>
       <c r="AY19">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA19">
         <v>9</v>
@@ -5590,10 +5590,10 @@
         <v>3</v>
       </c>
       <c r="AY20">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ20">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA20">
         <v>7</v>
@@ -5796,10 +5796,10 @@
         <v>4</v>
       </c>
       <c r="AY21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA21">
         <v>9</v>
@@ -6002,10 +6002,10 @@
         <v>1</v>
       </c>
       <c r="AY22">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA22">
         <v>7</v>
@@ -6208,10 +6208,10 @@
         <v>4</v>
       </c>
       <c r="AY23">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ23">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA23">
         <v>5</v>
@@ -6414,10 +6414,10 @@
         <v>6</v>
       </c>
       <c r="AY24">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ24">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA24">
         <v>6</v>
@@ -6620,10 +6620,10 @@
         <v>4</v>
       </c>
       <c r="AY25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ25">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA25">
         <v>0</v>
@@ -6826,10 +6826,10 @@
         <v>4</v>
       </c>
       <c r="AY26">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ26">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA26">
         <v>6</v>
@@ -7032,10 +7032,10 @@
         <v>7</v>
       </c>
       <c r="AY27">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ27">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA27">
         <v>5</v>
@@ -7238,10 +7238,10 @@
         <v>4</v>
       </c>
       <c r="AY28">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ28">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BA28">
         <v>3</v>
@@ -7444,19 +7444,19 @@
         <v>4</v>
       </c>
       <c r="AY29">
+        <v>10</v>
+      </c>
+      <c r="AZ29">
         <v>11</v>
       </c>
-      <c r="AZ29">
-        <v>14</v>
-      </c>
       <c r="BA29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB29">
         <v>5</v>
       </c>
       <c r="BC29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD29">
         <v>1.34</v>
@@ -7650,10 +7650,10 @@
         <v>2</v>
       </c>
       <c r="AY30">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ30">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA30">
         <v>0</v>
@@ -7856,10 +7856,10 @@
         <v>5</v>
       </c>
       <c r="AY31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ31">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA31">
         <v>3</v>
@@ -8062,10 +8062,10 @@
         <v>8</v>
       </c>
       <c r="AY32">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ32">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA32">
         <v>2</v>
@@ -8268,10 +8268,10 @@
         <v>5</v>
       </c>
       <c r="AY33">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA33">
         <v>6</v>
@@ -8474,10 +8474,10 @@
         <v>5</v>
       </c>
       <c r="AY34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ34">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA34">
         <v>8</v>
@@ -8680,10 +8680,10 @@
         <v>5</v>
       </c>
       <c r="AY35">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ35">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BA35">
         <v>10</v>
@@ -8886,10 +8886,10 @@
         <v>6</v>
       </c>
       <c r="AY36">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ36">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA36">
         <v>2</v>
@@ -9092,7 +9092,7 @@
         <v>3</v>
       </c>
       <c r="AY37">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AZ37">
         <v>7</v>
@@ -9298,10 +9298,10 @@
         <v>4</v>
       </c>
       <c r="AY38">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA38">
         <v>3</v>
@@ -9504,10 +9504,10 @@
         <v>4</v>
       </c>
       <c r="AY39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA39">
         <v>6</v>
@@ -9710,10 +9710,10 @@
         <v>7</v>
       </c>
       <c r="AY40">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ40">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA40">
         <v>6</v>
@@ -9916,10 +9916,10 @@
         <v>3</v>
       </c>
       <c r="AY41">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ41">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA41">
         <v>6</v>
@@ -10122,10 +10122,10 @@
         <v>4</v>
       </c>
       <c r="AY42">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AZ42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA42">
         <v>9</v>
@@ -10328,10 +10328,10 @@
         <v>4</v>
       </c>
       <c r="AY43">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ43">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA43">
         <v>7</v>
@@ -10534,10 +10534,10 @@
         <v>5</v>
       </c>
       <c r="AY44">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ44">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA44">
         <v>7</v>
@@ -10740,10 +10740,10 @@
         <v>6</v>
       </c>
       <c r="AY45">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ45">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA45">
         <v>1</v>
@@ -10946,10 +10946,10 @@
         <v>6</v>
       </c>
       <c r="AY46">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ46">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA46">
         <v>1</v>
@@ -11152,10 +11152,10 @@
         <v>1</v>
       </c>
       <c r="AY47">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ47">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BA47">
         <v>4</v>
@@ -11358,10 +11358,10 @@
         <v>4</v>
       </c>
       <c r="AY48">
+        <v>7</v>
+      </c>
+      <c r="AZ48">
         <v>9</v>
-      </c>
-      <c r="AZ48">
-        <v>11</v>
       </c>
       <c r="BA48">
         <v>2</v>
@@ -11564,10 +11564,10 @@
         <v>5</v>
       </c>
       <c r="AY49">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ49">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA49">
         <v>5</v>
@@ -11770,10 +11770,10 @@
         <v>7</v>
       </c>
       <c r="AY50">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AZ50">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA50">
         <v>7</v>
@@ -11976,10 +11976,10 @@
         <v>5</v>
       </c>
       <c r="AY51">
+        <v>5</v>
+      </c>
+      <c r="AZ51">
         <v>8</v>
-      </c>
-      <c r="AZ51">
-        <v>11</v>
       </c>
       <c r="BA51">
         <v>2</v>
@@ -12182,10 +12182,10 @@
         <v>3</v>
       </c>
       <c r="AY52">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA52">
         <v>9</v>
@@ -12388,10 +12388,10 @@
         <v>8</v>
       </c>
       <c r="AY53">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ53">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA53">
         <v>5</v>
@@ -12594,10 +12594,10 @@
         <v>5</v>
       </c>
       <c r="AY54">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ54">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA54">
         <v>2</v>
@@ -12800,10 +12800,10 @@
         <v>5</v>
       </c>
       <c r="AY55">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ55">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA55">
         <v>5</v>
@@ -13009,7 +13009,7 @@
         <v>13</v>
       </c>
       <c r="AZ56">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA56">
         <v>2</v>
@@ -13212,10 +13212,10 @@
         <v>8</v>
       </c>
       <c r="AY57">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ57">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA57">
         <v>3</v>
@@ -13418,7 +13418,7 @@
         <v>2</v>
       </c>
       <c r="AY58">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ58">
         <v>4</v>
@@ -13624,10 +13624,10 @@
         <v>7</v>
       </c>
       <c r="AY59">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ59">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA59">
         <v>9</v>
@@ -13830,10 +13830,10 @@
         <v>4</v>
       </c>
       <c r="AY60">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ60">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA60">
         <v>5</v>
@@ -14036,10 +14036,10 @@
         <v>4</v>
       </c>
       <c r="AY61">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AZ61">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA61">
         <v>6</v>
@@ -14242,10 +14242,10 @@
         <v>5</v>
       </c>
       <c r="AY62">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ62">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA62">
         <v>8</v>
@@ -14448,10 +14448,10 @@
         <v>7</v>
       </c>
       <c r="AY63">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ63">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA63">
         <v>5</v>
@@ -14654,10 +14654,10 @@
         <v>6</v>
       </c>
       <c r="AY64">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ64">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA64">
         <v>2</v>
@@ -14860,10 +14860,10 @@
         <v>7</v>
       </c>
       <c r="AY65">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ65">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA65">
         <v>4</v>
@@ -15066,10 +15066,10 @@
         <v>4</v>
       </c>
       <c r="AY66">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA66">
         <v>5</v>
@@ -15272,10 +15272,10 @@
         <v>1</v>
       </c>
       <c r="AY67">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ67">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA67">
         <v>5</v>
@@ -15478,10 +15478,10 @@
         <v>5</v>
       </c>
       <c r="AY68">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ68">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="BA68">
         <v>1</v>
@@ -15687,7 +15687,7 @@
         <v>9</v>
       </c>
       <c r="AZ69">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA69">
         <v>1</v>
@@ -15890,10 +15890,10 @@
         <v>7</v>
       </c>
       <c r="AY70">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AZ70">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA70">
         <v>3</v>
@@ -16096,10 +16096,10 @@
         <v>4</v>
       </c>
       <c r="AY71">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ71">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA71">
         <v>7</v>
@@ -16302,10 +16302,10 @@
         <v>3</v>
       </c>
       <c r="AY72">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ72">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA72">
         <v>7</v>
@@ -16508,10 +16508,10 @@
         <v>3</v>
       </c>
       <c r="AY73">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ73">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA73">
         <v>7</v>
@@ -16717,7 +16717,7 @@
         <v>4</v>
       </c>
       <c r="AZ74">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA74">
         <v>3</v>
@@ -16920,10 +16920,10 @@
         <v>7</v>
       </c>
       <c r="AY75">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ75">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA75">
         <v>2</v>
@@ -17129,7 +17129,7 @@
         <v>10</v>
       </c>
       <c r="AZ76">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BA76">
         <v>4</v>
@@ -17332,10 +17332,10 @@
         <v>4</v>
       </c>
       <c r="AY77">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ77">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA77">
         <v>6</v>
@@ -17538,10 +17538,10 @@
         <v>7</v>
       </c>
       <c r="AY78">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ78">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA78">
         <v>8</v>
@@ -17744,10 +17744,10 @@
         <v>12</v>
       </c>
       <c r="AY79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ79">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA79">
         <v>5</v>
@@ -17950,10 +17950,10 @@
         <v>8</v>
       </c>
       <c r="AY80">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ80">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA80">
         <v>2</v>
@@ -18156,10 +18156,10 @@
         <v>5</v>
       </c>
       <c r="AY81">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ81">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA81">
         <v>4</v>
@@ -18362,10 +18362,10 @@
         <v>6</v>
       </c>
       <c r="AY82">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ82">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA82">
         <v>3</v>
@@ -18568,10 +18568,10 @@
         <v>4</v>
       </c>
       <c r="AY83">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AZ83">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA83">
         <v>13</v>
@@ -18774,10 +18774,10 @@
         <v>11</v>
       </c>
       <c r="AY84">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ84">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BA84">
         <v>2</v>
@@ -18980,10 +18980,10 @@
         <v>6</v>
       </c>
       <c r="AY85">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ85">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA85">
         <v>4</v>
@@ -19186,10 +19186,10 @@
         <v>6</v>
       </c>
       <c r="AY86">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ86">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA86">
         <v>6</v>
@@ -19392,10 +19392,10 @@
         <v>5</v>
       </c>
       <c r="AY87">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ87">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA87">
         <v>8</v>
@@ -19598,10 +19598,10 @@
         <v>5</v>
       </c>
       <c r="AY88">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ88">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA88">
         <v>3</v>
@@ -19804,10 +19804,10 @@
         <v>1</v>
       </c>
       <c r="AY89">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ89">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA89">
         <v>5</v>
@@ -20010,10 +20010,10 @@
         <v>9</v>
       </c>
       <c r="AY90">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ90">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA90">
         <v>2</v>
@@ -20216,10 +20216,10 @@
         <v>6</v>
       </c>
       <c r="AY91">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ91">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA91">
         <v>6</v>
@@ -20422,10 +20422,10 @@
         <v>4</v>
       </c>
       <c r="AY92">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ92">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA92">
         <v>6</v>
@@ -20628,10 +20628,10 @@
         <v>4</v>
       </c>
       <c r="AY93">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ93">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA93">
         <v>7</v>
@@ -20834,10 +20834,10 @@
         <v>3</v>
       </c>
       <c r="AY94">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ94">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA94">
         <v>4</v>
@@ -21040,10 +21040,10 @@
         <v>2</v>
       </c>
       <c r="AY95">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AZ95">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA95">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>8</v>
       </c>
       <c r="AZ97">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA97">
         <v>3</v>
@@ -21658,10 +21658,10 @@
         <v>7</v>
       </c>
       <c r="AY98">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ98">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA98">
         <v>4</v>
@@ -21864,10 +21864,10 @@
         <v>3</v>
       </c>
       <c r="AY99">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ99">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA99">
         <v>6</v>
@@ -22482,10 +22482,10 @@
         <v>4</v>
       </c>
       <c r="AY102">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ102">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA102">
         <v>5</v>
@@ -22688,10 +22688,10 @@
         <v>4</v>
       </c>
       <c r="AY103">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ103">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BA103">
         <v>6</v>
@@ -22894,10 +22894,10 @@
         <v>1</v>
       </c>
       <c r="AY104">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AZ104">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA104">
         <v>10</v>
@@ -23100,10 +23100,10 @@
         <v>5</v>
       </c>
       <c r="AY105">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ105">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA105">
         <v>5</v>
@@ -23306,10 +23306,10 @@
         <v>2</v>
       </c>
       <c r="AY106">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ106">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA106">
         <v>14</v>
@@ -23515,7 +23515,7 @@
         <v>12</v>
       </c>
       <c r="AZ107">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA107">
         <v>10</v>
@@ -23718,10 +23718,10 @@
         <v>3</v>
       </c>
       <c r="AY108">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ108">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA108">
         <v>4</v>
@@ -23924,10 +23924,10 @@
         <v>3</v>
       </c>
       <c r="AY109">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ109">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA109">
         <v>7</v>
@@ -24130,10 +24130,10 @@
         <v>6</v>
       </c>
       <c r="AY110">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ110">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA110">
         <v>6</v>
@@ -24336,10 +24336,10 @@
         <v>8</v>
       </c>
       <c r="AY111">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ111">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="BA111">
         <v>2</v>
@@ -24542,10 +24542,10 @@
         <v>2</v>
       </c>
       <c r="AY112">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ112">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA112">
         <v>5</v>
@@ -24748,10 +24748,10 @@
         <v>8</v>
       </c>
       <c r="AY113">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ113">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA113">
         <v>0</v>
@@ -24954,10 +24954,10 @@
         <v>4</v>
       </c>
       <c r="AY114">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ114">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA114">
         <v>4</v>
@@ -25160,10 +25160,10 @@
         <v>3</v>
       </c>
       <c r="AY115">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ115">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA115">
         <v>10</v>
@@ -25366,10 +25366,10 @@
         <v>4</v>
       </c>
       <c r="AY116">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AZ116">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA116">
         <v>8</v>
@@ -25572,10 +25572,10 @@
         <v>6</v>
       </c>
       <c r="AY117">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AZ117">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA117">
         <v>4</v>
@@ -25778,10 +25778,10 @@
         <v>7</v>
       </c>
       <c r="AY118">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ118">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BA118">
         <v>6</v>
@@ -25984,10 +25984,10 @@
         <v>4</v>
       </c>
       <c r="AY119">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ119">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA119">
         <v>4</v>
@@ -26190,10 +26190,10 @@
         <v>3</v>
       </c>
       <c r="AY120">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ120">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA120">
         <v>5</v>
@@ -26396,10 +26396,10 @@
         <v>2</v>
       </c>
       <c r="AY121">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ121">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA121">
         <v>11</v>
@@ -26602,7 +26602,7 @@
         <v>3</v>
       </c>
       <c r="AY122">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AZ122">
         <v>7</v>
@@ -26808,7 +26808,7 @@
         <v>4</v>
       </c>
       <c r="AY123">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ123">
         <v>8</v>
@@ -27014,10 +27014,10 @@
         <v>4</v>
       </c>
       <c r="AY124">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ124">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA124">
         <v>7</v>
@@ -27220,10 +27220,10 @@
         <v>2</v>
       </c>
       <c r="AY125">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AZ125">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BA125">
         <v>10</v>
@@ -27429,7 +27429,7 @@
         <v>11</v>
       </c>
       <c r="AZ126">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA126">
         <v>6</v>
@@ -27632,10 +27632,10 @@
         <v>4</v>
       </c>
       <c r="AY127">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ127">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA127">
         <v>4</v>
@@ -27838,10 +27838,10 @@
         <v>2</v>
       </c>
       <c r="AY128">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ128">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA128">
         <v>8</v>
@@ -28044,10 +28044,10 @@
         <v>8</v>
       </c>
       <c r="AY129">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ129">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA129">
         <v>3</v>
@@ -29898,10 +29898,10 @@
         <v>4</v>
       </c>
       <c r="AY138">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AZ138">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA138">
         <v>12</v>
@@ -30104,10 +30104,10 @@
         <v>7</v>
       </c>
       <c r="AY139">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ139">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA139">
         <v>4</v>
@@ -30310,10 +30310,10 @@
         <v>2</v>
       </c>
       <c r="AY140">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ140">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA140">
         <v>2</v>
@@ -30516,10 +30516,10 @@
         <v>4</v>
       </c>
       <c r="AY141">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ141">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA141">
         <v>4</v>
@@ -30725,7 +30725,7 @@
         <v>11</v>
       </c>
       <c r="AZ142">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA142">
         <v>2</v>
@@ -31134,10 +31134,10 @@
         <v>4</v>
       </c>
       <c r="AY144">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AZ144">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA144">
         <v>10</v>
@@ -31340,10 +31340,10 @@
         <v>6</v>
       </c>
       <c r="AY145">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ145">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA145">
         <v>3</v>
@@ -31546,10 +31546,10 @@
         <v>6</v>
       </c>
       <c r="AY146">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ146">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA146">
         <v>3</v>
@@ -31752,10 +31752,10 @@
         <v>2</v>
       </c>
       <c r="AY147">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ147">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA147">
         <v>4</v>
@@ -31958,10 +31958,10 @@
         <v>13</v>
       </c>
       <c r="AY148">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ148">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA148">
         <v>1</v>
@@ -32164,10 +32164,10 @@
         <v>6</v>
       </c>
       <c r="AY149">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ149">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA149">
         <v>8</v>
@@ -32370,10 +32370,10 @@
         <v>5</v>
       </c>
       <c r="AY150">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AZ150">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA150">
         <v>6</v>
@@ -32782,10 +32782,10 @@
         <v>5</v>
       </c>
       <c r="AY152">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ152">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA152">
         <v>2</v>
@@ -32988,10 +32988,10 @@
         <v>2</v>
       </c>
       <c r="AY153">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ153">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA153">
         <v>6</v>
@@ -33194,10 +33194,10 @@
         <v>4</v>
       </c>
       <c r="AY154">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ154">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA154">
         <v>3</v>
@@ -33400,10 +33400,10 @@
         <v>3</v>
       </c>
       <c r="AY155">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ155">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA155">
         <v>6</v>
@@ -33606,10 +33606,10 @@
         <v>3</v>
       </c>
       <c r="AY156">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AZ156">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA156">
         <v>4</v>
@@ -33812,10 +33812,10 @@
         <v>3</v>
       </c>
       <c r="AY157">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ157">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA157">
         <v>5</v>
@@ -34018,10 +34018,10 @@
         <v>3</v>
       </c>
       <c r="AY158">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ158">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA158">
         <v>4</v>
@@ -34224,10 +34224,10 @@
         <v>7</v>
       </c>
       <c r="AY159">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AZ159">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA159">
         <v>1</v>
@@ -34430,10 +34430,10 @@
         <v>7</v>
       </c>
       <c r="AY160">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ160">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BA160">
         <v>4</v>
@@ -34636,10 +34636,10 @@
         <v>2</v>
       </c>
       <c r="AY161">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ161">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BA161">
         <v>2</v>
@@ -34842,10 +34842,10 @@
         <v>10</v>
       </c>
       <c r="AY162">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ162">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="BA162">
         <v>2</v>
@@ -35048,10 +35048,10 @@
         <v>5</v>
       </c>
       <c r="AY163">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ163">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA163">
         <v>4</v>
@@ -35254,10 +35254,10 @@
         <v>2</v>
       </c>
       <c r="AY164">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ164">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA164">
         <v>6</v>
@@ -35460,10 +35460,10 @@
         <v>1</v>
       </c>
       <c r="AY165">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AZ165">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA165">
         <v>9</v>
@@ -35666,10 +35666,10 @@
         <v>4</v>
       </c>
       <c r="AY166">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ166">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA166">
         <v>4</v>
@@ -35872,10 +35872,10 @@
         <v>3</v>
       </c>
       <c r="AY167">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ167">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA167">
         <v>4</v>
@@ -36078,10 +36078,10 @@
         <v>6</v>
       </c>
       <c r="AY168">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ168">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA168">
         <v>4</v>
@@ -36284,10 +36284,10 @@
         <v>10</v>
       </c>
       <c r="AY169">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ169">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BA169">
         <v>1</v>
@@ -36493,7 +36493,7 @@
         <v>12</v>
       </c>
       <c r="AZ170">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BA170">
         <v>5</v>
@@ -36696,7 +36696,7 @@
         <v>0</v>
       </c>
       <c r="AY171">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="AZ171">
         <v>2</v>
@@ -36902,7 +36902,7 @@
         <v>3</v>
       </c>
       <c r="AY172">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ172">
         <v>6</v>
@@ -37111,7 +37111,7 @@
         <v>5</v>
       </c>
       <c r="AZ173">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA173">
         <v>2</v>
@@ -37314,10 +37314,10 @@
         <v>10</v>
       </c>
       <c r="AY174">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AZ174">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA174">
         <v>8</v>
@@ -37520,10 +37520,10 @@
         <v>6</v>
       </c>
       <c r="AY175">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ175">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA175">
         <v>3</v>
@@ -37726,10 +37726,10 @@
         <v>3</v>
       </c>
       <c r="AY176">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="AZ176">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA176">
         <v>12</v>
@@ -37932,10 +37932,10 @@
         <v>11</v>
       </c>
       <c r="AY177">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AZ177">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA177">
         <v>10</v>
@@ -38138,10 +38138,10 @@
         <v>4</v>
       </c>
       <c r="AY178">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ178">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA178">
         <v>4</v>
@@ -38344,10 +38344,10 @@
         <v>14</v>
       </c>
       <c r="AY179">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ179">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA179">
         <v>4</v>
@@ -38550,7 +38550,7 @@
         <v>9</v>
       </c>
       <c r="AY180">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AZ180">
         <v>18</v>
@@ -38756,10 +38756,10 @@
         <v>9</v>
       </c>
       <c r="AY181">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ181">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA181">
         <v>4</v>
@@ -38962,10 +38962,10 @@
         <v>6</v>
       </c>
       <c r="AY182">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ182">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA182">
         <v>6</v>
@@ -39168,7 +39168,7 @@
         <v>6</v>
       </c>
       <c r="AY183">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ183">
         <v>12</v>
@@ -39374,10 +39374,10 @@
         <v>13</v>
       </c>
       <c r="AY184">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ184">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BA184">
         <v>3</v>
@@ -39580,10 +39580,10 @@
         <v>8</v>
       </c>
       <c r="AY185">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AZ185">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA185">
         <v>10</v>
@@ -39789,7 +39789,7 @@
         <v>12</v>
       </c>
       <c r="AZ186">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA186">
         <v>2</v>
@@ -39995,7 +39995,7 @@
         <v>9</v>
       </c>
       <c r="AZ187">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA187">
         <v>1</v>
@@ -40198,10 +40198,10 @@
         <v>3</v>
       </c>
       <c r="AY188">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AZ188">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA188">
         <v>9</v>
@@ -40407,7 +40407,7 @@
         <v>9</v>
       </c>
       <c r="AZ189">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA189">
         <v>5</v>
@@ -40610,10 +40610,10 @@
         <v>9</v>
       </c>
       <c r="AY190">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ190">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA190">
         <v>5</v>
@@ -40816,7 +40816,7 @@
         <v>4</v>
       </c>
       <c r="AY191">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ191">
         <v>9</v>
@@ -41228,10 +41228,10 @@
         <v>6</v>
       </c>
       <c r="AY193">
+        <v>9</v>
+      </c>
+      <c r="AZ193">
         <v>11</v>
-      </c>
-      <c r="AZ193">
-        <v>13</v>
       </c>
       <c r="BA193">
         <v>4</v>
@@ -41437,7 +41437,7 @@
         <v>6</v>
       </c>
       <c r="AZ194">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA194">
         <v>3</v>
@@ -41640,10 +41640,10 @@
         <v>8</v>
       </c>
       <c r="AY195">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="AZ195">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA195">
         <v>8</v>
@@ -41846,7 +41846,7 @@
         <v>2</v>
       </c>
       <c r="AY196">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ196">
         <v>5</v>
@@ -42058,13 +42058,13 @@
         <v>-1</v>
       </c>
       <c r="BA197">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BB197">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BC197">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="BD197">
         <v>1.5</v>
@@ -42258,10 +42258,10 @@
         <v>15</v>
       </c>
       <c r="AY198">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ198">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA198">
         <v>2</v>
@@ -42464,10 +42464,10 @@
         <v>11</v>
       </c>
       <c r="AY199">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ199">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA199">
         <v>3</v>
@@ -42670,10 +42670,10 @@
         <v>11</v>
       </c>
       <c r="AY200">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ200">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA200">
         <v>8</v>
@@ -42876,10 +42876,10 @@
         <v>6</v>
       </c>
       <c r="AY201">
+        <v>12</v>
+      </c>
+      <c r="AZ201">
         <v>13</v>
-      </c>
-      <c r="AZ201">
-        <v>15</v>
       </c>
       <c r="BA201">
         <v>1</v>
@@ -43082,7 +43082,7 @@
         <v>3</v>
       </c>
       <c r="AY202">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ202">
         <v>5</v>
@@ -43288,10 +43288,10 @@
         <v>9</v>
       </c>
       <c r="AY203">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ203">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA203">
         <v>2</v>
@@ -43494,10 +43494,10 @@
         <v>13</v>
       </c>
       <c r="AY204">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ204">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA204">
         <v>3</v>
@@ -43700,10 +43700,10 @@
         <v>6</v>
       </c>
       <c r="AY205">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ205">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA205">
         <v>5</v>
@@ -44112,10 +44112,10 @@
         <v>4</v>
       </c>
       <c r="AY207">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AZ207">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA207">
         <v>10</v>
@@ -44318,10 +44318,10 @@
         <v>4</v>
       </c>
       <c r="AY208">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ208">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA208">
         <v>9</v>
@@ -44524,10 +44524,10 @@
         <v>14</v>
       </c>
       <c r="AY209">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ209">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BA209">
         <v>7</v>
@@ -44730,7 +44730,7 @@
         <v>4</v>
       </c>
       <c r="AY210">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ210">
         <v>8</v>
@@ -44936,10 +44936,10 @@
         <v>5</v>
       </c>
       <c r="AY211">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ211">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA211">
         <v>5</v>
@@ -45142,7 +45142,7 @@
         <v>5</v>
       </c>
       <c r="AY212">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ212">
         <v>10</v>
@@ -45348,10 +45348,10 @@
         <v>6</v>
       </c>
       <c r="AY213">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AZ213">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA213">
         <v>13</v>
@@ -45554,10 +45554,10 @@
         <v>13</v>
       </c>
       <c r="AY214">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ214">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA214">
         <v>7</v>
@@ -45763,7 +45763,7 @@
         <v>7</v>
       </c>
       <c r="AZ215">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA215">
         <v>2</v>
@@ -45966,7 +45966,7 @@
         <v>4</v>
       </c>
       <c r="AY216">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ216">
         <v>10</v>
@@ -46384,13 +46384,13 @@
         <v>-1</v>
       </c>
       <c r="BA218">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="BB218">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BC218">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="BD218">
         <v>1.63</v>
@@ -46590,13 +46590,13 @@
         <v>-1</v>
       </c>
       <c r="BA219">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BB219">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BC219">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BD219">
         <v>2.35</v>
@@ -46796,13 +46796,13 @@
         <v>-1</v>
       </c>
       <c r="BA220">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BB220">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BC220">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BD220">
         <v>2.4</v>
@@ -47002,13 +47002,13 @@
         <v>-1</v>
       </c>
       <c r="BA221">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="BB221">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BC221">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="BD221">
         <v>1.38</v>
@@ -47208,13 +47208,13 @@
         <v>-1</v>
       </c>
       <c r="BA222">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BB222">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BC222">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BD222">
         <v>1.85</v>
@@ -47414,13 +47414,13 @@
         <v>-1</v>
       </c>
       <c r="BA223">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BB223">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BC223">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="BD223">
         <v>1.5</v>
@@ -47614,10 +47614,10 @@
         <v>2</v>
       </c>
       <c r="AY224">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ224">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA224">
         <v>3</v>
@@ -47820,10 +47820,10 @@
         <v>8</v>
       </c>
       <c r="AY225">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ225">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA225">
         <v>3</v>
@@ -48026,10 +48026,10 @@
         <v>9</v>
       </c>
       <c r="AY226">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AZ226">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA226">
         <v>10</v>
@@ -48232,10 +48232,10 @@
         <v>14</v>
       </c>
       <c r="AY227">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ227">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BA227">
         <v>5</v>
@@ -48438,10 +48438,10 @@
         <v>5</v>
       </c>
       <c r="AY228">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ228">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA228">
         <v>9</v>
@@ -48644,7 +48644,7 @@
         <v>3</v>
       </c>
       <c r="AY229">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AZ229">
         <v>3</v>
@@ -48850,10 +48850,10 @@
         <v>11</v>
       </c>
       <c r="AY230">
+        <v>12</v>
+      </c>
+      <c r="AZ230">
         <v>17</v>
-      </c>
-      <c r="AZ230">
-        <v>22</v>
       </c>
       <c r="BA230">
         <v>5</v>
@@ -49056,10 +49056,10 @@
         <v>7</v>
       </c>
       <c r="AY231">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ231">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA231">
         <v>8</v>
@@ -49262,10 +49262,10 @@
         <v>9</v>
       </c>
       <c r="AY232">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ232">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA232">
         <v>7</v>
@@ -49468,10 +49468,10 @@
         <v>8</v>
       </c>
       <c r="AY233">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ233">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA233">
         <v>6</v>
@@ -49674,10 +49674,10 @@
         <v>7</v>
       </c>
       <c r="AY234">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ234">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA234">
         <v>10</v>
@@ -49883,7 +49883,7 @@
         <v>13</v>
       </c>
       <c r="AZ235">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA235">
         <v>3</v>
@@ -50086,10 +50086,10 @@
         <v>1</v>
       </c>
       <c r="AY236">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ236">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA236">
         <v>5</v>
@@ -50295,7 +50295,7 @@
         <v>11</v>
       </c>
       <c r="AZ237">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA237">
         <v>3</v>
@@ -50498,10 +50498,10 @@
         <v>7</v>
       </c>
       <c r="AY238">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="AZ238">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA238">
         <v>3</v>
@@ -50704,7 +50704,7 @@
         <v>8</v>
       </c>
       <c r="AY239">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ239">
         <v>10</v>
@@ -50910,10 +50910,10 @@
         <v>5</v>
       </c>
       <c r="AY240">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="AZ240">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA240">
         <v>13</v>
@@ -51116,10 +51116,10 @@
         <v>15</v>
       </c>
       <c r="AY241">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ241">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BA241">
         <v>3</v>
@@ -51322,7 +51322,7 @@
         <v>5</v>
       </c>
       <c r="AY242">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ242">
         <v>14</v>
@@ -51528,7 +51528,7 @@
         <v>10</v>
       </c>
       <c r="AY243">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ243">
         <v>15</v>
@@ -51734,10 +51734,10 @@
         <v>5</v>
       </c>
       <c r="AY244">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ244">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA244">
         <v>5</v>
@@ -51940,10 +51940,10 @@
         <v>6</v>
       </c>
       <c r="AY245">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ245">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA245">
         <v>3</v>
@@ -52146,7 +52146,7 @@
         <v>3</v>
       </c>
       <c r="AY246">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ246">
         <v>9</v>
@@ -52155,10 +52155,10 @@
         <v>3</v>
       </c>
       <c r="BB246">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC246">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD246">
         <v>1.36</v>
@@ -52352,10 +52352,10 @@
         <v>6</v>
       </c>
       <c r="AY247">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ247">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA247">
         <v>4</v>
@@ -52558,10 +52558,10 @@
         <v>4</v>
       </c>
       <c r="AY248">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ248">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA248">
         <v>13</v>
@@ -52764,7 +52764,7 @@
         <v>2</v>
       </c>
       <c r="AY249">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ249">
         <v>6</v>
@@ -52970,7 +52970,7 @@
         <v>8</v>
       </c>
       <c r="AY250">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ250">
         <v>10</v>
@@ -53176,10 +53176,10 @@
         <v>2</v>
       </c>
       <c r="AY251">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ251">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA251">
         <v>9</v>
@@ -53382,10 +53382,10 @@
         <v>8</v>
       </c>
       <c r="AY252">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AZ252">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA252">
         <v>6</v>
@@ -53588,7 +53588,7 @@
         <v>5</v>
       </c>
       <c r="AY253">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ253">
         <v>15</v>
@@ -53794,10 +53794,10 @@
         <v>16</v>
       </c>
       <c r="AY254">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ254">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BA254">
         <v>2</v>
@@ -54000,10 +54000,10 @@
         <v>12</v>
       </c>
       <c r="AY255">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ255">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA255">
         <v>4</v>
@@ -54206,10 +54206,10 @@
         <v>7</v>
       </c>
       <c r="AY256">
+        <v>10</v>
+      </c>
+      <c r="AZ256">
         <v>12</v>
-      </c>
-      <c r="AZ256">
-        <v>16</v>
       </c>
       <c r="BA256">
         <v>5</v>
@@ -54412,10 +54412,10 @@
         <v>14</v>
       </c>
       <c r="AY257">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ257">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA257">
         <v>4</v>
@@ -54618,10 +54618,10 @@
         <v>7</v>
       </c>
       <c r="AY258">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ258">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA258">
         <v>8</v>
@@ -54824,10 +54824,10 @@
         <v>6</v>
       </c>
       <c r="AY259">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ259">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA259">
         <v>2</v>
@@ -55030,7 +55030,7 @@
         <v>6</v>
       </c>
       <c r="AY260">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ260">
         <v>8</v>
@@ -55236,7 +55236,7 @@
         <v>0</v>
       </c>
       <c r="AY261">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ261">
         <v>3</v>
@@ -55442,7 +55442,7 @@
         <v>1</v>
       </c>
       <c r="AY262">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ262">
         <v>5</v>
@@ -55648,7 +55648,7 @@
         <v>6</v>
       </c>
       <c r="AY263">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ263">
         <v>12</v>
@@ -55854,10 +55854,10 @@
         <v>12</v>
       </c>
       <c r="AY264">
+        <v>15</v>
+      </c>
+      <c r="AZ264">
         <v>16</v>
-      </c>
-      <c r="AZ264">
-        <v>17</v>
       </c>
       <c r="BA264">
         <v>6</v>
@@ -56060,7 +56060,7 @@
         <v>4</v>
       </c>
       <c r="AY265">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ265">
         <v>7</v>
@@ -56266,10 +56266,10 @@
         <v>9</v>
       </c>
       <c r="AY266">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ266">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA266">
         <v>5</v>
@@ -56472,7 +56472,7 @@
         <v>5</v>
       </c>
       <c r="AY267">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="AZ267">
         <v>9</v>
@@ -56678,10 +56678,10 @@
         <v>7</v>
       </c>
       <c r="AY268">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ268">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA268">
         <v>8</v>
@@ -57090,10 +57090,10 @@
         <v>8</v>
       </c>
       <c r="AY270">
+        <v>9</v>
+      </c>
+      <c r="AZ270">
         <v>12</v>
-      </c>
-      <c r="AZ270">
-        <v>15</v>
       </c>
       <c r="BA270">
         <v>7</v>
@@ -57296,10 +57296,10 @@
         <v>8</v>
       </c>
       <c r="AY271">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ271">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA271">
         <v>7</v>
@@ -57505,7 +57505,7 @@
         <v>13</v>
       </c>
       <c r="AZ272">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA272">
         <v>6</v>
@@ -57708,10 +57708,10 @@
         <v>2</v>
       </c>
       <c r="AY273">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ273">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA273">
         <v>3</v>
@@ -57914,10 +57914,10 @@
         <v>4</v>
       </c>
       <c r="AY274">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ274">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA274">
         <v>7</v>
@@ -58120,10 +58120,10 @@
         <v>12</v>
       </c>
       <c r="AY275">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ275">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA275">
         <v>6</v>
@@ -58532,10 +58532,10 @@
         <v>7</v>
       </c>
       <c r="AY277">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ277">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA277">
         <v>10</v>
@@ -58738,10 +58738,10 @@
         <v>18</v>
       </c>
       <c r="AY278">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ278">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BA278">
         <v>2</v>
@@ -58944,10 +58944,10 @@
         <v>10</v>
       </c>
       <c r="AY279">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ279">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA279">
         <v>2</v>
@@ -59150,10 +59150,10 @@
         <v>6</v>
       </c>
       <c r="AY280">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ280">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA280">
         <v>9</v>
@@ -59359,7 +59359,7 @@
         <v>12</v>
       </c>
       <c r="AZ281">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA281">
         <v>8</v>
@@ -59562,10 +59562,10 @@
         <v>15</v>
       </c>
       <c r="AY282">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ282">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BA282">
         <v>6</v>
@@ -59768,10 +59768,10 @@
         <v>6</v>
       </c>
       <c r="AY283">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ283">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA283">
         <v>5</v>
@@ -59974,7 +59974,7 @@
         <v>4</v>
       </c>
       <c r="AY284">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ284">
         <v>13</v>
@@ -60180,7 +60180,7 @@
         <v>8</v>
       </c>
       <c r="AY285">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ285">
         <v>10</v>
@@ -60386,10 +60386,10 @@
         <v>11</v>
       </c>
       <c r="AY286">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ286">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA286">
         <v>4</v>
@@ -60592,10 +60592,10 @@
         <v>7</v>
       </c>
       <c r="AY287">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AZ287">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA287">
         <v>4</v>
@@ -60798,10 +60798,10 @@
         <v>9</v>
       </c>
       <c r="AY288">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ288">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA288">
         <v>4</v>
@@ -61004,10 +61004,10 @@
         <v>7</v>
       </c>
       <c r="AY289">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ289">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA289">
         <v>6</v>
@@ -61210,10 +61210,10 @@
         <v>5</v>
       </c>
       <c r="AY290">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ290">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA290">
         <v>1</v>
@@ -61416,7 +61416,7 @@
         <v>5</v>
       </c>
       <c r="AY291">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ291">
         <v>9</v>
@@ -61622,7 +61622,7 @@
         <v>2</v>
       </c>
       <c r="AY292">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AZ292">
         <v>6</v>
@@ -61828,10 +61828,10 @@
         <v>5</v>
       </c>
       <c r="AY293">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ293">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA293">
         <v>3</v>
@@ -62034,10 +62034,10 @@
         <v>6</v>
       </c>
       <c r="AY294">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ294">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA294">
         <v>6</v>
@@ -62446,19 +62446,19 @@
         <v>7</v>
       </c>
       <c r="AY296">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ296">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA296">
         <v>7</v>
       </c>
       <c r="BB296">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC296">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD296">
         <v>1.9</v>
@@ -62652,10 +62652,10 @@
         <v>8</v>
       </c>
       <c r="AY297">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ297">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA297">
         <v>2</v>
@@ -62858,10 +62858,10 @@
         <v>10</v>
       </c>
       <c r="AY298">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ298">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA298">
         <v>2</v>
@@ -63064,10 +63064,10 @@
         <v>8</v>
       </c>
       <c r="AY299">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ299">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA299">
         <v>6</v>
@@ -63270,10 +63270,10 @@
         <v>6</v>
       </c>
       <c r="AY300">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ300">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA300">
         <v>3</v>
@@ -63476,10 +63476,10 @@
         <v>12</v>
       </c>
       <c r="AY301">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ301">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="BA301">
         <v>4</v>
@@ -63682,10 +63682,10 @@
         <v>9</v>
       </c>
       <c r="AY302">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ302">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA302">
         <v>6</v>
@@ -64094,10 +64094,10 @@
         <v>10</v>
       </c>
       <c r="AY304">
+        <v>12</v>
+      </c>
+      <c r="AZ304">
         <v>16</v>
-      </c>
-      <c r="AZ304">
-        <v>18</v>
       </c>
       <c r="BA304">
         <v>4</v>
@@ -64300,10 +64300,10 @@
         <v>9</v>
       </c>
       <c r="AY305">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AZ305">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA305">
         <v>4</v>
@@ -64506,10 +64506,10 @@
         <v>8</v>
       </c>
       <c r="AY306">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ306">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA306">
         <v>6</v>
@@ -64712,10 +64712,10 @@
         <v>9</v>
       </c>
       <c r="AY307">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ307">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA307">
         <v>8</v>
@@ -64918,10 +64918,10 @@
         <v>8</v>
       </c>
       <c r="AY308">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ308">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA308">
         <v>6</v>
@@ -65127,7 +65127,7 @@
         <v>4</v>
       </c>
       <c r="AZ309">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BA309">
         <v>4</v>
@@ -65330,7 +65330,7 @@
         <v>7</v>
       </c>
       <c r="AY310">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ310">
         <v>15</v>
@@ -65536,10 +65536,10 @@
         <v>1</v>
       </c>
       <c r="AY311">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ311">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA311">
         <v>5</v>
@@ -65742,10 +65742,10 @@
         <v>3</v>
       </c>
       <c r="AY312">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ312">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA312">
         <v>2</v>
@@ -65948,10 +65948,10 @@
         <v>9</v>
       </c>
       <c r="AY313">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ313">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA313">
         <v>3</v>
@@ -66154,7 +66154,7 @@
         <v>6</v>
       </c>
       <c r="AY314">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AZ314">
         <v>12</v>
@@ -66360,10 +66360,10 @@
         <v>13</v>
       </c>
       <c r="AY315">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ315">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA315">
         <v>9</v>
@@ -66566,10 +66566,10 @@
         <v>2</v>
       </c>
       <c r="AY316">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ316">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA316">
         <v>4</v>
